--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fastest" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Segments'!$A$11:$U$312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Diversified'!$A$11:$U$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Concentrated'!$A$11:$U$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Global'!$A$11:$U$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fastest'!$A$11:$U$72</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -26912,6 +26918,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:U312"/>
   <mergeCells count="2">
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="A2:U2"/>
@@ -32246,6 +32253,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:U72"/>
   <mergeCells count="2">
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="A2:U2"/>
@@ -37620,6 +37628,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:U72"/>
   <mergeCells count="2">
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="A2:U2"/>
@@ -43012,6 +43021,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:U72"/>
   <mergeCells count="2">
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="A2:U2"/>
@@ -48366,6 +48376,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A11:U72"/>
   <mergeCells count="2">
     <mergeCell ref="A10:U10"/>
     <mergeCell ref="A2:U2"/>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:G20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,6 +552,8 @@
     <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -574,6 +576,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -581,8 +584,9 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>UNIVERSE STATS</t>
         </is>
@@ -692,8 +696,9 @@
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TABS IN THIS WORKBOOK</t>
         </is>
@@ -814,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U312"/>
+  <dimension ref="A1:U312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -840,6 +845,7 @@
     <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -870,6 +876,7 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -974,8 +981,9 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY ETA</t>
         </is>
@@ -1185,16 +1193,8 @@
       <c r="S13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U13" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T13" s="17" t="n"/>
+      <c r="U13" s="15" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -1270,11 +1270,7 @@
       <c r="S14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T14" s="17" t="n"/>
       <c r="U14" s="15" t="inlineStr">
         <is>
           <t>American Southern +39%</t>
@@ -1431,29 +1427,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q16" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R16" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="17" t="n"/>
       <c r="S16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U16" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T16" s="17" t="n"/>
+      <c r="U16" s="15" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="13" t="n">
@@ -1518,29 +1498,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q17" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R17" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="17" t="n"/>
       <c r="S17" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U17" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T17" s="17" t="n"/>
+      <c r="U17" s="15" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="13" t="n">
@@ -1609,29 +1573,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q18" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R18" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="17" t="n"/>
       <c r="S18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U18" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T18" s="17" t="n"/>
+      <c r="U18" s="15" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="13" t="n">
@@ -1700,29 +1648,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q19" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q19" s="15" t="n"/>
+      <c r="R19" s="17" t="n"/>
       <c r="S19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U19" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T19" s="17" t="n"/>
+      <c r="U19" s="15" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n">
@@ -1791,29 +1723,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q20" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R20" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="17" t="n"/>
       <c r="S20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U20" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T20" s="17" t="n"/>
+      <c r="U20" s="15" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="13" t="n">
@@ -1882,29 +1798,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q21" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="17" t="n"/>
       <c r="S21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U21" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T21" s="17" t="n"/>
+      <c r="U21" s="15" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="13" t="n">
@@ -2056,29 +1956,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q23" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q23" s="15" t="n"/>
+      <c r="R23" s="17" t="n"/>
       <c r="S23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U23" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T23" s="17" t="n"/>
+      <c r="U23" s="15" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="13" t="n">
@@ -2143,16 +2027,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q24" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q24" s="15" t="n"/>
+      <c r="R24" s="17" t="n"/>
       <c r="S24" s="18" t="n">
         <v>2</v>
       </c>
@@ -2161,11 +2037,7 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="U24" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U24" s="15" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="13" t="n">
@@ -2396,16 +2268,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q27" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q27" s="15" t="n"/>
+      <c r="R27" s="17" t="n"/>
       <c r="S27" s="18" t="n">
         <v>5</v>
       </c>
@@ -2414,11 +2278,7 @@
           <t>US 85%; CN 8%; Other Countries 2%</t>
         </is>
       </c>
-      <c r="U27" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U27" s="15" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="13" t="n">
@@ -2483,29 +2343,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q28" s="15" t="n"/>
+      <c r="R28" s="17" t="n"/>
       <c r="S28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T28" s="17" t="n"/>
+      <c r="U28" s="15" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -2581,11 +2425,7 @@
       <c r="S29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T29" s="17" t="n"/>
       <c r="U29" s="15" t="inlineStr">
         <is>
           <t>Reportable +288%</t>
@@ -2611,11 +2451,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E30" s="17" t="n"/>
       <c r="F30" s="18" t="n">
         <v>2186936064</v>
       </c>
@@ -2655,29 +2491,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q30" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q30" s="15" t="n"/>
+      <c r="R30" s="17" t="n"/>
       <c r="S30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U30" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T30" s="17" t="n"/>
+      <c r="U30" s="15" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="13" t="n">
@@ -2742,29 +2562,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q31" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q31" s="15" t="n"/>
+      <c r="R31" s="17" t="n"/>
       <c r="S31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U31" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T31" s="17" t="n"/>
+      <c r="U31" s="15" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="13" t="n">
@@ -2829,16 +2633,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q32" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R32" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q32" s="15" t="n"/>
+      <c r="R32" s="17" t="n"/>
       <c r="S32" s="18" t="n">
         <v>2</v>
       </c>
@@ -2847,11 +2643,7 @@
           <t>US 95%; Non Us 5%</t>
         </is>
       </c>
-      <c r="U32" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U32" s="15" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="13" t="n">
@@ -2920,29 +2712,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q33" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R33" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q33" s="15" t="n"/>
+      <c r="R33" s="17" t="n"/>
       <c r="S33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T33" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U33" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T33" s="17" t="n"/>
+      <c r="U33" s="15" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="13" t="n">
@@ -3009,29 +2785,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q34" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R34" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q34" s="15" t="n"/>
+      <c r="R34" s="17" t="n"/>
       <c r="S34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T34" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U34" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T34" s="17" t="n"/>
+      <c r="U34" s="15" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="13" t="n">
@@ -3185,29 +2945,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q36" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="17" t="n"/>
       <c r="S36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U36" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T36" s="17" t="n"/>
+      <c r="U36" s="15" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="13" t="n">
@@ -3270,16 +3014,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q37" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R37" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q37" s="15" t="n"/>
+      <c r="R37" s="17" t="n"/>
       <c r="S37" s="18" t="n">
         <v>6</v>
       </c>
@@ -3288,11 +3024,7 @@
           <t>North America 24%; US 24%; EMEA 19%</t>
         </is>
       </c>
-      <c r="U37" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U37" s="15" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -3444,29 +3176,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q39" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R39" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q39" s="15" t="n"/>
+      <c r="R39" s="17" t="n"/>
       <c r="S39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U39" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T39" s="17" t="n"/>
+      <c r="U39" s="15" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -3540,11 +3256,7 @@
       <c r="S40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T40" s="17" t="n"/>
       <c r="U40" s="15" t="inlineStr">
         <is>
           <t>Genie Retail Energy  +19%</t>
@@ -3697,29 +3409,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q42" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R42" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q42" s="15" t="n"/>
+      <c r="R42" s="17" t="n"/>
       <c r="S42" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U42" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T42" s="17" t="n"/>
+      <c r="U42" s="15" t="n"/>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="13" t="n">
@@ -3882,11 +3578,7 @@
       <c r="S44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T44" s="17" t="n"/>
       <c r="U44" s="15" t="inlineStr">
         <is>
           <t>Commercial Banking +44%</t>
@@ -3960,29 +3652,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q45" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R45" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q45" s="15" t="n"/>
+      <c r="R45" s="17" t="n"/>
       <c r="S45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U45" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T45" s="17" t="n"/>
+      <c r="U45" s="15" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="13" t="n">
@@ -4058,11 +3734,7 @@
       <c r="S46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T46" s="17" t="n"/>
       <c r="U46" s="15" t="inlineStr">
         <is>
           <t>Zedge Marketplace +2%</t>
@@ -4221,29 +3893,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q48" s="15" t="n"/>
+      <c r="R48" s="17" t="n"/>
       <c r="S48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T48" s="17" t="n"/>
+      <c r="U48" s="15" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -4306,16 +3962,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q49" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q49" s="15" t="n"/>
+      <c r="R49" s="17" t="n"/>
       <c r="S49" s="18" t="n">
         <v>2</v>
       </c>
@@ -4324,11 +3972,7 @@
           <t>North America 100%; Asia 0%</t>
         </is>
       </c>
-      <c r="U49" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U49" s="15" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="13" t="n">
@@ -4476,29 +4120,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q51" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q51" s="15" t="n"/>
+      <c r="R51" s="17" t="n"/>
       <c r="S51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U51" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T51" s="17" t="n"/>
+      <c r="U51" s="15" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="13" t="n">
@@ -4567,29 +4195,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q52" s="15" t="n"/>
+      <c r="R52" s="17" t="n"/>
       <c r="S52" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T52" s="17" t="n"/>
+      <c r="U52" s="15" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -4654,29 +4266,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q53" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q53" s="15" t="n"/>
+      <c r="R53" s="17" t="n"/>
       <c r="S53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U53" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T53" s="17" t="n"/>
+      <c r="U53" s="15" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="13" t="n">
@@ -4824,29 +4420,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q55" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R55" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q55" s="15" t="n"/>
+      <c r="R55" s="17" t="n"/>
       <c r="S55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T55" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U55" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T55" s="17" t="n"/>
+      <c r="U55" s="15" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="13" t="n">
@@ -4915,29 +4495,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q56" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R56" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q56" s="15" t="n"/>
+      <c r="R56" s="17" t="n"/>
       <c r="S56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U56" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T56" s="17" t="n"/>
+      <c r="U56" s="15" t="n"/>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="13" t="n">
@@ -5011,11 +4575,7 @@
       <c r="S57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T57" s="17" t="n"/>
       <c r="U57" s="15" t="inlineStr">
         <is>
           <t>Publishing -18%</t>
@@ -5085,29 +4645,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q58" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R58" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q58" s="15" t="n"/>
+      <c r="R58" s="17" t="n"/>
       <c r="S58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U58" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T58" s="17" t="n"/>
+      <c r="U58" s="15" t="n"/>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="13" t="n">
@@ -5264,11 +4808,7 @@
       <c r="S60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T60" s="17" t="n"/>
       <c r="U60" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -5349,11 +4889,7 @@
       <c r="S61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T61" s="17" t="n"/>
       <c r="U61" s="15" t="inlineStr">
         <is>
           <t>Medicare +10%</t>
@@ -5427,29 +4963,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q62" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q62" s="15" t="n"/>
+      <c r="R62" s="17" t="n"/>
       <c r="S62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U62" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T62" s="17" t="n"/>
+      <c r="U62" s="15" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="13" t="n">
@@ -5529,11 +5049,7 @@
       <c r="S63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T63" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T63" s="17" t="n"/>
       <c r="U63" s="15" t="inlineStr">
         <is>
           <t>Banking Operations -74%</t>
@@ -5607,29 +5123,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q64" s="15" t="n"/>
+      <c r="R64" s="17" t="n"/>
       <c r="S64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T64" s="17" t="n"/>
+      <c r="U64" s="15" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n">
@@ -5703,11 +5203,7 @@
       <c r="S65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T65" s="17" t="n"/>
       <c r="U65" s="15" t="inlineStr">
         <is>
           <t>Reportable -5%</t>
@@ -5777,29 +5273,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q66" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q66" s="15" t="n"/>
+      <c r="R66" s="17" t="n"/>
       <c r="S66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U66" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T66" s="17" t="n"/>
+      <c r="U66" s="15" t="n"/>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="13" t="n">
@@ -5868,29 +5348,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q67" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R67" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q67" s="15" t="n"/>
+      <c r="R67" s="17" t="n"/>
       <c r="S67" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U67" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T67" s="17" t="n"/>
+      <c r="U67" s="15" t="n"/>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="13" t="n">
@@ -6044,29 +5508,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q69" s="15" t="n"/>
+      <c r="R69" s="17" t="n"/>
       <c r="S69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T69" s="17" t="n"/>
+      <c r="U69" s="15" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n">
@@ -6214,29 +5662,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q71" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q71" s="15" t="n"/>
+      <c r="R71" s="17" t="n"/>
       <c r="S71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U71" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T71" s="17" t="n"/>
+      <c r="U71" s="15" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="13" t="n">
@@ -6301,16 +5733,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q72" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R72" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q72" s="15" t="n"/>
+      <c r="R72" s="17" t="n"/>
       <c r="S72" s="18" t="n">
         <v>4</v>
       </c>
@@ -6319,11 +5743,7 @@
           <t>US 65%; EMEA 28%; Asia Pacific 6%</t>
         </is>
       </c>
-      <c r="U72" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U72" s="15" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="13" t="n">
@@ -6386,29 +5806,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q73" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R73" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q73" s="15" t="n"/>
+      <c r="R73" s="17" t="n"/>
       <c r="S73" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U73" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T73" s="17" t="n"/>
+      <c r="U73" s="15" t="n"/>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="13" t="n">
@@ -6488,11 +5892,7 @@
       <c r="S74" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T74" s="17" t="n"/>
       <c r="U74" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -6571,11 +5971,7 @@
       <c r="S75" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T75" s="17" t="n"/>
       <c r="U75" s="15" t="inlineStr">
         <is>
           <t>Reportable +22%</t>
@@ -6643,29 +6039,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q76" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R76" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q76" s="15" t="n"/>
+      <c r="R76" s="17" t="n"/>
       <c r="S76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U76" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T76" s="17" t="n"/>
+      <c r="U76" s="15" t="n"/>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="13" t="n">
@@ -6730,29 +6110,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q77" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R77" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q77" s="15" t="n"/>
+      <c r="R77" s="17" t="n"/>
       <c r="S77" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U77" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T77" s="17" t="n"/>
+      <c r="U77" s="15" t="n"/>
     </row>
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="13" t="n">
@@ -6817,16 +6181,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q78" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R78" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q78" s="15" t="n"/>
+      <c r="R78" s="17" t="n"/>
       <c r="S78" s="18" t="n">
         <v>1</v>
       </c>
@@ -6835,11 +6191,7 @@
           <t>Non Us 100%</t>
         </is>
       </c>
-      <c r="U78" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U78" s="15" t="n"/>
     </row>
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="13" t="n">
@@ -6913,11 +6265,7 @@
       <c r="S79" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T79" s="17" t="n"/>
       <c r="U79" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments +15%</t>
@@ -6996,11 +6344,7 @@
       <c r="S80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T80" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T80" s="17" t="n"/>
       <c r="U80" s="15" t="inlineStr">
         <is>
           <t>Reportable +23%</t>
@@ -7166,11 +6510,7 @@
       <c r="S82" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T82" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T82" s="17" t="n"/>
       <c r="U82" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -7244,29 +6584,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q83" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R83" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q83" s="15" t="n"/>
+      <c r="R83" s="17" t="n"/>
       <c r="S83" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T83" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U83" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T83" s="17" t="n"/>
+      <c r="U83" s="15" t="n"/>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="13" t="n">
@@ -7331,29 +6655,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q84" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R84" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q84" s="15" t="n"/>
+      <c r="R84" s="17" t="n"/>
       <c r="S84" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U84" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T84" s="17" t="n"/>
+      <c r="U84" s="15" t="n"/>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="13" t="n">
@@ -7590,29 +6898,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q87" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R87" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q87" s="15" t="n"/>
+      <c r="R87" s="17" t="n"/>
       <c r="S87" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U87" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T87" s="17" t="n"/>
+      <c r="U87" s="15" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="13" t="n">
@@ -7675,16 +6967,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q88" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R88" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q88" s="15" t="n"/>
+      <c r="R88" s="17" t="n"/>
       <c r="S88" s="18" t="n">
         <v>2</v>
       </c>
@@ -7693,11 +6977,7 @@
           <t>US 99%; Non Us 1%</t>
         </is>
       </c>
-      <c r="U88" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U88" s="15" t="n"/>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -7860,11 +7140,7 @@
       <c r="S90" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T90" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T90" s="17" t="n"/>
       <c r="U90" s="15" t="inlineStr">
         <is>
           <t>Reportable +4%</t>
@@ -7932,29 +7208,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q91" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R91" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q91" s="15" t="n"/>
+      <c r="R91" s="17" t="n"/>
       <c r="S91" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T91" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U91" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T91" s="17" t="n"/>
+      <c r="U91" s="15" t="n"/>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -8019,16 +7279,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q92" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R92" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q92" s="15" t="n"/>
+      <c r="R92" s="17" t="n"/>
       <c r="S92" s="18" t="n">
         <v>4</v>
       </c>
@@ -8037,11 +7289,7 @@
           <t>US 71%; GB 12%; Other International 11%</t>
         </is>
       </c>
-      <c r="U92" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U92" s="15" t="n"/>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="13" t="n">
@@ -8200,11 +7448,7 @@
       <c r="S94" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T94" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T94" s="17" t="n"/>
       <c r="U94" s="15" t="inlineStr">
         <is>
           <t>Local Distribution +26%</t>
@@ -8274,16 +7518,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q95" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R95" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q95" s="15" t="n"/>
+      <c r="R95" s="17" t="n"/>
       <c r="S95" s="18" t="n">
         <v>2</v>
       </c>
@@ -8292,11 +7528,7 @@
           <t>US 96%; Non Us 4%</t>
         </is>
       </c>
-      <c r="U95" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U95" s="15" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -8359,29 +7591,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q96" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R96" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q96" s="15" t="n"/>
+      <c r="R96" s="17" t="n"/>
       <c r="S96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U96" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T96" s="17" t="n"/>
+      <c r="U96" s="15" t="n"/>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="13" t="n">
@@ -8455,11 +7671,7 @@
       <c r="S97" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T97" s="17" t="n"/>
       <c r="U97" s="15" t="inlineStr">
         <is>
           <t>Optex Systems OPX Ri +31%</t>
@@ -8538,11 +7750,7 @@
       <c r="S98" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T98" s="17" t="n"/>
       <c r="U98" s="15" t="inlineStr">
         <is>
           <t>Optavia -36%</t>
@@ -8704,11 +7912,7 @@
       <c r="S100" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T100" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T100" s="17" t="n"/>
       <c r="U100" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -8776,29 +7980,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q101" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R101" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q101" s="15" t="n"/>
+      <c r="R101" s="17" t="n"/>
       <c r="S101" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U101" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T101" s="17" t="n"/>
+      <c r="U101" s="15" t="n"/>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="13" t="n">
@@ -8952,29 +8140,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q103" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R103" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q103" s="15" t="n"/>
+      <c r="R103" s="17" t="n"/>
       <c r="S103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U103" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T103" s="17" t="n"/>
+      <c r="U103" s="15" t="n"/>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="13" t="n">
@@ -9045,29 +8217,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q104" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R104" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q104" s="15" t="n"/>
+      <c r="R104" s="17" t="n"/>
       <c r="S104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T104" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U104" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T104" s="17" t="n"/>
+      <c r="U104" s="15" t="n"/>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="13" t="n">
@@ -9132,29 +8288,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q105" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R105" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q105" s="15" t="n"/>
+      <c r="R105" s="17" t="n"/>
       <c r="S105" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U105" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T105" s="17" t="n"/>
+      <c r="U105" s="15" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="13" t="n">
@@ -9219,29 +8359,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q106" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R106" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q106" s="15" t="n"/>
+      <c r="R106" s="17" t="n"/>
       <c r="S106" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U106" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T106" s="17" t="n"/>
+      <c r="U106" s="15" t="n"/>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="13" t="n">
@@ -9306,16 +8430,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q107" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R107" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q107" s="15" t="n"/>
+      <c r="R107" s="17" t="n"/>
       <c r="S107" s="18" t="n">
         <v>2</v>
       </c>
@@ -9324,11 +8440,7 @@
           <t>US 96%; Non Us 4%</t>
         </is>
       </c>
-      <c r="U107" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U107" s="15" t="n"/>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="13" t="n">
@@ -9478,16 +8590,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q109" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R109" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q109" s="15" t="n"/>
+      <c r="R109" s="17" t="n"/>
       <c r="S109" s="18" t="n">
         <v>2</v>
       </c>
@@ -9496,11 +8600,7 @@
           <t>US 58%; Non Us 42%</t>
         </is>
       </c>
-      <c r="U109" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U109" s="15" t="n"/>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="13" t="n">
@@ -9652,29 +8752,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q111" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R111" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q111" s="15" t="n"/>
+      <c r="R111" s="17" t="n"/>
       <c r="S111" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T111" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U111" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T111" s="17" t="n"/>
+      <c r="U111" s="15" t="n"/>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="13" t="n">
@@ -9739,29 +8823,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q112" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R112" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q112" s="15" t="n"/>
+      <c r="R112" s="17" t="n"/>
       <c r="S112" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U112" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T112" s="17" t="n"/>
+      <c r="U112" s="15" t="n"/>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="13" t="n">
@@ -9837,11 +8905,7 @@
       <c r="S113" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T113" s="17" t="n"/>
       <c r="U113" s="15" t="inlineStr">
         <is>
           <t>Reportable -100%</t>
@@ -9915,29 +8979,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q114" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R114" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q114" s="15" t="n"/>
+      <c r="R114" s="17" t="n"/>
       <c r="S114" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U114" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T114" s="17" t="n"/>
+      <c r="U114" s="15" t="n"/>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n">
@@ -10000,29 +9048,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q115" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R115" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q115" s="15" t="n"/>
+      <c r="R115" s="17" t="n"/>
       <c r="S115" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U115" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T115" s="17" t="n"/>
+      <c r="U115" s="15" t="n"/>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="13" t="n">
@@ -10085,29 +9117,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q116" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R116" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q116" s="15" t="n"/>
+      <c r="R116" s="17" t="n"/>
       <c r="S116" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U116" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T116" s="17" t="n"/>
+      <c r="U116" s="15" t="n"/>
     </row>
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="13" t="n">
@@ -10170,29 +9186,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q117" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R117" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q117" s="15" t="n"/>
+      <c r="R117" s="17" t="n"/>
       <c r="S117" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U117" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T117" s="17" t="n"/>
+      <c r="U117" s="15" t="n"/>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="13" t="n">
@@ -10261,29 +9261,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q118" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R118" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q118" s="15" t="n"/>
+      <c r="R118" s="17" t="n"/>
       <c r="S118" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T118" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U118" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T118" s="17" t="n"/>
+      <c r="U118" s="15" t="n"/>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="13" t="n">
@@ -10346,29 +9330,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q119" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R119" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q119" s="15" t="n"/>
+      <c r="R119" s="17" t="n"/>
       <c r="S119" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T119" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U119" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T119" s="17" t="n"/>
+      <c r="U119" s="15" t="n"/>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="13" t="n">
@@ -10442,11 +9410,7 @@
       <c r="S120" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T120" s="17" t="n"/>
       <c r="U120" s="15" t="inlineStr">
         <is>
           <t>Hawaii Energy Connec +30%</t>
@@ -10514,16 +9478,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q121" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R121" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q121" s="15" t="n"/>
+      <c r="R121" s="17" t="n"/>
       <c r="S121" s="18" t="n">
         <v>6</v>
       </c>
@@ -10532,11 +9488,7 @@
           <t>North America 30%; US 27%; EMEA 25%</t>
         </is>
       </c>
-      <c r="U121" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U121" s="15" t="n"/>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="13" t="n">
@@ -10616,11 +9568,7 @@
       <c r="S122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T122" s="17" t="n"/>
       <c r="U122" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +15%</t>
@@ -10690,29 +9638,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q123" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R123" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q123" s="15" t="n"/>
+      <c r="R123" s="17" t="n"/>
       <c r="S123" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U123" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T123" s="17" t="n"/>
+      <c r="U123" s="15" t="n"/>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="13" t="n">
@@ -10777,29 +9709,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q124" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R124" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q124" s="15" t="n"/>
+      <c r="R124" s="17" t="n"/>
       <c r="S124" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U124" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T124" s="17" t="n"/>
+      <c r="U124" s="15" t="n"/>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="13" t="n">
@@ -10951,29 +9867,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q126" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R126" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q126" s="15" t="n"/>
+      <c r="R126" s="17" t="n"/>
       <c r="S126" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T126" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U126" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T126" s="17" t="n"/>
+      <c r="U126" s="15" t="n"/>
     </row>
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="13" t="n">
@@ -11038,29 +9938,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q127" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R127" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q127" s="15" t="n"/>
+      <c r="R127" s="17" t="n"/>
       <c r="S127" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U127" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T127" s="17" t="n"/>
+      <c r="U127" s="15" t="n"/>
     </row>
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="13" t="n">
@@ -11225,11 +10109,7 @@
       <c r="S129" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T129" s="17" t="n"/>
       <c r="U129" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -11299,29 +10179,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q130" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R130" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q130" s="15" t="n"/>
+      <c r="R130" s="17" t="n"/>
       <c r="S130" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U130" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T130" s="17" t="n"/>
+      <c r="U130" s="15" t="n"/>
     </row>
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="13" t="n">
@@ -11395,11 +10259,7 @@
       <c r="S131" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T131" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T131" s="17" t="n"/>
       <c r="U131" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +64%</t>
@@ -11478,11 +10338,7 @@
       <c r="S132" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T132" s="17" t="n"/>
       <c r="U132" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments  +1%</t>
@@ -11563,11 +10419,7 @@
       <c r="S133" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T133" s="17" t="n"/>
       <c r="U133" s="15" t="inlineStr">
         <is>
           <t>Reportable -77%</t>
@@ -11646,11 +10498,7 @@
       <c r="S134" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T134" s="17" t="n"/>
       <c r="U134" s="15" t="inlineStr">
         <is>
           <t>Pandora And Off Plat -0%</t>
@@ -11720,16 +10568,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q135" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R135" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q135" s="15" t="n"/>
+      <c r="R135" s="17" t="n"/>
       <c r="S135" s="18" t="n">
         <v>9</v>
       </c>
@@ -11738,11 +10578,7 @@
           <t>Europe 26%; Americas 21%; US 20%</t>
         </is>
       </c>
-      <c r="U135" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U135" s="15" t="n"/>
     </row>
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="13" t="n">
@@ -11816,11 +10652,7 @@
       <c r="S136" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T136" s="17" t="n"/>
       <c r="U136" s="15" t="inlineStr">
         <is>
           <t>Operating +23%</t>
@@ -11888,16 +10720,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q137" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R137" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q137" s="15" t="n"/>
+      <c r="R137" s="17" t="n"/>
       <c r="S137" s="18" t="n">
         <v>2</v>
       </c>
@@ -11906,11 +10730,7 @@
           <t>US 97%; Non Us 3%</t>
         </is>
       </c>
-      <c r="U137" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U137" s="15" t="n"/>
     </row>
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="13" t="n">
@@ -11979,29 +10799,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q138" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R138" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q138" s="15" t="n"/>
+      <c r="R138" s="17" t="n"/>
       <c r="S138" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U138" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T138" s="17" t="n"/>
+      <c r="U138" s="15" t="n"/>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="13" t="n">
@@ -12166,11 +10970,7 @@
       <c r="S140" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T140" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T140" s="17" t="n"/>
       <c r="U140" s="15" t="inlineStr">
         <is>
           <t>Financial Services +11%</t>
@@ -12240,29 +11040,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q141" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R141" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q141" s="15" t="n"/>
+      <c r="R141" s="17" t="n"/>
       <c r="S141" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T141" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U141" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T141" s="17" t="n"/>
+      <c r="U141" s="15" t="n"/>
     </row>
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="13" t="n">
@@ -12331,29 +11115,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q142" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R142" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q142" s="15" t="n"/>
+      <c r="R142" s="17" t="n"/>
       <c r="S142" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T142" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U142" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T142" s="17" t="n"/>
+      <c r="U142" s="15" t="n"/>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="13" t="n">
@@ -12429,11 +11197,7 @@
       <c r="S143" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T143" s="17" t="n"/>
       <c r="U143" s="15" t="inlineStr">
         <is>
           <t>Mid Con Barnett Shal +180%</t>
@@ -12501,29 +11265,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q144" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R144" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q144" s="15" t="n"/>
+      <c r="R144" s="17" t="n"/>
       <c r="S144" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T144" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U144" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T144" s="17" t="n"/>
+      <c r="U144" s="15" t="n"/>
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="13" t="n">
@@ -12586,29 +11334,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q145" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R145" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q145" s="15" t="n"/>
+      <c r="R145" s="17" t="n"/>
       <c r="S145" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T145" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U145" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T145" s="17" t="n"/>
+      <c r="U145" s="15" t="n"/>
     </row>
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="13" t="n">
@@ -12682,11 +11414,7 @@
       <c r="S146" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T146" s="17" t="n"/>
       <c r="U146" s="15" t="inlineStr">
         <is>
           <t>Direct To Consumers -6%</t>
@@ -12765,11 +11493,7 @@
       <c r="S147" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T147" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T147" s="17" t="n"/>
       <c r="U147" s="15" t="inlineStr">
         <is>
           <t>Reportable -69%</t>
@@ -13005,16 +11729,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q150" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R150" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q150" s="15" t="n"/>
+      <c r="R150" s="17" t="n"/>
       <c r="S150" s="18" t="n">
         <v>2</v>
       </c>
@@ -13023,11 +11739,7 @@
           <t>North America 78%; EMEA 22%</t>
         </is>
       </c>
-      <c r="U150" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U150" s="15" t="n"/>
     </row>
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="13" t="n">
@@ -13436,29 +12148,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q155" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R155" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q155" s="15" t="n"/>
+      <c r="R155" s="17" t="n"/>
       <c r="S155" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T155" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U155" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T155" s="17" t="n"/>
+      <c r="U155" s="15" t="n"/>
     </row>
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="13" t="n">
@@ -13523,29 +12219,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q156" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R156" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q156" s="15" t="n"/>
+      <c r="R156" s="17" t="n"/>
       <c r="S156" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T156" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U156" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T156" s="17" t="n"/>
+      <c r="U156" s="15" t="n"/>
     </row>
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="13" t="n">
@@ -13608,29 +12288,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q157" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R157" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q157" s="15" t="n"/>
+      <c r="R157" s="17" t="n"/>
       <c r="S157" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T157" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U157" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T157" s="17" t="n"/>
+      <c r="U157" s="15" t="n"/>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="13" t="n">
@@ -13778,16 +12442,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q159" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R159" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q159" s="15" t="n"/>
+      <c r="R159" s="17" t="n"/>
       <c r="S159" s="18" t="n">
         <v>4</v>
       </c>
@@ -13796,11 +12452,7 @@
           <t>North America 42%; US 41%; Rest Of World 12%</t>
         </is>
       </c>
-      <c r="U159" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U159" s="15" t="n"/>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="13" t="n">
@@ -13865,29 +12517,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q160" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R160" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q160" s="15" t="n"/>
+      <c r="R160" s="17" t="n"/>
       <c r="S160" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U160" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T160" s="17" t="n"/>
+      <c r="U160" s="15" t="n"/>
     </row>
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="13" t="n">
@@ -14044,11 +12680,7 @@
       <c r="S162" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T162" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T162" s="17" t="n"/>
       <c r="U162" s="15" t="inlineStr">
         <is>
           <t>Reportable +17%</t>
@@ -14122,29 +12754,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q163" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R163" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q163" s="15" t="n"/>
+      <c r="R163" s="17" t="n"/>
       <c r="S163" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T163" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U163" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T163" s="17" t="n"/>
+      <c r="U163" s="15" t="n"/>
     </row>
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="13" t="n">
@@ -14220,11 +12836,7 @@
       <c r="S164" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T164" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T164" s="17" t="n"/>
       <c r="U164" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments +79%</t>
@@ -14303,11 +12915,7 @@
       <c r="S165" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T165" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T165" s="17" t="n"/>
       <c r="U165" s="15" t="inlineStr">
         <is>
           <t>Reportable +22%</t>
@@ -14388,11 +12996,7 @@
       <c r="S166" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T166" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T166" s="17" t="n"/>
       <c r="U166" s="15" t="inlineStr">
         <is>
           <t>Reportable -100%</t>
@@ -14460,29 +13064,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q167" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R167" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q167" s="15" t="n"/>
+      <c r="R167" s="17" t="n"/>
       <c r="S167" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T167" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U167" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T167" s="17" t="n"/>
+      <c r="U167" s="15" t="n"/>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="13" t="n">
@@ -14628,29 +13216,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q169" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R169" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q169" s="15" t="n"/>
+      <c r="R169" s="17" t="n"/>
       <c r="S169" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T169" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U169" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T169" s="17" t="n"/>
+      <c r="U169" s="15" t="n"/>
     </row>
     <row r="170" ht="16" customHeight="1">
       <c r="A170" s="13" t="n">
@@ -14726,16 +13298,8 @@
       <c r="S170" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T170" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U170" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T170" s="17" t="n"/>
+      <c r="U170" s="15" t="n"/>
     </row>
     <row r="171" ht="16" customHeight="1">
       <c r="A171" s="13" t="n">
@@ -14800,16 +13364,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q171" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R171" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q171" s="15" t="n"/>
+      <c r="R171" s="17" t="n"/>
       <c r="S171" s="18" t="n">
         <v>2</v>
       </c>
@@ -14818,11 +13374,7 @@
           <t>US 62%; Non Us 38%</t>
         </is>
       </c>
-      <c r="U171" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U171" s="15" t="n"/>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="13" t="n">
@@ -14891,29 +13443,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q172" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R172" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q172" s="15" t="n"/>
+      <c r="R172" s="17" t="n"/>
       <c r="S172" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T172" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U172" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T172" s="17" t="n"/>
+      <c r="U172" s="15" t="n"/>
     </row>
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="13" t="n">
@@ -14978,29 +13514,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q173" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R173" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q173" s="15" t="n"/>
+      <c r="R173" s="17" t="n"/>
       <c r="S173" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T173" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U173" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T173" s="17" t="n"/>
+      <c r="U173" s="15" t="n"/>
     </row>
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="13" t="n">
@@ -15069,29 +13589,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q174" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R174" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q174" s="15" t="n"/>
+      <c r="R174" s="17" t="n"/>
       <c r="S174" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T174" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U174" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T174" s="17" t="n"/>
+      <c r="U174" s="15" t="n"/>
     </row>
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="13" t="n">
@@ -15167,11 +13671,7 @@
       <c r="S175" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T175" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T175" s="17" t="n"/>
       <c r="U175" s="15" t="inlineStr">
         <is>
           <t>Institutional Produc +22%</t>
@@ -15252,11 +13752,7 @@
       <c r="S176" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T176" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T176" s="17" t="n"/>
       <c r="U176" s="15" t="inlineStr">
         <is>
           <t>Storage Solutions +8%</t>
@@ -15337,11 +13833,7 @@
       <c r="S177" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T177" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T177" s="17" t="n"/>
       <c r="U177" s="15" t="inlineStr">
         <is>
           <t>Gyre Pharmaceuticals +10%</t>
@@ -15494,29 +13986,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q179" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R179" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q179" s="15" t="n"/>
+      <c r="R179" s="17" t="n"/>
       <c r="S179" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T179" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U179" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T179" s="17" t="n"/>
+      <c r="U179" s="15" t="n"/>
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="13" t="n">
@@ -15753,29 +14229,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q182" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R182" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q182" s="15" t="n"/>
+      <c r="R182" s="17" t="n"/>
       <c r="S182" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T182" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U182" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T182" s="17" t="n"/>
+      <c r="U182" s="15" t="n"/>
     </row>
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="13" t="n">
@@ -15849,11 +14309,7 @@
       <c r="S183" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T183" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T183" s="17" t="n"/>
       <c r="U183" s="15" t="inlineStr">
         <is>
           <t>Towers +6%</t>
@@ -15921,29 +14377,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q184" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R184" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q184" s="15" t="n"/>
+      <c r="R184" s="17" t="n"/>
       <c r="S184" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T184" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U184" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T184" s="17" t="n"/>
+      <c r="U184" s="15" t="n"/>
     </row>
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="13" t="n">
@@ -16006,29 +14446,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q185" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R185" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q185" s="15" t="n"/>
+      <c r="R185" s="17" t="n"/>
       <c r="S185" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T185" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U185" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T185" s="17" t="n"/>
+      <c r="U185" s="15" t="n"/>
     </row>
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="13" t="n">
@@ -16346,29 +14770,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q189" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R189" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q189" s="15" t="n"/>
+      <c r="R189" s="17" t="n"/>
       <c r="S189" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T189" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U189" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T189" s="17" t="n"/>
+      <c r="U189" s="15" t="n"/>
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="13" t="n">
@@ -16431,29 +14839,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q190" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R190" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q190" s="15" t="n"/>
+      <c r="R190" s="17" t="n"/>
       <c r="S190" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U190" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T190" s="17" t="n"/>
+      <c r="U190" s="15" t="n"/>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="13" t="n">
@@ -16612,11 +15004,7 @@
       <c r="S192" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T192" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T192" s="17" t="n"/>
       <c r="U192" s="15" t="inlineStr">
         <is>
           <t>Accessories +2%</t>
@@ -16778,11 +15166,7 @@
       <c r="S194" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T194" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T194" s="17" t="n"/>
       <c r="U194" s="15" t="inlineStr">
         <is>
           <t>Large Account +9%</t>
@@ -16946,16 +15330,8 @@
       <c r="S196" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T196" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U196" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T196" s="17" t="n"/>
+      <c r="U196" s="15" t="n"/>
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="13" t="n">
@@ -17035,11 +15411,7 @@
       <c r="S197" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T197" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T197" s="17" t="n"/>
       <c r="U197" s="15" t="inlineStr">
         <is>
           <t>Reportable -1%</t>
@@ -17120,11 +15492,7 @@
       <c r="S198" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T198" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T198" s="17" t="n"/>
       <c r="U198" s="15" t="inlineStr">
         <is>
           <t>Program Of All Inclu +12%</t>
@@ -17203,11 +15571,7 @@
       <c r="S199" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T199" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T199" s="17" t="n"/>
       <c r="U199" s="15" t="inlineStr">
         <is>
           <t>Canadian Factory Bui +18%</t>
@@ -17281,29 +15645,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q200" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R200" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q200" s="15" t="n"/>
+      <c r="R200" s="17" t="n"/>
       <c r="S200" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T200" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U200" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T200" s="17" t="n"/>
+      <c r="U200" s="15" t="n"/>
     </row>
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="13" t="n">
@@ -17700,16 +16048,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q205" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R205" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q205" s="15" t="n"/>
+      <c r="R205" s="17" t="n"/>
       <c r="S205" s="18" t="n">
         <v>2</v>
       </c>
@@ -17718,11 +16058,7 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="U205" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U205" s="15" t="n"/>
     </row>
     <row r="206" ht="16" customHeight="1">
       <c r="A206" s="13" t="n">
@@ -17876,16 +16212,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q207" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R207" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q207" s="15" t="n"/>
+      <c r="R207" s="17" t="n"/>
       <c r="S207" s="18" t="n">
         <v>3</v>
       </c>
@@ -17894,11 +16222,7 @@
           <t>US 58%; Europe 32%; Other Than Us And Europe 10%</t>
         </is>
       </c>
-      <c r="U207" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U207" s="15" t="n"/>
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="13" t="n">
@@ -17963,16 +16287,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q208" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R208" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q208" s="15" t="n"/>
+      <c r="R208" s="17" t="n"/>
       <c r="S208" s="18" t="n">
         <v>5</v>
       </c>
@@ -17981,11 +16297,7 @@
           <t>US 92%; Non Us 6%; CA 1%</t>
         </is>
       </c>
-      <c r="U208" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U208" s="15" t="n"/>
     </row>
     <row r="209" ht="16" customHeight="1">
       <c r="A209" s="13" t="n">
@@ -18061,11 +16373,7 @@
       <c r="S209" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T209" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T209" s="17" t="n"/>
       <c r="U209" s="15" t="inlineStr">
         <is>
           <t>Insurance Services +47%</t>
@@ -18133,29 +16441,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q210" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R210" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q210" s="15" t="n"/>
+      <c r="R210" s="17" t="n"/>
       <c r="S210" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T210" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U210" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T210" s="17" t="n"/>
+      <c r="U210" s="15" t="n"/>
     </row>
     <row r="211" ht="16" customHeight="1">
       <c r="A211" s="13" t="n">
@@ -18229,11 +16521,7 @@
       <c r="S211" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T211" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T211" s="17" t="n"/>
       <c r="U211" s="15" t="inlineStr">
         <is>
           <t>System Integration S +78%</t>
@@ -18307,29 +16595,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q212" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R212" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q212" s="15" t="n"/>
+      <c r="R212" s="17" t="n"/>
       <c r="S212" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T212" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U212" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T212" s="17" t="n"/>
+      <c r="U212" s="15" t="n"/>
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="13" t="n">
@@ -18403,11 +16675,7 @@
       <c r="S213" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T213" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T213" s="17" t="n"/>
       <c r="U213" s="15" t="inlineStr">
         <is>
           <t>Mortgage Insurance -1%</t>
@@ -18475,16 +16743,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q214" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R214" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q214" s="15" t="n"/>
+      <c r="R214" s="17" t="n"/>
       <c r="S214" s="18" t="n">
         <v>5</v>
       </c>
@@ -18493,11 +16753,7 @@
           <t>US 76%; Non Us 12%; EMEA 7%</t>
         </is>
       </c>
-      <c r="U214" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U214" s="15" t="n"/>
     </row>
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="13" t="n">
@@ -18562,16 +16818,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q215" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R215" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q215" s="15" t="n"/>
+      <c r="R215" s="17" t="n"/>
       <c r="S215" s="18" t="n">
         <v>8</v>
       </c>
@@ -18580,11 +16828,7 @@
           <t>CN 27%; JP 19%; Europe 15%</t>
         </is>
       </c>
-      <c r="U215" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U215" s="15" t="n"/>
     </row>
     <row r="216" ht="16" customHeight="1">
       <c r="A216" s="13" t="n">
@@ -18653,29 +16897,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q216" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R216" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q216" s="15" t="n"/>
+      <c r="R216" s="17" t="n"/>
       <c r="S216" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T216" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U216" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T216" s="17" t="n"/>
+      <c r="U216" s="15" t="n"/>
     </row>
     <row r="217" ht="16" customHeight="1">
       <c r="A217" s="13" t="n">
@@ -18738,16 +16966,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q217" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R217" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q217" s="15" t="n"/>
+      <c r="R217" s="17" t="n"/>
       <c r="S217" s="18" t="n">
         <v>2</v>
       </c>
@@ -18756,11 +16976,7 @@
           <t>US 96%; Non Us 4%</t>
         </is>
       </c>
-      <c r="U217" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U217" s="15" t="n"/>
     </row>
     <row r="218" ht="16" customHeight="1">
       <c r="A218" s="13" t="n">
@@ -18823,16 +17039,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q218" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R218" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q218" s="15" t="n"/>
+      <c r="R218" s="17" t="n"/>
       <c r="S218" s="18" t="n">
         <v>3</v>
       </c>
@@ -18841,11 +17049,7 @@
           <t>US 64%; Europe 26%; Non US Or Europe 10%</t>
         </is>
       </c>
-      <c r="U218" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U218" s="15" t="n"/>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="13" t="n">
@@ -18912,29 +17116,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q219" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R219" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q219" s="15" t="n"/>
+      <c r="R219" s="17" t="n"/>
       <c r="S219" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T219" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U219" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T219" s="17" t="n"/>
+      <c r="U219" s="15" t="n"/>
     </row>
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="13" t="n">
@@ -18999,16 +17187,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q220" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R220" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q220" s="15" t="n"/>
+      <c r="R220" s="17" t="n"/>
       <c r="S220" s="18" t="n">
         <v>2</v>
       </c>
@@ -19017,11 +17197,7 @@
           <t>US 60%; Non Us 40%</t>
         </is>
       </c>
-      <c r="U220" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U220" s="15" t="n"/>
     </row>
     <row r="221" ht="16" customHeight="1">
       <c r="A221" s="13" t="n">
@@ -19086,29 +17262,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q221" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R221" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q221" s="15" t="n"/>
+      <c r="R221" s="17" t="n"/>
       <c r="S221" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T221" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U221" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T221" s="17" t="n"/>
+      <c r="U221" s="15" t="n"/>
     </row>
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="13" t="n">
@@ -19177,29 +17337,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q222" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R222" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q222" s="15" t="n"/>
+      <c r="R222" s="17" t="n"/>
       <c r="S222" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T222" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U222" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T222" s="17" t="n"/>
+      <c r="U222" s="15" t="n"/>
     </row>
     <row r="223" ht="16" customHeight="1">
       <c r="A223" s="13" t="n">
@@ -19266,29 +17410,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q223" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R223" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q223" s="15" t="n"/>
+      <c r="R223" s="17" t="n"/>
       <c r="S223" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T223" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U223" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T223" s="17" t="n"/>
+      <c r="U223" s="15" t="n"/>
     </row>
     <row r="224" ht="16" customHeight="1">
       <c r="A224" s="13" t="n">
@@ -19357,29 +17485,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q224" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R224" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q224" s="15" t="n"/>
+      <c r="R224" s="17" t="n"/>
       <c r="S224" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T224" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U224" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T224" s="17" t="n"/>
+      <c r="U224" s="15" t="n"/>
     </row>
     <row r="225" ht="16" customHeight="1">
       <c r="A225" s="13" t="n">
@@ -19453,11 +17565,7 @@
       <c r="S225" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T225" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T225" s="17" t="n"/>
       <c r="U225" s="15" t="inlineStr">
         <is>
           <t>Southeast -3%</t>
@@ -19608,29 +17716,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q227" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R227" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q227" s="15" t="n"/>
+      <c r="R227" s="17" t="n"/>
       <c r="S227" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T227" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U227" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T227" s="17" t="n"/>
+      <c r="U227" s="15" t="n"/>
     </row>
     <row r="228" ht="16" customHeight="1">
       <c r="A228" s="13" t="n">
@@ -19699,29 +17791,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q228" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R228" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q228" s="15" t="n"/>
+      <c r="R228" s="17" t="n"/>
       <c r="S228" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T228" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U228" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T228" s="17" t="n"/>
+      <c r="U228" s="15" t="n"/>
     </row>
     <row r="229" ht="16" customHeight="1">
       <c r="A229" s="13" t="n">
@@ -19797,11 +17873,7 @@
       <c r="S229" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T229" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T229" s="17" t="n"/>
       <c r="U229" s="15" t="inlineStr">
         <is>
           <t>Tutoring -6%</t>
@@ -19875,29 +17947,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q230" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R230" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q230" s="15" t="n"/>
+      <c r="R230" s="17" t="n"/>
       <c r="S230" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T230" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U230" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T230" s="17" t="n"/>
+      <c r="U230" s="15" t="n"/>
     </row>
     <row r="231" ht="16" customHeight="1">
       <c r="A231" s="13" t="n">
@@ -19960,16 +18016,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q231" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R231" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q231" s="15" t="n"/>
+      <c r="R231" s="17" t="n"/>
       <c r="S231" s="18" t="n">
         <v>2</v>
       </c>
@@ -19978,11 +18026,7 @@
           <t>US 82%; Non Us 18%</t>
         </is>
       </c>
-      <c r="U231" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U231" s="15" t="n"/>
     </row>
     <row r="232" ht="16" customHeight="1">
       <c r="A232" s="13" t="n">
@@ -20045,16 +18089,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q232" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R232" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q232" s="15" t="n"/>
+      <c r="R232" s="17" t="n"/>
       <c r="S232" s="18" t="n">
         <v>4</v>
       </c>
@@ -20063,11 +18099,7 @@
           <t>Haynesville 40%; Northeast Appalachia 37%; Southwest Appalac</t>
         </is>
       </c>
-      <c r="U232" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U232" s="15" t="n"/>
     </row>
     <row r="233" ht="16" customHeight="1">
       <c r="A233" s="13" t="n">
@@ -20143,11 +18175,7 @@
       <c r="S233" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T233" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T233" s="17" t="n"/>
       <c r="U233" s="15" t="inlineStr">
         <is>
           <t>Merchant Services +4%</t>
@@ -20217,29 +18245,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q234" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R234" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q234" s="15" t="n"/>
+      <c r="R234" s="17" t="n"/>
       <c r="S234" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T234" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U234" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T234" s="17" t="n"/>
+      <c r="U234" s="15" t="n"/>
     </row>
     <row r="235" ht="16" customHeight="1">
       <c r="A235" s="13" t="n">
@@ -20308,29 +18320,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q235" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R235" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q235" s="15" t="n"/>
+      <c r="R235" s="17" t="n"/>
       <c r="S235" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T235" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U235" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T235" s="17" t="n"/>
+      <c r="U235" s="15" t="n"/>
     </row>
     <row r="236" ht="16" customHeight="1">
       <c r="A236" s="13" t="n">
@@ -20393,16 +18389,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q236" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R236" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q236" s="15" t="n"/>
+      <c r="R236" s="17" t="n"/>
       <c r="S236" s="18" t="n">
         <v>2</v>
       </c>
@@ -20411,11 +18399,7 @@
           <t>Non Us 59%; US 41%</t>
         </is>
       </c>
-      <c r="U236" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U236" s="15" t="n"/>
     </row>
     <row r="237" ht="16" customHeight="1">
       <c r="A237" s="13" t="n">
@@ -20478,29 +18462,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q237" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R237" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q237" s="15" t="n"/>
+      <c r="R237" s="17" t="n"/>
       <c r="S237" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T237" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U237" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T237" s="17" t="n"/>
+      <c r="U237" s="15" t="n"/>
     </row>
     <row r="238" ht="16" customHeight="1">
       <c r="A238" s="13" t="n">
@@ -20657,11 +18625,7 @@
       <c r="S239" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T239" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T239" s="17" t="n"/>
       <c r="U239" s="15" t="inlineStr">
         <is>
           <t>Environmental Servic +8%</t>
@@ -20687,11 +18651,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E240" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E240" s="17" t="n"/>
       <c r="F240" s="18" t="n">
         <v>1578189440</v>
       </c>
@@ -20816,16 +18776,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q241" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R241" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q241" s="15" t="n"/>
+      <c r="R241" s="17" t="n"/>
       <c r="S241" s="18" t="n">
         <v>6</v>
       </c>
@@ -20834,11 +18786,7 @@
           <t>US 75%; Non Us 16%; Europe 5%</t>
         </is>
       </c>
-      <c r="U241" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U241" s="15" t="n"/>
     </row>
     <row r="242" ht="16" customHeight="1">
       <c r="A242" s="13" t="n">
@@ -20986,16 +18934,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q243" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R243" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q243" s="15" t="n"/>
+      <c r="R243" s="17" t="n"/>
       <c r="S243" s="18" t="n">
         <v>5</v>
       </c>
@@ -21004,11 +18944,7 @@
           <t>US 92%; ZA 3%; BS 3%</t>
         </is>
       </c>
-      <c r="U243" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U243" s="15" t="n"/>
     </row>
     <row r="244" ht="16" customHeight="1">
       <c r="A244" s="13" t="n">
@@ -21071,29 +19007,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q244" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R244" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q244" s="15" t="n"/>
+      <c r="R244" s="17" t="n"/>
       <c r="S244" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T244" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U244" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T244" s="17" t="n"/>
+      <c r="U244" s="15" t="n"/>
     </row>
     <row r="245" ht="16" customHeight="1">
       <c r="A245" s="13" t="n">
@@ -21241,16 +19161,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q246" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R246" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q246" s="15" t="n"/>
+      <c r="R246" s="17" t="n"/>
       <c r="S246" s="18" t="n">
         <v>2</v>
       </c>
@@ -21259,11 +19171,7 @@
           <t>US 100%; Non Us 0%</t>
         </is>
       </c>
-      <c r="U246" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U246" s="15" t="n"/>
     </row>
     <row r="247" ht="16" customHeight="1">
       <c r="A247" s="13" t="n">
@@ -21415,29 +19323,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q248" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R248" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q248" s="15" t="n"/>
+      <c r="R248" s="17" t="n"/>
       <c r="S248" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T248" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U248" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T248" s="17" t="n"/>
+      <c r="U248" s="15" t="n"/>
     </row>
     <row r="249" ht="16" customHeight="1">
       <c r="A249" s="13" t="n">
@@ -21500,16 +19392,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q249" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R249" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q249" s="15" t="n"/>
+      <c r="R249" s="17" t="n"/>
       <c r="S249" s="18" t="n">
         <v>6</v>
       </c>
@@ -21518,11 +19402,7 @@
           <t>CN 42%; US 28%; KR 27%</t>
         </is>
       </c>
-      <c r="U249" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U249" s="15" t="n"/>
     </row>
     <row r="250" ht="16" customHeight="1">
       <c r="A250" s="13" t="n">
@@ -21596,11 +19476,7 @@
       <c r="S250" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T250" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T250" s="17" t="n"/>
       <c r="U250" s="15" t="inlineStr">
         <is>
           <t>Reportable +11%</t>
@@ -21679,11 +19555,7 @@
       <c r="S251" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T251" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T251" s="17" t="n"/>
       <c r="U251" s="15" t="inlineStr">
         <is>
           <t>Operating +2%</t>
@@ -21753,29 +19625,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q252" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R252" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q252" s="15" t="n"/>
+      <c r="R252" s="17" t="n"/>
       <c r="S252" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T252" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U252" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T252" s="17" t="n"/>
+      <c r="U252" s="15" t="n"/>
     </row>
     <row r="253" ht="16" customHeight="1">
       <c r="A253" s="13" t="n">
@@ -21838,16 +19694,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q253" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R253" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q253" s="15" t="n"/>
+      <c r="R253" s="17" t="n"/>
       <c r="S253" s="18" t="n">
         <v>5</v>
       </c>
@@ -21856,11 +19704,7 @@
           <t>North America 34%; US 31%; EMEA 27%</t>
         </is>
       </c>
-      <c r="U253" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U253" s="15" t="n"/>
     </row>
     <row r="254" ht="16" customHeight="1">
       <c r="A254" s="13" t="n">
@@ -21925,29 +19769,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q254" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R254" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q254" s="15" t="n"/>
+      <c r="R254" s="17" t="n"/>
       <c r="S254" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T254" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U254" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T254" s="17" t="n"/>
+      <c r="U254" s="15" t="n"/>
     </row>
     <row r="255" ht="16" customHeight="1">
       <c r="A255" s="13" t="n">
@@ -22095,29 +19923,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q256" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R256" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q256" s="15" t="n"/>
+      <c r="R256" s="17" t="n"/>
       <c r="S256" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T256" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U256" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T256" s="17" t="n"/>
+      <c r="U256" s="15" t="n"/>
     </row>
     <row r="257" ht="16" customHeight="1">
       <c r="A257" s="13" t="n">
@@ -22280,11 +20092,7 @@
       <c r="S258" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T258" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T258" s="17" t="n"/>
       <c r="U258" s="15" t="inlineStr">
         <is>
           <t>Banking +10%</t>
@@ -22352,16 +20160,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q259" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R259" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q259" s="15" t="n"/>
+      <c r="R259" s="17" t="n"/>
       <c r="S259" s="18" t="n">
         <v>2</v>
       </c>
@@ -22370,11 +20170,7 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="U259" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U259" s="15" t="n"/>
     </row>
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="13" t="n">
@@ -22439,29 +20235,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q260" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R260" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q260" s="15" t="n"/>
+      <c r="R260" s="17" t="n"/>
       <c r="S260" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T260" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U260" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T260" s="17" t="n"/>
+      <c r="U260" s="15" t="n"/>
     </row>
     <row r="261" ht="16" customHeight="1">
       <c r="A261" s="13" t="n">
@@ -22526,16 +20306,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q261" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R261" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q261" s="15" t="n"/>
+      <c r="R261" s="17" t="n"/>
       <c r="S261" s="18" t="n">
         <v>4</v>
       </c>
@@ -22544,11 +20316,7 @@
           <t>US 45%; Europe Middle East And Africa 26%; Asia Pacific 25%</t>
         </is>
       </c>
-      <c r="U261" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U261" s="15" t="n"/>
     </row>
     <row r="262" ht="16" customHeight="1">
       <c r="A262" s="13" t="n">
@@ -22613,29 +20381,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q262" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R262" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q262" s="15" t="n"/>
+      <c r="R262" s="17" t="n"/>
       <c r="S262" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T262" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U262" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T262" s="17" t="n"/>
+      <c r="U262" s="15" t="n"/>
     </row>
     <row r="263" ht="16" customHeight="1">
       <c r="A263" s="13" t="n">
@@ -22704,29 +20456,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q263" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R263" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q263" s="15" t="n"/>
+      <c r="R263" s="17" t="n"/>
       <c r="S263" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T263" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U263" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T263" s="17" t="n"/>
+      <c r="U263" s="15" t="n"/>
     </row>
     <row r="264" ht="16" customHeight="1">
       <c r="A264" s="13" t="n">
@@ -22791,29 +20527,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q264" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R264" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q264" s="15" t="n"/>
+      <c r="R264" s="17" t="n"/>
       <c r="S264" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T264" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U264" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T264" s="17" t="n"/>
+      <c r="U264" s="15" t="n"/>
     </row>
     <row r="265" ht="16" customHeight="1">
       <c r="A265" s="13" t="n">
@@ -22876,16 +20596,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q265" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R265" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q265" s="15" t="n"/>
+      <c r="R265" s="17" t="n"/>
       <c r="S265" s="18" t="n">
         <v>2</v>
       </c>
@@ -22894,11 +20606,7 @@
           <t>Global 70%; Ous 30%</t>
         </is>
       </c>
-      <c r="U265" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U265" s="15" t="n"/>
     </row>
     <row r="266" ht="16" customHeight="1">
       <c r="A266" s="13" t="n">
@@ -22961,29 +20669,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q266" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R266" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q266" s="15" t="n"/>
+      <c r="R266" s="17" t="n"/>
       <c r="S266" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T266" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U266" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T266" s="17" t="n"/>
+      <c r="U266" s="15" t="n"/>
     </row>
     <row r="267" ht="16" customHeight="1">
       <c r="A267" s="13" t="n">
@@ -23059,11 +20751,7 @@
       <c r="S267" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T267" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T267" s="17" t="n"/>
       <c r="U267" s="15" t="inlineStr">
         <is>
           <t>Reportable -5%</t>
@@ -23227,11 +20915,7 @@
       <c r="S269" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T269" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T269" s="17" t="n"/>
       <c r="U269" s="15" t="inlineStr">
         <is>
           <t>Medicare +62%</t>
@@ -23386,29 +21070,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q271" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R271" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q271" s="15" t="n"/>
+      <c r="R271" s="17" t="n"/>
       <c r="S271" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T271" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U271" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T271" s="17" t="n"/>
+      <c r="U271" s="15" t="n"/>
     </row>
     <row r="272" ht="16" customHeight="1">
       <c r="A272" s="13" t="n">
@@ -23556,29 +21224,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q273" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R273" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q273" s="15" t="n"/>
+      <c r="R273" s="17" t="n"/>
       <c r="S273" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T273" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U273" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T273" s="17" t="n"/>
+      <c r="U273" s="15" t="n"/>
     </row>
     <row r="274" ht="16" customHeight="1">
       <c r="A274" s="13" t="n">
@@ -23652,11 +21304,7 @@
       <c r="S274" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T274" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T274" s="17" t="n"/>
       <c r="U274" s="15" t="inlineStr">
         <is>
           <t>Utility Coal Mining +29%</t>
@@ -23811,29 +21459,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q276" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R276" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q276" s="15" t="n"/>
+      <c r="R276" s="17" t="n"/>
       <c r="S276" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T276" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U276" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T276" s="17" t="n"/>
+      <c r="U276" s="15" t="n"/>
     </row>
     <row r="277" ht="16" customHeight="1">
       <c r="A277" s="13" t="n">
@@ -23979,29 +21611,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q278" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R278" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q278" s="15" t="n"/>
+      <c r="R278" s="17" t="n"/>
       <c r="S278" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T278" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U278" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T278" s="17" t="n"/>
+      <c r="U278" s="15" t="n"/>
     </row>
     <row r="279" ht="16" customHeight="1">
       <c r="A279" s="13" t="n">
@@ -24232,16 +21848,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q281" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R281" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q281" s="15" t="n"/>
+      <c r="R281" s="17" t="n"/>
       <c r="S281" s="18" t="n">
         <v>3</v>
       </c>
@@ -24250,11 +21858,7 @@
           <t>US 43%; Europe And Other 37%; Asia And Middle East 20%</t>
         </is>
       </c>
-      <c r="U281" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U281" s="15" t="n"/>
     </row>
     <row r="282" ht="16" customHeight="1">
       <c r="A282" s="13" t="n">
@@ -24328,11 +21932,7 @@
       <c r="S282" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T282" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T282" s="17" t="n"/>
       <c r="U282" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +0%</t>
@@ -24358,11 +21958,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E283" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E283" s="17" t="n"/>
       <c r="F283" s="18" t="n">
         <v>264062080</v>
       </c>
@@ -24413,11 +22009,7 @@
       <c r="S283" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T283" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T283" s="17" t="n"/>
       <c r="U283" s="15" t="inlineStr">
         <is>
           <t>Seniors Housing Comm +4%</t>
@@ -24503,11 +22095,7 @@
           <t>North America 89%; Asia Pacific 9%; Europe 3%</t>
         </is>
       </c>
-      <c r="U284" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U284" s="15" t="n"/>
     </row>
     <row r="285" ht="16" customHeight="1">
       <c r="A285" s="13" t="n">
@@ -24576,29 +22164,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q285" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R285" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q285" s="15" t="n"/>
+      <c r="R285" s="17" t="n"/>
       <c r="S285" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T285" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U285" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T285" s="17" t="n"/>
+      <c r="U285" s="15" t="n"/>
     </row>
     <row r="286" ht="16" customHeight="1">
       <c r="A286" s="13" t="n">
@@ -24667,29 +22239,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q286" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R286" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q286" s="15" t="n"/>
+      <c r="R286" s="17" t="n"/>
       <c r="S286" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T286" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U286" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T286" s="17" t="n"/>
+      <c r="U286" s="15" t="n"/>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="13" t="n">
@@ -24841,29 +22397,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q288" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R288" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q288" s="15" t="n"/>
+      <c r="R288" s="17" t="n"/>
       <c r="S288" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T288" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U288" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T288" s="17" t="n"/>
+      <c r="U288" s="15" t="n"/>
     </row>
     <row r="289" ht="16" customHeight="1">
       <c r="A289" s="13" t="n">
@@ -24939,11 +22479,7 @@
       <c r="S289" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T289" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T289" s="17" t="n"/>
       <c r="U289" s="15" t="inlineStr">
         <is>
           <t>Banking +15%</t>
@@ -25013,29 +22549,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q290" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R290" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q290" s="15" t="n"/>
+      <c r="R290" s="17" t="n"/>
       <c r="S290" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T290" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U290" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T290" s="17" t="n"/>
+      <c r="U290" s="15" t="n"/>
     </row>
     <row r="291" ht="16" customHeight="1">
       <c r="A291" s="13" t="n">
@@ -25098,29 +22618,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q291" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R291" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q291" s="15" t="n"/>
+      <c r="R291" s="17" t="n"/>
       <c r="S291" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T291" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U291" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T291" s="17" t="n"/>
+      <c r="U291" s="15" t="n"/>
     </row>
     <row r="292" ht="16" customHeight="1">
       <c r="A292" s="13" t="n">
@@ -25266,29 +22770,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q293" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R293" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q293" s="15" t="n"/>
+      <c r="R293" s="17" t="n"/>
       <c r="S293" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T293" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U293" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T293" s="17" t="n"/>
+      <c r="U293" s="15" t="n"/>
     </row>
     <row r="294" ht="16" customHeight="1">
       <c r="A294" s="13" t="n">
@@ -25440,29 +22928,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q295" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R295" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q295" s="15" t="n"/>
+      <c r="R295" s="17" t="n"/>
       <c r="S295" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T295" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U295" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T295" s="17" t="n"/>
+      <c r="U295" s="15" t="n"/>
     </row>
     <row r="296" ht="16" customHeight="1">
       <c r="A296" s="13" t="n">
@@ -25525,16 +22997,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q296" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R296" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q296" s="15" t="n"/>
+      <c r="R296" s="17" t="n"/>
       <c r="S296" s="18" t="n">
         <v>2</v>
       </c>
@@ -25543,11 +23007,7 @@
           <t>US 99%; Non Us 1%</t>
         </is>
       </c>
-      <c r="U296" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U296" s="15" t="n"/>
     </row>
     <row r="297" ht="16" customHeight="1">
       <c r="A297" s="13" t="n">
@@ -25623,11 +23083,7 @@
       <c r="S297" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T297" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T297" s="17" t="n"/>
       <c r="U297" s="15" t="inlineStr">
         <is>
           <t>Timber +327%</t>
@@ -25780,29 +23236,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q299" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R299" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q299" s="15" t="n"/>
+      <c r="R299" s="17" t="n"/>
       <c r="S299" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T299" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U299" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T299" s="17" t="n"/>
+      <c r="U299" s="15" t="n"/>
     </row>
     <row r="300" ht="16" customHeight="1">
       <c r="A300" s="13" t="n">
@@ -25865,16 +23305,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q300" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R300" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q300" s="15" t="n"/>
+      <c r="R300" s="17" t="n"/>
       <c r="S300" s="18" t="n">
         <v>2</v>
       </c>
@@ -25883,11 +23315,7 @@
           <t>Non Us 58%; US 42%</t>
         </is>
       </c>
-      <c r="U300" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U300" s="15" t="n"/>
     </row>
     <row r="301" ht="16" customHeight="1">
       <c r="A301" s="13" t="n">
@@ -25950,29 +23378,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q301" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R301" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q301" s="15" t="n"/>
+      <c r="R301" s="17" t="n"/>
       <c r="S301" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T301" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U301" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T301" s="17" t="n"/>
+      <c r="U301" s="15" t="n"/>
     </row>
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="13" t="n">
@@ -26046,11 +23458,7 @@
       <c r="S302" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T302" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T302" s="17" t="n"/>
       <c r="U302" s="15" t="inlineStr">
         <is>
           <t>Shale +38%</t>
@@ -26129,11 +23537,7 @@
       <c r="S303" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T303" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T303" s="17" t="n"/>
       <c r="U303" s="15" t="inlineStr">
         <is>
           <t>Wealth Solutions +15%</t>
@@ -26201,29 +23605,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q304" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R304" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q304" s="15" t="n"/>
+      <c r="R304" s="17" t="n"/>
       <c r="S304" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T304" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U304" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T304" s="17" t="n"/>
+      <c r="U304" s="15" t="n"/>
     </row>
     <row r="305" ht="16" customHeight="1">
       <c r="A305" s="13" t="n">
@@ -26292,29 +23680,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q305" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R305" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q305" s="15" t="n"/>
+      <c r="R305" s="17" t="n"/>
       <c r="S305" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T305" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U305" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T305" s="17" t="n"/>
+      <c r="U305" s="15" t="n"/>
     </row>
     <row r="306" ht="16" customHeight="1">
       <c r="A306" s="13" t="n">
@@ -26388,11 +23760,7 @@
       <c r="S306" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T306" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T306" s="17" t="n"/>
       <c r="U306" s="15" t="inlineStr">
         <is>
           <t>Good Times +2%</t>
@@ -26543,29 +23911,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q308" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R308" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q308" s="15" t="n"/>
+      <c r="R308" s="17" t="n"/>
       <c r="S308" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T308" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U308" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T308" s="17" t="n"/>
+      <c r="U308" s="15" t="n"/>
     </row>
     <row r="309" ht="16" customHeight="1">
       <c r="A309" s="13" t="n">
@@ -26630,16 +23982,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q309" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R309" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q309" s="15" t="n"/>
+      <c r="R309" s="17" t="n"/>
       <c r="S309" s="18" t="n">
         <v>4</v>
       </c>
@@ -26648,11 +23992,7 @@
           <t>North America 90%; EMEA 10%; Rest Of World 0%</t>
         </is>
       </c>
-      <c r="U309" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U309" s="15" t="n"/>
     </row>
     <row r="310" ht="16" customHeight="1">
       <c r="A310" s="13" t="n">
@@ -26721,29 +24061,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q310" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R310" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q310" s="15" t="n"/>
+      <c r="R310" s="17" t="n"/>
       <c r="S310" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T310" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U310" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T310" s="17" t="n"/>
+      <c r="U310" s="15" t="n"/>
     </row>
     <row r="311" ht="16" customHeight="1">
       <c r="A311" s="13" t="n">
@@ -26808,29 +24132,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q311" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R311" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q311" s="15" t="n"/>
+      <c r="R311" s="17" t="n"/>
       <c r="S311" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T311" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U311" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T311" s="17" t="n"/>
+      <c r="U311" s="15" t="n"/>
     </row>
     <row r="312" ht="16" customHeight="1">
       <c r="A312" s="13" t="n">
@@ -26893,16 +24201,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q312" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R312" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q312" s="15" t="n"/>
+      <c r="R312" s="17" t="n"/>
       <c r="S312" s="18" t="n">
         <v>5</v>
       </c>
@@ -26911,11 +24211,7 @@
           <t>US 61%; Non Us 20%; Europe 13%</t>
         </is>
       </c>
-      <c r="U312" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U312" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A11:U312"/>
@@ -26933,7 +24229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -26959,6 +24255,7 @@
     <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -26989,6 +24286,7 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -27093,8 +24391,9 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY ETA</t>
         </is>
@@ -27976,11 +25275,7 @@
       <c r="S21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T21" s="17" t="n"/>
       <c r="U21" s="15" t="inlineStr">
         <is>
           <t>Accessories +2%</t>
@@ -28059,11 +25354,7 @@
       <c r="S22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T22" s="17" t="n"/>
       <c r="U22" s="15" t="inlineStr">
         <is>
           <t>System Integration S +78%</t>
@@ -28142,11 +25433,7 @@
       <c r="S23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T23" s="17" t="n"/>
       <c r="U23" s="15" t="inlineStr">
         <is>
           <t>Southeast -3%</t>
@@ -28391,11 +25678,7 @@
       <c r="S26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T26" s="17" t="n"/>
       <c r="U26" s="15" t="inlineStr">
         <is>
           <t>Development +21%</t>
@@ -28474,11 +25757,7 @@
       <c r="S27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T27" s="17" t="n"/>
       <c r="U27" s="15" t="inlineStr">
         <is>
           <t>Southeast Reportable -12%</t>
@@ -28891,11 +26170,7 @@
       <c r="S32" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T32" s="17" t="n"/>
       <c r="U32" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +56%</t>
@@ -28976,11 +26251,7 @@
       <c r="S33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T33" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T33" s="17" t="n"/>
       <c r="U33" s="15" t="inlineStr">
         <is>
           <t>Spices And Flavor So -75%</t>
@@ -29142,11 +26413,7 @@
       <c r="S35" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T35" s="17" t="n"/>
       <c r="U35" s="15" t="inlineStr">
         <is>
           <t>Healthcare Services +55%</t>
@@ -29225,11 +26492,7 @@
       <c r="S36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T36" s="17" t="n"/>
       <c r="U36" s="15" t="inlineStr">
         <is>
           <t>Branded Products +2%</t>
@@ -29646,11 +26909,7 @@
       <c r="S41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T41" s="17" t="n"/>
       <c r="U41" s="15" t="inlineStr">
         <is>
           <t>Poland +5%</t>
@@ -29729,11 +26988,7 @@
       <c r="S42" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T42" s="17" t="n"/>
       <c r="U42" s="15" t="inlineStr">
         <is>
           <t>Brokerage +3%</t>
@@ -30146,11 +27401,7 @@
       <c r="S47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T47" s="17" t="n"/>
       <c r="U47" s="15" t="inlineStr">
         <is>
           <t>Intralot B2B -24%</t>
@@ -30229,11 +27480,7 @@
       <c r="S48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T48" s="17" t="n"/>
       <c r="U48" s="15" t="inlineStr">
         <is>
           <t>Total Operating Segm +10%</t>
@@ -30397,11 +27644,7 @@
       <c r="S50" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T50" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T50" s="17" t="n"/>
       <c r="U50" s="15" t="inlineStr">
         <is>
           <t>Southwest -5%</t>
@@ -30484,11 +27727,7 @@
       <c r="S51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T51" s="17" t="n"/>
       <c r="U51" s="15" t="inlineStr">
         <is>
           <t>Segment Benefits And +3%</t>
@@ -30733,11 +27972,7 @@
       <c r="S54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T54" s="17" t="n"/>
       <c r="U54" s="15" t="inlineStr">
         <is>
           <t>Retirement And Incom +23%</t>
@@ -30816,11 +28051,7 @@
       <c r="S55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T55" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T55" s="17" t="n"/>
       <c r="U55" s="15" t="inlineStr">
         <is>
           <t>Online +17%</t>
@@ -30984,11 +28215,7 @@
       <c r="S57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T57" s="17" t="n"/>
       <c r="U57" s="15" t="inlineStr">
         <is>
           <t>Service And Retailin +7%</t>
@@ -31150,11 +28377,7 @@
       <c r="S59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T59" s="17" t="n"/>
       <c r="U59" s="15" t="inlineStr">
         <is>
           <t>Financial Services +124%</t>
@@ -31233,11 +28456,7 @@
       <c r="S60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T60" s="17" t="n"/>
       <c r="U60" s="15" t="inlineStr">
         <is>
           <t>Colombia Operations +11%</t>
@@ -31346,11 +28565,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E62" s="17" t="n"/>
       <c r="F62" s="18" t="n">
         <v>13223558144</v>
       </c>
@@ -31401,11 +28616,7 @@
       <c r="S62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T62" s="17" t="n"/>
       <c r="U62" s="15" t="inlineStr">
         <is>
           <t>Installation And Mai +22%</t>
@@ -31816,11 +29027,7 @@
       <c r="S67" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T67" s="17" t="n"/>
       <c r="U67" s="15" t="inlineStr">
         <is>
           <t>Americas +20%</t>
@@ -31899,11 +29106,7 @@
       <c r="S68" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T68" s="17" t="n"/>
       <c r="U68" s="15" t="inlineStr">
         <is>
           <t>Farming And Agricult +35%</t>
@@ -32156,11 +29359,7 @@
       <c r="S71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T71" s="17" t="n"/>
       <c r="U71" s="15" t="inlineStr">
         <is>
           <t>Warehouse Lending +17%</t>
@@ -32241,11 +29440,7 @@
       <c r="S72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T72" s="17" t="n"/>
       <c r="U72" s="15" t="inlineStr">
         <is>
           <t>Underwriting Capacit +18%</t>
@@ -32268,7 +29463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -32294,6 +29489,7 @@
     <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -32324,6 +29520,7 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -32428,8 +29625,9 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY ETA</t>
         </is>
@@ -32803,11 +30001,7 @@
       <c r="S15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T15" s="17" t="n"/>
       <c r="U15" s="15" t="inlineStr">
         <is>
           <t>Genie Retail Energy  +19%</t>
@@ -32971,11 +30165,7 @@
       <c r="S17" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T17" s="17" t="n"/>
       <c r="U17" s="15" t="inlineStr">
         <is>
           <t>Zedge Marketplace +2%</t>
@@ -33139,11 +30329,7 @@
       <c r="S19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T19" s="17" t="n"/>
       <c r="U19" s="15" t="inlineStr">
         <is>
           <t>Publishing -18%</t>
@@ -33305,11 +30491,7 @@
       <c r="S21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T21" s="17" t="n"/>
       <c r="U21" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -33390,11 +30572,7 @@
       <c r="S22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T22" s="17" t="n"/>
       <c r="U22" s="15" t="inlineStr">
         <is>
           <t>Medicare +10%</t>
@@ -33479,11 +30657,7 @@
       <c r="S23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T23" s="17" t="n"/>
       <c r="U23" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -33562,11 +30736,7 @@
       <c r="S24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T24" s="17" t="n"/>
       <c r="U24" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments +15%</t>
@@ -33647,11 +30817,7 @@
       <c r="S25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T25" s="17" t="n"/>
       <c r="U25" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -33904,11 +31070,7 @@
       <c r="S28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T28" s="17" t="n"/>
       <c r="U28" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -33993,11 +31155,7 @@
       <c r="S29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T29" s="17" t="n"/>
       <c r="U29" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +15%</t>
@@ -34082,11 +31240,7 @@
       <c r="S30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T30" s="17" t="n"/>
       <c r="U30" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -34165,11 +31319,7 @@
       <c r="S31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T31" s="17" t="n"/>
       <c r="U31" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments  +1%</t>
@@ -34248,11 +31398,7 @@
       <c r="S32" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T32" s="17" t="n"/>
       <c r="U32" s="15" t="inlineStr">
         <is>
           <t>Pandora And Off Plat -0%</t>
@@ -34339,11 +31485,7 @@
       <c r="S33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T33" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T33" s="17" t="n"/>
       <c r="U33" s="15" t="inlineStr">
         <is>
           <t>Financial Services +11%</t>
@@ -34509,11 +31651,7 @@
       <c r="S35" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T35" s="17" t="n"/>
       <c r="U35" s="15" t="inlineStr">
         <is>
           <t>Institutional Produc +22%</t>
@@ -34594,11 +31732,7 @@
       <c r="S36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T36" s="17" t="n"/>
       <c r="U36" s="15" t="inlineStr">
         <is>
           <t>Storage Solutions +8%</t>
@@ -34677,11 +31811,7 @@
       <c r="S37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T37" s="17" t="n"/>
       <c r="U37" s="15" t="inlineStr">
         <is>
           <t>Towers +6%</t>
@@ -34928,11 +32058,7 @@
       <c r="S40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T40" s="17" t="n"/>
       <c r="U40" s="15" t="inlineStr">
         <is>
           <t>Program Of All Inclu +12%</t>
@@ -35011,11 +32137,7 @@
       <c r="S41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T41" s="17" t="n"/>
       <c r="U41" s="15" t="inlineStr">
         <is>
           <t>Canadian Factory Bui +18%</t>
@@ -35179,11 +32301,7 @@
       <c r="S43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T43" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T43" s="17" t="n"/>
       <c r="U43" s="15" t="inlineStr">
         <is>
           <t>Merchant Services +4%</t>
@@ -35594,11 +32712,7 @@
       <c r="S48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T48" s="17" t="n"/>
       <c r="U48" s="15" t="inlineStr">
         <is>
           <t>Shale +38%</t>
@@ -35679,11 +32793,7 @@
       <c r="S49" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T49" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T49" s="17" t="n"/>
       <c r="U49" s="15" t="inlineStr">
         <is>
           <t>Eastern Hemisphere +78%</t>
@@ -35762,11 +32872,7 @@
       <c r="S50" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T50" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T50" s="17" t="n"/>
       <c r="U50" s="15" t="inlineStr">
         <is>
           <t>Transmission +162%</t>
@@ -35877,11 +32983,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E52" s="17" t="n"/>
       <c r="F52" s="18" t="n">
         <v>10732237824</v>
       </c>
@@ -36098,11 +33200,7 @@
       <c r="S54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T54" s="17" t="n"/>
       <c r="U54" s="15" t="inlineStr">
         <is>
           <t>Life Sciences +32%</t>
@@ -36187,11 +33285,7 @@
       <c r="S55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T55" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T55" s="17" t="n"/>
       <c r="U55" s="15" t="inlineStr">
         <is>
           <t>Wealth +10%</t>
@@ -36270,11 +33364,7 @@
       <c r="S56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T56" s="17" t="n"/>
       <c r="U56" s="15" t="inlineStr">
         <is>
           <t>Gas Utility +13%</t>
@@ -36355,11 +33445,7 @@
       <c r="S57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T57" s="17" t="n"/>
       <c r="U57" s="15" t="inlineStr">
         <is>
           <t>Snack Food Products +5%</t>
@@ -36521,11 +33607,7 @@
       <c r="S59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T59" s="17" t="n"/>
       <c r="U59" s="15" t="inlineStr">
         <is>
           <t>Defense +43%</t>
@@ -36693,11 +33775,7 @@
       <c r="S61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T61" s="17" t="n"/>
       <c r="U61" s="15" t="inlineStr">
         <is>
           <t>Wealth Management Se +17%</t>
@@ -36776,11 +33854,7 @@
       <c r="S62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T62" s="17" t="n"/>
       <c r="U62" s="15" t="inlineStr">
         <is>
           <t>Chilis Restaurants +25%</t>
@@ -37029,11 +34103,7 @@
       <c r="S65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T65" s="17" t="n"/>
       <c r="U65" s="15" t="inlineStr">
         <is>
           <t>Banking Services +34%</t>
@@ -37282,11 +34352,7 @@
       <c r="S68" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T68" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T68" s="17" t="n"/>
       <c r="U68" s="15" t="inlineStr">
         <is>
           <t>Digital Assets +42%</t>
@@ -37365,11 +34431,7 @@
       <c r="S69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T69" s="17" t="n"/>
       <c r="U69" s="15" t="inlineStr">
         <is>
           <t>Healthcare IT +11%</t>
@@ -37533,16 +34595,8 @@
       <c r="S71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U71" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T71" s="17" t="n"/>
+      <c r="U71" s="15" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="13" t="n">
@@ -37616,11 +34670,7 @@
       <c r="S72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T72" s="17" t="n"/>
       <c r="U72" s="15" t="inlineStr">
         <is>
           <t>Subscription Operati +50%</t>
@@ -37643,7 +34693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -37669,6 +34719,7 @@
     <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -37699,6 +34750,7 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -37803,8 +34855,9 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY ETA</t>
         </is>
@@ -38254,16 +35307,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q16" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R16" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="17" t="n"/>
       <c r="S16" s="18" t="n">
         <v>5</v>
       </c>
@@ -38272,11 +35317,7 @@
           <t>US 85%; CN 8%; Other Countries 2%</t>
         </is>
       </c>
-      <c r="U16" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U16" s="15" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="13" t="n">
@@ -38339,16 +35380,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q17" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R17" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="17" t="n"/>
       <c r="S17" s="18" t="n">
         <v>6</v>
       </c>
@@ -38357,11 +35390,7 @@
           <t>North America 24%; US 24%; EMEA 19%</t>
         </is>
       </c>
-      <c r="U17" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U17" s="15" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="13" t="n">
@@ -38679,16 +35708,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q21" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="17" t="n"/>
       <c r="S21" s="18" t="n">
         <v>4</v>
       </c>
@@ -38697,11 +35718,7 @@
           <t>US 65%; EMEA 28%; Asia Pacific 6%</t>
         </is>
       </c>
-      <c r="U21" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U21" s="15" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="13" t="n">
@@ -38934,16 +35951,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q24" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q24" s="15" t="n"/>
+      <c r="R24" s="17" t="n"/>
       <c r="S24" s="18" t="n">
         <v>4</v>
       </c>
@@ -38952,11 +35961,7 @@
           <t>US 71%; GB 12%; Other International 11%</t>
         </is>
       </c>
-      <c r="U24" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U24" s="15" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="13" t="n">
@@ -39102,16 +36107,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q26" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R26" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q26" s="15" t="n"/>
+      <c r="R26" s="17" t="n"/>
       <c r="S26" s="18" t="n">
         <v>6</v>
       </c>
@@ -39120,11 +36117,7 @@
           <t>North America 30%; US 27%; EMEA 25%</t>
         </is>
       </c>
-      <c r="U26" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U26" s="15" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="13" t="n">
@@ -39274,16 +36267,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q28" s="15" t="n"/>
+      <c r="R28" s="17" t="n"/>
       <c r="S28" s="18" t="n">
         <v>9</v>
       </c>
@@ -39292,11 +36277,7 @@
           <t>Europe 26%; Americas 21%; US 20%</t>
         </is>
       </c>
-      <c r="U28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U28" s="15" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -39950,16 +36931,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q36" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="17" t="n"/>
       <c r="S36" s="18" t="n">
         <v>4</v>
       </c>
@@ -39968,11 +36941,7 @@
           <t>North America 42%; US 41%; Rest Of World 12%</t>
         </is>
       </c>
-      <c r="U36" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U36" s="15" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="13" t="n">
@@ -40539,16 +37508,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q43" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R43" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q43" s="15" t="n"/>
+      <c r="R43" s="17" t="n"/>
       <c r="S43" s="18" t="n">
         <v>5</v>
       </c>
@@ -40557,11 +37518,7 @@
           <t>US 92%; Non Us 6%; CA 1%</t>
         </is>
       </c>
-      <c r="U43" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U43" s="15" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="13" t="n">
@@ -40624,16 +37581,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q44" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q44" s="15" t="n"/>
+      <c r="R44" s="17" t="n"/>
       <c r="S44" s="18" t="n">
         <v>5</v>
       </c>
@@ -40642,11 +37591,7 @@
           <t>US 76%; Non Us 12%; EMEA 7%</t>
         </is>
       </c>
-      <c r="U44" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U44" s="15" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -40711,16 +37656,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q45" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R45" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q45" s="15" t="n"/>
+      <c r="R45" s="17" t="n"/>
       <c r="S45" s="18" t="n">
         <v>8</v>
       </c>
@@ -40729,11 +37666,7 @@
           <t>CN 27%; JP 19%; Europe 15%</t>
         </is>
       </c>
-      <c r="U45" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U45" s="15" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="13" t="n">
@@ -40796,16 +37729,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q46" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R46" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q46" s="15" t="n"/>
+      <c r="R46" s="17" t="n"/>
       <c r="S46" s="18" t="n">
         <v>4</v>
       </c>
@@ -40814,11 +37739,7 @@
           <t>Haynesville 40%; Northeast Appalachia 37%; Southwest Appalac</t>
         </is>
       </c>
-      <c r="U46" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U46" s="15" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -40966,16 +37887,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q48" s="15" t="n"/>
+      <c r="R48" s="17" t="n"/>
       <c r="S48" s="18" t="n">
         <v>6</v>
       </c>
@@ -40984,11 +37897,7 @@
           <t>US 75%; Non Us 16%; Europe 5%</t>
         </is>
       </c>
-      <c r="U48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U48" s="15" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -41136,16 +38045,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q50" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q50" s="15" t="n"/>
+      <c r="R50" s="17" t="n"/>
       <c r="S50" s="18" t="n">
         <v>5</v>
       </c>
@@ -41154,11 +38055,7 @@
           <t>US 92%; ZA 3%; BS 3%</t>
         </is>
       </c>
-      <c r="U50" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U50" s="15" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="13" t="n">
@@ -41304,16 +38201,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q52" s="15" t="n"/>
+      <c r="R52" s="17" t="n"/>
       <c r="S52" s="18" t="n">
         <v>6</v>
       </c>
@@ -41322,11 +38211,7 @@
           <t>CN 42%; US 28%; KR 27%</t>
         </is>
       </c>
-      <c r="U52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U52" s="15" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -41389,16 +38274,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q53" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q53" s="15" t="n"/>
+      <c r="R53" s="17" t="n"/>
       <c r="S53" s="18" t="n">
         <v>5</v>
       </c>
@@ -41407,11 +38284,7 @@
           <t>North America 34%; US 31%; EMEA 27%</t>
         </is>
       </c>
-      <c r="U53" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U53" s="15" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="13" t="n">
@@ -41476,16 +38349,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q54" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R54" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q54" s="15" t="n"/>
+      <c r="R54" s="17" t="n"/>
       <c r="S54" s="18" t="n">
         <v>4</v>
       </c>
@@ -41494,11 +38359,7 @@
           <t>US 45%; Europe Middle East And Africa 26%; Asia Pacific 25%</t>
         </is>
       </c>
-      <c r="U54" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U54" s="15" t="n"/>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="13" t="n">
@@ -42152,16 +39013,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q62" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q62" s="15" t="n"/>
+      <c r="R62" s="17" t="n"/>
       <c r="S62" s="18" t="n">
         <v>4</v>
       </c>
@@ -42170,11 +39023,7 @@
           <t>North America 90%; EMEA 10%; Rest Of World 0%</t>
         </is>
       </c>
-      <c r="U62" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U62" s="15" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="13" t="n">
@@ -42237,16 +39086,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q63" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R63" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q63" s="15" t="n"/>
+      <c r="R63" s="17" t="n"/>
       <c r="S63" s="18" t="n">
         <v>5</v>
       </c>
@@ -42255,11 +39096,7 @@
           <t>US 61%; Non Us 20%; Europe 13%</t>
         </is>
       </c>
-      <c r="U63" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U63" s="15" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="13" t="n">
@@ -42324,16 +39161,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q64" s="15" t="n"/>
+      <c r="R64" s="17" t="n"/>
       <c r="S64" s="18" t="n">
         <v>7</v>
       </c>
@@ -42342,11 +39171,7 @@
           <t>US 90%; Europe 5%; Asia 2%</t>
         </is>
       </c>
-      <c r="U64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U64" s="15" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n">
@@ -42537,11 +39362,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E67" s="17" t="n"/>
       <c r="F67" s="18" t="n">
         <v>10732237824</v>
       </c>
@@ -42745,16 +39566,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="Q69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="R69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="Q69" s="15" t="n"/>
+      <c r="R69" s="17" t="n"/>
       <c r="S69" s="18" t="n">
         <v>4</v>
       </c>
@@ -42763,11 +39576,7 @@
           <t>US 56%; Europe 18%; Rest Of World 18%</t>
         </is>
       </c>
-      <c r="U69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="U69" s="15" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n">
@@ -43036,7 +39845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:U72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -43062,6 +39871,7 @@
     <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -43092,6 +39902,7 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -43196,8 +40007,9 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY ETA</t>
         </is>
@@ -43407,11 +40219,7 @@
       <c r="S13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T13" s="17" t="n"/>
       <c r="U13" s="15" t="inlineStr">
         <is>
           <t>American Southern +39%</t>
@@ -43745,11 +40553,7 @@
       <c r="S17" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T17" s="17" t="n"/>
       <c r="U17" s="15" t="inlineStr">
         <is>
           <t>Commercial Banking +44%</t>
@@ -43998,11 +40802,7 @@
       <c r="S20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T20" s="17" t="n"/>
       <c r="U20" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -44087,11 +40887,7 @@
       <c r="S21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T21" s="17" t="n"/>
       <c r="U21" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -44172,11 +40968,7 @@
       <c r="S22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T22" s="17" t="n"/>
       <c r="U22" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -44255,11 +41047,7 @@
       <c r="S23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T23" s="17" t="n"/>
       <c r="U23" s="15" t="inlineStr">
         <is>
           <t>Local Distribution +26%</t>
@@ -44338,11 +41126,7 @@
       <c r="S24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T24" s="17" t="n"/>
       <c r="U24" s="15" t="inlineStr">
         <is>
           <t>Optex Systems OPX Ri +31%</t>
@@ -44421,11 +41205,7 @@
       <c r="S25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T25" s="17" t="n"/>
       <c r="U25" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -44587,11 +41367,7 @@
       <c r="S27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T27" s="17" t="n"/>
       <c r="U27" s="15" t="inlineStr">
         <is>
           <t>Hawaii Energy Connec +30%</t>
@@ -44676,11 +41452,7 @@
       <c r="S28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T28" s="17" t="n"/>
       <c r="U28" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -44761,11 +41533,7 @@
       <c r="S29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T29" s="17" t="n"/>
       <c r="U29" s="15" t="inlineStr">
         <is>
           <t>Mid Con Barnett Shal +180%</t>
@@ -45431,11 +42199,7 @@
       <c r="S37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T37" s="17" t="n"/>
       <c r="U37" s="15" t="inlineStr">
         <is>
           <t>Insurance Services +47%</t>
@@ -45514,11 +42278,7 @@
       <c r="S38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T38" s="17" t="n"/>
       <c r="U38" s="15" t="inlineStr">
         <is>
           <t>System Integration S +78%</t>
@@ -45765,11 +42525,7 @@
       <c r="S41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T41" s="17" t="n"/>
       <c r="U41" s="15" t="inlineStr">
         <is>
           <t>Medicare +62%</t>
@@ -45848,11 +42604,7 @@
       <c r="S42" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T42" s="17" t="n"/>
       <c r="U42" s="15" t="inlineStr">
         <is>
           <t>Utility Coal Mining +29%</t>
@@ -46016,11 +42768,7 @@
       <c r="S44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T44" s="17" t="n"/>
       <c r="U44" s="15" t="inlineStr">
         <is>
           <t>Timber +327%</t>
@@ -46099,11 +42847,7 @@
       <c r="S45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T45" s="17" t="n"/>
       <c r="U45" s="15" t="inlineStr">
         <is>
           <t>Shale +38%</t>
@@ -46184,11 +42928,7 @@
       <c r="S46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T46" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T46" s="17" t="n"/>
       <c r="U46" s="15" t="inlineStr">
         <is>
           <t>Eastern Hemisphere +78%</t>
@@ -46267,11 +43007,7 @@
       <c r="S47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T47" s="17" t="n"/>
       <c r="U47" s="15" t="inlineStr">
         <is>
           <t>Transmission +162%</t>
@@ -46382,11 +43118,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E49" s="17" t="n"/>
       <c r="F49" s="18" t="n">
         <v>10732237824</v>
       </c>
@@ -46603,11 +43335,7 @@
       <c r="S51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T51" s="17" t="n"/>
       <c r="U51" s="15" t="inlineStr">
         <is>
           <t>Life Sciences +32%</t>
@@ -46769,11 +43497,7 @@
       <c r="S53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T53" s="17" t="n"/>
       <c r="U53" s="15" t="inlineStr">
         <is>
           <t>Defense +43%</t>
@@ -46852,11 +43576,7 @@
       <c r="S54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T54" s="17" t="n"/>
       <c r="U54" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +56%</t>
@@ -47020,11 +43740,7 @@
       <c r="S56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T56" s="17" t="n"/>
       <c r="U56" s="15" t="inlineStr">
         <is>
           <t>Nimble Title Holding +88%</t>
@@ -47103,11 +43819,7 @@
       <c r="S57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T57" s="17" t="n"/>
       <c r="U57" s="15" t="inlineStr">
         <is>
           <t>Healthcare Services +55%</t>
@@ -47190,11 +43902,7 @@
       <c r="S58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T58" s="17" t="n"/>
       <c r="U58" s="15" t="inlineStr">
         <is>
           <t>Banking Services +34%</t>
@@ -47524,11 +44232,7 @@
       <c r="S62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T62" s="17" t="n"/>
       <c r="U62" s="15" t="inlineStr">
         <is>
           <t>Digital Assets +42%</t>
@@ -47775,11 +44479,7 @@
       <c r="S65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T65" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T65" s="17" t="n"/>
       <c r="U65" s="15" t="inlineStr">
         <is>
           <t>Subscription Operati +50%</t>
@@ -47858,11 +44558,7 @@
       <c r="S66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T66" s="17" t="n"/>
       <c r="U66" s="15" t="inlineStr">
         <is>
           <t>Owner Direct Relatio +41%</t>
@@ -47943,11 +44639,7 @@
       <c r="S67" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T67" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T67" s="17" t="n"/>
       <c r="U67" s="15" t="inlineStr">
         <is>
           <t>Security Solutions +103%</t>
@@ -48109,11 +44801,7 @@
       <c r="S69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T69" s="17" t="n"/>
       <c r="U69" s="15" t="inlineStr">
         <is>
           <t>Mobile Fuel Delivery +195%</t>
@@ -48228,11 +44916,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E71" s="17" t="n"/>
       <c r="F71" s="18" t="n">
         <v>4947405312</v>
       </c>
@@ -48364,11 +45048,7 @@
       <c r="S72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T72" s="17" t="n"/>
       <c r="U72" s="15" t="inlineStr">
         <is>
           <t>United Kingdom +43%</t>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -627,32 +627,32 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2,744</t>
+          <t>2,827</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>451</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>670</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>380</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10.9% of segment-covered</t>
+          <t>10.6% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -10946,10 +10946,8 @@
       <c r="M140" s="20" t="n">
         <v>-1.897588315217392</v>
       </c>
-      <c r="N140" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N140" s="22" t="n">
+        <v>-64.87603317998357</v>
       </c>
       <c r="O140" s="18" t="n">
         <v>2</v>
@@ -17397,10 +17395,8 @@
       <c r="M223" s="20" t="n">
         <v>-0.1533199794407697</v>
       </c>
-      <c r="N223" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N223" s="22" t="n">
+        <v>-15.78947450975963</v>
       </c>
       <c r="O223" s="18" t="n">
         <v>0</v>
@@ -24344,7 +24340,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.2% of segment-covered</t>
+          <t>2.1% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -29578,7 +29574,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.2% of segment-covered</t>
+          <t>2.1% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -31461,10 +31457,8 @@
       <c r="M33" s="20" t="n">
         <v>-1.897588315217392</v>
       </c>
-      <c r="N33" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N33" s="22" t="n">
+        <v>-64.87603317998357</v>
       </c>
       <c r="O33" s="18" t="n">
         <v>2</v>
@@ -34808,7 +34802,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.2% of segment-covered</t>
+          <t>2.1% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -39960,7 +39954,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.2% of segment-covered</t>
+          <t>2.1% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -8918,12 +8918,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>COSO</t>
+          <t>SIEB</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>CoastalSouth Bancshares, Inc.</t>
+          <t>Siebert Financial Corp.</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="F114" s="18" t="n">
-        <v>326702400</v>
+        <v>69599592</v>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
@@ -8949,43 +8949,53 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I114" s="20" t="n">
-        <v>12.204545</v>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>-21.25150433941449</v>
-      </c>
-      <c r="K114" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I114" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J114" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K114" s="22" t="n">
+        <v>5.17888936540735</v>
       </c>
       <c r="L114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.23199371130981</v>
+      </c>
+      <c r="M114" s="20" t="n">
+        <v>-1.897588315217392</v>
       </c>
       <c r="N114" s="22" t="n">
-        <v>26.10063202591439</v>
+        <v>-64.87603317998357</v>
       </c>
       <c r="O114" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q114" s="15" t="n"/>
-      <c r="R114" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="P114" s="20" t="n">
+        <v>0.9865046689171856</v>
+      </c>
+      <c r="Q114" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services (99%)</t>
+        </is>
+      </c>
+      <c r="R114" s="17" t="inlineStr">
+        <is>
+          <t>Financial Services 99%; Media Sports And Entertainment 1%</t>
+        </is>
+      </c>
       <c r="S114" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T114" s="17" t="n"/>
-      <c r="U114" s="15" t="n"/>
+      <c r="U114" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services +11%</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n">
@@ -8993,12 +9003,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>GENC</t>
+          <t>COSO</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>Gencor Industries, Inc.</t>
+          <t>CoastalSouth Bancshares, Inc.</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -9008,37 +9018,43 @@
       </c>
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F115" s="18" t="n">
-        <v>222503920</v>
+        <v>326702400</v>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H115" s="20" t="n">
-        <v>5.414</v>
+      <c r="H115" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I115" s="20" t="n">
-        <v>17.056181</v>
+        <v>12.204545</v>
       </c>
       <c r="J115" s="22" t="n">
-        <v>10.74008646076678</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>9.653633066284021</v>
+        <v>-21.25150433941449</v>
+      </c>
+      <c r="K115" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L115" s="22" t="n">
-        <v>13.72795033364932</v>
-      </c>
-      <c r="M115" s="20" t="n">
-        <v>-9.984835149955996</v>
+        <v>0</v>
+      </c>
+      <c r="M115" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N115" s="22" t="n">
-        <v>3.9158808074461</v>
+        <v>26.10063202591439</v>
       </c>
       <c r="O115" s="18" t="n">
         <v>0</v>
@@ -9062,12 +9078,12 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>CRMD</t>
+          <t>GENC</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>CorMedix Inc.</t>
+          <t>Gencor Industries, Inc.</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
@@ -9077,37 +9093,37 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F116" s="18" t="n">
-        <v>615847296</v>
-      </c>
-      <c r="G116" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>222503920</v>
+      </c>
+      <c r="G116" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H116" s="20" t="n">
-        <v>2.558</v>
+        <v>5.414</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>3.6175113</v>
+        <v>17.056181</v>
       </c>
       <c r="J116" s="22" t="n">
-        <v>10.76033467943529</v>
+        <v>10.74008646076678</v>
       </c>
       <c r="K116" s="22" t="n">
-        <v>59.72797205767642</v>
+        <v>9.653633066284021</v>
       </c>
       <c r="L116" s="22" t="n">
-        <v>53.68693204238568</v>
+        <v>13.72795033364932</v>
       </c>
       <c r="M116" s="20" t="n">
-        <v>0.0022886577129476</v>
+        <v>-9.984835149955996</v>
       </c>
       <c r="N116" s="22" t="n">
-        <v>-35.4148805667681</v>
+        <v>3.9158808074461</v>
       </c>
       <c r="O116" s="18" t="n">
         <v>0</v>
@@ -9131,12 +9147,12 @@
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>SMID</t>
+          <t>CRMD</t>
         </is>
       </c>
       <c r="C117" s="15" t="inlineStr">
         <is>
-          <t>Smith-Midland Corporation</t>
+          <t>CorMedix Inc.</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
@@ -9146,11 +9162,11 @@
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F117" s="18" t="n">
-        <v>157869984</v>
+        <v>615847296</v>
       </c>
       <c r="G117" s="24" t="inlineStr">
         <is>
@@ -9158,25 +9174,25 @@
         </is>
       </c>
       <c r="H117" s="20" t="n">
-        <v>8.513999999999999</v>
+        <v>2.558</v>
       </c>
       <c r="I117" s="20" t="n">
-        <v>15.025252</v>
+        <v>3.6175113</v>
       </c>
       <c r="J117" s="22" t="n">
-        <v>-1.33140004307622</v>
+        <v>10.76033467943529</v>
       </c>
       <c r="K117" s="22" t="n">
-        <v>23.5026343072573</v>
+        <v>59.72797205767642</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>21.55148427969094</v>
+        <v>53.68693204238568</v>
       </c>
       <c r="M117" s="20" t="n">
-        <v>-0.3648145389542678</v>
+        <v>0.0022886577129476</v>
       </c>
       <c r="N117" s="22" t="n">
-        <v>-5.50939003710083</v>
+        <v>-35.4148805667681</v>
       </c>
       <c r="O117" s="18" t="n">
         <v>0</v>
@@ -9200,12 +9216,12 @@
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>TRST</t>
+          <t>SMID</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>TrustCo Bank Corp NY</t>
+          <t>Smith-Midland Corporation</t>
         </is>
       </c>
       <c r="D118" s="16" t="inlineStr">
@@ -9215,43 +9231,37 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F118" s="18" t="n">
-        <v>955173248</v>
-      </c>
-      <c r="G118" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="H118" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>157869984</v>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="H118" s="20" t="n">
+        <v>8.513999999999999</v>
       </c>
       <c r="I118" s="20" t="n">
-        <v>16.029325</v>
+        <v>15.025252</v>
       </c>
       <c r="J118" s="22" t="n">
-        <v>5.41001892070669</v>
-      </c>
-      <c r="K118" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-1.33140004307622</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>23.5026343072573</v>
       </c>
       <c r="L118" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.55148427969094</v>
+      </c>
+      <c r="M118" s="20" t="n">
+        <v>-0.3648145389542678</v>
       </c>
       <c r="N118" s="22" t="n">
-        <v>54.78020860532192</v>
+        <v>-5.50939003710083</v>
       </c>
       <c r="O118" s="18" t="n">
         <v>0</v>
@@ -9275,12 +9285,12 @@
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>QTWO</t>
+          <t>TRST</t>
         </is>
       </c>
       <c r="C119" s="15" t="inlineStr">
         <is>
-          <t>Q2 Holdings, Inc.</t>
+          <t>TrustCo Bank Corp NY</t>
         </is>
       </c>
       <c r="D119" s="16" t="inlineStr">
@@ -9290,37 +9300,43 @@
       </c>
       <c r="E119" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F119" s="18" t="n">
-        <v>2999186432</v>
-      </c>
-      <c r="G119" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="H119" s="20" t="n">
-        <v>30.444</v>
+        <v>955173248</v>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="H119" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I119" s="20" t="n">
-        <v>42.39823</v>
+        <v>16.029325</v>
       </c>
       <c r="J119" s="22" t="n">
-        <v>3.71867384690194</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>18.83167993346798</v>
+        <v>5.41001892070669</v>
+      </c>
+      <c r="K119" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L119" s="22" t="n">
-        <v>16.52474500352978</v>
-      </c>
-      <c r="M119" s="20" t="n">
-        <v>-0.2577192775699007</v>
+        <v>0</v>
+      </c>
+      <c r="M119" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N119" s="22" t="n">
-        <v>-47.170678900731</v>
+        <v>54.78020860532192</v>
       </c>
       <c r="O119" s="18" t="n">
         <v>0</v>
@@ -9344,12 +9360,12 @@
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>SUNE</t>
+          <t>QTWO</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>SUNation Energy Inc. Common St</t>
+          <t>Q2 Holdings, Inc.</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
@@ -9359,63 +9375,53 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F120" s="18" t="n">
-        <v>10143001</v>
-      </c>
-      <c r="G120" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>2999186432</v>
+      </c>
+      <c r="G120" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H120" s="20" t="n">
-        <v>-1.219154062695544</v>
+        <v>30.444</v>
       </c>
       <c r="I120" s="20" t="n">
-        <v>0.024325127</v>
+        <v>42.39823</v>
       </c>
       <c r="J120" s="22" t="n">
-        <v>-202.6520054738409</v>
+        <v>3.71867384690194</v>
       </c>
       <c r="K120" s="22" t="n">
-        <v>-35.17300762638625</v>
+        <v>18.83167993346798</v>
       </c>
       <c r="L120" s="22" t="n">
-        <v>-9.68347120242926</v>
+        <v>16.52474500352978</v>
       </c>
       <c r="M120" s="20" t="n">
-        <v>-0.4118934629871731</v>
+        <v>-0.2577192775699007</v>
       </c>
       <c r="N120" s="22" t="n">
-        <v>-19.51219441279421</v>
+        <v>-47.170678900731</v>
       </c>
       <c r="O120" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="P120" s="20" t="n">
-        <v>0.5750863857690269</v>
-      </c>
-      <c r="Q120" s="15" t="inlineStr">
-        <is>
-          <t>Sunation NY (69%)</t>
-        </is>
-      </c>
-      <c r="R120" s="17" t="inlineStr">
-        <is>
-          <t>Sunation NY 69%; Hawaii Energy Connection 31%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P120" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q120" s="15" t="n"/>
+      <c r="R120" s="17" t="n"/>
       <c r="S120" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T120" s="17" t="n"/>
-      <c r="U120" s="15" t="inlineStr">
-        <is>
-          <t>Hawaii Energy Connec +30%</t>
-        </is>
-      </c>
+      <c r="U120" s="15" t="n"/>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="13" t="n">
@@ -9423,12 +9429,12 @@
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>FRSH</t>
+          <t>SUNE</t>
         </is>
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>Freshworks Inc. Class A Common</t>
+          <t>SUNation Energy Inc. Common St</t>
         </is>
       </c>
       <c r="D121" s="16" t="inlineStr">
@@ -9438,11 +9444,11 @@
       </c>
       <c r="E121" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F121" s="18" t="n">
-        <v>2722876672</v>
+        <v>10143001</v>
       </c>
       <c r="G121" s="19" t="inlineStr">
         <is>
@@ -9450,45 +9456,51 @@
         </is>
       </c>
       <c r="H121" s="20" t="n">
-        <v>57.225</v>
+        <v>-1.219154062695544</v>
       </c>
       <c r="I121" s="20" t="n">
-        <v>16.147541</v>
+        <v>0.024325127</v>
       </c>
       <c r="J121" s="22" t="n">
-        <v>8.84784932596617</v>
+        <v>-202.6520054738409</v>
       </c>
       <c r="K121" s="22" t="n">
-        <v>5.582241290864149</v>
+        <v>-35.17300762638625</v>
       </c>
       <c r="L121" s="22" t="n">
-        <v>4.92682820440121</v>
+        <v>-9.68347120242926</v>
       </c>
       <c r="M121" s="20" t="n">
-        <v>-17.25127559935696</v>
+        <v>-0.4118934629871731</v>
       </c>
       <c r="N121" s="22" t="n">
-        <v>-37.93574946904199</v>
+        <v>-19.51219441279421</v>
       </c>
       <c r="O121" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q121" s="15" t="n"/>
-      <c r="R121" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="P121" s="20" t="n">
+        <v>0.5750863857690269</v>
+      </c>
+      <c r="Q121" s="15" t="inlineStr">
+        <is>
+          <t>Sunation NY (69%)</t>
+        </is>
+      </c>
+      <c r="R121" s="17" t="inlineStr">
+        <is>
+          <t>Sunation NY 69%; Hawaii Energy Connection 31%</t>
+        </is>
+      </c>
       <c r="S121" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="T121" s="17" t="inlineStr">
-        <is>
-          <t>North America 30%; US 27%; EMEA 25%</t>
-        </is>
-      </c>
-      <c r="U121" s="15" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="T121" s="17" t="n"/>
+      <c r="U121" s="15" t="inlineStr">
+        <is>
+          <t>Hawaii Energy Connec +30%</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="13" t="n">
@@ -9496,12 +9508,12 @@
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>WSFS</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>WSFS Financial Corporation</t>
+          <t>Freshworks Inc. Class A Common</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
@@ -9511,69 +9523,57 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F122" s="18" t="n">
-        <v>4026127616</v>
+        <v>2722876672</v>
       </c>
       <c r="G122" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H122" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H122" s="20" t="n">
+        <v>57.225</v>
       </c>
       <c r="I122" s="20" t="n">
-        <v>13.789661</v>
+        <v>16.147541</v>
       </c>
       <c r="J122" s="22" t="n">
-        <v>6.158366732153779</v>
-      </c>
-      <c r="K122" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.84784932596617</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>5.582241290864149</v>
       </c>
       <c r="L122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.92682820440121</v>
+      </c>
+      <c r="M122" s="20" t="n">
+        <v>-17.25127559935696</v>
       </c>
       <c r="N122" s="22" t="n">
-        <v>37.01048893948796</v>
+        <v>-37.93574946904199</v>
       </c>
       <c r="O122" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P122" s="20" t="n">
-        <v>0.5461404223281471</v>
-      </c>
-      <c r="Q122" s="15" t="inlineStr">
-        <is>
-          <t>Wsfs Bank (70%)</t>
-        </is>
-      </c>
-      <c r="R122" s="17" t="inlineStr">
-        <is>
-          <t>Wsfs Bank 70%; Wealth Management 22%; Cash Connect 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P122" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q122" s="15" t="n"/>
+      <c r="R122" s="17" t="n"/>
       <c r="S122" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="17" t="n"/>
-      <c r="U122" s="15" t="inlineStr">
-        <is>
-          <t>Wealth Management +15%</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="T122" s="17" t="inlineStr">
+        <is>
+          <t>North America 30%; US 27%; EMEA 25%</t>
+        </is>
+      </c>
+      <c r="U122" s="15" t="n"/>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="13" t="n">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>RXST</t>
+          <t>WSFS</t>
         </is>
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>RxSight Inc. Common Stock</t>
+          <t>WSFS Financial Corporation</t>
         </is>
       </c>
       <c r="D123" s="16" t="inlineStr">
@@ -9596,55 +9596,69 @@
       </c>
       <c r="E123" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F123" s="18" t="n">
-        <v>221885824</v>
+        <v>4026127616</v>
       </c>
       <c r="G123" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H123" s="20" t="n">
-        <v>-0.7888837692804765</v>
-      </c>
-      <c r="I123" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I123" s="20" t="n">
+        <v>13.789661</v>
       </c>
       <c r="J123" s="22" t="n">
-        <v>-8.225567245596439</v>
-      </c>
-      <c r="K123" s="22" t="n">
-        <v>-66.3179452171687</v>
+        <v>6.158366732153779</v>
+      </c>
+      <c r="K123" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L123" s="22" t="n">
-        <v>-26.46713265913147</v>
-      </c>
-      <c r="M123" s="20" t="n">
-        <v>6.099176804427837</v>
+        <v>0</v>
+      </c>
+      <c r="M123" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N123" s="22" t="n">
-        <v>-57.32532194388769</v>
+        <v>37.01048893948796</v>
       </c>
       <c r="O123" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q123" s="15" t="n"/>
-      <c r="R123" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="P123" s="20" t="n">
+        <v>0.5461404223281471</v>
+      </c>
+      <c r="Q123" s="15" t="inlineStr">
+        <is>
+          <t>Wsfs Bank (70%)</t>
+        </is>
+      </c>
+      <c r="R123" s="17" t="inlineStr">
+        <is>
+          <t>Wsfs Bank 70%; Wealth Management 22%; Cash Connect 8%</t>
+        </is>
+      </c>
       <c r="S123" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T123" s="17" t="n"/>
-      <c r="U123" s="15" t="n"/>
+      <c r="U123" s="15" t="inlineStr">
+        <is>
+          <t>Wealth Management +15%</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="13" t="n">
@@ -9652,12 +9666,12 @@
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>ACCS</t>
+          <t>RXST</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>ACCESS Newswire Inc. Common St</t>
+          <t>RxSight Inc. Common Stock</t>
         </is>
       </c>
       <c r="D124" s="16" t="inlineStr">
@@ -9667,11 +9681,11 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F124" s="18" t="n">
-        <v>26553866</v>
+        <v>221885824</v>
       </c>
       <c r="G124" s="19" t="inlineStr">
         <is>
@@ -9679,7 +9693,7 @@
         </is>
       </c>
       <c r="H124" s="20" t="n">
-        <v>20.806</v>
+        <v>-0.7888837692804765</v>
       </c>
       <c r="I124" s="21" t="inlineStr">
         <is>
@@ -9687,19 +9701,19 @@
         </is>
       </c>
       <c r="J124" s="22" t="n">
-        <v>10.91194270159679</v>
+        <v>-8.225567245596439</v>
       </c>
       <c r="K124" s="22" t="n">
-        <v>-6.34942688433483</v>
+        <v>-66.3179452171687</v>
       </c>
       <c r="L124" s="22" t="n">
-        <v>4.30169326672266</v>
+        <v>-26.46713265913147</v>
       </c>
       <c r="M124" s="20" t="n">
-        <v>-0.1562178828365878</v>
+        <v>6.099176804427837</v>
       </c>
       <c r="N124" s="22" t="n">
-        <v>-25.5839796713547</v>
+        <v>-57.32532194388769</v>
       </c>
       <c r="O124" s="18" t="n">
         <v>0</v>
@@ -9723,12 +9737,12 @@
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>TACT</t>
+          <t>ACCS</t>
         </is>
       </c>
       <c r="C125" s="15" t="inlineStr">
         <is>
-          <t>TransAct Technologies Incorpor</t>
+          <t>ACCESS Newswire Inc. Common St</t>
         </is>
       </c>
       <c r="D125" s="16" t="inlineStr">
@@ -9738,11 +9752,11 @@
       </c>
       <c r="E125" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F125" s="18" t="n">
-        <v>54515660</v>
+        <v>26553866</v>
       </c>
       <c r="G125" s="19" t="inlineStr">
         <is>
@@ -9750,55 +9764,43 @@
         </is>
       </c>
       <c r="H125" s="20" t="n">
-        <v>15.2490059473237</v>
-      </c>
-      <c r="I125" s="20" t="n">
-        <v>55.99555555555556</v>
+        <v>20.806</v>
+      </c>
+      <c r="I125" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J125" s="22" t="n">
-        <v>-10.67708135131403</v>
+        <v>10.91194270159679</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>3.8075407154012</v>
+        <v>-6.34942688433483</v>
       </c>
       <c r="L125" s="22" t="n">
-        <v>-0.14180264180264</v>
+        <v>4.30169326672266</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>231.1232876712329</v>
+        <v>-0.1562178828365878</v>
       </c>
       <c r="N125" s="22" t="n">
-        <v>2.28571210588727</v>
+        <v>-25.5839796713547</v>
       </c>
       <c r="O125" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P125" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q125" s="15" t="inlineStr">
-        <is>
-          <t>Transact (100%)</t>
-        </is>
-      </c>
-      <c r="R125" s="17" t="inlineStr">
-        <is>
-          <t>Transact 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P125" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q125" s="15" t="n"/>
+      <c r="R125" s="17" t="n"/>
       <c r="S125" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T125" s="17" t="inlineStr">
-        <is>
-          <t>US 80%; Non Us 20%</t>
-        </is>
-      </c>
-      <c r="U125" s="15" t="inlineStr">
-        <is>
-          <t>Transact +19%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T125" s="17" t="n"/>
+      <c r="U125" s="15" t="n"/>
     </row>
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="13" t="n">
@@ -9806,12 +9808,12 @@
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>NBBK</t>
+          <t>TACT</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>NB Bancorp Inc. Common Stock</t>
+          <t>TransAct Technologies Incorpor</t>
         </is>
       </c>
       <c r="D126" s="16" t="inlineStr">
@@ -9821,59 +9823,67 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F126" s="18" t="n">
-        <v>933929408</v>
+        <v>54515660</v>
       </c>
       <c r="G126" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H126" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H126" s="20" t="n">
+        <v>15.2490059473237</v>
       </c>
       <c r="I126" s="20" t="n">
-        <v>15.547444</v>
+        <v>55.99555555555556</v>
       </c>
       <c r="J126" s="22" t="n">
-        <v>6.8259973458476</v>
-      </c>
-      <c r="K126" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-10.67708135131403</v>
+      </c>
+      <c r="K126" s="22" t="n">
+        <v>3.8075407154012</v>
       </c>
       <c r="L126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-0.14180264180264</v>
+      </c>
+      <c r="M126" s="20" t="n">
+        <v>231.1232876712329</v>
       </c>
       <c r="N126" s="22" t="n">
-        <v>9.52875917003306</v>
+        <v>2.28571210588727</v>
       </c>
       <c r="O126" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q126" s="15" t="n"/>
-      <c r="R126" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="P126" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q126" s="15" t="inlineStr">
+        <is>
+          <t>Transact (100%)</t>
+        </is>
+      </c>
+      <c r="R126" s="17" t="inlineStr">
+        <is>
+          <t>Transact 100%</t>
+        </is>
+      </c>
       <c r="S126" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="17" t="n"/>
-      <c r="U126" s="15" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="T126" s="17" t="inlineStr">
+        <is>
+          <t>US 80%; Non Us 20%</t>
+        </is>
+      </c>
+      <c r="U126" s="15" t="inlineStr">
+        <is>
+          <t>Transact +19%</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="13" t="n">
@@ -9881,12 +9891,12 @@
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>ACRV</t>
+          <t>NBBK</t>
         </is>
       </c>
       <c r="C127" s="15" t="inlineStr">
         <is>
-          <t>Acrivon Therapeutics Inc. Comm</t>
+          <t>NB Bancorp Inc. Common Stock</t>
         </is>
       </c>
       <c r="D127" s="16" t="inlineStr">
@@ -9896,39 +9906,43 @@
       </c>
       <c r="E127" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F127" s="18" t="n">
-        <v>71906904</v>
+        <v>933929408</v>
       </c>
       <c r="G127" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H127" s="20" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="I127" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H127" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I127" s="20" t="n">
+        <v>15.547444</v>
       </c>
       <c r="J127" s="22" t="n">
-        <v>-86.23919495512193</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>2505.630026809652</v>
+        <v>6.8259973458476</v>
+      </c>
+      <c r="K127" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L127" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M127" s="20" t="n">
-        <v>1.400142584402716</v>
+      <c r="M127" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N127" s="22" t="n">
-        <v>60.9090856875271</v>
+        <v>9.52875917003306</v>
       </c>
       <c r="O127" s="18" t="n">
         <v>0</v>
@@ -9952,12 +9966,12 @@
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>BOOM</t>
+          <t>ACRV</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>DMC Global Inc.</t>
+          <t>Acrivon Therapeutics Inc. Comm</t>
         </is>
       </c>
       <c r="D128" s="16" t="inlineStr">
@@ -9967,11 +9981,11 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F128" s="18" t="n">
-        <v>123836296</v>
+        <v>71906904</v>
       </c>
       <c r="G128" s="19" t="inlineStr">
         <is>
@@ -9979,7 +9993,7 @@
         </is>
       </c>
       <c r="H128" s="20" t="n">
-        <v>13.541</v>
+        <v>0.289</v>
       </c>
       <c r="I128" s="21" t="inlineStr">
         <is>
@@ -9987,49 +10001,35 @@
         </is>
       </c>
       <c r="J128" s="22" t="n">
-        <v>8.129076452317911</v>
+        <v>-86.23919495512193</v>
       </c>
       <c r="K128" s="22" t="n">
-        <v>2.69253759150435</v>
+        <v>2505.630026809652</v>
       </c>
       <c r="L128" s="22" t="n">
-        <v>3.75265505975483</v>
+        <v>0</v>
       </c>
       <c r="M128" s="20" t="n">
-        <v>1.020321876704855</v>
+        <v>1.400142584402716</v>
       </c>
       <c r="N128" s="22" t="n">
-        <v>1.0204036947789</v>
+        <v>60.9090856875271</v>
       </c>
       <c r="O128" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P128" s="20" t="n">
-        <v>0.3822472055915061</v>
-      </c>
-      <c r="Q128" s="15" t="inlineStr">
-        <is>
-          <t>Dyna Energetics (44%)</t>
-        </is>
-      </c>
-      <c r="R128" s="17" t="inlineStr">
-        <is>
-          <t>Dyna Energetics 44%; Arcadia Products 40%; Nobel Clad 15%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P128" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q128" s="15" t="n"/>
+      <c r="R128" s="17" t="n"/>
       <c r="S128" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="T128" s="17" t="inlineStr">
-        <is>
-          <t>US 41%; West 33%; Rest Of The World 5%</t>
-        </is>
-      </c>
-      <c r="U128" s="15" t="inlineStr">
-        <is>
-          <t>Arcadia Products -1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T128" s="17" t="n"/>
+      <c r="U128" s="15" t="n"/>
     </row>
     <row r="129" ht="16" customHeight="1">
       <c r="A129" s="13" t="n">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>NRIM</t>
+          <t>BOOM</t>
         </is>
       </c>
       <c r="C129" s="15" t="inlineStr">
         <is>
-          <t>Northrim BanCorp, Inc.</t>
+          <t>DMC Global Inc.</t>
         </is>
       </c>
       <c r="D129" s="16" t="inlineStr">
@@ -10052,67 +10052,67 @@
       </c>
       <c r="E129" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F129" s="18" t="n">
-        <v>621963648</v>
+        <v>123836296</v>
       </c>
       <c r="G129" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H129" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I129" s="20" t="n">
-        <v>9.708333</v>
+      <c r="H129" s="20" t="n">
+        <v>13.541</v>
+      </c>
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J129" s="22" t="n">
-        <v>7.154905282262169</v>
-      </c>
-      <c r="K129" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.129076452317911</v>
+      </c>
+      <c r="K129" s="22" t="n">
+        <v>2.69253759150435</v>
       </c>
       <c r="L129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.75265505975483</v>
+      </c>
+      <c r="M129" s="20" t="n">
+        <v>1.020321876704855</v>
       </c>
       <c r="N129" s="22" t="n">
-        <v>7.62249350229726</v>
+        <v>1.0204036947789</v>
       </c>
       <c r="O129" s="18" t="n">
         <v>3</v>
       </c>
       <c r="P129" s="20" t="n">
-        <v>0.6090673877493771</v>
+        <v>0.3822472055915061</v>
       </c>
       <c r="Q129" s="15" t="inlineStr">
         <is>
-          <t>Community Banking (76%)</t>
+          <t>Dyna Energetics (44%)</t>
         </is>
       </c>
       <c r="R129" s="17" t="inlineStr">
         <is>
-          <t>Community Banking 76%; Home Mortgage Lending 17%; Specialty Finance 7%</t>
+          <t>Dyna Energetics 44%; Arcadia Products 40%; Nobel Clad 15%</t>
         </is>
       </c>
       <c r="S129" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="17" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="T129" s="17" t="inlineStr">
+        <is>
+          <t>US 41%; West 33%; Rest Of The World 5%</t>
+        </is>
+      </c>
       <c r="U129" s="15" t="inlineStr">
         <is>
-          <t>Specialty Finance +257%</t>
+          <t>Arcadia Products -1%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>PASG</t>
+          <t>NRIM</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Passage Bio, Inc.</t>
+          <t>Northrim BanCorp, Inc.</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
@@ -10137,55 +10137,69 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F130" s="18" t="n">
-        <v>15100206</v>
+        <v>621963648</v>
       </c>
       <c r="G130" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H130" s="20" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="I130" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H130" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I130" s="20" t="n">
+        <v>9.708333</v>
       </c>
       <c r="J130" s="22" t="n">
-        <v>-188.1721537819593</v>
-      </c>
-      <c r="K130" s="22" t="n">
-        <v>1219.643866591294</v>
+        <v>7.154905282262169</v>
+      </c>
+      <c r="K130" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L130" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M130" s="20" t="n">
-        <v>0.5254932465879358</v>
+      <c r="M130" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N130" s="22" t="n">
-        <v>-12.12121649988203</v>
+        <v>7.62249350229726</v>
       </c>
       <c r="O130" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q130" s="15" t="n"/>
-      <c r="R130" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="P130" s="20" t="n">
+        <v>0.6090673877493771</v>
+      </c>
+      <c r="Q130" s="15" t="inlineStr">
+        <is>
+          <t>Community Banking (76%)</t>
+        </is>
+      </c>
+      <c r="R130" s="17" t="inlineStr">
+        <is>
+          <t>Community Banking 76%; Home Mortgage Lending 17%; Specialty Finance 7%</t>
+        </is>
+      </c>
       <c r="S130" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T130" s="17" t="n"/>
-      <c r="U130" s="15" t="n"/>
+      <c r="U130" s="15" t="inlineStr">
+        <is>
+          <t>Specialty Finance +257%</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="13" t="n">
@@ -10193,12 +10207,12 @@
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>PASG</t>
         </is>
       </c>
       <c r="C131" s="15" t="inlineStr">
         <is>
-          <t>Rigel Pharmaceuticals, Inc.</t>
+          <t>Passage Bio, Inc.</t>
         </is>
       </c>
       <c r="D131" s="16" t="inlineStr">
@@ -10212,7 +10226,7 @@
         </is>
       </c>
       <c r="F131" s="18" t="n">
-        <v>715845440</v>
+        <v>15100206</v>
       </c>
       <c r="G131" s="19" t="inlineStr">
         <is>
@@ -10220,51 +10234,43 @@
         </is>
       </c>
       <c r="H131" s="20" t="n">
-        <v>4.842</v>
-      </c>
-      <c r="I131" s="20" t="n">
-        <v>2.0057023</v>
+        <v>0.333</v>
+      </c>
+      <c r="I131" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J131" s="22" t="n">
-        <v>-1.43550383550229</v>
+        <v>-188.1721537819593</v>
       </c>
       <c r="K131" s="22" t="n">
-        <v>27.15453070970258</v>
+        <v>1219.643866591294</v>
       </c>
       <c r="L131" s="22" t="n">
-        <v>43.79434694279223</v>
+        <v>0</v>
       </c>
       <c r="M131" s="20" t="n">
-        <v>0.1557346455313411</v>
+        <v>0.5254932465879358</v>
       </c>
       <c r="N131" s="22" t="n">
-        <v>46.96048918565198</v>
+        <v>-12.12121649988203</v>
       </c>
       <c r="O131" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P131" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q131" s="15" t="inlineStr">
-        <is>
-          <t>Single Reportable (100%)</t>
-        </is>
-      </c>
-      <c r="R131" s="17" t="inlineStr">
-        <is>
-          <t>Single Reportable 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P131" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q131" s="15" t="n"/>
+      <c r="R131" s="17" t="n"/>
       <c r="S131" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T131" s="17" t="n"/>
-      <c r="U131" s="15" t="inlineStr">
-        <is>
-          <t>Single Reportable +64%</t>
-        </is>
-      </c>
+      <c r="U131" s="15" t="n"/>
     </row>
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="13" t="n">
@@ -10272,12 +10278,12 @@
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>CATO</t>
+          <t>RIGL</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>The Cato Corporation</t>
+          <t>Rigel Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="D132" s="16" t="inlineStr">
@@ -10287,11 +10293,11 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F132" s="18" t="n">
-        <v>66662584</v>
+        <v>715845440</v>
       </c>
       <c r="G132" s="19" t="inlineStr">
         <is>
@@ -10299,40 +10305,40 @@
         </is>
       </c>
       <c r="H132" s="20" t="n">
-        <v>134.466</v>
+        <v>4.842</v>
       </c>
       <c r="I132" s="20" t="n">
-        <v>2.916295653927599</v>
+        <v>2.0057023</v>
       </c>
       <c r="J132" s="22" t="n">
-        <v>34.35404370485792</v>
+        <v>-1.43550383550229</v>
       </c>
       <c r="K132" s="22" t="n">
-        <v>6.90904715732555</v>
+        <v>27.15453070970258</v>
       </c>
       <c r="L132" s="22" t="n">
-        <v>0.39782078028546</v>
+        <v>43.79434694279223</v>
       </c>
       <c r="M132" s="20" t="n">
-        <v>29.52748942714341</v>
+        <v>0.1557346455313411</v>
       </c>
       <c r="N132" s="22" t="n">
-        <v>6.521741571708831</v>
+        <v>46.96048918565198</v>
       </c>
       <c r="O132" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P132" s="20" t="n">
-        <v>0.9920879293908172</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segments Re (100%)</t>
+          <t>Single Reportable (100%)</t>
         </is>
       </c>
       <c r="R132" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segments Retail 100%; Reportable Segments Credit 0%</t>
+          <t>Single Reportable 100%</t>
         </is>
       </c>
       <c r="S132" s="18" t="n">
@@ -10341,7 +10347,7 @@
       <c r="T132" s="17" t="n"/>
       <c r="U132" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segments  +1%</t>
+          <t>Single Reportable +64%</t>
         </is>
       </c>
     </row>
@@ -10351,12 +10357,12 @@
       </c>
       <c r="B133" s="14" t="inlineStr">
         <is>
-          <t>AKBA</t>
+          <t>CATO</t>
         </is>
       </c>
       <c r="C133" s="15" t="inlineStr">
         <is>
-          <t>Akebia Therapeutics, Inc.</t>
+          <t>The Cato Corporation</t>
         </is>
       </c>
       <c r="D133" s="16" t="inlineStr">
@@ -10366,11 +10372,11 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F133" s="18" t="n">
-        <v>305814400</v>
+        <v>66662584</v>
       </c>
       <c r="G133" s="19" t="inlineStr">
         <is>
@@ -10378,42 +10384,40 @@
         </is>
       </c>
       <c r="H133" s="20" t="n">
-        <v>28.087</v>
-      </c>
-      <c r="I133" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>134.466</v>
+      </c>
+      <c r="I133" s="20" t="n">
+        <v>2.916295653927599</v>
       </c>
       <c r="J133" s="22" t="n">
-        <v>21.06320195668403</v>
+        <v>34.35404370485792</v>
       </c>
       <c r="K133" s="22" t="n">
-        <v>-20.3691903301605</v>
+        <v>6.90904715732555</v>
       </c>
       <c r="L133" s="22" t="n">
-        <v>9.19871632034412</v>
+        <v>0.39782078028546</v>
       </c>
       <c r="M133" s="20" t="n">
-        <v>-6.123532931375708</v>
+        <v>29.52748942714341</v>
       </c>
       <c r="N133" s="22" t="n">
-        <v>-58.26771816145106</v>
+        <v>6.521741571708831</v>
       </c>
       <c r="O133" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P133" s="20" t="n">
-        <v>1</v>
+        <v>0.9920879293908172</v>
       </c>
       <c r="Q133" s="15" t="inlineStr">
         <is>
-          <t>Reportable (100%)</t>
+          <t>Reportable Segments Re (100%)</t>
         </is>
       </c>
       <c r="R133" s="17" t="inlineStr">
         <is>
-          <t>Reportable 100%</t>
+          <t>Reportable Segments Retail 100%; Reportable Segments Credit 0%</t>
         </is>
       </c>
       <c r="S133" s="18" t="n">
@@ -10422,7 +10426,7 @@
       <c r="T133" s="17" t="n"/>
       <c r="U133" s="15" t="inlineStr">
         <is>
-          <t>Reportable -77%</t>
+          <t>Reportable Segments  +1%</t>
         </is>
       </c>
     </row>
@@ -10432,12 +10436,12 @@
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>AKBA</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Sirius XM Holdings Inc.</t>
+          <t>Akebia Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D134" s="16" t="inlineStr">
@@ -10447,11 +10451,11 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F134" s="18" t="n">
-        <v>9543175168</v>
+        <v>305814400</v>
       </c>
       <c r="G134" s="19" t="inlineStr">
         <is>
@@ -10459,40 +10463,42 @@
         </is>
       </c>
       <c r="H134" s="20" t="n">
-        <v>7.839</v>
-      </c>
-      <c r="I134" s="20" t="n">
-        <v>12.0127125</v>
+        <v>28.087</v>
+      </c>
+      <c r="I134" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J134" s="22" t="n">
-        <v>12.80212302889506</v>
+        <v>21.06320195668403</v>
       </c>
       <c r="K134" s="22" t="n">
-        <v>10.57658645741083</v>
+        <v>-20.3691903301605</v>
       </c>
       <c r="L134" s="22" t="n">
-        <v>25.19519869479081</v>
+        <v>9.19871632034412</v>
       </c>
       <c r="M134" s="20" t="n">
-        <v>4.4736355226642</v>
+        <v>-6.123532931375708</v>
       </c>
       <c r="N134" s="22" t="n">
-        <v>37.51723087267589</v>
+        <v>-58.26771816145106</v>
       </c>
       <c r="O134" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P134" s="20" t="n">
-        <v>0.6308860972502057</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="15" t="inlineStr">
         <is>
-          <t>Sirius XM (76%)</t>
+          <t>Reportable (100%)</t>
         </is>
       </c>
       <c r="R134" s="17" t="inlineStr">
         <is>
-          <t>Sirius XM 76%; Pandora And Off Platform 24%</t>
+          <t>Reportable 100%</t>
         </is>
       </c>
       <c r="S134" s="18" t="n">
@@ -10501,7 +10507,7 @@
       <c r="T134" s="17" t="n"/>
       <c r="U134" s="15" t="inlineStr">
         <is>
-          <t>Pandora And Off Plat -0%</t>
+          <t>Reportable -77%</t>
         </is>
       </c>
     </row>
@@ -10511,12 +10517,12 @@
       </c>
       <c r="B135" s="14" t="inlineStr">
         <is>
-          <t>HURC</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="C135" s="15" t="inlineStr">
         <is>
-          <t>Hurco Companies, Inc.</t>
+          <t>Sirius XM Holdings Inc.</t>
         </is>
       </c>
       <c r="D135" s="16" t="inlineStr">
@@ -10526,11 +10532,11 @@
       </c>
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F135" s="18" t="n">
-        <v>145911536</v>
+        <v>9543175168</v>
       </c>
       <c r="G135" s="19" t="inlineStr">
         <is>
@@ -10538,47 +10544,51 @@
         </is>
       </c>
       <c r="H135" s="20" t="n">
-        <v>-6.862805819592628</v>
-      </c>
-      <c r="I135" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.839</v>
+      </c>
+      <c r="I135" s="20" t="n">
+        <v>12.0127125</v>
       </c>
       <c r="J135" s="22" t="n">
-        <v>3.75916957537465</v>
+        <v>12.80212302889506</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>-6.10196397965777</v>
+        <v>10.57658645741083</v>
       </c>
       <c r="L135" s="22" t="n">
-        <v>-5.89115926129091</v>
+        <v>25.19519869479081</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>3.535305528612997</v>
+        <v>4.4736355226642</v>
       </c>
       <c r="N135" s="22" t="n">
-        <v>11.83590644756314</v>
+        <v>37.51723087267589</v>
       </c>
       <c r="O135" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q135" s="15" t="n"/>
-      <c r="R135" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="P135" s="20" t="n">
+        <v>0.6308860972502057</v>
+      </c>
+      <c r="Q135" s="15" t="inlineStr">
+        <is>
+          <t>Sirius XM (76%)</t>
+        </is>
+      </c>
+      <c r="R135" s="17" t="inlineStr">
+        <is>
+          <t>Sirius XM 76%; Pandora And Off Platform 24%</t>
+        </is>
+      </c>
       <c r="S135" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="T135" s="17" t="inlineStr">
-        <is>
-          <t>Europe 26%; Americas 21%; US 20%</t>
-        </is>
-      </c>
-      <c r="U135" s="15" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="T135" s="17" t="n"/>
+      <c r="U135" s="15" t="inlineStr">
+        <is>
+          <t>Pandora And Off Plat -0%</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="13" t="n">
@@ -10586,12 +10596,12 @@
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>HURC</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Coffee Holding Co., Inc.</t>
+          <t>Hurco Companies, Inc.</t>
         </is>
       </c>
       <c r="D136" s="16" t="inlineStr">
@@ -10601,11 +10611,11 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F136" s="18" t="n">
-        <v>19123810</v>
+        <v>145911536</v>
       </c>
       <c r="G136" s="19" t="inlineStr">
         <is>
@@ -10613,51 +10623,47 @@
         </is>
       </c>
       <c r="H136" s="20" t="n">
-        <v>6.732</v>
-      </c>
-      <c r="I136" s="20" t="n">
-        <v>12.407407</v>
+        <v>-6.862805819592628</v>
+      </c>
+      <c r="I136" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J136" s="22" t="n">
-        <v>42.03289398842584</v>
+        <v>3.75916957537465</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>14.9836891396905</v>
+        <v>-6.10196397965777</v>
       </c>
       <c r="L136" s="22" t="n">
-        <v>4.4448932469455</v>
+        <v>-5.89115926129091</v>
       </c>
       <c r="M136" s="20" t="n">
-        <v>0.4654342573568866</v>
+        <v>3.535305528612997</v>
       </c>
       <c r="N136" s="22" t="n">
-        <v>25.28308922858965</v>
+        <v>11.83590644756314</v>
       </c>
       <c r="O136" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P136" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q136" s="15" t="inlineStr">
-        <is>
-          <t>Operating (100%)</t>
-        </is>
-      </c>
-      <c r="R136" s="17" t="inlineStr">
-        <is>
-          <t>Operating 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P136" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q136" s="15" t="n"/>
+      <c r="R136" s="17" t="n"/>
       <c r="S136" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" s="17" t="n"/>
-      <c r="U136" s="15" t="inlineStr">
-        <is>
-          <t>Operating +23%</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="T136" s="17" t="inlineStr">
+        <is>
+          <t>Europe 26%; Americas 21%; US 20%</t>
+        </is>
+      </c>
+      <c r="U136" s="15" t="n"/>
     </row>
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="13" t="n">
@@ -10665,12 +10671,12 @@
       </c>
       <c r="B137" s="14" t="inlineStr">
         <is>
-          <t>CLFD</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C137" s="15" t="inlineStr">
         <is>
-          <t>Clearfield, Inc.</t>
+          <t>Coffee Holding Co., Inc.</t>
         </is>
       </c>
       <c r="D137" s="16" t="inlineStr">
@@ -10680,11 +10686,11 @@
       </c>
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F137" s="18" t="n">
-        <v>524960864</v>
+        <v>19123810</v>
       </c>
       <c r="G137" s="19" t="inlineStr">
         <is>
@@ -10692,45 +10698,51 @@
         </is>
       </c>
       <c r="H137" s="20" t="n">
-        <v>91.926</v>
+        <v>6.732</v>
       </c>
       <c r="I137" s="20" t="n">
-        <v>167.95653</v>
+        <v>12.407407</v>
       </c>
       <c r="J137" s="22" t="n">
-        <v>2.22637049013564</v>
+        <v>42.03289398842584</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>-0.9055781066418901</v>
+        <v>14.9836891396905</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>10.26651185578426</v>
+        <v>4.4448932469455</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>-5.776034516571877</v>
+        <v>0.4654342573568866</v>
       </c>
       <c r="N137" s="22" t="n">
-        <v>11.62432290838696</v>
+        <v>25.28308922858965</v>
       </c>
       <c r="O137" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q137" s="15" t="n"/>
-      <c r="R137" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="P137" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="15" t="inlineStr">
+        <is>
+          <t>Operating (100%)</t>
+        </is>
+      </c>
+      <c r="R137" s="17" t="inlineStr">
+        <is>
+          <t>Operating 100%</t>
+        </is>
+      </c>
       <c r="S137" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T137" s="17" t="inlineStr">
-        <is>
-          <t>US 97%; Non Us 3%</t>
-        </is>
-      </c>
-      <c r="U137" s="15" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="T137" s="17" t="n"/>
+      <c r="U137" s="15" t="inlineStr">
+        <is>
+          <t>Operating +23%</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="13" t="n">
@@ -10738,12 +10750,12 @@
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>CLFD</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provident Financial Holdings, </t>
+          <t>Clearfield, Inc.</t>
         </is>
       </c>
       <c r="D138" s="16" t="inlineStr">
@@ -10753,43 +10765,37 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F138" s="18" t="n">
-        <v>107563488</v>
+        <v>524960864</v>
       </c>
       <c r="G138" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H138" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H138" s="20" t="n">
+        <v>91.926</v>
       </c>
       <c r="I138" s="20" t="n">
-        <v>18.494625</v>
+        <v>167.95653</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>8.407967835537141</v>
-      </c>
-      <c r="K138" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.22637049013564</v>
+      </c>
+      <c r="K138" s="22" t="n">
+        <v>-0.9055781066418901</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.26651185578426</v>
+      </c>
+      <c r="M138" s="20" t="n">
+        <v>-5.776034516571877</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>13.3670912336621</v>
+        <v>11.62432290838696</v>
       </c>
       <c r="O138" s="18" t="n">
         <v>0</v>
@@ -10802,9 +10808,13 @@
       <c r="Q138" s="15" t="n"/>
       <c r="R138" s="17" t="n"/>
       <c r="S138" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T138" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="T138" s="17" t="inlineStr">
+        <is>
+          <t>US 97%; Non Us 3%</t>
+        </is>
+      </c>
       <c r="U138" s="15" t="n"/>
     </row>
     <row r="139" ht="16" customHeight="1">
@@ -10813,12 +10823,12 @@
       </c>
       <c r="B139" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="C139" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t xml:space="preserve">Provident Financial Holdings, </t>
         </is>
       </c>
       <c r="D139" s="16" t="inlineStr">
@@ -10828,67 +10838,59 @@
       </c>
       <c r="E139" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F139" s="18" t="n">
-        <v>108295240</v>
+        <v>107563488</v>
       </c>
       <c r="G139" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H139" s="20" t="n">
-        <v>11.138</v>
+      <c r="H139" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I139" s="20" t="n">
-        <v>21.333334</v>
+        <v>18.494625</v>
       </c>
       <c r="J139" s="22" t="n">
-        <v>1.84264170445135</v>
-      </c>
-      <c r="K139" s="22" t="n">
-        <v>16.80549850408138</v>
+        <v>8.407967835537141</v>
+      </c>
+      <c r="K139" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L139" s="22" t="n">
-        <v>24.49495025980879</v>
-      </c>
-      <c r="M139" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>0</v>
+      </c>
+      <c r="M139" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N139" s="22" t="n">
-        <v>63.28571864536831</v>
+        <v>13.3670912336621</v>
       </c>
       <c r="O139" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="P139" s="20" t="n">
-        <v>0.425811579408509</v>
-      </c>
-      <c r="Q139" s="15" t="inlineStr">
-        <is>
-          <t>Marine Technology Busi (56%)</t>
-        </is>
-      </c>
-      <c r="R139" s="17" t="inlineStr">
-        <is>
-          <t>Marine Technology Business Products 56%; Defense Engineering Services Business S</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P139" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q139" s="15" t="n"/>
+      <c r="R139" s="17" t="n"/>
       <c r="S139" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T139" s="17" t="inlineStr">
-        <is>
-          <t>Americas 35%; Europe 31%; Australia And Asia 28%</t>
-        </is>
-      </c>
-      <c r="U139" s="15" t="inlineStr">
-        <is>
-          <t>Defense Engineering  +6%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T139" s="17" t="n"/>
+      <c r="U139" s="15" t="n"/>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="13" t="n">
@@ -10896,12 +10898,12 @@
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>SIEB</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Siebert Financial Corp.</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D140" s="16" t="inlineStr">
@@ -10911,67 +10913,65 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F140" s="18" t="n">
-        <v>69599592</v>
+        <v>108295240</v>
       </c>
       <c r="G140" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H140" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I140" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J140" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H140" s="20" t="n">
+        <v>11.138</v>
+      </c>
+      <c r="I140" s="20" t="n">
+        <v>21.333334</v>
+      </c>
+      <c r="J140" s="22" t="n">
+        <v>1.84264170445135</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>5.17888936540735</v>
+        <v>16.80549850408138</v>
       </c>
       <c r="L140" s="22" t="n">
-        <v>7.23199371130981</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="M140" s="20" t="n">
-        <v>-1.897588315217392</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="N140" s="22" t="n">
-        <v>-64.87603317998357</v>
+        <v>63.28571864536831</v>
       </c>
       <c r="O140" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P140" s="20" t="n">
-        <v>0.9865046689171856</v>
+        <v>0.425811579408509</v>
       </c>
       <c r="Q140" s="15" t="inlineStr">
         <is>
-          <t>Financial Services (99%)</t>
+          <t>Marine Technology Busi (56%)</t>
         </is>
       </c>
       <c r="R140" s="17" t="inlineStr">
         <is>
-          <t>Financial Services 99%; Media Sports And Entertainment 1%</t>
+          <t>Marine Technology Business Products 56%; Defense Engineering Services Business S</t>
         </is>
       </c>
       <c r="S140" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="T140" s="17" t="inlineStr">
+        <is>
+          <t>Americas 35%; Europe 31%; Australia And Asia 28%</t>
+        </is>
+      </c>
       <c r="U140" s="15" t="inlineStr">
         <is>
-          <t>Financial Services +11%</t>
+          <t>Defense Engineering  +6%</t>
         </is>
       </c>
     </row>
@@ -16759,12 +16759,12 @@
       </c>
       <c r="B215" s="14" t="inlineStr">
         <is>
-          <t>ALGM</t>
+          <t>ETST</t>
         </is>
       </c>
       <c r="C215" s="15" t="inlineStr">
         <is>
-          <t>Allegro MicroSystems, Inc.</t>
+          <t>Earth Science Tech, Inc.</t>
         </is>
       </c>
       <c r="D215" s="16" t="inlineStr">
@@ -16774,39 +16774,39 @@
       </c>
       <c r="E215" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F215" s="18" t="n">
-        <v>10785431552</v>
-      </c>
-      <c r="G215" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>43226132</v>
+      </c>
+      <c r="G215" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H215" s="20" t="n">
-        <v>102.984</v>
-      </c>
-      <c r="I215" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J215" s="22" t="n">
-        <v>1.45955566109384</v>
+        <v>9.584</v>
+      </c>
+      <c r="I215" s="20" t="n">
+        <v>15.000001</v>
+      </c>
+      <c r="J215" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K215" s="22" t="n">
-        <v>1.72249294213012</v>
+        <v>53.80440161697887</v>
       </c>
       <c r="L215" s="22" t="n">
-        <v>8.40662130826337</v>
+        <v>10.49770988671045</v>
       </c>
       <c r="M215" s="20" t="n">
-        <v>1.583960335173133</v>
+        <v>-0.1533199794407697</v>
       </c>
       <c r="N215" s="22" t="n">
-        <v>77.3446585625084</v>
+        <v>-15.78947450975963</v>
       </c>
       <c r="O215" s="18" t="n">
         <v>0</v>
@@ -16819,13 +16819,9 @@
       <c r="Q215" s="15" t="n"/>
       <c r="R215" s="17" t="n"/>
       <c r="S215" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="T215" s="17" t="inlineStr">
-        <is>
-          <t>CN 27%; JP 19%; Europe 15%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T215" s="17" t="n"/>
       <c r="U215" s="15" t="n"/>
     </row>
     <row r="216" ht="16" customHeight="1">
@@ -16834,12 +16830,12 @@
       </c>
       <c r="B216" s="14" t="inlineStr">
         <is>
-          <t>SFST</t>
+          <t>ALGM</t>
         </is>
       </c>
       <c r="C216" s="15" t="inlineStr">
         <is>
-          <t>Southern First Bancshares, Inc</t>
+          <t>Allegro MicroSystems, Inc.</t>
         </is>
       </c>
       <c r="D216" s="16" t="inlineStr">
@@ -16849,43 +16845,39 @@
       </c>
       <c r="E216" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F216" s="18" t="n">
-        <v>578939776</v>
-      </c>
-      <c r="G216" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="H216" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I216" s="20" t="n">
-        <v>14.373239</v>
+        <v>10785431552</v>
+      </c>
+      <c r="G216" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="H216" s="20" t="n">
+        <v>102.984</v>
+      </c>
+      <c r="I216" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J216" s="22" t="n">
-        <v>3.03631449834383</v>
-      </c>
-      <c r="K216" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.45955566109384</v>
+      </c>
+      <c r="K216" s="22" t="n">
+        <v>1.72249294213012</v>
       </c>
       <c r="L216" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.40662130826337</v>
+      </c>
+      <c r="M216" s="20" t="n">
+        <v>1.583960335173133</v>
       </c>
       <c r="N216" s="22" t="n">
-        <v>46.83578253190569</v>
+        <v>77.3446585625084</v>
       </c>
       <c r="O216" s="18" t="n">
         <v>0</v>
@@ -16898,9 +16890,13 @@
       <c r="Q216" s="15" t="n"/>
       <c r="R216" s="17" t="n"/>
       <c r="S216" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T216" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="T216" s="17" t="inlineStr">
+        <is>
+          <t>CN 27%; JP 19%; Europe 15%</t>
+        </is>
+      </c>
       <c r="U216" s="15" t="n"/>
     </row>
     <row r="217" ht="16" customHeight="1">
@@ -16909,12 +16905,12 @@
       </c>
       <c r="B217" s="14" t="inlineStr">
         <is>
-          <t>FATN</t>
+          <t>SFST</t>
         </is>
       </c>
       <c r="C217" s="15" t="inlineStr">
         <is>
-          <t>FatPipe Inc. Common Stock</t>
+          <t>Southern First Bancshares, Inc</t>
         </is>
       </c>
       <c r="D217" s="16" t="inlineStr">
@@ -16924,37 +16920,43 @@
       </c>
       <c r="E217" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F217" s="18" t="n">
-        <v>84707784</v>
+        <v>578939776</v>
       </c>
       <c r="G217" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H217" s="20" t="n">
-        <v>21.523</v>
+      <c r="H217" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I217" s="20" t="n">
-        <v>17.257143</v>
+        <v>14.373239</v>
       </c>
       <c r="J217" s="22" t="n">
-        <v>-1.45887439123651</v>
-      </c>
-      <c r="K217" s="22" t="n">
-        <v>14.34799023925575</v>
+        <v>3.03631449834383</v>
+      </c>
+      <c r="K217" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L217" s="22" t="n">
-        <v>14.43825219466334</v>
-      </c>
-      <c r="M217" s="20" t="n">
-        <v>-0.1617276693742073</v>
+        <v>0</v>
+      </c>
+      <c r="M217" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N217" s="22" t="n">
-        <v>-55.9613349104299</v>
+        <v>46.83578253190569</v>
       </c>
       <c r="O217" s="18" t="n">
         <v>0</v>
@@ -16967,13 +16969,9 @@
       <c r="Q217" s="15" t="n"/>
       <c r="R217" s="17" t="n"/>
       <c r="S217" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T217" s="17" t="inlineStr">
-        <is>
-          <t>US 96%; Non Us 4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T217" s="17" t="n"/>
       <c r="U217" s="15" t="n"/>
     </row>
     <row r="218" ht="16" customHeight="1">
@@ -16982,12 +16980,12 @@
       </c>
       <c r="B218" s="14" t="inlineStr">
         <is>
-          <t>ALNY</t>
+          <t>FATN</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
         <is>
-          <t>Alnylam Pharmaceuticals, Inc.</t>
+          <t>FatPipe Inc. Common Stock</t>
         </is>
       </c>
       <c r="D218" s="16" t="inlineStr">
@@ -16997,11 +16995,11 @@
       </c>
       <c r="E218" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F218" s="18" t="n">
-        <v>38901559296</v>
+        <v>84707784</v>
       </c>
       <c r="G218" s="19" t="inlineStr">
         <is>
@@ -17009,25 +17007,25 @@
         </is>
       </c>
       <c r="H218" s="20" t="n">
-        <v>48.16</v>
+        <v>21.523</v>
       </c>
       <c r="I218" s="20" t="n">
-        <v>73.02506</v>
+        <v>17.257143</v>
       </c>
       <c r="J218" s="22" t="n">
-        <v>1.61995031088219</v>
+        <v>-1.45887439123651</v>
       </c>
       <c r="K218" s="22" t="n">
-        <v>-131.6113410564707</v>
+        <v>14.34799023925575</v>
       </c>
       <c r="L218" s="22" t="n">
-        <v>21.56497795738342</v>
+        <v>14.43825219466334</v>
       </c>
       <c r="M218" s="20" t="n">
-        <v>-1.878003059036814</v>
+        <v>-0.1617276693742073</v>
       </c>
       <c r="N218" s="22" t="n">
-        <v>2.92387965641219</v>
+        <v>-55.9613349104299</v>
       </c>
       <c r="O218" s="18" t="n">
         <v>0</v>
@@ -17040,11 +17038,11 @@
       <c r="Q218" s="15" t="n"/>
       <c r="R218" s="17" t="n"/>
       <c r="S218" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T218" s="17" t="inlineStr">
         <is>
-          <t>US 64%; Europe 26%; Non US Or Europe 10%</t>
+          <t>US 96%; Non Us 4%</t>
         </is>
       </c>
       <c r="U218" s="15" t="n"/>
@@ -17055,12 +17053,12 @@
       </c>
       <c r="B219" s="14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>ALNY</t>
         </is>
       </c>
       <c r="C219" s="15" t="inlineStr">
         <is>
-          <t>LendingClub Corporation</t>
+          <t>Alnylam Pharmaceuticals, Inc.</t>
         </is>
       </c>
       <c r="D219" s="16" t="inlineStr">
@@ -17070,11 +17068,11 @@
       </c>
       <c r="E219" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F219" s="18" t="n">
-        <v>2215891200</v>
+        <v>38901559296</v>
       </c>
       <c r="G219" s="19" t="inlineStr">
         <is>
@@ -17082,29 +17080,25 @@
         </is>
       </c>
       <c r="H219" s="20" t="n">
-        <v>4.862</v>
+        <v>48.16</v>
       </c>
       <c r="I219" s="20" t="n">
-        <v>12.806666</v>
+        <v>73.02506</v>
       </c>
       <c r="J219" s="22" t="n">
-        <v>-97.55883274375822</v>
-      </c>
-      <c r="K219" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.61995031088219</v>
+      </c>
+      <c r="K219" s="22" t="n">
+        <v>-131.6113410564707</v>
       </c>
       <c r="L219" s="22" t="n">
-        <v>21.381001</v>
-      </c>
-      <c r="M219" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.56497795738342</v>
+      </c>
+      <c r="M219" s="20" t="n">
+        <v>-1.878003059036814</v>
       </c>
       <c r="N219" s="22" t="n">
-        <v>47.2143524830653</v>
+        <v>2.92387965641219</v>
       </c>
       <c r="O219" s="18" t="n">
         <v>0</v>
@@ -17117,9 +17111,13 @@
       <c r="Q219" s="15" t="n"/>
       <c r="R219" s="17" t="n"/>
       <c r="S219" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T219" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="T219" s="17" t="inlineStr">
+        <is>
+          <t>US 64%; Europe 26%; Non US Or Europe 10%</t>
+        </is>
+      </c>
       <c r="U219" s="15" t="n"/>
     </row>
     <row r="220" ht="16" customHeight="1">
@@ -17128,12 +17126,12 @@
       </c>
       <c r="B220" s="14" t="inlineStr">
         <is>
-          <t>ASAN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C220" s="15" t="inlineStr">
         <is>
-          <t>Asana, Inc.</t>
+          <t>LendingClub Corporation</t>
         </is>
       </c>
       <c r="D220" s="16" t="inlineStr">
@@ -17143,11 +17141,11 @@
       </c>
       <c r="E220" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F220" s="18" t="n">
-        <v>1606653440</v>
+        <v>2215891200</v>
       </c>
       <c r="G220" s="19" t="inlineStr">
         <is>
@@ -17155,27 +17153,29 @@
         </is>
       </c>
       <c r="H220" s="20" t="n">
-        <v>-8.123680517291266</v>
-      </c>
-      <c r="I220" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.862</v>
+      </c>
+      <c r="I220" s="20" t="n">
+        <v>12.806666</v>
       </c>
       <c r="J220" s="22" t="n">
-        <v>5.21506708496677</v>
-      </c>
-      <c r="K220" s="22" t="n">
-        <v>593.3103900360537</v>
+        <v>-97.55883274375822</v>
+      </c>
+      <c r="K220" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L220" s="22" t="n">
-        <v>-20.10379283920456</v>
-      </c>
-      <c r="M220" s="20" t="n">
-        <v>1.161307569410374</v>
+        <v>21.381001</v>
+      </c>
+      <c r="M220" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N220" s="22" t="n">
-        <v>-65.68898774779171</v>
+        <v>47.2143524830653</v>
       </c>
       <c r="O220" s="18" t="n">
         <v>0</v>
@@ -17188,13 +17188,9 @@
       <c r="Q220" s="15" t="n"/>
       <c r="R220" s="17" t="n"/>
       <c r="S220" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T220" s="17" t="inlineStr">
-        <is>
-          <t>US 60%; Non Us 40%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T220" s="17" t="n"/>
       <c r="U220" s="15" t="n"/>
     </row>
     <row r="221" ht="16" customHeight="1">
@@ -17203,12 +17199,12 @@
       </c>
       <c r="B221" s="14" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>ASAN</t>
         </is>
       </c>
       <c r="C221" s="15" t="inlineStr">
         <is>
-          <t>Instil Bio, Inc.</t>
+          <t>Asana, Inc.</t>
         </is>
       </c>
       <c r="D221" s="16" t="inlineStr">
@@ -17218,11 +17214,11 @@
       </c>
       <c r="E221" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F221" s="18" t="n">
-        <v>50390088</v>
+        <v>1606653440</v>
       </c>
       <c r="G221" s="19" t="inlineStr">
         <is>
@@ -17230,7 +17226,7 @@
         </is>
       </c>
       <c r="H221" s="20" t="n">
-        <v>-0.908630976186148</v>
+        <v>-8.123680517291266</v>
       </c>
       <c r="I221" s="21" t="inlineStr">
         <is>
@@ -17238,19 +17234,19 @@
         </is>
       </c>
       <c r="J221" s="22" t="n">
-        <v>-99.73588426442328</v>
+        <v>5.21506708496677</v>
       </c>
       <c r="K221" s="22" t="n">
-        <v>-71.9501116620614</v>
+        <v>593.3103900360537</v>
       </c>
       <c r="L221" s="22" t="n">
-        <v>0</v>
+        <v>-20.10379283920456</v>
       </c>
       <c r="M221" s="20" t="n">
-        <v>-1.184148336666061</v>
+        <v>1.161307569410374</v>
       </c>
       <c r="N221" s="22" t="n">
-        <v>-45.50979428646714</v>
+        <v>-65.68898774779171</v>
       </c>
       <c r="O221" s="18" t="n">
         <v>0</v>
@@ -17263,9 +17259,13 @@
       <c r="Q221" s="15" t="n"/>
       <c r="R221" s="17" t="n"/>
       <c r="S221" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T221" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="T221" s="17" t="inlineStr">
+        <is>
+          <t>US 60%; Non Us 40%</t>
+        </is>
+      </c>
       <c r="U221" s="15" t="n"/>
     </row>
     <row r="222" ht="16" customHeight="1">
@@ -17274,12 +17274,12 @@
       </c>
       <c r="B222" s="14" t="inlineStr">
         <is>
-          <t>CBKM</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="C222" s="15" t="inlineStr">
         <is>
-          <t>Consumers Bancorp, Inc.</t>
+          <t>Instil Bio, Inc.</t>
         </is>
       </c>
       <c r="D222" s="16" t="inlineStr">
@@ -17289,43 +17289,39 @@
       </c>
       <c r="E222" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F222" s="18" t="n">
-        <v>92739416</v>
+        <v>50390088</v>
       </c>
       <c r="G222" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H222" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I222" s="20" t="n">
-        <v>8.829342</v>
+      <c r="H222" s="20" t="n">
+        <v>-0.908630976186148</v>
+      </c>
+      <c r="I222" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J222" s="22" t="n">
-        <v>11.2038687095359</v>
-      </c>
-      <c r="K222" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-99.73588426442328</v>
+      </c>
+      <c r="K222" s="22" t="n">
+        <v>-71.9501116620614</v>
       </c>
       <c r="L222" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M222" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="M222" s="20" t="n">
+        <v>-1.184148336666061</v>
       </c>
       <c r="N222" s="22" t="n">
-        <v>44.15947036183197</v>
+        <v>-45.50979428646714</v>
       </c>
       <c r="O222" s="18" t="n">
         <v>0</v>
@@ -17349,12 +17345,12 @@
       </c>
       <c r="B223" s="14" t="inlineStr">
         <is>
-          <t>ETST</t>
+          <t>CBKM</t>
         </is>
       </c>
       <c r="C223" s="15" t="inlineStr">
         <is>
-          <t>Earth Science Tech, Inc.</t>
+          <t>Consumers Bancorp, Inc.</t>
         </is>
       </c>
       <c r="D223" s="16" t="inlineStr">
@@ -17364,39 +17360,43 @@
       </c>
       <c r="E223" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F223" s="18" t="n">
-        <v>43226132</v>
+        <v>92739416</v>
       </c>
       <c r="G223" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H223" s="20" t="n">
-        <v>9.584</v>
+      <c r="H223" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I223" s="20" t="n">
-        <v>15.000001</v>
-      </c>
-      <c r="J223" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K223" s="22" t="n">
-        <v>53.80440161697887</v>
+        <v>8.829342</v>
+      </c>
+      <c r="J223" s="22" t="n">
+        <v>11.2038687095359</v>
+      </c>
+      <c r="K223" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L223" s="22" t="n">
-        <v>10.49770988671045</v>
-      </c>
-      <c r="M223" s="20" t="n">
-        <v>-0.1533199794407697</v>
+        <v>0</v>
+      </c>
+      <c r="M223" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N223" s="22" t="n">
-        <v>-15.78947450975963</v>
+        <v>44.15947036183197</v>
       </c>
       <c r="O223" s="18" t="n">
         <v>0</v>
@@ -31079,12 +31079,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>WSFS</t>
+          <t>SIEB</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>WSFS Financial Corporation</t>
+          <t>Siebert Financial Corp.</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -31098,7 +31098,7 @@
         </is>
       </c>
       <c r="F29" s="18" t="n">
-        <v>4026127616</v>
+        <v>69599592</v>
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
@@ -31110,42 +31110,42 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I29" s="20" t="n">
-        <v>13.789661</v>
-      </c>
-      <c r="J29" s="22" t="n">
-        <v>6.158366732153779</v>
-      </c>
-      <c r="K29" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="n">
+        <v>5.17888936540735</v>
       </c>
       <c r="L29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.23199371130981</v>
+      </c>
+      <c r="M29" s="20" t="n">
+        <v>-1.897588315217392</v>
       </c>
       <c r="N29" s="22" t="n">
-        <v>37.01048893948796</v>
+        <v>-64.87603317998357</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" s="20" t="n">
-        <v>0.5461404223281471</v>
+        <v>0.9865046689171856</v>
       </c>
       <c r="Q29" s="15" t="inlineStr">
         <is>
-          <t>Wsfs Bank (70%)</t>
+          <t>Financial Services (99%)</t>
         </is>
       </c>
       <c r="R29" s="17" t="inlineStr">
         <is>
-          <t>Wsfs Bank 70%; Wealth Management 22%; Cash Connect 8%</t>
+          <t>Financial Services 99%; Media Sports And Entertainment 1%</t>
         </is>
       </c>
       <c r="S29" s="18" t="n">
@@ -31154,7 +31154,7 @@
       <c r="T29" s="17" t="n"/>
       <c r="U29" s="15" t="inlineStr">
         <is>
-          <t>Wealth Management +15%</t>
+          <t>Financial Services +11%</t>
         </is>
       </c>
     </row>
@@ -31164,12 +31164,12 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>NRIM</t>
+          <t>WSFS</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Northrim BanCorp, Inc.</t>
+          <t>WSFS Financial Corporation</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -31183,7 +31183,7 @@
         </is>
       </c>
       <c r="F30" s="18" t="n">
-        <v>621963648</v>
+        <v>4026127616</v>
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
@@ -31196,10 +31196,10 @@
         </is>
       </c>
       <c r="I30" s="20" t="n">
-        <v>9.708333</v>
+        <v>13.789661</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>7.154905282262169</v>
+        <v>6.158366732153779</v>
       </c>
       <c r="K30" s="21" t="inlineStr">
         <is>
@@ -31215,22 +31215,22 @@
         </is>
       </c>
       <c r="N30" s="22" t="n">
-        <v>7.62249350229726</v>
+        <v>37.01048893948796</v>
       </c>
       <c r="O30" s="18" t="n">
         <v>3</v>
       </c>
       <c r="P30" s="20" t="n">
-        <v>0.6090673877493771</v>
+        <v>0.5461404223281471</v>
       </c>
       <c r="Q30" s="15" t="inlineStr">
         <is>
-          <t>Community Banking (76%)</t>
+          <t>Wsfs Bank (70%)</t>
         </is>
       </c>
       <c r="R30" s="17" t="inlineStr">
         <is>
-          <t>Community Banking 76%; Home Mortgage Lending 17%; Specialty Finance 7%</t>
+          <t>Wsfs Bank 70%; Wealth Management 22%; Cash Connect 8%</t>
         </is>
       </c>
       <c r="S30" s="18" t="n">
@@ -31239,7 +31239,7 @@
       <c r="T30" s="17" t="n"/>
       <c r="U30" s="15" t="inlineStr">
         <is>
-          <t>Specialty Finance +257%</t>
+          <t>Wealth Management +15%</t>
         </is>
       </c>
     </row>
@@ -31249,12 +31249,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>CATO</t>
+          <t>NRIM</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>The Cato Corporation</t>
+          <t>Northrim BanCorp, Inc.</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -31264,52 +31264,58 @@
       </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F31" s="18" t="n">
-        <v>66662584</v>
+        <v>621963648</v>
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H31" s="20" t="n">
-        <v>134.466</v>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I31" s="20" t="n">
-        <v>2.916295653927599</v>
+        <v>9.708333</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>34.35404370485792</v>
-      </c>
-      <c r="K31" s="22" t="n">
-        <v>6.90904715732555</v>
+        <v>7.154905282262169</v>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L31" s="22" t="n">
-        <v>0.39782078028546</v>
-      </c>
-      <c r="M31" s="20" t="n">
-        <v>29.52748942714341</v>
+        <v>0</v>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N31" s="22" t="n">
-        <v>6.521741571708831</v>
+        <v>7.62249350229726</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>0.9920879293908172</v>
+        <v>0.6090673877493771</v>
       </c>
       <c r="Q31" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segments Re (100%)</t>
+          <t>Community Banking (76%)</t>
         </is>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segments Retail 100%; Reportable Segments Credit 0%</t>
+          <t>Community Banking 76%; Home Mortgage Lending 17%; Specialty Finance 7%</t>
         </is>
       </c>
       <c r="S31" s="18" t="n">
@@ -31318,7 +31324,7 @@
       <c r="T31" s="17" t="n"/>
       <c r="U31" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segments  +1%</t>
+          <t>Specialty Finance +257%</t>
         </is>
       </c>
     </row>
@@ -31328,12 +31334,12 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>CATO</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Sirius XM Holdings Inc.</t>
+          <t>The Cato Corporation</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -31343,11 +31349,11 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F32" s="18" t="n">
-        <v>9543175168</v>
+        <v>66662584</v>
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
@@ -31355,40 +31361,40 @@
         </is>
       </c>
       <c r="H32" s="20" t="n">
-        <v>7.839</v>
+        <v>134.466</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>12.0127125</v>
+        <v>2.916295653927599</v>
       </c>
       <c r="J32" s="22" t="n">
-        <v>12.80212302889506</v>
+        <v>34.35404370485792</v>
       </c>
       <c r="K32" s="22" t="n">
-        <v>10.57658645741083</v>
+        <v>6.90904715732555</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>25.19519869479081</v>
+        <v>0.39782078028546</v>
       </c>
       <c r="M32" s="20" t="n">
-        <v>4.4736355226642</v>
+        <v>29.52748942714341</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>37.51723087267589</v>
+        <v>6.521741571708831</v>
       </c>
       <c r="O32" s="18" t="n">
         <v>2</v>
       </c>
       <c r="P32" s="20" t="n">
-        <v>0.6308860972502057</v>
+        <v>0.9920879293908172</v>
       </c>
       <c r="Q32" s="15" t="inlineStr">
         <is>
-          <t>Sirius XM (76%)</t>
+          <t>Reportable Segments Re (100%)</t>
         </is>
       </c>
       <c r="R32" s="17" t="inlineStr">
         <is>
-          <t>Sirius XM 76%; Pandora And Off Platform 24%</t>
+          <t>Reportable Segments Retail 100%; Reportable Segments Credit 0%</t>
         </is>
       </c>
       <c r="S32" s="18" t="n">
@@ -31397,7 +31403,7 @@
       <c r="T32" s="17" t="n"/>
       <c r="U32" s="15" t="inlineStr">
         <is>
-          <t>Pandora And Off Plat -0%</t>
+          <t>Reportable Segments  +1%</t>
         </is>
       </c>
     </row>
@@ -31407,12 +31413,12 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>SIEB</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Siebert Financial Corp.</t>
+          <t>Sirius XM Holdings Inc.</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -31422,58 +31428,52 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F33" s="18" t="n">
-        <v>69599592</v>
+        <v>9543175168</v>
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J33" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H33" s="20" t="n">
+        <v>7.839</v>
+      </c>
+      <c r="I33" s="20" t="n">
+        <v>12.0127125</v>
+      </c>
+      <c r="J33" s="22" t="n">
+        <v>12.80212302889506</v>
       </c>
       <c r="K33" s="22" t="n">
-        <v>5.17888936540735</v>
+        <v>10.57658645741083</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>7.23199371130981</v>
+        <v>25.19519869479081</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>-1.897588315217392</v>
+        <v>4.4736355226642</v>
       </c>
       <c r="N33" s="22" t="n">
-        <v>-64.87603317998357</v>
+        <v>37.51723087267589</v>
       </c>
       <c r="O33" s="18" t="n">
         <v>2</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.9865046689171856</v>
+        <v>0.6308860972502057</v>
       </c>
       <c r="Q33" s="15" t="inlineStr">
         <is>
-          <t>Financial Services (99%)</t>
+          <t>Sirius XM (76%)</t>
         </is>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
-          <t>Financial Services 99%; Media Sports And Entertainment 1%</t>
+          <t>Sirius XM 76%; Pandora And Off Platform 24%</t>
         </is>
       </c>
       <c r="S33" s="18" t="n">
@@ -31482,7 +31482,7 @@
       <c r="T33" s="17" t="n"/>
       <c r="U33" s="15" t="inlineStr">
         <is>
-          <t>Financial Services +11%</t>
+          <t>Pandora And Off Plat -0%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Segments" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diversified" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concentrated" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fastest" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All Segments" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Diversified" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Concentrated" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Global" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Fastest" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Segments'!$A$11:$U$312</definedName>
@@ -627,32 +627,32 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2,827</t>
+          <t>3,040</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>459</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>748</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>689</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>406</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10.6% of segment-covered</t>
+          <t>9.9% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.1% of segment-covered</t>
+          <t>2.0% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -29574,7 +29574,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.1% of segment-covered</t>
+          <t>2.0% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -34802,7 +34802,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.1% of segment-covered</t>
+          <t>2.0% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -39954,7 +39954,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.1% of segment-covered</t>
+          <t>2.0% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -627,32 +627,32 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>3,040</t>
+          <t>3,205</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>402</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>699</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>414</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>9.9% of segment-covered</t>
+          <t>9.4% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3455,8 +3455,10 @@
       <c r="I43" s="20" t="n">
         <v>2.9061136</v>
       </c>
-      <c r="J43" s="22" t="n">
-        <v>-206.4949365087135</v>
+      <c r="J43" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K43" s="22" t="n">
         <v>56.43538438885526</v>
@@ -4855,8 +4857,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J61" s="22" t="n">
-        <v>436.2651481650357</v>
+      <c r="J61" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K61" s="22" t="n">
         <v>-9.166353313327489</v>
@@ -9461,8 +9465,10 @@
       <c r="I121" s="20" t="n">
         <v>0.024325127</v>
       </c>
-      <c r="J121" s="22" t="n">
-        <v>-202.6520054738409</v>
+      <c r="J121" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K121" s="22" t="n">
         <v>-35.17300762638625</v>
@@ -12260,8 +12266,10 @@
       <c r="H157" s="20" t="n">
         <v>9.939</v>
       </c>
-      <c r="I157" s="20" t="n">
-        <v>2680.972728760845</v>
+      <c r="I157" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J157" s="22" t="n">
         <v>11.39714304666466</v>
@@ -12960,8 +12968,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J166" s="22" t="n">
-        <v>-240.8575827473552</v>
+      <c r="J166" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K166" s="22" t="n">
         <v>-1023.737559896793</v>
@@ -24340,7 +24350,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.0% of segment-covered</t>
+          <t>1.9% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -29574,7 +29584,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.0% of segment-covered</t>
+          <t>1.9% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -30042,8 +30052,10 @@
       <c r="I16" s="20" t="n">
         <v>2.9061136</v>
       </c>
-      <c r="J16" s="22" t="n">
-        <v>-206.4949365087135</v>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K16" s="22" t="n">
         <v>56.43538438885526</v>
@@ -30534,8 +30546,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J22" s="22" t="n">
-        <v>436.2651481650357</v>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K22" s="22" t="n">
         <v>-9.166353313327489</v>
@@ -34802,7 +34816,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.0% of segment-covered</t>
+          <t>1.9% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -39954,7 +39968,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2.0% of segment-covered</t>
+          <t>1.9% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -40424,8 +40438,10 @@
       <c r="I16" s="20" t="n">
         <v>2.9061136</v>
       </c>
-      <c r="J16" s="22" t="n">
-        <v>-206.4949365087135</v>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K16" s="22" t="n">
         <v>56.43538438885526</v>
@@ -41327,8 +41343,10 @@
       <c r="I27" s="20" t="n">
         <v>0.024325127</v>
       </c>
-      <c r="J27" s="22" t="n">
-        <v>-202.6520054738409</v>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K27" s="22" t="n">
         <v>-35.17300762638625</v>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -1491,8 +1491,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J17" s="22" t="n">
-        <v>-213.8091129573654</v>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
@@ -5706,8 +5708,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J72" s="22" t="n">
-        <v>505.149115120589</v>
+      <c r="J72" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K72" s="22" t="n">
         <v>-9.166353313327489</v>
@@ -8413,8 +8417,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J107" s="22" t="n">
-        <v>-245.0043097953793</v>
+      <c r="J107" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K107" s="22" t="n">
         <v>5.17888936540735</v>
@@ -10747,8 +10753,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J137" s="22" t="n">
-        <v>-349.0853798671735</v>
+      <c r="J137" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K137" s="21" t="inlineStr">
         <is>
@@ -12431,8 +12439,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J159" s="22" t="n">
-        <v>-329.6068902734481</v>
+      <c r="J159" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K159" s="22" t="n">
         <v>-39.58303441635305</v>
@@ -14431,8 +14441,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J185" s="22" t="n">
-        <v>-244.5076553591149</v>
+      <c r="J185" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K185" s="21" t="inlineStr">
         <is>
@@ -16822,8 +16834,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J216" s="22" t="n">
-        <v>-384.104451539463</v>
+      <c r="J216" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K216" s="21" t="inlineStr">
         <is>
@@ -30822,8 +30836,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J24" s="22" t="n">
-        <v>505.149115120589</v>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K24" s="22" t="n">
         <v>-9.166353313327489</v>
@@ -31470,8 +31486,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J32" s="22" t="n">
-        <v>-245.0043097953793</v>
+      <c r="J32" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K32" s="22" t="n">
         <v>5.17888936540735</v>
@@ -41698,8 +41716,10 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J30" s="22" t="n">
-        <v>-329.6068902734481</v>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K30" s="22" t="n">
         <v>-39.58303441635305</v>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -1162,10 +1162,8 @@
       <c r="J13" s="22" t="n">
         <v>36.66783771232035</v>
       </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K13" s="22" t="n">
+        <v>207.2668711656441</v>
       </c>
       <c r="L13" s="22" t="n">
         <v>28.30357984274423</v>
@@ -1241,10 +1239,8 @@
       <c r="J14" s="22" t="n">
         <v>36.57989337944194</v>
       </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K14" s="22" t="n">
+        <v>-9.731226124022729</v>
       </c>
       <c r="L14" s="22" t="n">
         <v>7.89126355897411</v>
@@ -22206,12 +22202,12 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>JOUT</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
         <is>
-          <t>Johnson Outdoors Inc.</t>
+          <t>Metropolitan Bank Holding Corp</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
@@ -22221,67 +22217,59 @@
       </c>
       <c r="E286" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F286" s="18" t="n">
-        <v>489901344</v>
+        <v>1237248640</v>
       </c>
       <c r="G286" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H286" s="20" t="n">
-        <v>15.414</v>
+      <c r="H286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I286" s="20" t="n">
-        <v>26.50606053853296</v>
+        <v>12.33869</v>
       </c>
       <c r="J286" s="22" t="n">
-        <v>-34.23847463411765</v>
-      </c>
-      <c r="K286" s="22" t="n">
-        <v>6.32393274792691</v>
+        <v>11.56099812769128</v>
+      </c>
+      <c r="K286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L286" s="22" t="n">
-        <v>4.722703016296919</v>
-      </c>
-      <c r="M286" s="20" t="n">
-        <v>-2.839526226734348</v>
+        <v>0</v>
+      </c>
+      <c r="M286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N286" s="22" t="n">
-        <v>53.34578870086434</v>
+        <v>31.66505529209152</v>
       </c>
       <c r="O286" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P286" s="20" t="n">
-        <v>0.605555628096546</v>
-      </c>
-      <c r="Q286" s="15" t="inlineStr">
-        <is>
-          <t>Fishing (76%)</t>
-        </is>
-      </c>
-      <c r="R286" s="17" t="inlineStr">
-        <is>
-          <t>Fishing 76%; Diving 13%; Camping Watercraft Recreation 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q286" s="15" t="n"/>
+      <c r="R286" s="17" t="n"/>
       <c r="S286" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T286" s="17" t="inlineStr">
-        <is>
-          <t>US 87%; CA 6%; Europe 5%</t>
-        </is>
-      </c>
-      <c r="U286" s="15" t="inlineStr">
-        <is>
-          <t>Diving +2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T286" s="17" t="n"/>
+      <c r="U286" s="15" t="n"/>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="13" t="n">
@@ -22289,12 +22277,12 @@
       </c>
       <c r="B287" s="14" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>JOUT</t>
         </is>
       </c>
       <c r="C287" s="15" t="inlineStr">
         <is>
-          <t>Metropolitan Bank Holding Corp</t>
+          <t>Johnson Outdoors Inc.</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
@@ -22304,59 +22292,67 @@
       </c>
       <c r="E287" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F287" s="18" t="n">
-        <v>1237248640</v>
+        <v>489901344</v>
       </c>
       <c r="G287" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H287" s="20" t="n">
+        <v>15.414</v>
       </c>
       <c r="I287" s="20" t="n">
-        <v>12.33869</v>
+        <v>26.50606053853296</v>
       </c>
       <c r="J287" s="22" t="n">
-        <v>11.56099812769128</v>
-      </c>
-      <c r="K287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-34.23847463411765</v>
+      </c>
+      <c r="K287" s="22" t="n">
+        <v>6.32393274792691</v>
       </c>
       <c r="L287" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.722703016296919</v>
+      </c>
+      <c r="M287" s="20" t="n">
+        <v>-2.839526226734348</v>
       </c>
       <c r="N287" s="22" t="n">
-        <v>31.66505529209152</v>
+        <v>53.34578870086434</v>
       </c>
       <c r="O287" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q287" s="15" t="n"/>
-      <c r="R287" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="P287" s="20" t="n">
+        <v>0.605555628096546</v>
+      </c>
+      <c r="Q287" s="15" t="inlineStr">
+        <is>
+          <t>Fishing (76%)</t>
+        </is>
+      </c>
+      <c r="R287" s="17" t="inlineStr">
+        <is>
+          <t>Fishing 76%; Diving 13%; Camping Watercraft Recreation 11%</t>
+        </is>
+      </c>
       <c r="S287" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T287" s="17" t="n"/>
-      <c r="U287" s="15" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="T287" s="17" t="inlineStr">
+        <is>
+          <t>US 87%; CA 6%; Europe 5%</t>
+        </is>
+      </c>
+      <c r="U287" s="15" t="inlineStr">
+        <is>
+          <t>Diving +2%</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="16" customHeight="1">
       <c r="A288" s="13" t="n">
@@ -29922,10 +29918,8 @@
       <c r="J13" s="22" t="n">
         <v>36.57989337944194</v>
       </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K13" s="22" t="n">
+        <v>-9.731226124022729</v>
       </c>
       <c r="L13" s="22" t="n">
         <v>7.89126355897411</v>
@@ -35164,10 +35158,8 @@
       <c r="J13" s="22" t="n">
         <v>36.57989337944194</v>
       </c>
-      <c r="K13" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K13" s="22" t="n">
+        <v>-9.731226124022729</v>
       </c>
       <c r="L13" s="22" t="n">
         <v>7.89126355897411</v>
@@ -38394,10 +38386,8 @@
       <c r="J53" s="22" t="n">
         <v>-40.599217817621</v>
       </c>
-      <c r="K53" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="K53" s="22" t="n">
+        <v>-75.04378283712785</v>
       </c>
       <c r="L53" s="22" t="n">
         <v>-1.94399620313241</v>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -1487,10 +1487,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="J17" s="22" t="n">
+        <v>-185.6403503861519</v>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
@@ -5704,10 +5702,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J72" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="J72" s="22" t="n">
+        <v>-72.77112322684269</v>
       </c>
       <c r="K72" s="22" t="n">
         <v>-9.166353313327489</v>
@@ -30830,10 +30826,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="J24" s="22" t="n">
+        <v>-72.77112322684269</v>
       </c>
       <c r="K24" s="22" t="n">
         <v>-9.166353313327489</v>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -627,32 +627,32 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>3,205</t>
+          <t>3,214</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>475</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>404</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>794</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>416</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>9.4% of segment-covered</t>
+          <t>9.3% of segment-covered</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -22198,12 +22198,12 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>JOUT</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
         <is>
-          <t>Metropolitan Bank Holding Corp</t>
+          <t>Johnson Outdoors Inc.</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
@@ -22213,59 +22213,67 @@
       </c>
       <c r="E286" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F286" s="18" t="n">
-        <v>1237248640</v>
+        <v>489901344</v>
       </c>
       <c r="G286" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H286" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H286" s="20" t="n">
+        <v>15.414</v>
       </c>
       <c r="I286" s="20" t="n">
-        <v>12.33869</v>
+        <v>26.50606053853296</v>
       </c>
       <c r="J286" s="22" t="n">
-        <v>11.56099812769128</v>
-      </c>
-      <c r="K286" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-34.23847463411765</v>
+      </c>
+      <c r="K286" s="22" t="n">
+        <v>6.32393274792691</v>
       </c>
       <c r="L286" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M286" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.722703016296919</v>
+      </c>
+      <c r="M286" s="20" t="n">
+        <v>-2.839526226734348</v>
       </c>
       <c r="N286" s="22" t="n">
-        <v>31.66505529209152</v>
+        <v>53.34578870086434</v>
       </c>
       <c r="O286" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P286" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q286" s="15" t="n"/>
-      <c r="R286" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="P286" s="20" t="n">
+        <v>0.605555628096546</v>
+      </c>
+      <c r="Q286" s="15" t="inlineStr">
+        <is>
+          <t>Fishing (76%)</t>
+        </is>
+      </c>
+      <c r="R286" s="17" t="inlineStr">
+        <is>
+          <t>Fishing 76%; Diving 13%; Camping Watercraft Recreation 11%</t>
+        </is>
+      </c>
       <c r="S286" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T286" s="17" t="n"/>
-      <c r="U286" s="15" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="T286" s="17" t="inlineStr">
+        <is>
+          <t>US 87%; CA 6%; Europe 5%</t>
+        </is>
+      </c>
+      <c r="U286" s="15" t="inlineStr">
+        <is>
+          <t>Diving +2%</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="13" t="n">
@@ -22273,12 +22281,12 @@
       </c>
       <c r="B287" s="14" t="inlineStr">
         <is>
-          <t>JOUT</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="C287" s="15" t="inlineStr">
         <is>
-          <t>Johnson Outdoors Inc.</t>
+          <t>Metropolitan Bank Holding Corp</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
@@ -22288,67 +22296,59 @@
       </c>
       <c r="E287" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F287" s="18" t="n">
-        <v>489901344</v>
+        <v>1237248640</v>
       </c>
       <c r="G287" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H287" s="20" t="n">
-        <v>15.414</v>
+      <c r="H287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I287" s="20" t="n">
-        <v>26.50606053853296</v>
+        <v>12.33869</v>
       </c>
       <c r="J287" s="22" t="n">
-        <v>-34.23847463411765</v>
-      </c>
-      <c r="K287" s="22" t="n">
-        <v>6.32393274792691</v>
+        <v>11.56099812769128</v>
+      </c>
+      <c r="K287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L287" s="22" t="n">
-        <v>4.722703016296919</v>
-      </c>
-      <c r="M287" s="20" t="n">
-        <v>-2.839526226734348</v>
+        <v>0</v>
+      </c>
+      <c r="M287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N287" s="22" t="n">
-        <v>53.34578870086434</v>
+        <v>31.66505529209152</v>
       </c>
       <c r="O287" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P287" s="20" t="n">
-        <v>0.605555628096546</v>
-      </c>
-      <c r="Q287" s="15" t="inlineStr">
-        <is>
-          <t>Fishing (76%)</t>
-        </is>
-      </c>
-      <c r="R287" s="17" t="inlineStr">
-        <is>
-          <t>Fishing 76%; Diving 13%; Camping Watercraft Recreation 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q287" s="15" t="n"/>
+      <c r="R287" s="17" t="n"/>
       <c r="S287" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T287" s="17" t="inlineStr">
-        <is>
-          <t>US 87%; CA 6%; Europe 5%</t>
-        </is>
-      </c>
-      <c r="U287" s="15" t="inlineStr">
-        <is>
-          <t>Diving +2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T287" s="17" t="n"/>
+      <c r="U287" s="15" t="n"/>
     </row>
     <row r="288" ht="16" customHeight="1">
       <c r="A288" s="13" t="n">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>BALY</t>
+          <t>BBXIB</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Bally'S Corporation</t>
+          <t>BBX Capital, Inc.</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
@@ -28752,11 +28752,11 @@
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F63" s="18" t="n">
-        <v>733252928</v>
+        <v>49186460</v>
       </c>
       <c r="G63" s="19" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         </is>
       </c>
       <c r="H63" s="20" t="n">
-        <v>23.661</v>
+        <v>-5.40957818114807</v>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
@@ -28772,43 +28772,47 @@
         </is>
       </c>
       <c r="J63" s="22" t="n">
-        <v>-70.66868548761342</v>
+        <v>-94.174291054896</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>-1.45483923953113</v>
+        <v>-16.44198945340402</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>9.525642550682569</v>
+        <v>-14.94378696187978</v>
       </c>
       <c r="M63" s="20" t="n">
-        <v>14.92238631163372</v>
+        <v>-0.4861328664885285</v>
       </c>
       <c r="N63" s="22" t="n">
-        <v>7.380075456400011</v>
+        <v>21.52580455179199</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P63" s="20" t="n">
-        <v>0.3636883871993316</v>
+        <v>0.2850433298645005</v>
       </c>
       <c r="Q63" s="15" t="inlineStr">
         <is>
-          <t>Casinos Resorts (56%)</t>
+          <t>Bbx Sweet Holdings (39%)</t>
         </is>
       </c>
       <c r="R63" s="17" t="inlineStr">
         <is>
-          <t>Casinos Resorts 56%; International Interactive 16%; Intralot B2C 15%</t>
+          <t>Bbx Sweet Holdings 39%; Renin Holdings LLC 29%; Altman 16%</t>
         </is>
       </c>
       <c r="S63" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="T63" s="17" t="inlineStr">
+        <is>
+          <t>Non Us 67%; CA 33%</t>
+        </is>
+      </c>
       <c r="U63" s="15" t="inlineStr">
         <is>
-          <t>Intralot B2B -24%</t>
+          <t>Bbx Sweet Holdings +39%</t>
         </is>
       </c>
     </row>
@@ -28818,12 +28822,12 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>ZD</t>
+          <t>BALY</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Ziff Davis Inc. Common Stock</t>
+          <t>Bally'S Corporation</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -28833,11 +28837,11 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F64" s="18" t="n">
-        <v>1857240832</v>
+        <v>733252928</v>
       </c>
       <c r="G64" s="19" t="inlineStr">
         <is>
@@ -28845,53 +28849,51 @@
         </is>
       </c>
       <c r="H64" s="20" t="n">
-        <v>5.399</v>
-      </c>
-      <c r="I64" s="20" t="n">
-        <v>43.094017</v>
+        <v>23.661</v>
+      </c>
+      <c r="I64" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J64" s="22" t="n">
-        <v>8.34598809915534</v>
+        <v>-70.66868548761342</v>
       </c>
       <c r="K64" s="22" t="n">
-        <v>4.83228178651303</v>
+        <v>-1.45483923953113</v>
       </c>
       <c r="L64" s="22" t="n">
-        <v>23.10724139166577</v>
+        <v>9.525642550682569</v>
       </c>
       <c r="M64" s="20" t="n">
-        <v>0.7737902119589203</v>
+        <v>14.92238631163372</v>
       </c>
       <c r="N64" s="22" t="n">
-        <v>22.98117793085206</v>
+        <v>7.380075456400011</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P64" s="20" t="n">
-        <v>0.2143031565403679</v>
+        <v>0.3636883871993316</v>
       </c>
       <c r="Q64" s="15" t="inlineStr">
         <is>
-          <t>Health And Wellness (27%)</t>
+          <t>Casinos Resorts (56%)</t>
         </is>
       </c>
       <c r="R64" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health And Wellness 27%; Technology And Shopping 25%; Cybersecurity And Martech </t>
+          <t>Casinos Resorts 56%; International Interactive 16%; Intralot B2C 15%</t>
         </is>
       </c>
       <c r="S64" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T64" s="17" t="inlineStr">
-        <is>
-          <t>US 84%; Non Us 16%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T64" s="17" t="n"/>
       <c r="U64" s="15" t="inlineStr">
         <is>
-          <t>Health And Wellness +11%</t>
+          <t>Intralot B2B -24%</t>
         </is>
       </c>
     </row>
@@ -28901,12 +28903,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>LGIH</t>
+          <t>AILIM</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>LGI Homes, Inc.</t>
+          <t>Ameren Illinois Company</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
@@ -28916,11 +28918,11 @@
       </c>
       <c r="E65" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F65" s="18" t="n">
-        <v>1529613184</v>
+        <v>2036192000</v>
       </c>
       <c r="G65" s="19" t="inlineStr">
         <is>
@@ -28928,40 +28930,40 @@
         </is>
       </c>
       <c r="H65" s="20" t="n">
-        <v>36.709</v>
+        <v>4.717642619311876</v>
       </c>
       <c r="I65" s="20" t="n">
-        <v>21.657894</v>
+        <v>4.5842643</v>
       </c>
       <c r="J65" s="22" t="n">
-        <v>-22.0697028094676</v>
+        <v>-2.30823026512234</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>1.64070153314025</v>
+        <v>7.96729943189691</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>4.99910384629171</v>
+        <v>46.87825182101977</v>
       </c>
       <c r="M65" s="20" t="n">
-        <v>19.75262918877576</v>
+        <v>3.587680355160932</v>
       </c>
       <c r="N65" s="22" t="n">
-        <v>-29.365494679094</v>
+        <v>12.0169146635057</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P65" s="20" t="n">
-        <v>0.2168651756381262</v>
+        <v>0.2156909199657141</v>
       </c>
       <c r="Q65" s="15" t="inlineStr">
         <is>
-          <t>Central Reportable (27%)</t>
+          <t>Union Electric Company (36%)</t>
         </is>
       </c>
       <c r="R65" s="17" t="inlineStr">
         <is>
-          <t>Central Reportable 27%; Southeast Reportable 25%; West Reportable 20%</t>
+          <t>Union Electric Company 36%; Ameren Illinois Electric Distribution 21%; Ameren Il</t>
         </is>
       </c>
       <c r="S65" s="18" t="n">
@@ -28970,7 +28972,7 @@
       <c r="T65" s="17" t="n"/>
       <c r="U65" s="15" t="inlineStr">
         <is>
-          <t>Southeast Reportable -12%</t>
+          <t>Union Electric Compa -81%</t>
         </is>
       </c>
     </row>
@@ -28980,12 +28982,12 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>ANGO</t>
+          <t>ZD</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>AngioDynamics, Inc.</t>
+          <t>Ziff Davis Inc. Common Stock</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -28995,11 +28997,11 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F66" s="18" t="n">
-        <v>553673472</v>
+        <v>1857240832</v>
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
@@ -29007,57 +29009,53 @@
         </is>
       </c>
       <c r="H66" s="20" t="n">
-        <v>154.1408945640277</v>
-      </c>
-      <c r="I66" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.399</v>
+      </c>
+      <c r="I66" s="20" t="n">
+        <v>43.094017</v>
       </c>
       <c r="J66" s="22" t="n">
-        <v>-19.82765414883135</v>
+        <v>8.34598809915534</v>
       </c>
       <c r="K66" s="22" t="n">
-        <v>-29.29316030601931</v>
+        <v>4.83228178651303</v>
       </c>
       <c r="L66" s="22" t="n">
-        <v>0.87369511514861</v>
-      </c>
-      <c r="M66" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>23.10724139166577</v>
+      </c>
+      <c r="M66" s="20" t="n">
+        <v>0.7737902119589203</v>
       </c>
       <c r="N66" s="22" t="n">
-        <v>17.44820466911453</v>
+        <v>22.98117793085206</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P66" s="20" t="n">
-        <v>0.2638440893100342</v>
+        <v>0.2143031565403679</v>
       </c>
       <c r="Q66" s="15" t="inlineStr">
         <is>
-          <t>Med Device (31%)</t>
+          <t>Health And Wellness (27%)</t>
         </is>
       </c>
       <c r="R66" s="17" t="inlineStr">
         <is>
-          <t>Med Device 31%; Med Device 29%; Med Tech 25%</t>
+          <t xml:space="preserve">Health And Wellness 27%; Technology And Shopping 25%; Cybersecurity And Martech </t>
         </is>
       </c>
       <c r="S66" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T66" s="17" t="inlineStr">
         <is>
-          <t>US 82%; Non Us 14%; International 3%</t>
+          <t>US 84%; Non Us 16%</t>
         </is>
       </c>
       <c r="U66" s="15" t="inlineStr">
         <is>
-          <t>Med Tech +37%</t>
+          <t>Health And Wellness +11%</t>
         </is>
       </c>
     </row>
@@ -29067,12 +29065,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>LGIH</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Ralph Lauren Corporation Class</t>
+          <t>LGI Homes, Inc.</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -29082,11 +29080,11 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F67" s="18" t="n">
-        <v>24470740992</v>
+        <v>1529613184</v>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
@@ -29094,53 +29092,49 @@
         </is>
       </c>
       <c r="H67" s="20" t="n">
-        <v>16.717</v>
+        <v>36.709</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>27.247183</v>
+        <v>21.657894</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>3.27476083036231</v>
+        <v>-22.0697028094676</v>
       </c>
       <c r="K67" s="22" t="n">
-        <v>56.35903073173063</v>
+        <v>1.64070153314025</v>
       </c>
       <c r="L67" s="22" t="n">
-        <v>18.05286832213938</v>
+        <v>4.99910384629171</v>
       </c>
       <c r="M67" s="20" t="n">
-        <v>0.6446856440712677</v>
+        <v>19.75262918877576</v>
       </c>
       <c r="N67" s="22" t="n">
-        <v>37.76939056738206</v>
+        <v>-29.365494679094</v>
       </c>
       <c r="O67" s="18" t="n">
         <v>5</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>0.3374629326871758</v>
+        <v>0.2168651756381262</v>
       </c>
       <c r="Q67" s="15" t="inlineStr">
         <is>
-          <t>North America (43%)</t>
+          <t>Central Reportable (27%)</t>
         </is>
       </c>
       <c r="R67" s="17" t="inlineStr">
         <is>
-          <t>North America 43%; Europe 31%; Asia 25%</t>
+          <t>Central Reportable 27%; Southeast Reportable 25%; West Reportable 20%</t>
         </is>
       </c>
       <c r="S67" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T67" s="17" t="inlineStr">
-        <is>
-          <t>Americas 32%; US 30%; Europe 21%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T67" s="17" t="n"/>
       <c r="U67" s="15" t="inlineStr">
         <is>
-          <t>Asia +23%</t>
+          <t>Southeast Reportable -12%</t>
         </is>
       </c>
     </row>
@@ -29150,12 +29144,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>ANGO</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>IES Holdings, Inc.</t>
+          <t>AngioDynamics, Inc.</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -29165,11 +29159,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>16238614528</v>
+        <v>553673472</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -29177,53 +29171,57 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>6.032</v>
-      </c>
-      <c r="I68" s="20" t="n">
-        <v>9.522522</v>
+        <v>154.1408945640277</v>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J68" s="22" t="n">
-        <v>10.44035429017092</v>
+        <v>-19.82765414883135</v>
       </c>
       <c r="K68" s="22" t="n">
-        <v>36.29365645046329</v>
+        <v>-29.29316030601931</v>
       </c>
       <c r="L68" s="22" t="n">
-        <v>49.92574591602538</v>
-      </c>
-      <c r="M68" s="20" t="n">
-        <v>0.3174689021092482</v>
+        <v>0.87369511514861</v>
+      </c>
+      <c r="M68" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N68" s="22" t="n">
-        <v>39.81650218185786</v>
+        <v>17.44820466911453</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>0.2348193870274426</v>
+        <v>0.2638440893100342</v>
       </c>
       <c r="Q68" s="15" t="inlineStr">
         <is>
-          <t>UAN (29%)</t>
+          <t>Med Device (31%)</t>
         </is>
       </c>
       <c r="R68" s="17" t="inlineStr">
         <is>
-          <t>UAN 29%; Ammonia 27%; Urea 25%</t>
+          <t>Med Device 31%; Med Device 29%; Med Tech 25%</t>
         </is>
       </c>
       <c r="S68" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T68" s="17" t="inlineStr">
         <is>
-          <t>North America 52%; US 23%; Europeand Other 10%</t>
+          <t>US 82%; Non Us 14%; International 3%</t>
         </is>
       </c>
       <c r="U68" s="15" t="inlineStr">
         <is>
-          <t>UAN +29%</t>
+          <t>Med Tech +37%</t>
         </is>
       </c>
     </row>
@@ -29233,12 +29231,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Boyd Gaming Corporation</t>
+          <t>Ralph Lauren Corporation Class</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -29252,7 +29250,7 @@
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>6667415040</v>
+        <v>24470740992</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -29260,49 +29258,53 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>7.799</v>
+        <v>16.717</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>3.965517</v>
+        <v>27.247183</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>7.00265050461545</v>
+        <v>3.27476083036231</v>
       </c>
       <c r="K69" s="22" t="n">
-        <v>16.8187845866867</v>
+        <v>56.35903073173063</v>
       </c>
       <c r="L69" s="22" t="n">
-        <v>67.88213810456836</v>
+        <v>18.05286832213938</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.6827473523004249</v>
+        <v>0.6446856440712677</v>
       </c>
       <c r="N69" s="22" t="n">
-        <v>9.149903301097559</v>
+        <v>37.76939056738206</v>
       </c>
       <c r="O69" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="P69" s="20" t="n">
+        <v>0.3374629326871758</v>
+      </c>
+      <c r="Q69" s="15" t="inlineStr">
+        <is>
+          <t>North America (43%)</t>
+        </is>
+      </c>
+      <c r="R69" s="17" t="inlineStr">
+        <is>
+          <t>North America 43%; Europe 31%; Asia 25%</t>
+        </is>
+      </c>
+      <c r="S69" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="P69" s="20" t="n">
-        <v>0.3844755148157384</v>
-      </c>
-      <c r="Q69" s="15" t="inlineStr">
-        <is>
-          <t>Midwest And South (55%)</t>
-        </is>
-      </c>
-      <c r="R69" s="17" t="inlineStr">
-        <is>
-          <t>Midwest And South 55%; Las Vegas Locals 24%; Online 15%</t>
-        </is>
-      </c>
-      <c r="S69" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" s="17" t="n"/>
+      <c r="T69" s="17" t="inlineStr">
+        <is>
+          <t>Americas 32%; US 30%; Europe 21%</t>
+        </is>
+      </c>
       <c r="U69" s="15" t="inlineStr">
         <is>
-          <t>Online +17%</t>
+          <t>Asia +23%</t>
         </is>
       </c>
     </row>
@@ -29312,12 +29314,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>MORN</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Morningstar, Inc.</t>
+          <t>IES Holdings, Inc.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -29327,11 +29329,11 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>5881032192</v>
+        <v>16238614528</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -29339,40 +29341,40 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>11.344</v>
+        <v>6.032</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>15.829067</v>
+        <v>9.522522</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>2.42704489253352</v>
+        <v>10.44035429017092</v>
       </c>
       <c r="K70" s="22" t="n">
-        <v>23.16894855775621</v>
+        <v>36.29365645046329</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>30.82841652049115</v>
+        <v>49.92574591602538</v>
       </c>
       <c r="M70" s="20" t="n">
-        <v>1.577654209233157</v>
+        <v>0.3174689021092482</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>-40.9052016570997</v>
+        <v>39.81650218185786</v>
       </c>
       <c r="O70" s="18" t="n">
         <v>6</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>0.2508840927268516</v>
+        <v>0.2348193870274426</v>
       </c>
       <c r="Q70" s="15" t="inlineStr">
         <is>
-          <t>Morningstar Data And A (37%)</t>
+          <t>UAN (29%)</t>
         </is>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
-          <t>Morningstar Data And Analytics 37%; Pitch Book 28%; Morningstar Credit 13%</t>
+          <t>UAN 29%; Ammonia 27%; Urea 25%</t>
         </is>
       </c>
       <c r="S70" s="18" t="n">
@@ -29380,12 +29382,12 @@
       </c>
       <c r="T70" s="17" t="inlineStr">
         <is>
-          <t>US 56%; Non United States 22%; Europe Excluding United Kingd</t>
+          <t>North America 52%; US 23%; Europeand Other 10%</t>
         </is>
       </c>
       <c r="U70" s="15" t="inlineStr">
         <is>
-          <t>Morningstar Credit +22%</t>
+          <t>UAN +29%</t>
         </is>
       </c>
     </row>
@@ -29395,12 +29397,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>ONT</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Onterris Inc. Common Stock</t>
+          <t>Boyd Gaming Corporation</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -29410,11 +29412,11 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>724230144</v>
+        <v>6667415040</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -29422,53 +29424,49 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>16.378</v>
+        <v>7.799</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>133.6</v>
+        <v>3.965517</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>-8.53148707933356</v>
+        <v>7.00265050461545</v>
       </c>
       <c r="K71" s="22" t="n">
-        <v>1.09656856547805</v>
+        <v>16.8187845866867</v>
       </c>
       <c r="L71" s="22" t="n">
-        <v>9.83735843513481</v>
+        <v>67.88213810456836</v>
       </c>
       <c r="M71" s="20" t="n">
-        <v>3.391209625105565</v>
+        <v>0.6827473523004249</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>-20.50882534955431</v>
+        <v>9.149903301097559</v>
       </c>
       <c r="O71" s="18" t="n">
         <v>4</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>0.3314348693108636</v>
+        <v>0.3844755148157384</v>
       </c>
       <c r="Q71" s="15" t="inlineStr">
         <is>
-          <t>Assessment Permitting  (34%)</t>
+          <t>Midwest And South (55%)</t>
         </is>
       </c>
       <c r="R71" s="17" t="inlineStr">
         <is>
-          <t>Assessment Permitting And Response 34%; Remediation And Reuse 34%; Measurement A</t>
+          <t>Midwest And South 55%; Las Vegas Locals 24%; Online 15%</t>
         </is>
       </c>
       <c r="S71" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T71" s="17" t="inlineStr">
-        <is>
-          <t>US 82%; CA 14%; Other International 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T71" s="17" t="n"/>
       <c r="U71" s="15" t="inlineStr">
         <is>
-          <t>Assessment Permittin +43%</t>
+          <t>Online +17%</t>
         </is>
       </c>
     </row>
@@ -29478,12 +29476,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>ICFI</t>
+          <t>MORN</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Icf International, Inc.</t>
+          <t>Morningstar, Inc.</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -29493,11 +29491,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>1294629888</v>
+        <v>5881032192</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -29505,53 +29503,53 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>9.545999999999999</v>
+        <v>11.344</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>15.444924</v>
+        <v>15.829067</v>
       </c>
       <c r="J72" s="22" t="n">
-        <v>-7.31631169383114</v>
+        <v>2.42704489253352</v>
       </c>
       <c r="K72" s="22" t="n">
-        <v>10.3385336795687</v>
+        <v>23.16894855775621</v>
       </c>
       <c r="L72" s="22" t="n">
-        <v>11.17134288827532</v>
+        <v>30.82841652049115</v>
       </c>
       <c r="M72" s="20" t="n">
-        <v>2.087444193484964</v>
+        <v>1.577654209233157</v>
       </c>
       <c r="N72" s="22" t="n">
-        <v>-30.44028095764692</v>
+        <v>-40.9052016570997</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>0.2989645592018218</v>
+        <v>0.2508840927268516</v>
       </c>
       <c r="Q72" s="15" t="inlineStr">
         <is>
-          <t>US State And Internati (42%)</t>
+          <t>Morningstar Data And A (37%)</t>
         </is>
       </c>
       <c r="R72" s="17" t="inlineStr">
         <is>
-          <t>US State And International Government 42%; US Federal Government 29%; Commercial</t>
+          <t>Morningstar Data And Analytics 37%; Pitch Book 28%; Morningstar Credit 13%</t>
         </is>
       </c>
       <c r="S72" s="18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T72" s="17" t="inlineStr">
         <is>
-          <t>US 92%; Non Us 8%</t>
+          <t>US 56%; Non United States 22%; Europe Excluding United Kingd</t>
         </is>
       </c>
       <c r="U72" s="15" t="inlineStr">
         <is>
-          <t>Commercial +23%</t>
+          <t>Morningstar Credit +22%</t>
         </is>
       </c>
     </row>
@@ -44776,12 +44774,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Textron Inc.</t>
+          <t>Cosmos Holdings Inc.</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -44791,11 +44789,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>15862152192</v>
+        <v>15783100</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -44803,53 +44801,51 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>11.026</v>
-      </c>
-      <c r="I68" s="20" t="n">
-        <v>17.408398</v>
+        <v>-2.265769243206465</v>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J68" s="22" t="n">
-        <v>-2.6803229068672</v>
+        <v>-54.49139902807433</v>
       </c>
       <c r="K68" s="22" t="n">
-        <v>14.59637046307884</v>
+        <v>-43.90414491780297</v>
       </c>
       <c r="L68" s="22" t="n">
-        <v>11.18646299710297</v>
+        <v>-23.21524229102561</v>
       </c>
       <c r="M68" s="20" t="n">
-        <v>1.291936433195997</v>
+        <v>-1.231101675508694</v>
       </c>
       <c r="N68" s="22" t="n">
-        <v>25.09145155795542</v>
+        <v>-32.376681033034</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>0.3022887133229401</v>
+        <v>0.8617579542623139</v>
       </c>
       <c r="Q68" s="15" t="inlineStr">
         <is>
-          <t>Textron Aviation (40%)</t>
+          <t>Wholesale (93%)</t>
         </is>
       </c>
       <c r="R68" s="17" t="inlineStr">
         <is>
-          <t>Textron Aviation 40%; Bell 27%; Industrial 26%</t>
+          <t>Wholesale 93%; Nutraceuticals And Pharmaceuticals 5%; Pharmamanufacturing 2%</t>
         </is>
       </c>
       <c r="S68" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T68" s="17" t="inlineStr">
-        <is>
-          <t>US 69%; International 14%; Europe 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T68" s="17" t="n"/>
       <c r="U68" s="15" t="inlineStr">
         <is>
-          <t>Finance +50%</t>
+          <t>Nutraceuticals And P +117%</t>
         </is>
       </c>
     </row>
@@ -44859,12 +44855,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Urban Outfitters, Inc.</t>
+          <t>Textron Inc.</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -44874,11 +44870,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>6297604096</v>
+        <v>15862152192</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -44886,49 +44882,53 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>9.372999999999999</v>
+        <v>11.026</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>14.142308</v>
+        <v>17.408398</v>
       </c>
       <c r="J69" s="22" t="n">
-        <v>-2.38208438242834</v>
+        <v>-2.6803229068672</v>
       </c>
       <c r="K69" s="22" t="n">
-        <v>22.14267757694075</v>
+        <v>14.59637046307884</v>
       </c>
       <c r="L69" s="22" t="n">
-        <v>11.84586309091286</v>
+        <v>11.18646299710297</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.7251890210339813</v>
+        <v>1.291936433195997</v>
       </c>
       <c r="N69" s="22" t="n">
-        <v>-0.27318255804295</v>
+        <v>25.09145155795542</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.8181571682030334</v>
+        <v>0.3022887133229401</v>
       </c>
       <c r="Q69" s="15" t="inlineStr">
         <is>
-          <t>Retail Operations (90%)</t>
+          <t>Textron Aviation (40%)</t>
         </is>
       </c>
       <c r="R69" s="17" t="inlineStr">
         <is>
-          <t>Retail Operations 90%; Wholesale Operations 5%; Subscription Operations 5%</t>
+          <t>Textron Aviation 40%; Bell 27%; Industrial 26%</t>
         </is>
       </c>
       <c r="S69" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="T69" s="17" t="inlineStr">
+        <is>
+          <t>US 69%; International 14%; Europe 9%</t>
+        </is>
+      </c>
       <c r="U69" s="15" t="inlineStr">
         <is>
-          <t>Subscription Operati +50%</t>
+          <t>Finance +50%</t>
         </is>
       </c>
     </row>
@@ -44938,12 +44938,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>LMB</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Limbach Holdings, Inc.</t>
+          <t>Urban Outfitters, Inc.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -44953,11 +44953,11 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>968705920</v>
+        <v>6297604096</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -44965,40 +44965,40 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>16.376</v>
+        <v>9.372999999999999</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>29.656935</v>
+        <v>14.142308</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>-0.7220198183623701</v>
+        <v>-2.38208438242834</v>
       </c>
       <c r="K70" s="22" t="n">
-        <v>15.34248993223126</v>
+        <v>22.14267757694075</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>10.80621022751869</v>
+        <v>11.84586309091286</v>
       </c>
       <c r="M70" s="20" t="n">
-        <v>0.6370412762000143</v>
+        <v>0.7251890210339813</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>-40.76220352900898</v>
+        <v>-0.27318255804295</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>0.544960857181082</v>
+        <v>0.8181571682030334</v>
       </c>
       <c r="Q70" s="15" t="inlineStr">
         <is>
-          <t>Owner Direct Relations (65%)</t>
+          <t>Retail Operations (90%)</t>
         </is>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
-          <t>Owner Direct Relationships 65%; General Contractor Construction Manager Relation</t>
+          <t>Retail Operations 90%; Wholesale Operations 5%; Subscription Operations 5%</t>
         </is>
       </c>
       <c r="S70" s="18" t="n">
@@ -45007,7 +45007,7 @@
       <c r="T70" s="17" t="n"/>
       <c r="U70" s="15" t="inlineStr">
         <is>
-          <t>Owner Direct Relatio +41%</t>
+          <t>Subscription Operati +50%</t>
         </is>
       </c>
     </row>
@@ -45017,12 +45017,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>LMB</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Telos Corporation</t>
+          <t>Limbach Holdings, Inc.</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -45032,11 +45032,11 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>336686304</v>
+        <v>968705920</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -45044,42 +45044,40 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>-10.77324023011307</v>
-      </c>
-      <c r="I71" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.376</v>
+      </c>
+      <c r="I71" s="20" t="n">
+        <v>29.656935</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>4.36735540960422</v>
+        <v>-0.7220198183623701</v>
       </c>
       <c r="K71" s="22" t="n">
-        <v>-34.77000960111722</v>
+        <v>15.34248993223126</v>
       </c>
       <c r="L71" s="22" t="n">
-        <v>-15.29383210460847</v>
+        <v>10.80621022751869</v>
       </c>
       <c r="M71" s="20" t="n">
-        <v>1.790160682404285</v>
+        <v>0.6370412762000143</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>59.09089554439946</v>
+        <v>-40.76220352900898</v>
       </c>
       <c r="O71" s="18" t="n">
         <v>2</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>0.7045033237128298</v>
+        <v>0.544960857181082</v>
       </c>
       <c r="Q71" s="15" t="inlineStr">
         <is>
-          <t>Security Solutions (82%)</t>
+          <t>Owner Direct Relations (65%)</t>
         </is>
       </c>
       <c r="R71" s="17" t="inlineStr">
         <is>
-          <t>Security Solutions 82%; Secure Networks 18%</t>
+          <t>Owner Direct Relationships 65%; General Contractor Construction Manager Relation</t>
         </is>
       </c>
       <c r="S71" s="18" t="n">
@@ -45088,7 +45086,7 @@
       <c r="T71" s="17" t="n"/>
       <c r="U71" s="15" t="inlineStr">
         <is>
-          <t>Security Solutions +103%</t>
+          <t>Owner Direct Relatio +41%</t>
         </is>
       </c>
     </row>
@@ -45098,12 +45096,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Sunoco LP</t>
+          <t>Telos Corporation</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -45113,11 +45111,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>12529394688</v>
+        <v>336686304</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -45125,53 +45123,51 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>10.608</v>
-      </c>
-      <c r="I72" s="20" t="n">
-        <v>16.964285</v>
+        <v>-10.77324023011307</v>
+      </c>
+      <c r="I72" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J72" s="22" t="n">
-        <v>6.31074646035847</v>
+        <v>4.36735540960422</v>
       </c>
       <c r="K72" s="22" t="n">
-        <v>12.76646139270487</v>
+        <v>-34.77000960111722</v>
       </c>
       <c r="L72" s="22" t="n">
-        <v>8.12711643657202</v>
+        <v>-15.29383210460847</v>
       </c>
       <c r="M72" s="20" t="n">
-        <v>5.294070512820513</v>
+        <v>1.790160682404285</v>
       </c>
       <c r="N72" s="22" t="n">
-        <v>36.76778730902324</v>
+        <v>59.09089554439946</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>0.8700313372360839</v>
+        <v>0.7045033237128298</v>
       </c>
       <c r="Q72" s="15" t="inlineStr">
         <is>
-          <t>Fuel Distribution (93%)</t>
+          <t>Security Solutions (82%)</t>
         </is>
       </c>
       <c r="R72" s="17" t="inlineStr">
         <is>
-          <t>Fuel Distribution 93%; Terminals 4%; Pipeline Systems 2%</t>
+          <t>Security Solutions 82%; Secure Networks 18%</t>
         </is>
       </c>
       <c r="S72" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T72" s="17" t="inlineStr">
-        <is>
-          <t>US 96%; CA 2%; Foreign 1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T72" s="17" t="n"/>
       <c r="U72" s="15" t="inlineStr">
         <is>
-          <t>Pipeline Systems +33%</t>
+          <t>Security Solutions +103%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -627,7 +627,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>3,214</t>
+          <t>3,218</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>417</t>
         </is>
       </c>
     </row>
@@ -22198,12 +22198,12 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>JOUT</t>
+          <t>MCB</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
         <is>
-          <t>Johnson Outdoors Inc.</t>
+          <t>Metropolitan Bank Holding Corp</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
@@ -22213,67 +22213,59 @@
       </c>
       <c r="E286" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F286" s="18" t="n">
-        <v>489901344</v>
+        <v>1237248640</v>
       </c>
       <c r="G286" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H286" s="20" t="n">
-        <v>15.414</v>
+      <c r="H286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I286" s="20" t="n">
-        <v>26.50606053853296</v>
+        <v>12.33869</v>
       </c>
       <c r="J286" s="22" t="n">
-        <v>-34.23847463411765</v>
-      </c>
-      <c r="K286" s="22" t="n">
-        <v>6.32393274792691</v>
+        <v>11.56099812769128</v>
+      </c>
+      <c r="K286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L286" s="22" t="n">
-        <v>4.722703016296919</v>
-      </c>
-      <c r="M286" s="20" t="n">
-        <v>-2.839526226734348</v>
+        <v>0</v>
+      </c>
+      <c r="M286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N286" s="22" t="n">
-        <v>53.34578870086434</v>
+        <v>31.66505529209152</v>
       </c>
       <c r="O286" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P286" s="20" t="n">
-        <v>0.605555628096546</v>
-      </c>
-      <c r="Q286" s="15" t="inlineStr">
-        <is>
-          <t>Fishing (76%)</t>
-        </is>
-      </c>
-      <c r="R286" s="17" t="inlineStr">
-        <is>
-          <t>Fishing 76%; Diving 13%; Camping Watercraft Recreation 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q286" s="15" t="n"/>
+      <c r="R286" s="17" t="n"/>
       <c r="S286" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T286" s="17" t="inlineStr">
-        <is>
-          <t>US 87%; CA 6%; Europe 5%</t>
-        </is>
-      </c>
-      <c r="U286" s="15" t="inlineStr">
-        <is>
-          <t>Diving +2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T286" s="17" t="n"/>
+      <c r="U286" s="15" t="n"/>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="13" t="n">
@@ -22281,12 +22273,12 @@
       </c>
       <c r="B287" s="14" t="inlineStr">
         <is>
-          <t>MCB</t>
+          <t>JOUT</t>
         </is>
       </c>
       <c r="C287" s="15" t="inlineStr">
         <is>
-          <t>Metropolitan Bank Holding Corp</t>
+          <t>Johnson Outdoors Inc.</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
@@ -22296,59 +22288,67 @@
       </c>
       <c r="E287" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F287" s="18" t="n">
-        <v>1237248640</v>
+        <v>489901344</v>
       </c>
       <c r="G287" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H287" s="20" t="n">
+        <v>15.414</v>
       </c>
       <c r="I287" s="20" t="n">
-        <v>12.33869</v>
+        <v>26.50606053853296</v>
       </c>
       <c r="J287" s="22" t="n">
-        <v>11.56099812769128</v>
-      </c>
-      <c r="K287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-34.23847463411765</v>
+      </c>
+      <c r="K287" s="22" t="n">
+        <v>6.32393274792691</v>
       </c>
       <c r="L287" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.722703016296919</v>
+      </c>
+      <c r="M287" s="20" t="n">
+        <v>-2.839526226734348</v>
       </c>
       <c r="N287" s="22" t="n">
-        <v>31.66505529209152</v>
+        <v>53.34578870086434</v>
       </c>
       <c r="O287" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q287" s="15" t="n"/>
-      <c r="R287" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="P287" s="20" t="n">
+        <v>0.605555628096546</v>
+      </c>
+      <c r="Q287" s="15" t="inlineStr">
+        <is>
+          <t>Fishing (76%)</t>
+        </is>
+      </c>
+      <c r="R287" s="17" t="inlineStr">
+        <is>
+          <t>Fishing 76%; Diving 13%; Camping Watercraft Recreation 11%</t>
+        </is>
+      </c>
       <c r="S287" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T287" s="17" t="n"/>
-      <c r="U287" s="15" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="T287" s="17" t="inlineStr">
+        <is>
+          <t>US 87%; CA 6%; Europe 5%</t>
+        </is>
+      </c>
+      <c r="U287" s="15" t="inlineStr">
+        <is>
+          <t>Diving +2%</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="16" customHeight="1">
       <c r="A288" s="13" t="n">

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A3:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,8 +552,6 @@
     <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -576,7 +574,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -584,9 +581,8 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>UNIVERSE STATS</t>
         </is>
@@ -696,9 +692,8 @@
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TABS IN THIS WORKBOOK</t>
         </is>
@@ -819,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X312"/>
+  <dimension ref="A2:X312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -848,7 +843,6 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -882,7 +876,6 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -990,9 +983,8 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -1231,8 +1223,16 @@
       <c r="V13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="17" t="n"/>
-      <c r="X13" s="15" t="n"/>
+      <c r="W13" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X13" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -1321,7 +1321,11 @@
       <c r="V14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="17" t="n"/>
+      <c r="W14" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X14" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -1505,7 +1509,11 @@
       <c r="V16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="17" t="n"/>
+      <c r="W16" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X16" s="15" t="inlineStr">
         <is>
           <t>American Southern +39%</t>
@@ -1695,7 +1703,11 @@
       <c r="V18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="17" t="n"/>
+      <c r="W18" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X18" s="15" t="inlineStr">
         <is>
           <t>Reportable +267%</t>
@@ -1885,7 +1897,11 @@
       <c r="V20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="17" t="n"/>
+      <c r="W20" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X20" s="15" t="inlineStr">
         <is>
           <t>Commercial Banking +44%</t>
@@ -1966,8 +1982,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T21" s="15" t="n"/>
-      <c r="U21" s="17" t="n"/>
+      <c r="T21" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U21" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V21" s="18" t="n">
         <v>3</v>
       </c>
@@ -1976,7 +2000,11 @@
           <t>CA 68%; IL 26%; Other Countries 6%</t>
         </is>
       </c>
-      <c r="X21" s="15" t="n"/>
+      <c r="X21" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="13" t="n">
@@ -2348,13 +2376,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T25" s="15" t="n"/>
-      <c r="U25" s="17" t="n"/>
+      <c r="T25" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U25" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="17" t="n"/>
-      <c r="X25" s="15" t="n"/>
+      <c r="W25" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X25" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="13" t="n">
@@ -2432,13 +2476,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T26" s="15" t="n"/>
-      <c r="U26" s="17" t="n"/>
+      <c r="T26" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U26" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="17" t="n"/>
-      <c r="X26" s="15" t="n"/>
+      <c r="W26" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X26" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="13" t="n">
@@ -2518,13 +2578,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T27" s="15" t="n"/>
-      <c r="U27" s="17" t="n"/>
+      <c r="T27" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U27" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="17" t="n"/>
-      <c r="X27" s="15" t="n"/>
+      <c r="W27" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X27" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="13" t="n">
@@ -2694,13 +2770,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T29" s="15" t="n"/>
-      <c r="U29" s="17" t="n"/>
+      <c r="T29" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U29" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="17" t="n"/>
-      <c r="X29" s="15" t="n"/>
+      <c r="W29" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X29" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="13" t="n">
@@ -2787,7 +2879,11 @@
       <c r="V30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="17" t="n"/>
+      <c r="W30" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X30" s="15" t="inlineStr">
         <is>
           <t>Reportable +288%</t>
@@ -2870,13 +2966,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T31" s="15" t="n"/>
-      <c r="U31" s="17" t="n"/>
+      <c r="T31" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U31" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="n"/>
-      <c r="X31" s="15" t="n"/>
+      <c r="W31" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X31" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="13" t="n">
@@ -2956,13 +3068,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T32" s="15" t="n"/>
-      <c r="U32" s="17" t="n"/>
+      <c r="T32" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U32" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V32" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="17" t="n"/>
-      <c r="X32" s="15" t="n"/>
+      <c r="W32" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X32" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="13" t="n">
@@ -3138,8 +3266,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T34" s="15" t="n"/>
-      <c r="U34" s="17" t="n"/>
+      <c r="T34" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U34" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V34" s="18" t="n">
         <v>2</v>
       </c>
@@ -3148,7 +3284,11 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="X34" s="15" t="n"/>
+      <c r="X34" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="13" t="n">
@@ -3261,7 +3401,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E36" s="17" t="n"/>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F36" s="18" t="n">
         <v>2186936064</v>
       </c>
@@ -3314,13 +3458,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T36" s="15" t="n"/>
-      <c r="U36" s="17" t="n"/>
+      <c r="T36" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U36" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="17" t="n"/>
-      <c r="X36" s="15" t="n"/>
+      <c r="W36" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X36" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="13" t="n">
@@ -3398,13 +3558,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T37" s="15" t="n"/>
-      <c r="U37" s="17" t="n"/>
+      <c r="T37" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="17" t="n"/>
-      <c r="X37" s="15" t="n"/>
+      <c r="W37" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X37" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -3482,13 +3658,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T38" s="15" t="n"/>
-      <c r="U38" s="17" t="n"/>
+      <c r="T38" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U38" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="17" t="n"/>
-      <c r="X38" s="15" t="n"/>
+      <c r="W38" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X38" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="13" t="n">
@@ -3560,8 +3752,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T39" s="15" t="n"/>
-      <c r="U39" s="17" t="n"/>
+      <c r="T39" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U39" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V39" s="18" t="n">
         <v>5</v>
       </c>
@@ -3570,7 +3770,11 @@
           <t>US 85%; CN 8%; Other Countries 2%</t>
         </is>
       </c>
-      <c r="X39" s="15" t="n"/>
+      <c r="X39" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -3655,7 +3859,11 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="n"/>
+      <c r="W40" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>Publishing -18%</t>
@@ -3930,13 +4138,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T43" s="15" t="n"/>
-      <c r="U43" s="17" t="n"/>
+      <c r="T43" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U43" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="17" t="n"/>
-      <c r="X43" s="15" t="n"/>
+      <c r="W43" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X43" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="13" t="n">
@@ -4012,13 +4236,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T44" s="15" t="n"/>
-      <c r="U44" s="17" t="n"/>
+      <c r="T44" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U44" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="17" t="n"/>
-      <c r="X44" s="15" t="n"/>
+      <c r="W44" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X44" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -4101,7 +4341,11 @@
       <c r="V45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="17" t="n"/>
+      <c r="W45" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X45" s="15" t="inlineStr">
         <is>
           <t>Genie Retail Energy  +19%</t>
@@ -4180,8 +4424,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T46" s="15" t="n"/>
-      <c r="U46" s="17" t="n"/>
+      <c r="T46" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U46" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V46" s="18" t="n">
         <v>2</v>
       </c>
@@ -4190,7 +4442,11 @@
           <t>Domestic Sales 98%; International Sales 2%</t>
         </is>
       </c>
-      <c r="X46" s="15" t="n"/>
+      <c r="X46" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -4266,13 +4522,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T47" s="15" t="n"/>
-      <c r="U47" s="17" t="n"/>
+      <c r="T47" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U47" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="17" t="n"/>
-      <c r="X47" s="15" t="n"/>
+      <c r="W47" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X47" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="13" t="n">
@@ -4293,7 +4565,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E48" s="17" t="n"/>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F48" s="18" t="n">
         <v>532783922.1609974</v>
       </c>
@@ -4348,13 +4624,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T48" s="15" t="n"/>
-      <c r="U48" s="17" t="n"/>
+      <c r="T48" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U48" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="17" t="n"/>
-      <c r="X48" s="15" t="n"/>
+      <c r="W48" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X48" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -4434,8 +4726,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T49" s="15" t="n"/>
-      <c r="U49" s="17" t="n"/>
+      <c r="T49" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U49" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V49" s="18" t="n">
         <v>2</v>
       </c>
@@ -4444,7 +4744,11 @@
           <t>US 74%; Non Us 26%</t>
         </is>
       </c>
-      <c r="X49" s="15" t="n"/>
+      <c r="X49" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="13" t="n">
@@ -4618,13 +4922,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T51" s="15" t="n"/>
-      <c r="U51" s="17" t="n"/>
+      <c r="T51" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U51" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W51" s="17" t="n"/>
-      <c r="X51" s="15" t="n"/>
+      <c r="W51" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X51" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="13" t="n">
@@ -4698,8 +5018,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T52" s="15" t="n"/>
-      <c r="U52" s="17" t="n"/>
+      <c r="T52" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U52" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V52" s="18" t="n">
         <v>6</v>
       </c>
@@ -4708,7 +5036,11 @@
           <t>North America 24%; US 24%; EMEA 19%</t>
         </is>
       </c>
-      <c r="X52" s="15" t="n"/>
+      <c r="X52" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -4786,13 +5118,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T53" s="15" t="n"/>
-      <c r="U53" s="17" t="n"/>
+      <c r="T53" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U53" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="17" t="n"/>
-      <c r="X53" s="15" t="n"/>
+      <c r="W53" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X53" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="13" t="n">
@@ -4870,13 +5218,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T54" s="15" t="n"/>
-      <c r="U54" s="17" t="n"/>
+      <c r="T54" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U54" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W54" s="17" t="n"/>
-      <c r="X54" s="15" t="n"/>
+      <c r="W54" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X54" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="13" t="n">
@@ -4954,8 +5318,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T55" s="15" t="n"/>
-      <c r="U55" s="17" t="n"/>
+      <c r="T55" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U55" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V55" s="18" t="n">
         <v>2</v>
       </c>
@@ -4964,7 +5336,11 @@
           <t>US 95%; Non Us 5%</t>
         </is>
       </c>
-      <c r="X55" s="15" t="n"/>
+      <c r="X55" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="13" t="n">
@@ -5051,7 +5427,11 @@
       <c r="V56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W56" s="17" t="n"/>
+      <c r="W56" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X56" s="15" t="inlineStr">
         <is>
           <t>Zedge Marketplace +2%</t>
@@ -5130,13 +5510,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T57" s="15" t="n"/>
-      <c r="U57" s="17" t="n"/>
+      <c r="T57" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U57" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="17" t="n"/>
-      <c r="X57" s="15" t="n"/>
+      <c r="W57" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X57" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="13" t="n">
@@ -5212,13 +5608,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T58" s="15" t="n"/>
-      <c r="U58" s="17" t="n"/>
+      <c r="T58" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U58" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W58" s="17" t="n"/>
-      <c r="X58" s="15" t="n"/>
+      <c r="W58" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X58" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="13" t="n">
@@ -5296,13 +5708,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T59" s="15" t="n"/>
-      <c r="U59" s="17" t="n"/>
+      <c r="T59" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U59" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="17" t="n"/>
-      <c r="X59" s="15" t="n"/>
+      <c r="W59" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X59" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="13" t="n">
@@ -5382,13 +5810,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T60" s="15" t="n"/>
-      <c r="U60" s="17" t="n"/>
+      <c r="T60" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U60" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="n"/>
-      <c r="X60" s="15" t="n"/>
+      <c r="W60" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X60" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="13" t="n">
@@ -5466,13 +5910,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T61" s="15" t="n"/>
-      <c r="U61" s="17" t="n"/>
+      <c r="T61" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U61" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="17" t="n"/>
-      <c r="X61" s="15" t="n"/>
+      <c r="W61" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X61" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="13" t="n">
@@ -5561,7 +6021,11 @@
       <c r="V62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="17" t="n"/>
+      <c r="W62" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X62" s="15" t="inlineStr">
         <is>
           <t>Medicare +10%</t>
@@ -5651,7 +6115,11 @@
       <c r="V63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="17" t="n"/>
+      <c r="W63" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X63" s="15" t="inlineStr">
         <is>
           <t>Reportable -5%</t>
@@ -5734,13 +6202,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T64" s="15" t="n"/>
-      <c r="U64" s="17" t="n"/>
+      <c r="T64" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U64" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="17" t="n"/>
-      <c r="X64" s="15" t="n"/>
+      <c r="W64" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X64" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n">
@@ -5827,7 +6311,11 @@
       <c r="V65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="17" t="n"/>
+      <c r="W65" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X65" s="15" t="inlineStr">
         <is>
           <t>Annuities +88%</t>
@@ -5910,13 +6398,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T66" s="15" t="n"/>
-      <c r="U66" s="17" t="n"/>
+      <c r="T66" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U66" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="17" t="n"/>
-      <c r="X66" s="15" t="n"/>
+      <c r="W66" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X66" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="13" t="n">
@@ -6090,13 +6594,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T68" s="15" t="n"/>
-      <c r="U68" s="17" t="n"/>
+      <c r="T68" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U68" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V68" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W68" s="17" t="n"/>
-      <c r="X68" s="15" t="n"/>
+      <c r="W68" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X68" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="13" t="n">
@@ -6170,13 +6690,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T69" s="15" t="n"/>
-      <c r="U69" s="17" t="n"/>
+      <c r="T69" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U69" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="17" t="n"/>
-      <c r="X69" s="15" t="n"/>
+      <c r="W69" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X69" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n">
@@ -6252,13 +6788,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T70" s="15" t="n"/>
-      <c r="U70" s="17" t="n"/>
+      <c r="T70" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U70" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V70" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W70" s="17" t="n"/>
-      <c r="X70" s="15" t="n"/>
+      <c r="W70" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X70" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="13" t="n">
@@ -6439,7 +6991,11 @@
       <c r="V72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W72" s="17" t="n"/>
+      <c r="W72" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X72" s="15" t="inlineStr">
         <is>
           <t>Real Estate Operatio -11%</t>
@@ -6529,7 +7085,11 @@
       <c r="V73" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W73" s="17" t="n"/>
+      <c r="W73" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X73" s="15" t="inlineStr">
         <is>
           <t>Reportable +22%</t>
@@ -6608,13 +7168,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T74" s="15" t="n"/>
-      <c r="U74" s="17" t="n"/>
+      <c r="T74" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U74" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V74" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W74" s="17" t="n"/>
-      <c r="X74" s="15" t="n"/>
+      <c r="W74" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X74" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="13" t="n">
@@ -6688,13 +7264,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T75" s="15" t="n"/>
-      <c r="U75" s="17" t="n"/>
+      <c r="T75" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U75" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V75" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W75" s="17" t="n"/>
-      <c r="X75" s="15" t="n"/>
+      <c r="W75" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X75" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="13" t="n">
@@ -6772,13 +7364,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T76" s="15" t="n"/>
-      <c r="U76" s="17" t="n"/>
+      <c r="T76" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U76" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W76" s="17" t="n"/>
-      <c r="X76" s="15" t="n"/>
+      <c r="W76" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X76" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="13" t="n">
@@ -6867,7 +7475,11 @@
       <c r="V77" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W77" s="17" t="n"/>
+      <c r="W77" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
           <t>RX +22%</t>
@@ -7046,13 +7658,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T79" s="15" t="n"/>
-      <c r="U79" s="17" t="n"/>
+      <c r="T79" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U79" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V79" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W79" s="17" t="n"/>
-      <c r="X79" s="15" t="n"/>
+      <c r="W79" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X79" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="13" t="n">
@@ -7130,13 +7758,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T80" s="15" t="n"/>
-      <c r="U80" s="17" t="n"/>
+      <c r="T80" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U80" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="17" t="n"/>
-      <c r="X80" s="15" t="n"/>
+      <c r="W80" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X80" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="13" t="n">
@@ -7221,7 +7865,11 @@
       <c r="V81" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W81" s="17" t="n"/>
+      <c r="W81" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X81" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments -74%</t>
@@ -7304,13 +7952,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T82" s="15" t="n"/>
-      <c r="U82" s="17" t="n"/>
+      <c r="T82" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U82" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V82" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="17" t="n"/>
-      <c r="X82" s="15" t="n"/>
+      <c r="W82" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X82" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="13" t="n">
@@ -7395,7 +8059,11 @@
       <c r="V83" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W83" s="17" t="n"/>
+      <c r="W83" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X83" s="15" t="inlineStr">
         <is>
           <t>Land Development +4%</t>
@@ -7476,13 +8144,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T84" s="15" t="n"/>
-      <c r="U84" s="17" t="n"/>
+      <c r="T84" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U84" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V84" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W84" s="17" t="n"/>
-      <c r="X84" s="15" t="n"/>
+      <c r="W84" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X84" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="13" t="n">
@@ -7569,7 +8253,11 @@
       <c r="V85" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W85" s="17" t="n"/>
+      <c r="W85" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X85" s="15" t="inlineStr">
         <is>
           <t>Financial Services +11%</t>
@@ -7750,13 +8438,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T87" s="15" t="n"/>
-      <c r="U87" s="17" t="n"/>
+      <c r="T87" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U87" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V87" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W87" s="17" t="n"/>
-      <c r="X87" s="15" t="n"/>
+      <c r="W87" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X87" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="13" t="n">
@@ -7836,8 +8540,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T88" s="15" t="n"/>
-      <c r="U88" s="17" t="n"/>
+      <c r="T88" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U88" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V88" s="18" t="n">
         <v>1</v>
       </c>
@@ -7846,7 +8558,11 @@
           <t>Foreign Countries 100%</t>
         </is>
       </c>
-      <c r="X88" s="15" t="n"/>
+      <c r="X88" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -7926,13 +8642,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T89" s="15" t="n"/>
-      <c r="U89" s="17" t="n"/>
+      <c r="T89" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U89" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V89" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W89" s="17" t="n"/>
-      <c r="X89" s="15" t="n"/>
+      <c r="W89" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X89" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="13" t="n">
@@ -8004,13 +8736,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T90" s="15" t="n"/>
-      <c r="U90" s="17" t="n"/>
+      <c r="T90" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U90" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V90" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W90" s="17" t="n"/>
-      <c r="X90" s="15" t="n"/>
+      <c r="W90" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X90" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="13" t="n">
@@ -8090,8 +8838,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T91" s="15" t="n"/>
-      <c r="U91" s="17" t="n"/>
+      <c r="T91" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U91" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V91" s="18" t="n">
         <v>2</v>
       </c>
@@ -8100,7 +8856,11 @@
           <t>JP 100%; US 0%</t>
         </is>
       </c>
-      <c r="X91" s="15" t="n"/>
+      <c r="X91" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -8121,7 +8881,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E92" s="17" t="n"/>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F92" s="18" t="n">
         <v>28291916</v>
       </c>
@@ -8176,13 +8940,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T92" s="15" t="n"/>
-      <c r="U92" s="17" t="n"/>
+      <c r="T92" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U92" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V92" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W92" s="17" t="n"/>
-      <c r="X92" s="15" t="n"/>
+      <c r="W92" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X92" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="13" t="n">
@@ -8360,13 +9140,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T94" s="15" t="n"/>
-      <c r="U94" s="17" t="n"/>
+      <c r="T94" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U94" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V94" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="17" t="n"/>
-      <c r="X94" s="15" t="n"/>
+      <c r="W94" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X94" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="13" t="n">
@@ -8440,8 +9236,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T95" s="15" t="n"/>
-      <c r="U95" s="17" t="n"/>
+      <c r="T95" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U95" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V95" s="18" t="n">
         <v>2</v>
       </c>
@@ -8450,7 +9254,11 @@
           <t>North America 100%; Asia 0%</t>
         </is>
       </c>
-      <c r="X95" s="15" t="n"/>
+      <c r="X95" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -8532,13 +9340,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T96" s="15" t="n"/>
-      <c r="U96" s="17" t="n"/>
+      <c r="T96" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U96" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="17" t="n"/>
-      <c r="X96" s="15" t="n"/>
+      <c r="W96" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X96" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="13" t="n">
@@ -8657,7 +9481,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E98" s="17" t="n"/>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F98" s="18" t="n">
         <v>3800670000.000001</v>
       </c>
@@ -8712,13 +9540,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T98" s="15" t="n"/>
-      <c r="U98" s="17" t="n"/>
+      <c r="T98" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U98" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V98" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="17" t="n"/>
-      <c r="X98" s="15" t="n"/>
+      <c r="W98" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X98" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="13" t="n">
@@ -8807,7 +9651,11 @@
       <c r="V99" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W99" s="17" t="n"/>
+      <c r="W99" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X99" s="15" t="inlineStr">
         <is>
           <t>Core Banking -1%</t>
@@ -8886,8 +9734,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T100" s="15" t="n"/>
-      <c r="U100" s="17" t="n"/>
+      <c r="T100" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U100" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V100" s="18" t="n">
         <v>2</v>
       </c>
@@ -8896,7 +9752,11 @@
           <t>US 58%; Non Us 42%</t>
         </is>
       </c>
-      <c r="X100" s="15" t="n"/>
+      <c r="X100" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="13" t="n">
@@ -8979,7 +9839,11 @@
       <c r="V101" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W101" s="17" t="n"/>
+      <c r="W101" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X101" s="15" t="inlineStr">
         <is>
           <t>Pandora And Off Plat -0%</t>
@@ -9069,7 +9933,11 @@
       <c r="V102" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="17" t="n"/>
+      <c r="W102" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -9152,13 +10020,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T103" s="15" t="n"/>
-      <c r="U103" s="17" t="n"/>
+      <c r="T103" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U103" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W103" s="17" t="n"/>
-      <c r="X103" s="15" t="n"/>
+      <c r="W103" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X103" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="13" t="n">
@@ -9238,13 +10122,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T104" s="15" t="n"/>
-      <c r="U104" s="17" t="n"/>
+      <c r="T104" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U104" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="17" t="n"/>
-      <c r="X104" s="15" t="n"/>
+      <c r="W104" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X104" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="13" t="n">
@@ -9338,7 +10238,11 @@
           <t>North America 89%; Asia Pacific 9%; Europe 3%</t>
         </is>
       </c>
-      <c r="X105" s="15" t="n"/>
+      <c r="X105" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="13" t="n">
@@ -9425,7 +10329,11 @@
       <c r="V106" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W106" s="17" t="n"/>
+      <c r="W106" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X106" s="15" t="inlineStr">
         <is>
           <t>Enact +2%</t>
@@ -9513,7 +10421,11 @@
       <c r="V107" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W107" s="17" t="n"/>
+      <c r="W107" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X107" s="15" t="inlineStr">
         <is>
           <t>Institutional Produc +22%</t>
@@ -9539,7 +10451,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E108" s="17" t="n"/>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F108" s="18" t="n">
         <v>1620210438</v>
       </c>
@@ -9684,8 +10600,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T109" s="15" t="n"/>
-      <c r="U109" s="17" t="n"/>
+      <c r="T109" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U109" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V109" s="18" t="n">
         <v>2</v>
       </c>
@@ -9694,7 +10618,11 @@
           <t>US 100%; Non Us 0%</t>
         </is>
       </c>
-      <c r="X109" s="15" t="n"/>
+      <c r="X109" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="13" t="n">
@@ -9869,7 +10797,11 @@
       <c r="V111" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W111" s="17" t="n"/>
+      <c r="W111" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X111" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments  +1%</t>
@@ -9950,8 +10882,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T112" s="15" t="n"/>
-      <c r="U112" s="17" t="n"/>
+      <c r="T112" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U112" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V112" s="18" t="n">
         <v>1</v>
       </c>
@@ -9960,7 +10900,11 @@
           <t>Non Us 100%</t>
         </is>
       </c>
-      <c r="X112" s="15" t="n"/>
+      <c r="X112" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="13" t="n">
@@ -10034,8 +10978,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T113" s="15" t="n"/>
-      <c r="U113" s="17" t="n"/>
+      <c r="T113" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U113" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V113" s="18" t="n">
         <v>2</v>
       </c>
@@ -10044,7 +10996,11 @@
           <t>US 99%; Non Us 1%</t>
         </is>
       </c>
-      <c r="X113" s="15" t="n"/>
+      <c r="X113" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="13" t="n">
@@ -10065,7 +11021,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E114" s="17" t="n"/>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F114" s="18" t="n">
         <v>12285029</v>
       </c>
@@ -10116,8 +11076,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T114" s="15" t="n"/>
-      <c r="U114" s="17" t="n"/>
+      <c r="T114" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U114" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V114" s="18" t="n">
         <v>5</v>
       </c>
@@ -10126,7 +11094,11 @@
           <t>US 96%; SV 3%; AR 0%</t>
         </is>
       </c>
-      <c r="X114" s="15" t="n"/>
+      <c r="X114" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n">
@@ -10208,13 +11180,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T115" s="15" t="n"/>
-      <c r="U115" s="17" t="n"/>
+      <c r="T115" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U115" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V115" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W115" s="17" t="n"/>
-      <c r="X115" s="15" t="n"/>
+      <c r="W115" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X115" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="13" t="n">
@@ -10303,7 +11291,11 @@
       <c r="V116" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="17" t="n"/>
+      <c r="W116" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X116" s="15" t="inlineStr">
         <is>
           <t>Real Estate One +10%</t>
@@ -10386,13 +11378,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T117" s="15" t="n"/>
-      <c r="U117" s="17" t="n"/>
+      <c r="T117" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U117" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V117" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W117" s="17" t="n"/>
-      <c r="X117" s="15" t="n"/>
+      <c r="W117" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X117" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="13" t="n">
@@ -10470,13 +11478,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T118" s="15" t="n"/>
-      <c r="U118" s="17" t="n"/>
+      <c r="T118" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U118" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V118" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W118" s="17" t="n"/>
-      <c r="X118" s="15" t="n"/>
+      <c r="W118" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X118" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="13" t="n">
@@ -10561,7 +11585,11 @@
       <c r="V119" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W119" s="17" t="n"/>
+      <c r="W119" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X119" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments +15%</t>
@@ -10740,13 +11768,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T121" s="15" t="n"/>
-      <c r="U121" s="17" t="n"/>
+      <c r="T121" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U121" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V121" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W121" s="17" t="n"/>
-      <c r="X121" s="15" t="n"/>
+      <c r="W121" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X121" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="13" t="n">
@@ -10826,13 +11870,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T122" s="15" t="n"/>
-      <c r="U122" s="17" t="n"/>
+      <c r="T122" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U122" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W122" s="17" t="n"/>
-      <c r="X122" s="15" t="n"/>
+      <c r="W122" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X122" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="13" t="n">
@@ -10908,13 +11968,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T123" s="15" t="n"/>
-      <c r="U123" s="17" t="n"/>
+      <c r="T123" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U123" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V123" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W123" s="17" t="n"/>
-      <c r="X123" s="15" t="n"/>
+      <c r="W123" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X123" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="13" t="n">
@@ -10992,13 +12068,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T124" s="15" t="n"/>
-      <c r="U124" s="17" t="n"/>
+      <c r="T124" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U124" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V124" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W124" s="17" t="n"/>
-      <c r="X124" s="15" t="n"/>
+      <c r="W124" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X124" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="13" t="n">
@@ -11074,8 +12166,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T125" s="15" t="n"/>
-      <c r="U125" s="17" t="n"/>
+      <c r="T125" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U125" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V125" s="18" t="n">
         <v>4</v>
       </c>
@@ -11084,7 +12184,11 @@
           <t>US 71%; GB 12%; Other International 11%</t>
         </is>
       </c>
-      <c r="X125" s="15" t="n"/>
+      <c r="X125" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="13" t="n">
@@ -11258,13 +12362,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T127" s="15" t="n"/>
-      <c r="U127" s="17" t="n"/>
+      <c r="T127" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U127" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V127" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W127" s="17" t="n"/>
-      <c r="X127" s="15" t="n"/>
+      <c r="W127" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X127" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="13" t="n">
@@ -11347,7 +12467,11 @@
       <c r="V128" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W128" s="17" t="n"/>
+      <c r="W128" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X128" s="15" t="inlineStr">
         <is>
           <t>Optavia -36%</t>
@@ -11557,7 +12681,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E131" s="17" t="n"/>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F131" s="18" t="n">
         <v>2302047000</v>
       </c>
@@ -11615,7 +12743,11 @@
       <c r="V131" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W131" s="17" t="n"/>
+      <c r="W131" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X131" s="15" t="inlineStr">
         <is>
           <t>Array +58%</t>
@@ -11694,13 +12826,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T132" s="15" t="n"/>
-      <c r="U132" s="17" t="n"/>
+      <c r="T132" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U132" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V132" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W132" s="17" t="n"/>
-      <c r="X132" s="15" t="n"/>
+      <c r="W132" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X132" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="13" t="n">
@@ -11776,13 +12924,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T133" s="15" t="n"/>
-      <c r="U133" s="17" t="n"/>
+      <c r="T133" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U133" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V133" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W133" s="17" t="n"/>
-      <c r="X133" s="15" t="n"/>
+      <c r="W133" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X133" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="16" customHeight="1">
       <c r="A134" s="13" t="n">
@@ -11858,13 +13022,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T134" s="15" t="n"/>
-      <c r="U134" s="17" t="n"/>
+      <c r="T134" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U134" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V134" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W134" s="17" t="n"/>
-      <c r="X134" s="15" t="n"/>
+      <c r="W134" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X134" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="13" t="n">
@@ -11953,7 +13133,11 @@
       <c r="V135" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W135" s="17" t="n"/>
+      <c r="W135" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X135" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -12139,7 +13323,11 @@
       <c r="V137" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W137" s="17" t="n"/>
+      <c r="W137" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X137" s="15" t="inlineStr">
         <is>
           <t>Reportable +4%</t>
@@ -12226,13 +13414,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T138" s="15" t="n"/>
-      <c r="U138" s="17" t="n"/>
+      <c r="T138" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U138" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V138" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W138" s="17" t="n"/>
-      <c r="X138" s="15" t="n"/>
+      <c r="W138" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X138" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="13" t="n">
@@ -12308,13 +13512,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T139" s="15" t="n"/>
-      <c r="U139" s="17" t="n"/>
+      <c r="T139" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U139" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V139" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W139" s="17" t="n"/>
-      <c r="X139" s="15" t="n"/>
+      <c r="W139" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X139" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="13" t="n">
@@ -12586,13 +13806,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T142" s="15" t="n"/>
-      <c r="U142" s="17" t="n"/>
+      <c r="T142" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U142" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V142" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W142" s="17" t="n"/>
-      <c r="X142" s="15" t="n"/>
+      <c r="W142" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X142" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="13" t="n">
@@ -12764,13 +14000,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T144" s="15" t="n"/>
-      <c r="U144" s="17" t="n"/>
+      <c r="T144" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U144" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V144" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W144" s="17" t="n"/>
-      <c r="X144" s="15" t="n"/>
+      <c r="W144" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X144" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="13" t="n">
@@ -12848,13 +14100,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T145" s="15" t="n"/>
-      <c r="U145" s="17" t="n"/>
+      <c r="T145" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U145" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V145" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W145" s="17" t="n"/>
-      <c r="X145" s="15" t="n"/>
+      <c r="W145" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X145" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="13" t="n">
@@ -12947,7 +14215,11 @@
       <c r="V146" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W146" s="17" t="n"/>
+      <c r="W146" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X146" s="15" t="inlineStr">
         <is>
           <t>Reportable -100%</t>
@@ -13043,7 +14315,11 @@
       <c r="V147" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W147" s="17" t="n"/>
+      <c r="W147" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X147" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +8%</t>
@@ -13126,13 +14402,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T148" s="15" t="n"/>
-      <c r="U148" s="17" t="n"/>
+      <c r="T148" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U148" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V148" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W148" s="17" t="n"/>
-      <c r="X148" s="15" t="n"/>
+      <c r="W148" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X148" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="16" customHeight="1">
       <c r="A149" s="13" t="n">
@@ -13302,13 +14594,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T150" s="15" t="n"/>
-      <c r="U150" s="17" t="n"/>
+      <c r="T150" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U150" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V150" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W150" s="17" t="n"/>
-      <c r="X150" s="15" t="n"/>
+      <c r="W150" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X150" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="13" t="n">
@@ -13486,8 +14794,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T152" s="15" t="n"/>
-      <c r="U152" s="17" t="n"/>
+      <c r="T152" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U152" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V152" s="18" t="n">
         <v>4</v>
       </c>
@@ -13496,7 +14812,11 @@
           <t>US 65%; EMEA 28%; Asia Pacific 6%</t>
         </is>
       </c>
-      <c r="X152" s="15" t="n"/>
+      <c r="X152" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="13" t="n">
@@ -13574,13 +14894,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T153" s="15" t="n"/>
-      <c r="U153" s="17" t="n"/>
+      <c r="T153" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U153" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V153" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W153" s="17" t="n"/>
-      <c r="X153" s="15" t="n"/>
+      <c r="W153" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X153" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="13" t="n">
@@ -13652,13 +14988,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T154" s="15" t="n"/>
-      <c r="U154" s="17" t="n"/>
+      <c r="T154" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U154" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V154" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W154" s="17" t="n"/>
-      <c r="X154" s="15" t="n"/>
+      <c r="W154" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X154" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="13" t="n">
@@ -13736,13 +15088,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T155" s="15" t="n"/>
-      <c r="U155" s="17" t="n"/>
+      <c r="T155" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U155" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V155" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W155" s="17" t="n"/>
-      <c r="X155" s="15" t="n"/>
+      <c r="W155" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X155" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="13" t="n">
@@ -13827,7 +15195,11 @@
       <c r="V156" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W156" s="17" t="n"/>
+      <c r="W156" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X156" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -13910,13 +15282,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T157" s="15" t="n"/>
-      <c r="U157" s="17" t="n"/>
+      <c r="T157" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U157" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V157" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W157" s="17" t="n"/>
-      <c r="X157" s="15" t="n"/>
+      <c r="W157" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X157" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="13" t="n">
@@ -13992,8 +15380,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T158" s="15" t="n"/>
-      <c r="U158" s="17" t="n"/>
+      <c r="T158" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U158" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V158" s="18" t="n">
         <v>9</v>
       </c>
@@ -14002,7 +15398,11 @@
           <t>Europe 26%; Americas 21%; US 20%</t>
         </is>
       </c>
-      <c r="X158" s="15" t="n"/>
+      <c r="X158" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="13" t="n">
@@ -14080,13 +15480,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T159" s="15" t="n"/>
-      <c r="U159" s="17" t="n"/>
+      <c r="T159" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U159" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V159" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W159" s="17" t="n"/>
-      <c r="X159" s="15" t="n"/>
+      <c r="W159" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X159" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="13" t="n">
@@ -14173,7 +15589,11 @@
       <c r="V160" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W160" s="17" t="n"/>
+      <c r="W160" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X160" s="15" t="inlineStr">
         <is>
           <t>Hawaii Energy Connec +30%</t>
@@ -14252,13 +15672,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T161" s="15" t="n"/>
-      <c r="U161" s="17" t="n"/>
+      <c r="T161" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U161" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V161" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W161" s="17" t="n"/>
-      <c r="X161" s="15" t="n"/>
+      <c r="W161" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X161" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="13" t="n">
@@ -14336,13 +15772,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T162" s="15" t="n"/>
-      <c r="U162" s="17" t="n"/>
+      <c r="T162" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U162" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V162" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W162" s="17" t="n"/>
-      <c r="X162" s="15" t="n"/>
+      <c r="W162" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X162" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="13" t="n">
@@ -14420,13 +15872,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T163" s="15" t="n"/>
-      <c r="U163" s="17" t="n"/>
+      <c r="T163" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U163" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V163" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W163" s="17" t="n"/>
-      <c r="X163" s="15" t="n"/>
+      <c r="W163" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X163" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="13" t="n">
@@ -14506,13 +15974,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T164" s="15" t="n"/>
-      <c r="U164" s="17" t="n"/>
+      <c r="T164" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U164" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V164" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W164" s="17" t="n"/>
-      <c r="X164" s="15" t="n"/>
+      <c r="W164" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X164" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="13" t="n">
@@ -14590,13 +16074,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T165" s="15" t="n"/>
-      <c r="U165" s="17" t="n"/>
+      <c r="T165" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U165" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V165" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W165" s="17" t="n"/>
-      <c r="X165" s="15" t="n"/>
+      <c r="W165" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X165" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="13" t="n">
@@ -14676,13 +16176,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T166" s="15" t="n"/>
-      <c r="U166" s="17" t="n"/>
+      <c r="T166" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U166" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V166" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W166" s="17" t="n"/>
-      <c r="X166" s="15" t="n"/>
+      <c r="W166" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X166" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="13" t="n">
@@ -14764,13 +16280,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T167" s="15" t="n"/>
-      <c r="U167" s="17" t="n"/>
+      <c r="T167" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U167" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V167" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W167" s="17" t="n"/>
-      <c r="X167" s="15" t="n"/>
+      <c r="W167" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X167" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="13" t="n">
@@ -14844,8 +16376,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T168" s="15" t="n"/>
-      <c r="U168" s="17" t="n"/>
+      <c r="T168" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U168" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V168" s="18" t="n">
         <v>2</v>
       </c>
@@ -14854,7 +16394,11 @@
           <t>North America 78%; EMEA 22%</t>
         </is>
       </c>
-      <c r="X168" s="15" t="n"/>
+      <c r="X168" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="13" t="n">
@@ -14943,7 +16487,11 @@
       <c r="V169" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W169" s="17" t="n"/>
+      <c r="W169" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X169" s="15" t="inlineStr">
         <is>
           <t>Consumer Banking +9%</t>
@@ -15118,8 +16666,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T171" s="15" t="n"/>
-      <c r="U171" s="17" t="n"/>
+      <c r="T171" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U171" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V171" s="18" t="n">
         <v>2</v>
       </c>
@@ -15128,7 +16684,11 @@
           <t>US 97%; Non Us 3%</t>
         </is>
       </c>
-      <c r="X171" s="15" t="n"/>
+      <c r="X171" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="13" t="n">
@@ -15149,7 +16709,11 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="E172" s="17" t="n"/>
+      <c r="E172" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F172" s="18" t="n">
         <v>40103256</v>
       </c>
@@ -15300,13 +16864,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T173" s="15" t="n"/>
-      <c r="U173" s="17" t="n"/>
+      <c r="T173" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U173" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V173" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W173" s="17" t="n"/>
-      <c r="X173" s="15" t="n"/>
+      <c r="W173" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X173" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="13" t="n">
@@ -15389,7 +16969,11 @@
       <c r="V174" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W174" s="17" t="n"/>
+      <c r="W174" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X174" s="15" t="inlineStr">
         <is>
           <t>Towers +6%</t>
@@ -15470,8 +17054,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T175" s="15" t="n"/>
-      <c r="U175" s="17" t="n"/>
+      <c r="T175" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U175" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V175" s="18" t="n">
         <v>3</v>
       </c>
@@ -15480,7 +17072,11 @@
           <t>US 58%; Europe 32%; Other Than Us And Europe 10%</t>
         </is>
       </c>
-      <c r="X175" s="15" t="n"/>
+      <c r="X175" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="13" t="n">
@@ -15567,7 +17163,11 @@
       <c r="V176" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W176" s="17" t="n"/>
+      <c r="W176" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X176" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +4%</t>
@@ -15650,13 +17250,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T177" s="15" t="n"/>
-      <c r="U177" s="17" t="n"/>
+      <c r="T177" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U177" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V177" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W177" s="17" t="n"/>
-      <c r="X177" s="15" t="n"/>
+      <c r="W177" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X177" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="13" t="n">
@@ -15732,13 +17348,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T178" s="15" t="n"/>
-      <c r="U178" s="17" t="n"/>
+      <c r="T178" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U178" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V178" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W178" s="17" t="n"/>
-      <c r="X178" s="15" t="n"/>
+      <c r="W178" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X178" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="13" t="n">
@@ -15827,8 +17459,16 @@
       <c r="V179" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W179" s="17" t="n"/>
-      <c r="X179" s="15" t="n"/>
+      <c r="W179" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X179" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="13" t="n">
@@ -15906,8 +17546,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T180" s="15" t="n"/>
-      <c r="U180" s="17" t="n"/>
+      <c r="T180" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U180" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V180" s="18" t="n">
         <v>2</v>
       </c>
@@ -15916,7 +17564,11 @@
           <t>Non Us 59%; US 41%</t>
         </is>
       </c>
-      <c r="X180" s="15" t="n"/>
+      <c r="X180" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="13" t="n">
@@ -15994,13 +17646,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T181" s="15" t="n"/>
-      <c r="U181" s="17" t="n"/>
+      <c r="T181" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U181" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V181" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W181" s="17" t="n"/>
-      <c r="X181" s="15" t="n"/>
+      <c r="W181" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X181" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="13" t="n">
@@ -16083,7 +17751,11 @@
       <c r="V182" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W182" s="17" t="n"/>
+      <c r="W182" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X182" s="15" t="inlineStr">
         <is>
           <t>University Group +35%</t>
@@ -16162,8 +17834,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T183" s="15" t="n"/>
-      <c r="U183" s="17" t="n"/>
+      <c r="T183" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U183" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V183" s="18" t="n">
         <v>2</v>
       </c>
@@ -16172,7 +17852,11 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="X183" s="15" t="n"/>
+      <c r="X183" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="13" t="n">
@@ -16263,7 +17947,11 @@
       <c r="V184" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W184" s="17" t="n"/>
+      <c r="W184" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X184" s="15" t="inlineStr">
         <is>
           <t>Reportable +14%</t>
@@ -16359,7 +18047,11 @@
       <c r="V185" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W185" s="17" t="n"/>
+      <c r="W185" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X185" s="15" t="inlineStr">
         <is>
           <t>The +37%</t>
@@ -16442,13 +18134,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T186" s="15" t="n"/>
-      <c r="U186" s="17" t="n"/>
+      <c r="T186" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U186" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V186" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W186" s="17" t="n"/>
-      <c r="X186" s="15" t="n"/>
+      <c r="W186" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X186" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="13" t="n">
@@ -16520,13 +18228,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T187" s="15" t="n"/>
-      <c r="U187" s="17" t="n"/>
+      <c r="T187" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U187" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V187" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W187" s="17" t="n"/>
-      <c r="X187" s="15" t="n"/>
+      <c r="W187" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X187" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="13" t="n">
@@ -16611,7 +18335,11 @@
       <c r="V188" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W188" s="17" t="n"/>
+      <c r="W188" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X188" s="15" t="inlineStr">
         <is>
           <t>Banking +15%</t>
@@ -16694,13 +18422,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T189" s="15" t="n"/>
-      <c r="U189" s="17" t="n"/>
+      <c r="T189" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U189" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V189" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W189" s="17" t="n"/>
-      <c r="X189" s="15" t="n"/>
+      <c r="W189" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X189" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="13" t="n">
@@ -16787,7 +18531,11 @@
       <c r="V190" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W190" s="17" t="n"/>
+      <c r="W190" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X190" s="15" t="inlineStr">
         <is>
           <t>Reportable -77%</t>
@@ -16872,8 +18620,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T191" s="15" t="n"/>
-      <c r="U191" s="17" t="n"/>
+      <c r="T191" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U191" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V191" s="18" t="n">
         <v>4</v>
       </c>
@@ -16882,7 +18638,11 @@
           <t>EMEA 48%; Americas 41%; Asia Pacific 11%</t>
         </is>
       </c>
-      <c r="X191" s="15" t="n"/>
+      <c r="X191" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="13" t="n">
@@ -16960,13 +18720,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T192" s="15" t="n"/>
-      <c r="U192" s="17" t="n"/>
+      <c r="T192" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U192" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V192" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W192" s="17" t="n"/>
-      <c r="X192" s="15" t="n"/>
+      <c r="W192" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X192" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="13" t="n">
@@ -17046,13 +18822,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T193" s="15" t="n"/>
-      <c r="U193" s="17" t="n"/>
+      <c r="T193" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U193" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V193" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W193" s="17" t="n"/>
-      <c r="X193" s="15" t="n"/>
+      <c r="W193" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X193" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="13" t="n">
@@ -17216,13 +19008,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T195" s="15" t="n"/>
-      <c r="U195" s="17" t="n"/>
+      <c r="T195" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U195" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V195" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W195" s="17" t="n"/>
-      <c r="X195" s="15" t="n"/>
+      <c r="W195" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X195" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="13" t="n">
@@ -17243,7 +19051,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E196" s="17" t="n"/>
+      <c r="E196" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F196" s="18" t="n">
         <v>8050602560</v>
       </c>
@@ -17301,7 +19113,11 @@
       <c r="V196" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W196" s="17" t="n"/>
+      <c r="W196" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X196" s="15" t="inlineStr">
         <is>
           <t>PC Business Insuranc +10%</t>
@@ -17386,13 +19202,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T197" s="15" t="n"/>
-      <c r="U197" s="17" t="n"/>
+      <c r="T197" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U197" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V197" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W197" s="17" t="n"/>
-      <c r="X197" s="15" t="n"/>
+      <c r="W197" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X197" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="13" t="n">
@@ -17475,7 +19307,11 @@
       <c r="V198" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W198" s="17" t="n"/>
+      <c r="W198" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X198" s="15" t="inlineStr">
         <is>
           <t>Operating +23%</t>
@@ -17567,7 +19403,11 @@
       <c r="V199" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W199" s="17" t="n"/>
+      <c r="W199" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X199" s="15" t="inlineStr">
         <is>
           <t>Mid Con Barnett Shal +180%</t>
@@ -17746,13 +19586,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T201" s="15" t="n"/>
-      <c r="U201" s="17" t="n"/>
+      <c r="T201" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U201" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V201" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W201" s="17" t="n"/>
-      <c r="X201" s="15" t="n"/>
+      <c r="W201" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X201" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="13" t="n">
@@ -18018,13 +19874,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T204" s="15" t="n"/>
-      <c r="U204" s="17" t="n"/>
+      <c r="T204" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U204" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V204" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W204" s="17" t="n"/>
-      <c r="X204" s="15" t="n"/>
+      <c r="W204" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X204" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="13" t="n">
@@ -18286,13 +20158,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T207" s="15" t="n"/>
-      <c r="U207" s="17" t="n"/>
+      <c r="T207" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U207" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V207" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W207" s="17" t="n"/>
-      <c r="X207" s="15" t="n"/>
+      <c r="W207" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X207" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="13" t="n">
@@ -18479,7 +20367,11 @@
       <c r="V209" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W209" s="17" t="n"/>
+      <c r="W209" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X209" s="15" t="inlineStr">
         <is>
           <t>Reportable -88%</t>
@@ -18575,7 +20467,11 @@
       <c r="V210" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W210" s="17" t="n"/>
+      <c r="W210" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X210" s="15" t="inlineStr">
         <is>
           <t>Operating +370%</t>
@@ -18654,8 +20550,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T211" s="15" t="n"/>
-      <c r="U211" s="17" t="n"/>
+      <c r="T211" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U211" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V211" s="18" t="n">
         <v>2</v>
       </c>
@@ -18664,7 +20568,11 @@
           <t>US 96%; Non Us 4%</t>
         </is>
       </c>
-      <c r="X211" s="15" t="n"/>
+      <c r="X211" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="13" t="n">
@@ -18738,13 +20646,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T212" s="15" t="n"/>
-      <c r="U212" s="17" t="n"/>
+      <c r="T212" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U212" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V212" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W212" s="17" t="n"/>
-      <c r="X212" s="15" t="n"/>
+      <c r="W212" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X212" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="13" t="n">
@@ -18833,7 +20757,11 @@
       <c r="V213" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W213" s="17" t="n"/>
+      <c r="W213" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X213" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +15%</t>
@@ -18859,7 +20787,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E214" s="17" t="n"/>
+      <c r="E214" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F214" s="18" t="n">
         <v>2411290575.93</v>
       </c>
@@ -18912,13 +20844,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T214" s="15" t="n"/>
-      <c r="U214" s="17" t="n"/>
+      <c r="T214" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U214" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V214" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W214" s="17" t="n"/>
-      <c r="X214" s="15" t="n"/>
+      <c r="W214" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X214" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="13" t="n">
@@ -19001,7 +20949,11 @@
       <c r="V215" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W215" s="17" t="n"/>
+      <c r="W215" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X215" s="15" t="inlineStr">
         <is>
           <t>Southeast -3%</t>
@@ -19084,8 +21036,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T216" s="15" t="n"/>
-      <c r="U216" s="17" t="n"/>
+      <c r="T216" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U216" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V216" s="18" t="n">
         <v>3</v>
       </c>
@@ -19094,7 +21054,11 @@
           <t>US 86%; Europe 8%; Rest Of The World Except US And Europe 6%</t>
         </is>
       </c>
-      <c r="X216" s="15" t="n"/>
+      <c r="X216" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="16" customHeight="1">
       <c r="A217" s="13" t="n">
@@ -19266,13 +21230,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T218" s="15" t="n"/>
-      <c r="U218" s="17" t="n"/>
+      <c r="T218" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U218" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V218" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W218" s="17" t="n"/>
-      <c r="X218" s="15" t="n"/>
+      <c r="W218" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X218" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="13" t="n">
@@ -19352,8 +21332,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T219" s="15" t="n"/>
-      <c r="U219" s="17" t="n"/>
+      <c r="T219" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U219" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V219" s="18" t="n">
         <v>1</v>
       </c>
@@ -19362,7 +21350,11 @@
           <t>Non Us 100%</t>
         </is>
       </c>
-      <c r="X219" s="15" t="n"/>
+      <c r="X219" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="13" t="n">
@@ -19532,13 +21524,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T221" s="15" t="n"/>
-      <c r="U221" s="17" t="n"/>
+      <c r="T221" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U221" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V221" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W221" s="17" t="n"/>
-      <c r="X221" s="15" t="n"/>
+      <c r="W221" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X221" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="13" t="n">
@@ -19612,13 +21620,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T222" s="15" t="n"/>
-      <c r="U222" s="17" t="n"/>
+      <c r="T222" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U222" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V222" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W222" s="17" t="n"/>
-      <c r="X222" s="15" t="n"/>
+      <c r="W222" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X222" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="16" customHeight="1">
       <c r="A223" s="13" t="n">
@@ -19703,7 +21727,11 @@
       <c r="V223" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W223" s="17" t="n"/>
+      <c r="W223" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X223" s="15" t="inlineStr">
         <is>
           <t>Reportable +23%</t>
@@ -19793,7 +21821,11 @@
       <c r="V224" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W224" s="17" t="n"/>
+      <c r="W224" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X224" s="15" t="inlineStr">
         <is>
           <t>Mastercraft -8%</t>
@@ -19876,13 +21908,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T225" s="15" t="n"/>
-      <c r="U225" s="17" t="n"/>
+      <c r="T225" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U225" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V225" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W225" s="17" t="n"/>
-      <c r="X225" s="15" t="n"/>
+      <c r="W225" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X225" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="16" customHeight="1">
       <c r="A226" s="13" t="n">
@@ -19956,13 +22004,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T226" s="15" t="n"/>
-      <c r="U226" s="17" t="n"/>
+      <c r="T226" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U226" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V226" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W226" s="17" t="n"/>
-      <c r="X226" s="15" t="n"/>
+      <c r="W226" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X226" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="16" customHeight="1">
       <c r="A227" s="13" t="n">
@@ -20047,7 +22111,11 @@
       <c r="V227" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W227" s="17" t="n"/>
+      <c r="W227" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X227" s="15" t="inlineStr">
         <is>
           <t>Timber +327%</t>
@@ -20224,8 +22292,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T229" s="15" t="n"/>
-      <c r="U229" s="17" t="n"/>
+      <c r="T229" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U229" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V229" s="18" t="n">
         <v>2</v>
       </c>
@@ -20234,7 +22310,11 @@
           <t>CA 54%; US 46%</t>
         </is>
       </c>
-      <c r="X229" s="15" t="n"/>
+      <c r="X229" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="16" customHeight="1">
       <c r="A230" s="13" t="n">
@@ -20310,13 +22390,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T230" s="15" t="n"/>
-      <c r="U230" s="17" t="n"/>
+      <c r="T230" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U230" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V230" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W230" s="17" t="n"/>
-      <c r="X230" s="15" t="n"/>
+      <c r="W230" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X230" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="16" customHeight="1">
       <c r="A231" s="13" t="n">
@@ -20484,13 +22580,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T232" s="15" t="n"/>
-      <c r="U232" s="17" t="n"/>
+      <c r="T232" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U232" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V232" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W232" s="17" t="n"/>
-      <c r="X232" s="15" t="n"/>
+      <c r="W232" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X232" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="16" customHeight="1">
       <c r="A233" s="13" t="n">
@@ -20568,8 +22680,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T233" s="15" t="n"/>
-      <c r="U233" s="17" t="n"/>
+      <c r="T233" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U233" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V233" s="18" t="n">
         <v>4</v>
       </c>
@@ -20578,7 +22698,11 @@
           <t>North America 42%; US 41%; Rest Of World 12%</t>
         </is>
       </c>
-      <c r="X233" s="15" t="n"/>
+      <c r="X233" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="16" customHeight="1">
       <c r="A234" s="13" t="n">
@@ -20763,7 +22887,11 @@
       <c r="V235" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W235" s="17" t="n"/>
+      <c r="W235" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X235" s="15" t="inlineStr">
         <is>
           <t>Single Reportable -99%</t>
@@ -20940,13 +23068,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T237" s="15" t="n"/>
-      <c r="U237" s="17" t="n"/>
+      <c r="T237" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U237" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V237" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W237" s="17" t="n"/>
-      <c r="X237" s="15" t="n"/>
+      <c r="W237" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X237" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="16" customHeight="1">
       <c r="A238" s="13" t="n">
@@ -21024,8 +23168,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T238" s="15" t="n"/>
-      <c r="U238" s="17" t="n"/>
+      <c r="T238" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U238" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V238" s="18" t="n">
         <v>4</v>
       </c>
@@ -21034,7 +23186,11 @@
           <t>US 82%; Africa 12%; Europe 3%</t>
         </is>
       </c>
-      <c r="X238" s="15" t="n"/>
+      <c r="X238" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="16" customHeight="1">
       <c r="A239" s="13" t="n">
@@ -21200,8 +23356,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T240" s="15" t="n"/>
-      <c r="U240" s="17" t="n"/>
+      <c r="T240" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U240" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V240" s="18" t="n">
         <v>5</v>
       </c>
@@ -21210,7 +23374,11 @@
           <t>US 61%; Non Us 20%; Europe 13%</t>
         </is>
       </c>
-      <c r="X240" s="15" t="n"/>
+      <c r="X240" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="16" customHeight="1">
       <c r="A241" s="13" t="n">
@@ -21481,7 +23649,11 @@
       <c r="V243" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W243" s="17" t="n"/>
+      <c r="W243" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X243" s="15" t="inlineStr">
         <is>
           <t>Retirement And Incom +23%</t>
@@ -21562,13 +23734,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T244" s="15" t="n"/>
-      <c r="U244" s="17" t="n"/>
+      <c r="T244" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U244" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V244" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W244" s="17" t="n"/>
-      <c r="X244" s="15" t="n"/>
+      <c r="W244" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X244" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="16" customHeight="1">
       <c r="A245" s="13" t="n">
@@ -21653,7 +23841,11 @@
       <c r="V245" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W245" s="17" t="n"/>
+      <c r="W245" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X245" s="15" t="inlineStr">
         <is>
           <t>Reportable +25%</t>
@@ -21747,8 +23939,16 @@
       <c r="V246" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W246" s="17" t="n"/>
-      <c r="X246" s="15" t="n"/>
+      <c r="W246" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X246" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="16" customHeight="1">
       <c r="A247" s="13" t="n">
@@ -21824,8 +24024,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T247" s="15" t="n"/>
-      <c r="U247" s="17" t="n"/>
+      <c r="T247" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U247" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V247" s="18" t="n">
         <v>5</v>
       </c>
@@ -21834,7 +24042,11 @@
           <t>US 92%; Non Us 6%; CA 1%</t>
         </is>
       </c>
-      <c r="X247" s="15" t="n"/>
+      <c r="X247" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="16" customHeight="1">
       <c r="A248" s="13" t="n">
@@ -22009,7 +24221,11 @@
       <c r="V249" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W249" s="17" t="n"/>
+      <c r="W249" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X249" s="15" t="inlineStr">
         <is>
           <t>Restaurant Food Sale +224%</t>
@@ -22092,13 +24308,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T250" s="15" t="n"/>
-      <c r="U250" s="17" t="n"/>
+      <c r="T250" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U250" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V250" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W250" s="17" t="n"/>
-      <c r="X250" s="15" t="n"/>
+      <c r="W250" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X250" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="16" customHeight="1">
       <c r="A251" s="13" t="n">
@@ -22183,7 +24415,11 @@
       <c r="V251" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W251" s="17" t="n"/>
+      <c r="W251" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X251" s="15" t="inlineStr">
         <is>
           <t>Reportable +17%</t>
@@ -22262,13 +24498,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T252" s="15" t="n"/>
-      <c r="U252" s="17" t="n"/>
+      <c r="T252" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U252" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V252" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W252" s="17" t="n"/>
-      <c r="X252" s="15" t="n"/>
+      <c r="W252" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X252" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="16" customHeight="1">
       <c r="A253" s="13" t="n">
@@ -22357,7 +24609,11 @@
       <c r="V253" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W253" s="17" t="n"/>
+      <c r="W253" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X253" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +16%</t>
@@ -22440,13 +24696,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T254" s="15" t="n"/>
-      <c r="U254" s="17" t="n"/>
+      <c r="T254" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U254" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V254" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W254" s="17" t="n"/>
-      <c r="X254" s="15" t="n"/>
+      <c r="W254" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X254" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="16" customHeight="1">
       <c r="A255" s="13" t="n">
@@ -22524,13 +24796,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T255" s="15" t="n"/>
-      <c r="U255" s="17" t="n"/>
+      <c r="T255" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U255" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V255" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W255" s="17" t="n"/>
-      <c r="X255" s="15" t="n"/>
+      <c r="W255" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X255" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="16" customHeight="1">
       <c r="A256" s="13" t="n">
@@ -22619,7 +24907,11 @@
       <c r="V256" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W256" s="17" t="n"/>
+      <c r="W256" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X256" s="15" t="inlineStr">
         <is>
           <t>Storage Solutions +8%</t>
@@ -22704,13 +24996,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T257" s="15" t="n"/>
-      <c r="U257" s="17" t="n"/>
+      <c r="T257" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U257" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V257" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W257" s="17" t="n"/>
-      <c r="X257" s="15" t="n"/>
+      <c r="W257" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X257" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="16" customHeight="1">
       <c r="A258" s="13" t="n">
@@ -22784,13 +25092,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T258" s="15" t="n"/>
-      <c r="U258" s="17" t="n"/>
+      <c r="T258" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U258" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V258" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W258" s="17" t="n"/>
-      <c r="X258" s="15" t="n"/>
+      <c r="W258" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X258" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="16" customHeight="1">
       <c r="A259" s="13" t="n">
@@ -22868,13 +25192,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T259" s="15" t="n"/>
-      <c r="U259" s="17" t="n"/>
+      <c r="T259" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U259" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V259" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W259" s="17" t="n"/>
-      <c r="X259" s="15" t="n"/>
+      <c r="W259" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X259" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="13" t="n">
@@ -22948,8 +25288,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T260" s="15" t="n"/>
-      <c r="U260" s="17" t="n"/>
+      <c r="T260" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U260" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V260" s="18" t="n">
         <v>9</v>
       </c>
@@ -22958,7 +25306,11 @@
           <t>Asia Pacific 26%; Europe 22%; CN 19%</t>
         </is>
       </c>
-      <c r="X260" s="15" t="n"/>
+      <c r="X260" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="16" customHeight="1">
       <c r="A261" s="13" t="n">
@@ -23130,13 +25482,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T262" s="15" t="n"/>
-      <c r="U262" s="17" t="n"/>
+      <c r="T262" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U262" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V262" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W262" s="17" t="n"/>
-      <c r="X262" s="15" t="n"/>
+      <c r="W262" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X262" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="16" customHeight="1">
       <c r="A263" s="13" t="n">
@@ -23210,8 +25578,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T263" s="15" t="n"/>
-      <c r="U263" s="17" t="n"/>
+      <c r="T263" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U263" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V263" s="18" t="n">
         <v>2</v>
       </c>
@@ -23220,7 +25596,11 @@
           <t>US 99%; Non Us 1%</t>
         </is>
       </c>
-      <c r="X263" s="15" t="n"/>
+      <c r="X263" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="16" customHeight="1">
       <c r="A264" s="13" t="n">
@@ -23292,13 +25672,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T264" s="15" t="n"/>
-      <c r="U264" s="17" t="n"/>
+      <c r="T264" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U264" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V264" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W264" s="17" t="n"/>
-      <c r="X264" s="15" t="n"/>
+      <c r="W264" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X264" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="16" customHeight="1">
       <c r="A265" s="13" t="n">
@@ -23468,13 +25864,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T266" s="15" t="n"/>
-      <c r="U266" s="17" t="n"/>
+      <c r="T266" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U266" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V266" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W266" s="17" t="n"/>
-      <c r="X266" s="15" t="n"/>
+      <c r="W266" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X266" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="16" customHeight="1">
       <c r="A267" s="13" t="n">
@@ -23552,13 +25964,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T267" s="15" t="n"/>
-      <c r="U267" s="17" t="n"/>
+      <c r="T267" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U267" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V267" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W267" s="17" t="n"/>
-      <c r="X267" s="15" t="n"/>
+      <c r="W267" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X267" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="16" customHeight="1">
       <c r="A268" s="13" t="n">
@@ -23641,7 +26069,11 @@
       <c r="V268" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W268" s="17" t="n"/>
+      <c r="W268" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X268" s="15" t="inlineStr">
         <is>
           <t>Accessories +2%</t>
@@ -23765,7 +26197,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E270" s="17" t="n"/>
+      <c r="E270" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F270" s="18" t="n">
         <v>190471602.2</v>
       </c>
@@ -23820,13 +26256,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T270" s="15" t="n"/>
-      <c r="U270" s="17" t="n"/>
+      <c r="T270" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U270" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V270" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W270" s="17" t="n"/>
-      <c r="X270" s="15" t="n"/>
+      <c r="W270" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X270" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="16" customHeight="1">
       <c r="A271" s="13" t="n">
@@ -23847,7 +26299,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E271" s="17" t="n"/>
+      <c r="E271" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F271" s="18" t="n">
         <v>492385408</v>
       </c>
@@ -23898,13 +26354,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T271" s="15" t="n"/>
-      <c r="U271" s="17" t="n"/>
+      <c r="T271" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U271" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V271" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W271" s="17" t="n"/>
-      <c r="X271" s="15" t="n"/>
+      <c r="W271" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X271" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="16" customHeight="1">
       <c r="A272" s="13" t="n">
@@ -23989,7 +26461,11 @@
       <c r="V272" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W272" s="17" t="n"/>
+      <c r="W272" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X272" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +24%</t>
@@ -24077,7 +26553,11 @@
       <c r="V273" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W273" s="17" t="n"/>
+      <c r="W273" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X273" s="15" t="inlineStr">
         <is>
           <t>Good Times +2%</t>
@@ -24160,13 +26640,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T274" s="15" t="n"/>
-      <c r="U274" s="17" t="n"/>
+      <c r="T274" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U274" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V274" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W274" s="17" t="n"/>
-      <c r="X274" s="15" t="n"/>
+      <c r="W274" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X274" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="16" customHeight="1">
       <c r="A275" s="13" t="n">
@@ -24249,7 +26745,11 @@
       <c r="V275" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W275" s="17" t="n"/>
+      <c r="W275" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X275" s="15" t="inlineStr">
         <is>
           <t>Canadian Factory Bui +18%</t>
@@ -24334,13 +26834,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T276" s="15" t="n"/>
-      <c r="U276" s="17" t="n"/>
+      <c r="T276" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U276" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V276" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W276" s="17" t="n"/>
-      <c r="X276" s="15" t="n"/>
+      <c r="W276" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X276" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="16" customHeight="1">
       <c r="A277" s="13" t="n">
@@ -24361,7 +26877,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E277" s="17" t="n"/>
+      <c r="E277" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F277" s="18" t="n">
         <v>23538974</v>
       </c>
@@ -24410,13 +26930,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T277" s="15" t="n"/>
-      <c r="U277" s="17" t="n"/>
+      <c r="T277" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U277" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V277" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W277" s="17" t="n"/>
-      <c r="X277" s="15" t="n"/>
+      <c r="W277" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X277" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="16" customHeight="1">
       <c r="A278" s="13" t="n">
@@ -24499,7 +27035,11 @@
       <c r="V278" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W278" s="17" t="n"/>
+      <c r="W278" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X278" s="15" t="inlineStr">
         <is>
           <t>Specialty Property C +10%</t>
@@ -24593,7 +27133,11 @@
       <c r="V279" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W279" s="17" t="n"/>
+      <c r="W279" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X279" s="15" t="inlineStr">
         <is>
           <t>Banking Operations -74%</t>
@@ -24685,7 +27229,11 @@
       <c r="V280" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W280" s="17" t="n"/>
+      <c r="W280" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X280" s="15" t="inlineStr">
         <is>
           <t>Insurance Services +47%</t>
@@ -24768,8 +27316,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T281" s="15" t="n"/>
-      <c r="U281" s="17" t="n"/>
+      <c r="T281" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U281" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V281" s="18" t="n">
         <v>6</v>
       </c>
@@ -24778,7 +27334,11 @@
           <t>Americas 28%; US 26%; EMEA 26%</t>
         </is>
       </c>
-      <c r="X281" s="15" t="n"/>
+      <c r="X281" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="16" customHeight="1">
       <c r="A282" s="13" t="n">
@@ -24965,7 +27525,11 @@
       <c r="V283" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W283" s="17" t="n"/>
+      <c r="W283" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X283" s="15" t="inlineStr">
         <is>
           <t>Medicare +62%</t>
@@ -25155,8 +27719,16 @@
       <c r="V285" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W285" s="17" t="n"/>
-      <c r="X285" s="15" t="n"/>
+      <c r="W285" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X285" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="16" customHeight="1">
       <c r="A286" s="13" t="n">
@@ -25234,13 +27806,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T286" s="15" t="n"/>
-      <c r="U286" s="17" t="n"/>
+      <c r="T286" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U286" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V286" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W286" s="17" t="n"/>
-      <c r="X286" s="15" t="n"/>
+      <c r="W286" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X286" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="13" t="n">
@@ -25325,7 +27913,11 @@
       <c r="V287" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W287" s="17" t="n"/>
+      <c r="W287" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X287" s="15" t="inlineStr">
         <is>
           <t>Environmental Servic +8%</t>
@@ -25410,13 +28002,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T288" s="15" t="n"/>
-      <c r="U288" s="17" t="n"/>
+      <c r="T288" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U288" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V288" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W288" s="17" t="n"/>
-      <c r="X288" s="15" t="n"/>
+      <c r="W288" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X288" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="16" customHeight="1">
       <c r="A289" s="13" t="n">
@@ -25501,7 +28109,11 @@
       <c r="V289" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W289" s="17" t="n"/>
+      <c r="W289" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X289" s="15" t="inlineStr">
         <is>
           <t>Protection Services -74%</t>
@@ -25672,8 +28284,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T291" s="15" t="n"/>
-      <c r="U291" s="17" t="n"/>
+      <c r="T291" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U291" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V291" s="18" t="n">
         <v>8</v>
       </c>
@@ -25682,7 +28302,11 @@
           <t>CN 27%; JP 19%; Europe 15%</t>
         </is>
       </c>
-      <c r="X291" s="15" t="n"/>
+      <c r="X291" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="16" customHeight="1">
       <c r="A292" s="13" t="n">
@@ -25762,13 +28386,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T292" s="15" t="n"/>
-      <c r="U292" s="17" t="n"/>
+      <c r="T292" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U292" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V292" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W292" s="17" t="n"/>
-      <c r="X292" s="15" t="n"/>
+      <c r="W292" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X292" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="16" customHeight="1">
       <c r="A293" s="13" t="n">
@@ -25947,8 +28587,16 @@
       <c r="V294" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W294" s="17" t="n"/>
-      <c r="X294" s="15" t="n"/>
+      <c r="W294" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X294" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="16" customHeight="1">
       <c r="A295" s="13" t="n">
@@ -26114,8 +28762,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T296" s="15" t="n"/>
-      <c r="U296" s="17" t="n"/>
+      <c r="T296" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U296" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V296" s="18" t="n">
         <v>4</v>
       </c>
@@ -26124,7 +28780,11 @@
           <t>Haynesville 40%; Northeast Appalachia 37%; Southwest Appalac</t>
         </is>
       </c>
-      <c r="X296" s="15" t="n"/>
+      <c r="X296" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="16" customHeight="1">
       <c r="A297" s="13" t="n">
@@ -26296,8 +28956,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T298" s="15" t="n"/>
-      <c r="U298" s="17" t="n"/>
+      <c r="T298" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U298" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V298" s="18" t="n">
         <v>2</v>
       </c>
@@ -26306,7 +28974,11 @@
           <t>US 60%; Non Us 40%</t>
         </is>
       </c>
-      <c r="X298" s="15" t="n"/>
+      <c r="X298" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="16" customHeight="1">
       <c r="A299" s="13" t="n">
@@ -26393,7 +29065,11 @@
       <c r="V299" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W299" s="17" t="n"/>
+      <c r="W299" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X299" s="15" t="inlineStr">
         <is>
           <t>Reportable +11%</t>
@@ -26489,7 +29165,11 @@
       <c r="V300" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W300" s="17" t="n"/>
+      <c r="W300" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X300" s="15" t="inlineStr">
         <is>
           <t>Tutoring -6%</t>
@@ -26572,13 +29252,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T301" s="15" t="n"/>
-      <c r="U301" s="17" t="n"/>
+      <c r="T301" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U301" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V301" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W301" s="17" t="n"/>
-      <c r="X301" s="15" t="n"/>
+      <c r="W301" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X301" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="13" t="n">
@@ -26650,13 +29346,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T302" s="15" t="n"/>
-      <c r="U302" s="17" t="n"/>
+      <c r="T302" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U302" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V302" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W302" s="17" t="n"/>
-      <c r="X302" s="15" t="n"/>
+      <c r="W302" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X302" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="16" customHeight="1">
       <c r="A303" s="13" t="n">
@@ -26929,7 +29641,11 @@
       <c r="V305" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W305" s="17" t="n"/>
+      <c r="W305" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X305" s="15" t="inlineStr">
         <is>
           <t>Single Operating -1%</t>
@@ -27017,7 +29733,11 @@
       <c r="V306" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W306" s="17" t="n"/>
+      <c r="W306" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X306" s="15" t="inlineStr">
         <is>
           <t>Reportable +7%</t>
@@ -27111,7 +29831,11 @@
       <c r="V307" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W307" s="17" t="n"/>
+      <c r="W307" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X307" s="15" t="inlineStr">
         <is>
           <t>Outdoor -4%</t>
@@ -27192,13 +29916,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T308" s="15" t="n"/>
-      <c r="U308" s="17" t="n"/>
+      <c r="T308" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U308" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V308" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W308" s="17" t="n"/>
-      <c r="X308" s="15" t="n"/>
+      <c r="W308" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X308" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="16" customHeight="1">
       <c r="A309" s="13" t="n">
@@ -27278,13 +30018,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T309" s="15" t="n"/>
-      <c r="U309" s="17" t="n"/>
+      <c r="T309" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U309" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V309" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W309" s="17" t="n"/>
-      <c r="X309" s="15" t="n"/>
+      <c r="W309" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X309" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="16" customHeight="1">
       <c r="A310" s="13" t="n">
@@ -27360,13 +30116,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T310" s="15" t="n"/>
-      <c r="U310" s="17" t="n"/>
+      <c r="T310" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U310" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V310" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W310" s="17" t="n"/>
-      <c r="X310" s="15" t="n"/>
+      <c r="W310" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X310" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="16" customHeight="1">
       <c r="A311" s="13" t="n">
@@ -27442,8 +30214,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T311" s="15" t="n"/>
-      <c r="U311" s="17" t="n"/>
+      <c r="T311" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U311" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V311" s="18" t="n">
         <v>3</v>
       </c>
@@ -27452,7 +30232,11 @@
           <t>US 64%; Europe 26%; Non US Or Europe 10%</t>
         </is>
       </c>
-      <c r="X311" s="15" t="n"/>
+      <c r="X311" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="16" customHeight="1">
       <c r="A312" s="13" t="n">
@@ -27530,13 +30314,29 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T312" s="15" t="n"/>
-      <c r="U312" s="17" t="n"/>
+      <c r="T312" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U312" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V312" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W312" s="17" t="n"/>
-      <c r="X312" s="15" t="n"/>
+      <c r="W312" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X312" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A11:X312"/>
@@ -27554,7 +30354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A2:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27583,7 +30383,6 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -27617,7 +30416,6 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -27725,9 +30523,8 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -28154,7 +30951,11 @@
       <c r="V15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="17" t="n"/>
+      <c r="W15" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X15" s="15" t="inlineStr">
         <is>
           <t>Annuities +88%</t>
@@ -28466,7 +31267,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E19" s="17" t="n"/>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F19" s="18" t="n">
         <v>8050602560</v>
       </c>
@@ -28524,7 +31329,11 @@
       <c r="V19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="17" t="n"/>
+      <c r="W19" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X19" s="15" t="inlineStr">
         <is>
           <t>PC Business Insuranc +10%</t>
@@ -28708,7 +31517,11 @@
       <c r="V21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="17" t="n"/>
+      <c r="W21" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X21" s="15" t="inlineStr">
         <is>
           <t>Southeast -3%</t>
@@ -28986,7 +31799,11 @@
       <c r="V24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="17" t="n"/>
+      <c r="W24" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X24" s="15" t="inlineStr">
         <is>
           <t>Retirement And Incom +23%</t>
@@ -29074,7 +31891,11 @@
       <c r="V25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="17" t="n"/>
+      <c r="W25" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X25" s="15" t="inlineStr">
         <is>
           <t>Accessories +2%</t>
@@ -29358,8 +32179,16 @@
       <c r="V28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="17" t="n"/>
-      <c r="X28" s="15" t="n"/>
+      <c r="W28" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="X28" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -29540,7 +32369,11 @@
       <c r="V30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="17" t="n"/>
+      <c r="W30" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X30" s="15" t="inlineStr">
         <is>
           <t>Service And Retailin +7%</t>
@@ -29632,7 +32465,11 @@
       <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="n"/>
+      <c r="W31" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X31" s="15" t="inlineStr">
         <is>
           <t>ES Lines +20%</t>
@@ -29820,7 +32657,11 @@
       <c r="V33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="17" t="n"/>
+      <c r="W33" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X33" s="15" t="inlineStr">
         <is>
           <t>Jefferson Terminal +6%</t>
@@ -30476,7 +33317,11 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="n"/>
+      <c r="W40" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>Segment Benefits And +3%</t>
@@ -30842,7 +33687,11 @@
       <c r="V44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="17" t="n"/>
+      <c r="W44" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X44" s="15" t="inlineStr">
         <is>
           <t>Development +21%</t>
@@ -30932,7 +33781,11 @@
       <c r="V45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="17" t="n"/>
+      <c r="W45" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X45" s="15" t="inlineStr">
         <is>
           <t>Spices And Flavor So -75%</t>
@@ -31020,7 +33873,11 @@
       <c r="V46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W46" s="17" t="n"/>
+      <c r="W46" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X46" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +56%</t>
@@ -31584,7 +34441,11 @@
       <c r="V52" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="17" t="n"/>
+      <c r="W52" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X52" s="15" t="inlineStr">
         <is>
           <t>Warehouse Lending +17%</t>
@@ -31858,7 +34719,11 @@
       <c r="V55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W55" s="17" t="n"/>
+      <c r="W55" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X55" s="15" t="inlineStr">
         <is>
           <t>Healthcare Services +55%</t>
@@ -31952,7 +34817,11 @@
       <c r="V56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W56" s="17" t="n"/>
+      <c r="W56" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X56" s="15" t="inlineStr">
         <is>
           <t>Poland +5%</t>
@@ -32228,7 +35097,11 @@
       <c r="V59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="17" t="n"/>
+      <c r="W59" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X59" s="15" t="inlineStr">
         <is>
           <t>Orlando FL +11%</t>
@@ -32320,7 +35193,11 @@
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="n"/>
+      <c r="W60" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X60" s="15" t="inlineStr">
         <is>
           <t>Total Operating Segm +10%</t>
@@ -32414,7 +35291,11 @@
       <c r="V61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="17" t="n"/>
+      <c r="W61" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X61" s="15" t="inlineStr">
         <is>
           <t>Sulfur Services +26%</t>
@@ -32504,7 +35385,11 @@
       <c r="V62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="17" t="n"/>
+      <c r="W62" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X62" s="15" t="inlineStr">
         <is>
           <t>Personal Lines Insur +22%</t>
@@ -33062,7 +35947,11 @@
       <c r="V68" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W68" s="17" t="n"/>
+      <c r="W68" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X68" s="15" t="inlineStr">
         <is>
           <t>Corporate And Other +22%</t>
@@ -33150,7 +36039,11 @@
       <c r="V69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="17" t="n"/>
+      <c r="W69" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X69" s="15" t="inlineStr">
         <is>
           <t>Southwest -5%</t>
@@ -33268,7 +36161,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E71" s="17" t="n"/>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F71" s="18" t="n">
         <v>11270994454.29</v>
       </c>
@@ -33330,7 +36227,11 @@
       <c r="V71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="17" t="n"/>
+      <c r="W71" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
           <t>Real Assets Group -73%</t>
@@ -33445,7 +36346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A2:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -33474,7 +36375,6 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -33508,7 +36408,6 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -33616,9 +36515,8 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -33859,7 +36757,11 @@
       <c r="V13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="17" t="n"/>
+      <c r="W13" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X13" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -34135,7 +37037,11 @@
       <c r="V16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="17" t="n"/>
+      <c r="W16" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X16" s="15" t="inlineStr">
         <is>
           <t>Publishing -18%</t>
@@ -34415,7 +37321,11 @@
       <c r="V19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="17" t="n"/>
+      <c r="W19" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X19" s="15" t="inlineStr">
         <is>
           <t>Genie Retail Energy  +19%</t>
@@ -34507,7 +37417,11 @@
       <c r="V20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="17" t="n"/>
+      <c r="W20" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X20" s="15" t="inlineStr">
         <is>
           <t>Zedge Marketplace +2%</t>
@@ -34601,7 +37515,11 @@
       <c r="V21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="17" t="n"/>
+      <c r="W21" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X21" s="15" t="inlineStr">
         <is>
           <t>Medicare +10%</t>
@@ -34791,7 +37709,11 @@
       <c r="V23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="17" t="n"/>
+      <c r="W23" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X23" s="15" t="inlineStr">
         <is>
           <t>Financial Services +11%</t>
@@ -35181,7 +38103,11 @@
       <c r="V27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="17" t="n"/>
+      <c r="W27" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X27" s="15" t="inlineStr">
         <is>
           <t>Core Banking -1%</t>
@@ -35269,7 +38195,11 @@
       <c r="V28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="17" t="n"/>
+      <c r="W28" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X28" s="15" t="inlineStr">
         <is>
           <t>Pandora And Off Plat -0%</t>
@@ -35359,7 +38289,11 @@
       <c r="V29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="17" t="n"/>
+      <c r="W29" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X29" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -35451,7 +38385,11 @@
       <c r="V30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="17" t="n"/>
+      <c r="W30" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X30" s="15" t="inlineStr">
         <is>
           <t>Enact +2%</t>
@@ -35539,7 +38477,11 @@
       <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="n"/>
+      <c r="W31" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X31" s="15" t="inlineStr">
         <is>
           <t>Institutional Produc +22%</t>
@@ -35719,7 +38661,11 @@
       <c r="V33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="17" t="n"/>
+      <c r="W33" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X33" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments  +1%</t>
@@ -35809,7 +38755,11 @@
       <c r="V34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="17" t="n"/>
+      <c r="W34" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X34" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments +15%</t>
@@ -35903,7 +38853,11 @@
       <c r="V35" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="17" t="n"/>
+      <c r="W35" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X35" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -35999,7 +38953,11 @@
       <c r="V36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="17" t="n"/>
+      <c r="W36" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X36" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +8%</t>
@@ -36187,7 +39145,11 @@
       <c r="V38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="17" t="n"/>
+      <c r="W38" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X38" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -36275,7 +39237,11 @@
       <c r="V39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W39" s="17" t="n"/>
+      <c r="W39" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X39" s="15" t="inlineStr">
         <is>
           <t>Towers +6%</t>
@@ -36363,7 +39329,11 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="n"/>
+      <c r="W40" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>University Group +35%</t>
@@ -36551,7 +39521,11 @@
       <c r="V42" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W42" s="17" t="n"/>
+      <c r="W42" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X42" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +15%</t>
@@ -36641,7 +39615,11 @@
       <c r="V43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="17" t="n"/>
+      <c r="W43" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X43" s="15" t="inlineStr">
         <is>
           <t>Mastercraft -8%</t>
@@ -37013,7 +39991,11 @@
       <c r="V47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="17" t="n"/>
+      <c r="W47" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X47" s="15" t="inlineStr">
         <is>
           <t>Storage Solutions +8%</t>
@@ -37101,7 +40083,11 @@
       <c r="V48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="17" t="n"/>
+      <c r="W48" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X48" s="15" t="inlineStr">
         <is>
           <t>Canadian Factory Bui +18%</t>
@@ -37189,7 +40175,11 @@
       <c r="V49" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W49" s="17" t="n"/>
+      <c r="W49" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X49" s="15" t="inlineStr">
         <is>
           <t>Specialty Property C +10%</t>
@@ -37279,7 +40269,11 @@
       <c r="V50" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W50" s="17" t="n"/>
+      <c r="W50" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X50" s="15" t="inlineStr">
         <is>
           <t>Protection Services -74%</t>
@@ -37467,7 +40461,11 @@
       <c r="V52" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="17" t="n"/>
+      <c r="W52" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X52" s="15" t="inlineStr">
         <is>
           <t>Outdoor -4%</t>
@@ -38217,7 +41215,11 @@
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="n"/>
+      <c r="W60" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X60" s="15" t="inlineStr">
         <is>
           <t>Shale +38%</t>
@@ -38399,7 +41401,11 @@
       <c r="V62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="17" t="n"/>
+      <c r="W62" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X62" s="15" t="inlineStr">
         <is>
           <t>Healthcare IT +11%</t>
@@ -38493,7 +41499,11 @@
       <c r="V63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="17" t="n"/>
+      <c r="W63" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X63" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -38585,7 +41595,11 @@
       <c r="V64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="17" t="n"/>
+      <c r="W64" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X64" s="15" t="inlineStr">
         <is>
           <t>Respiratory And Oxyg +24%</t>
@@ -38767,7 +41781,11 @@
       <c r="V66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="17" t="n"/>
+      <c r="W66" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X66" s="15" t="inlineStr">
         <is>
           <t>Program Of All Inclu +12%</t>
@@ -39039,7 +42057,11 @@
       <c r="V69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="17" t="n"/>
+      <c r="W69" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X69" s="15" t="inlineStr">
         <is>
           <t>All Other Segments -71%</t>
@@ -39227,7 +42249,11 @@
       <c r="V71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="17" t="n"/>
+      <c r="W71" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
           <t>Indirect -32%</t>
@@ -39342,7 +42368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X72"/>
+  <dimension ref="A2:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -39371,7 +42397,6 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -39405,7 +42430,6 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -39513,9 +42537,8 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -40117,8 +43140,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T17" s="15" t="n"/>
-      <c r="U17" s="17" t="n"/>
+      <c r="T17" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U17" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V17" s="18" t="n">
         <v>5</v>
       </c>
@@ -40127,7 +43158,11 @@
           <t>US 85%; CN 8%; Other Countries 2%</t>
         </is>
       </c>
-      <c r="X17" s="15" t="n"/>
+      <c r="X17" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="13" t="n">
@@ -40295,8 +43330,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T19" s="15" t="n"/>
-      <c r="U19" s="17" t="n"/>
+      <c r="T19" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U19" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V19" s="18" t="n">
         <v>6</v>
       </c>
@@ -40305,7 +43348,11 @@
           <t>North America 24%; US 24%; EMEA 19%</t>
         </is>
       </c>
-      <c r="X19" s="15" t="n"/>
+      <c r="X19" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n">
@@ -40620,7 +43667,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E23" s="17" t="n"/>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F23" s="18" t="n">
         <v>12285029</v>
       </c>
@@ -40671,8 +43722,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T23" s="15" t="n"/>
-      <c r="U23" s="17" t="n"/>
+      <c r="T23" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U23" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V23" s="18" t="n">
         <v>5</v>
       </c>
@@ -40681,7 +43740,11 @@
           <t>US 96%; SV 3%; AR 0%</t>
         </is>
       </c>
-      <c r="X23" s="15" t="n"/>
+      <c r="X23" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="13" t="n">
@@ -40757,8 +43820,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T24" s="15" t="n"/>
-      <c r="U24" s="17" t="n"/>
+      <c r="T24" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U24" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V24" s="18" t="n">
         <v>4</v>
       </c>
@@ -40767,7 +43838,11 @@
           <t>US 71%; GB 12%; Other International 11%</t>
         </is>
       </c>
-      <c r="X24" s="15" t="n"/>
+      <c r="X24" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="13" t="n">
@@ -41129,8 +44204,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T28" s="15" t="n"/>
-      <c r="U28" s="17" t="n"/>
+      <c r="T28" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U28" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V28" s="18" t="n">
         <v>4</v>
       </c>
@@ -41139,7 +44222,11 @@
           <t>US 65%; EMEA 28%; Asia Pacific 6%</t>
         </is>
       </c>
-      <c r="X28" s="15" t="n"/>
+      <c r="X28" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -41215,8 +44302,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T29" s="15" t="n"/>
-      <c r="U29" s="17" t="n"/>
+      <c r="T29" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U29" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V29" s="18" t="n">
         <v>9</v>
       </c>
@@ -41225,7 +44320,11 @@
           <t>Europe 26%; Americas 21%; US 20%</t>
         </is>
       </c>
-      <c r="X29" s="15" t="n"/>
+      <c r="X29" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="13" t="n">
@@ -41305,8 +44404,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T30" s="15" t="n"/>
-      <c r="U30" s="17" t="n"/>
+      <c r="T30" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U30" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V30" s="18" t="n">
         <v>4</v>
       </c>
@@ -41315,7 +44422,11 @@
           <t>EMEA 48%; Americas 41%; Asia Pacific 11%</t>
         </is>
       </c>
-      <c r="X30" s="15" t="n"/>
+      <c r="X30" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="13" t="n">
@@ -41957,8 +45068,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T37" s="15" t="n"/>
-      <c r="U37" s="17" t="n"/>
+      <c r="T37" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U37" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V37" s="18" t="n">
         <v>4</v>
       </c>
@@ -41967,7 +45086,11 @@
           <t>North America 42%; US 41%; Rest Of World 12%</t>
         </is>
       </c>
-      <c r="X37" s="15" t="n"/>
+      <c r="X37" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -42137,8 +45260,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T39" s="15" t="n"/>
-      <c r="U39" s="17" t="n"/>
+      <c r="T39" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U39" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V39" s="18" t="n">
         <v>4</v>
       </c>
@@ -42147,7 +45278,11 @@
           <t>US 82%; Africa 12%; Europe 3%</t>
         </is>
       </c>
-      <c r="X39" s="15" t="n"/>
+      <c r="X39" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -42313,8 +45448,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T41" s="15" t="n"/>
-      <c r="U41" s="17" t="n"/>
+      <c r="T41" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U41" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V41" s="18" t="n">
         <v>5</v>
       </c>
@@ -42323,7 +45466,11 @@
           <t>US 61%; Non Us 20%; Europe 13%</t>
         </is>
       </c>
-      <c r="X41" s="15" t="n"/>
+      <c r="X41" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="13" t="n">
@@ -42399,8 +45546,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T42" s="15" t="n"/>
-      <c r="U42" s="17" t="n"/>
+      <c r="T42" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U42" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V42" s="18" t="n">
         <v>5</v>
       </c>
@@ -42409,7 +45564,11 @@
           <t>US 92%; Non Us 6%; CA 1%</t>
         </is>
       </c>
-      <c r="X42" s="15" t="n"/>
+      <c r="X42" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="13" t="n">
@@ -42575,8 +45734,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T44" s="15" t="n"/>
-      <c r="U44" s="17" t="n"/>
+      <c r="T44" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U44" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V44" s="18" t="n">
         <v>9</v>
       </c>
@@ -42585,7 +45752,11 @@
           <t>Asia Pacific 26%; Europe 22%; CN 19%</t>
         </is>
       </c>
-      <c r="X44" s="15" t="n"/>
+      <c r="X44" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -42761,8 +45932,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T46" s="15" t="n"/>
-      <c r="U46" s="17" t="n"/>
+      <c r="T46" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U46" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V46" s="18" t="n">
         <v>6</v>
       </c>
@@ -42771,7 +45950,11 @@
           <t>Americas 28%; US 26%; EMEA 26%</t>
         </is>
       </c>
-      <c r="X46" s="15" t="n"/>
+      <c r="X46" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -42843,8 +46026,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T47" s="15" t="n"/>
-      <c r="U47" s="17" t="n"/>
+      <c r="T47" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U47" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V47" s="18" t="n">
         <v>8</v>
       </c>
@@ -42853,7 +46044,11 @@
           <t>CN 27%; JP 19%; Europe 15%</t>
         </is>
       </c>
-      <c r="X47" s="15" t="n"/>
+      <c r="X47" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="13" t="n">
@@ -42925,8 +46120,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T48" s="15" t="n"/>
-      <c r="U48" s="17" t="n"/>
+      <c r="T48" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U48" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V48" s="18" t="n">
         <v>4</v>
       </c>
@@ -42935,7 +46138,11 @@
           <t>Haynesville 40%; Northeast Appalachia 37%; Southwest Appalac</t>
         </is>
       </c>
-      <c r="X48" s="15" t="n"/>
+      <c r="X48" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -43291,8 +46498,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T52" s="15" t="n"/>
-      <c r="U52" s="17" t="n"/>
+      <c r="T52" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U52" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V52" s="18" t="n">
         <v>6</v>
       </c>
@@ -43301,7 +46516,11 @@
           <t>North America 30%; US 27%; EMEA 25%</t>
         </is>
       </c>
-      <c r="X52" s="15" t="n"/>
+      <c r="X52" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -43943,8 +47162,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T59" s="15" t="n"/>
-      <c r="U59" s="17" t="n"/>
+      <c r="T59" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U59" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V59" s="18" t="n">
         <v>4</v>
       </c>
@@ -43953,7 +47180,11 @@
           <t>US 45%; Europe Middle East And Africa 26%; Asia Pacific 25%</t>
         </is>
       </c>
-      <c r="X59" s="15" t="n"/>
+      <c r="X59" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="13" t="n">
@@ -44405,8 +47636,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T64" s="15" t="n"/>
-      <c r="U64" s="17" t="n"/>
+      <c r="T64" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U64" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V64" s="18" t="n">
         <v>5</v>
       </c>
@@ -44415,7 +47654,11 @@
           <t>US 76%; Non Us 12%; EMEA 7%</t>
         </is>
       </c>
-      <c r="X64" s="15" t="n"/>
+      <c r="X64" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n">
@@ -44489,8 +47732,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T65" s="15" t="n"/>
-      <c r="U65" s="17" t="n"/>
+      <c r="T65" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U65" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V65" s="18" t="n">
         <v>4</v>
       </c>
@@ -44499,7 +47750,11 @@
           <t>US 69%; Other Countries 17%; DE 11%</t>
         </is>
       </c>
-      <c r="X65" s="15" t="n"/>
+      <c r="X65" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="13" t="n">
@@ -44759,8 +48014,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T68" s="15" t="n"/>
-      <c r="U68" s="17" t="n"/>
+      <c r="T68" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U68" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V68" s="18" t="n">
         <v>5</v>
       </c>
@@ -44769,7 +48032,11 @@
           <t>North America 34%; US 31%; EMEA 27%</t>
         </is>
       </c>
-      <c r="X68" s="15" t="n"/>
+      <c r="X68" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="13" t="n">
@@ -44843,8 +48110,16 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T69" s="15" t="n"/>
-      <c r="U69" s="17" t="n"/>
+      <c r="T69" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="U69" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="V69" s="18" t="n">
         <v>7</v>
       </c>
@@ -44853,7 +48128,11 @@
           <t>US 90%; Europe 5%; Asia 2%</t>
         </is>
       </c>
-      <c r="X69" s="15" t="n"/>
+      <c r="X69" s="15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n">
@@ -45157,7 +48436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X162"/>
+  <dimension ref="A2:X162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -45186,7 +48465,6 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -45220,7 +48498,6 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -45328,9 +48605,8 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -45665,7 +48941,11 @@
       <c r="V14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="17" t="n"/>
+      <c r="W14" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X14" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -45755,7 +49035,11 @@
       <c r="V15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="17" t="n"/>
+      <c r="W15" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X15" s="15" t="inlineStr">
         <is>
           <t>International +344%</t>
@@ -46413,7 +49697,11 @@
       <c r="V22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="17" t="n"/>
+      <c r="W22" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X22" s="15" t="inlineStr">
         <is>
           <t>Distribution +302%</t>
@@ -46501,7 +49789,11 @@
       <c r="V23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="17" t="n"/>
+      <c r="W23" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X23" s="15" t="inlineStr">
         <is>
           <t>Corporate And Other +270%</t>
@@ -46591,7 +49883,11 @@
       <c r="V24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="17" t="n"/>
+      <c r="W24" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X24" s="15" t="inlineStr">
         <is>
           <t>Timber +327%</t>
@@ -46681,7 +49977,11 @@
       <c r="V25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="17" t="n"/>
+      <c r="W25" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X25" s="15" t="inlineStr">
         <is>
           <t>Land Management And  +309%</t>
@@ -46775,7 +50075,11 @@
       <c r="V26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="17" t="n"/>
+      <c r="W26" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X26" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -46869,7 +50173,11 @@
       <c r="V27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="17" t="n"/>
+      <c r="W27" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X27" s="15" t="inlineStr">
         <is>
           <t>Metals +249%</t>
@@ -47521,7 +50829,11 @@
       <c r="V34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="17" t="n"/>
+      <c r="W34" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X34" s="15" t="inlineStr">
         <is>
           <t>Software And Service +222%</t>
@@ -47705,7 +51017,11 @@
       <c r="V36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="17" t="n"/>
+      <c r="W36" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X36" s="15" t="inlineStr">
         <is>
           <t>Real Estate +246%</t>
@@ -47919,7 +51235,11 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="E39" s="17" t="n"/>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F39" s="18" t="n">
         <v>40103256</v>
       </c>
@@ -48073,7 +51393,11 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="n"/>
+      <c r="W40" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +257%</t>
@@ -48161,7 +51485,11 @@
       <c r="V41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W41" s="17" t="n"/>
+      <c r="W41" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X41" s="15" t="inlineStr">
         <is>
           <t>Restaurant Food Sale +224%</t>
@@ -49125,7 +52453,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E52" s="17" t="n"/>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F52" s="18" t="n">
         <v>4947405312</v>
       </c>
@@ -49285,7 +52617,11 @@
       <c r="V53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="17" t="n"/>
+      <c r="W53" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X53" s="15" t="inlineStr">
         <is>
           <t>Mobile Fuel Delivery +195%</t>
@@ -49657,7 +52993,11 @@
       <c r="V57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="17" t="n"/>
+      <c r="W57" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X57" s="15" t="inlineStr">
         <is>
           <t>Mid Con Barnett Shal +180%</t>
@@ -49777,7 +53117,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E59" s="17" t="n"/>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F59" s="18" t="n">
         <v>56211529728</v>
       </c>
@@ -49835,7 +53179,11 @@
       <c r="V59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="17" t="n"/>
+      <c r="W59" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X59" s="15" t="inlineStr">
         <is>
           <t>Refined Products And +192%</t>
@@ -49923,7 +53271,11 @@
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="n"/>
+      <c r="W60" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X60" s="15" t="inlineStr">
         <is>
           <t>Lennar Other +191%</t>
@@ -49949,7 +53301,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E61" s="17" t="n"/>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F61" s="18" t="n">
         <v>15829233282.24</v>
       </c>
@@ -50023,7 +53379,11 @@
       <c r="V61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="17" t="n"/>
+      <c r="W61" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X61" s="15" t="inlineStr">
         <is>
           <t>Proshares Ultra Shor +207%</t>
@@ -50301,7 +53661,11 @@
       <c r="V64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="17" t="n"/>
+      <c r="W64" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X64" s="15" t="inlineStr">
         <is>
           <t>Four +170%</t>
@@ -50395,7 +53759,11 @@
       <c r="V65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="17" t="n"/>
+      <c r="W65" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X65" s="15" t="inlineStr">
         <is>
           <t>Corporate And Other +153%</t>
@@ -50483,7 +53851,11 @@
       <c r="V66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="17" t="n"/>
+      <c r="W66" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X66" s="15" t="inlineStr">
         <is>
           <t>Transmission +162%</t>
@@ -50787,7 +54159,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E70" s="17" t="n"/>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F70" s="18" t="n">
         <v>682785117.6</v>
       </c>
@@ -50853,7 +54229,11 @@
       <c r="V70" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W70" s="17" t="n"/>
+      <c r="W70" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
           <t>Granite Creek Mining +190%</t>
@@ -50943,7 +54323,11 @@
       <c r="V71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="17" t="n"/>
+      <c r="W71" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
           <t>Sphere Entertainment +164%</t>
@@ -51031,7 +54415,11 @@
       <c r="V72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W72" s="17" t="n"/>
+      <c r="W72" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X72" s="15" t="inlineStr">
         <is>
           <t>NW Holdings Other +141%</t>
@@ -51793,7 +55181,11 @@
       <c r="V80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="17" t="n"/>
+      <c r="W80" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X80" s="15" t="inlineStr">
         <is>
           <t>Commercial +128%</t>
@@ -51975,7 +55367,11 @@
       <c r="V82" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="17" t="n"/>
+      <c r="W82" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X82" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +118%</t>
@@ -52533,7 +55929,11 @@
       <c r="V88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="17" t="n"/>
+      <c r="W88" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X88" s="15" t="inlineStr">
         <is>
           <t>Financial Services +124%</t>
@@ -52623,7 +56023,11 @@
       <c r="V89" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W89" s="17" t="n"/>
+      <c r="W89" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X89" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +99%</t>
@@ -52813,7 +56217,11 @@
       <c r="V91" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W91" s="17" t="n"/>
+      <c r="W91" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X91" s="15" t="inlineStr">
         <is>
           <t>Debt And Preferred E +113%</t>
@@ -53091,7 +56499,11 @@
       <c r="V94" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="17" t="n"/>
+      <c r="W94" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X94" s="15" t="inlineStr">
         <is>
           <t>Engineering +103%</t>
@@ -53277,7 +56689,11 @@
       <c r="V96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="17" t="n"/>
+      <c r="W96" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X96" s="15" t="inlineStr">
         <is>
           <t>Security Solutions +103%</t>
@@ -53369,7 +56785,11 @@
       <c r="V97" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W97" s="17" t="n"/>
+      <c r="W97" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X97" s="15" t="inlineStr">
         <is>
           <t>Nimble Title Holding +88%</t>
@@ -53827,7 +57247,11 @@
       <c r="V102" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="17" t="n"/>
+      <c r="W102" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
           <t>Asset Closure +90%</t>
@@ -53919,7 +57343,11 @@
       <c r="V103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W103" s="17" t="n"/>
+      <c r="W103" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X103" s="15" t="inlineStr">
         <is>
           <t>Annuities +88%</t>
@@ -54009,7 +57437,11 @@
       <c r="V104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="17" t="n"/>
+      <c r="W104" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X104" s="15" t="inlineStr">
         <is>
           <t>Portfolio Management +76%</t>
@@ -54477,7 +57909,11 @@
       <c r="V109" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W109" s="17" t="n"/>
+      <c r="W109" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X109" s="15" t="inlineStr">
         <is>
           <t>Financial Services +71%</t>
@@ -54569,7 +58005,11 @@
       <c r="V110" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W110" s="17" t="n"/>
+      <c r="W110" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X110" s="15" t="inlineStr">
         <is>
           <t>Water Treatment +83%</t>
@@ -54755,7 +58195,11 @@
       <c r="V112" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W112" s="17" t="n"/>
+      <c r="W112" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X112" s="15" t="inlineStr">
         <is>
           <t>Eastern Hemisphere +78%</t>
@@ -54849,7 +58293,11 @@
       <c r="V113" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W113" s="17" t="n"/>
+      <c r="W113" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X113" s="15" t="inlineStr">
         <is>
           <t>Branded +69%</t>
@@ -54937,7 +58385,11 @@
       <c r="V114" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W114" s="17" t="n"/>
+      <c r="W114" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X114" s="15" t="inlineStr">
         <is>
           <t>Financial +66%</t>
@@ -55117,7 +58569,11 @@
       <c r="V116" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="17" t="n"/>
+      <c r="W116" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X116" s="15" t="inlineStr">
         <is>
           <t>Onsite Health Clinic +72%</t>
@@ -55143,7 +58599,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E117" s="17" t="n"/>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F117" s="18" t="n">
         <v>704822781.0700001</v>
       </c>
@@ -55201,7 +58661,11 @@
       <c r="V117" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W117" s="17" t="n"/>
+      <c r="W117" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X117" s="15" t="inlineStr">
         <is>
           <t>Commercial Loan Inve +70%</t>
@@ -55291,7 +58755,11 @@
       <c r="V118" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W118" s="17" t="n"/>
+      <c r="W118" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X118" s="15" t="inlineStr">
         <is>
           <t>Onshore Facilities A +67%</t>
@@ -55477,7 +58945,11 @@
       <c r="V120" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W120" s="17" t="n"/>
+      <c r="W120" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X120" s="15" t="inlineStr">
         <is>
           <t>Hospitality +73%</t>
@@ -55573,7 +59045,11 @@
       <c r="V121" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W121" s="17" t="n"/>
+      <c r="W121" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X121" s="15" t="inlineStr">
         <is>
           <t>High Performance Com +75%</t>
@@ -55665,7 +59141,11 @@
       <c r="V122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W122" s="17" t="n"/>
+      <c r="W122" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X122" s="15" t="inlineStr">
         <is>
           <t>Medicare +62%</t>
@@ -56231,7 +59711,11 @@
       <c r="V128" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W128" s="17" t="n"/>
+      <c r="W128" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X128" s="15" t="inlineStr">
         <is>
           <t>Bank +56%</t>
@@ -56319,7 +59803,11 @@
       <c r="V129" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W129" s="17" t="n"/>
+      <c r="W129" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X129" s="15" t="inlineStr">
         <is>
           <t>Electrical +62%</t>
@@ -56439,7 +59927,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E131" s="17" t="n"/>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F131" s="18" t="n">
         <v>935408752.55</v>
       </c>
@@ -56593,7 +60085,11 @@
       <c r="V132" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W132" s="17" t="n"/>
+      <c r="W132" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X132" s="15" t="inlineStr">
         <is>
           <t>Telehealth Subscript +67%</t>
@@ -56873,7 +60369,11 @@
       <c r="V135" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W135" s="17" t="n"/>
+      <c r="W135" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X135" s="15" t="inlineStr">
         <is>
           <t>E Infrastructure Sol +59%</t>
@@ -56969,7 +60469,11 @@
       <c r="V136" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W136" s="17" t="n"/>
+      <c r="W136" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X136" s="15" t="inlineStr">
         <is>
           <t>Banking +62%</t>
@@ -57057,7 +60561,11 @@
       <c r="V137" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W137" s="17" t="n"/>
+      <c r="W137" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X137" s="15" t="inlineStr">
         <is>
           <t>Healthcare Services +55%</t>
@@ -57239,7 +60747,11 @@
       <c r="V139" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W139" s="17" t="n"/>
+      <c r="W139" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X139" s="15" t="inlineStr">
         <is>
           <t>Pipeline +55%</t>
@@ -57327,7 +60839,11 @@
       <c r="V140" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W140" s="17" t="n"/>
+      <c r="W140" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X140" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +56%</t>
@@ -57545,7 +61061,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E143" s="17" t="n"/>
+      <c r="E143" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F143" s="18" t="n">
         <v>2302047000</v>
       </c>
@@ -57603,7 +61123,11 @@
       <c r="V143" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W143" s="17" t="n"/>
+      <c r="W143" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X143" s="15" t="inlineStr">
         <is>
           <t>Array +58%</t>
@@ -57975,7 +61499,11 @@
       <c r="V147" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W147" s="17" t="n"/>
+      <c r="W147" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X147" s="15" t="inlineStr">
         <is>
           <t>United States +52%</t>
@@ -58155,7 +61683,11 @@
       <c r="V149" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W149" s="17" t="n"/>
+      <c r="W149" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X149" s="15" t="inlineStr">
         <is>
           <t>Senior Housing Opera +47%</t>
@@ -58467,7 +61999,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E153" s="17" t="n"/>
+      <c r="E153" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="F153" s="18" t="n">
         <v>161733088160.3101</v>
       </c>
@@ -58625,7 +62161,11 @@
       <c r="V154" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W154" s="17" t="n"/>
+      <c r="W154" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X154" s="15" t="inlineStr">
         <is>
           <t>Kudu Investment Mana +54%</t>
@@ -58715,7 +62255,11 @@
       <c r="V155" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W155" s="17" t="n"/>
+      <c r="W155" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X155" s="15" t="inlineStr">
         <is>
           <t>Mid Atlantic Region +54%</t>
@@ -58895,7 +62439,11 @@
       <c r="V157" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W157" s="17" t="n"/>
+      <c r="W157" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X157" s="15" t="inlineStr">
         <is>
           <t>Integrated Upstream  +49%</t>
@@ -59079,7 +62627,11 @@
       <c r="V159" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W159" s="17" t="n"/>
+      <c r="W159" s="17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="X159" s="15" t="inlineStr">
         <is>
           <t>Consumer +48%</t>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:G20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -552,6 +552,8 @@
     <col width="6" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -574,6 +576,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -581,8 +584,9 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>UNIVERSE STATS</t>
         </is>
@@ -692,8 +696,9 @@
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TABS IN THIS WORKBOOK</t>
         </is>
@@ -814,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X312"/>
+  <dimension ref="A1:X312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -843,6 +848,7 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -876,6 +882,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -983,8 +990,9 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -1223,16 +1231,8 @@
       <c r="V13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X13" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W13" s="17" t="n"/>
+      <c r="X13" s="15" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -1321,11 +1321,7 @@
       <c r="V14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W14" s="17" t="n"/>
       <c r="X14" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -1509,11 +1505,7 @@
       <c r="V16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W16" s="17" t="n"/>
       <c r="X16" s="15" t="inlineStr">
         <is>
           <t>American Southern +39%</t>
@@ -1703,11 +1695,7 @@
       <c r="V18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W18" s="17" t="n"/>
       <c r="X18" s="15" t="inlineStr">
         <is>
           <t>Reportable +267%</t>
@@ -1897,11 +1885,7 @@
       <c r="V20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W20" s="17" t="n"/>
       <c r="X20" s="15" t="inlineStr">
         <is>
           <t>Commercial Banking +44%</t>
@@ -1982,16 +1966,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T21" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T21" s="15" t="n"/>
+      <c r="U21" s="17" t="n"/>
       <c r="V21" s="18" t="n">
         <v>3</v>
       </c>
@@ -2000,11 +1976,7 @@
           <t>CA 68%; IL 26%; Other Countries 6%</t>
         </is>
       </c>
-      <c r="X21" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X21" s="15" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="13" t="n">
@@ -2376,29 +2348,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T25" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U25" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T25" s="15" t="n"/>
+      <c r="U25" s="17" t="n"/>
       <c r="V25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X25" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W25" s="17" t="n"/>
+      <c r="X25" s="15" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="13" t="n">
@@ -2476,29 +2432,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T26" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U26" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T26" s="15" t="n"/>
+      <c r="U26" s="17" t="n"/>
       <c r="V26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X26" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W26" s="17" t="n"/>
+      <c r="X26" s="15" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="13" t="n">
@@ -2578,29 +2518,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T27" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T27" s="15" t="n"/>
+      <c r="U27" s="17" t="n"/>
       <c r="V27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X27" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W27" s="17" t="n"/>
+      <c r="X27" s="15" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="13" t="n">
@@ -2770,29 +2694,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T29" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T29" s="15" t="n"/>
+      <c r="U29" s="17" t="n"/>
       <c r="V29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X29" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W29" s="17" t="n"/>
+      <c r="X29" s="15" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="13" t="n">
@@ -2879,11 +2787,7 @@
       <c r="V30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W30" s="17" t="n"/>
       <c r="X30" s="15" t="inlineStr">
         <is>
           <t>Reportable +288%</t>
@@ -2966,29 +2870,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T31" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T31" s="15" t="n"/>
+      <c r="U31" s="17" t="n"/>
       <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X31" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W31" s="17" t="n"/>
+      <c r="X31" s="15" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="13" t="n">
@@ -3068,29 +2956,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T32" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U32" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T32" s="15" t="n"/>
+      <c r="U32" s="17" t="n"/>
       <c r="V32" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X32" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W32" s="17" t="n"/>
+      <c r="X32" s="15" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="13" t="n">
@@ -3266,16 +3138,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T34" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U34" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T34" s="15" t="n"/>
+      <c r="U34" s="17" t="n"/>
       <c r="V34" s="18" t="n">
         <v>2</v>
       </c>
@@ -3284,11 +3148,7 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="X34" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X34" s="15" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="13" t="n">
@@ -3401,11 +3261,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E36" s="17" t="n"/>
       <c r="F36" s="18" t="n">
         <v>2186936064</v>
       </c>
@@ -3458,29 +3314,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T36" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T36" s="15" t="n"/>
+      <c r="U36" s="17" t="n"/>
       <c r="V36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X36" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W36" s="17" t="n"/>
+      <c r="X36" s="15" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="13" t="n">
@@ -3558,29 +3398,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T37" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T37" s="15" t="n"/>
+      <c r="U37" s="17" t="n"/>
       <c r="V37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X37" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W37" s="17" t="n"/>
+      <c r="X37" s="15" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -3658,29 +3482,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T38" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U38" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T38" s="15" t="n"/>
+      <c r="U38" s="17" t="n"/>
       <c r="V38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X38" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W38" s="17" t="n"/>
+      <c r="X38" s="15" t="n"/>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="13" t="n">
@@ -3752,16 +3560,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T39" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U39" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T39" s="15" t="n"/>
+      <c r="U39" s="17" t="n"/>
       <c r="V39" s="18" t="n">
         <v>5</v>
       </c>
@@ -3770,11 +3570,7 @@
           <t>US 85%; CN 8%; Other Countries 2%</t>
         </is>
       </c>
-      <c r="X39" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X39" s="15" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -3859,11 +3655,7 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W40" s="17" t="n"/>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>Publishing -18%</t>
@@ -4138,29 +3930,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T43" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U43" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T43" s="15" t="n"/>
+      <c r="U43" s="17" t="n"/>
       <c r="V43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X43" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W43" s="17" t="n"/>
+      <c r="X43" s="15" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="13" t="n">
@@ -4236,29 +4012,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T44" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T44" s="15" t="n"/>
+      <c r="U44" s="17" t="n"/>
       <c r="V44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X44" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W44" s="17" t="n"/>
+      <c r="X44" s="15" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -4341,11 +4101,7 @@
       <c r="V45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W45" s="17" t="n"/>
       <c r="X45" s="15" t="inlineStr">
         <is>
           <t>Genie Retail Energy  +19%</t>
@@ -4424,16 +4180,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T46" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U46" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T46" s="15" t="n"/>
+      <c r="U46" s="17" t="n"/>
       <c r="V46" s="18" t="n">
         <v>2</v>
       </c>
@@ -4442,11 +4190,7 @@
           <t>Domestic Sales 98%; International Sales 2%</t>
         </is>
       </c>
-      <c r="X46" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X46" s="15" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -4522,29 +4266,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T47" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U47" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T47" s="15" t="n"/>
+      <c r="U47" s="17" t="n"/>
       <c r="V47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X47" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W47" s="17" t="n"/>
+      <c r="X47" s="15" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="13" t="n">
@@ -4565,11 +4293,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E48" s="17" t="n"/>
       <c r="F48" s="18" t="n">
         <v>532783922.1609974</v>
       </c>
@@ -4624,29 +4348,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T48" s="15" t="n"/>
+      <c r="U48" s="17" t="n"/>
       <c r="V48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W48" s="17" t="n"/>
+      <c r="X48" s="15" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -4726,16 +4434,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T49" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U49" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T49" s="15" t="n"/>
+      <c r="U49" s="17" t="n"/>
       <c r="V49" s="18" t="n">
         <v>2</v>
       </c>
@@ -4744,11 +4444,7 @@
           <t>US 74%; Non Us 26%</t>
         </is>
       </c>
-      <c r="X49" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X49" s="15" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="13" t="n">
@@ -4922,29 +4618,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T51" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U51" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T51" s="15" t="n"/>
+      <c r="U51" s="17" t="n"/>
       <c r="V51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W51" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X51" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W51" s="17" t="n"/>
+      <c r="X51" s="15" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="13" t="n">
@@ -5018,16 +4698,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T52" s="15" t="n"/>
+      <c r="U52" s="17" t="n"/>
       <c r="V52" s="18" t="n">
         <v>6</v>
       </c>
@@ -5036,11 +4708,7 @@
           <t>North America 24%; US 24%; EMEA 19%</t>
         </is>
       </c>
-      <c r="X52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X52" s="15" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -5118,29 +4786,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T53" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T53" s="15" t="n"/>
+      <c r="U53" s="17" t="n"/>
       <c r="V53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X53" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W53" s="17" t="n"/>
+      <c r="X53" s="15" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="13" t="n">
@@ -5218,29 +4870,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T54" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U54" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T54" s="15" t="n"/>
+      <c r="U54" s="17" t="n"/>
       <c r="V54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W54" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X54" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W54" s="17" t="n"/>
+      <c r="X54" s="15" t="n"/>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="13" t="n">
@@ -5318,16 +4954,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T55" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U55" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T55" s="15" t="n"/>
+      <c r="U55" s="17" t="n"/>
       <c r="V55" s="18" t="n">
         <v>2</v>
       </c>
@@ -5336,11 +4964,7 @@
           <t>US 95%; Non Us 5%</t>
         </is>
       </c>
-      <c r="X55" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X55" s="15" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="13" t="n">
@@ -5427,11 +5051,7 @@
       <c r="V56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W56" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W56" s="17" t="n"/>
       <c r="X56" s="15" t="inlineStr">
         <is>
           <t>Zedge Marketplace +2%</t>
@@ -5510,29 +5130,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T57" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T57" s="15" t="n"/>
+      <c r="U57" s="17" t="n"/>
       <c r="V57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X57" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W57" s="17" t="n"/>
+      <c r="X57" s="15" t="n"/>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="13" t="n">
@@ -5608,29 +5212,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T58" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U58" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T58" s="15" t="n"/>
+      <c r="U58" s="17" t="n"/>
       <c r="V58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W58" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X58" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W58" s="17" t="n"/>
+      <c r="X58" s="15" t="n"/>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="13" t="n">
@@ -5708,29 +5296,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T59" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T59" s="15" t="n"/>
+      <c r="U59" s="17" t="n"/>
       <c r="V59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X59" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W59" s="17" t="n"/>
+      <c r="X59" s="15" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="13" t="n">
@@ -5810,29 +5382,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T60" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T60" s="15" t="n"/>
+      <c r="U60" s="17" t="n"/>
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X60" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W60" s="17" t="n"/>
+      <c r="X60" s="15" t="n"/>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="13" t="n">
@@ -5910,29 +5466,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T61" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T61" s="15" t="n"/>
+      <c r="U61" s="17" t="n"/>
       <c r="V61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X61" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W61" s="17" t="n"/>
+      <c r="X61" s="15" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="13" t="n">
@@ -6021,11 +5561,7 @@
       <c r="V62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W62" s="17" t="n"/>
       <c r="X62" s="15" t="inlineStr">
         <is>
           <t>Medicare +10%</t>
@@ -6115,11 +5651,7 @@
       <c r="V63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W63" s="17" t="n"/>
       <c r="X63" s="15" t="inlineStr">
         <is>
           <t>Reportable -5%</t>
@@ -6202,29 +5734,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T64" s="15" t="n"/>
+      <c r="U64" s="17" t="n"/>
       <c r="V64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W64" s="17" t="n"/>
+      <c r="X64" s="15" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n">
@@ -6311,11 +5827,7 @@
       <c r="V65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W65" s="17" t="n"/>
       <c r="X65" s="15" t="inlineStr">
         <is>
           <t>Annuities +88%</t>
@@ -6398,29 +5910,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T66" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T66" s="15" t="n"/>
+      <c r="U66" s="17" t="n"/>
       <c r="V66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X66" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W66" s="17" t="n"/>
+      <c r="X66" s="15" t="n"/>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="13" t="n">
@@ -6594,29 +6090,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T68" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U68" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T68" s="15" t="n"/>
+      <c r="U68" s="17" t="n"/>
       <c r="V68" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W68" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X68" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W68" s="17" t="n"/>
+      <c r="X68" s="15" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="13" t="n">
@@ -6690,29 +6170,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T69" s="15" t="n"/>
+      <c r="U69" s="17" t="n"/>
       <c r="V69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W69" s="17" t="n"/>
+      <c r="X69" s="15" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n">
@@ -6788,29 +6252,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T70" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U70" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T70" s="15" t="n"/>
+      <c r="U70" s="17" t="n"/>
       <c r="V70" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W70" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X70" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W70" s="17" t="n"/>
+      <c r="X70" s="15" t="n"/>
     </row>
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="13" t="n">
@@ -6991,11 +6439,7 @@
       <c r="V72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W72" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W72" s="17" t="n"/>
       <c r="X72" s="15" t="inlineStr">
         <is>
           <t>Real Estate Operatio -11%</t>
@@ -7085,11 +6529,7 @@
       <c r="V73" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W73" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W73" s="17" t="n"/>
       <c r="X73" s="15" t="inlineStr">
         <is>
           <t>Reportable +22%</t>
@@ -7168,29 +6608,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T74" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U74" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T74" s="15" t="n"/>
+      <c r="U74" s="17" t="n"/>
       <c r="V74" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W74" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X74" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W74" s="17" t="n"/>
+      <c r="X74" s="15" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="13" t="n">
@@ -7264,29 +6688,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T75" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U75" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T75" s="15" t="n"/>
+      <c r="U75" s="17" t="n"/>
       <c r="V75" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W75" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X75" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W75" s="17" t="n"/>
+      <c r="X75" s="15" t="n"/>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="13" t="n">
@@ -7364,29 +6772,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T76" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U76" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T76" s="15" t="n"/>
+      <c r="U76" s="17" t="n"/>
       <c r="V76" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W76" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X76" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W76" s="17" t="n"/>
+      <c r="X76" s="15" t="n"/>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="13" t="n">
@@ -7475,11 +6867,7 @@
       <c r="V77" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W77" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W77" s="17" t="n"/>
       <c r="X77" s="15" t="inlineStr">
         <is>
           <t>RX +22%</t>
@@ -7658,29 +7046,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T79" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U79" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T79" s="15" t="n"/>
+      <c r="U79" s="17" t="n"/>
       <c r="V79" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W79" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X79" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W79" s="17" t="n"/>
+      <c r="X79" s="15" t="n"/>
     </row>
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="13" t="n">
@@ -7758,29 +7130,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T80" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U80" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T80" s="15" t="n"/>
+      <c r="U80" s="17" t="n"/>
       <c r="V80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X80" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W80" s="17" t="n"/>
+      <c r="X80" s="15" t="n"/>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="13" t="n">
@@ -7865,11 +7221,7 @@
       <c r="V81" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W81" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W81" s="17" t="n"/>
       <c r="X81" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments -74%</t>
@@ -7952,29 +7304,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T82" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U82" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T82" s="15" t="n"/>
+      <c r="U82" s="17" t="n"/>
       <c r="V82" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X82" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W82" s="17" t="n"/>
+      <c r="X82" s="15" t="n"/>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="13" t="n">
@@ -8059,11 +7395,7 @@
       <c r="V83" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W83" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W83" s="17" t="n"/>
       <c r="X83" s="15" t="inlineStr">
         <is>
           <t>Land Development +4%</t>
@@ -8144,29 +7476,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T84" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U84" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T84" s="15" t="n"/>
+      <c r="U84" s="17" t="n"/>
       <c r="V84" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W84" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X84" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W84" s="17" t="n"/>
+      <c r="X84" s="15" t="n"/>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="13" t="n">
@@ -8253,11 +7569,7 @@
       <c r="V85" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W85" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W85" s="17" t="n"/>
       <c r="X85" s="15" t="inlineStr">
         <is>
           <t>Financial Services +11%</t>
@@ -8438,29 +7750,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T87" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U87" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T87" s="15" t="n"/>
+      <c r="U87" s="17" t="n"/>
       <c r="V87" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W87" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X87" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W87" s="17" t="n"/>
+      <c r="X87" s="15" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="13" t="n">
@@ -8540,16 +7836,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T88" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U88" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T88" s="15" t="n"/>
+      <c r="U88" s="17" t="n"/>
       <c r="V88" s="18" t="n">
         <v>1</v>
       </c>
@@ -8558,11 +7846,7 @@
           <t>Foreign Countries 100%</t>
         </is>
       </c>
-      <c r="X88" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X88" s="15" t="n"/>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -8642,29 +7926,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T89" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U89" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T89" s="15" t="n"/>
+      <c r="U89" s="17" t="n"/>
       <c r="V89" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W89" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X89" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W89" s="17" t="n"/>
+      <c r="X89" s="15" t="n"/>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="13" t="n">
@@ -8736,29 +8004,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T90" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U90" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T90" s="15" t="n"/>
+      <c r="U90" s="17" t="n"/>
       <c r="V90" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W90" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X90" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W90" s="17" t="n"/>
+      <c r="X90" s="15" t="n"/>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="13" t="n">
@@ -8838,16 +8090,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T91" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U91" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T91" s="15" t="n"/>
+      <c r="U91" s="17" t="n"/>
       <c r="V91" s="18" t="n">
         <v>2</v>
       </c>
@@ -8856,11 +8100,7 @@
           <t>JP 100%; US 0%</t>
         </is>
       </c>
-      <c r="X91" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X91" s="15" t="n"/>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -8881,11 +8121,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E92" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E92" s="17" t="n"/>
       <c r="F92" s="18" t="n">
         <v>28291916</v>
       </c>
@@ -8940,29 +8176,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T92" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U92" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T92" s="15" t="n"/>
+      <c r="U92" s="17" t="n"/>
       <c r="V92" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W92" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X92" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W92" s="17" t="n"/>
+      <c r="X92" s="15" t="n"/>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="13" t="n">
@@ -9140,29 +8360,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T94" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U94" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T94" s="15" t="n"/>
+      <c r="U94" s="17" t="n"/>
       <c r="V94" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X94" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W94" s="17" t="n"/>
+      <c r="X94" s="15" t="n"/>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="13" t="n">
@@ -9236,16 +8440,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T95" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U95" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T95" s="15" t="n"/>
+      <c r="U95" s="17" t="n"/>
       <c r="V95" s="18" t="n">
         <v>2</v>
       </c>
@@ -9254,11 +8450,7 @@
           <t>North America 100%; Asia 0%</t>
         </is>
       </c>
-      <c r="X95" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X95" s="15" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -9340,29 +8532,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T96" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U96" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T96" s="15" t="n"/>
+      <c r="U96" s="17" t="n"/>
       <c r="V96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X96" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W96" s="17" t="n"/>
+      <c r="X96" s="15" t="n"/>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="13" t="n">
@@ -9481,11 +8657,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E98" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E98" s="17" t="n"/>
       <c r="F98" s="18" t="n">
         <v>3800670000.000001</v>
       </c>
@@ -9540,29 +8712,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T98" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U98" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T98" s="15" t="n"/>
+      <c r="U98" s="17" t="n"/>
       <c r="V98" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X98" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W98" s="17" t="n"/>
+      <c r="X98" s="15" t="n"/>
     </row>
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="13" t="n">
@@ -9651,11 +8807,7 @@
       <c r="V99" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W99" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W99" s="17" t="n"/>
       <c r="X99" s="15" t="inlineStr">
         <is>
           <t>Core Banking -1%</t>
@@ -9734,16 +8886,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T100" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U100" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T100" s="15" t="n"/>
+      <c r="U100" s="17" t="n"/>
       <c r="V100" s="18" t="n">
         <v>2</v>
       </c>
@@ -9752,11 +8896,7 @@
           <t>US 58%; Non Us 42%</t>
         </is>
       </c>
-      <c r="X100" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X100" s="15" t="n"/>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="13" t="n">
@@ -9839,11 +8979,7 @@
       <c r="V101" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W101" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W101" s="17" t="n"/>
       <c r="X101" s="15" t="inlineStr">
         <is>
           <t>Pandora And Off Plat -0%</t>
@@ -9933,11 +9069,7 @@
       <c r="V102" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W102" s="17" t="n"/>
       <c r="X102" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -10020,29 +9152,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T103" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U103" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T103" s="15" t="n"/>
+      <c r="U103" s="17" t="n"/>
       <c r="V103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W103" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X103" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W103" s="17" t="n"/>
+      <c r="X103" s="15" t="n"/>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="13" t="n">
@@ -10122,29 +9238,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T104" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U104" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T104" s="15" t="n"/>
+      <c r="U104" s="17" t="n"/>
       <c r="V104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X104" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W104" s="17" t="n"/>
+      <c r="X104" s="15" t="n"/>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="13" t="n">
@@ -10238,11 +9338,7 @@
           <t>North America 89%; Asia Pacific 9%; Europe 3%</t>
         </is>
       </c>
-      <c r="X105" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X105" s="15" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="13" t="n">
@@ -10329,11 +9425,7 @@
       <c r="V106" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W106" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W106" s="17" t="n"/>
       <c r="X106" s="15" t="inlineStr">
         <is>
           <t>Enact +2%</t>
@@ -10421,11 +9513,7 @@
       <c r="V107" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W107" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W107" s="17" t="n"/>
       <c r="X107" s="15" t="inlineStr">
         <is>
           <t>Institutional Produc +22%</t>
@@ -10451,11 +9539,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E108" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E108" s="17" t="n"/>
       <c r="F108" s="18" t="n">
         <v>1620210438</v>
       </c>
@@ -10600,16 +9684,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T109" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U109" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T109" s="15" t="n"/>
+      <c r="U109" s="17" t="n"/>
       <c r="V109" s="18" t="n">
         <v>2</v>
       </c>
@@ -10618,11 +9694,7 @@
           <t>US 100%; Non Us 0%</t>
         </is>
       </c>
-      <c r="X109" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X109" s="15" t="n"/>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="13" t="n">
@@ -10797,11 +9869,7 @@
       <c r="V111" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W111" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W111" s="17" t="n"/>
       <c r="X111" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments  +1%</t>
@@ -10882,16 +9950,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T112" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U112" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T112" s="15" t="n"/>
+      <c r="U112" s="17" t="n"/>
       <c r="V112" s="18" t="n">
         <v>1</v>
       </c>
@@ -10900,11 +9960,7 @@
           <t>Non Us 100%</t>
         </is>
       </c>
-      <c r="X112" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X112" s="15" t="n"/>
     </row>
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="13" t="n">
@@ -10978,16 +10034,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T113" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U113" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T113" s="15" t="n"/>
+      <c r="U113" s="17" t="n"/>
       <c r="V113" s="18" t="n">
         <v>2</v>
       </c>
@@ -10996,11 +10044,7 @@
           <t>US 99%; Non Us 1%</t>
         </is>
       </c>
-      <c r="X113" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X113" s="15" t="n"/>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="13" t="n">
@@ -11021,11 +10065,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E114" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E114" s="17" t="n"/>
       <c r="F114" s="18" t="n">
         <v>12285029</v>
       </c>
@@ -11076,16 +10116,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T114" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U114" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T114" s="15" t="n"/>
+      <c r="U114" s="17" t="n"/>
       <c r="V114" s="18" t="n">
         <v>5</v>
       </c>
@@ -11094,11 +10126,7 @@
           <t>US 96%; SV 3%; AR 0%</t>
         </is>
       </c>
-      <c r="X114" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X114" s="15" t="n"/>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n">
@@ -11180,29 +10208,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T115" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U115" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T115" s="15" t="n"/>
+      <c r="U115" s="17" t="n"/>
       <c r="V115" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W115" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X115" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W115" s="17" t="n"/>
+      <c r="X115" s="15" t="n"/>
     </row>
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="13" t="n">
@@ -11291,11 +10303,7 @@
       <c r="V116" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W116" s="17" t="n"/>
       <c r="X116" s="15" t="inlineStr">
         <is>
           <t>Real Estate One +10%</t>
@@ -11378,29 +10386,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T117" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U117" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T117" s="15" t="n"/>
+      <c r="U117" s="17" t="n"/>
       <c r="V117" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W117" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X117" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W117" s="17" t="n"/>
+      <c r="X117" s="15" t="n"/>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="13" t="n">
@@ -11478,29 +10470,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T118" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U118" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T118" s="15" t="n"/>
+      <c r="U118" s="17" t="n"/>
       <c r="V118" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W118" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X118" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W118" s="17" t="n"/>
+      <c r="X118" s="15" t="n"/>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="13" t="n">
@@ -11585,11 +10561,7 @@
       <c r="V119" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W119" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W119" s="17" t="n"/>
       <c r="X119" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments +15%</t>
@@ -11768,29 +10740,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T121" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U121" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T121" s="15" t="n"/>
+      <c r="U121" s="17" t="n"/>
       <c r="V121" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W121" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X121" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W121" s="17" t="n"/>
+      <c r="X121" s="15" t="n"/>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="13" t="n">
@@ -11870,29 +10826,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T122" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U122" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T122" s="15" t="n"/>
+      <c r="U122" s="17" t="n"/>
       <c r="V122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W122" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X122" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W122" s="17" t="n"/>
+      <c r="X122" s="15" t="n"/>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="13" t="n">
@@ -11968,29 +10908,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T123" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U123" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T123" s="15" t="n"/>
+      <c r="U123" s="17" t="n"/>
       <c r="V123" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W123" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X123" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W123" s="17" t="n"/>
+      <c r="X123" s="15" t="n"/>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="13" t="n">
@@ -12068,29 +10992,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T124" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U124" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T124" s="15" t="n"/>
+      <c r="U124" s="17" t="n"/>
       <c r="V124" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W124" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X124" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W124" s="17" t="n"/>
+      <c r="X124" s="15" t="n"/>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="13" t="n">
@@ -12166,16 +11074,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T125" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U125" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T125" s="15" t="n"/>
+      <c r="U125" s="17" t="n"/>
       <c r="V125" s="18" t="n">
         <v>4</v>
       </c>
@@ -12184,11 +11084,7 @@
           <t>US 71%; GB 12%; Other International 11%</t>
         </is>
       </c>
-      <c r="X125" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X125" s="15" t="n"/>
     </row>
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="13" t="n">
@@ -12362,29 +11258,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T127" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U127" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T127" s="15" t="n"/>
+      <c r="U127" s="17" t="n"/>
       <c r="V127" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W127" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X127" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W127" s="17" t="n"/>
+      <c r="X127" s="15" t="n"/>
     </row>
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="13" t="n">
@@ -12467,11 +11347,7 @@
       <c r="V128" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W128" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W128" s="17" t="n"/>
       <c r="X128" s="15" t="inlineStr">
         <is>
           <t>Optavia -36%</t>
@@ -12681,11 +11557,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E131" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E131" s="17" t="n"/>
       <c r="F131" s="18" t="n">
         <v>2302047000</v>
       </c>
@@ -12743,11 +11615,7 @@
       <c r="V131" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W131" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W131" s="17" t="n"/>
       <c r="X131" s="15" t="inlineStr">
         <is>
           <t>Array +58%</t>
@@ -12826,29 +11694,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T132" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U132" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T132" s="15" t="n"/>
+      <c r="U132" s="17" t="n"/>
       <c r="V132" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W132" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X132" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W132" s="17" t="n"/>
+      <c r="X132" s="15" t="n"/>
     </row>
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="13" t="n">
@@ -12924,29 +11776,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T133" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U133" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T133" s="15" t="n"/>
+      <c r="U133" s="17" t="n"/>
       <c r="V133" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W133" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X133" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W133" s="17" t="n"/>
+      <c r="X133" s="15" t="n"/>
     </row>
     <row r="134" ht="16" customHeight="1">
       <c r="A134" s="13" t="n">
@@ -13022,29 +11858,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T134" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U134" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T134" s="15" t="n"/>
+      <c r="U134" s="17" t="n"/>
       <c r="V134" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W134" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X134" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W134" s="17" t="n"/>
+      <c r="X134" s="15" t="n"/>
     </row>
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="13" t="n">
@@ -13133,11 +11953,7 @@
       <c r="V135" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W135" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W135" s="17" t="n"/>
       <c r="X135" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -13323,11 +12139,7 @@
       <c r="V137" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W137" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W137" s="17" t="n"/>
       <c r="X137" s="15" t="inlineStr">
         <is>
           <t>Reportable +4%</t>
@@ -13414,29 +12226,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T138" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U138" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T138" s="15" t="n"/>
+      <c r="U138" s="17" t="n"/>
       <c r="V138" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W138" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X138" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W138" s="17" t="n"/>
+      <c r="X138" s="15" t="n"/>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="13" t="n">
@@ -13512,29 +12308,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T139" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U139" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T139" s="15" t="n"/>
+      <c r="U139" s="17" t="n"/>
       <c r="V139" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W139" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X139" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W139" s="17" t="n"/>
+      <c r="X139" s="15" t="n"/>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="13" t="n">
@@ -13806,29 +12586,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T142" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U142" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T142" s="15" t="n"/>
+      <c r="U142" s="17" t="n"/>
       <c r="V142" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W142" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X142" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W142" s="17" t="n"/>
+      <c r="X142" s="15" t="n"/>
     </row>
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="13" t="n">
@@ -14000,29 +12764,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T144" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U144" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T144" s="15" t="n"/>
+      <c r="U144" s="17" t="n"/>
       <c r="V144" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W144" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X144" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W144" s="17" t="n"/>
+      <c r="X144" s="15" t="n"/>
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="13" t="n">
@@ -14100,29 +12848,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T145" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U145" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T145" s="15" t="n"/>
+      <c r="U145" s="17" t="n"/>
       <c r="V145" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W145" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X145" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W145" s="17" t="n"/>
+      <c r="X145" s="15" t="n"/>
     </row>
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="13" t="n">
@@ -14215,11 +12947,7 @@
       <c r="V146" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W146" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W146" s="17" t="n"/>
       <c r="X146" s="15" t="inlineStr">
         <is>
           <t>Reportable -100%</t>
@@ -14315,11 +13043,7 @@
       <c r="V147" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W147" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W147" s="17" t="n"/>
       <c r="X147" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +8%</t>
@@ -14402,29 +13126,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T148" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U148" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T148" s="15" t="n"/>
+      <c r="U148" s="17" t="n"/>
       <c r="V148" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W148" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X148" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W148" s="17" t="n"/>
+      <c r="X148" s="15" t="n"/>
     </row>
     <row r="149" ht="16" customHeight="1">
       <c r="A149" s="13" t="n">
@@ -14594,29 +13302,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T150" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U150" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T150" s="15" t="n"/>
+      <c r="U150" s="17" t="n"/>
       <c r="V150" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W150" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X150" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W150" s="17" t="n"/>
+      <c r="X150" s="15" t="n"/>
     </row>
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="13" t="n">
@@ -14794,16 +13486,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T152" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U152" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T152" s="15" t="n"/>
+      <c r="U152" s="17" t="n"/>
       <c r="V152" s="18" t="n">
         <v>4</v>
       </c>
@@ -14812,11 +13496,7 @@
           <t>US 65%; EMEA 28%; Asia Pacific 6%</t>
         </is>
       </c>
-      <c r="X152" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X152" s="15" t="n"/>
     </row>
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="13" t="n">
@@ -14894,29 +13574,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T153" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U153" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T153" s="15" t="n"/>
+      <c r="U153" s="17" t="n"/>
       <c r="V153" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W153" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X153" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W153" s="17" t="n"/>
+      <c r="X153" s="15" t="n"/>
     </row>
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="13" t="n">
@@ -14988,29 +13652,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T154" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U154" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T154" s="15" t="n"/>
+      <c r="U154" s="17" t="n"/>
       <c r="V154" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W154" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X154" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W154" s="17" t="n"/>
+      <c r="X154" s="15" t="n"/>
     </row>
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="13" t="n">
@@ -15088,29 +13736,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T155" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U155" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T155" s="15" t="n"/>
+      <c r="U155" s="17" t="n"/>
       <c r="V155" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W155" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X155" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W155" s="17" t="n"/>
+      <c r="X155" s="15" t="n"/>
     </row>
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="13" t="n">
@@ -15195,11 +13827,7 @@
       <c r="V156" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W156" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W156" s="17" t="n"/>
       <c r="X156" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -15282,29 +13910,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T157" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U157" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T157" s="15" t="n"/>
+      <c r="U157" s="17" t="n"/>
       <c r="V157" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W157" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X157" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W157" s="17" t="n"/>
+      <c r="X157" s="15" t="n"/>
     </row>
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="13" t="n">
@@ -15380,16 +13992,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T158" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U158" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T158" s="15" t="n"/>
+      <c r="U158" s="17" t="n"/>
       <c r="V158" s="18" t="n">
         <v>9</v>
       </c>
@@ -15398,11 +14002,7 @@
           <t>Europe 26%; Americas 21%; US 20%</t>
         </is>
       </c>
-      <c r="X158" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X158" s="15" t="n"/>
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="13" t="n">
@@ -15480,29 +14080,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T159" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U159" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T159" s="15" t="n"/>
+      <c r="U159" s="17" t="n"/>
       <c r="V159" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W159" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X159" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W159" s="17" t="n"/>
+      <c r="X159" s="15" t="n"/>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="13" t="n">
@@ -15589,11 +14173,7 @@
       <c r="V160" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W160" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W160" s="17" t="n"/>
       <c r="X160" s="15" t="inlineStr">
         <is>
           <t>Hawaii Energy Connec +30%</t>
@@ -15672,29 +14252,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T161" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U161" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T161" s="15" t="n"/>
+      <c r="U161" s="17" t="n"/>
       <c r="V161" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W161" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X161" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W161" s="17" t="n"/>
+      <c r="X161" s="15" t="n"/>
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="13" t="n">
@@ -15772,29 +14336,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T162" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U162" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T162" s="15" t="n"/>
+      <c r="U162" s="17" t="n"/>
       <c r="V162" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W162" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X162" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W162" s="17" t="n"/>
+      <c r="X162" s="15" t="n"/>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="13" t="n">
@@ -15872,29 +14420,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T163" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U163" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T163" s="15" t="n"/>
+      <c r="U163" s="17" t="n"/>
       <c r="V163" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W163" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X163" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W163" s="17" t="n"/>
+      <c r="X163" s="15" t="n"/>
     </row>
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="13" t="n">
@@ -15974,29 +14506,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T164" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U164" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T164" s="15" t="n"/>
+      <c r="U164" s="17" t="n"/>
       <c r="V164" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W164" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X164" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W164" s="17" t="n"/>
+      <c r="X164" s="15" t="n"/>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="13" t="n">
@@ -16074,29 +14590,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T165" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U165" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T165" s="15" t="n"/>
+      <c r="U165" s="17" t="n"/>
       <c r="V165" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W165" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X165" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W165" s="17" t="n"/>
+      <c r="X165" s="15" t="n"/>
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="13" t="n">
@@ -16176,29 +14676,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T166" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U166" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T166" s="15" t="n"/>
+      <c r="U166" s="17" t="n"/>
       <c r="V166" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W166" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X166" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W166" s="17" t="n"/>
+      <c r="X166" s="15" t="n"/>
     </row>
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="13" t="n">
@@ -16280,29 +14764,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T167" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U167" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T167" s="15" t="n"/>
+      <c r="U167" s="17" t="n"/>
       <c r="V167" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W167" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X167" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W167" s="17" t="n"/>
+      <c r="X167" s="15" t="n"/>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="13" t="n">
@@ -16376,16 +14844,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T168" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U168" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T168" s="15" t="n"/>
+      <c r="U168" s="17" t="n"/>
       <c r="V168" s="18" t="n">
         <v>2</v>
       </c>
@@ -16394,11 +14854,7 @@
           <t>North America 78%; EMEA 22%</t>
         </is>
       </c>
-      <c r="X168" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X168" s="15" t="n"/>
     </row>
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="13" t="n">
@@ -16487,11 +14943,7 @@
       <c r="V169" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W169" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W169" s="17" t="n"/>
       <c r="X169" s="15" t="inlineStr">
         <is>
           <t>Consumer Banking +9%</t>
@@ -16666,16 +15118,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T171" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U171" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T171" s="15" t="n"/>
+      <c r="U171" s="17" t="n"/>
       <c r="V171" s="18" t="n">
         <v>2</v>
       </c>
@@ -16684,11 +15128,7 @@
           <t>US 97%; Non Us 3%</t>
         </is>
       </c>
-      <c r="X171" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X171" s="15" t="n"/>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="13" t="n">
@@ -16709,11 +15149,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="E172" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E172" s="17" t="n"/>
       <c r="F172" s="18" t="n">
         <v>40103256</v>
       </c>
@@ -16864,29 +15300,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T173" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U173" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T173" s="15" t="n"/>
+      <c r="U173" s="17" t="n"/>
       <c r="V173" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W173" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X173" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W173" s="17" t="n"/>
+      <c r="X173" s="15" t="n"/>
     </row>
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="13" t="n">
@@ -16969,11 +15389,7 @@
       <c r="V174" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W174" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W174" s="17" t="n"/>
       <c r="X174" s="15" t="inlineStr">
         <is>
           <t>Towers +6%</t>
@@ -17054,16 +15470,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T175" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U175" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T175" s="15" t="n"/>
+      <c r="U175" s="17" t="n"/>
       <c r="V175" s="18" t="n">
         <v>3</v>
       </c>
@@ -17072,11 +15480,7 @@
           <t>US 58%; Europe 32%; Other Than Us And Europe 10%</t>
         </is>
       </c>
-      <c r="X175" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X175" s="15" t="n"/>
     </row>
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="13" t="n">
@@ -17163,11 +15567,7 @@
       <c r="V176" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W176" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W176" s="17" t="n"/>
       <c r="X176" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +4%</t>
@@ -17250,29 +15650,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T177" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U177" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T177" s="15" t="n"/>
+      <c r="U177" s="17" t="n"/>
       <c r="V177" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W177" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X177" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W177" s="17" t="n"/>
+      <c r="X177" s="15" t="n"/>
     </row>
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="13" t="n">
@@ -17348,29 +15732,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T178" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U178" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T178" s="15" t="n"/>
+      <c r="U178" s="17" t="n"/>
       <c r="V178" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W178" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X178" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W178" s="17" t="n"/>
+      <c r="X178" s="15" t="n"/>
     </row>
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="13" t="n">
@@ -17459,16 +15827,8 @@
       <c r="V179" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W179" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X179" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W179" s="17" t="n"/>
+      <c r="X179" s="15" t="n"/>
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="13" t="n">
@@ -17546,16 +15906,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T180" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U180" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T180" s="15" t="n"/>
+      <c r="U180" s="17" t="n"/>
       <c r="V180" s="18" t="n">
         <v>2</v>
       </c>
@@ -17564,11 +15916,7 @@
           <t>Non Us 59%; US 41%</t>
         </is>
       </c>
-      <c r="X180" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X180" s="15" t="n"/>
     </row>
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="13" t="n">
@@ -17646,29 +15994,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T181" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U181" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T181" s="15" t="n"/>
+      <c r="U181" s="17" t="n"/>
       <c r="V181" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W181" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X181" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W181" s="17" t="n"/>
+      <c r="X181" s="15" t="n"/>
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="13" t="n">
@@ -17751,11 +16083,7 @@
       <c r="V182" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W182" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W182" s="17" t="n"/>
       <c r="X182" s="15" t="inlineStr">
         <is>
           <t>University Group +35%</t>
@@ -17834,16 +16162,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T183" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U183" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T183" s="15" t="n"/>
+      <c r="U183" s="17" t="n"/>
       <c r="V183" s="18" t="n">
         <v>2</v>
       </c>
@@ -17852,11 +16172,7 @@
           <t>US 91%; Non Us 9%</t>
         </is>
       </c>
-      <c r="X183" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X183" s="15" t="n"/>
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="13" t="n">
@@ -17947,11 +16263,7 @@
       <c r="V184" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W184" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W184" s="17" t="n"/>
       <c r="X184" s="15" t="inlineStr">
         <is>
           <t>Reportable +14%</t>
@@ -18047,11 +16359,7 @@
       <c r="V185" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W185" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W185" s="17" t="n"/>
       <c r="X185" s="15" t="inlineStr">
         <is>
           <t>The +37%</t>
@@ -18134,29 +16442,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T186" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U186" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T186" s="15" t="n"/>
+      <c r="U186" s="17" t="n"/>
       <c r="V186" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W186" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X186" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W186" s="17" t="n"/>
+      <c r="X186" s="15" t="n"/>
     </row>
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="13" t="n">
@@ -18228,29 +16520,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T187" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U187" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T187" s="15" t="n"/>
+      <c r="U187" s="17" t="n"/>
       <c r="V187" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W187" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X187" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W187" s="17" t="n"/>
+      <c r="X187" s="15" t="n"/>
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="13" t="n">
@@ -18335,11 +16611,7 @@
       <c r="V188" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W188" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W188" s="17" t="n"/>
       <c r="X188" s="15" t="inlineStr">
         <is>
           <t>Banking +15%</t>
@@ -18422,29 +16694,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T189" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U189" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T189" s="15" t="n"/>
+      <c r="U189" s="17" t="n"/>
       <c r="V189" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W189" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X189" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W189" s="17" t="n"/>
+      <c r="X189" s="15" t="n"/>
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="13" t="n">
@@ -18531,11 +16787,7 @@
       <c r="V190" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W190" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W190" s="17" t="n"/>
       <c r="X190" s="15" t="inlineStr">
         <is>
           <t>Reportable -77%</t>
@@ -18620,16 +16872,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T191" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U191" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T191" s="15" t="n"/>
+      <c r="U191" s="17" t="n"/>
       <c r="V191" s="18" t="n">
         <v>4</v>
       </c>
@@ -18638,11 +16882,7 @@
           <t>EMEA 48%; Americas 41%; Asia Pacific 11%</t>
         </is>
       </c>
-      <c r="X191" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X191" s="15" t="n"/>
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="13" t="n">
@@ -18720,29 +16960,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T192" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U192" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T192" s="15" t="n"/>
+      <c r="U192" s="17" t="n"/>
       <c r="V192" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W192" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X192" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W192" s="17" t="n"/>
+      <c r="X192" s="15" t="n"/>
     </row>
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="13" t="n">
@@ -18822,29 +17046,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T193" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U193" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T193" s="15" t="n"/>
+      <c r="U193" s="17" t="n"/>
       <c r="V193" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W193" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X193" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W193" s="17" t="n"/>
+      <c r="X193" s="15" t="n"/>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="13" t="n">
@@ -19008,29 +17216,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T195" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U195" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T195" s="15" t="n"/>
+      <c r="U195" s="17" t="n"/>
       <c r="V195" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W195" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X195" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W195" s="17" t="n"/>
+      <c r="X195" s="15" t="n"/>
     </row>
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="13" t="n">
@@ -19051,11 +17243,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E196" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E196" s="17" t="n"/>
       <c r="F196" s="18" t="n">
         <v>8050602560</v>
       </c>
@@ -19113,11 +17301,7 @@
       <c r="V196" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W196" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W196" s="17" t="n"/>
       <c r="X196" s="15" t="inlineStr">
         <is>
           <t>PC Business Insuranc +10%</t>
@@ -19202,29 +17386,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T197" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U197" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T197" s="15" t="n"/>
+      <c r="U197" s="17" t="n"/>
       <c r="V197" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W197" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X197" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W197" s="17" t="n"/>
+      <c r="X197" s="15" t="n"/>
     </row>
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="13" t="n">
@@ -19307,11 +17475,7 @@
       <c r="V198" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W198" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W198" s="17" t="n"/>
       <c r="X198" s="15" t="inlineStr">
         <is>
           <t>Operating +23%</t>
@@ -19403,11 +17567,7 @@
       <c r="V199" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W199" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W199" s="17" t="n"/>
       <c r="X199" s="15" t="inlineStr">
         <is>
           <t>Mid Con Barnett Shal +180%</t>
@@ -19586,29 +17746,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T201" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U201" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T201" s="15" t="n"/>
+      <c r="U201" s="17" t="n"/>
       <c r="V201" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W201" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X201" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W201" s="17" t="n"/>
+      <c r="X201" s="15" t="n"/>
     </row>
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="13" t="n">
@@ -19874,29 +18018,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T204" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U204" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T204" s="15" t="n"/>
+      <c r="U204" s="17" t="n"/>
       <c r="V204" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W204" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X204" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W204" s="17" t="n"/>
+      <c r="X204" s="15" t="n"/>
     </row>
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="13" t="n">
@@ -20158,29 +18286,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T207" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U207" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T207" s="15" t="n"/>
+      <c r="U207" s="17" t="n"/>
       <c r="V207" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W207" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X207" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W207" s="17" t="n"/>
+      <c r="X207" s="15" t="n"/>
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="13" t="n">
@@ -20367,11 +18479,7 @@
       <c r="V209" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W209" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W209" s="17" t="n"/>
       <c r="X209" s="15" t="inlineStr">
         <is>
           <t>Reportable -88%</t>
@@ -20467,11 +18575,7 @@
       <c r="V210" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W210" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W210" s="17" t="n"/>
       <c r="X210" s="15" t="inlineStr">
         <is>
           <t>Operating +370%</t>
@@ -20550,16 +18654,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T211" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U211" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T211" s="15" t="n"/>
+      <c r="U211" s="17" t="n"/>
       <c r="V211" s="18" t="n">
         <v>2</v>
       </c>
@@ -20568,11 +18664,7 @@
           <t>US 96%; Non Us 4%</t>
         </is>
       </c>
-      <c r="X211" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X211" s="15" t="n"/>
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="13" t="n">
@@ -20646,29 +18738,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T212" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U212" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T212" s="15" t="n"/>
+      <c r="U212" s="17" t="n"/>
       <c r="V212" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W212" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X212" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W212" s="17" t="n"/>
+      <c r="X212" s="15" t="n"/>
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="13" t="n">
@@ -20757,11 +18833,7 @@
       <c r="V213" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W213" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W213" s="17" t="n"/>
       <c r="X213" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +15%</t>
@@ -20787,11 +18859,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E214" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E214" s="17" t="n"/>
       <c r="F214" s="18" t="n">
         <v>2411290575.93</v>
       </c>
@@ -20844,29 +18912,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T214" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U214" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T214" s="15" t="n"/>
+      <c r="U214" s="17" t="n"/>
       <c r="V214" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W214" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X214" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W214" s="17" t="n"/>
+      <c r="X214" s="15" t="n"/>
     </row>
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="13" t="n">
@@ -20949,11 +19001,7 @@
       <c r="V215" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W215" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W215" s="17" t="n"/>
       <c r="X215" s="15" t="inlineStr">
         <is>
           <t>Southeast -3%</t>
@@ -21036,16 +19084,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T216" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U216" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T216" s="15" t="n"/>
+      <c r="U216" s="17" t="n"/>
       <c r="V216" s="18" t="n">
         <v>3</v>
       </c>
@@ -21054,11 +19094,7 @@
           <t>US 86%; Europe 8%; Rest Of The World Except US And Europe 6%</t>
         </is>
       </c>
-      <c r="X216" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X216" s="15" t="n"/>
     </row>
     <row r="217" ht="16" customHeight="1">
       <c r="A217" s="13" t="n">
@@ -21230,29 +19266,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T218" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U218" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T218" s="15" t="n"/>
+      <c r="U218" s="17" t="n"/>
       <c r="V218" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W218" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X218" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W218" s="17" t="n"/>
+      <c r="X218" s="15" t="n"/>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="13" t="n">
@@ -21332,16 +19352,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T219" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U219" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T219" s="15" t="n"/>
+      <c r="U219" s="17" t="n"/>
       <c r="V219" s="18" t="n">
         <v>1</v>
       </c>
@@ -21350,11 +19362,7 @@
           <t>Non Us 100%</t>
         </is>
       </c>
-      <c r="X219" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X219" s="15" t="n"/>
     </row>
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="13" t="n">
@@ -21524,29 +19532,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T221" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U221" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T221" s="15" t="n"/>
+      <c r="U221" s="17" t="n"/>
       <c r="V221" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W221" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X221" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W221" s="17" t="n"/>
+      <c r="X221" s="15" t="n"/>
     </row>
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="13" t="n">
@@ -21620,29 +19612,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T222" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U222" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T222" s="15" t="n"/>
+      <c r="U222" s="17" t="n"/>
       <c r="V222" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W222" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X222" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W222" s="17" t="n"/>
+      <c r="X222" s="15" t="n"/>
     </row>
     <row r="223" ht="16" customHeight="1">
       <c r="A223" s="13" t="n">
@@ -21727,11 +19703,7 @@
       <c r="V223" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W223" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W223" s="17" t="n"/>
       <c r="X223" s="15" t="inlineStr">
         <is>
           <t>Reportable +23%</t>
@@ -21821,11 +19793,7 @@
       <c r="V224" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W224" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W224" s="17" t="n"/>
       <c r="X224" s="15" t="inlineStr">
         <is>
           <t>Mastercraft -8%</t>
@@ -21908,29 +19876,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T225" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U225" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T225" s="15" t="n"/>
+      <c r="U225" s="17" t="n"/>
       <c r="V225" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W225" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X225" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W225" s="17" t="n"/>
+      <c r="X225" s="15" t="n"/>
     </row>
     <row r="226" ht="16" customHeight="1">
       <c r="A226" s="13" t="n">
@@ -22004,29 +19956,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T226" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U226" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T226" s="15" t="n"/>
+      <c r="U226" s="17" t="n"/>
       <c r="V226" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W226" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X226" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W226" s="17" t="n"/>
+      <c r="X226" s="15" t="n"/>
     </row>
     <row r="227" ht="16" customHeight="1">
       <c r="A227" s="13" t="n">
@@ -22111,11 +20047,7 @@
       <c r="V227" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W227" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W227" s="17" t="n"/>
       <c r="X227" s="15" t="inlineStr">
         <is>
           <t>Timber +327%</t>
@@ -22292,16 +20224,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T229" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U229" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T229" s="15" t="n"/>
+      <c r="U229" s="17" t="n"/>
       <c r="V229" s="18" t="n">
         <v>2</v>
       </c>
@@ -22310,11 +20234,7 @@
           <t>CA 54%; US 46%</t>
         </is>
       </c>
-      <c r="X229" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X229" s="15" t="n"/>
     </row>
     <row r="230" ht="16" customHeight="1">
       <c r="A230" s="13" t="n">
@@ -22390,29 +20310,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T230" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U230" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T230" s="15" t="n"/>
+      <c r="U230" s="17" t="n"/>
       <c r="V230" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W230" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X230" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W230" s="17" t="n"/>
+      <c r="X230" s="15" t="n"/>
     </row>
     <row r="231" ht="16" customHeight="1">
       <c r="A231" s="13" t="n">
@@ -22580,29 +20484,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T232" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U232" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T232" s="15" t="n"/>
+      <c r="U232" s="17" t="n"/>
       <c r="V232" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W232" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X232" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W232" s="17" t="n"/>
+      <c r="X232" s="15" t="n"/>
     </row>
     <row r="233" ht="16" customHeight="1">
       <c r="A233" s="13" t="n">
@@ -22680,16 +20568,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T233" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U233" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T233" s="15" t="n"/>
+      <c r="U233" s="17" t="n"/>
       <c r="V233" s="18" t="n">
         <v>4</v>
       </c>
@@ -22698,11 +20578,7 @@
           <t>North America 42%; US 41%; Rest Of World 12%</t>
         </is>
       </c>
-      <c r="X233" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X233" s="15" t="n"/>
     </row>
     <row r="234" ht="16" customHeight="1">
       <c r="A234" s="13" t="n">
@@ -22887,11 +20763,7 @@
       <c r="V235" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W235" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W235" s="17" t="n"/>
       <c r="X235" s="15" t="inlineStr">
         <is>
           <t>Single Reportable -99%</t>
@@ -23068,29 +20940,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T237" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U237" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T237" s="15" t="n"/>
+      <c r="U237" s="17" t="n"/>
       <c r="V237" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W237" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X237" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W237" s="17" t="n"/>
+      <c r="X237" s="15" t="n"/>
     </row>
     <row r="238" ht="16" customHeight="1">
       <c r="A238" s="13" t="n">
@@ -23168,16 +21024,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T238" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U238" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T238" s="15" t="n"/>
+      <c r="U238" s="17" t="n"/>
       <c r="V238" s="18" t="n">
         <v>4</v>
       </c>
@@ -23186,11 +21034,7 @@
           <t>US 82%; Africa 12%; Europe 3%</t>
         </is>
       </c>
-      <c r="X238" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X238" s="15" t="n"/>
     </row>
     <row r="239" ht="16" customHeight="1">
       <c r="A239" s="13" t="n">
@@ -23356,16 +21200,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T240" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U240" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T240" s="15" t="n"/>
+      <c r="U240" s="17" t="n"/>
       <c r="V240" s="18" t="n">
         <v>5</v>
       </c>
@@ -23374,11 +21210,7 @@
           <t>US 61%; Non Us 20%; Europe 13%</t>
         </is>
       </c>
-      <c r="X240" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X240" s="15" t="n"/>
     </row>
     <row r="241" ht="16" customHeight="1">
       <c r="A241" s="13" t="n">
@@ -23649,11 +21481,7 @@
       <c r="V243" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W243" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W243" s="17" t="n"/>
       <c r="X243" s="15" t="inlineStr">
         <is>
           <t>Retirement And Incom +23%</t>
@@ -23734,29 +21562,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T244" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U244" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T244" s="15" t="n"/>
+      <c r="U244" s="17" t="n"/>
       <c r="V244" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W244" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X244" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W244" s="17" t="n"/>
+      <c r="X244" s="15" t="n"/>
     </row>
     <row r="245" ht="16" customHeight="1">
       <c r="A245" s="13" t="n">
@@ -23841,11 +21653,7 @@
       <c r="V245" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W245" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W245" s="17" t="n"/>
       <c r="X245" s="15" t="inlineStr">
         <is>
           <t>Reportable +25%</t>
@@ -23939,16 +21747,8 @@
       <c r="V246" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W246" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X246" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W246" s="17" t="n"/>
+      <c r="X246" s="15" t="n"/>
     </row>
     <row r="247" ht="16" customHeight="1">
       <c r="A247" s="13" t="n">
@@ -24024,16 +21824,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T247" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U247" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T247" s="15" t="n"/>
+      <c r="U247" s="17" t="n"/>
       <c r="V247" s="18" t="n">
         <v>5</v>
       </c>
@@ -24042,11 +21834,7 @@
           <t>US 92%; Non Us 6%; CA 1%</t>
         </is>
       </c>
-      <c r="X247" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X247" s="15" t="n"/>
     </row>
     <row r="248" ht="16" customHeight="1">
       <c r="A248" s="13" t="n">
@@ -24221,11 +22009,7 @@
       <c r="V249" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W249" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W249" s="17" t="n"/>
       <c r="X249" s="15" t="inlineStr">
         <is>
           <t>Restaurant Food Sale +224%</t>
@@ -24308,29 +22092,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T250" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U250" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T250" s="15" t="n"/>
+      <c r="U250" s="17" t="n"/>
       <c r="V250" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W250" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X250" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W250" s="17" t="n"/>
+      <c r="X250" s="15" t="n"/>
     </row>
     <row r="251" ht="16" customHeight="1">
       <c r="A251" s="13" t="n">
@@ -24415,11 +22183,7 @@
       <c r="V251" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W251" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W251" s="17" t="n"/>
       <c r="X251" s="15" t="inlineStr">
         <is>
           <t>Reportable +17%</t>
@@ -24498,29 +22262,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T252" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U252" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T252" s="15" t="n"/>
+      <c r="U252" s="17" t="n"/>
       <c r="V252" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W252" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X252" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W252" s="17" t="n"/>
+      <c r="X252" s="15" t="n"/>
     </row>
     <row r="253" ht="16" customHeight="1">
       <c r="A253" s="13" t="n">
@@ -24609,11 +22357,7 @@
       <c r="V253" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W253" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W253" s="17" t="n"/>
       <c r="X253" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +16%</t>
@@ -24696,29 +22440,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T254" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U254" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T254" s="15" t="n"/>
+      <c r="U254" s="17" t="n"/>
       <c r="V254" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W254" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X254" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W254" s="17" t="n"/>
+      <c r="X254" s="15" t="n"/>
     </row>
     <row r="255" ht="16" customHeight="1">
       <c r="A255" s="13" t="n">
@@ -24796,29 +22524,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T255" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U255" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T255" s="15" t="n"/>
+      <c r="U255" s="17" t="n"/>
       <c r="V255" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W255" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X255" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W255" s="17" t="n"/>
+      <c r="X255" s="15" t="n"/>
     </row>
     <row r="256" ht="16" customHeight="1">
       <c r="A256" s="13" t="n">
@@ -24907,11 +22619,7 @@
       <c r="V256" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W256" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W256" s="17" t="n"/>
       <c r="X256" s="15" t="inlineStr">
         <is>
           <t>Storage Solutions +8%</t>
@@ -24996,29 +22704,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T257" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U257" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T257" s="15" t="n"/>
+      <c r="U257" s="17" t="n"/>
       <c r="V257" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W257" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X257" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W257" s="17" t="n"/>
+      <c r="X257" s="15" t="n"/>
     </row>
     <row r="258" ht="16" customHeight="1">
       <c r="A258" s="13" t="n">
@@ -25092,29 +22784,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T258" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U258" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T258" s="15" t="n"/>
+      <c r="U258" s="17" t="n"/>
       <c r="V258" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W258" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X258" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W258" s="17" t="n"/>
+      <c r="X258" s="15" t="n"/>
     </row>
     <row r="259" ht="16" customHeight="1">
       <c r="A259" s="13" t="n">
@@ -25192,29 +22868,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T259" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U259" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T259" s="15" t="n"/>
+      <c r="U259" s="17" t="n"/>
       <c r="V259" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W259" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X259" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W259" s="17" t="n"/>
+      <c r="X259" s="15" t="n"/>
     </row>
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="13" t="n">
@@ -25288,16 +22948,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T260" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U260" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T260" s="15" t="n"/>
+      <c r="U260" s="17" t="n"/>
       <c r="V260" s="18" t="n">
         <v>9</v>
       </c>
@@ -25306,11 +22958,7 @@
           <t>Asia Pacific 26%; Europe 22%; CN 19%</t>
         </is>
       </c>
-      <c r="X260" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X260" s="15" t="n"/>
     </row>
     <row r="261" ht="16" customHeight="1">
       <c r="A261" s="13" t="n">
@@ -25482,29 +23130,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T262" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U262" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T262" s="15" t="n"/>
+      <c r="U262" s="17" t="n"/>
       <c r="V262" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W262" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X262" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W262" s="17" t="n"/>
+      <c r="X262" s="15" t="n"/>
     </row>
     <row r="263" ht="16" customHeight="1">
       <c r="A263" s="13" t="n">
@@ -25578,16 +23210,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T263" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U263" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T263" s="15" t="n"/>
+      <c r="U263" s="17" t="n"/>
       <c r="V263" s="18" t="n">
         <v>2</v>
       </c>
@@ -25596,11 +23220,7 @@
           <t>US 99%; Non Us 1%</t>
         </is>
       </c>
-      <c r="X263" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X263" s="15" t="n"/>
     </row>
     <row r="264" ht="16" customHeight="1">
       <c r="A264" s="13" t="n">
@@ -25672,29 +23292,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T264" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U264" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T264" s="15" t="n"/>
+      <c r="U264" s="17" t="n"/>
       <c r="V264" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W264" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X264" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W264" s="17" t="n"/>
+      <c r="X264" s="15" t="n"/>
     </row>
     <row r="265" ht="16" customHeight="1">
       <c r="A265" s="13" t="n">
@@ -25864,29 +23468,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T266" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U266" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T266" s="15" t="n"/>
+      <c r="U266" s="17" t="n"/>
       <c r="V266" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W266" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X266" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W266" s="17" t="n"/>
+      <c r="X266" s="15" t="n"/>
     </row>
     <row r="267" ht="16" customHeight="1">
       <c r="A267" s="13" t="n">
@@ -25964,29 +23552,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T267" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U267" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T267" s="15" t="n"/>
+      <c r="U267" s="17" t="n"/>
       <c r="V267" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W267" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X267" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W267" s="17" t="n"/>
+      <c r="X267" s="15" t="n"/>
     </row>
     <row r="268" ht="16" customHeight="1">
       <c r="A268" s="13" t="n">
@@ -26069,11 +23641,7 @@
       <c r="V268" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W268" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W268" s="17" t="n"/>
       <c r="X268" s="15" t="inlineStr">
         <is>
           <t>Accessories +2%</t>
@@ -26197,11 +23765,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E270" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E270" s="17" t="n"/>
       <c r="F270" s="18" t="n">
         <v>190471602.2</v>
       </c>
@@ -26256,29 +23820,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T270" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U270" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T270" s="15" t="n"/>
+      <c r="U270" s="17" t="n"/>
       <c r="V270" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W270" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X270" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W270" s="17" t="n"/>
+      <c r="X270" s="15" t="n"/>
     </row>
     <row r="271" ht="16" customHeight="1">
       <c r="A271" s="13" t="n">
@@ -26299,11 +23847,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E271" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E271" s="17" t="n"/>
       <c r="F271" s="18" t="n">
         <v>492385408</v>
       </c>
@@ -26354,29 +23898,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T271" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U271" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T271" s="15" t="n"/>
+      <c r="U271" s="17" t="n"/>
       <c r="V271" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W271" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X271" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W271" s="17" t="n"/>
+      <c r="X271" s="15" t="n"/>
     </row>
     <row r="272" ht="16" customHeight="1">
       <c r="A272" s="13" t="n">
@@ -26461,11 +23989,7 @@
       <c r="V272" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W272" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W272" s="17" t="n"/>
       <c r="X272" s="15" t="inlineStr">
         <is>
           <t>Single Reportable +24%</t>
@@ -26553,11 +24077,7 @@
       <c r="V273" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W273" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W273" s="17" t="n"/>
       <c r="X273" s="15" t="inlineStr">
         <is>
           <t>Good Times +2%</t>
@@ -26640,29 +24160,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T274" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U274" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T274" s="15" t="n"/>
+      <c r="U274" s="17" t="n"/>
       <c r="V274" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W274" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X274" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W274" s="17" t="n"/>
+      <c r="X274" s="15" t="n"/>
     </row>
     <row r="275" ht="16" customHeight="1">
       <c r="A275" s="13" t="n">
@@ -26745,11 +24249,7 @@
       <c r="V275" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W275" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W275" s="17" t="n"/>
       <c r="X275" s="15" t="inlineStr">
         <is>
           <t>Canadian Factory Bui +18%</t>
@@ -26834,29 +24334,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T276" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U276" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T276" s="15" t="n"/>
+      <c r="U276" s="17" t="n"/>
       <c r="V276" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W276" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X276" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W276" s="17" t="n"/>
+      <c r="X276" s="15" t="n"/>
     </row>
     <row r="277" ht="16" customHeight="1">
       <c r="A277" s="13" t="n">
@@ -26877,11 +24361,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E277" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E277" s="17" t="n"/>
       <c r="F277" s="18" t="n">
         <v>23538974</v>
       </c>
@@ -26930,29 +24410,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T277" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U277" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T277" s="15" t="n"/>
+      <c r="U277" s="17" t="n"/>
       <c r="V277" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W277" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X277" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W277" s="17" t="n"/>
+      <c r="X277" s="15" t="n"/>
     </row>
     <row r="278" ht="16" customHeight="1">
       <c r="A278" s="13" t="n">
@@ -27035,11 +24499,7 @@
       <c r="V278" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W278" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W278" s="17" t="n"/>
       <c r="X278" s="15" t="inlineStr">
         <is>
           <t>Specialty Property C +10%</t>
@@ -27133,11 +24593,7 @@
       <c r="V279" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W279" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W279" s="17" t="n"/>
       <c r="X279" s="15" t="inlineStr">
         <is>
           <t>Banking Operations -74%</t>
@@ -27229,11 +24685,7 @@
       <c r="V280" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W280" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W280" s="17" t="n"/>
       <c r="X280" s="15" t="inlineStr">
         <is>
           <t>Insurance Services +47%</t>
@@ -27316,16 +24768,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T281" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U281" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T281" s="15" t="n"/>
+      <c r="U281" s="17" t="n"/>
       <c r="V281" s="18" t="n">
         <v>6</v>
       </c>
@@ -27334,11 +24778,7 @@
           <t>Americas 28%; US 26%; EMEA 26%</t>
         </is>
       </c>
-      <c r="X281" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X281" s="15" t="n"/>
     </row>
     <row r="282" ht="16" customHeight="1">
       <c r="A282" s="13" t="n">
@@ -27525,11 +24965,7 @@
       <c r="V283" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W283" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W283" s="17" t="n"/>
       <c r="X283" s="15" t="inlineStr">
         <is>
           <t>Medicare +62%</t>
@@ -27719,16 +25155,8 @@
       <c r="V285" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W285" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X285" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W285" s="17" t="n"/>
+      <c r="X285" s="15" t="n"/>
     </row>
     <row r="286" ht="16" customHeight="1">
       <c r="A286" s="13" t="n">
@@ -27806,29 +25234,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T286" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U286" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T286" s="15" t="n"/>
+      <c r="U286" s="17" t="n"/>
       <c r="V286" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W286" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X286" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W286" s="17" t="n"/>
+      <c r="X286" s="15" t="n"/>
     </row>
     <row r="287" ht="16" customHeight="1">
       <c r="A287" s="13" t="n">
@@ -27913,11 +25325,7 @@
       <c r="V287" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W287" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W287" s="17" t="n"/>
       <c r="X287" s="15" t="inlineStr">
         <is>
           <t>Environmental Servic +8%</t>
@@ -28002,29 +25410,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T288" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U288" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T288" s="15" t="n"/>
+      <c r="U288" s="17" t="n"/>
       <c r="V288" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W288" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X288" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W288" s="17" t="n"/>
+      <c r="X288" s="15" t="n"/>
     </row>
     <row r="289" ht="16" customHeight="1">
       <c r="A289" s="13" t="n">
@@ -28109,11 +25501,7 @@
       <c r="V289" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W289" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W289" s="17" t="n"/>
       <c r="X289" s="15" t="inlineStr">
         <is>
           <t>Protection Services -74%</t>
@@ -28284,16 +25672,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T291" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U291" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T291" s="15" t="n"/>
+      <c r="U291" s="17" t="n"/>
       <c r="V291" s="18" t="n">
         <v>8</v>
       </c>
@@ -28302,11 +25682,7 @@
           <t>CN 27%; JP 19%; Europe 15%</t>
         </is>
       </c>
-      <c r="X291" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X291" s="15" t="n"/>
     </row>
     <row r="292" ht="16" customHeight="1">
       <c r="A292" s="13" t="n">
@@ -28386,29 +25762,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T292" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U292" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T292" s="15" t="n"/>
+      <c r="U292" s="17" t="n"/>
       <c r="V292" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W292" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X292" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W292" s="17" t="n"/>
+      <c r="X292" s="15" t="n"/>
     </row>
     <row r="293" ht="16" customHeight="1">
       <c r="A293" s="13" t="n">
@@ -28587,16 +25947,8 @@
       <c r="V294" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W294" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X294" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W294" s="17" t="n"/>
+      <c r="X294" s="15" t="n"/>
     </row>
     <row r="295" ht="16" customHeight="1">
       <c r="A295" s="13" t="n">
@@ -28762,16 +26114,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T296" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U296" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T296" s="15" t="n"/>
+      <c r="U296" s="17" t="n"/>
       <c r="V296" s="18" t="n">
         <v>4</v>
       </c>
@@ -28780,11 +26124,7 @@
           <t>Haynesville 40%; Northeast Appalachia 37%; Southwest Appalac</t>
         </is>
       </c>
-      <c r="X296" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X296" s="15" t="n"/>
     </row>
     <row r="297" ht="16" customHeight="1">
       <c r="A297" s="13" t="n">
@@ -28956,16 +26296,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T298" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U298" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T298" s="15" t="n"/>
+      <c r="U298" s="17" t="n"/>
       <c r="V298" s="18" t="n">
         <v>2</v>
       </c>
@@ -28974,11 +26306,7 @@
           <t>US 60%; Non Us 40%</t>
         </is>
       </c>
-      <c r="X298" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X298" s="15" t="n"/>
     </row>
     <row r="299" ht="16" customHeight="1">
       <c r="A299" s="13" t="n">
@@ -29065,11 +26393,7 @@
       <c r="V299" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W299" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W299" s="17" t="n"/>
       <c r="X299" s="15" t="inlineStr">
         <is>
           <t>Reportable +11%</t>
@@ -29165,11 +26489,7 @@
       <c r="V300" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W300" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W300" s="17" t="n"/>
       <c r="X300" s="15" t="inlineStr">
         <is>
           <t>Tutoring -6%</t>
@@ -29252,29 +26572,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T301" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U301" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T301" s="15" t="n"/>
+      <c r="U301" s="17" t="n"/>
       <c r="V301" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W301" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X301" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W301" s="17" t="n"/>
+      <c r="X301" s="15" t="n"/>
     </row>
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="13" t="n">
@@ -29346,29 +26650,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T302" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U302" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T302" s="15" t="n"/>
+      <c r="U302" s="17" t="n"/>
       <c r="V302" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W302" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X302" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W302" s="17" t="n"/>
+      <c r="X302" s="15" t="n"/>
     </row>
     <row r="303" ht="16" customHeight="1">
       <c r="A303" s="13" t="n">
@@ -29641,11 +26929,7 @@
       <c r="V305" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W305" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W305" s="17" t="n"/>
       <c r="X305" s="15" t="inlineStr">
         <is>
           <t>Single Operating -1%</t>
@@ -29733,11 +27017,7 @@
       <c r="V306" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W306" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W306" s="17" t="n"/>
       <c r="X306" s="15" t="inlineStr">
         <is>
           <t>Reportable +7%</t>
@@ -29831,11 +27111,7 @@
       <c r="V307" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W307" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W307" s="17" t="n"/>
       <c r="X307" s="15" t="inlineStr">
         <is>
           <t>Outdoor -4%</t>
@@ -29916,29 +27192,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T308" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U308" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T308" s="15" t="n"/>
+      <c r="U308" s="17" t="n"/>
       <c r="V308" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W308" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X308" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W308" s="17" t="n"/>
+      <c r="X308" s="15" t="n"/>
     </row>
     <row r="309" ht="16" customHeight="1">
       <c r="A309" s="13" t="n">
@@ -30018,29 +27278,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T309" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U309" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T309" s="15" t="n"/>
+      <c r="U309" s="17" t="n"/>
       <c r="V309" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W309" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X309" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W309" s="17" t="n"/>
+      <c r="X309" s="15" t="n"/>
     </row>
     <row r="310" ht="16" customHeight="1">
       <c r="A310" s="13" t="n">
@@ -30116,29 +27360,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T310" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U310" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T310" s="15" t="n"/>
+      <c r="U310" s="17" t="n"/>
       <c r="V310" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W310" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X310" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W310" s="17" t="n"/>
+      <c r="X310" s="15" t="n"/>
     </row>
     <row r="311" ht="16" customHeight="1">
       <c r="A311" s="13" t="n">
@@ -30214,16 +27442,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T311" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U311" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T311" s="15" t="n"/>
+      <c r="U311" s="17" t="n"/>
       <c r="V311" s="18" t="n">
         <v>3</v>
       </c>
@@ -30232,11 +27452,7 @@
           <t>US 64%; Europe 26%; Non US Or Europe 10%</t>
         </is>
       </c>
-      <c r="X311" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X311" s="15" t="n"/>
     </row>
     <row r="312" ht="16" customHeight="1">
       <c r="A312" s="13" t="n">
@@ -30314,29 +27530,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T312" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U312" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T312" s="15" t="n"/>
+      <c r="U312" s="17" t="n"/>
       <c r="V312" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W312" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X312" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W312" s="17" t="n"/>
+      <c r="X312" s="15" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A11:X312"/>
@@ -30354,7 +27554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X72"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -30383,6 +27583,7 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -30416,6 +27617,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -30523,8 +27725,9 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -30951,11 +28154,7 @@
       <c r="V15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W15" s="17" t="n"/>
       <c r="X15" s="15" t="inlineStr">
         <is>
           <t>Annuities +88%</t>
@@ -31267,11 +28466,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E19" s="17" t="n"/>
       <c r="F19" s="18" t="n">
         <v>8050602560</v>
       </c>
@@ -31329,11 +28524,7 @@
       <c r="V19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W19" s="17" t="n"/>
       <c r="X19" s="15" t="inlineStr">
         <is>
           <t>PC Business Insuranc +10%</t>
@@ -31517,11 +28708,7 @@
       <c r="V21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W21" s="17" t="n"/>
       <c r="X21" s="15" t="inlineStr">
         <is>
           <t>Southeast -3%</t>
@@ -31799,11 +28986,7 @@
       <c r="V24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W24" s="17" t="n"/>
       <c r="X24" s="15" t="inlineStr">
         <is>
           <t>Retirement And Incom +23%</t>
@@ -31891,11 +29074,7 @@
       <c r="V25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W25" s="17" t="n"/>
       <c r="X25" s="15" t="inlineStr">
         <is>
           <t>Accessories +2%</t>
@@ -32179,16 +29358,8 @@
       <c r="V28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="X28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W28" s="17" t="n"/>
+      <c r="X28" s="15" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -32369,11 +29540,7 @@
       <c r="V30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W30" s="17" t="n"/>
       <c r="X30" s="15" t="inlineStr">
         <is>
           <t>Service And Retailin +7%</t>
@@ -32465,11 +29632,7 @@
       <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W31" s="17" t="n"/>
       <c r="X31" s="15" t="inlineStr">
         <is>
           <t>ES Lines +20%</t>
@@ -32657,11 +29820,7 @@
       <c r="V33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W33" s="17" t="n"/>
       <c r="X33" s="15" t="inlineStr">
         <is>
           <t>Jefferson Terminal +6%</t>
@@ -33317,11 +30476,7 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W40" s="17" t="n"/>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>Segment Benefits And +3%</t>
@@ -33687,11 +30842,7 @@
       <c r="V44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W44" s="17" t="n"/>
       <c r="X44" s="15" t="inlineStr">
         <is>
           <t>Development +21%</t>
@@ -33781,11 +30932,7 @@
       <c r="V45" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W45" s="17" t="n"/>
       <c r="X45" s="15" t="inlineStr">
         <is>
           <t>Spices And Flavor So -75%</t>
@@ -33873,11 +31020,7 @@
       <c r="V46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W46" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W46" s="17" t="n"/>
       <c r="X46" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +56%</t>
@@ -34441,11 +31584,7 @@
       <c r="V52" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W52" s="17" t="n"/>
       <c r="X52" s="15" t="inlineStr">
         <is>
           <t>Warehouse Lending +17%</t>
@@ -34719,11 +31858,7 @@
       <c r="V55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W55" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W55" s="17" t="n"/>
       <c r="X55" s="15" t="inlineStr">
         <is>
           <t>Healthcare Services +55%</t>
@@ -34817,11 +31952,7 @@
       <c r="V56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W56" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W56" s="17" t="n"/>
       <c r="X56" s="15" t="inlineStr">
         <is>
           <t>Poland +5%</t>
@@ -35097,11 +32228,7 @@
       <c r="V59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W59" s="17" t="n"/>
       <c r="X59" s="15" t="inlineStr">
         <is>
           <t>Orlando FL +11%</t>
@@ -35193,11 +32320,7 @@
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W60" s="17" t="n"/>
       <c r="X60" s="15" t="inlineStr">
         <is>
           <t>Total Operating Segm +10%</t>
@@ -35291,11 +32414,7 @@
       <c r="V61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W61" s="17" t="n"/>
       <c r="X61" s="15" t="inlineStr">
         <is>
           <t>Sulfur Services +26%</t>
@@ -35385,11 +32504,7 @@
       <c r="V62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W62" s="17" t="n"/>
       <c r="X62" s="15" t="inlineStr">
         <is>
           <t>Personal Lines Insur +22%</t>
@@ -35947,11 +33062,7 @@
       <c r="V68" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W68" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W68" s="17" t="n"/>
       <c r="X68" s="15" t="inlineStr">
         <is>
           <t>Corporate And Other +22%</t>
@@ -36039,11 +33150,7 @@
       <c r="V69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
           <t>Southwest -5%</t>
@@ -36161,11 +33268,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E71" s="17" t="n"/>
       <c r="F71" s="18" t="n">
         <v>11270994454.29</v>
       </c>
@@ -36227,11 +33330,7 @@
       <c r="V71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W71" s="17" t="n"/>
       <c r="X71" s="15" t="inlineStr">
         <is>
           <t>Real Assets Group -73%</t>
@@ -36346,7 +33445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X72"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -36375,6 +33474,7 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -36408,6 +33508,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -36515,8 +33616,9 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -36757,11 +33859,7 @@
       <c r="V13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W13" s="17" t="n"/>
       <c r="X13" s="15" t="inlineStr">
         <is>
           <t>Credit Card +37%</t>
@@ -37037,11 +34135,7 @@
       <c r="V16" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W16" s="17" t="n"/>
       <c r="X16" s="15" t="inlineStr">
         <is>
           <t>Publishing -18%</t>
@@ -37321,11 +34415,7 @@
       <c r="V19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W19" s="17" t="n"/>
       <c r="X19" s="15" t="inlineStr">
         <is>
           <t>Genie Retail Energy  +19%</t>
@@ -37417,11 +34507,7 @@
       <c r="V20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W20" s="17" t="n"/>
       <c r="X20" s="15" t="inlineStr">
         <is>
           <t>Zedge Marketplace +2%</t>
@@ -37515,11 +34601,7 @@
       <c r="V21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W21" s="17" t="n"/>
       <c r="X21" s="15" t="inlineStr">
         <is>
           <t>Medicare +10%</t>
@@ -37709,11 +34791,7 @@
       <c r="V23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W23" s="17" t="n"/>
       <c r="X23" s="15" t="inlineStr">
         <is>
           <t>Financial Services +11%</t>
@@ -38103,11 +35181,7 @@
       <c r="V27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W27" s="17" t="n"/>
       <c r="X27" s="15" t="inlineStr">
         <is>
           <t>Core Banking -1%</t>
@@ -38195,11 +35269,7 @@
       <c r="V28" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W28" s="17" t="n"/>
       <c r="X28" s="15" t="inlineStr">
         <is>
           <t>Pandora And Off Plat -0%</t>
@@ -38289,11 +35359,7 @@
       <c r="V29" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W29" s="17" t="n"/>
       <c r="X29" s="15" t="inlineStr">
         <is>
           <t>Ingredients +45%</t>
@@ -38385,11 +35451,7 @@
       <c r="V30" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W30" s="17" t="n"/>
       <c r="X30" s="15" t="inlineStr">
         <is>
           <t>Enact +2%</t>
@@ -38477,11 +35539,7 @@
       <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W31" s="17" t="n"/>
       <c r="X31" s="15" t="inlineStr">
         <is>
           <t>Institutional Produc +22%</t>
@@ -38661,11 +35719,7 @@
       <c r="V33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W33" s="17" t="n"/>
       <c r="X33" s="15" t="inlineStr">
         <is>
           <t>Reportable Segments  +1%</t>
@@ -38755,11 +35809,7 @@
       <c r="V34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W34" s="17" t="n"/>
       <c r="X34" s="15" t="inlineStr">
         <is>
           <t>Commercial Segments +15%</t>
@@ -38853,11 +35903,7 @@
       <c r="V35" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W35" s="17" t="n"/>
       <c r="X35" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -38953,11 +35999,7 @@
       <c r="V36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W36" s="17" t="n"/>
       <c r="X36" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +8%</t>
@@ -39145,11 +36187,7 @@
       <c r="V38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W38" s="17" t="n"/>
       <c r="X38" s="15" t="inlineStr">
         <is>
           <t>Gaming +30%</t>
@@ -39237,11 +36275,7 @@
       <c r="V39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W39" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W39" s="17" t="n"/>
       <c r="X39" s="15" t="inlineStr">
         <is>
           <t>Towers +6%</t>
@@ -39329,11 +36363,7 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W40" s="17" t="n"/>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>University Group +35%</t>
@@ -39521,11 +36551,7 @@
       <c r="V42" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W42" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W42" s="17" t="n"/>
       <c r="X42" s="15" t="inlineStr">
         <is>
           <t>Wealth Management +15%</t>
@@ -39615,11 +36641,7 @@
       <c r="V43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W43" s="17" t="n"/>
       <c r="X43" s="15" t="inlineStr">
         <is>
           <t>Mastercraft -8%</t>
@@ -39991,11 +37013,7 @@
       <c r="V47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W47" s="17" t="n"/>
       <c r="X47" s="15" t="inlineStr">
         <is>
           <t>Storage Solutions +8%</t>
@@ -40083,11 +37101,7 @@
       <c r="V48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W48" s="17" t="n"/>
       <c r="X48" s="15" t="inlineStr">
         <is>
           <t>Canadian Factory Bui +18%</t>
@@ -40175,11 +37189,7 @@
       <c r="V49" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W49" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W49" s="17" t="n"/>
       <c r="X49" s="15" t="inlineStr">
         <is>
           <t>Specialty Property C +10%</t>
@@ -40269,11 +37279,7 @@
       <c r="V50" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W50" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W50" s="17" t="n"/>
       <c r="X50" s="15" t="inlineStr">
         <is>
           <t>Protection Services -74%</t>
@@ -40461,11 +37467,7 @@
       <c r="V52" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W52" s="17" t="n"/>
       <c r="X52" s="15" t="inlineStr">
         <is>
           <t>Outdoor -4%</t>
@@ -41215,11 +38217,7 @@
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W60" s="17" t="n"/>
       <c r="X60" s="15" t="inlineStr">
         <is>
           <t>Shale +38%</t>
@@ -41401,11 +38399,7 @@
       <c r="V62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W62" s="17" t="n"/>
       <c r="X62" s="15" t="inlineStr">
         <is>
           <t>Healthcare IT +11%</t>
@@ -41499,11 +38493,7 @@
       <c r="V63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W63" s="17" t="n"/>
       <c r="X63" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -41595,11 +38585,7 @@
       <c r="V64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W64" s="17" t="n"/>
       <c r="X64" s="15" t="inlineStr">
         <is>
           <t>Respiratory And Oxyg +24%</t>
@@ -41781,11 +38767,7 @@
       <c r="V66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W66" s="17" t="n"/>
       <c r="X66" s="15" t="inlineStr">
         <is>
           <t>Program Of All Inclu +12%</t>
@@ -42057,11 +39039,7 @@
       <c r="V69" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
           <t>All Other Segments -71%</t>
@@ -42249,11 +39227,7 @@
       <c r="V71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W71" s="17" t="n"/>
       <c r="X71" s="15" t="inlineStr">
         <is>
           <t>Indirect -32%</t>
@@ -42368,7 +39342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X72"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -42397,6 +39371,7 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -42430,6 +39405,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -42537,8 +39513,9 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -43140,16 +40117,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T17" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U17" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T17" s="15" t="n"/>
+      <c r="U17" s="17" t="n"/>
       <c r="V17" s="18" t="n">
         <v>5</v>
       </c>
@@ -43158,11 +40127,7 @@
           <t>US 85%; CN 8%; Other Countries 2%</t>
         </is>
       </c>
-      <c r="X17" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X17" s="15" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="13" t="n">
@@ -43330,16 +40295,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T19" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U19" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T19" s="15" t="n"/>
+      <c r="U19" s="17" t="n"/>
       <c r="V19" s="18" t="n">
         <v>6</v>
       </c>
@@ -43348,11 +40305,7 @@
           <t>North America 24%; US 24%; EMEA 19%</t>
         </is>
       </c>
-      <c r="X19" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X19" s="15" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n">
@@ -43667,11 +40620,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E23" s="17" t="n"/>
       <c r="F23" s="18" t="n">
         <v>12285029</v>
       </c>
@@ -43722,16 +40671,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T23" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T23" s="15" t="n"/>
+      <c r="U23" s="17" t="n"/>
       <c r="V23" s="18" t="n">
         <v>5</v>
       </c>
@@ -43740,11 +40681,7 @@
           <t>US 96%; SV 3%; AR 0%</t>
         </is>
       </c>
-      <c r="X23" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X23" s="15" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="13" t="n">
@@ -43820,16 +40757,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T24" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T24" s="15" t="n"/>
+      <c r="U24" s="17" t="n"/>
       <c r="V24" s="18" t="n">
         <v>4</v>
       </c>
@@ -43838,11 +40767,7 @@
           <t>US 71%; GB 12%; Other International 11%</t>
         </is>
       </c>
-      <c r="X24" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X24" s="15" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="13" t="n">
@@ -44204,16 +41129,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U28" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T28" s="15" t="n"/>
+      <c r="U28" s="17" t="n"/>
       <c r="V28" s="18" t="n">
         <v>4</v>
       </c>
@@ -44222,11 +41139,7 @@
           <t>US 65%; EMEA 28%; Asia Pacific 6%</t>
         </is>
       </c>
-      <c r="X28" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X28" s="15" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n">
@@ -44302,16 +41215,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T29" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U29" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T29" s="15" t="n"/>
+      <c r="U29" s="17" t="n"/>
       <c r="V29" s="18" t="n">
         <v>9</v>
       </c>
@@ -44320,11 +41225,7 @@
           <t>Europe 26%; Americas 21%; US 20%</t>
         </is>
       </c>
-      <c r="X29" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X29" s="15" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="13" t="n">
@@ -44404,16 +41305,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T30" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U30" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T30" s="15" t="n"/>
+      <c r="U30" s="17" t="n"/>
       <c r="V30" s="18" t="n">
         <v>4</v>
       </c>
@@ -44422,11 +41315,7 @@
           <t>EMEA 48%; Americas 41%; Asia Pacific 11%</t>
         </is>
       </c>
-      <c r="X30" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X30" s="15" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="13" t="n">
@@ -45068,16 +41957,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T37" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U37" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T37" s="15" t="n"/>
+      <c r="U37" s="17" t="n"/>
       <c r="V37" s="18" t="n">
         <v>4</v>
       </c>
@@ -45086,11 +41967,7 @@
           <t>North America 42%; US 41%; Rest Of World 12%</t>
         </is>
       </c>
-      <c r="X37" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X37" s="15" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="13" t="n">
@@ -45260,16 +42137,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T39" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U39" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T39" s="15" t="n"/>
+      <c r="U39" s="17" t="n"/>
       <c r="V39" s="18" t="n">
         <v>4</v>
       </c>
@@ -45278,11 +42147,7 @@
           <t>US 82%; Africa 12%; Europe 3%</t>
         </is>
       </c>
-      <c r="X39" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X39" s="15" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="13" t="n">
@@ -45448,16 +42313,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T41" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U41" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T41" s="15" t="n"/>
+      <c r="U41" s="17" t="n"/>
       <c r="V41" s="18" t="n">
         <v>5</v>
       </c>
@@ -45466,11 +42323,7 @@
           <t>US 61%; Non Us 20%; Europe 13%</t>
         </is>
       </c>
-      <c r="X41" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X41" s="15" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="13" t="n">
@@ -45546,16 +42399,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T42" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U42" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T42" s="15" t="n"/>
+      <c r="U42" s="17" t="n"/>
       <c r="V42" s="18" t="n">
         <v>5</v>
       </c>
@@ -45564,11 +42409,7 @@
           <t>US 92%; Non Us 6%; CA 1%</t>
         </is>
       </c>
-      <c r="X42" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X42" s="15" t="n"/>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="13" t="n">
@@ -45734,16 +42575,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T44" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U44" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T44" s="15" t="n"/>
+      <c r="U44" s="17" t="n"/>
       <c r="V44" s="18" t="n">
         <v>9</v>
       </c>
@@ -45752,11 +42585,7 @@
           <t>Asia Pacific 26%; Europe 22%; CN 19%</t>
         </is>
       </c>
-      <c r="X44" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X44" s="15" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="13" t="n">
@@ -45932,16 +42761,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T46" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U46" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T46" s="15" t="n"/>
+      <c r="U46" s="17" t="n"/>
       <c r="V46" s="18" t="n">
         <v>6</v>
       </c>
@@ -45950,11 +42771,7 @@
           <t>Americas 28%; US 26%; EMEA 26%</t>
         </is>
       </c>
-      <c r="X46" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X46" s="15" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="13" t="n">
@@ -46026,16 +42843,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T47" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U47" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T47" s="15" t="n"/>
+      <c r="U47" s="17" t="n"/>
       <c r="V47" s="18" t="n">
         <v>8</v>
       </c>
@@ -46044,11 +42853,7 @@
           <t>CN 27%; JP 19%; Europe 15%</t>
         </is>
       </c>
-      <c r="X47" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X47" s="15" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="13" t="n">
@@ -46120,16 +42925,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U48" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T48" s="15" t="n"/>
+      <c r="U48" s="17" t="n"/>
       <c r="V48" s="18" t="n">
         <v>4</v>
       </c>
@@ -46138,11 +42935,7 @@
           <t>Haynesville 40%; Northeast Appalachia 37%; Southwest Appalac</t>
         </is>
       </c>
-      <c r="X48" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X48" s="15" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n">
@@ -46498,16 +43291,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T52" s="15" t="n"/>
+      <c r="U52" s="17" t="n"/>
       <c r="V52" s="18" t="n">
         <v>6</v>
       </c>
@@ -46516,11 +43301,7 @@
           <t>North America 30%; US 27%; EMEA 25%</t>
         </is>
       </c>
-      <c r="X52" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X52" s="15" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n">
@@ -47162,16 +43943,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T59" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T59" s="15" t="n"/>
+      <c r="U59" s="17" t="n"/>
       <c r="V59" s="18" t="n">
         <v>4</v>
       </c>
@@ -47180,11 +43953,7 @@
           <t>US 45%; Europe Middle East And Africa 26%; Asia Pacific 25%</t>
         </is>
       </c>
-      <c r="X59" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X59" s="15" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="13" t="n">
@@ -47636,16 +44405,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T64" s="15" t="n"/>
+      <c r="U64" s="17" t="n"/>
       <c r="V64" s="18" t="n">
         <v>5</v>
       </c>
@@ -47654,11 +44415,7 @@
           <t>US 76%; Non Us 12%; EMEA 7%</t>
         </is>
       </c>
-      <c r="X64" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X64" s="15" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n">
@@ -47732,16 +44489,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T65" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U65" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T65" s="15" t="n"/>
+      <c r="U65" s="17" t="n"/>
       <c r="V65" s="18" t="n">
         <v>4</v>
       </c>
@@ -47750,11 +44499,7 @@
           <t>US 69%; Other Countries 17%; DE 11%</t>
         </is>
       </c>
-      <c r="X65" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X65" s="15" t="n"/>
     </row>
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="13" t="n">
@@ -48014,16 +44759,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T68" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U68" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T68" s="15" t="n"/>
+      <c r="U68" s="17" t="n"/>
       <c r="V68" s="18" t="n">
         <v>5</v>
       </c>
@@ -48032,11 +44769,7 @@
           <t>North America 34%; US 31%; EMEA 27%</t>
         </is>
       </c>
-      <c r="X68" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X68" s="15" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="13" t="n">
@@ -48110,16 +44843,8 @@
           <t>–</t>
         </is>
       </c>
-      <c r="T69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="U69" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="T69" s="15" t="n"/>
+      <c r="U69" s="17" t="n"/>
       <c r="V69" s="18" t="n">
         <v>7</v>
       </c>
@@ -48128,11 +44853,7 @@
           <t>US 90%; Europe 5%; Asia 2%</t>
         </is>
       </c>
-      <c r="X69" s="15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="X69" s="15" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n">
@@ -48436,7 +45157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X162"/>
+  <dimension ref="A1:X162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -48465,6 +45186,7 @@
     <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
@@ -48498,6 +45220,7 @@
       <c r="W3" s="2" t="n"/>
       <c r="X3" s="2" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -48605,8 +45328,9 @@
       <c r="W8" s="8" t="n"/>
       <c r="X8" s="8" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>HEADLINE VALUATION + SEGMENT DETAIL — TOP BY CONFIRMED ETA</t>
         </is>
@@ -48941,11 +45665,7 @@
       <c r="V14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W14" s="17" t="n"/>
       <c r="X14" s="15" t="inlineStr">
         <is>
           <t>Gevo +414%</t>
@@ -49035,11 +45755,7 @@
       <c r="V15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W15" s="17" t="n"/>
       <c r="X15" s="15" t="inlineStr">
         <is>
           <t>International +344%</t>
@@ -49697,11 +46413,7 @@
       <c r="V22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W22" s="17" t="n"/>
       <c r="X22" s="15" t="inlineStr">
         <is>
           <t>Distribution +302%</t>
@@ -49789,11 +46501,7 @@
       <c r="V23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W23" s="17" t="n"/>
       <c r="X23" s="15" t="inlineStr">
         <is>
           <t>Corporate And Other +270%</t>
@@ -49883,11 +46591,7 @@
       <c r="V24" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W24" s="17" t="n"/>
       <c r="X24" s="15" t="inlineStr">
         <is>
           <t>Timber +327%</t>
@@ -49977,11 +46681,7 @@
       <c r="V25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W25" s="17" t="n"/>
       <c r="X25" s="15" t="inlineStr">
         <is>
           <t>Land Management And  +309%</t>
@@ -50075,11 +46775,7 @@
       <c r="V26" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W26" s="17" t="n"/>
       <c r="X26" s="15" t="inlineStr">
         <is>
           <t>Specialty Finance +257%</t>
@@ -50173,11 +46869,7 @@
       <c r="V27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W27" s="17" t="n"/>
       <c r="X27" s="15" t="inlineStr">
         <is>
           <t>Metals +249%</t>
@@ -50829,11 +47521,7 @@
       <c r="V34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W34" s="17" t="n"/>
       <c r="X34" s="15" t="inlineStr">
         <is>
           <t>Software And Service +222%</t>
@@ -51017,11 +47705,7 @@
       <c r="V36" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W36" s="17" t="n"/>
       <c r="X36" s="15" t="inlineStr">
         <is>
           <t>Real Estate +246%</t>
@@ -51235,11 +47919,7 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E39" s="17" t="n"/>
       <c r="F39" s="18" t="n">
         <v>40103256</v>
       </c>
@@ -51393,11 +48073,7 @@
       <c r="V40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W40" s="17" t="n"/>
       <c r="X40" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +257%</t>
@@ -51485,11 +48161,7 @@
       <c r="V41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W41" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W41" s="17" t="n"/>
       <c r="X41" s="15" t="inlineStr">
         <is>
           <t>Restaurant Food Sale +224%</t>
@@ -52453,11 +49125,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E52" s="17" t="n"/>
       <c r="F52" s="18" t="n">
         <v>4947405312</v>
       </c>
@@ -52617,11 +49285,7 @@
       <c r="V53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W53" s="17" t="n"/>
       <c r="X53" s="15" t="inlineStr">
         <is>
           <t>Mobile Fuel Delivery +195%</t>
@@ -52993,11 +49657,7 @@
       <c r="V57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W57" s="17" t="n"/>
       <c r="X57" s="15" t="inlineStr">
         <is>
           <t>Mid Con Barnett Shal +180%</t>
@@ -53117,11 +49777,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E59" s="17" t="n"/>
       <c r="F59" s="18" t="n">
         <v>56211529728</v>
       </c>
@@ -53179,11 +49835,7 @@
       <c r="V59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W59" s="17" t="n"/>
       <c r="X59" s="15" t="inlineStr">
         <is>
           <t>Refined Products And +192%</t>
@@ -53271,11 +49923,7 @@
       <c r="V60" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W60" s="17" t="n"/>
       <c r="X60" s="15" t="inlineStr">
         <is>
           <t>Lennar Other +191%</t>
@@ -53301,11 +49949,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E61" s="17" t="n"/>
       <c r="F61" s="18" t="n">
         <v>15829233282.24</v>
       </c>
@@ -53379,11 +50023,7 @@
       <c r="V61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W61" s="17" t="n"/>
       <c r="X61" s="15" t="inlineStr">
         <is>
           <t>Proshares Ultra Shor +207%</t>
@@ -53661,11 +50301,7 @@
       <c r="V64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W64" s="17" t="n"/>
       <c r="X64" s="15" t="inlineStr">
         <is>
           <t>Four +170%</t>
@@ -53759,11 +50395,7 @@
       <c r="V65" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W65" s="17" t="n"/>
       <c r="X65" s="15" t="inlineStr">
         <is>
           <t>Corporate And Other +153%</t>
@@ -53851,11 +50483,7 @@
       <c r="V66" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W66" s="17" t="n"/>
       <c r="X66" s="15" t="inlineStr">
         <is>
           <t>Transmission +162%</t>
@@ -54159,11 +50787,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E70" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E70" s="17" t="n"/>
       <c r="F70" s="18" t="n">
         <v>682785117.6</v>
       </c>
@@ -54229,11 +50853,7 @@
       <c r="V70" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W70" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W70" s="17" t="n"/>
       <c r="X70" s="15" t="inlineStr">
         <is>
           <t>Granite Creek Mining +190%</t>
@@ -54323,11 +50943,7 @@
       <c r="V71" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W71" s="17" t="n"/>
       <c r="X71" s="15" t="inlineStr">
         <is>
           <t>Sphere Entertainment +164%</t>
@@ -54415,11 +51031,7 @@
       <c r="V72" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W72" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W72" s="17" t="n"/>
       <c r="X72" s="15" t="inlineStr">
         <is>
           <t>NW Holdings Other +141%</t>
@@ -55181,11 +51793,7 @@
       <c r="V80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W80" s="17" t="n"/>
       <c r="X80" s="15" t="inlineStr">
         <is>
           <t>Commercial +128%</t>
@@ -55367,11 +51975,7 @@
       <c r="V82" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W82" s="17" t="n"/>
       <c r="X82" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +118%</t>
@@ -55929,11 +52533,7 @@
       <c r="V88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W88" s="17" t="n"/>
       <c r="X88" s="15" t="inlineStr">
         <is>
           <t>Financial Services +124%</t>
@@ -56023,11 +52623,7 @@
       <c r="V89" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W89" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W89" s="17" t="n"/>
       <c r="X89" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +99%</t>
@@ -56217,11 +52813,7 @@
       <c r="V91" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W91" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W91" s="17" t="n"/>
       <c r="X91" s="15" t="inlineStr">
         <is>
           <t>Debt And Preferred E +113%</t>
@@ -56499,11 +53091,7 @@
       <c r="V94" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W94" s="17" t="n"/>
       <c r="X94" s="15" t="inlineStr">
         <is>
           <t>Engineering +103%</t>
@@ -56689,11 +53277,7 @@
       <c r="V96" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W96" s="17" t="n"/>
       <c r="X96" s="15" t="inlineStr">
         <is>
           <t>Security Solutions +103%</t>
@@ -56785,11 +53369,7 @@
       <c r="V97" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W97" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W97" s="17" t="n"/>
       <c r="X97" s="15" t="inlineStr">
         <is>
           <t>Nimble Title Holding +88%</t>
@@ -57247,11 +53827,7 @@
       <c r="V102" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W102" s="17" t="n"/>
       <c r="X102" s="15" t="inlineStr">
         <is>
           <t>Asset Closure +90%</t>
@@ -57343,11 +53919,7 @@
       <c r="V103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W103" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W103" s="17" t="n"/>
       <c r="X103" s="15" t="inlineStr">
         <is>
           <t>Annuities +88%</t>
@@ -57437,11 +54009,7 @@
       <c r="V104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W104" s="17" t="n"/>
       <c r="X104" s="15" t="inlineStr">
         <is>
           <t>Portfolio Management +76%</t>
@@ -57909,11 +54477,7 @@
       <c r="V109" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W109" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W109" s="17" t="n"/>
       <c r="X109" s="15" t="inlineStr">
         <is>
           <t>Financial Services +71%</t>
@@ -58005,11 +54569,7 @@
       <c r="V110" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W110" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W110" s="17" t="n"/>
       <c r="X110" s="15" t="inlineStr">
         <is>
           <t>Water Treatment +83%</t>
@@ -58195,11 +54755,7 @@
       <c r="V112" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W112" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W112" s="17" t="n"/>
       <c r="X112" s="15" t="inlineStr">
         <is>
           <t>Eastern Hemisphere +78%</t>
@@ -58293,11 +54849,7 @@
       <c r="V113" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W113" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W113" s="17" t="n"/>
       <c r="X113" s="15" t="inlineStr">
         <is>
           <t>Branded +69%</t>
@@ -58385,11 +54937,7 @@
       <c r="V114" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W114" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W114" s="17" t="n"/>
       <c r="X114" s="15" t="inlineStr">
         <is>
           <t>Financial +66%</t>
@@ -58569,11 +55117,7 @@
       <c r="V116" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W116" s="17" t="n"/>
       <c r="X116" s="15" t="inlineStr">
         <is>
           <t>Onsite Health Clinic +72%</t>
@@ -58599,11 +55143,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E117" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E117" s="17" t="n"/>
       <c r="F117" s="18" t="n">
         <v>704822781.0700001</v>
       </c>
@@ -58661,11 +55201,7 @@
       <c r="V117" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W117" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W117" s="17" t="n"/>
       <c r="X117" s="15" t="inlineStr">
         <is>
           <t>Commercial Loan Inve +70%</t>
@@ -58755,11 +55291,7 @@
       <c r="V118" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W118" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W118" s="17" t="n"/>
       <c r="X118" s="15" t="inlineStr">
         <is>
           <t>Onshore Facilities A +67%</t>
@@ -58945,11 +55477,7 @@
       <c r="V120" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W120" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W120" s="17" t="n"/>
       <c r="X120" s="15" t="inlineStr">
         <is>
           <t>Hospitality +73%</t>
@@ -59045,11 +55573,7 @@
       <c r="V121" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W121" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W121" s="17" t="n"/>
       <c r="X121" s="15" t="inlineStr">
         <is>
           <t>High Performance Com +75%</t>
@@ -59141,11 +55665,7 @@
       <c r="V122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W122" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W122" s="17" t="n"/>
       <c r="X122" s="15" t="inlineStr">
         <is>
           <t>Medicare +62%</t>
@@ -59711,11 +56231,7 @@
       <c r="V128" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W128" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W128" s="17" t="n"/>
       <c r="X128" s="15" t="inlineStr">
         <is>
           <t>Bank +56%</t>
@@ -59803,11 +56319,7 @@
       <c r="V129" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W129" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W129" s="17" t="n"/>
       <c r="X129" s="15" t="inlineStr">
         <is>
           <t>Electrical +62%</t>
@@ -59927,11 +56439,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E131" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E131" s="17" t="n"/>
       <c r="F131" s="18" t="n">
         <v>935408752.55</v>
       </c>
@@ -60085,11 +56593,7 @@
       <c r="V132" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W132" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W132" s="17" t="n"/>
       <c r="X132" s="15" t="inlineStr">
         <is>
           <t>Telehealth Subscript +67%</t>
@@ -60369,11 +56873,7 @@
       <c r="V135" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W135" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W135" s="17" t="n"/>
       <c r="X135" s="15" t="inlineStr">
         <is>
           <t>E Infrastructure Sol +59%</t>
@@ -60469,11 +56969,7 @@
       <c r="V136" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W136" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W136" s="17" t="n"/>
       <c r="X136" s="15" t="inlineStr">
         <is>
           <t>Banking +62%</t>
@@ -60561,11 +57057,7 @@
       <c r="V137" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W137" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W137" s="17" t="n"/>
       <c r="X137" s="15" t="inlineStr">
         <is>
           <t>Healthcare Services +55%</t>
@@ -60747,11 +57239,7 @@
       <c r="V139" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W139" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W139" s="17" t="n"/>
       <c r="X139" s="15" t="inlineStr">
         <is>
           <t>Pipeline +55%</t>
@@ -60839,11 +57327,7 @@
       <c r="V140" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W140" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W140" s="17" t="n"/>
       <c r="X140" s="15" t="inlineStr">
         <is>
           <t>All Other Segments +56%</t>
@@ -61061,11 +57545,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E143" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E143" s="17" t="n"/>
       <c r="F143" s="18" t="n">
         <v>2302047000</v>
       </c>
@@ -61123,11 +57603,7 @@
       <c r="V143" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W143" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W143" s="17" t="n"/>
       <c r="X143" s="15" t="inlineStr">
         <is>
           <t>Array +58%</t>
@@ -61499,11 +57975,7 @@
       <c r="V147" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W147" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W147" s="17" t="n"/>
       <c r="X147" s="15" t="inlineStr">
         <is>
           <t>United States +52%</t>
@@ -61683,11 +58155,7 @@
       <c r="V149" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W149" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W149" s="17" t="n"/>
       <c r="X149" s="15" t="inlineStr">
         <is>
           <t>Senior Housing Opera +47%</t>
@@ -61999,11 +58467,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E153" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E153" s="17" t="n"/>
       <c r="F153" s="18" t="n">
         <v>161733088160.3101</v>
       </c>
@@ -62161,11 +58625,7 @@
       <c r="V154" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W154" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W154" s="17" t="n"/>
       <c r="X154" s="15" t="inlineStr">
         <is>
           <t>Kudu Investment Mana +54%</t>
@@ -62255,11 +58715,7 @@
       <c r="V155" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W155" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W155" s="17" t="n"/>
       <c r="X155" s="15" t="inlineStr">
         <is>
           <t>Mid Atlantic Region +54%</t>
@@ -62439,11 +58895,7 @@
       <c r="V157" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W157" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W157" s="17" t="n"/>
       <c r="X157" s="15" t="inlineStr">
         <is>
           <t>Integrated Upstream  +49%</t>
@@ -62627,11 +59079,7 @@
       <c r="V159" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W159" s="17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="W159" s="17" t="n"/>
       <c r="X159" s="15" t="inlineStr">
         <is>
           <t>Consumer +48%</t>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -8202,17 +8202,17 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>BNC</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Micware Co. Ltd. American Depo</t>
+          <t>CEA Industries Inc. Common Sto</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>200540528</v>
+        <v>117105648</v>
       </c>
       <c r="G92" s="19" t="inlineStr">
         <is>
@@ -8229,21 +8229,19 @@
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>0.4515807303367515</v>
+        <v>0.6248851029254567</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>19.852942</v>
+        <v>0.0064324588</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>0.0238744351354948</v>
+        <v>0.3209393555330036</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>0.0091588624114498</v>
-      </c>
-      <c r="L92" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.502435322965224</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>-2.60911839196688</v>
       </c>
       <c r="M92" s="21" t="inlineStr">
         <is>
@@ -8251,33 +8249,39 @@
         </is>
       </c>
       <c r="N92" s="22" t="n">
-        <v>24.58992997926714</v>
+        <v>49.05763952706174</v>
       </c>
       <c r="O92" s="22" t="n">
-        <v>18.04218527853984</v>
+        <v>1123.050207258394</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>0.307284762176941</v>
+        <v>-0.043155834361193</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>-58.84146245727219</v>
+        <v>-62.13592226588784</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T92" s="15" t="n"/>
-      <c r="U92" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" s="15" t="inlineStr">
+        <is>
+          <t>CEA Industry (100%)</t>
+        </is>
+      </c>
+      <c r="U92" s="17" t="inlineStr">
+        <is>
+          <t>CEA Industry 100%</t>
+        </is>
+      </c>
       <c r="V92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="W92" s="17" t="inlineStr">
         <is>
-          <t>JP 98%; International 2%</t>
+          <t>CA 91%; US 9%</t>
         </is>
       </c>
       <c r="X92" s="15" t="n"/>
@@ -8288,12 +8292,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>RLX</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>CEA Industries Inc. Common Sto</t>
+          <t>Rlx Technology Inc.</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -8303,11 +8307,11 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>117105648</v>
+        <v>2273393664</v>
       </c>
       <c r="G93" s="19" t="inlineStr">
         <is>
@@ -8315,59 +8319,57 @@
         </is>
       </c>
       <c r="H93" s="20" t="n">
-        <v>0.6248851029254567</v>
+        <v>-133.9863626918812</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>0.0064324588</v>
+        <v>16.909092</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>0.3209393555330036</v>
+        <v>0.9801533</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>7.502435322965224</v>
+        <v>0.51921856</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>-2.60911839196688</v>
-      </c>
-      <c r="M93" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.20715198755828</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>5.38</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>49.05763952706174</v>
+        <v>3.17186207827716</v>
       </c>
       <c r="O93" s="22" t="n">
-        <v>1123.050207258394</v>
+        <v>9.07933087209199</v>
       </c>
       <c r="P93" s="20" t="n">
-        <v>-0.043155834361193</v>
+        <v>-14.67579135780852</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>-62.13592226588784</v>
+        <v>-16.21621665160441</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>1</v>
+        <v>0.7340932777350748</v>
       </c>
       <c r="T93" s="15" t="inlineStr">
         <is>
-          <t>CEA Industry (100%)</t>
+          <t>Core Markets (84%)</t>
         </is>
       </c>
       <c r="U93" s="17" t="inlineStr">
         <is>
-          <t>CEA Industry 100%</t>
+          <t>Core Markets 84%; Europe Acquisition 16%</t>
         </is>
       </c>
       <c r="V93" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W93" s="17" t="inlineStr">
         <is>
-          <t>CA 91%; US 9%</t>
+          <t>HK 34%; CN 31%; Countries Other Than China And United Kingdo</t>
         </is>
       </c>
       <c r="X93" s="15" t="n"/>
@@ -8378,12 +8380,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>RLX</t>
+          <t>KTTA</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Rlx Technology Inc.</t>
+          <t>Pasithea Therapeutics Corp. Co</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -8393,11 +8395,11 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>2273393664</v>
+        <v>18157410</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
@@ -8405,59 +8407,57 @@
         </is>
       </c>
       <c r="H94" s="20" t="n">
-        <v>-133.9863626918812</v>
-      </c>
-      <c r="I94" s="20" t="n">
-        <v>16.909092</v>
+        <v>1.871</v>
+      </c>
+      <c r="I94" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.9801533</v>
+        <v>0.24722475</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>0.51921856</v>
+        <v>37.31800254439853</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>6.20715198755828</v>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="N94" s="22" t="n">
-        <v>3.17186207827716</v>
+        <v>-75.68926236044288</v>
+      </c>
+      <c r="M94" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N94" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O94" s="22" t="n">
-        <v>9.07933087209199</v>
-      </c>
-      <c r="P94" s="20" t="n">
-        <v>-14.67579135780852</v>
+        <v>-3174.405570547457</v>
+      </c>
+      <c r="P94" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>-16.21621665160441</v>
+        <v>-9.407668978648449</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S94" s="20" t="n">
-        <v>0.7340932777350748</v>
-      </c>
-      <c r="T94" s="15" t="inlineStr">
-        <is>
-          <t>Core Markets (84%)</t>
-        </is>
-      </c>
-      <c r="U94" s="17" t="inlineStr">
-        <is>
-          <t>Core Markets 84%; Europe Acquisition 16%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S94" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T94" s="15" t="n"/>
+      <c r="U94" s="17" t="n"/>
       <c r="V94" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W94" s="17" t="inlineStr">
-        <is>
-          <t>HK 34%; CN 31%; Countries Other Than China And United Kingdo</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W94" s="17" t="n"/>
       <c r="X94" s="15" t="n"/>
     </row>
     <row r="95" ht="16" customHeight="1">
@@ -8466,26 +8466,26 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>KTTA</t>
+          <t>MWC</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Pasithea Therapeutics Corp. Co</t>
+          <t>Micware Co. Ltd. American Depo</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>18157410</v>
+        <v>200540528</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
@@ -8493,42 +8493,38 @@
         </is>
       </c>
       <c r="H95" s="20" t="n">
-        <v>1.871</v>
-      </c>
-      <c r="I95" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.4515807303367515</v>
+      </c>
+      <c r="I95" s="20" t="n">
+        <v>19.852942</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>0.24722475</v>
+        <v>0.0238744351354948</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>37.31800254439853</v>
-      </c>
-      <c r="L95" s="22" t="n">
-        <v>-75.68926236044288</v>
+        <v>0.0091588624114498</v>
+      </c>
+      <c r="L95" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M95" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N95" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N95" s="22" t="n">
+        <v>24.58992997926714</v>
       </c>
       <c r="O95" s="22" t="n">
-        <v>-3174.405570547457</v>
-      </c>
-      <c r="P95" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>18.04218527853984</v>
+      </c>
+      <c r="P95" s="20" t="n">
+        <v>0.307284762176941</v>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>-9.407668978648449</v>
+        <v>-58.84146245727219</v>
       </c>
       <c r="R95" s="18" t="n">
         <v>0</v>
@@ -8541,9 +8537,13 @@
       <c r="T95" s="15" t="n"/>
       <c r="U95" s="17" t="n"/>
       <c r="V95" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W95" s="17" t="inlineStr">
+        <is>
+          <t>JP 98%; International 2%</t>
+        </is>
+      </c>
       <c r="X95" s="15" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
@@ -14000,91 +14000,83 @@
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>LGPS</t>
+          <t>FCCO</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>LogProstyle Inc. Common Shares</t>
+          <t>First Community Corporation</t>
         </is>
       </c>
       <c r="D158" s="16" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F158" s="18" t="n">
-        <v>28066240</v>
+        <v>311354432</v>
       </c>
       <c r="G158" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H158" s="20" t="n">
-        <v>11.30448758239022</v>
+      <c r="H158" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I158" s="20" t="n">
-        <v>5.1682606</v>
+        <v>12.791507</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>0.0070678140203218</v>
+        <v>1.4100273</v>
       </c>
       <c r="K158" s="20" t="n">
-        <v>0.0013590796650376</v>
-      </c>
-      <c r="L158" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M158" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N158" s="22" t="n">
-        <v>6.413053831654871</v>
+        <v>3.7495415</v>
+      </c>
+      <c r="L158" s="22" t="n">
+        <v>5.14829354633747</v>
+      </c>
+      <c r="M158" s="22" t="n">
+        <v>1.73209876112208</v>
+      </c>
+      <c r="N158" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O158" s="22" t="n">
-        <v>7.27474752209538</v>
-      </c>
-      <c r="P158" s="20" t="n">
-        <v>8.492030230938919</v>
+        <v>0</v>
+      </c>
+      <c r="P158" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q158" s="22" t="n">
-        <v>-8.843762286939159</v>
+        <v>24.76480132963891</v>
       </c>
       <c r="R158" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S158" s="20" t="n">
-        <v>0.8379545771357341</v>
-      </c>
-      <c r="T158" s="15" t="inlineStr">
-        <is>
-          <t>Real Estates (91%)</t>
-        </is>
-      </c>
-      <c r="U158" s="17" t="inlineStr">
-        <is>
-          <t>Real Estates 91%; Hotels 6%; Other 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S158" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T158" s="15" t="n"/>
+      <c r="U158" s="17" t="n"/>
       <c r="V158" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W158" s="17" t="n"/>
-      <c r="X158" s="15" t="inlineStr">
-        <is>
-          <t>Real Estates +10%</t>
-        </is>
-      </c>
+      <c r="X158" s="15" t="n"/>
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="13" t="n">
@@ -14092,12 +14084,12 @@
       </c>
       <c r="B159" s="14" t="inlineStr">
         <is>
-          <t>FCCO</t>
+          <t>TUYA</t>
         </is>
       </c>
       <c r="C159" s="15" t="inlineStr">
         <is>
-          <t>First Community Corporation</t>
+          <t>Tuya Inc.</t>
         </is>
       </c>
       <c r="D159" s="16" t="inlineStr">
@@ -14107,68 +14099,72 @@
       </c>
       <c r="E159" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F159" s="18" t="n">
-        <v>311354432</v>
+        <v>1103599104</v>
       </c>
       <c r="G159" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H159" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H159" s="20" t="n">
+        <v>7.751</v>
       </c>
       <c r="I159" s="20" t="n">
-        <v>12.791507</v>
+        <v>18</v>
       </c>
       <c r="J159" s="20" t="n">
-        <v>1.4100273</v>
+        <v>1.1015912</v>
       </c>
       <c r="K159" s="20" t="n">
-        <v>3.7495415</v>
+        <v>3.3647752</v>
       </c>
       <c r="L159" s="22" t="n">
-        <v>5.14829354633747</v>
+        <v>6.696634650402899</v>
       </c>
       <c r="M159" s="22" t="n">
-        <v>1.73209876112208</v>
-      </c>
-      <c r="N159" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.36</v>
+      </c>
+      <c r="N159" s="22" t="n">
+        <v>8.703003100904489</v>
       </c>
       <c r="O159" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P159" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.94541798869452</v>
+      </c>
+      <c r="P159" s="20" t="n">
+        <v>-46.12537371955105</v>
       </c>
       <c r="Q159" s="22" t="n">
-        <v>24.76480132963891</v>
+        <v>-22.61391349797465</v>
       </c>
       <c r="R159" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T159" s="15" t="n"/>
-      <c r="U159" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S159" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T159" s="15" t="inlineStr">
+        <is>
+          <t>Single Reporting (100%)</t>
+        </is>
+      </c>
+      <c r="U159" s="17" t="inlineStr">
+        <is>
+          <t>Single Reporting 100%</t>
+        </is>
+      </c>
       <c r="V159" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W159" s="17" t="n"/>
-      <c r="X159" s="15" t="n"/>
+      <c r="X159" s="15" t="inlineStr">
+        <is>
+          <t>Single Reporting +8%</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="13" t="n">
@@ -14176,12 +14172,12 @@
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>TUYA</t>
+          <t>HFBL</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Tuya Inc.</t>
+          <t xml:space="preserve">Home Federal Bancorp, Inc. of </t>
         </is>
       </c>
       <c r="D160" s="16" t="inlineStr">
@@ -14191,72 +14187,68 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F160" s="18" t="n">
-        <v>1103599104</v>
+        <v>64101128</v>
       </c>
       <c r="G160" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H160" s="20" t="n">
-        <v>7.751</v>
+      <c r="H160" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I160" s="20" t="n">
-        <v>18</v>
+        <v>10.709184</v>
       </c>
       <c r="J160" s="20" t="n">
-        <v>1.1015912</v>
+        <v>1.0916371</v>
       </c>
       <c r="K160" s="20" t="n">
-        <v>3.3647752</v>
+        <v>2.7703834</v>
       </c>
       <c r="L160" s="22" t="n">
-        <v>6.696634650402899</v>
+        <v>16.94622775080168</v>
       </c>
       <c r="M160" s="22" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="N160" s="22" t="n">
-        <v>8.703003100904489</v>
+        <v>2.69090379019187</v>
+      </c>
+      <c r="N160" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O160" s="22" t="n">
-        <v>3.94541798869452</v>
-      </c>
-      <c r="P160" s="20" t="n">
-        <v>-46.12537371955105</v>
+        <v>0</v>
+      </c>
+      <c r="P160" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q160" s="22" t="n">
-        <v>-22.61391349797465</v>
+        <v>52.2046862669974</v>
       </c>
       <c r="R160" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S160" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T160" s="15" t="inlineStr">
-        <is>
-          <t>Single Reporting (100%)</t>
-        </is>
-      </c>
-      <c r="U160" s="17" t="inlineStr">
-        <is>
-          <t>Single Reporting 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S160" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T160" s="15" t="n"/>
+      <c r="U160" s="17" t="n"/>
       <c r="V160" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W160" s="17" t="n"/>
-      <c r="X160" s="15" t="inlineStr">
-        <is>
-          <t>Single Reporting +8%</t>
-        </is>
-      </c>
+      <c r="X160" s="15" t="n"/>
     </row>
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="13" t="n">
@@ -14264,12 +14256,12 @@
       </c>
       <c r="B161" s="14" t="inlineStr">
         <is>
-          <t>HFBL</t>
+          <t>INVE</t>
         </is>
       </c>
       <c r="C161" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home Federal Bancorp, Inc. of </t>
+          <t>Identiv, Inc.</t>
         </is>
       </c>
       <c r="D161" s="16" t="inlineStr">
@@ -14279,36 +14271,38 @@
       </c>
       <c r="E161" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F161" s="18" t="n">
-        <v>64101128</v>
+        <v>62896272</v>
       </c>
       <c r="G161" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H161" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I161" s="20" t="n">
-        <v>10.709184</v>
+      <c r="H161" s="20" t="n">
+        <v>3.476</v>
+      </c>
+      <c r="I161" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J161" s="20" t="n">
-        <v>1.0916371</v>
+        <v>0.45748207</v>
       </c>
       <c r="K161" s="20" t="n">
-        <v>2.7703834</v>
+        <v>2.661938</v>
       </c>
       <c r="L161" s="22" t="n">
-        <v>16.94622775080168</v>
-      </c>
-      <c r="M161" s="22" t="n">
-        <v>2.69090379019187</v>
+        <v>-23.45767011437498</v>
+      </c>
+      <c r="M161" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N161" s="21" t="inlineStr">
         <is>
@@ -14316,7 +14310,7 @@
         </is>
       </c>
       <c r="O161" s="22" t="n">
-        <v>0</v>
+        <v>-86.16866833839251</v>
       </c>
       <c r="P161" s="21" t="inlineStr">
         <is>
@@ -14324,7 +14318,7 @@
         </is>
       </c>
       <c r="Q161" s="22" t="n">
-        <v>52.2046862669974</v>
+        <v>-16.82540297658396</v>
       </c>
       <c r="R161" s="18" t="n">
         <v>0</v>
@@ -14337,9 +14331,13 @@
       <c r="T161" s="15" t="n"/>
       <c r="U161" s="17" t="n"/>
       <c r="V161" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W161" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W161" s="17" t="inlineStr">
+        <is>
+          <t>Americas 47%; Europe And Middle East 33%; Asia Pacific 20%</t>
+        </is>
+      </c>
       <c r="X161" s="15" t="n"/>
     </row>
     <row r="162" ht="16" customHeight="1">
@@ -14348,12 +14346,12 @@
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>INVE</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Identiv, Inc.</t>
+          <t>Transcontinental Realty Invest</t>
         </is>
       </c>
       <c r="D162" s="16" t="inlineStr">
@@ -14363,11 +14361,11 @@
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F162" s="18" t="n">
-        <v>62896272</v>
+        <v>430669952</v>
       </c>
       <c r="G162" s="19" t="inlineStr">
         <is>
@@ -14375,62 +14373,62 @@
         </is>
       </c>
       <c r="H162" s="20" t="n">
-        <v>3.476</v>
-      </c>
-      <c r="I162" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>114.464</v>
+      </c>
+      <c r="I162" s="20" t="n">
+        <v>45.733944</v>
       </c>
       <c r="J162" s="20" t="n">
-        <v>0.45748207</v>
+        <v>0.5085229999999999</v>
       </c>
       <c r="K162" s="20" t="n">
-        <v>2.661938</v>
+        <v>8.719251</v>
       </c>
       <c r="L162" s="22" t="n">
-        <v>-23.45767011437498</v>
+        <v>-0.96269211144865</v>
       </c>
       <c r="M162" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N162" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N162" s="22" t="n">
+        <v>2.90803925982063</v>
       </c>
       <c r="O162" s="22" t="n">
-        <v>-86.16866833839251</v>
-      </c>
-      <c r="P162" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>87.99335720139757</v>
+      </c>
+      <c r="P162" s="20" t="n">
+        <v>4.822520159807838</v>
       </c>
       <c r="Q162" s="22" t="n">
-        <v>-16.82540297658396</v>
+        <v>0.78420114833133</v>
       </c>
       <c r="R162" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S162" s="20" t="n">
+        <v>0.5765484496217432</v>
+      </c>
+      <c r="T162" s="15" t="inlineStr">
+        <is>
+          <t>Residential (70%)</t>
+        </is>
+      </c>
+      <c r="U162" s="17" t="inlineStr">
+        <is>
+          <t>Residential 70%; Commercial Segments 30%</t>
+        </is>
+      </c>
+      <c r="V162" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S162" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T162" s="15" t="n"/>
-      <c r="U162" s="17" t="n"/>
-      <c r="V162" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W162" s="17" t="inlineStr">
-        <is>
-          <t>Americas 47%; Europe And Middle East 33%; Asia Pacific 20%</t>
-        </is>
-      </c>
-      <c r="X162" s="15" t="n"/>
+      <c r="W162" s="17" t="n"/>
+      <c r="X162" s="15" t="inlineStr">
+        <is>
+          <t>Commercial Segments +15%</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="13" t="n">
@@ -14438,12 +14436,12 @@
       </c>
       <c r="B163" s="14" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C163" s="15" t="inlineStr">
         <is>
-          <t>Transcontinental Realty Invest</t>
+          <t>The LGL Group, Inc.</t>
         </is>
       </c>
       <c r="D163" s="16" t="inlineStr">
@@ -14453,11 +14451,11 @@
       </c>
       <c r="E163" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F163" s="18" t="n">
-        <v>430669952</v>
+        <v>44608460</v>
       </c>
       <c r="G163" s="19" t="inlineStr">
         <is>
@@ -14465,60 +14463,66 @@
         </is>
       </c>
       <c r="H163" s="20" t="n">
-        <v>114.464</v>
+        <v>1.723</v>
       </c>
       <c r="I163" s="20" t="n">
-        <v>45.733944</v>
+        <v>135.0532271386431</v>
       </c>
       <c r="J163" s="20" t="n">
-        <v>0.5085229999999999</v>
+        <v>0.97999716</v>
       </c>
       <c r="K163" s="20" t="n">
-        <v>8.719251</v>
+        <v>10.287929</v>
       </c>
       <c r="L163" s="22" t="n">
-        <v>-0.96269211144865</v>
-      </c>
-      <c r="M163" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N163" s="22" t="n">
-        <v>2.90803925982063</v>
+        <v>2.07718822715239</v>
+      </c>
+      <c r="M163" s="22" t="n">
+        <v>0.01310528849938</v>
+      </c>
+      <c r="N163" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O163" s="22" t="n">
-        <v>87.99335720139757</v>
-      </c>
-      <c r="P163" s="20" t="n">
-        <v>4.822520159807838</v>
+        <v>6.47637323099064</v>
+      </c>
+      <c r="P163" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q163" s="22" t="n">
-        <v>0.78420114833133</v>
+        <v>1.59651865959342</v>
       </c>
       <c r="R163" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S163" s="20" t="n">
-        <v>0.5765484496217432</v>
+        <v>0.5814947574810531</v>
       </c>
       <c r="T163" s="15" t="inlineStr">
         <is>
-          <t>Residential (70%)</t>
+          <t>Electronic Instruments (70%)</t>
         </is>
       </c>
       <c r="U163" s="17" t="inlineStr">
         <is>
-          <t>Residential 70%; Commercial Segments 30%</t>
+          <t>Electronic Instruments 70%; Merchant Investment 30%</t>
         </is>
       </c>
       <c r="V163" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W163" s="17" t="inlineStr">
+        <is>
+          <t>US 46%; Non Us 27%; All Other Foreign Countries 7%</t>
+        </is>
+      </c>
       <c r="X163" s="15" t="inlineStr">
         <is>
-          <t>Commercial Segments +15%</t>
+          <t>Electronic Instrumen +53%</t>
         </is>
       </c>
     </row>
@@ -14528,12 +14532,12 @@
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>SOHU</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>The LGL Group, Inc.</t>
+          <t>Sohu.Com Limited</t>
         </is>
       </c>
       <c r="D164" s="16" t="inlineStr">
@@ -14543,11 +14547,11 @@
       </c>
       <c r="E164" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F164" s="18" t="n">
-        <v>44608460</v>
+        <v>356275008</v>
       </c>
       <c r="G164" s="19" t="inlineStr">
         <is>
@@ -14555,30 +14559,30 @@
         </is>
       </c>
       <c r="H164" s="20" t="n">
-        <v>1.723</v>
+        <v>25.625</v>
       </c>
       <c r="I164" s="20" t="n">
-        <v>135.0532271386431</v>
+        <v>1.5349742</v>
       </c>
       <c r="J164" s="20" t="n">
-        <v>0.97999716</v>
+        <v>0.24177259</v>
       </c>
       <c r="K164" s="20" t="n">
-        <v>10.287929</v>
+        <v>0.60388464</v>
       </c>
       <c r="L164" s="22" t="n">
-        <v>2.07718822715239</v>
-      </c>
-      <c r="M164" s="22" t="n">
-        <v>0.01310528849938</v>
-      </c>
-      <c r="N164" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-1.49828078875518</v>
+      </c>
+      <c r="M164" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N164" s="22" t="n">
+        <v>-8.16107964110563</v>
       </c>
       <c r="O164" s="22" t="n">
-        <v>6.47637323099064</v>
+        <v>-13.89105184886015</v>
       </c>
       <c r="P164" s="21" t="inlineStr">
         <is>
@@ -14586,37 +14590,23 @@
         </is>
       </c>
       <c r="Q164" s="22" t="n">
-        <v>1.59651865959342</v>
+        <v>-9.334348445605679</v>
       </c>
       <c r="R164" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S164" s="20" t="n">
-        <v>0.5814947574810531</v>
-      </c>
-      <c r="T164" s="15" t="inlineStr">
-        <is>
-          <t>Electronic Instruments (70%)</t>
-        </is>
-      </c>
-      <c r="U164" s="17" t="inlineStr">
-        <is>
-          <t>Electronic Instruments 70%; Merchant Investment 30%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S164" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T164" s="15" t="n"/>
+      <c r="U164" s="17" t="n"/>
       <c r="V164" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W164" s="17" t="inlineStr">
-        <is>
-          <t>US 46%; Non Us 27%; All Other Foreign Countries 7%</t>
-        </is>
-      </c>
-      <c r="X164" s="15" t="inlineStr">
-        <is>
-          <t>Electronic Instrumen +53%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W164" s="17" t="n"/>
+      <c r="X164" s="15" t="n"/>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="13" t="n">
@@ -14624,12 +14614,12 @@
       </c>
       <c r="B165" s="14" t="inlineStr">
         <is>
-          <t>SOHU</t>
+          <t>CGEN</t>
         </is>
       </c>
       <c r="C165" s="15" t="inlineStr">
         <is>
-          <t>Sohu.Com Limited</t>
+          <t>Compugen Ltd</t>
         </is>
       </c>
       <c r="D165" s="16" t="inlineStr">
@@ -14639,11 +14629,11 @@
       </c>
       <c r="E165" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F165" s="18" t="n">
-        <v>356275008</v>
+        <v>197681888</v>
       </c>
       <c r="G165" s="19" t="inlineStr">
         <is>
@@ -14651,19 +14641,19 @@
         </is>
       </c>
       <c r="H165" s="20" t="n">
-        <v>25.625</v>
+        <v>2.104</v>
       </c>
       <c r="I165" s="20" t="n">
-        <v>1.5349742</v>
+        <v>5.5</v>
       </c>
       <c r="J165" s="20" t="n">
-        <v>0.24177259</v>
+        <v>2.0734127</v>
       </c>
       <c r="K165" s="20" t="n">
-        <v>0.60388464</v>
+        <v>2.7207923</v>
       </c>
       <c r="L165" s="22" t="n">
-        <v>-1.49828078875518</v>
+        <v>15.84768352677813</v>
       </c>
       <c r="M165" s="21" t="inlineStr">
         <is>
@@ -14671,34 +14661,42 @@
         </is>
       </c>
       <c r="N165" s="22" t="n">
-        <v>-8.16107964110563</v>
+        <v>258.167133673974</v>
       </c>
       <c r="O165" s="22" t="n">
-        <v>-13.89105184886015</v>
-      </c>
-      <c r="P165" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>43.70430432631521</v>
+      </c>
+      <c r="P165" s="20" t="n">
+        <v>-4.036077369949829</v>
       </c>
       <c r="Q165" s="22" t="n">
-        <v>-9.334348445605679</v>
+        <v>25.90361181892626</v>
       </c>
       <c r="R165" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T165" s="15" t="n"/>
-      <c r="U165" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S165" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T165" s="15" t="inlineStr">
+        <is>
+          <t>Single Operating (100%)</t>
+        </is>
+      </c>
+      <c r="U165" s="17" t="inlineStr">
+        <is>
+          <t>Single Operating 100%</t>
+        </is>
+      </c>
       <c r="V165" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W165" s="17" t="n"/>
-      <c r="X165" s="15" t="n"/>
+      <c r="X165" s="15" t="inlineStr">
+        <is>
+          <t>Single Operating +161%</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="13" t="n">
@@ -14706,12 +14704,12 @@
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>CGEN</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Compugen Ltd</t>
+          <t>Criteo S.A.</t>
         </is>
       </c>
       <c r="D166" s="16" t="inlineStr">
@@ -14721,11 +14719,11 @@
       </c>
       <c r="E166" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F166" s="18" t="n">
-        <v>197681888</v>
+        <v>887318336</v>
       </c>
       <c r="G166" s="19" t="inlineStr">
         <is>
@@ -14733,19 +14731,19 @@
         </is>
       </c>
       <c r="H166" s="20" t="n">
-        <v>2.104</v>
+        <v>2.455</v>
       </c>
       <c r="I166" s="20" t="n">
-        <v>5.5</v>
+        <v>8.2910795</v>
       </c>
       <c r="J166" s="20" t="n">
-        <v>2.0734127</v>
+        <v>0.78100127</v>
       </c>
       <c r="K166" s="20" t="n">
-        <v>2.7207923</v>
+        <v>0.4626013</v>
       </c>
       <c r="L166" s="22" t="n">
-        <v>15.84768352677813</v>
+        <v>3.28799696978199</v>
       </c>
       <c r="M166" s="21" t="inlineStr">
         <is>
@@ -14753,40 +14751,44 @@
         </is>
       </c>
       <c r="N166" s="22" t="n">
-        <v>258.167133673974</v>
+        <v>12.09779410050992</v>
       </c>
       <c r="O166" s="22" t="n">
-        <v>43.70430432631521</v>
+        <v>7.25799885125514</v>
       </c>
       <c r="P166" s="20" t="n">
-        <v>-4.036077369949829</v>
+        <v>-2.407378490646129</v>
       </c>
       <c r="Q166" s="22" t="n">
-        <v>25.90361181892626</v>
+        <v>-25.89173351257982</v>
       </c>
       <c r="R166" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S166" s="20" t="n">
-        <v>1</v>
+        <v>0.877480231574409</v>
       </c>
       <c r="T166" s="15" t="inlineStr">
         <is>
-          <t>Single Operating (100%)</t>
+          <t>Performance Media (93%)</t>
         </is>
       </c>
       <c r="U166" s="17" t="inlineStr">
         <is>
-          <t>Single Operating 100%</t>
+          <t>Performance Media 93%; Retail Media 7%</t>
         </is>
       </c>
       <c r="V166" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" s="17" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="W166" s="17" t="inlineStr">
+        <is>
+          <t>Americas 26%; US 23%; EMEA 23%</t>
+        </is>
+      </c>
       <c r="X166" s="15" t="inlineStr">
         <is>
-          <t>Single Operating +161%</t>
+          <t>Retail Media +11%</t>
         </is>
       </c>
     </row>
@@ -14796,26 +14798,26 @@
       </c>
       <c r="B167" s="14" t="inlineStr">
         <is>
-          <t>CRTO</t>
+          <t>LGPS</t>
         </is>
       </c>
       <c r="C167" s="15" t="inlineStr">
         <is>
-          <t>Criteo S.A.</t>
+          <t>LogProstyle Inc. Common Shares</t>
         </is>
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E167" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F167" s="18" t="n">
-        <v>887318336</v>
+        <v>28066240</v>
       </c>
       <c r="G167" s="19" t="inlineStr">
         <is>
@@ -14823,19 +14825,21 @@
         </is>
       </c>
       <c r="H167" s="20" t="n">
-        <v>2.455</v>
+        <v>11.30448758239022</v>
       </c>
       <c r="I167" s="20" t="n">
-        <v>8.2910795</v>
+        <v>5.1682606</v>
       </c>
       <c r="J167" s="20" t="n">
-        <v>0.78100127</v>
+        <v>0.0070678140203218</v>
       </c>
       <c r="K167" s="20" t="n">
-        <v>0.4626013</v>
-      </c>
-      <c r="L167" s="22" t="n">
-        <v>3.28799696978199</v>
+        <v>0.0013590796650376</v>
+      </c>
+      <c r="L167" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M167" s="21" t="inlineStr">
         <is>
@@ -14843,44 +14847,40 @@
         </is>
       </c>
       <c r="N167" s="22" t="n">
-        <v>12.09779410050992</v>
+        <v>6.413053831654871</v>
       </c>
       <c r="O167" s="22" t="n">
-        <v>7.25799885125514</v>
+        <v>7.27474752209538</v>
       </c>
       <c r="P167" s="20" t="n">
-        <v>-2.407378490646129</v>
+        <v>8.492030230938919</v>
       </c>
       <c r="Q167" s="22" t="n">
-        <v>-25.89173351257982</v>
+        <v>-8.843762286939159</v>
       </c>
       <c r="R167" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S167" s="20" t="n">
-        <v>0.877480231574409</v>
+        <v>0.8379545771357341</v>
       </c>
       <c r="T167" s="15" t="inlineStr">
         <is>
-          <t>Performance Media (93%)</t>
+          <t>Real Estates (91%)</t>
         </is>
       </c>
       <c r="U167" s="17" t="inlineStr">
         <is>
-          <t>Performance Media 93%; Retail Media 7%</t>
+          <t>Real Estates 91%; Hotels 6%; Other 3%</t>
         </is>
       </c>
       <c r="V167" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W167" s="17" t="inlineStr">
-        <is>
-          <t>Americas 26%; US 23%; EMEA 23%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W167" s="17" t="n"/>
       <c r="X167" s="15" t="inlineStr">
         <is>
-          <t>Retail Media +11%</t>
+          <t>Real Estates +10%</t>
         </is>
       </c>
     </row>
@@ -22842,12 +22842,12 @@
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>LTCH</t>
         </is>
       </c>
       <c r="C258" s="15" t="inlineStr">
         <is>
-          <t>RCM Technologies, Inc.</t>
+          <t>Latch Inc. Common Stock</t>
         </is>
       </c>
       <c r="D258" s="16" t="inlineStr">
@@ -22857,11 +22857,11 @@
       </c>
       <c r="E258" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F258" s="18" t="n">
-        <v>200225088</v>
+        <v>32851562</v>
       </c>
       <c r="G258" s="19" t="inlineStr">
         <is>
@@ -22869,60 +22869,64 @@
         </is>
       </c>
       <c r="H258" s="20" t="n">
-        <v>8.760999999999999</v>
-      </c>
-      <c r="I258" s="20" t="n">
-        <v>13.325473</v>
+        <v>-0.0075030035299217</v>
+      </c>
+      <c r="I258" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J258" s="20" t="n">
-        <v>4.4812818</v>
+        <v>0.0870110976914682</v>
       </c>
       <c r="K258" s="20" t="n">
-        <v>0.62970006</v>
-      </c>
-      <c r="L258" s="22" t="n">
-        <v>14.27938087426353</v>
-      </c>
-      <c r="M258" s="22" t="n">
-        <v>7.441462044564701</v>
-      </c>
-      <c r="N258" s="22" t="n">
-        <v>55.34887070062165</v>
+        <v>0.794283413926499</v>
+      </c>
+      <c r="L258" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M258" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N258" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O258" s="22" t="n">
-        <v>8.34648282426018</v>
-      </c>
-      <c r="P258" s="20" t="n">
-        <v>0.8158970704077422</v>
+        <v>-351.3757253384913</v>
+      </c>
+      <c r="P258" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q258" s="22" t="n">
-        <v>-0.77252533785857</v>
+        <v>71.42858359278503</v>
       </c>
       <c r="R258" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S258" s="20" t="n">
-        <v>0.4181480808503012</v>
-      </c>
-      <c r="T258" s="15" t="inlineStr">
-        <is>
-          <t>Specialty Health Care (51%)</t>
-        </is>
-      </c>
-      <c r="U258" s="17" t="inlineStr">
-        <is>
-          <t>Specialty Health Care 51%; Engineering 38%; Life Sciences Data Solutions 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S258" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T258" s="15" t="n"/>
+      <c r="U258" s="17" t="n"/>
       <c r="V258" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W258" s="17" t="n"/>
-      <c r="X258" s="15" t="inlineStr">
-        <is>
-          <t>Engineering +49%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W258" s="17" t="inlineStr">
+        <is>
+          <t>Non Us 100%</t>
+        </is>
+      </c>
+      <c r="X258" s="15" t="n"/>
     </row>
     <row r="259" ht="16" customHeight="1">
       <c r="A259" s="13" t="n">
@@ -22930,12 +22934,12 @@
       </c>
       <c r="B259" s="14" t="inlineStr">
         <is>
-          <t>PBHC</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="C259" s="15" t="inlineStr">
         <is>
-          <t>Pathfinder Bancorp, Inc.</t>
+          <t>RCM Technologies, Inc.</t>
         </is>
       </c>
       <c r="D259" s="16" t="inlineStr">
@@ -22945,68 +22949,72 @@
       </c>
       <c r="E259" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F259" s="18" t="n">
-        <v>102606536</v>
+        <v>200225088</v>
       </c>
       <c r="G259" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H259" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H259" s="20" t="n">
+        <v>8.760999999999999</v>
       </c>
       <c r="I259" s="20" t="n">
-        <v>13.96428325612177</v>
+        <v>13.325473</v>
       </c>
       <c r="J259" s="20" t="n">
-        <v>0.8302536</v>
+        <v>4.4812818</v>
       </c>
       <c r="K259" s="20" t="n">
-        <v>3.423413</v>
+        <v>0.62970006</v>
       </c>
       <c r="L259" s="22" t="n">
-        <v>12.70377220280993</v>
+        <v>14.27938087426353</v>
       </c>
       <c r="M259" s="22" t="n">
-        <v>1.39099315110043</v>
-      </c>
-      <c r="N259" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.441462044564701</v>
+      </c>
+      <c r="N259" s="22" t="n">
+        <v>55.34887070062165</v>
       </c>
       <c r="O259" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.34648282426018</v>
+      </c>
+      <c r="P259" s="20" t="n">
+        <v>0.8158970704077422</v>
       </c>
       <c r="Q259" s="22" t="n">
-        <v>-7.86345363685683</v>
+        <v>-0.77252533785857</v>
       </c>
       <c r="R259" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S259" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T259" s="15" t="n"/>
-      <c r="U259" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="S259" s="20" t="n">
+        <v>0.4181480808503012</v>
+      </c>
+      <c r="T259" s="15" t="inlineStr">
+        <is>
+          <t>Specialty Health Care (51%)</t>
+        </is>
+      </c>
+      <c r="U259" s="17" t="inlineStr">
+        <is>
+          <t>Specialty Health Care 51%; Engineering 38%; Life Sciences Data Solutions 11%</t>
+        </is>
+      </c>
       <c r="V259" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W259" s="17" t="n"/>
-      <c r="X259" s="15" t="n"/>
+      <c r="X259" s="15" t="inlineStr">
+        <is>
+          <t>Engineering +49%</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="13" t="n">
@@ -23014,12 +23022,12 @@
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>SMID</t>
+          <t>PBHC</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
         <is>
-          <t>Smith-Midland Corporation</t>
+          <t>Pathfinder Bancorp, Inc.</t>
         </is>
       </c>
       <c r="D260" s="16" t="inlineStr">
@@ -23029,46 +23037,52 @@
       </c>
       <c r="E260" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F260" s="18" t="n">
-        <v>157869984</v>
-      </c>
-      <c r="G260" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="H260" s="20" t="n">
-        <v>8.513999999999999</v>
+        <v>102606536</v>
+      </c>
+      <c r="G260" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="H260" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I260" s="20" t="n">
-        <v>15.025252</v>
+        <v>13.96428325612177</v>
       </c>
       <c r="J260" s="20" t="n">
-        <v>2.8363047</v>
+        <v>0.8302536</v>
       </c>
       <c r="K260" s="20" t="n">
-        <v>1.7100302</v>
+        <v>3.423413</v>
       </c>
       <c r="L260" s="22" t="n">
-        <v>-1.33140004307622</v>
+        <v>12.70377220280993</v>
       </c>
       <c r="M260" s="22" t="n">
+        <v>1.39099315110043</v>
+      </c>
+      <c r="N260" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O260" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="N260" s="22" t="n">
-        <v>23.5026343072573</v>
-      </c>
-      <c r="O260" s="22" t="n">
-        <v>21.55148427969094</v>
-      </c>
-      <c r="P260" s="20" t="n">
-        <v>-0.3648145389542678</v>
+      <c r="P260" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q260" s="22" t="n">
-        <v>-5.50939003710083</v>
+        <v>-7.86345363685683</v>
       </c>
       <c r="R260" s="18" t="n">
         <v>0</v>
@@ -23092,12 +23106,12 @@
       </c>
       <c r="B261" s="14" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>SMID</t>
         </is>
       </c>
       <c r="C261" s="15" t="inlineStr">
         <is>
-          <t>Hanmi Financial Corporation</t>
+          <t>Smith-Midland Corporation</t>
         </is>
       </c>
       <c r="D261" s="16" t="inlineStr">
@@ -23107,74 +23121,62 @@
       </c>
       <c r="E261" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F261" s="18" t="n">
-        <v>972469440</v>
-      </c>
-      <c r="G261" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>157869984</v>
+      </c>
+      <c r="G261" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H261" s="20" t="n">
-        <v>7.437587824860818</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="I261" s="20" t="n">
-        <v>12.190297</v>
+        <v>15.025252</v>
       </c>
       <c r="J261" s="20" t="n">
-        <v>1.2036252</v>
+        <v>2.8363047</v>
       </c>
       <c r="K261" s="20" t="n">
-        <v>3.676925</v>
+        <v>1.7100302</v>
       </c>
       <c r="L261" s="22" t="n">
-        <v>11.99772815882008</v>
+        <v>-1.33140004307622</v>
       </c>
       <c r="M261" s="22" t="n">
-        <v>3.67615130332913</v>
+        <v>0</v>
       </c>
       <c r="N261" s="22" t="n">
-        <v>14.10544231322912</v>
+        <v>23.5026343072573</v>
       </c>
       <c r="O261" s="22" t="n">
-        <v>30.38684440898463</v>
-      </c>
-      <c r="P261" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.55148427969094</v>
+      </c>
+      <c r="P261" s="20" t="n">
+        <v>-0.3648145389542678</v>
       </c>
       <c r="Q261" s="22" t="n">
-        <v>26.35181147857969</v>
+        <v>-5.50939003710083</v>
       </c>
       <c r="R261" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S261" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T261" s="15" t="inlineStr">
-        <is>
-          <t>Banking (100%)</t>
-        </is>
-      </c>
-      <c r="U261" s="17" t="inlineStr">
-        <is>
-          <t>Banking 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S261" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T261" s="15" t="n"/>
+      <c r="U261" s="17" t="n"/>
       <c r="V261" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W261" s="17" t="n"/>
-      <c r="X261" s="15" t="inlineStr">
-        <is>
-          <t>Banking +15%</t>
-        </is>
-      </c>
+      <c r="X261" s="15" t="n"/>
     </row>
     <row r="262" ht="16" customHeight="1">
       <c r="A262" s="13" t="n">
@@ -23182,12 +23184,12 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>TPET</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C262" s="15" t="inlineStr">
         <is>
-          <t>Trio Petroleum Corp</t>
+          <t>Hanmi Financial Corporation</t>
         </is>
       </c>
       <c r="D262" s="16" t="inlineStr">
@@ -23197,11 +23199,11 @@
       </c>
       <c r="E262" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F262" s="18" t="n">
-        <v>12850906</v>
+        <v>972469440</v>
       </c>
       <c r="G262" s="19" t="inlineStr">
         <is>
@@ -23209,32 +23211,28 @@
         </is>
       </c>
       <c r="H262" s="20" t="n">
-        <v>1.716</v>
-      </c>
-      <c r="I262" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.437587824860818</v>
+      </c>
+      <c r="I262" s="20" t="n">
+        <v>12.190297</v>
       </c>
       <c r="J262" s="20" t="n">
-        <v>0.34600717</v>
+        <v>1.2036252</v>
       </c>
       <c r="K262" s="20" t="n">
-        <v>18.488012</v>
+        <v>3.676925</v>
       </c>
       <c r="L262" s="22" t="n">
-        <v>-23.59537140805481</v>
-      </c>
-      <c r="M262" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.99772815882008</v>
+      </c>
+      <c r="M262" s="22" t="n">
+        <v>3.67615130332913</v>
       </c>
       <c r="N262" s="22" t="n">
-        <v>-27.73349846628827</v>
+        <v>14.10544231322912</v>
       </c>
       <c r="O262" s="22" t="n">
-        <v>0</v>
+        <v>30.38684440898463</v>
       </c>
       <c r="P262" s="21" t="inlineStr">
         <is>
@@ -23242,23 +23240,33 @@
         </is>
       </c>
       <c r="Q262" s="22" t="n">
-        <v>-81.41333394580417</v>
+        <v>26.35181147857969</v>
       </c>
       <c r="R262" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S262" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T262" s="15" t="n"/>
-      <c r="U262" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S262" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T262" s="15" t="inlineStr">
+        <is>
+          <t>Banking (100%)</t>
+        </is>
+      </c>
+      <c r="U262" s="17" t="inlineStr">
+        <is>
+          <t>Banking 100%</t>
+        </is>
+      </c>
       <c r="V262" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W262" s="17" t="n"/>
-      <c r="X262" s="15" t="n"/>
+      <c r="X262" s="15" t="inlineStr">
+        <is>
+          <t>Banking +15%</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="16" customHeight="1">
       <c r="A263" s="13" t="n">
@@ -23266,12 +23274,12 @@
       </c>
       <c r="B263" s="14" t="inlineStr">
         <is>
-          <t>AKBA</t>
+          <t>TPET</t>
         </is>
       </c>
       <c r="C263" s="15" t="inlineStr">
         <is>
-          <t>Akebia Therapeutics, Inc.</t>
+          <t>Trio Petroleum Corp</t>
         </is>
       </c>
       <c r="D263" s="16" t="inlineStr">
@@ -23281,11 +23289,11 @@
       </c>
       <c r="E263" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F263" s="18" t="n">
-        <v>305814400</v>
+        <v>12850906</v>
       </c>
       <c r="G263" s="19" t="inlineStr">
         <is>
@@ -23293,7 +23301,7 @@
         </is>
       </c>
       <c r="H263" s="20" t="n">
-        <v>28.087</v>
+        <v>1.716</v>
       </c>
       <c r="I263" s="21" t="inlineStr">
         <is>
@@ -23301,13 +23309,13 @@
         </is>
       </c>
       <c r="J263" s="20" t="n">
-        <v>11.176471</v>
+        <v>0.34600717</v>
       </c>
       <c r="K263" s="20" t="n">
-        <v>1.3158741</v>
+        <v>18.488012</v>
       </c>
       <c r="L263" s="22" t="n">
-        <v>21.06320195668403</v>
+        <v>-23.59537140805481</v>
       </c>
       <c r="M263" s="21" t="inlineStr">
         <is>
@@ -23315,42 +23323,34 @@
         </is>
       </c>
       <c r="N263" s="22" t="n">
-        <v>-20.3691903301605</v>
+        <v>-27.73349846628827</v>
       </c>
       <c r="O263" s="22" t="n">
-        <v>9.19871632034412</v>
-      </c>
-      <c r="P263" s="20" t="n">
-        <v>-6.123532931375708</v>
+        <v>0</v>
+      </c>
+      <c r="P263" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q263" s="22" t="n">
-        <v>-58.26771816145106</v>
+        <v>-81.41333394580417</v>
       </c>
       <c r="R263" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S263" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T263" s="15" t="inlineStr">
-        <is>
-          <t>Reportable (100%)</t>
-        </is>
-      </c>
-      <c r="U263" s="17" t="inlineStr">
-        <is>
-          <t>Reportable 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S263" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T263" s="15" t="n"/>
+      <c r="U263" s="17" t="n"/>
       <c r="V263" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W263" s="17" t="n"/>
-      <c r="X263" s="15" t="inlineStr">
-        <is>
-          <t>Reportable +47%</t>
-        </is>
-      </c>
+      <c r="X263" s="15" t="n"/>
     </row>
     <row r="264" ht="16" customHeight="1">
       <c r="A264" s="13" t="n">
@@ -23358,12 +23358,12 @@
       </c>
       <c r="B264" s="14" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>AKBA</t>
         </is>
       </c>
       <c r="C264" s="15" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Akebia Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D264" s="16" t="inlineStr">
@@ -23373,11 +23373,11 @@
       </c>
       <c r="E264" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F264" s="18" t="n">
-        <v>290289216</v>
+        <v>305814400</v>
       </c>
       <c r="G264" s="19" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="H264" s="20" t="n">
-        <v>1.938</v>
+        <v>28.087</v>
       </c>
       <c r="I264" s="21" t="inlineStr">
         <is>
@@ -23393,54 +23393,56 @@
         </is>
       </c>
       <c r="J264" s="20" t="n">
-        <v>0.5912596</v>
+        <v>11.176471</v>
       </c>
       <c r="K264" s="20" t="n">
-        <v>2.465071</v>
+        <v>1.3158741</v>
       </c>
       <c r="L264" s="22" t="n">
-        <v>-19.25127525233317</v>
+        <v>21.06320195668403</v>
       </c>
       <c r="M264" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N264" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N264" s="22" t="n">
+        <v>-20.3691903301605</v>
       </c>
       <c r="O264" s="22" t="n">
-        <v>-117.0241221433662</v>
-      </c>
-      <c r="P264" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.19871632034412</v>
+      </c>
+      <c r="P264" s="20" t="n">
+        <v>-6.123532931375708</v>
       </c>
       <c r="Q264" s="22" t="n">
-        <v>-2.54167440699175</v>
+        <v>-58.26771816145106</v>
       </c>
       <c r="R264" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S264" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T264" s="15" t="inlineStr">
+        <is>
+          <t>Reportable (100%)</t>
+        </is>
+      </c>
+      <c r="U264" s="17" t="inlineStr">
+        <is>
+          <t>Reportable 100%</t>
+        </is>
+      </c>
+      <c r="V264" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S264" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T264" s="15" t="n"/>
-      <c r="U264" s="17" t="n"/>
-      <c r="V264" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W264" s="17" t="inlineStr">
-        <is>
-          <t>Americas 44%; EMEA 40%; Asia Pacific 16%</t>
-        </is>
-      </c>
-      <c r="X264" s="15" t="n"/>
+      <c r="W264" s="17" t="n"/>
+      <c r="X264" s="15" t="inlineStr">
+        <is>
+          <t>Reportable +47%</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="16" customHeight="1">
       <c r="A265" s="13" t="n">
@@ -23448,12 +23450,12 @@
       </c>
       <c r="B265" s="14" t="inlineStr">
         <is>
-          <t>GHG</t>
+          <t>NNDM</t>
         </is>
       </c>
       <c r="C265" s="15" t="inlineStr">
         <is>
-          <t>Greentree Hospitality Group Lt</t>
+          <t>Nano Dimension Ltd.</t>
         </is>
       </c>
       <c r="D265" s="16" t="inlineStr">
@@ -23463,11 +23465,11 @@
       </c>
       <c r="E265" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F265" s="18" t="n">
-        <v>114003888</v>
+        <v>290289216</v>
       </c>
       <c r="G265" s="19" t="inlineStr">
         <is>
@@ -23475,60 +23477,62 @@
         </is>
       </c>
       <c r="H265" s="20" t="n">
-        <v>-2.258489766586047</v>
-      </c>
-      <c r="I265" s="20" t="n">
-        <v>4.7079167</v>
+        <v>1.938</v>
+      </c>
+      <c r="I265" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J265" s="20" t="n">
-        <v>0.4910807</v>
+        <v>0.5912596</v>
       </c>
       <c r="K265" s="20" t="n">
-        <v>0.10388986</v>
+        <v>2.465071</v>
       </c>
       <c r="L265" s="22" t="n">
-        <v>2.52369024466955</v>
-      </c>
-      <c r="M265" s="22" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="N265" s="22" t="n">
-        <v>23.86689445916182</v>
+        <v>-19.25127525233317</v>
+      </c>
+      <c r="M265" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N265" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O265" s="22" t="n">
-        <v>12.44580913896663</v>
-      </c>
-      <c r="P265" s="20" t="n">
-        <v>-9.805486307018036</v>
+        <v>-117.0241221433662</v>
+      </c>
+      <c r="P265" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q265" s="22" t="n">
-        <v>-46.44549519371849</v>
+        <v>-2.54167440699175</v>
       </c>
       <c r="R265" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S265" s="20" t="n">
-        <v>0.429524466410785</v>
-      </c>
-      <c r="T265" s="15" t="inlineStr">
-        <is>
-          <t>Revenue From External  (50%)</t>
-        </is>
-      </c>
-      <c r="U265" s="17" t="inlineStr">
-        <is>
-          <t>Revenue From External Customers 50%; Hotel Business 42%; Restaurant Business 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S265" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T265" s="15" t="n"/>
+      <c r="U265" s="17" t="n"/>
       <c r="V265" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W265" s="17" t="n"/>
-      <c r="X265" s="15" t="inlineStr">
-        <is>
-          <t>Hotel Business -88%</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W265" s="17" t="inlineStr">
+        <is>
+          <t>Americas 44%; EMEA 40%; Asia Pacific 16%</t>
+        </is>
+      </c>
+      <c r="X265" s="15" t="n"/>
     </row>
     <row r="266" ht="16" customHeight="1">
       <c r="A266" s="13" t="n">
@@ -23536,12 +23540,12 @@
       </c>
       <c r="B266" s="14" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>GHG</t>
         </is>
       </c>
       <c r="C266" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provident Financial Holdings, </t>
+          <t>Greentree Hospitality Group Lt</t>
         </is>
       </c>
       <c r="D266" s="16" t="inlineStr">
@@ -23551,68 +23555,72 @@
       </c>
       <c r="E266" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F266" s="18" t="n">
-        <v>107563488</v>
+        <v>114003888</v>
       </c>
       <c r="G266" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H266" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H266" s="20" t="n">
+        <v>-2.258489766586047</v>
       </c>
       <c r="I266" s="20" t="n">
-        <v>18.494625</v>
+        <v>4.7079167</v>
       </c>
       <c r="J266" s="20" t="n">
-        <v>0.8592697</v>
+        <v>0.4910807</v>
       </c>
       <c r="K266" s="20" t="n">
-        <v>2.7159069</v>
+        <v>0.10388986</v>
       </c>
       <c r="L266" s="22" t="n">
-        <v>8.407967835537141</v>
+        <v>2.52369024466955</v>
       </c>
       <c r="M266" s="22" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N266" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.31</v>
+      </c>
+      <c r="N266" s="22" t="n">
+        <v>23.86689445916182</v>
       </c>
       <c r="O266" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P266" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.44580913896663</v>
+      </c>
+      <c r="P266" s="20" t="n">
+        <v>-9.805486307018036</v>
       </c>
       <c r="Q266" s="22" t="n">
-        <v>13.3670912336621</v>
+        <v>-46.44549519371849</v>
       </c>
       <c r="R266" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S266" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T266" s="15" t="n"/>
-      <c r="U266" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="S266" s="20" t="n">
+        <v>0.429524466410785</v>
+      </c>
+      <c r="T266" s="15" t="inlineStr">
+        <is>
+          <t>Revenue From External  (50%)</t>
+        </is>
+      </c>
+      <c r="U266" s="17" t="inlineStr">
+        <is>
+          <t>Revenue From External Customers 50%; Hotel Business 42%; Restaurant Business 8%</t>
+        </is>
+      </c>
       <c r="V266" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W266" s="17" t="n"/>
-      <c r="X266" s="15" t="n"/>
+      <c r="X266" s="15" t="inlineStr">
+        <is>
+          <t>Hotel Business -88%</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="16" customHeight="1">
       <c r="A267" s="13" t="n">
@@ -23620,12 +23628,12 @@
       </c>
       <c r="B267" s="14" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="C267" s="15" t="inlineStr">
         <is>
-          <t>Eagle Bancorp, Inc.</t>
+          <t xml:space="preserve">Provident Financial Holdings, </t>
         </is>
       </c>
       <c r="D267" s="16" t="inlineStr">
@@ -23639,7 +23647,7 @@
         </is>
       </c>
       <c r="F267" s="18" t="n">
-        <v>888337280</v>
+        <v>107563488</v>
       </c>
       <c r="G267" s="19" t="inlineStr">
         <is>
@@ -23651,22 +23659,20 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I267" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I267" s="20" t="n">
+        <v>18.494625</v>
       </c>
       <c r="J267" s="20" t="n">
-        <v>0.77562106</v>
+        <v>0.8592697</v>
       </c>
       <c r="K267" s="20" t="n">
-        <v>41.56547</v>
+        <v>2.7159069</v>
       </c>
       <c r="L267" s="22" t="n">
-        <v>2.78226065129031</v>
+        <v>8.407967835537141</v>
       </c>
       <c r="M267" s="22" t="n">
-        <v>0.67000003</v>
+        <v>3.26</v>
       </c>
       <c r="N267" s="21" t="inlineStr">
         <is>
@@ -23682,7 +23688,7 @@
         </is>
       </c>
       <c r="Q267" s="22" t="n">
-        <v>29.46670442220106</v>
+        <v>13.3670912336621</v>
       </c>
       <c r="R267" s="18" t="n">
         <v>0</v>
@@ -23706,12 +23712,12 @@
       </c>
       <c r="B268" s="14" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C268" s="15" t="inlineStr">
         <is>
-          <t>NetSol Technologies, Inc.</t>
+          <t>Eagle Bancorp, Inc.</t>
         </is>
       </c>
       <c r="D268" s="16" t="inlineStr">
@@ -23721,76 +23727,70 @@
       </c>
       <c r="E268" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F268" s="18" t="n">
-        <v>54156448</v>
+        <v>888337280</v>
       </c>
       <c r="G268" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H268" s="20" t="n">
-        <v>8.028</v>
-      </c>
-      <c r="I268" s="20" t="n">
-        <v>30.399998</v>
+      <c r="H268" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I268" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J268" s="20" t="n">
-        <v>1.4531548</v>
+        <v>0.77562106</v>
       </c>
       <c r="K268" s="20" t="n">
-        <v>0.7515241</v>
+        <v>41.56547</v>
       </c>
       <c r="L268" s="22" t="n">
-        <v>23.63076201077865</v>
+        <v>2.78226065129031</v>
       </c>
       <c r="M268" s="22" t="n">
-        <v>0.63160459216738</v>
-      </c>
-      <c r="N268" s="22" t="n">
-        <v>17.62031993223545</v>
+        <v>0.67000003</v>
+      </c>
+      <c r="N268" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O268" s="22" t="n">
-        <v>11.42576524536094</v>
-      </c>
-      <c r="P268" s="20" t="n">
-        <v>-1.044695203416191</v>
+        <v>0</v>
+      </c>
+      <c r="P268" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q268" s="22" t="n">
-        <v>44.01409423225983</v>
+        <v>29.46670442220106</v>
       </c>
       <c r="R268" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S268" s="20" t="n">
-        <v>0.669742156156933</v>
-      </c>
-      <c r="T268" s="15" t="inlineStr">
-        <is>
-          <t>Europe Country (81%)</t>
-        </is>
-      </c>
-      <c r="U268" s="17" t="inlineStr">
-        <is>
-          <t>Europe Country 81%; Asia Pacific Region 13%; North America Country 7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S268" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T268" s="15" t="n"/>
+      <c r="U268" s="17" t="n"/>
       <c r="V268" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W268" s="17" t="inlineStr">
-        <is>
-          <t>CN 26%; GB 22%; US 16%</t>
-        </is>
-      </c>
-      <c r="X268" s="15" t="inlineStr">
-        <is>
-          <t>Asia Pacific Region +40%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W268" s="17" t="n"/>
+      <c r="X268" s="15" t="n"/>
     </row>
     <row r="269" ht="16" customHeight="1">
       <c r="A269" s="13" t="n">
@@ -23798,12 +23798,12 @@
       </c>
       <c r="B269" s="14" t="inlineStr">
         <is>
-          <t>TRAK</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C269" s="15" t="inlineStr">
         <is>
-          <t>Repositrak, Inc.</t>
+          <t>NetSol Technologies, Inc.</t>
         </is>
       </c>
       <c r="D269" s="16" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="F269" s="18" t="n">
-        <v>167015040</v>
+        <v>54156448</v>
       </c>
       <c r="G269" s="19" t="inlineStr">
         <is>
@@ -23825,50 +23825,64 @@
         </is>
       </c>
       <c r="H269" s="20" t="n">
-        <v>17.205</v>
+        <v>8.028</v>
       </c>
       <c r="I269" s="20" t="n">
-        <v>24.837837</v>
+        <v>30.399998</v>
       </c>
       <c r="J269" s="20" t="n">
-        <v>3.308135</v>
+        <v>1.4531548</v>
       </c>
       <c r="K269" s="20" t="n">
-        <v>7.115574</v>
+        <v>0.7515241</v>
       </c>
       <c r="L269" s="22" t="n">
-        <v>4.01658976341292</v>
+        <v>23.63076201077865</v>
       </c>
       <c r="M269" s="22" t="n">
-        <v>0.8699999999999999</v>
+        <v>0.63160459216738</v>
       </c>
       <c r="N269" s="22" t="n">
-        <v>32.2653613392671</v>
+        <v>17.62031993223545</v>
       </c>
       <c r="O269" s="22" t="n">
-        <v>36.66715653889693</v>
+        <v>11.42576524536094</v>
       </c>
       <c r="P269" s="20" t="n">
-        <v>-2.653272610335161</v>
+        <v>-1.044695203416191</v>
       </c>
       <c r="Q269" s="22" t="n">
-        <v>-53.73035208751867</v>
+        <v>44.01409423225983</v>
       </c>
       <c r="R269" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S269" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T269" s="15" t="n"/>
-      <c r="U269" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="S269" s="20" t="n">
+        <v>0.669742156156933</v>
+      </c>
+      <c r="T269" s="15" t="inlineStr">
+        <is>
+          <t>Europe Country (81%)</t>
+        </is>
+      </c>
+      <c r="U269" s="17" t="inlineStr">
+        <is>
+          <t>Europe Country 81%; Asia Pacific Region 13%; North America Country 7%</t>
+        </is>
+      </c>
       <c r="V269" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W269" s="17" t="n"/>
-      <c r="X269" s="15" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="W269" s="17" t="inlineStr">
+        <is>
+          <t>CN 26%; GB 22%; US 16%</t>
+        </is>
+      </c>
+      <c r="X269" s="15" t="inlineStr">
+        <is>
+          <t>Asia Pacific Region +40%</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="16" customHeight="1">
       <c r="A270" s="13" t="n">
@@ -23876,12 +23890,12 @@
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TRAK</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
         <is>
-          <t>Chagee Holdings Ltd.</t>
+          <t>Repositrak, Inc.</t>
         </is>
       </c>
       <c r="D270" s="16" t="inlineStr">
@@ -23891,11 +23905,11 @@
       </c>
       <c r="E270" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F270" s="18" t="n">
-        <v>2315866880</v>
+        <v>167015040</v>
       </c>
       <c r="G270" s="19" t="inlineStr">
         <is>
@@ -23903,36 +23917,34 @@
         </is>
       </c>
       <c r="H270" s="20" t="n">
-        <v>-18.82014472994232</v>
+        <v>17.205</v>
       </c>
       <c r="I270" s="20" t="n">
-        <v>16.630136</v>
+        <v>24.837837</v>
       </c>
       <c r="J270" s="20" t="n">
-        <v>2.0134957</v>
+        <v>3.308135</v>
       </c>
       <c r="K270" s="20" t="n">
-        <v>0.17731571</v>
+        <v>7.115574</v>
       </c>
       <c r="L270" s="22" t="n">
-        <v>7.57638539223808</v>
-      </c>
-      <c r="M270" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.01658976341292</v>
+      </c>
+      <c r="M270" s="22" t="n">
+        <v>0.8699999999999999</v>
       </c>
       <c r="N270" s="22" t="n">
-        <v>85.72643403189771</v>
+        <v>32.2653613392671</v>
       </c>
       <c r="O270" s="22" t="n">
-        <v>11.57176494554469</v>
+        <v>36.66715653889693</v>
       </c>
       <c r="P270" s="20" t="n">
-        <v>-5.999493363518522</v>
+        <v>-2.653272610335161</v>
       </c>
       <c r="Q270" s="22" t="n">
-        <v>-50.65640095101563</v>
+        <v>-53.73035208751867</v>
       </c>
       <c r="R270" s="18" t="n">
         <v>0</v>
@@ -23956,12 +23968,12 @@
       </c>
       <c r="B271" s="14" t="inlineStr">
         <is>
-          <t>LENZ</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C271" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LENZ Therapeutics Inc. Common </t>
+          <t>Chagee Holdings Ltd.</t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
@@ -23971,11 +23983,11 @@
       </c>
       <c r="E271" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F271" s="18" t="n">
-        <v>230141264</v>
+        <v>2315866880</v>
       </c>
       <c r="G271" s="19" t="inlineStr">
         <is>
@@ -23983,68 +23995,52 @@
         </is>
       </c>
       <c r="H271" s="20" t="n">
-        <v>0.6757298873980474</v>
-      </c>
-      <c r="I271" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-18.82014472994232</v>
+      </c>
+      <c r="I271" s="20" t="n">
+        <v>16.630136</v>
       </c>
       <c r="J271" s="20" t="n">
-        <v>0.809390424809822</v>
+        <v>2.0134957</v>
       </c>
       <c r="K271" s="20" t="n">
-        <v>12.05685582564962</v>
+        <v>0.17731571</v>
       </c>
       <c r="L271" s="22" t="n">
-        <v>-30.41479775656399</v>
+        <v>7.57638539223808</v>
       </c>
       <c r="M271" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N271" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N271" s="22" t="n">
+        <v>85.72643403189771</v>
       </c>
       <c r="O271" s="22" t="n">
-        <v>-475.9587175188601</v>
-      </c>
-      <c r="P271" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.57176494554469</v>
+      </c>
+      <c r="P271" s="20" t="n">
+        <v>-5.999493363518522</v>
       </c>
       <c r="Q271" s="22" t="n">
-        <v>-73.15288913086155</v>
+        <v>-50.65640095101563</v>
       </c>
       <c r="R271" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S271" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T271" s="15" t="inlineStr">
-        <is>
-          <t>Reportable (100%)</t>
-        </is>
-      </c>
-      <c r="U271" s="17" t="inlineStr">
-        <is>
-          <t>Reportable 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S271" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T271" s="15" t="n"/>
+      <c r="U271" s="17" t="n"/>
       <c r="V271" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W271" s="17" t="n"/>
-      <c r="X271" s="15" t="inlineStr">
-        <is>
-          <t>Reportable +10%</t>
-        </is>
-      </c>
+      <c r="X271" s="15" t="n"/>
     </row>
     <row r="272" ht="16" customHeight="1">
       <c r="A272" s="13" t="n">
@@ -24052,12 +24048,12 @@
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>LENZ</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
         <is>
-          <t>Coffee Holding Co., Inc.</t>
+          <t xml:space="preserve">LENZ Therapeutics Inc. Common </t>
         </is>
       </c>
       <c r="D272" s="16" t="inlineStr">
@@ -24067,11 +24063,11 @@
       </c>
       <c r="E272" s="17" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F272" s="18" t="n">
-        <v>19123810</v>
+        <v>230141264</v>
       </c>
       <c r="G272" s="19" t="inlineStr">
         <is>
@@ -24079,34 +24075,42 @@
         </is>
       </c>
       <c r="H272" s="20" t="n">
-        <v>6.732</v>
-      </c>
-      <c r="I272" s="20" t="n">
-        <v>12.407407</v>
+        <v>0.6757298873980474</v>
+      </c>
+      <c r="I272" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J272" s="20" t="n">
-        <v>0.6649464</v>
+        <v>0.809390424809822</v>
       </c>
       <c r="K272" s="20" t="n">
-        <v>0.1924889</v>
+        <v>12.05685582564962</v>
       </c>
       <c r="L272" s="22" t="n">
-        <v>42.03289398842584</v>
-      </c>
-      <c r="M272" s="22" t="n">
-        <v>2.3608044636242</v>
-      </c>
-      <c r="N272" s="22" t="n">
-        <v>14.9836891396905</v>
+        <v>-30.41479775656399</v>
+      </c>
+      <c r="M272" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N272" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O272" s="22" t="n">
-        <v>4.4448932469455</v>
-      </c>
-      <c r="P272" s="20" t="n">
-        <v>0.4654342573568866</v>
+        <v>-475.9587175188601</v>
+      </c>
+      <c r="P272" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q272" s="22" t="n">
-        <v>25.28308922858965</v>
+        <v>-73.15288913086155</v>
       </c>
       <c r="R272" s="18" t="n">
         <v>1</v>
@@ -24116,12 +24120,12 @@
       </c>
       <c r="T272" s="15" t="inlineStr">
         <is>
-          <t>Operating (100%)</t>
+          <t>Reportable (100%)</t>
         </is>
       </c>
       <c r="U272" s="17" t="inlineStr">
         <is>
-          <t>Operating 100%</t>
+          <t>Reportable 100%</t>
         </is>
       </c>
       <c r="V272" s="18" t="n">
@@ -24130,7 +24134,7 @@
       <c r="W272" s="17" t="n"/>
       <c r="X272" s="15" t="inlineStr">
         <is>
-          <t>Operating +23%</t>
+          <t>Reportable +10%</t>
         </is>
       </c>
     </row>
@@ -24140,26 +24144,26 @@
       </c>
       <c r="B273" s="14" t="inlineStr">
         <is>
-          <t>LAES</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C273" s="15" t="inlineStr">
         <is>
-          <t>SEALSQ Corp Ordinary Shares</t>
+          <t>Coffee Holding Co., Inc.</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E273" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F273" s="18" t="n">
-        <v>603717568</v>
+        <v>19123810</v>
       </c>
       <c r="G273" s="19" t="inlineStr">
         <is>
@@ -24167,68 +24171,58 @@
         </is>
       </c>
       <c r="H273" s="20" t="n">
-        <v>-3.5408472509913</v>
-      </c>
-      <c r="I273" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.732</v>
+      </c>
+      <c r="I273" s="20" t="n">
+        <v>12.407407</v>
       </c>
       <c r="J273" s="20" t="n">
-        <v>1.308141067977153</v>
+        <v>0.6649464</v>
       </c>
       <c r="K273" s="20" t="n">
-        <v>33.07678983125137</v>
+        <v>0.1924889</v>
       </c>
       <c r="L273" s="22" t="n">
-        <v>-5.38331195291636</v>
-      </c>
-      <c r="M273" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>42.03289398842584</v>
+      </c>
+      <c r="M273" s="22" t="n">
+        <v>2.3608044636242</v>
       </c>
       <c r="N273" s="22" t="n">
-        <v>-87.41461486085792</v>
+        <v>14.9836891396905</v>
       </c>
       <c r="O273" s="22" t="n">
-        <v>-214.2011834319526</v>
-      </c>
-      <c r="P273" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.4448932469455</v>
+      </c>
+      <c r="P273" s="20" t="n">
+        <v>0.4654342573568866</v>
       </c>
       <c r="Q273" s="22" t="n">
-        <v>-25.34435391982463</v>
+        <v>25.28308922858965</v>
       </c>
       <c r="R273" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S273" s="20" t="n">
-        <v>0.4229554701846919</v>
+        <v>1</v>
       </c>
       <c r="T273" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (51%)</t>
+          <t>Operating (100%)</t>
         </is>
       </c>
       <c r="U273" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 51%; Semiconductors 40%; A</t>
+          <t>Operating 100%</t>
         </is>
       </c>
       <c r="V273" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W273" s="17" t="inlineStr">
-        <is>
-          <t>North America 57%; EMEA 24%; Asia Pacific 18%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W273" s="17" t="n"/>
       <c r="X273" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment A +71%</t>
+          <t>Operating +23%</t>
         </is>
       </c>
     </row>
@@ -24238,26 +24232,26 @@
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>LAES</t>
         </is>
       </c>
       <c r="C274" s="15" t="inlineStr">
         <is>
-          <t>Summit Midstream Corporation C</t>
+          <t>SEALSQ Corp Ordinary Shares</t>
         </is>
       </c>
       <c r="D274" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E274" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F274" s="18" t="n">
-        <v>408350272</v>
+        <v>603717568</v>
       </c>
       <c r="G274" s="19" t="inlineStr">
         <is>
@@ -24265,7 +24259,7 @@
         </is>
       </c>
       <c r="H274" s="20" t="n">
-        <v>10.058</v>
+        <v>-3.5408472509913</v>
       </c>
       <c r="I274" s="21" t="inlineStr">
         <is>
@@ -24273,13 +24267,13 @@
         </is>
       </c>
       <c r="J274" s="20" t="n">
-        <v>0.8319027</v>
+        <v>1.308141067977153</v>
       </c>
       <c r="K274" s="20" t="n">
-        <v>0.7170657</v>
+        <v>33.07678983125137</v>
       </c>
       <c r="L274" s="22" t="n">
-        <v>10.03778223667121</v>
+        <v>-5.38331195291636</v>
       </c>
       <c r="M274" s="21" t="inlineStr">
         <is>
@@ -24287,40 +24281,46 @@
         </is>
       </c>
       <c r="N274" s="22" t="n">
-        <v>5.83452766424261</v>
+        <v>-87.41461486085792</v>
       </c>
       <c r="O274" s="22" t="n">
-        <v>36.9029214130808</v>
-      </c>
-      <c r="P274" s="20" t="n">
-        <v>4.995931118267544</v>
+        <v>-214.2011834319526</v>
+      </c>
+      <c r="P274" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q274" s="22" t="n">
-        <v>9.063143471208871</v>
+        <v>-25.34435391982463</v>
       </c>
       <c r="R274" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S274" s="20" t="n">
+        <v>0.4229554701846919</v>
+      </c>
+      <c r="T274" s="15" t="inlineStr">
+        <is>
+          <t>Reportable Segment Agg (51%)</t>
+        </is>
+      </c>
+      <c r="U274" s="17" t="inlineStr">
+        <is>
+          <t>Reportable Segment Aggregation Before Other Operating 51%; Semiconductors 40%; A</t>
+        </is>
+      </c>
+      <c r="V274" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S274" s="20" t="n">
-        <v>0.4390669204993302</v>
-      </c>
-      <c r="T274" s="15" t="inlineStr">
-        <is>
-          <t>Rockies (59%)</t>
-        </is>
-      </c>
-      <c r="U274" s="17" t="inlineStr">
-        <is>
-          <t>Rockies 59%; Mid Con Barnett Shale 28%; Piceance Basin 12%</t>
-        </is>
-      </c>
-      <c r="V274" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W274" s="17" t="n"/>
+      <c r="W274" s="17" t="inlineStr">
+        <is>
+          <t>North America 57%; EMEA 24%; Asia Pacific 18%</t>
+        </is>
+      </c>
       <c r="X274" s="15" t="inlineStr">
         <is>
-          <t>Mid Con Barnett Shal +180%</t>
+          <t>Reportable Segment A +71%</t>
         </is>
       </c>
     </row>
@@ -24330,12 +24330,12 @@
       </c>
       <c r="B275" s="14" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="C275" s="15" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Summit Midstream Corporation C</t>
         </is>
       </c>
       <c r="D275" s="16" t="inlineStr">
@@ -24345,11 +24345,11 @@
       </c>
       <c r="E275" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F275" s="18" t="n">
-        <v>4215082496</v>
+        <v>408350272</v>
       </c>
       <c r="G275" s="19" t="inlineStr">
         <is>
@@ -24357,19 +24357,21 @@
         </is>
       </c>
       <c r="H275" s="20" t="n">
-        <v>4.739</v>
-      </c>
-      <c r="I275" s="20" t="n">
-        <v>11.591954</v>
+        <v>10.058</v>
+      </c>
+      <c r="I275" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J275" s="20" t="n">
-        <v>1.2405436</v>
+        <v>0.8319027</v>
       </c>
       <c r="K275" s="20" t="n">
-        <v>0.75873274</v>
+        <v>0.7170657</v>
       </c>
       <c r="L275" s="22" t="n">
-        <v>3.04209736677507</v>
+        <v>10.03778223667121</v>
       </c>
       <c r="M275" s="21" t="inlineStr">
         <is>
@@ -24377,44 +24379,40 @@
         </is>
       </c>
       <c r="N275" s="22" t="n">
-        <v>19.02852891767159</v>
+        <v>5.83452766424261</v>
       </c>
       <c r="O275" s="22" t="n">
-        <v>12.67463785398956</v>
+        <v>36.9029214130808</v>
       </c>
       <c r="P275" s="20" t="n">
-        <v>-1.063746751310127</v>
+        <v>4.995931118267544</v>
       </c>
       <c r="Q275" s="22" t="n">
-        <v>-43.14897876018519</v>
+        <v>9.063143471208871</v>
       </c>
       <c r="R275" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S275" s="20" t="n">
-        <v>0.6871057761739574</v>
+        <v>0.4390669204993302</v>
       </c>
       <c r="T275" s="15" t="inlineStr">
         <is>
-          <t>Americas (81%)</t>
+          <t>Rockies (59%)</t>
         </is>
       </c>
       <c r="U275" s="17" t="inlineStr">
         <is>
-          <t>Americas 81%; Europe 19%</t>
+          <t>Rockies 59%; Mid Con Barnett Shale 28%; Piceance Basin 12%</t>
         </is>
       </c>
       <c r="V275" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W275" s="17" t="inlineStr">
-        <is>
-          <t>Americas 20%; North America 19%; US 17%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W275" s="17" t="n"/>
       <c r="X275" s="15" t="inlineStr">
         <is>
-          <t>Americas +1%</t>
+          <t>Mid Con Barnett Shal +180%</t>
         </is>
       </c>
     </row>
@@ -24424,12 +24422,12 @@
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>WSBC</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C276" s="15" t="inlineStr">
         <is>
-          <t>WesBanco, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D276" s="16" t="inlineStr">
@@ -24439,76 +24437,76 @@
       </c>
       <c r="E276" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F276" s="18" t="n">
-        <v>3731805696</v>
+        <v>4215082496</v>
       </c>
       <c r="G276" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H276" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H276" s="20" t="n">
+        <v>4.739</v>
       </c>
       <c r="I276" s="20" t="n">
-        <v>11.90184</v>
+        <v>11.591954</v>
       </c>
       <c r="J276" s="20" t="n">
-        <v>0.9697332400000001</v>
+        <v>1.2405436</v>
       </c>
       <c r="K276" s="20" t="n">
-        <v>3.5964322</v>
+        <v>0.75873274</v>
       </c>
       <c r="L276" s="22" t="n">
-        <v>12.55457183695235</v>
-      </c>
-      <c r="M276" s="22" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="N276" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.04209736677507</v>
+      </c>
+      <c r="M276" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N276" s="22" t="n">
+        <v>19.02852891767159</v>
       </c>
       <c r="O276" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P276" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.67463785398956</v>
+      </c>
+      <c r="P276" s="20" t="n">
+        <v>-1.063746751310127</v>
       </c>
       <c r="Q276" s="22" t="n">
-        <v>18.52732332607427</v>
+        <v>-43.14897876018519</v>
       </c>
       <c r="R276" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S276" s="20" t="n">
-        <v>0.93390832547567</v>
+        <v>0.6871057761739574</v>
       </c>
       <c r="T276" s="15" t="inlineStr">
         <is>
-          <t>Community Banking (97%)</t>
+          <t>Americas (81%)</t>
         </is>
       </c>
       <c r="U276" s="17" t="inlineStr">
         <is>
-          <t>Community Banking 97%; Trust And Investment Services 3%</t>
+          <t>Americas 81%; Europe 19%</t>
         </is>
       </c>
       <c r="V276" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W276" s="17" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="W276" s="17" t="inlineStr">
+        <is>
+          <t>Americas 20%; North America 19%; US 17%</t>
+        </is>
+      </c>
       <c r="X276" s="15" t="inlineStr">
         <is>
-          <t>Community Banking +55%</t>
+          <t>Americas +1%</t>
         </is>
       </c>
     </row>
@@ -24518,12 +24516,12 @@
       </c>
       <c r="B277" s="14" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>WSBC</t>
         </is>
       </c>
       <c r="C277" s="15" t="inlineStr">
         <is>
-          <t>Skycorp Solar Group Limited</t>
+          <t>WesBanco, Inc.</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
@@ -24533,44 +24531,44 @@
       </c>
       <c r="E277" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F277" s="18" t="n">
-        <v>51708092</v>
+        <v>3731805696</v>
       </c>
       <c r="G277" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H277" s="20" t="n">
-        <v>-8.059603435542593</v>
-      </c>
-      <c r="I277" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H277" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I277" s="20" t="n">
+        <v>11.90184</v>
       </c>
       <c r="J277" s="20" t="n">
-        <v>0.25254583</v>
+        <v>0.9697332400000001</v>
       </c>
       <c r="K277" s="20" t="n">
-        <v>0.816729</v>
+        <v>3.5964322</v>
       </c>
       <c r="L277" s="22" t="n">
-        <v>4.6561048897337</v>
-      </c>
-      <c r="M277" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N277" s="22" t="n">
-        <v>-24.17948316363512</v>
+        <v>12.55457183695235</v>
+      </c>
+      <c r="M277" s="22" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N277" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O277" s="22" t="n">
-        <v>-3.42902383332009</v>
+        <v>0</v>
       </c>
       <c r="P277" s="21" t="inlineStr">
         <is>
@@ -24578,27 +24576,33 @@
         </is>
       </c>
       <c r="Q277" s="22" t="n">
-        <v>-92.81853265752804</v>
+        <v>18.52732332607427</v>
       </c>
       <c r="R277" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S277" s="20" t="n">
+        <v>0.93390832547567</v>
+      </c>
+      <c r="T277" s="15" t="inlineStr">
+        <is>
+          <t>Community Banking (97%)</t>
+        </is>
+      </c>
+      <c r="U277" s="17" t="inlineStr">
+        <is>
+          <t>Community Banking 97%; Trust And Investment Services 3%</t>
+        </is>
+      </c>
+      <c r="V277" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S277" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T277" s="15" t="n"/>
-      <c r="U277" s="17" t="n"/>
-      <c r="V277" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W277" s="17" t="inlineStr">
-        <is>
-          <t>CN 62%; Asia 23%; Other 15%</t>
-        </is>
-      </c>
-      <c r="X277" s="15" t="n"/>
+      <c r="W277" s="17" t="n"/>
+      <c r="X277" s="15" t="inlineStr">
+        <is>
+          <t>Community Banking +55%</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="16" customHeight="1">
       <c r="A278" s="13" t="n">
@@ -24606,26 +24610,26 @@
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>NBP</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C278" s="15" t="inlineStr">
         <is>
-          <t>NovaBridge Biosciences America</t>
+          <t>Skycorp Solar Group Limited</t>
         </is>
       </c>
       <c r="D278" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E278" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F278" s="18" t="n">
-        <v>215106224</v>
+        <v>51708092</v>
       </c>
       <c r="G278" s="19" t="inlineStr">
         <is>
@@ -24633,7 +24637,7 @@
         </is>
       </c>
       <c r="H278" s="20" t="n">
-        <v>-0.1274247897950702</v>
+        <v>-8.059603435542593</v>
       </c>
       <c r="I278" s="21" t="inlineStr">
         <is>
@@ -24641,26 +24645,24 @@
         </is>
       </c>
       <c r="J278" s="20" t="n">
-        <v>0.931433673535665</v>
+        <v>0.25254583</v>
       </c>
       <c r="K278" s="20" t="n">
-        <v>55.25461700488056</v>
+        <v>0.816729</v>
       </c>
       <c r="L278" s="22" t="n">
-        <v>-9.578523399676241</v>
+        <v>4.6561048897337</v>
       </c>
       <c r="M278" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N278" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N278" s="22" t="n">
+        <v>-24.17948316363512</v>
       </c>
       <c r="O278" s="22" t="n">
-        <v>-2419.753403544824</v>
+        <v>-3.42902383332009</v>
       </c>
       <c r="P278" s="21" t="inlineStr">
         <is>
@@ -24668,28 +24670,26 @@
         </is>
       </c>
       <c r="Q278" s="22" t="n">
-        <v>-12.67606035817856</v>
+        <v>-92.81853265752804</v>
       </c>
       <c r="R278" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S278" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T278" s="15" t="inlineStr">
-        <is>
-          <t>Oncology (100%)</t>
-        </is>
-      </c>
-      <c r="U278" s="17" t="inlineStr">
-        <is>
-          <t>Oncology 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S278" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T278" s="15" t="n"/>
+      <c r="U278" s="17" t="n"/>
       <c r="V278" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W278" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W278" s="17" t="inlineStr">
+        <is>
+          <t>CN 62%; Asia 23%; Other 15%</t>
+        </is>
+      </c>
       <c r="X278" s="15" t="n"/>
     </row>
     <row r="279" ht="16" customHeight="1">
@@ -24698,26 +24698,26 @@
       </c>
       <c r="B279" s="14" t="inlineStr">
         <is>
-          <t>MHH</t>
+          <t>NBP</t>
         </is>
       </c>
       <c r="C279" s="15" t="inlineStr">
         <is>
-          <t>Mastech Digital, Inc.</t>
+          <t>NovaBridge Biosciences America</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E279" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F279" s="18" t="n">
-        <v>92506016</v>
+        <v>215106224</v>
       </c>
       <c r="G279" s="19" t="inlineStr">
         <is>
@@ -24725,66 +24725,64 @@
         </is>
       </c>
       <c r="H279" s="20" t="n">
-        <v>10.015</v>
-      </c>
-      <c r="I279" s="20" t="n">
-        <v>40.57895</v>
+        <v>-0.1274247897950702</v>
+      </c>
+      <c r="I279" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J279" s="20" t="n">
-        <v>1.0158103</v>
+        <v>0.931433673535665</v>
       </c>
       <c r="K279" s="20" t="n">
-        <v>0.5023761</v>
+        <v>55.25461700488056</v>
       </c>
       <c r="L279" s="22" t="n">
-        <v>12.68861683768958</v>
+        <v>-9.578523399676241</v>
       </c>
       <c r="M279" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N279" s="22" t="n">
-        <v>0.001811725487354156</v>
+      <c r="N279" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O279" s="22" t="n">
-        <v>1.7374628339717</v>
-      </c>
-      <c r="P279" s="20" t="n">
-        <v>-10.25924812030075</v>
+        <v>-2419.753403544824</v>
+      </c>
+      <c r="P279" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q279" s="22" t="n">
-        <v>-16.09871122854541</v>
+        <v>-12.67606035817856</v>
       </c>
       <c r="R279" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S279" s="20" t="n">
-        <v>0.7127125270080983</v>
+        <v>1</v>
       </c>
       <c r="T279" s="15" t="inlineStr">
         <is>
-          <t>IT Staffing Services (83%)</t>
+          <t>Oncology (100%)</t>
         </is>
       </c>
       <c r="U279" s="17" t="inlineStr">
         <is>
-          <t>IT Staffing Services 83%; Data And Analytics Services 17%</t>
+          <t>Oncology 100%</t>
         </is>
       </c>
       <c r="V279" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W279" s="17" t="inlineStr">
-        <is>
-          <t>US 99%; India And Other 1%; CA 0%</t>
-        </is>
-      </c>
-      <c r="X279" s="15" t="inlineStr">
-        <is>
-          <t>IT Staffing Services -3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W279" s="17" t="n"/>
+      <c r="X279" s="15" t="n"/>
     </row>
     <row r="280" ht="16" customHeight="1">
       <c r="A280" s="13" t="n">
@@ -24792,12 +24790,12 @@
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>UBOH</t>
+          <t>MHH</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
         <is>
-          <t>United Bancshares, Inc.</t>
+          <t>Mastech Digital, Inc.</t>
         </is>
       </c>
       <c r="D280" s="16" t="inlineStr">
@@ -24807,70 +24805,78 @@
       </c>
       <c r="E280" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F280" s="18" t="n">
-        <v>109671704</v>
+        <v>92506016</v>
       </c>
       <c r="G280" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H280" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H280" s="20" t="n">
+        <v>10.015</v>
       </c>
       <c r="I280" s="20" t="n">
-        <v>8.494279000000001</v>
+        <v>40.57895</v>
       </c>
       <c r="J280" s="20" t="n">
-        <v>1.033575888944387</v>
+        <v>1.0158103</v>
       </c>
       <c r="K280" s="20" t="n">
-        <v>2.323060876932853</v>
+        <v>0.5023761</v>
       </c>
       <c r="L280" s="22" t="n">
-        <v>12.72069229452293</v>
+        <v>12.68861683768958</v>
       </c>
       <c r="M280" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N280" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N280" s="22" t="n">
+        <v>0.001811725487354156</v>
       </c>
       <c r="O280" s="22" t="n">
-        <v>26.577</v>
-      </c>
-      <c r="P280" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.7374628339717</v>
+      </c>
+      <c r="P280" s="20" t="n">
+        <v>-10.25924812030075</v>
       </c>
       <c r="Q280" s="22" t="n">
-        <v>43.15061893304754</v>
+        <v>-16.09871122854541</v>
       </c>
       <c r="R280" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S280" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T280" s="15" t="n"/>
-      <c r="U280" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S280" s="20" t="n">
+        <v>0.7127125270080983</v>
+      </c>
+      <c r="T280" s="15" t="inlineStr">
+        <is>
+          <t>IT Staffing Services (83%)</t>
+        </is>
+      </c>
+      <c r="U280" s="17" t="inlineStr">
+        <is>
+          <t>IT Staffing Services 83%; Data And Analytics Services 17%</t>
+        </is>
+      </c>
       <c r="V280" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W280" s="17" t="n"/>
-      <c r="X280" s="15" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W280" s="17" t="inlineStr">
+        <is>
+          <t>US 99%; India And Other 1%; CA 0%</t>
+        </is>
+      </c>
+      <c r="X280" s="15" t="inlineStr">
+        <is>
+          <t>IT Staffing Services -3%</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="16" customHeight="1">
       <c r="A281" s="13" t="n">
@@ -24878,12 +24884,12 @@
       </c>
       <c r="B281" s="14" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>UBOH</t>
         </is>
       </c>
       <c r="C281" s="15" t="inlineStr">
         <is>
-          <t>Inmode Ltd.</t>
+          <t>United Bancshares, Inc.</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
@@ -24893,48 +24899,54 @@
       </c>
       <c r="E281" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F281" s="18" t="n">
-        <v>840943680</v>
+        <v>109671704</v>
       </c>
       <c r="G281" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H281" s="20" t="n">
-        <v>4.908</v>
+      <c r="H281" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I281" s="20" t="n">
-        <v>10.837037</v>
+        <v>8.494279000000001</v>
       </c>
       <c r="J281" s="20" t="n">
-        <v>1.3567653</v>
+        <v>1.033575888944387</v>
       </c>
       <c r="K281" s="20" t="n">
-        <v>2.2446833</v>
+        <v>2.323060876932853</v>
       </c>
       <c r="L281" s="22" t="n">
-        <v>10.02266881891543</v>
+        <v>12.72069229452293</v>
       </c>
       <c r="M281" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N281" s="22" t="n">
-        <v>22.43159816631858</v>
+      <c r="N281" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O281" s="22" t="n">
-        <v>23.23432165076451</v>
-      </c>
-      <c r="P281" s="20" t="n">
-        <v>-7.106875581312155</v>
+        <v>26.577</v>
+      </c>
+      <c r="P281" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q281" s="22" t="n">
-        <v>3.10077904911207</v>
+        <v>43.15061893304754</v>
       </c>
       <c r="R281" s="18" t="n">
         <v>0</v>
@@ -24947,13 +24959,9 @@
       <c r="T281" s="15" t="n"/>
       <c r="U281" s="17" t="n"/>
       <c r="V281" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W281" s="17" t="inlineStr">
-        <is>
-          <t>US 54%; Europe 21%; Asia 13%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W281" s="17" t="n"/>
       <c r="X281" s="15" t="n"/>
     </row>
     <row r="282" ht="16" customHeight="1">
@@ -24962,12 +24970,12 @@
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="C282" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>Inmode Ltd.</t>
         </is>
       </c>
       <c r="D282" s="16" t="inlineStr">
@@ -24977,11 +24985,11 @@
       </c>
       <c r="E282" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F282" s="18" t="n">
-        <v>108295240</v>
+        <v>840943680</v>
       </c>
       <c r="G282" s="19" t="inlineStr">
         <is>
@@ -24989,19 +24997,19 @@
         </is>
       </c>
       <c r="H282" s="20" t="n">
-        <v>11.138</v>
+        <v>4.908</v>
       </c>
       <c r="I282" s="20" t="n">
-        <v>21.333334</v>
+        <v>10.837037</v>
       </c>
       <c r="J282" s="20" t="n">
-        <v>1.7627617</v>
+        <v>1.3567653</v>
       </c>
       <c r="K282" s="20" t="n">
-        <v>3.8745956</v>
+        <v>2.2446833</v>
       </c>
       <c r="L282" s="22" t="n">
-        <v>1.84264170445135</v>
+        <v>10.02266881891543</v>
       </c>
       <c r="M282" s="21" t="inlineStr">
         <is>
@@ -25009,46 +25017,36 @@
         </is>
       </c>
       <c r="N282" s="22" t="n">
-        <v>16.80549850408138</v>
+        <v>22.43159816631858</v>
       </c>
       <c r="O282" s="22" t="n">
-        <v>24.49495025980879</v>
+        <v>23.23432165076451</v>
       </c>
       <c r="P282" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>-7.106875581312155</v>
       </c>
       <c r="Q282" s="22" t="n">
-        <v>63.28571864536831</v>
+        <v>3.10077904911207</v>
       </c>
       <c r="R282" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S282" s="20" t="n">
-        <v>0.3385873824755823</v>
-      </c>
-      <c r="T282" s="15" t="inlineStr">
-        <is>
-          <t>Defense Engineering Se (45%)</t>
-        </is>
-      </c>
-      <c r="U282" s="17" t="inlineStr">
-        <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S282" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T282" s="15" t="n"/>
+      <c r="U282" s="17" t="n"/>
       <c r="V282" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W282" s="17" t="inlineStr">
         <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
-        </is>
-      </c>
-      <c r="X282" s="15" t="inlineStr">
-        <is>
-          <t>Marine Technology Bu +185%</t>
-        </is>
-      </c>
+          <t>US 54%; Europe 21%; Asia 13%</t>
+        </is>
+      </c>
+      <c r="X282" s="15" t="n"/>
     </row>
     <row r="283" ht="16" customHeight="1">
       <c r="A283" s="13" t="n">
@@ -25056,12 +25054,12 @@
       </c>
       <c r="B283" s="14" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C283" s="15" t="inlineStr">
         <is>
-          <t>Pegasystems Inc.</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
@@ -25071,11 +25069,11 @@
       </c>
       <c r="E283" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F283" s="18" t="n">
-        <v>5143832064</v>
+        <v>108295240</v>
       </c>
       <c r="G283" s="19" t="inlineStr">
         <is>
@@ -25083,62 +25081,64 @@
         </is>
       </c>
       <c r="H283" s="20" t="n">
-        <v>22.891</v>
+        <v>11.138</v>
       </c>
       <c r="I283" s="20" t="n">
-        <v>16.637838</v>
+        <v>21.333334</v>
       </c>
       <c r="J283" s="20" t="n">
-        <v>7.358355</v>
+        <v>1.7627617</v>
       </c>
       <c r="K283" s="20" t="n">
-        <v>3.025513</v>
+        <v>3.8745956</v>
       </c>
       <c r="L283" s="22" t="n">
-        <v>11.23669009802985</v>
-      </c>
-      <c r="M283" s="22" t="n">
-        <v>0.22092398679639</v>
+        <v>1.84264170445135</v>
+      </c>
+      <c r="M283" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N283" s="22" t="n">
-        <v>44.9328253275009</v>
+        <v>16.80549850408138</v>
       </c>
       <c r="O283" s="22" t="n">
-        <v>12.97742790056418</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="P283" s="20" t="n">
-        <v>-1.821221378197574</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q283" s="22" t="n">
-        <v>-30.73425955897104</v>
+        <v>63.28571864536831</v>
       </c>
       <c r="R283" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S283" s="20" t="n">
-        <v>1</v>
+        <v>0.3385873824755823</v>
       </c>
       <c r="T283" s="15" t="inlineStr">
         <is>
-          <t>Reportable (100%)</t>
+          <t>Defense Engineering Se (45%)</t>
         </is>
       </c>
       <c r="U283" s="17" t="inlineStr">
         <is>
-          <t>Reportable 100%</t>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
         </is>
       </c>
       <c r="V283" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W283" s="17" t="inlineStr">
         <is>
-          <t>US 55%; EMEA 16%; Asia Pacific 12%</t>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
         </is>
       </c>
       <c r="X283" s="15" t="inlineStr">
         <is>
-          <t>Reportable +17%</t>
+          <t>Marine Technology Bu +185%</t>
         </is>
       </c>
     </row>
@@ -25148,12 +25148,12 @@
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>SCNX</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="C284" s="15" t="inlineStr">
         <is>
-          <t>Scienture Holdings Inc. Common</t>
+          <t>Pegasystems Inc.</t>
         </is>
       </c>
       <c r="D284" s="16" t="inlineStr">
@@ -25163,11 +25163,11 @@
       </c>
       <c r="E284" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F284" s="18" t="n">
-        <v>16374219</v>
+        <v>5143832064</v>
       </c>
       <c r="G284" s="19" t="inlineStr">
         <is>
@@ -25175,56 +25175,64 @@
         </is>
       </c>
       <c r="H284" s="20" t="n">
-        <v>-0.2500849747464531</v>
-      </c>
-      <c r="I284" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.891</v>
+      </c>
+      <c r="I284" s="20" t="n">
+        <v>16.637838</v>
       </c>
       <c r="J284" s="20" t="n">
-        <v>0.2335158204495856</v>
+        <v>7.358355</v>
       </c>
       <c r="K284" s="20" t="n">
-        <v>37.93762178267831</v>
+        <v>3.025513</v>
       </c>
       <c r="L284" s="22" t="n">
-        <v>-81.71188500654596</v>
-      </c>
-      <c r="M284" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.23669009802985</v>
+      </c>
+      <c r="M284" s="22" t="n">
+        <v>0.22092398679639</v>
       </c>
       <c r="N284" s="22" t="n">
-        <v>-62.10204060447323</v>
+        <v>44.9328253275009</v>
       </c>
       <c r="O284" s="22" t="n">
-        <v>-9020.237066418911</v>
-      </c>
-      <c r="P284" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.97742790056418</v>
+      </c>
+      <c r="P284" s="20" t="n">
+        <v>-1.821221378197574</v>
       </c>
       <c r="Q284" s="22" t="n">
-        <v>-55.22222135390762</v>
+        <v>-30.73425955897104</v>
       </c>
       <c r="R284" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S284" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T284" s="15" t="n"/>
-      <c r="U284" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S284" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T284" s="15" t="inlineStr">
+        <is>
+          <t>Reportable (100%)</t>
+        </is>
+      </c>
+      <c r="U284" s="17" t="inlineStr">
+        <is>
+          <t>Reportable 100%</t>
+        </is>
+      </c>
       <c r="V284" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W284" s="17" t="n"/>
-      <c r="X284" s="15" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W284" s="17" t="inlineStr">
+        <is>
+          <t>US 55%; EMEA 16%; Asia Pacific 12%</t>
+        </is>
+      </c>
+      <c r="X284" s="15" t="inlineStr">
+        <is>
+          <t>Reportable +17%</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="16" customHeight="1">
       <c r="A285" s="13" t="n">
@@ -25232,12 +25240,12 @@
       </c>
       <c r="B285" s="14" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>SCNX</t>
         </is>
       </c>
       <c r="C285" s="15" t="inlineStr">
         <is>
-          <t>Lincoln National Corporation</t>
+          <t>Scienture Holdings Inc. Common</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
@@ -25247,76 +25255,68 @@
       </c>
       <c r="E285" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F285" s="18" t="n">
-        <v>7021348864</v>
+        <v>16374219</v>
       </c>
       <c r="G285" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H285" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I285" s="20" t="n">
-        <v>4.0175056</v>
+      <c r="H285" s="20" t="n">
+        <v>-0.2500849747464531</v>
+      </c>
+      <c r="I285" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J285" s="20" t="n">
-        <v>0.76102054</v>
+        <v>0.2335158204495856</v>
       </c>
       <c r="K285" s="20" t="n">
-        <v>0.37288097</v>
+        <v>37.93762178267831</v>
       </c>
       <c r="L285" s="22" t="n">
-        <v>3.52715173185971</v>
-      </c>
-      <c r="M285" s="22" t="n">
-        <v>4.9000002</v>
+        <v>-81.71188500654596</v>
+      </c>
+      <c r="M285" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N285" s="22" t="n">
-        <v>-8.60173683631966</v>
+        <v>-62.10204060447323</v>
       </c>
       <c r="O285" s="22" t="n">
+        <v>-9020.237066418911</v>
+      </c>
+      <c r="P285" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q285" s="22" t="n">
+        <v>-55.22222135390762</v>
+      </c>
+      <c r="R285" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P285" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q285" s="22" t="n">
-        <v>15.68577893399005</v>
-      </c>
-      <c r="R285" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S285" s="20" t="n">
-        <v>0.2943665648071563</v>
-      </c>
-      <c r="T285" s="15" t="inlineStr">
-        <is>
-          <t>Group Protection (34%)</t>
-        </is>
-      </c>
-      <c r="U285" s="17" t="inlineStr">
-        <is>
-          <t>Group Protection 34%; Life 32%; Annuities 27%</t>
-        </is>
-      </c>
+      <c r="S285" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T285" s="15" t="n"/>
+      <c r="U285" s="17" t="n"/>
       <c r="V285" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W285" s="17" t="n"/>
-      <c r="X285" s="15" t="inlineStr">
-        <is>
-          <t>Annuities +102%</t>
-        </is>
-      </c>
+      <c r="X285" s="15" t="n"/>
     </row>
     <row r="286" ht="16" customHeight="1">
       <c r="A286" s="13" t="n">
@@ -25324,12 +25324,12 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>LNC</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
         <is>
-          <t>Cricut, Inc.</t>
+          <t>Lincoln National Corporation</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
@@ -25339,74 +25339,74 @@
       </c>
       <c r="E286" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F286" s="18" t="n">
-        <v>971830720</v>
+        <v>7021348864</v>
       </c>
       <c r="G286" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H286" s="20" t="n">
-        <v>7.711</v>
+      <c r="H286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I286" s="20" t="n">
-        <v>13.617647</v>
+        <v>4.0175056</v>
       </c>
       <c r="J286" s="20" t="n">
-        <v>2.7187319</v>
+        <v>0.76102054</v>
       </c>
       <c r="K286" s="20" t="n">
-        <v>1.3772779</v>
+        <v>0.37288097</v>
       </c>
       <c r="L286" s="22" t="n">
-        <v>21.31320627082333</v>
+        <v>3.52715173185971</v>
       </c>
       <c r="M286" s="22" t="n">
-        <v>4.32</v>
+        <v>4.9000002</v>
       </c>
       <c r="N286" s="22" t="n">
-        <v>136.3676368894197</v>
+        <v>-8.60173683631966</v>
       </c>
       <c r="O286" s="22" t="n">
-        <v>18.75038799063179</v>
-      </c>
-      <c r="P286" s="20" t="n">
-        <v>-1.986666566339852</v>
+        <v>0</v>
+      </c>
+      <c r="P286" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q286" s="22" t="n">
-        <v>-27.59702330899697</v>
+        <v>15.68577893399005</v>
       </c>
       <c r="R286" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S286" s="20" t="n">
-        <v>0.5029003141229101</v>
+        <v>0.2943665648071563</v>
       </c>
       <c r="T286" s="15" t="inlineStr">
         <is>
-          <t>Accessories And Materi (54%)</t>
+          <t>Group Protection (34%)</t>
         </is>
       </c>
       <c r="U286" s="17" t="inlineStr">
         <is>
-          <t>Accessories And Materials 54%; Subscriptions 46%</t>
+          <t>Group Protection 34%; Life 32%; Annuities 27%</t>
         </is>
       </c>
       <c r="V286" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W286" s="17" t="inlineStr">
-        <is>
-          <t>North America 76%; International 24%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W286" s="17" t="n"/>
       <c r="X286" s="15" t="inlineStr">
         <is>
-          <t>Subscriptions +5%</t>
+          <t>Annuities +102%</t>
         </is>
       </c>
     </row>
@@ -25416,12 +25416,12 @@
       </c>
       <c r="B287" s="14" t="inlineStr">
         <is>
-          <t>OMCC</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="C287" s="15" t="inlineStr">
         <is>
-          <t>Old Market Capital Corporation</t>
+          <t>Cricut, Inc.</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
@@ -25431,11 +25431,11 @@
       </c>
       <c r="E287" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F287" s="18" t="n">
-        <v>28974532</v>
+        <v>971830720</v>
       </c>
       <c r="G287" s="19" t="inlineStr">
         <is>
@@ -25443,56 +25443,64 @@
         </is>
       </c>
       <c r="H287" s="20" t="n">
-        <v>-19.26914102564102</v>
-      </c>
-      <c r="I287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.711</v>
+      </c>
+      <c r="I287" s="20" t="n">
+        <v>13.617647</v>
       </c>
       <c r="J287" s="20" t="n">
-        <v>0.5290676</v>
+        <v>2.7187319</v>
       </c>
       <c r="K287" s="20" t="n">
-        <v>2.294044</v>
+        <v>1.3772779</v>
       </c>
       <c r="L287" s="22" t="n">
-        <v>-10.14684206115908</v>
-      </c>
-      <c r="M287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.31320627082333</v>
+      </c>
+      <c r="M287" s="22" t="n">
+        <v>4.32</v>
       </c>
       <c r="N287" s="22" t="n">
-        <v>-9.60052219321148</v>
+        <v>136.3676368894197</v>
       </c>
       <c r="O287" s="22" t="n">
-        <v>-10.8424787523723</v>
-      </c>
-      <c r="P287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>18.75038799063179</v>
+      </c>
+      <c r="P287" s="20" t="n">
+        <v>-1.986666566339852</v>
       </c>
       <c r="Q287" s="22" t="n">
-        <v>-15.69767377388159</v>
+        <v>-27.59702330899697</v>
       </c>
       <c r="R287" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S287" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T287" s="15" t="n"/>
-      <c r="U287" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S287" s="20" t="n">
+        <v>0.5029003141229101</v>
+      </c>
+      <c r="T287" s="15" t="inlineStr">
+        <is>
+          <t>Accessories And Materi (54%)</t>
+        </is>
+      </c>
+      <c r="U287" s="17" t="inlineStr">
+        <is>
+          <t>Accessories And Materials 54%; Subscriptions 46%</t>
+        </is>
+      </c>
       <c r="V287" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W287" s="17" t="n"/>
-      <c r="X287" s="15" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W287" s="17" t="inlineStr">
+        <is>
+          <t>North America 76%; International 24%</t>
+        </is>
+      </c>
+      <c r="X287" s="15" t="inlineStr">
+        <is>
+          <t>Subscriptions +5%</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="16" customHeight="1">
       <c r="A288" s="13" t="n">
@@ -25500,12 +25508,12 @@
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>CSBR</t>
+          <t>OMCC</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
         <is>
-          <t>Champions Oncology, Inc.</t>
+          <t>Old Market Capital Corporation</t>
         </is>
       </c>
       <c r="D288" s="16" t="inlineStr">
@@ -25515,11 +25523,11 @@
       </c>
       <c r="E288" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F288" s="18" t="n">
-        <v>80821328</v>
+        <v>28974532</v>
       </c>
       <c r="G288" s="19" t="inlineStr">
         <is>
@@ -25527,7 +25535,7 @@
         </is>
       </c>
       <c r="H288" s="20" t="n">
-        <v>-101.9253919793014</v>
+        <v>-19.26914102564102</v>
       </c>
       <c r="I288" s="21" t="inlineStr">
         <is>
@@ -25535,13 +25543,13 @@
         </is>
       </c>
       <c r="J288" s="20" t="n">
-        <v>18.87026103198692</v>
+        <v>0.5290676</v>
       </c>
       <c r="K288" s="20" t="n">
-        <v>1.394817893138202</v>
+        <v>2.294044</v>
       </c>
       <c r="L288" s="22" t="n">
-        <v>4.72152598135977</v>
+        <v>-10.14684206115908</v>
       </c>
       <c r="M288" s="21" t="inlineStr">
         <is>
@@ -25549,16 +25557,18 @@
         </is>
       </c>
       <c r="N288" s="22" t="n">
-        <v>-28.77898854428611</v>
+        <v>-9.60052219321148</v>
       </c>
       <c r="O288" s="22" t="n">
-        <v>8.51855400140512</v>
-      </c>
-      <c r="P288" s="20" t="n">
-        <v>2.888745148771022</v>
+        <v>-10.8424787523723</v>
+      </c>
+      <c r="P288" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q288" s="22" t="n">
-        <v>-33.93870721388012</v>
+        <v>-15.69767377388159</v>
       </c>
       <c r="R288" s="18" t="n">
         <v>0</v>
@@ -25582,12 +25592,12 @@
       </c>
       <c r="B289" s="14" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CSBR</t>
         </is>
       </c>
       <c r="C289" s="15" t="inlineStr">
         <is>
-          <t>Azenta Inc.</t>
+          <t>Champions Oncology, Inc.</t>
         </is>
       </c>
       <c r="D289" s="16" t="inlineStr">
@@ -25601,7 +25611,7 @@
         </is>
       </c>
       <c r="F289" s="18" t="n">
-        <v>1175366528</v>
+        <v>80821328</v>
       </c>
       <c r="G289" s="19" t="inlineStr">
         <is>
@@ -25609,7 +25619,7 @@
         </is>
       </c>
       <c r="H289" s="20" t="n">
-        <v>23.166</v>
+        <v>-101.9253919793014</v>
       </c>
       <c r="I289" s="21" t="inlineStr">
         <is>
@@ -25617,60 +25627,46 @@
         </is>
       </c>
       <c r="J289" s="20" t="n">
-        <v>0.75600356</v>
+        <v>18.87026103198692</v>
       </c>
       <c r="K289" s="20" t="n">
-        <v>1.9704914</v>
+        <v>1.394817893138202</v>
       </c>
       <c r="L289" s="22" t="n">
-        <v>9.92176777589456</v>
-      </c>
-      <c r="M289" s="22" t="n">
+        <v>4.72152598135977</v>
+      </c>
+      <c r="M289" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N289" s="22" t="n">
+        <v>-28.77898854428611</v>
+      </c>
+      <c r="O289" s="22" t="n">
+        <v>8.51855400140512</v>
+      </c>
+      <c r="P289" s="20" t="n">
+        <v>2.888745148771022</v>
+      </c>
+      <c r="Q289" s="22" t="n">
+        <v>-33.93870721388012</v>
+      </c>
+      <c r="R289" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N289" s="22" t="n">
-        <v>-13.85304502611689</v>
-      </c>
-      <c r="O289" s="22" t="n">
-        <v>6.65789859233674</v>
-      </c>
-      <c r="P289" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q289" s="22" t="n">
-        <v>-40.02245972716416</v>
-      </c>
-      <c r="R289" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S289" s="20" t="n">
-        <v>0.276261370165999</v>
-      </c>
-      <c r="T289" s="15" t="inlineStr">
-        <is>
-          <t>Sample Management Solu (35%)</t>
-        </is>
-      </c>
-      <c r="U289" s="17" t="inlineStr">
-        <is>
-          <t>Sample Management Solutions 35%; Multiomics 29%; Core Products 22%</t>
-        </is>
-      </c>
+      <c r="S289" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T289" s="15" t="n"/>
+      <c r="U289" s="17" t="n"/>
       <c r="V289" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W289" s="17" t="inlineStr">
-        <is>
-          <t>US 61%; Europe 18%; CN 10%</t>
-        </is>
-      </c>
-      <c r="X289" s="15" t="inlineStr">
-        <is>
-          <t>Sample Repository So +27%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W289" s="17" t="n"/>
+      <c r="X289" s="15" t="n"/>
     </row>
     <row r="290" ht="16" customHeight="1">
       <c r="A290" s="13" t="n">
@@ -25678,12 +25674,12 @@
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>TRDA</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C290" s="15" t="inlineStr">
         <is>
-          <t>Entrada Therapeutics Inc. Comm</t>
+          <t>Azenta Inc.</t>
         </is>
       </c>
       <c r="D290" s="16" t="inlineStr">
@@ -25697,7 +25693,7 @@
         </is>
       </c>
       <c r="F290" s="18" t="n">
-        <v>247675536</v>
+        <v>1175366528</v>
       </c>
       <c r="G290" s="19" t="inlineStr">
         <is>
@@ -25705,7 +25701,7 @@
         </is>
       </c>
       <c r="H290" s="20" t="n">
-        <v>-0.1611489837583386</v>
+        <v>23.166</v>
       </c>
       <c r="I290" s="21" t="inlineStr">
         <is>
@@ -25713,26 +25709,22 @@
         </is>
       </c>
       <c r="J290" s="20" t="n">
-        <v>0.8090455324973133</v>
+        <v>0.75600356</v>
       </c>
       <c r="K290" s="20" t="n">
-        <v>9.7429501593171</v>
+        <v>1.9704914</v>
       </c>
       <c r="L290" s="22" t="n">
-        <v>-52.30754804947711</v>
-      </c>
-      <c r="M290" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N290" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.92176777589456</v>
+      </c>
+      <c r="M290" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" s="22" t="n">
+        <v>-13.85304502611689</v>
       </c>
       <c r="O290" s="22" t="n">
-        <v>-605.0194720900043</v>
+        <v>6.65789859233674</v>
       </c>
       <c r="P290" s="21" t="inlineStr">
         <is>
@@ -25740,31 +25732,35 @@
         </is>
       </c>
       <c r="Q290" s="22" t="n">
-        <v>-21.42856891183762</v>
+        <v>-40.02245972716416</v>
       </c>
       <c r="R290" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S290" s="20" t="n">
-        <v>1</v>
+        <v>0.276261370165999</v>
       </c>
       <c r="T290" s="15" t="inlineStr">
         <is>
-          <t>Reportable (100%)</t>
+          <t>Sample Management Solu (35%)</t>
         </is>
       </c>
       <c r="U290" s="17" t="inlineStr">
         <is>
-          <t>Reportable 100%</t>
+          <t>Sample Management Solutions 35%; Multiomics 29%; Core Products 22%</t>
         </is>
       </c>
       <c r="V290" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W290" s="17" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="W290" s="17" t="inlineStr">
+        <is>
+          <t>US 61%; Europe 18%; CN 10%</t>
+        </is>
+      </c>
       <c r="X290" s="15" t="inlineStr">
         <is>
-          <t>Reportable -54%</t>
+          <t>Sample Repository So +27%</t>
         </is>
       </c>
     </row>
@@ -25774,12 +25770,12 @@
       </c>
       <c r="B291" s="14" t="inlineStr">
         <is>
-          <t>DSWL</t>
+          <t>TRDA</t>
         </is>
       </c>
       <c r="C291" s="15" t="inlineStr">
         <is>
-          <t>Deswell Industries, Inc.</t>
+          <t>Entrada Therapeutics Inc. Comm</t>
         </is>
       </c>
       <c r="D291" s="16" t="inlineStr">
@@ -25789,11 +25785,11 @@
       </c>
       <c r="E291" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F291" s="18" t="n">
-        <v>59887352</v>
+        <v>247675536</v>
       </c>
       <c r="G291" s="19" t="inlineStr">
         <is>
@@ -25801,28 +25797,34 @@
         </is>
       </c>
       <c r="H291" s="20" t="n">
-        <v>-4.644454376163873</v>
-      </c>
-      <c r="I291" s="20" t="n">
-        <v>5.6268654</v>
+        <v>-0.1611489837583386</v>
+      </c>
+      <c r="I291" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J291" s="20" t="n">
-        <v>0.5474876</v>
+        <v>0.8090455324973133</v>
       </c>
       <c r="K291" s="20" t="n">
-        <v>0.97644544</v>
+        <v>9.7429501593171</v>
       </c>
       <c r="L291" s="22" t="n">
-        <v>22.04472156324427</v>
-      </c>
-      <c r="M291" s="22" t="n">
-        <v>5.3200003</v>
-      </c>
-      <c r="N291" s="22" t="n">
-        <v>4.47916525876167</v>
+        <v>-52.30754804947711</v>
+      </c>
+      <c r="M291" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N291" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O291" s="22" t="n">
-        <v>7.148350835675189</v>
+        <v>-605.0194720900043</v>
       </c>
       <c r="P291" s="21" t="inlineStr">
         <is>
@@ -25830,35 +25832,31 @@
         </is>
       </c>
       <c r="Q291" s="22" t="n">
-        <v>59.61997472641421</v>
+        <v>-21.42856891183762</v>
       </c>
       <c r="R291" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S291" s="20" t="n">
-        <v>0.7508045391738183</v>
+        <v>1</v>
       </c>
       <c r="T291" s="15" t="inlineStr">
         <is>
-          <t>Electronic Product (85%)</t>
+          <t>Reportable (100%)</t>
         </is>
       </c>
       <c r="U291" s="17" t="inlineStr">
         <is>
-          <t>Electronic Product 85%; Injection Molded Plastic Part 15%</t>
+          <t>Reportable 100%</t>
         </is>
       </c>
       <c r="V291" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W291" s="17" t="inlineStr">
-        <is>
-          <t>CN 21%; GB 20%; Europe 18%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W291" s="17" t="n"/>
       <c r="X291" s="15" t="inlineStr">
         <is>
-          <t>Electronic Product -7%</t>
+          <t>Reportable -54%</t>
         </is>
       </c>
     </row>
@@ -25868,12 +25866,12 @@
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>VRCA</t>
+          <t>DSWL</t>
         </is>
       </c>
       <c r="C292" s="15" t="inlineStr">
         <is>
-          <t>Verrica Pharmaceuticals Inc.</t>
+          <t>Deswell Industries, Inc.</t>
         </is>
       </c>
       <c r="D292" s="16" t="inlineStr">
@@ -25883,11 +25881,11 @@
       </c>
       <c r="E292" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F292" s="18" t="n">
-        <v>117502912</v>
+        <v>59887352</v>
       </c>
       <c r="G292" s="19" t="inlineStr">
         <is>
@@ -25895,34 +25893,28 @@
         </is>
       </c>
       <c r="H292" s="20" t="n">
-        <v>-2.777811366021892</v>
-      </c>
-      <c r="I292" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-4.644454376163873</v>
+      </c>
+      <c r="I292" s="20" t="n">
+        <v>5.6268654</v>
       </c>
       <c r="J292" s="20" t="n">
-        <v>7.3155084</v>
+        <v>0.5474876</v>
       </c>
       <c r="K292" s="20" t="n">
-        <v>3.1619954</v>
+        <v>0.97644544</v>
       </c>
       <c r="L292" s="22" t="n">
-        <v>-39.4688090793869</v>
-      </c>
-      <c r="M292" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N292" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.04472156324427</v>
+      </c>
+      <c r="M292" s="22" t="n">
+        <v>5.3200003</v>
+      </c>
+      <c r="N292" s="22" t="n">
+        <v>4.47916525876167</v>
       </c>
       <c r="O292" s="22" t="n">
-        <v>-41.03918271938718</v>
+        <v>7.148350835675189</v>
       </c>
       <c r="P292" s="21" t="inlineStr">
         <is>
@@ -25930,31 +25922,35 @@
         </is>
       </c>
       <c r="Q292" s="22" t="n">
-        <v>3.99999618530273</v>
+        <v>59.61997472641421</v>
       </c>
       <c r="R292" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S292" s="20" t="n">
-        <v>1</v>
+        <v>0.7508045391738183</v>
       </c>
       <c r="T292" s="15" t="inlineStr">
         <is>
-          <t>Operating (100%)</t>
+          <t>Electronic Product (85%)</t>
         </is>
       </c>
       <c r="U292" s="17" t="inlineStr">
         <is>
-          <t>Operating 100%</t>
+          <t>Electronic Product 85%; Injection Molded Plastic Part 15%</t>
         </is>
       </c>
       <c r="V292" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W292" s="17" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="W292" s="17" t="inlineStr">
+        <is>
+          <t>CN 21%; GB 20%; Europe 18%</t>
+        </is>
+      </c>
       <c r="X292" s="15" t="inlineStr">
         <is>
-          <t>Operating +370%</t>
+          <t>Electronic Product -7%</t>
         </is>
       </c>
     </row>
@@ -25964,12 +25960,12 @@
       </c>
       <c r="B293" s="14" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>VRCA</t>
         </is>
       </c>
       <c r="C293" s="15" t="inlineStr">
         <is>
-          <t>Brilliant Earth Group Inc. Cla</t>
+          <t>Verrica Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="D293" s="16" t="inlineStr">
@@ -25979,11 +25975,11 @@
       </c>
       <c r="E293" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F293" s="18" t="n">
-        <v>104237232</v>
+        <v>117502912</v>
       </c>
       <c r="G293" s="19" t="inlineStr">
         <is>
@@ -25991,7 +25987,7 @@
         </is>
       </c>
       <c r="H293" s="20" t="n">
-        <v>5.124643397524071</v>
+        <v>-2.777811366021892</v>
       </c>
       <c r="I293" s="21" t="inlineStr">
         <is>
@@ -25999,48 +25995,60 @@
         </is>
       </c>
       <c r="J293" s="20" t="n">
-        <v>1.4589236</v>
+        <v>7.3155084</v>
       </c>
       <c r="K293" s="20" t="n">
-        <v>0.2352438</v>
+        <v>3.1619954</v>
       </c>
       <c r="L293" s="22" t="n">
-        <v>4.69729494608955</v>
-      </c>
-      <c r="M293" s="22" t="n">
-        <v>22.729999</v>
-      </c>
-      <c r="N293" s="22" t="n">
-        <v>-19.22447700929374</v>
+        <v>-39.4688090793869</v>
+      </c>
+      <c r="M293" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N293" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O293" s="22" t="n">
-        <v>2.6588461723084</v>
-      </c>
-      <c r="P293" s="20" t="n">
-        <v>-3.527338376891334</v>
+        <v>-41.03918271938718</v>
+      </c>
+      <c r="P293" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q293" s="22" t="n">
-        <v>-10.49357992488675</v>
+        <v>3.99999618530273</v>
       </c>
       <c r="R293" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S293" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T293" s="15" t="inlineStr">
+        <is>
+          <t>Operating (100%)</t>
+        </is>
+      </c>
+      <c r="U293" s="17" t="inlineStr">
+        <is>
+          <t>Operating 100%</t>
+        </is>
+      </c>
+      <c r="V293" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S293" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T293" s="15" t="n"/>
-      <c r="U293" s="17" t="n"/>
-      <c r="V293" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W293" s="17" t="inlineStr">
-        <is>
-          <t>US 96%; Non Us 4%</t>
-        </is>
-      </c>
-      <c r="X293" s="15" t="n"/>
+      <c r="W293" s="17" t="n"/>
+      <c r="X293" s="15" t="inlineStr">
+        <is>
+          <t>Operating +370%</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="16" customHeight="1">
       <c r="A294" s="13" t="n">
@@ -26048,12 +26056,12 @@
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>LGCY</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C294" s="15" t="inlineStr">
         <is>
-          <t>Legacy Education Inc.</t>
+          <t>Brilliant Earth Group Inc. Cla</t>
         </is>
       </c>
       <c r="D294" s="16" t="inlineStr">
@@ -26067,7 +26075,7 @@
         </is>
       </c>
       <c r="F294" s="18" t="n">
-        <v>144233232</v>
+        <v>104237232</v>
       </c>
       <c r="G294" s="19" t="inlineStr">
         <is>
@@ -26075,36 +26083,36 @@
         </is>
       </c>
       <c r="H294" s="20" t="n">
-        <v>11.741</v>
-      </c>
-      <c r="I294" s="20" t="n">
-        <v>18.999998</v>
+        <v>5.124643397524071</v>
+      </c>
+      <c r="I294" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J294" s="20" t="n">
-        <v>2.9089053</v>
+        <v>1.4589236</v>
       </c>
       <c r="K294" s="20" t="n">
-        <v>1.8514082</v>
+        <v>0.2352438</v>
       </c>
       <c r="L294" s="22" t="n">
-        <v>5.53478271914478</v>
-      </c>
-      <c r="M294" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69729494608955</v>
+      </c>
+      <c r="M294" s="22" t="n">
+        <v>22.729999</v>
       </c>
       <c r="N294" s="22" t="n">
-        <v>45.16348160383653</v>
+        <v>-19.22447700929374</v>
       </c>
       <c r="O294" s="22" t="n">
-        <v>17.18455257254128</v>
+        <v>2.6588461723084</v>
       </c>
       <c r="P294" s="20" t="n">
-        <v>-1.558726694400639</v>
+        <v>-3.527338376891334</v>
       </c>
       <c r="Q294" s="22" t="n">
-        <v>-2.48075254288006</v>
+        <v>-10.49357992488675</v>
       </c>
       <c r="R294" s="18" t="n">
         <v>0</v>
@@ -26117,9 +26125,13 @@
       <c r="T294" s="15" t="n"/>
       <c r="U294" s="17" t="n"/>
       <c r="V294" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W294" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W294" s="17" t="inlineStr">
+        <is>
+          <t>US 96%; Non Us 4%</t>
+        </is>
+      </c>
       <c r="X294" s="15" t="n"/>
     </row>
     <row r="295" ht="16" customHeight="1">
@@ -26128,12 +26140,12 @@
       </c>
       <c r="B295" s="14" t="inlineStr">
         <is>
-          <t>WSFS</t>
+          <t>LGCY</t>
         </is>
       </c>
       <c r="C295" s="15" t="inlineStr">
         <is>
-          <t>WSFS Financial Corporation</t>
+          <t>Legacy Education Inc.</t>
         </is>
       </c>
       <c r="D295" s="16" t="inlineStr">
@@ -26143,78 +26155,64 @@
       </c>
       <c r="E295" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F295" s="18" t="n">
-        <v>4026127616</v>
+        <v>144233232</v>
       </c>
       <c r="G295" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H295" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H295" s="20" t="n">
+        <v>11.741</v>
       </c>
       <c r="I295" s="20" t="n">
-        <v>13.789661</v>
+        <v>18.999998</v>
       </c>
       <c r="J295" s="20" t="n">
-        <v>1.508757</v>
+        <v>2.9089053</v>
       </c>
       <c r="K295" s="20" t="n">
-        <v>3.8152764</v>
+        <v>1.8514082</v>
       </c>
       <c r="L295" s="22" t="n">
-        <v>6.158366732153779</v>
-      </c>
-      <c r="M295" s="22" t="n">
-        <v>0.96865806418899</v>
-      </c>
-      <c r="N295" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.53478271914478</v>
+      </c>
+      <c r="M295" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N295" s="22" t="n">
+        <v>45.16348160383653</v>
       </c>
       <c r="O295" s="22" t="n">
+        <v>17.18455257254128</v>
+      </c>
+      <c r="P295" s="20" t="n">
+        <v>-1.558726694400639</v>
+      </c>
+      <c r="Q295" s="22" t="n">
+        <v>-2.48075254288006</v>
+      </c>
+      <c r="R295" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P295" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q295" s="22" t="n">
-        <v>37.01048893948796</v>
-      </c>
-      <c r="R295" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S295" s="20" t="n">
-        <v>0.5282319551986966</v>
-      </c>
-      <c r="T295" s="15" t="inlineStr">
-        <is>
-          <t>Wsfs Bank (68%)</t>
-        </is>
-      </c>
-      <c r="U295" s="17" t="inlineStr">
-        <is>
-          <t>Wsfs Bank 68%; Wealth Management 24%; Cash Connect 8%</t>
-        </is>
-      </c>
+      <c r="S295" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T295" s="15" t="n"/>
+      <c r="U295" s="17" t="n"/>
       <c r="V295" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W295" s="17" t="n"/>
-      <c r="X295" s="15" t="inlineStr">
-        <is>
-          <t>Wealth Management +15%</t>
-        </is>
-      </c>
+      <c r="X295" s="15" t="n"/>
     </row>
     <row r="296" ht="16" customHeight="1">
       <c r="A296" s="13" t="n">
@@ -26222,12 +26220,12 @@
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>LIDR</t>
+          <t>WSFS</t>
         </is>
       </c>
       <c r="C296" s="15" t="inlineStr">
         <is>
-          <t>AEye Inc. Class A Common Stock</t>
+          <t>WSFS Financial Corporation</t>
         </is>
       </c>
       <c r="D296" s="16" t="inlineStr">
@@ -26237,44 +26235,44 @@
       </c>
       <c r="E296" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F296" s="18" t="n">
-        <v>62061860</v>
+        <v>4026127616</v>
       </c>
       <c r="G296" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H296" s="20" t="n">
-        <v>0.4025600520648444</v>
-      </c>
-      <c r="I296" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H296" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I296" s="20" t="n">
+        <v>13.789661</v>
       </c>
       <c r="J296" s="20" t="n">
-        <v>0.8362328877870001</v>
+        <v>1.508757</v>
       </c>
       <c r="K296" s="20" t="n">
-        <v>229.8587407407408</v>
+        <v>3.8152764</v>
       </c>
       <c r="L296" s="22" t="n">
-        <v>-46.4359269928423</v>
-      </c>
-      <c r="M296" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N296" s="22" t="n">
-        <v>-85.9514449638759</v>
+        <v>6.158366732153779</v>
+      </c>
+      <c r="M296" s="22" t="n">
+        <v>0.96865806418899</v>
+      </c>
+      <c r="N296" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O296" s="22" t="n">
-        <v>-13469.62025316456</v>
+        <v>0</v>
       </c>
       <c r="P296" s="21" t="inlineStr">
         <is>
@@ -26282,27 +26280,33 @@
         </is>
       </c>
       <c r="Q296" s="22" t="n">
-        <v>17.54386405205137</v>
+        <v>37.01048893948796</v>
       </c>
       <c r="R296" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S296" s="20" t="n">
+        <v>0.5282319551986966</v>
+      </c>
+      <c r="T296" s="15" t="inlineStr">
+        <is>
+          <t>Wsfs Bank (68%)</t>
+        </is>
+      </c>
+      <c r="U296" s="17" t="inlineStr">
+        <is>
+          <t>Wsfs Bank 68%; Wealth Management 24%; Cash Connect 8%</t>
+        </is>
+      </c>
+      <c r="V296" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S296" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T296" s="15" t="n"/>
-      <c r="U296" s="17" t="n"/>
-      <c r="V296" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W296" s="17" t="inlineStr">
-        <is>
-          <t>US 50%; Europe 40%; Asia 10%</t>
-        </is>
-      </c>
-      <c r="X296" s="15" t="n"/>
+      <c r="W296" s="17" t="n"/>
+      <c r="X296" s="15" t="inlineStr">
+        <is>
+          <t>Wealth Management +15%</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="16" customHeight="1">
       <c r="A297" s="13" t="n">
@@ -26310,12 +26314,12 @@
       </c>
       <c r="B297" s="14" t="inlineStr">
         <is>
-          <t>MDRR</t>
+          <t>LIDR</t>
         </is>
       </c>
       <c r="C297" s="15" t="inlineStr">
         <is>
-          <t>Medalist Diversified REIT, Inc</t>
+          <t>AEye Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
@@ -26325,11 +26329,11 @@
       </c>
       <c r="E297" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F297" s="18" t="n">
-        <v>18760158</v>
+        <v>62061860</v>
       </c>
       <c r="G297" s="19" t="inlineStr">
         <is>
@@ -26337,19 +26341,21 @@
         </is>
       </c>
       <c r="H297" s="20" t="n">
-        <v>2.780036825807078</v>
-      </c>
-      <c r="I297" s="20" t="n">
-        <v>3.1219242</v>
+        <v>0.4025600520648444</v>
+      </c>
+      <c r="I297" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J297" s="20" t="n">
-        <v>0.8411720476936947</v>
+        <v>0.8362328877870001</v>
       </c>
       <c r="K297" s="20" t="n">
-        <v>1.83307724860549</v>
+        <v>229.8587407407408</v>
       </c>
       <c r="L297" s="22" t="n">
-        <v>-7.52920631052254</v>
+        <v>-46.4359269928423</v>
       </c>
       <c r="M297" s="21" t="inlineStr">
         <is>
@@ -26357,42 +26363,38 @@
         </is>
       </c>
       <c r="N297" s="22" t="n">
-        <v>30.01538674616187</v>
+        <v>-85.9514449638759</v>
       </c>
       <c r="O297" s="22" t="n">
-        <v>154.4775402450331</v>
-      </c>
-      <c r="P297" s="20" t="n">
-        <v>1.270310578241797</v>
+        <v>-13469.62025316456</v>
+      </c>
+      <c r="P297" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q297" s="22" t="n">
-        <v>1.73967414151658</v>
+        <v>17.54386405205137</v>
       </c>
       <c r="R297" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T297" s="15" t="n"/>
+      <c r="U297" s="17" t="n"/>
+      <c r="V297" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="S297" s="20" t="n">
-        <v>0.4570947911909182</v>
-      </c>
-      <c r="T297" s="15" t="inlineStr">
-        <is>
-          <t>Retail Center Properti (61%)</t>
-        </is>
-      </c>
-      <c r="U297" s="17" t="inlineStr">
-        <is>
-          <t>Retail Center Properties 61%; Propertyrevenues 27%; Single Tenant Net Lease 12%</t>
-        </is>
-      </c>
-      <c r="V297" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W297" s="17" t="n"/>
-      <c r="X297" s="15" t="inlineStr">
-        <is>
-          <t>Single Tenant Net Le +251%</t>
-        </is>
-      </c>
+      <c r="W297" s="17" t="inlineStr">
+        <is>
+          <t>US 50%; Europe 40%; Asia 10%</t>
+        </is>
+      </c>
+      <c r="X297" s="15" t="n"/>
     </row>
     <row r="298" ht="16" customHeight="1">
       <c r="A298" s="13" t="n">
@@ -26400,12 +26402,12 @@
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>DUO</t>
+          <t>MDRR</t>
         </is>
       </c>
       <c r="C298" s="15" t="inlineStr">
         <is>
-          <t>Fangdd Network Group Ltd.</t>
+          <t>Medalist Diversified REIT, Inc</t>
         </is>
       </c>
       <c r="D298" s="16" t="inlineStr">
@@ -26415,11 +26417,11 @@
       </c>
       <c r="E298" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F298" s="18" t="n">
-        <v>25684806</v>
+        <v>18760158</v>
       </c>
       <c r="G298" s="19" t="inlineStr">
         <is>
@@ -26427,21 +26429,19 @@
         </is>
       </c>
       <c r="H298" s="20" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="I298" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.780036825807078</v>
+      </c>
+      <c r="I298" s="20" t="n">
+        <v>3.1219242</v>
       </c>
       <c r="J298" s="20" t="n">
-        <v>0.30155513</v>
+        <v>0.8411720476936947</v>
       </c>
       <c r="K298" s="20" t="n">
-        <v>0.07238766000000001</v>
+        <v>1.83307724860549</v>
       </c>
       <c r="L298" s="22" t="n">
-        <v>-23.31605752734946</v>
+        <v>-7.52920631052254</v>
       </c>
       <c r="M298" s="21" t="inlineStr">
         <is>
@@ -26449,34 +26449,42 @@
         </is>
       </c>
       <c r="N298" s="22" t="n">
-        <v>-15.75163614728631</v>
+        <v>30.01538674616187</v>
       </c>
       <c r="O298" s="22" t="n">
-        <v>-34.64199136758706</v>
-      </c>
-      <c r="P298" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>154.4775402450331</v>
+      </c>
+      <c r="P298" s="20" t="n">
+        <v>1.270310578241797</v>
       </c>
       <c r="Q298" s="22" t="n">
-        <v>-66.20934943652108</v>
+        <v>1.73967414151658</v>
       </c>
       <c r="R298" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S298" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T298" s="15" t="n"/>
-      <c r="U298" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="S298" s="20" t="n">
+        <v>0.4570947911909182</v>
+      </c>
+      <c r="T298" s="15" t="inlineStr">
+        <is>
+          <t>Retail Center Properti (61%)</t>
+        </is>
+      </c>
+      <c r="U298" s="17" t="inlineStr">
+        <is>
+          <t>Retail Center Properties 61%; Propertyrevenues 27%; Single Tenant Net Lease 12%</t>
+        </is>
+      </c>
       <c r="V298" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W298" s="17" t="n"/>
-      <c r="X298" s="15" t="n"/>
+      <c r="X298" s="15" t="inlineStr">
+        <is>
+          <t>Single Tenant Net Le +251%</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="16" customHeight="1">
       <c r="A299" s="13" t="n">
@@ -26484,12 +26492,12 @@
       </c>
       <c r="B299" s="14" t="inlineStr">
         <is>
-          <t>CCS</t>
+          <t>DUO</t>
         </is>
       </c>
       <c r="C299" s="15" t="inlineStr">
         <is>
-          <t>Century Communities, Inc.</t>
+          <t>Fangdd Network Group Ltd.</t>
         </is>
       </c>
       <c r="D299" s="16" t="inlineStr">
@@ -26499,11 +26507,11 @@
       </c>
       <c r="E299" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F299" s="18" t="n">
-        <v>2066786816</v>
+        <v>25684806</v>
       </c>
       <c r="G299" s="19" t="inlineStr">
         <is>
@@ -26511,60 +26519,56 @@
         </is>
       </c>
       <c r="H299" s="20" t="n">
-        <v>14.787</v>
-      </c>
-      <c r="I299" s="20" t="n">
-        <v>16.18018</v>
+        <v>1.023</v>
+      </c>
+      <c r="I299" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J299" s="20" t="n">
-        <v>0.809483</v>
+        <v>0.30155513</v>
       </c>
       <c r="K299" s="20" t="n">
-        <v>0.5161474</v>
+        <v>0.07238766000000001</v>
       </c>
       <c r="L299" s="22" t="n">
-        <v>7.548742417841001</v>
-      </c>
-      <c r="M299" s="22" t="n">
-        <v>2.43149737225959</v>
+        <v>-23.31605752734946</v>
+      </c>
+      <c r="M299" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N299" s="22" t="n">
-        <v>2.58578602001868</v>
+        <v>-15.75163614728631</v>
       </c>
       <c r="O299" s="22" t="n">
-        <v>5.23343032178004</v>
-      </c>
-      <c r="P299" s="20" t="n">
-        <v>6.916582363046383</v>
+        <v>-34.64199136758706</v>
+      </c>
+      <c r="P299" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q299" s="22" t="n">
-        <v>-11.45115502443391</v>
+        <v>-66.20934943652108</v>
       </c>
       <c r="R299" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="S299" s="20" t="n">
-        <v>0.1890488694217202</v>
-      </c>
-      <c r="T299" s="15" t="inlineStr">
-        <is>
-          <t>Century Complete (23%)</t>
-        </is>
-      </c>
-      <c r="U299" s="17" t="inlineStr">
-        <is>
-          <t>Century Complete 23%; Mountain 21%; West 20%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S299" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T299" s="15" t="n"/>
+      <c r="U299" s="17" t="n"/>
       <c r="V299" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W299" s="17" t="n"/>
-      <c r="X299" s="15" t="inlineStr">
-        <is>
-          <t>Texas +6%</t>
-        </is>
-      </c>
+      <c r="X299" s="15" t="n"/>
     </row>
     <row r="300" ht="16" customHeight="1">
       <c r="A300" s="13" t="n">
@@ -26572,12 +26576,12 @@
       </c>
       <c r="B300" s="14" t="inlineStr">
         <is>
-          <t>AMRN</t>
+          <t>CCS</t>
         </is>
       </c>
       <c r="C300" s="15" t="inlineStr">
         <is>
-          <t>Amarin Corp Plc\Uk</t>
+          <t>Century Communities, Inc.</t>
         </is>
       </c>
       <c r="D300" s="16" t="inlineStr">
@@ -26587,11 +26591,11 @@
       </c>
       <c r="E300" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F300" s="18" t="n">
-        <v>333618496</v>
+        <v>2066786816</v>
       </c>
       <c r="G300" s="19" t="inlineStr">
         <is>
@@ -26599,60 +26603,60 @@
         </is>
       </c>
       <c r="H300" s="20" t="n">
-        <v>0.3312424123162403</v>
-      </c>
-      <c r="I300" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>14.787</v>
+      </c>
+      <c r="I300" s="20" t="n">
+        <v>16.18018</v>
       </c>
       <c r="J300" s="20" t="n">
-        <v>0.7427291</v>
+        <v>0.809483</v>
       </c>
       <c r="K300" s="20" t="n">
-        <v>1.5391077</v>
+        <v>0.5161474</v>
       </c>
       <c r="L300" s="22" t="n">
-        <v>-7.772950334264441</v>
-      </c>
-      <c r="M300" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.548742417841001</v>
+      </c>
+      <c r="M300" s="22" t="n">
+        <v>2.43149737225959</v>
       </c>
       <c r="N300" s="22" t="n">
-        <v>-16.83575549907395</v>
+        <v>2.58578602001868</v>
       </c>
       <c r="O300" s="22" t="n">
-        <v>-26.28221034548578</v>
-      </c>
-      <c r="P300" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.23343032178004</v>
+      </c>
+      <c r="P300" s="20" t="n">
+        <v>6.916582363046383</v>
       </c>
       <c r="Q300" s="22" t="n">
-        <v>2.0074048478698</v>
+        <v>-11.45115502443391</v>
       </c>
       <c r="R300" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="S300" s="20" t="n">
+        <v>0.1890488694217202</v>
+      </c>
+      <c r="T300" s="15" t="inlineStr">
+        <is>
+          <t>Century Complete (23%)</t>
+        </is>
+      </c>
+      <c r="U300" s="17" t="inlineStr">
+        <is>
+          <t>Century Complete 23%; Mountain 21%; West 20%</t>
+        </is>
+      </c>
+      <c r="V300" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S300" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T300" s="15" t="n"/>
-      <c r="U300" s="17" t="n"/>
-      <c r="V300" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W300" s="17" t="inlineStr">
-        <is>
-          <t>US 84%; Europe 10%; Rest Of The World Except US And Europe 6</t>
-        </is>
-      </c>
-      <c r="X300" s="15" t="n"/>
+      <c r="W300" s="17" t="n"/>
+      <c r="X300" s="15" t="inlineStr">
+        <is>
+          <t>Texas +6%</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="16" customHeight="1">
       <c r="A301" s="13" t="n">
@@ -26660,12 +26664,12 @@
       </c>
       <c r="B301" s="14" t="inlineStr">
         <is>
-          <t>ANIP</t>
+          <t>AMRN</t>
         </is>
       </c>
       <c r="C301" s="15" t="inlineStr">
         <is>
-          <t>Ani Pharmaceuticals, Inc</t>
+          <t>Amarin Corp Plc\Uk</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
@@ -26679,7 +26683,7 @@
         </is>
       </c>
       <c r="F301" s="18" t="n">
-        <v>1921075200</v>
+        <v>333618496</v>
       </c>
       <c r="G301" s="19" t="inlineStr">
         <is>
@@ -26687,19 +26691,21 @@
         </is>
       </c>
       <c r="H301" s="20" t="n">
-        <v>10.619</v>
-      </c>
-      <c r="I301" s="20" t="n">
-        <v>21.611252</v>
+        <v>0.3312424123162403</v>
+      </c>
+      <c r="I301" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J301" s="20" t="n">
-        <v>3.2079268</v>
+        <v>0.7427291</v>
       </c>
       <c r="K301" s="20" t="n">
-        <v>2.0797474</v>
+        <v>1.5391077</v>
       </c>
       <c r="L301" s="22" t="n">
-        <v>6.120582890248119</v>
+        <v>-7.772950334264441</v>
       </c>
       <c r="M301" s="21" t="inlineStr">
         <is>
@@ -26707,46 +26713,38 @@
         </is>
       </c>
       <c r="N301" s="22" t="n">
-        <v>20.70637542279365</v>
+        <v>-16.83575549907395</v>
       </c>
       <c r="O301" s="22" t="n">
-        <v>23.45439521703701</v>
-      </c>
-      <c r="P301" s="20" t="n">
-        <v>-0.0287015033888463</v>
+        <v>-26.28221034548578</v>
+      </c>
+      <c r="P301" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q301" s="22" t="n">
-        <v>26.41480058470028</v>
+        <v>2.0074048478698</v>
       </c>
       <c r="R301" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S301" s="20" t="n">
-        <v>0.5045751155060259</v>
-      </c>
-      <c r="T301" s="15" t="inlineStr">
-        <is>
-          <t>Rare Disease And Brand (55%)</t>
-        </is>
-      </c>
-      <c r="U301" s="17" t="inlineStr">
-        <is>
-          <t>Rare Disease And Brands 55%; Generics And Other 45%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S301" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T301" s="15" t="n"/>
+      <c r="U301" s="17" t="n"/>
       <c r="V301" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W301" s="17" t="inlineStr">
         <is>
-          <t>US 96%; Non Us 4%</t>
-        </is>
-      </c>
-      <c r="X301" s="15" t="inlineStr">
-        <is>
-          <t>Rare Disease And Bra +64%</t>
-        </is>
-      </c>
+          <t>US 84%; Europe 10%; Rest Of The World Except US And Europe 6</t>
+        </is>
+      </c>
+      <c r="X301" s="15" t="n"/>
     </row>
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="13" t="n">
@@ -26754,12 +26752,12 @@
       </c>
       <c r="B302" s="14" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>ANIP</t>
         </is>
       </c>
       <c r="C302" s="15" t="inlineStr">
         <is>
-          <t>Teekay Corporation Ltd.</t>
+          <t>Ani Pharmaceuticals, Inc</t>
         </is>
       </c>
       <c r="D302" s="16" t="inlineStr">
@@ -26769,11 +26767,11 @@
       </c>
       <c r="E302" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F302" s="18" t="n">
-        <v>935377088</v>
+        <v>1921075200</v>
       </c>
       <c r="G302" s="19" t="inlineStr">
         <is>
@@ -26781,19 +26779,19 @@
         </is>
       </c>
       <c r="H302" s="20" t="n">
-        <v>4.024</v>
+        <v>10.619</v>
       </c>
       <c r="I302" s="20" t="n">
-        <v>9.513273999999999</v>
+        <v>21.611252</v>
       </c>
       <c r="J302" s="20" t="n">
-        <v>1.2768738</v>
+        <v>3.2079268</v>
       </c>
       <c r="K302" s="20" t="n">
-        <v>0.9316737</v>
+        <v>2.0797474</v>
       </c>
       <c r="L302" s="22" t="n">
-        <v>11.92118146045501</v>
+        <v>6.120582890248119</v>
       </c>
       <c r="M302" s="21" t="inlineStr">
         <is>
@@ -26801,40 +26799,44 @@
         </is>
       </c>
       <c r="N302" s="22" t="n">
-        <v>24.78287343641048</v>
+        <v>20.70637542279365</v>
       </c>
       <c r="O302" s="22" t="n">
-        <v>41.01482854494903</v>
+        <v>23.45439521703701</v>
       </c>
       <c r="P302" s="20" t="n">
-        <v>-2.120166526673792</v>
+        <v>-0.0287015033888463</v>
       </c>
       <c r="Q302" s="22" t="n">
-        <v>56.60500796835277</v>
+        <v>26.41480058470028</v>
       </c>
       <c r="R302" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S302" s="20" t="n">
-        <v>0.7705855121065255</v>
+        <v>0.5045751155060259</v>
       </c>
       <c r="T302" s="15" t="inlineStr">
         <is>
-          <t>Tankers (87%)</t>
+          <t>Rare Disease And Brand (55%)</t>
         </is>
       </c>
       <c r="U302" s="17" t="inlineStr">
         <is>
-          <t>Tankers 87%; Marine Services And Other 13%</t>
+          <t>Rare Disease And Brands 55%; Generics And Other 45%</t>
         </is>
       </c>
       <c r="V302" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W302" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W302" s="17" t="inlineStr">
+        <is>
+          <t>US 96%; Non Us 4%</t>
+        </is>
+      </c>
       <c r="X302" s="15" t="inlineStr">
         <is>
-          <t>Marine Services And  +10%</t>
+          <t>Rare Disease And Bra +64%</t>
         </is>
       </c>
     </row>
@@ -26844,12 +26846,12 @@
       </c>
       <c r="B303" s="14" t="inlineStr">
         <is>
-          <t>AWRE</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C303" s="15" t="inlineStr">
         <is>
-          <t>Aware, Inc.</t>
+          <t>Teekay Corporation Ltd.</t>
         </is>
       </c>
       <c r="D303" s="16" t="inlineStr">
@@ -26859,11 +26861,11 @@
       </c>
       <c r="E303" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F303" s="18" t="n">
-        <v>28139898</v>
+        <v>935377088</v>
       </c>
       <c r="G303" s="19" t="inlineStr">
         <is>
@@ -26871,21 +26873,19 @@
         </is>
       </c>
       <c r="H303" s="20" t="n">
-        <v>-1.513124630984469</v>
-      </c>
-      <c r="I303" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.024</v>
+      </c>
+      <c r="I303" s="20" t="n">
+        <v>9.513273999999999</v>
       </c>
       <c r="J303" s="20" t="n">
-        <v>1.2275732</v>
+        <v>1.2768738</v>
       </c>
       <c r="K303" s="20" t="n">
-        <v>1.6484036</v>
+        <v>0.9316737</v>
       </c>
       <c r="L303" s="22" t="n">
-        <v>-19.12873855815686</v>
+        <v>11.92118146045501</v>
       </c>
       <c r="M303" s="21" t="inlineStr">
         <is>
@@ -26893,34 +26893,42 @@
         </is>
       </c>
       <c r="N303" s="22" t="n">
-        <v>-91.03151464667501</v>
+        <v>24.78287343641048</v>
       </c>
       <c r="O303" s="22" t="n">
-        <v>-45.63612933458294</v>
-      </c>
-      <c r="P303" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>41.01482854494903</v>
+      </c>
+      <c r="P303" s="20" t="n">
+        <v>-2.120166526673792</v>
       </c>
       <c r="Q303" s="22" t="n">
-        <v>-23.49397551426781</v>
+        <v>56.60500796835277</v>
       </c>
       <c r="R303" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S303" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T303" s="15" t="n"/>
-      <c r="U303" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S303" s="20" t="n">
+        <v>0.7705855121065255</v>
+      </c>
+      <c r="T303" s="15" t="inlineStr">
+        <is>
+          <t>Tankers (87%)</t>
+        </is>
+      </c>
+      <c r="U303" s="17" t="inlineStr">
+        <is>
+          <t>Tankers 87%; Marine Services And Other 13%</t>
+        </is>
+      </c>
       <c r="V303" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W303" s="17" t="n"/>
-      <c r="X303" s="15" t="n"/>
+      <c r="X303" s="15" t="inlineStr">
+        <is>
+          <t>Marine Services And  +10%</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="16" customHeight="1">
       <c r="A304" s="13" t="n">
@@ -26928,12 +26936,12 @@
       </c>
       <c r="B304" s="14" t="inlineStr">
         <is>
-          <t>LTCH</t>
+          <t>AWRE</t>
         </is>
       </c>
       <c r="C304" s="15" t="inlineStr">
         <is>
-          <t>Latch Inc. Common Stock</t>
+          <t>Aware, Inc.</t>
         </is>
       </c>
       <c r="D304" s="16" t="inlineStr">
@@ -26947,7 +26955,7 @@
         </is>
       </c>
       <c r="F304" s="18" t="n">
-        <v>32851562</v>
+        <v>28139898</v>
       </c>
       <c r="G304" s="19" t="inlineStr">
         <is>
@@ -26955,7 +26963,7 @@
         </is>
       </c>
       <c r="H304" s="20" t="n">
-        <v>-0.0075030035299217</v>
+        <v>-1.513124630984469</v>
       </c>
       <c r="I304" s="21" t="inlineStr">
         <is>
@@ -26963,28 +26971,24 @@
         </is>
       </c>
       <c r="J304" s="20" t="n">
-        <v>0.0870110976914682</v>
+        <v>1.2275732</v>
       </c>
       <c r="K304" s="20" t="n">
-        <v>0.794283413926499</v>
-      </c>
-      <c r="L304" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.6484036</v>
+      </c>
+      <c r="L304" s="22" t="n">
+        <v>-19.12873855815686</v>
       </c>
       <c r="M304" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N304" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N304" s="22" t="n">
+        <v>-91.03151464667501</v>
       </c>
       <c r="O304" s="22" t="n">
-        <v>-351.3757253384913</v>
+        <v>-45.63612933458294</v>
       </c>
       <c r="P304" s="21" t="inlineStr">
         <is>
@@ -26992,7 +26996,7 @@
         </is>
       </c>
       <c r="Q304" s="22" t="n">
-        <v>71.42858359278503</v>
+        <v>-23.49397551426781</v>
       </c>
       <c r="R304" s="18" t="n">
         <v>0</v>
@@ -27005,13 +27009,9 @@
       <c r="T304" s="15" t="n"/>
       <c r="U304" s="17" t="n"/>
       <c r="V304" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W304" s="17" t="inlineStr">
-        <is>
-          <t>Non Us 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W304" s="17" t="n"/>
       <c r="X304" s="15" t="n"/>
     </row>
     <row r="305" ht="16" customHeight="1">
@@ -33237,12 +33237,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>SNDR</t>
+          <t>CMCT</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Schneider National, Inc.</t>
+          <t>CIM Commercial Trust Corporati</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -33252,11 +33252,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>6355260928</v>
+        <v>10022646</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -33264,49 +33264,53 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>11.262</v>
+        <v>21.25711007962565</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>64.80356999999999</v>
+        <v>0.016938176</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>2.104134</v>
+        <v>0.0391425514049715</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>1.1206596</v>
-      </c>
-      <c r="L69" s="22" t="n">
-        <v>0.6860457893696701</v>
-      </c>
-      <c r="M69" s="22" t="n">
-        <v>1.1</v>
+        <v>0.08807942631666819</v>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M69" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N69" s="22" t="n">
-        <v>5.202221455241441</v>
+        <v>46.79635412727057</v>
       </c>
       <c r="O69" s="22" t="n">
-        <v>10.84925615173094</v>
+        <v>502.2000508218427</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.2708367181153533</v>
+        <v>1.289717709720373</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>50.42707445283197</v>
+        <v>-99.5848595732152</v>
       </c>
       <c r="R69" s="18" t="n">
         <v>4</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.34731905609149</v>
+        <v>0.3370207613496181</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Office Properties (43%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Truckload 26%; Logist</t>
+          <t>Office Properties 43%; Hotel Properties 36%; Multifamily Properties 14%</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
@@ -33315,7 +33319,7 @@
       <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Truckload +12%</t>
+          <t>Hotel Properties +10%</t>
         </is>
       </c>
     </row>
@@ -33325,12 +33329,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>SNDR</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Cnh Industrial N.V.</t>
+          <t>Schneider National, Inc.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -33344,7 +33348,7 @@
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>13676654592</v>
+        <v>6355260928</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -33352,62 +33356,58 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>35.749</v>
+        <v>11.262</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>34.46875</v>
+        <v>64.80356999999999</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>1.7597319</v>
+        <v>2.104134</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>0.7559086</v>
+        <v>1.1206596</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>-23.15624759473343</v>
+        <v>0.6860457893696701</v>
       </c>
       <c r="M70" s="22" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>26.69022000963545</v>
+        <v>5.202221455241441</v>
       </c>
       <c r="O70" s="22" t="n">
-        <v>12.77737298801086</v>
+        <v>10.84925615173094</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>-0.8216692586832556</v>
+        <v>0.2708367181153533</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>-14.53210106408921</v>
+        <v>50.42707445283197</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.2973036954946031</v>
+        <v>0.34731905609149</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Agricultural Equipment (37%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Agricultural Equipment 37%; Agriculture 37%; Construction Equipment 9%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Truckload 26%; Logist</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="W70" s="17" t="inlineStr">
-        <is>
-          <t>Rest Of World And Other 49%; US 16%; Others Countries 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W70" s="17" t="n"/>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Construction Equipme +12%</t>
+          <t>Truckload +12%</t>
         </is>
       </c>
     </row>
@@ -33417,12 +33417,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>CMCT</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>CIM Commercial Trust Corporati</t>
+          <t>Cnh Industrial N.V.</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -33432,11 +33432,11 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>10022646</v>
+        <v>13676654592</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -33444,62 +33444,62 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>21.25711007962565</v>
+        <v>35.749</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>0.016938176</v>
+        <v>34.46875</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>0.0391425514049715</v>
+        <v>1.7597319</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>0.08807942631666819</v>
-      </c>
-      <c r="L71" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M71" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.7559086</v>
+      </c>
+      <c r="L71" s="22" t="n">
+        <v>-23.15624759473343</v>
+      </c>
+      <c r="M71" s="22" t="n">
+        <v>0.91</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>46.79635412727057</v>
+        <v>26.69022000963545</v>
       </c>
       <c r="O71" s="22" t="n">
-        <v>502.2000508218427</v>
+        <v>12.77737298801086</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>1.289717709720373</v>
+        <v>-0.8216692586832556</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>-99.5848595732152</v>
+        <v>-14.53210106408921</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.3370207613496181</v>
+        <v>0.2973036954946031</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>Office Properties (43%)</t>
+          <t>Agricultural Equipment (37%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>Office Properties 43%; Hotel Properties 36%; Multifamily Properties 14%</t>
+          <t>Agricultural Equipment 37%; Agriculture 37%; Construction Equipment 9%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" s="17" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="W71" s="17" t="inlineStr">
+        <is>
+          <t>Rest Of World And Other 49%; US 16%; Others Countries 9%</t>
+        </is>
+      </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Hotel Properties +10%</t>
+          <t>Construction Equipme +12%</t>
         </is>
       </c>
     </row>
@@ -36984,26 +36984,26 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>LGPS</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>LogProstyle Inc. Common Shares</t>
+          <t>The LGL Group, Inc.</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F46" s="18" t="n">
-        <v>28066240</v>
+        <v>44608460</v>
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
@@ -37011,62 +37011,66 @@
         </is>
       </c>
       <c r="H46" s="20" t="n">
-        <v>11.30448758239022</v>
+        <v>1.723</v>
       </c>
       <c r="I46" s="20" t="n">
-        <v>5.1682606</v>
+        <v>135.0532271386431</v>
       </c>
       <c r="J46" s="20" t="n">
-        <v>0.0070678140203218</v>
+        <v>0.97999716</v>
       </c>
       <c r="K46" s="20" t="n">
-        <v>0.0013590796650376</v>
-      </c>
-      <c r="L46" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M46" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N46" s="22" t="n">
-        <v>6.413053831654871</v>
+        <v>10.287929</v>
+      </c>
+      <c r="L46" s="22" t="n">
+        <v>2.07718822715239</v>
+      </c>
+      <c r="M46" s="22" t="n">
+        <v>0.01310528849938</v>
+      </c>
+      <c r="N46" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O46" s="22" t="n">
-        <v>7.27474752209538</v>
-      </c>
-      <c r="P46" s="20" t="n">
-        <v>8.492030230938919</v>
+        <v>6.47637323099064</v>
+      </c>
+      <c r="P46" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q46" s="22" t="n">
-        <v>-8.843762286939159</v>
+        <v>1.59651865959342</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S46" s="20" t="n">
-        <v>0.8379545771357341</v>
+        <v>0.5814947574810531</v>
       </c>
       <c r="T46" s="15" t="inlineStr">
         <is>
-          <t>Real Estates (91%)</t>
+          <t>Electronic Instruments (70%)</t>
         </is>
       </c>
       <c r="U46" s="17" t="inlineStr">
         <is>
-          <t>Real Estates 91%; Hotels 6%; Other 3%</t>
+          <t>Electronic Instruments 70%; Merchant Investment 30%</t>
         </is>
       </c>
       <c r="V46" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W46" s="17" t="inlineStr">
+        <is>
+          <t>US 46%; Non Us 27%; All Other Foreign Countries 7%</t>
+        </is>
+      </c>
       <c r="X46" s="15" t="inlineStr">
         <is>
-          <t>Real Estates +10%</t>
+          <t>Electronic Instrumen +53%</t>
         </is>
       </c>
     </row>
@@ -37076,12 +37080,12 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>CRTO</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>The LGL Group, Inc.</t>
+          <t>Criteo S.A.</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -37091,11 +37095,11 @@
       </c>
       <c r="E47" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F47" s="18" t="n">
-        <v>44608460</v>
+        <v>887318336</v>
       </c>
       <c r="G47" s="19" t="inlineStr">
         <is>
@@ -37103,66 +37107,64 @@
         </is>
       </c>
       <c r="H47" s="20" t="n">
-        <v>1.723</v>
+        <v>2.455</v>
       </c>
       <c r="I47" s="20" t="n">
-        <v>135.0532271386431</v>
+        <v>8.2910795</v>
       </c>
       <c r="J47" s="20" t="n">
-        <v>0.97999716</v>
+        <v>0.78100127</v>
       </c>
       <c r="K47" s="20" t="n">
-        <v>10.287929</v>
+        <v>0.4626013</v>
       </c>
       <c r="L47" s="22" t="n">
-        <v>2.07718822715239</v>
-      </c>
-      <c r="M47" s="22" t="n">
-        <v>0.01310528849938</v>
-      </c>
-      <c r="N47" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.28799696978199</v>
+      </c>
+      <c r="M47" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N47" s="22" t="n">
+        <v>12.09779410050992</v>
       </c>
       <c r="O47" s="22" t="n">
-        <v>6.47637323099064</v>
-      </c>
-      <c r="P47" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.25799885125514</v>
+      </c>
+      <c r="P47" s="20" t="n">
+        <v>-2.407378490646129</v>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>1.59651865959342</v>
+        <v>-25.89173351257982</v>
       </c>
       <c r="R47" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S47" s="20" t="n">
-        <v>0.5814947574810531</v>
+        <v>0.877480231574409</v>
       </c>
       <c r="T47" s="15" t="inlineStr">
         <is>
-          <t>Electronic Instruments (70%)</t>
+          <t>Performance Media (93%)</t>
         </is>
       </c>
       <c r="U47" s="17" t="inlineStr">
         <is>
-          <t>Electronic Instruments 70%; Merchant Investment 30%</t>
+          <t>Performance Media 93%; Retail Media 7%</t>
         </is>
       </c>
       <c r="V47" s="18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W47" s="17" t="inlineStr">
         <is>
-          <t>US 46%; Non Us 27%; All Other Foreign Countries 7%</t>
+          <t>Americas 26%; US 23%; EMEA 23%</t>
         </is>
       </c>
       <c r="X47" s="15" t="inlineStr">
         <is>
-          <t>Electronic Instrumen +53%</t>
+          <t>Retail Media +11%</t>
         </is>
       </c>
     </row>
@@ -37172,26 +37174,26 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>CRTO</t>
+          <t>LGPS</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Criteo S.A.</t>
+          <t>LogProstyle Inc. Common Shares</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F48" s="18" t="n">
-        <v>887318336</v>
+        <v>28066240</v>
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
@@ -37199,19 +37201,21 @@
         </is>
       </c>
       <c r="H48" s="20" t="n">
-        <v>2.455</v>
+        <v>11.30448758239022</v>
       </c>
       <c r="I48" s="20" t="n">
-        <v>8.2910795</v>
+        <v>5.1682606</v>
       </c>
       <c r="J48" s="20" t="n">
-        <v>0.78100127</v>
+        <v>0.0070678140203218</v>
       </c>
       <c r="K48" s="20" t="n">
-        <v>0.4626013</v>
-      </c>
-      <c r="L48" s="22" t="n">
-        <v>3.28799696978199</v>
+        <v>0.0013590796650376</v>
+      </c>
+      <c r="L48" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M48" s="21" t="inlineStr">
         <is>
@@ -37219,44 +37223,40 @@
         </is>
       </c>
       <c r="N48" s="22" t="n">
-        <v>12.09779410050992</v>
+        <v>6.413053831654871</v>
       </c>
       <c r="O48" s="22" t="n">
-        <v>7.25799885125514</v>
+        <v>7.27474752209538</v>
       </c>
       <c r="P48" s="20" t="n">
-        <v>-2.407378490646129</v>
+        <v>8.492030230938919</v>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>-25.89173351257982</v>
+        <v>-8.843762286939159</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S48" s="20" t="n">
-        <v>0.877480231574409</v>
+        <v>0.8379545771357341</v>
       </c>
       <c r="T48" s="15" t="inlineStr">
         <is>
-          <t>Performance Media (93%)</t>
+          <t>Real Estates (91%)</t>
         </is>
       </c>
       <c r="U48" s="17" t="inlineStr">
         <is>
-          <t>Performance Media 93%; Retail Media 7%</t>
+          <t>Real Estates 91%; Hotels 6%; Other 3%</t>
         </is>
       </c>
       <c r="V48" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W48" s="17" t="inlineStr">
-        <is>
-          <t>Americas 26%; US 23%; EMEA 23%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W48" s="17" t="n"/>
       <c r="X48" s="15" t="inlineStr">
         <is>
-          <t>Retail Media +11%</t>
+          <t>Real Estates +10%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -8202,17 +8202,17 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>MWC</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>CEA Industries Inc. Common Sto</t>
+          <t>Micware Co. Ltd. American Depo</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>117105648</v>
+        <v>200540528</v>
       </c>
       <c r="G92" s="19" t="inlineStr">
         <is>
@@ -8229,19 +8229,21 @@
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>0.6248851029254567</v>
+        <v>0.4515807303367515</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>0.0064324588</v>
+        <v>19.852942</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>0.3209393555330036</v>
+        <v>0.0238744351354948</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>7.502435322965224</v>
-      </c>
-      <c r="L92" s="22" t="n">
-        <v>-2.60911839196688</v>
+        <v>0.0091588624114498</v>
+      </c>
+      <c r="L92" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M92" s="21" t="inlineStr">
         <is>
@@ -8249,39 +8251,33 @@
         </is>
       </c>
       <c r="N92" s="22" t="n">
-        <v>49.05763952706174</v>
+        <v>24.58992997926714</v>
       </c>
       <c r="O92" s="22" t="n">
-        <v>1123.050207258394</v>
+        <v>18.04218527853984</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>-0.043155834361193</v>
+        <v>0.307284762176941</v>
       </c>
       <c r="Q92" s="22" t="n">
-        <v>-62.13592226588784</v>
+        <v>-58.84146245727219</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S92" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T92" s="15" t="inlineStr">
-        <is>
-          <t>CEA Industry (100%)</t>
-        </is>
-      </c>
-      <c r="U92" s="17" t="inlineStr">
-        <is>
-          <t>CEA Industry 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S92" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T92" s="15" t="n"/>
+      <c r="U92" s="17" t="n"/>
       <c r="V92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="W92" s="17" t="inlineStr">
         <is>
-          <t>CA 91%; US 9%</t>
+          <t>JP 98%; International 2%</t>
         </is>
       </c>
       <c r="X92" s="15" t="n"/>
@@ -8292,12 +8288,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>RLX</t>
+          <t>BNC</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Rlx Technology Inc.</t>
+          <t>CEA Industries Inc. Common Sto</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -8307,11 +8303,11 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>2273393664</v>
+        <v>117105648</v>
       </c>
       <c r="G93" s="19" t="inlineStr">
         <is>
@@ -8319,57 +8315,59 @@
         </is>
       </c>
       <c r="H93" s="20" t="n">
-        <v>-133.9863626918812</v>
+        <v>0.6248851029254567</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>16.909092</v>
+        <v>0.0064324588</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>0.9801533</v>
+        <v>0.3209393555330036</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>0.51921856</v>
+        <v>7.502435322965224</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>6.20715198755828</v>
-      </c>
-      <c r="M93" s="22" t="n">
-        <v>5.38</v>
+        <v>-2.60911839196688</v>
+      </c>
+      <c r="M93" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N93" s="22" t="n">
-        <v>3.17186207827716</v>
+        <v>49.05763952706174</v>
       </c>
       <c r="O93" s="22" t="n">
-        <v>9.07933087209199</v>
+        <v>1123.050207258394</v>
       </c>
       <c r="P93" s="20" t="n">
-        <v>-14.67579135780852</v>
+        <v>-0.043155834361193</v>
       </c>
       <c r="Q93" s="22" t="n">
-        <v>-16.21621665160441</v>
+        <v>-62.13592226588784</v>
       </c>
       <c r="R93" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" s="15" t="inlineStr">
+        <is>
+          <t>CEA Industry (100%)</t>
+        </is>
+      </c>
+      <c r="U93" s="17" t="inlineStr">
+        <is>
+          <t>CEA Industry 100%</t>
+        </is>
+      </c>
+      <c r="V93" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S93" s="20" t="n">
-        <v>0.7340932777350748</v>
-      </c>
-      <c r="T93" s="15" t="inlineStr">
-        <is>
-          <t>Core Markets (84%)</t>
-        </is>
-      </c>
-      <c r="U93" s="17" t="inlineStr">
-        <is>
-          <t>Core Markets 84%; Europe Acquisition 16%</t>
-        </is>
-      </c>
-      <c r="V93" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="W93" s="17" t="inlineStr">
         <is>
-          <t>HK 34%; CN 31%; Countries Other Than China And United Kingdo</t>
+          <t>CA 91%; US 9%</t>
         </is>
       </c>
       <c r="X93" s="15" t="n"/>
@@ -8380,12 +8378,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>KTTA</t>
+          <t>RLX</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Pasithea Therapeutics Corp. Co</t>
+          <t>Rlx Technology Inc.</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -8395,11 +8393,11 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>18157410</v>
+        <v>2273393664</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
@@ -8407,57 +8405,59 @@
         </is>
       </c>
       <c r="H94" s="20" t="n">
-        <v>1.871</v>
-      </c>
-      <c r="I94" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-133.9863626918812</v>
+      </c>
+      <c r="I94" s="20" t="n">
+        <v>16.909092</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.24722475</v>
+        <v>0.9801533</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>37.31800254439853</v>
+        <v>0.51921856</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>-75.68926236044288</v>
-      </c>
-      <c r="M94" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N94" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.20715198755828</v>
+      </c>
+      <c r="M94" s="22" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>3.17186207827716</v>
       </c>
       <c r="O94" s="22" t="n">
-        <v>-3174.405570547457</v>
-      </c>
-      <c r="P94" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.07933087209199</v>
+      </c>
+      <c r="P94" s="20" t="n">
+        <v>-14.67579135780852</v>
       </c>
       <c r="Q94" s="22" t="n">
-        <v>-9.407668978648449</v>
+        <v>-16.21621665160441</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T94" s="15" t="n"/>
-      <c r="U94" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S94" s="20" t="n">
+        <v>0.7340932777350748</v>
+      </c>
+      <c r="T94" s="15" t="inlineStr">
+        <is>
+          <t>Core Markets (84%)</t>
+        </is>
+      </c>
+      <c r="U94" s="17" t="inlineStr">
+        <is>
+          <t>Core Markets 84%; Europe Acquisition 16%</t>
+        </is>
+      </c>
       <c r="V94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W94" s="17" t="inlineStr">
+        <is>
+          <t>HK 34%; CN 31%; Countries Other Than China And United Kingdo</t>
+        </is>
+      </c>
       <c r="X94" s="15" t="n"/>
     </row>
     <row r="95" ht="16" customHeight="1">
@@ -8466,26 +8466,26 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>KTTA</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Micware Co. Ltd. American Depo</t>
+          <t>Pasithea Therapeutics Corp. Co</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>200540528</v>
+        <v>18157410</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
@@ -8493,38 +8493,42 @@
         </is>
       </c>
       <c r="H95" s="20" t="n">
-        <v>0.4515807303367515</v>
-      </c>
-      <c r="I95" s="20" t="n">
-        <v>19.852942</v>
+        <v>1.871</v>
+      </c>
+      <c r="I95" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J95" s="20" t="n">
-        <v>0.0238744351354948</v>
+        <v>0.24722475</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>0.0091588624114498</v>
-      </c>
-      <c r="L95" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>37.31800254439853</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>-75.68926236044288</v>
       </c>
       <c r="M95" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N95" s="22" t="n">
-        <v>24.58992997926714</v>
+      <c r="N95" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O95" s="22" t="n">
-        <v>18.04218527853984</v>
-      </c>
-      <c r="P95" s="20" t="n">
-        <v>0.307284762176941</v>
+        <v>-3174.405570547457</v>
+      </c>
+      <c r="P95" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q95" s="22" t="n">
-        <v>-58.84146245727219</v>
+        <v>-9.407668978648449</v>
       </c>
       <c r="R95" s="18" t="n">
         <v>0</v>
@@ -8537,13 +8541,9 @@
       <c r="T95" s="15" t="n"/>
       <c r="U95" s="17" t="n"/>
       <c r="V95" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W95" s="17" t="inlineStr">
-        <is>
-          <t>JP 98%; International 2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W95" s="17" t="n"/>
       <c r="X95" s="15" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
@@ -22842,12 +22842,12 @@
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>LTCH</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="C258" s="15" t="inlineStr">
         <is>
-          <t>Latch Inc. Common Stock</t>
+          <t>RCM Technologies, Inc.</t>
         </is>
       </c>
       <c r="D258" s="16" t="inlineStr">
@@ -22857,11 +22857,11 @@
       </c>
       <c r="E258" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F258" s="18" t="n">
-        <v>32851562</v>
+        <v>200225088</v>
       </c>
       <c r="G258" s="19" t="inlineStr">
         <is>
@@ -22869,64 +22869,60 @@
         </is>
       </c>
       <c r="H258" s="20" t="n">
-        <v>-0.0075030035299217</v>
-      </c>
-      <c r="I258" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.760999999999999</v>
+      </c>
+      <c r="I258" s="20" t="n">
+        <v>13.325473</v>
       </c>
       <c r="J258" s="20" t="n">
-        <v>0.0870110976914682</v>
+        <v>4.4812818</v>
       </c>
       <c r="K258" s="20" t="n">
-        <v>0.794283413926499</v>
-      </c>
-      <c r="L258" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M258" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N258" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.62970006</v>
+      </c>
+      <c r="L258" s="22" t="n">
+        <v>14.27938087426353</v>
+      </c>
+      <c r="M258" s="22" t="n">
+        <v>7.441462044564701</v>
+      </c>
+      <c r="N258" s="22" t="n">
+        <v>55.34887070062165</v>
       </c>
       <c r="O258" s="22" t="n">
-        <v>-351.3757253384913</v>
-      </c>
-      <c r="P258" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.34648282426018</v>
+      </c>
+      <c r="P258" s="20" t="n">
+        <v>0.8158970704077422</v>
       </c>
       <c r="Q258" s="22" t="n">
-        <v>71.42858359278503</v>
+        <v>-0.77252533785857</v>
       </c>
       <c r="R258" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S258" s="20" t="n">
+        <v>0.4181480808503012</v>
+      </c>
+      <c r="T258" s="15" t="inlineStr">
+        <is>
+          <t>Specialty Health Care (51%)</t>
+        </is>
+      </c>
+      <c r="U258" s="17" t="inlineStr">
+        <is>
+          <t>Specialty Health Care 51%; Engineering 38%; Life Sciences Data Solutions 11%</t>
+        </is>
+      </c>
+      <c r="V258" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S258" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T258" s="15" t="n"/>
-      <c r="U258" s="17" t="n"/>
-      <c r="V258" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W258" s="17" t="inlineStr">
-        <is>
-          <t>Non Us 100%</t>
-        </is>
-      </c>
-      <c r="X258" s="15" t="n"/>
+      <c r="W258" s="17" t="n"/>
+      <c r="X258" s="15" t="inlineStr">
+        <is>
+          <t>Engineering +49%</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="16" customHeight="1">
       <c r="A259" s="13" t="n">
@@ -22934,12 +22930,12 @@
       </c>
       <c r="B259" s="14" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>PBHC</t>
         </is>
       </c>
       <c r="C259" s="15" t="inlineStr">
         <is>
-          <t>RCM Technologies, Inc.</t>
+          <t>Pathfinder Bancorp, Inc.</t>
         </is>
       </c>
       <c r="D259" s="16" t="inlineStr">
@@ -22949,72 +22945,68 @@
       </c>
       <c r="E259" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F259" s="18" t="n">
-        <v>200225088</v>
+        <v>102606536</v>
       </c>
       <c r="G259" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H259" s="20" t="n">
-        <v>8.760999999999999</v>
+      <c r="H259" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I259" s="20" t="n">
-        <v>13.325473</v>
+        <v>13.96428325612177</v>
       </c>
       <c r="J259" s="20" t="n">
-        <v>4.4812818</v>
+        <v>0.8302536</v>
       </c>
       <c r="K259" s="20" t="n">
-        <v>0.62970006</v>
+        <v>3.423413</v>
       </c>
       <c r="L259" s="22" t="n">
-        <v>14.27938087426353</v>
+        <v>12.70377220280993</v>
       </c>
       <c r="M259" s="22" t="n">
-        <v>7.441462044564701</v>
-      </c>
-      <c r="N259" s="22" t="n">
-        <v>55.34887070062165</v>
+        <v>1.39099315110043</v>
+      </c>
+      <c r="N259" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O259" s="22" t="n">
-        <v>8.34648282426018</v>
-      </c>
-      <c r="P259" s="20" t="n">
-        <v>0.8158970704077422</v>
+        <v>0</v>
+      </c>
+      <c r="P259" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q259" s="22" t="n">
-        <v>-0.77252533785857</v>
+        <v>-7.86345363685683</v>
       </c>
       <c r="R259" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S259" s="20" t="n">
-        <v>0.4181480808503012</v>
-      </c>
-      <c r="T259" s="15" t="inlineStr">
-        <is>
-          <t>Specialty Health Care (51%)</t>
-        </is>
-      </c>
-      <c r="U259" s="17" t="inlineStr">
-        <is>
-          <t>Specialty Health Care 51%; Engineering 38%; Life Sciences Data Solutions 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S259" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T259" s="15" t="n"/>
+      <c r="U259" s="17" t="n"/>
       <c r="V259" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W259" s="17" t="n"/>
-      <c r="X259" s="15" t="inlineStr">
-        <is>
-          <t>Engineering +49%</t>
-        </is>
-      </c>
+      <c r="X259" s="15" t="n"/>
     </row>
     <row r="260" ht="16" customHeight="1">
       <c r="A260" s="13" t="n">
@@ -23022,12 +23014,12 @@
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>PBHC</t>
+          <t>SMID</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
         <is>
-          <t>Pathfinder Bancorp, Inc.</t>
+          <t>Smith-Midland Corporation</t>
         </is>
       </c>
       <c r="D260" s="16" t="inlineStr">
@@ -23037,52 +23029,46 @@
       </c>
       <c r="E260" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F260" s="18" t="n">
-        <v>102606536</v>
-      </c>
-      <c r="G260" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="H260" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>157869984</v>
+      </c>
+      <c r="G260" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="H260" s="20" t="n">
+        <v>8.513999999999999</v>
       </c>
       <c r="I260" s="20" t="n">
-        <v>13.96428325612177</v>
+        <v>15.025252</v>
       </c>
       <c r="J260" s="20" t="n">
-        <v>0.8302536</v>
+        <v>2.8363047</v>
       </c>
       <c r="K260" s="20" t="n">
-        <v>3.423413</v>
+        <v>1.7100302</v>
       </c>
       <c r="L260" s="22" t="n">
-        <v>12.70377220280993</v>
+        <v>-1.33140004307622</v>
       </c>
       <c r="M260" s="22" t="n">
-        <v>1.39099315110043</v>
-      </c>
-      <c r="N260" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N260" s="22" t="n">
+        <v>23.5026343072573</v>
       </c>
       <c r="O260" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P260" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.55148427969094</v>
+      </c>
+      <c r="P260" s="20" t="n">
+        <v>-0.3648145389542678</v>
       </c>
       <c r="Q260" s="22" t="n">
-        <v>-7.86345363685683</v>
+        <v>-5.50939003710083</v>
       </c>
       <c r="R260" s="18" t="n">
         <v>0</v>
@@ -23106,12 +23092,12 @@
       </c>
       <c r="B261" s="14" t="inlineStr">
         <is>
-          <t>SMID</t>
+          <t>HAFC</t>
         </is>
       </c>
       <c r="C261" s="15" t="inlineStr">
         <is>
-          <t>Smith-Midland Corporation</t>
+          <t>Hanmi Financial Corporation</t>
         </is>
       </c>
       <c r="D261" s="16" t="inlineStr">
@@ -23121,62 +23107,74 @@
       </c>
       <c r="E261" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F261" s="18" t="n">
-        <v>157869984</v>
-      </c>
-      <c r="G261" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>972469440</v>
+      </c>
+      <c r="G261" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H261" s="20" t="n">
-        <v>8.513999999999999</v>
+        <v>7.437587824860818</v>
       </c>
       <c r="I261" s="20" t="n">
-        <v>15.025252</v>
+        <v>12.190297</v>
       </c>
       <c r="J261" s="20" t="n">
-        <v>2.8363047</v>
+        <v>1.2036252</v>
       </c>
       <c r="K261" s="20" t="n">
-        <v>1.7100302</v>
+        <v>3.676925</v>
       </c>
       <c r="L261" s="22" t="n">
-        <v>-1.33140004307622</v>
+        <v>11.99772815882008</v>
       </c>
       <c r="M261" s="22" t="n">
-        <v>0</v>
+        <v>3.67615130332913</v>
       </c>
       <c r="N261" s="22" t="n">
-        <v>23.5026343072573</v>
+        <v>14.10544231322912</v>
       </c>
       <c r="O261" s="22" t="n">
-        <v>21.55148427969094</v>
-      </c>
-      <c r="P261" s="20" t="n">
-        <v>-0.3648145389542678</v>
+        <v>30.38684440898463</v>
+      </c>
+      <c r="P261" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q261" s="22" t="n">
-        <v>-5.50939003710083</v>
+        <v>26.35181147857969</v>
       </c>
       <c r="R261" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S261" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T261" s="15" t="n"/>
-      <c r="U261" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S261" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T261" s="15" t="inlineStr">
+        <is>
+          <t>Banking (100%)</t>
+        </is>
+      </c>
+      <c r="U261" s="17" t="inlineStr">
+        <is>
+          <t>Banking 100%</t>
+        </is>
+      </c>
       <c r="V261" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W261" s="17" t="n"/>
-      <c r="X261" s="15" t="n"/>
+      <c r="X261" s="15" t="inlineStr">
+        <is>
+          <t>Banking +15%</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="16" customHeight="1">
       <c r="A262" s="13" t="n">
@@ -23184,12 +23182,12 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>HAFC</t>
+          <t>TPET</t>
         </is>
       </c>
       <c r="C262" s="15" t="inlineStr">
         <is>
-          <t>Hanmi Financial Corporation</t>
+          <t>Trio Petroleum Corp</t>
         </is>
       </c>
       <c r="D262" s="16" t="inlineStr">
@@ -23199,11 +23197,11 @@
       </c>
       <c r="E262" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F262" s="18" t="n">
-        <v>972469440</v>
+        <v>12850906</v>
       </c>
       <c r="G262" s="19" t="inlineStr">
         <is>
@@ -23211,28 +23209,32 @@
         </is>
       </c>
       <c r="H262" s="20" t="n">
-        <v>7.437587824860818</v>
-      </c>
-      <c r="I262" s="20" t="n">
-        <v>12.190297</v>
+        <v>1.716</v>
+      </c>
+      <c r="I262" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J262" s="20" t="n">
-        <v>1.2036252</v>
+        <v>0.34600717</v>
       </c>
       <c r="K262" s="20" t="n">
-        <v>3.676925</v>
+        <v>18.488012</v>
       </c>
       <c r="L262" s="22" t="n">
-        <v>11.99772815882008</v>
-      </c>
-      <c r="M262" s="22" t="n">
-        <v>3.67615130332913</v>
+        <v>-23.59537140805481</v>
+      </c>
+      <c r="M262" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N262" s="22" t="n">
-        <v>14.10544231322912</v>
+        <v>-27.73349846628827</v>
       </c>
       <c r="O262" s="22" t="n">
-        <v>30.38684440898463</v>
+        <v>0</v>
       </c>
       <c r="P262" s="21" t="inlineStr">
         <is>
@@ -23240,33 +23242,23 @@
         </is>
       </c>
       <c r="Q262" s="22" t="n">
-        <v>26.35181147857969</v>
+        <v>-81.41333394580417</v>
       </c>
       <c r="R262" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S262" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T262" s="15" t="inlineStr">
-        <is>
-          <t>Banking (100%)</t>
-        </is>
-      </c>
-      <c r="U262" s="17" t="inlineStr">
-        <is>
-          <t>Banking 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S262" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T262" s="15" t="n"/>
+      <c r="U262" s="17" t="n"/>
       <c r="V262" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W262" s="17" t="n"/>
-      <c r="X262" s="15" t="inlineStr">
-        <is>
-          <t>Banking +15%</t>
-        </is>
-      </c>
+      <c r="X262" s="15" t="n"/>
     </row>
     <row r="263" ht="16" customHeight="1">
       <c r="A263" s="13" t="n">
@@ -23274,12 +23266,12 @@
       </c>
       <c r="B263" s="14" t="inlineStr">
         <is>
-          <t>TPET</t>
+          <t>AKBA</t>
         </is>
       </c>
       <c r="C263" s="15" t="inlineStr">
         <is>
-          <t>Trio Petroleum Corp</t>
+          <t>Akebia Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="D263" s="16" t="inlineStr">
@@ -23289,11 +23281,11 @@
       </c>
       <c r="E263" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F263" s="18" t="n">
-        <v>12850906</v>
+        <v>305814400</v>
       </c>
       <c r="G263" s="19" t="inlineStr">
         <is>
@@ -23301,7 +23293,7 @@
         </is>
       </c>
       <c r="H263" s="20" t="n">
-        <v>1.716</v>
+        <v>28.087</v>
       </c>
       <c r="I263" s="21" t="inlineStr">
         <is>
@@ -23309,13 +23301,13 @@
         </is>
       </c>
       <c r="J263" s="20" t="n">
-        <v>0.34600717</v>
+        <v>11.176471</v>
       </c>
       <c r="K263" s="20" t="n">
-        <v>18.488012</v>
+        <v>1.3158741</v>
       </c>
       <c r="L263" s="22" t="n">
-        <v>-23.59537140805481</v>
+        <v>21.06320195668403</v>
       </c>
       <c r="M263" s="21" t="inlineStr">
         <is>
@@ -23323,34 +23315,42 @@
         </is>
       </c>
       <c r="N263" s="22" t="n">
-        <v>-27.73349846628827</v>
+        <v>-20.3691903301605</v>
       </c>
       <c r="O263" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.19871632034412</v>
+      </c>
+      <c r="P263" s="20" t="n">
+        <v>-6.123532931375708</v>
       </c>
       <c r="Q263" s="22" t="n">
-        <v>-81.41333394580417</v>
+        <v>-58.26771816145106</v>
       </c>
       <c r="R263" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S263" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T263" s="15" t="n"/>
-      <c r="U263" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S263" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T263" s="15" t="inlineStr">
+        <is>
+          <t>Reportable (100%)</t>
+        </is>
+      </c>
+      <c r="U263" s="17" t="inlineStr">
+        <is>
+          <t>Reportable 100%</t>
+        </is>
+      </c>
       <c r="V263" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W263" s="17" t="n"/>
-      <c r="X263" s="15" t="n"/>
+      <c r="X263" s="15" t="inlineStr">
+        <is>
+          <t>Reportable +47%</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="16" customHeight="1">
       <c r="A264" s="13" t="n">
@@ -23358,12 +23358,12 @@
       </c>
       <c r="B264" s="14" t="inlineStr">
         <is>
-          <t>AKBA</t>
+          <t>NNDM</t>
         </is>
       </c>
       <c r="C264" s="15" t="inlineStr">
         <is>
-          <t>Akebia Therapeutics, Inc.</t>
+          <t>Nano Dimension Ltd.</t>
         </is>
       </c>
       <c r="D264" s="16" t="inlineStr">
@@ -23373,11 +23373,11 @@
       </c>
       <c r="E264" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F264" s="18" t="n">
-        <v>305814400</v>
+        <v>290289216</v>
       </c>
       <c r="G264" s="19" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         </is>
       </c>
       <c r="H264" s="20" t="n">
-        <v>28.087</v>
+        <v>1.938</v>
       </c>
       <c r="I264" s="21" t="inlineStr">
         <is>
@@ -23393,56 +23393,54 @@
         </is>
       </c>
       <c r="J264" s="20" t="n">
-        <v>11.176471</v>
+        <v>0.5912596</v>
       </c>
       <c r="K264" s="20" t="n">
-        <v>1.3158741</v>
+        <v>2.465071</v>
       </c>
       <c r="L264" s="22" t="n">
-        <v>21.06320195668403</v>
+        <v>-19.25127525233317</v>
       </c>
       <c r="M264" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N264" s="22" t="n">
-        <v>-20.3691903301605</v>
+      <c r="N264" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O264" s="22" t="n">
-        <v>9.19871632034412</v>
-      </c>
-      <c r="P264" s="20" t="n">
-        <v>-6.123532931375708</v>
+        <v>-117.0241221433662</v>
+      </c>
+      <c r="P264" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q264" s="22" t="n">
-        <v>-58.26771816145106</v>
+        <v>-2.54167440699175</v>
       </c>
       <c r="R264" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S264" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T264" s="15" t="inlineStr">
-        <is>
-          <t>Reportable (100%)</t>
-        </is>
-      </c>
-      <c r="U264" s="17" t="inlineStr">
-        <is>
-          <t>Reportable 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S264" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T264" s="15" t="n"/>
+      <c r="U264" s="17" t="n"/>
       <c r="V264" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W264" s="17" t="n"/>
-      <c r="X264" s="15" t="inlineStr">
-        <is>
-          <t>Reportable +47%</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="W264" s="17" t="inlineStr">
+        <is>
+          <t>Americas 44%; EMEA 40%; Asia Pacific 16%</t>
+        </is>
+      </c>
+      <c r="X264" s="15" t="n"/>
     </row>
     <row r="265" ht="16" customHeight="1">
       <c r="A265" s="13" t="n">
@@ -23450,12 +23448,12 @@
       </c>
       <c r="B265" s="14" t="inlineStr">
         <is>
-          <t>NNDM</t>
+          <t>GHG</t>
         </is>
       </c>
       <c r="C265" s="15" t="inlineStr">
         <is>
-          <t>Nano Dimension Ltd.</t>
+          <t>Greentree Hospitality Group Lt</t>
         </is>
       </c>
       <c r="D265" s="16" t="inlineStr">
@@ -23465,11 +23463,11 @@
       </c>
       <c r="E265" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F265" s="18" t="n">
-        <v>290289216</v>
+        <v>114003888</v>
       </c>
       <c r="G265" s="19" t="inlineStr">
         <is>
@@ -23477,62 +23475,60 @@
         </is>
       </c>
       <c r="H265" s="20" t="n">
-        <v>1.938</v>
-      </c>
-      <c r="I265" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-2.258489766586047</v>
+      </c>
+      <c r="I265" s="20" t="n">
+        <v>4.7079167</v>
       </c>
       <c r="J265" s="20" t="n">
-        <v>0.5912596</v>
+        <v>0.4910807</v>
       </c>
       <c r="K265" s="20" t="n">
-        <v>2.465071</v>
+        <v>0.10388986</v>
       </c>
       <c r="L265" s="22" t="n">
-        <v>-19.25127525233317</v>
-      </c>
-      <c r="M265" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N265" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.52369024466955</v>
+      </c>
+      <c r="M265" s="22" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="N265" s="22" t="n">
+        <v>23.86689445916182</v>
       </c>
       <c r="O265" s="22" t="n">
-        <v>-117.0241221433662</v>
-      </c>
-      <c r="P265" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>12.44580913896663</v>
+      </c>
+      <c r="P265" s="20" t="n">
+        <v>-9.805486307018036</v>
       </c>
       <c r="Q265" s="22" t="n">
-        <v>-2.54167440699175</v>
+        <v>-46.44549519371849</v>
       </c>
       <c r="R265" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S265" s="20" t="n">
+        <v>0.429524466410785</v>
+      </c>
+      <c r="T265" s="15" t="inlineStr">
+        <is>
+          <t>Revenue From External  (50%)</t>
+        </is>
+      </c>
+      <c r="U265" s="17" t="inlineStr">
+        <is>
+          <t>Revenue From External Customers 50%; Hotel Business 42%; Restaurant Business 8%</t>
+        </is>
+      </c>
+      <c r="V265" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S265" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T265" s="15" t="n"/>
-      <c r="U265" s="17" t="n"/>
-      <c r="V265" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W265" s="17" t="inlineStr">
-        <is>
-          <t>Americas 44%; EMEA 40%; Asia Pacific 16%</t>
-        </is>
-      </c>
-      <c r="X265" s="15" t="n"/>
+      <c r="W265" s="17" t="n"/>
+      <c r="X265" s="15" t="inlineStr">
+        <is>
+          <t>Hotel Business -88%</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="16" customHeight="1">
       <c r="A266" s="13" t="n">
@@ -23540,12 +23536,12 @@
       </c>
       <c r="B266" s="14" t="inlineStr">
         <is>
-          <t>GHG</t>
+          <t>PROV</t>
         </is>
       </c>
       <c r="C266" s="15" t="inlineStr">
         <is>
-          <t>Greentree Hospitality Group Lt</t>
+          <t xml:space="preserve">Provident Financial Holdings, </t>
         </is>
       </c>
       <c r="D266" s="16" t="inlineStr">
@@ -23555,72 +23551,68 @@
       </c>
       <c r="E266" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F266" s="18" t="n">
-        <v>114003888</v>
+        <v>107563488</v>
       </c>
       <c r="G266" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H266" s="20" t="n">
-        <v>-2.258489766586047</v>
+      <c r="H266" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I266" s="20" t="n">
-        <v>4.7079167</v>
+        <v>18.494625</v>
       </c>
       <c r="J266" s="20" t="n">
-        <v>0.4910807</v>
+        <v>0.8592697</v>
       </c>
       <c r="K266" s="20" t="n">
-        <v>0.10388986</v>
+        <v>2.7159069</v>
       </c>
       <c r="L266" s="22" t="n">
-        <v>2.52369024466955</v>
+        <v>8.407967835537141</v>
       </c>
       <c r="M266" s="22" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="N266" s="22" t="n">
-        <v>23.86689445916182</v>
+        <v>3.26</v>
+      </c>
+      <c r="N266" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O266" s="22" t="n">
-        <v>12.44580913896663</v>
-      </c>
-      <c r="P266" s="20" t="n">
-        <v>-9.805486307018036</v>
+        <v>0</v>
+      </c>
+      <c r="P266" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q266" s="22" t="n">
-        <v>-46.44549519371849</v>
+        <v>13.3670912336621</v>
       </c>
       <c r="R266" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S266" s="20" t="n">
-        <v>0.429524466410785</v>
-      </c>
-      <c r="T266" s="15" t="inlineStr">
-        <is>
-          <t>Revenue From External  (50%)</t>
-        </is>
-      </c>
-      <c r="U266" s="17" t="inlineStr">
-        <is>
-          <t>Revenue From External Customers 50%; Hotel Business 42%; Restaurant Business 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S266" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T266" s="15" t="n"/>
+      <c r="U266" s="17" t="n"/>
       <c r="V266" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W266" s="17" t="n"/>
-      <c r="X266" s="15" t="inlineStr">
-        <is>
-          <t>Hotel Business -88%</t>
-        </is>
-      </c>
+      <c r="X266" s="15" t="n"/>
     </row>
     <row r="267" ht="16" customHeight="1">
       <c r="A267" s="13" t="n">
@@ -23628,12 +23620,12 @@
       </c>
       <c r="B267" s="14" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C267" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provident Financial Holdings, </t>
+          <t>Eagle Bancorp, Inc.</t>
         </is>
       </c>
       <c r="D267" s="16" t="inlineStr">
@@ -23647,7 +23639,7 @@
         </is>
       </c>
       <c r="F267" s="18" t="n">
-        <v>107563488</v>
+        <v>888337280</v>
       </c>
       <c r="G267" s="19" t="inlineStr">
         <is>
@@ -23659,20 +23651,22 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I267" s="20" t="n">
-        <v>18.494625</v>
+      <c r="I267" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J267" s="20" t="n">
-        <v>0.8592697</v>
+        <v>0.77562106</v>
       </c>
       <c r="K267" s="20" t="n">
-        <v>2.7159069</v>
+        <v>41.56547</v>
       </c>
       <c r="L267" s="22" t="n">
-        <v>8.407967835537141</v>
+        <v>2.78226065129031</v>
       </c>
       <c r="M267" s="22" t="n">
-        <v>3.26</v>
+        <v>0.67000003</v>
       </c>
       <c r="N267" s="21" t="inlineStr">
         <is>
@@ -23688,7 +23682,7 @@
         </is>
       </c>
       <c r="Q267" s="22" t="n">
-        <v>13.3670912336621</v>
+        <v>29.46670442220106</v>
       </c>
       <c r="R267" s="18" t="n">
         <v>0</v>
@@ -23712,12 +23706,12 @@
       </c>
       <c r="B268" s="14" t="inlineStr">
         <is>
-          <t>EGBN</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C268" s="15" t="inlineStr">
         <is>
-          <t>Eagle Bancorp, Inc.</t>
+          <t>NetSol Technologies, Inc.</t>
         </is>
       </c>
       <c r="D268" s="16" t="inlineStr">
@@ -23727,70 +23721,76 @@
       </c>
       <c r="E268" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F268" s="18" t="n">
-        <v>888337280</v>
+        <v>54156448</v>
       </c>
       <c r="G268" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H268" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I268" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H268" s="20" t="n">
+        <v>8.028</v>
+      </c>
+      <c r="I268" s="20" t="n">
+        <v>30.399998</v>
       </c>
       <c r="J268" s="20" t="n">
-        <v>0.77562106</v>
+        <v>1.4531548</v>
       </c>
       <c r="K268" s="20" t="n">
-        <v>41.56547</v>
+        <v>0.7515241</v>
       </c>
       <c r="L268" s="22" t="n">
-        <v>2.78226065129031</v>
+        <v>23.63076201077865</v>
       </c>
       <c r="M268" s="22" t="n">
-        <v>0.67000003</v>
-      </c>
-      <c r="N268" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.63160459216738</v>
+      </c>
+      <c r="N268" s="22" t="n">
+        <v>17.62031993223545</v>
       </c>
       <c r="O268" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P268" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.42576524536094</v>
+      </c>
+      <c r="P268" s="20" t="n">
+        <v>-1.044695203416191</v>
       </c>
       <c r="Q268" s="22" t="n">
-        <v>29.46670442220106</v>
+        <v>44.01409423225983</v>
       </c>
       <c r="R268" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S268" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T268" s="15" t="n"/>
-      <c r="U268" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="S268" s="20" t="n">
+        <v>0.669742156156933</v>
+      </c>
+      <c r="T268" s="15" t="inlineStr">
+        <is>
+          <t>Europe Country (81%)</t>
+        </is>
+      </c>
+      <c r="U268" s="17" t="inlineStr">
+        <is>
+          <t>Europe Country 81%; Asia Pacific Region 13%; North America Country 7%</t>
+        </is>
+      </c>
       <c r="V268" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W268" s="17" t="n"/>
-      <c r="X268" s="15" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="W268" s="17" t="inlineStr">
+        <is>
+          <t>CN 26%; GB 22%; US 16%</t>
+        </is>
+      </c>
+      <c r="X268" s="15" t="inlineStr">
+        <is>
+          <t>Asia Pacific Region +40%</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="16" customHeight="1">
       <c r="A269" s="13" t="n">
@@ -23798,12 +23798,12 @@
       </c>
       <c r="B269" s="14" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>TRAK</t>
         </is>
       </c>
       <c r="C269" s="15" t="inlineStr">
         <is>
-          <t>NetSol Technologies, Inc.</t>
+          <t>Repositrak, Inc.</t>
         </is>
       </c>
       <c r="D269" s="16" t="inlineStr">
@@ -23817,7 +23817,7 @@
         </is>
       </c>
       <c r="F269" s="18" t="n">
-        <v>54156448</v>
+        <v>167015040</v>
       </c>
       <c r="G269" s="19" t="inlineStr">
         <is>
@@ -23825,64 +23825,50 @@
         </is>
       </c>
       <c r="H269" s="20" t="n">
-        <v>8.028</v>
+        <v>17.205</v>
       </c>
       <c r="I269" s="20" t="n">
-        <v>30.399998</v>
+        <v>24.837837</v>
       </c>
       <c r="J269" s="20" t="n">
-        <v>1.4531548</v>
+        <v>3.308135</v>
       </c>
       <c r="K269" s="20" t="n">
-        <v>0.7515241</v>
+        <v>7.115574</v>
       </c>
       <c r="L269" s="22" t="n">
-        <v>23.63076201077865</v>
+        <v>4.01658976341292</v>
       </c>
       <c r="M269" s="22" t="n">
-        <v>0.63160459216738</v>
+        <v>0.8699999999999999</v>
       </c>
       <c r="N269" s="22" t="n">
-        <v>17.62031993223545</v>
+        <v>32.2653613392671</v>
       </c>
       <c r="O269" s="22" t="n">
-        <v>11.42576524536094</v>
+        <v>36.66715653889693</v>
       </c>
       <c r="P269" s="20" t="n">
-        <v>-1.044695203416191</v>
+        <v>-2.653272610335161</v>
       </c>
       <c r="Q269" s="22" t="n">
-        <v>44.01409423225983</v>
+        <v>-53.73035208751867</v>
       </c>
       <c r="R269" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S269" s="20" t="n">
-        <v>0.669742156156933</v>
-      </c>
-      <c r="T269" s="15" t="inlineStr">
-        <is>
-          <t>Europe Country (81%)</t>
-        </is>
-      </c>
-      <c r="U269" s="17" t="inlineStr">
-        <is>
-          <t>Europe Country 81%; Asia Pacific Region 13%; North America Country 7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S269" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T269" s="15" t="n"/>
+      <c r="U269" s="17" t="n"/>
       <c r="V269" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W269" s="17" t="inlineStr">
-        <is>
-          <t>CN 26%; GB 22%; US 16%</t>
-        </is>
-      </c>
-      <c r="X269" s="15" t="inlineStr">
-        <is>
-          <t>Asia Pacific Region +40%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W269" s="17" t="n"/>
+      <c r="X269" s="15" t="n"/>
     </row>
     <row r="270" ht="16" customHeight="1">
       <c r="A270" s="13" t="n">
@@ -23890,12 +23876,12 @@
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>TRAK</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
         <is>
-          <t>Repositrak, Inc.</t>
+          <t>Chagee Holdings Ltd.</t>
         </is>
       </c>
       <c r="D270" s="16" t="inlineStr">
@@ -23905,11 +23891,11 @@
       </c>
       <c r="E270" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F270" s="18" t="n">
-        <v>167015040</v>
+        <v>2315866880</v>
       </c>
       <c r="G270" s="19" t="inlineStr">
         <is>
@@ -23917,34 +23903,36 @@
         </is>
       </c>
       <c r="H270" s="20" t="n">
-        <v>17.205</v>
+        <v>-18.82014472994232</v>
       </c>
       <c r="I270" s="20" t="n">
-        <v>24.837837</v>
+        <v>16.630136</v>
       </c>
       <c r="J270" s="20" t="n">
-        <v>3.308135</v>
+        <v>2.0134957</v>
       </c>
       <c r="K270" s="20" t="n">
-        <v>7.115574</v>
+        <v>0.17731571</v>
       </c>
       <c r="L270" s="22" t="n">
-        <v>4.01658976341292</v>
-      </c>
-      <c r="M270" s="22" t="n">
-        <v>0.8699999999999999</v>
+        <v>7.57638539223808</v>
+      </c>
+      <c r="M270" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N270" s="22" t="n">
-        <v>32.2653613392671</v>
+        <v>85.72643403189771</v>
       </c>
       <c r="O270" s="22" t="n">
-        <v>36.66715653889693</v>
+        <v>11.57176494554469</v>
       </c>
       <c r="P270" s="20" t="n">
-        <v>-2.653272610335161</v>
+        <v>-5.999493363518522</v>
       </c>
       <c r="Q270" s="22" t="n">
-        <v>-53.73035208751867</v>
+        <v>-50.65640095101563</v>
       </c>
       <c r="R270" s="18" t="n">
         <v>0</v>
@@ -23968,12 +23956,12 @@
       </c>
       <c r="B271" s="14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LENZ</t>
         </is>
       </c>
       <c r="C271" s="15" t="inlineStr">
         <is>
-          <t>Chagee Holdings Ltd.</t>
+          <t xml:space="preserve">LENZ Therapeutics Inc. Common </t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
@@ -23983,11 +23971,11 @@
       </c>
       <c r="E271" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F271" s="18" t="n">
-        <v>2315866880</v>
+        <v>230141264</v>
       </c>
       <c r="G271" s="19" t="inlineStr">
         <is>
@@ -23995,52 +23983,68 @@
         </is>
       </c>
       <c r="H271" s="20" t="n">
-        <v>-18.82014472994232</v>
-      </c>
-      <c r="I271" s="20" t="n">
-        <v>16.630136</v>
+        <v>0.6757298873980474</v>
+      </c>
+      <c r="I271" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J271" s="20" t="n">
-        <v>2.0134957</v>
+        <v>0.809390424809822</v>
       </c>
       <c r="K271" s="20" t="n">
-        <v>0.17731571</v>
+        <v>12.05685582564962</v>
       </c>
       <c r="L271" s="22" t="n">
-        <v>7.57638539223808</v>
+        <v>-30.41479775656399</v>
       </c>
       <c r="M271" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N271" s="22" t="n">
-        <v>85.72643403189771</v>
+      <c r="N271" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O271" s="22" t="n">
-        <v>11.57176494554469</v>
-      </c>
-      <c r="P271" s="20" t="n">
-        <v>-5.999493363518522</v>
+        <v>-475.9587175188601</v>
+      </c>
+      <c r="P271" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q271" s="22" t="n">
-        <v>-50.65640095101563</v>
+        <v>-73.15288913086155</v>
       </c>
       <c r="R271" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S271" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T271" s="15" t="n"/>
-      <c r="U271" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S271" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T271" s="15" t="inlineStr">
+        <is>
+          <t>Reportable (100%)</t>
+        </is>
+      </c>
+      <c r="U271" s="17" t="inlineStr">
+        <is>
+          <t>Reportable 100%</t>
+        </is>
+      </c>
       <c r="V271" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W271" s="17" t="n"/>
-      <c r="X271" s="15" t="n"/>
+      <c r="X271" s="15" t="inlineStr">
+        <is>
+          <t>Reportable +10%</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="16" customHeight="1">
       <c r="A272" s="13" t="n">
@@ -24048,12 +24052,12 @@
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>LENZ</t>
+          <t>JVA</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LENZ Therapeutics Inc. Common </t>
+          <t>Coffee Holding Co., Inc.</t>
         </is>
       </c>
       <c r="D272" s="16" t="inlineStr">
@@ -24063,11 +24067,11 @@
       </c>
       <c r="E272" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Stapl</t>
         </is>
       </c>
       <c r="F272" s="18" t="n">
-        <v>230141264</v>
+        <v>19123810</v>
       </c>
       <c r="G272" s="19" t="inlineStr">
         <is>
@@ -24075,42 +24079,34 @@
         </is>
       </c>
       <c r="H272" s="20" t="n">
-        <v>0.6757298873980474</v>
-      </c>
-      <c r="I272" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.732</v>
+      </c>
+      <c r="I272" s="20" t="n">
+        <v>12.407407</v>
       </c>
       <c r="J272" s="20" t="n">
-        <v>0.809390424809822</v>
+        <v>0.6649464</v>
       </c>
       <c r="K272" s="20" t="n">
-        <v>12.05685582564962</v>
+        <v>0.1924889</v>
       </c>
       <c r="L272" s="22" t="n">
-        <v>-30.41479775656399</v>
-      </c>
-      <c r="M272" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N272" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>42.03289398842584</v>
+      </c>
+      <c r="M272" s="22" t="n">
+        <v>2.3608044636242</v>
+      </c>
+      <c r="N272" s="22" t="n">
+        <v>14.9836891396905</v>
       </c>
       <c r="O272" s="22" t="n">
-        <v>-475.9587175188601</v>
-      </c>
-      <c r="P272" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.4448932469455</v>
+      </c>
+      <c r="P272" s="20" t="n">
+        <v>0.4654342573568866</v>
       </c>
       <c r="Q272" s="22" t="n">
-        <v>-73.15288913086155</v>
+        <v>25.28308922858965</v>
       </c>
       <c r="R272" s="18" t="n">
         <v>1</v>
@@ -24120,12 +24116,12 @@
       </c>
       <c r="T272" s="15" t="inlineStr">
         <is>
-          <t>Reportable (100%)</t>
+          <t>Operating (100%)</t>
         </is>
       </c>
       <c r="U272" s="17" t="inlineStr">
         <is>
-          <t>Reportable 100%</t>
+          <t>Operating 100%</t>
         </is>
       </c>
       <c r="V272" s="18" t="n">
@@ -24134,7 +24130,7 @@
       <c r="W272" s="17" t="n"/>
       <c r="X272" s="15" t="inlineStr">
         <is>
-          <t>Reportable +10%</t>
+          <t>Operating +23%</t>
         </is>
       </c>
     </row>
@@ -24144,26 +24140,26 @@
       </c>
       <c r="B273" s="14" t="inlineStr">
         <is>
-          <t>JVA</t>
+          <t>LAES</t>
         </is>
       </c>
       <c r="C273" s="15" t="inlineStr">
         <is>
-          <t>Coffee Holding Co., Inc.</t>
+          <t>SEALSQ Corp Ordinary Shares</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E273" s="17" t="inlineStr">
         <is>
-          <t>Consumer Stapl</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F273" s="18" t="n">
-        <v>19123810</v>
+        <v>603717568</v>
       </c>
       <c r="G273" s="19" t="inlineStr">
         <is>
@@ -24171,58 +24167,68 @@
         </is>
       </c>
       <c r="H273" s="20" t="n">
-        <v>6.732</v>
-      </c>
-      <c r="I273" s="20" t="n">
-        <v>12.407407</v>
+        <v>-3.5408472509913</v>
+      </c>
+      <c r="I273" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J273" s="20" t="n">
-        <v>0.6649464</v>
+        <v>1.308141067977153</v>
       </c>
       <c r="K273" s="20" t="n">
-        <v>0.1924889</v>
+        <v>33.07678983125137</v>
       </c>
       <c r="L273" s="22" t="n">
-        <v>42.03289398842584</v>
-      </c>
-      <c r="M273" s="22" t="n">
-        <v>2.3608044636242</v>
+        <v>-5.38331195291636</v>
+      </c>
+      <c r="M273" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N273" s="22" t="n">
-        <v>14.9836891396905</v>
+        <v>-87.41461486085792</v>
       </c>
       <c r="O273" s="22" t="n">
-        <v>4.4448932469455</v>
-      </c>
-      <c r="P273" s="20" t="n">
-        <v>0.4654342573568866</v>
+        <v>-214.2011834319526</v>
+      </c>
+      <c r="P273" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q273" s="22" t="n">
-        <v>25.28308922858965</v>
+        <v>-25.34435391982463</v>
       </c>
       <c r="R273" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S273" s="20" t="n">
-        <v>1</v>
+        <v>0.4229554701846919</v>
       </c>
       <c r="T273" s="15" t="inlineStr">
         <is>
-          <t>Operating (100%)</t>
+          <t>Reportable Segment Agg (51%)</t>
         </is>
       </c>
       <c r="U273" s="17" t="inlineStr">
         <is>
-          <t>Operating 100%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 51%; Semiconductors 40%; A</t>
         </is>
       </c>
       <c r="V273" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W273" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W273" s="17" t="inlineStr">
+        <is>
+          <t>North America 57%; EMEA 24%; Asia Pacific 18%</t>
+        </is>
+      </c>
       <c r="X273" s="15" t="inlineStr">
         <is>
-          <t>Operating +23%</t>
+          <t>Reportable Segment A +71%</t>
         </is>
       </c>
     </row>
@@ -24232,26 +24238,26 @@
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>LAES</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="C274" s="15" t="inlineStr">
         <is>
-          <t>SEALSQ Corp Ordinary Shares</t>
+          <t>Summit Midstream Corporation C</t>
         </is>
       </c>
       <c r="D274" s="16" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E274" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F274" s="18" t="n">
-        <v>603717568</v>
+        <v>408350272</v>
       </c>
       <c r="G274" s="19" t="inlineStr">
         <is>
@@ -24259,7 +24265,7 @@
         </is>
       </c>
       <c r="H274" s="20" t="n">
-        <v>-3.5408472509913</v>
+        <v>10.058</v>
       </c>
       <c r="I274" s="21" t="inlineStr">
         <is>
@@ -24267,13 +24273,13 @@
         </is>
       </c>
       <c r="J274" s="20" t="n">
-        <v>1.308141067977153</v>
+        <v>0.8319027</v>
       </c>
       <c r="K274" s="20" t="n">
-        <v>33.07678983125137</v>
+        <v>0.7170657</v>
       </c>
       <c r="L274" s="22" t="n">
-        <v>-5.38331195291636</v>
+        <v>10.03778223667121</v>
       </c>
       <c r="M274" s="21" t="inlineStr">
         <is>
@@ -24281,46 +24287,40 @@
         </is>
       </c>
       <c r="N274" s="22" t="n">
-        <v>-87.41461486085792</v>
+        <v>5.83452766424261</v>
       </c>
       <c r="O274" s="22" t="n">
-        <v>-214.2011834319526</v>
-      </c>
-      <c r="P274" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>36.9029214130808</v>
+      </c>
+      <c r="P274" s="20" t="n">
+        <v>4.995931118267544</v>
       </c>
       <c r="Q274" s="22" t="n">
-        <v>-25.34435391982463</v>
+        <v>9.063143471208871</v>
       </c>
       <c r="R274" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S274" s="20" t="n">
-        <v>0.4229554701846919</v>
+        <v>0.4390669204993302</v>
       </c>
       <c r="T274" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (51%)</t>
+          <t>Rockies (59%)</t>
         </is>
       </c>
       <c r="U274" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 51%; Semiconductors 40%; A</t>
+          <t>Rockies 59%; Mid Con Barnett Shale 28%; Piceance Basin 12%</t>
         </is>
       </c>
       <c r="V274" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W274" s="17" t="inlineStr">
-        <is>
-          <t>North America 57%; EMEA 24%; Asia Pacific 18%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W274" s="17" t="n"/>
       <c r="X274" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment A +71%</t>
+          <t>Mid Con Barnett Shal +180%</t>
         </is>
       </c>
     </row>
@@ -24330,12 +24330,12 @@
       </c>
       <c r="B275" s="14" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C275" s="15" t="inlineStr">
         <is>
-          <t>Summit Midstream Corporation C</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D275" s="16" t="inlineStr">
@@ -24345,11 +24345,11 @@
       </c>
       <c r="E275" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F275" s="18" t="n">
-        <v>408350272</v>
+        <v>4215082496</v>
       </c>
       <c r="G275" s="19" t="inlineStr">
         <is>
@@ -24357,21 +24357,19 @@
         </is>
       </c>
       <c r="H275" s="20" t="n">
-        <v>10.058</v>
-      </c>
-      <c r="I275" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.739</v>
+      </c>
+      <c r="I275" s="20" t="n">
+        <v>11.591954</v>
       </c>
       <c r="J275" s="20" t="n">
-        <v>0.8319027</v>
+        <v>1.2405436</v>
       </c>
       <c r="K275" s="20" t="n">
-        <v>0.7170657</v>
+        <v>0.75873274</v>
       </c>
       <c r="L275" s="22" t="n">
-        <v>10.03778223667121</v>
+        <v>3.04209736677507</v>
       </c>
       <c r="M275" s="21" t="inlineStr">
         <is>
@@ -24379,40 +24377,44 @@
         </is>
       </c>
       <c r="N275" s="22" t="n">
-        <v>5.83452766424261</v>
+        <v>19.02852891767159</v>
       </c>
       <c r="O275" s="22" t="n">
-        <v>36.9029214130808</v>
+        <v>12.67463785398956</v>
       </c>
       <c r="P275" s="20" t="n">
-        <v>4.995931118267544</v>
+        <v>-1.063746751310127</v>
       </c>
       <c r="Q275" s="22" t="n">
-        <v>9.063143471208871</v>
+        <v>-43.14897876018519</v>
       </c>
       <c r="R275" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S275" s="20" t="n">
-        <v>0.4390669204993302</v>
+        <v>0.6871057761739574</v>
       </c>
       <c r="T275" s="15" t="inlineStr">
         <is>
-          <t>Rockies (59%)</t>
+          <t>Americas (81%)</t>
         </is>
       </c>
       <c r="U275" s="17" t="inlineStr">
         <is>
-          <t>Rockies 59%; Mid Con Barnett Shale 28%; Piceance Basin 12%</t>
+          <t>Americas 81%; Europe 19%</t>
         </is>
       </c>
       <c r="V275" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W275" s="17" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="W275" s="17" t="inlineStr">
+        <is>
+          <t>Americas 20%; North America 19%; US 17%</t>
+        </is>
+      </c>
       <c r="X275" s="15" t="inlineStr">
         <is>
-          <t>Mid Con Barnett Shal +180%</t>
+          <t>Americas +1%</t>
         </is>
       </c>
     </row>
@@ -24422,12 +24424,12 @@
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>WSBC</t>
         </is>
       </c>
       <c r="C276" s="15" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>WesBanco, Inc.</t>
         </is>
       </c>
       <c r="D276" s="16" t="inlineStr">
@@ -24437,76 +24439,76 @@
       </c>
       <c r="E276" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F276" s="18" t="n">
-        <v>4215082496</v>
+        <v>3731805696</v>
       </c>
       <c r="G276" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H276" s="20" t="n">
-        <v>4.739</v>
+      <c r="H276" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I276" s="20" t="n">
-        <v>11.591954</v>
+        <v>11.90184</v>
       </c>
       <c r="J276" s="20" t="n">
-        <v>1.2405436</v>
+        <v>0.9697332400000001</v>
       </c>
       <c r="K276" s="20" t="n">
-        <v>0.75873274</v>
+        <v>3.5964322</v>
       </c>
       <c r="L276" s="22" t="n">
-        <v>3.04209736677507</v>
-      </c>
-      <c r="M276" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N276" s="22" t="n">
-        <v>19.02852891767159</v>
+        <v>12.55457183695235</v>
+      </c>
+      <c r="M276" s="22" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N276" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O276" s="22" t="n">
-        <v>12.67463785398956</v>
-      </c>
-      <c r="P276" s="20" t="n">
-        <v>-1.063746751310127</v>
+        <v>0</v>
+      </c>
+      <c r="P276" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q276" s="22" t="n">
-        <v>-43.14897876018519</v>
+        <v>18.52732332607427</v>
       </c>
       <c r="R276" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S276" s="20" t="n">
-        <v>0.6871057761739574</v>
+        <v>0.93390832547567</v>
       </c>
       <c r="T276" s="15" t="inlineStr">
         <is>
-          <t>Americas (81%)</t>
+          <t>Community Banking (97%)</t>
         </is>
       </c>
       <c r="U276" s="17" t="inlineStr">
         <is>
-          <t>Americas 81%; Europe 19%</t>
+          <t>Community Banking 97%; Trust And Investment Services 3%</t>
         </is>
       </c>
       <c r="V276" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W276" s="17" t="inlineStr">
-        <is>
-          <t>Americas 20%; North America 19%; US 17%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W276" s="17" t="n"/>
       <c r="X276" s="15" t="inlineStr">
         <is>
-          <t>Americas +1%</t>
+          <t>Community Banking +55%</t>
         </is>
       </c>
     </row>
@@ -24516,12 +24518,12 @@
       </c>
       <c r="B277" s="14" t="inlineStr">
         <is>
-          <t>WSBC</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C277" s="15" t="inlineStr">
         <is>
-          <t>WesBanco, Inc.</t>
+          <t>Skycorp Solar Group Limited</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
@@ -24531,78 +24533,72 @@
       </c>
       <c r="E277" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F277" s="18" t="n">
-        <v>3731805696</v>
+        <v>51708092</v>
       </c>
       <c r="G277" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H277" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I277" s="20" t="n">
-        <v>11.90184</v>
+      <c r="H277" s="20" t="n">
+        <v>-8.059603435542593</v>
+      </c>
+      <c r="I277" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J277" s="20" t="n">
-        <v>0.9697332400000001</v>
+        <v>0.25254583</v>
       </c>
       <c r="K277" s="20" t="n">
-        <v>3.5964322</v>
+        <v>0.816729</v>
       </c>
       <c r="L277" s="22" t="n">
-        <v>12.55457183695235</v>
-      </c>
-      <c r="M277" s="22" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="N277" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.6561048897337</v>
+      </c>
+      <c r="M277" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N277" s="22" t="n">
+        <v>-24.17948316363512</v>
       </c>
       <c r="O277" s="22" t="n">
+        <v>-3.42902383332009</v>
+      </c>
+      <c r="P277" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q277" s="22" t="n">
+        <v>-92.81853265752804</v>
+      </c>
+      <c r="R277" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P277" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q277" s="22" t="n">
-        <v>18.52732332607427</v>
-      </c>
-      <c r="R277" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S277" s="20" t="n">
-        <v>0.93390832547567</v>
-      </c>
-      <c r="T277" s="15" t="inlineStr">
-        <is>
-          <t>Community Banking (97%)</t>
-        </is>
-      </c>
-      <c r="U277" s="17" t="inlineStr">
-        <is>
-          <t>Community Banking 97%; Trust And Investment Services 3%</t>
-        </is>
-      </c>
+      <c r="S277" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T277" s="15" t="n"/>
+      <c r="U277" s="17" t="n"/>
       <c r="V277" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W277" s="17" t="n"/>
-      <c r="X277" s="15" t="inlineStr">
-        <is>
-          <t>Community Banking +55%</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="W277" s="17" t="inlineStr">
+        <is>
+          <t>CN 62%; Asia 23%; Other 15%</t>
+        </is>
+      </c>
+      <c r="X277" s="15" t="n"/>
     </row>
     <row r="278" ht="16" customHeight="1">
       <c r="A278" s="13" t="n">
@@ -24610,26 +24606,26 @@
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>NBP</t>
         </is>
       </c>
       <c r="C278" s="15" t="inlineStr">
         <is>
-          <t>Skycorp Solar Group Limited</t>
+          <t>NovaBridge Biosciences America</t>
         </is>
       </c>
       <c r="D278" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E278" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F278" s="18" t="n">
-        <v>51708092</v>
+        <v>215106224</v>
       </c>
       <c r="G278" s="19" t="inlineStr">
         <is>
@@ -24637,7 +24633,7 @@
         </is>
       </c>
       <c r="H278" s="20" t="n">
-        <v>-8.059603435542593</v>
+        <v>-0.1274247897950702</v>
       </c>
       <c r="I278" s="21" t="inlineStr">
         <is>
@@ -24645,24 +24641,26 @@
         </is>
       </c>
       <c r="J278" s="20" t="n">
-        <v>0.25254583</v>
+        <v>0.931433673535665</v>
       </c>
       <c r="K278" s="20" t="n">
-        <v>0.816729</v>
+        <v>55.25461700488056</v>
       </c>
       <c r="L278" s="22" t="n">
-        <v>4.6561048897337</v>
+        <v>-9.578523399676241</v>
       </c>
       <c r="M278" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N278" s="22" t="n">
-        <v>-24.17948316363512</v>
+      <c r="N278" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O278" s="22" t="n">
-        <v>-3.42902383332009</v>
+        <v>-2419.753403544824</v>
       </c>
       <c r="P278" s="21" t="inlineStr">
         <is>
@@ -24670,26 +24668,28 @@
         </is>
       </c>
       <c r="Q278" s="22" t="n">
-        <v>-92.81853265752804</v>
+        <v>-12.67606035817856</v>
       </c>
       <c r="R278" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S278" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T278" s="15" t="inlineStr">
+        <is>
+          <t>Oncology (100%)</t>
+        </is>
+      </c>
+      <c r="U278" s="17" t="inlineStr">
+        <is>
+          <t>Oncology 100%</t>
+        </is>
+      </c>
+      <c r="V278" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S278" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T278" s="15" t="n"/>
-      <c r="U278" s="17" t="n"/>
-      <c r="V278" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W278" s="17" t="inlineStr">
-        <is>
-          <t>CN 62%; Asia 23%; Other 15%</t>
-        </is>
-      </c>
+      <c r="W278" s="17" t="n"/>
       <c r="X278" s="15" t="n"/>
     </row>
     <row r="279" ht="16" customHeight="1">
@@ -24698,26 +24698,26 @@
       </c>
       <c r="B279" s="14" t="inlineStr">
         <is>
-          <t>NBP</t>
+          <t>MHH</t>
         </is>
       </c>
       <c r="C279" s="15" t="inlineStr">
         <is>
-          <t>NovaBridge Biosciences America</t>
+          <t>Mastech Digital, Inc.</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E279" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F279" s="18" t="n">
-        <v>215106224</v>
+        <v>92506016</v>
       </c>
       <c r="G279" s="19" t="inlineStr">
         <is>
@@ -24725,64 +24725,66 @@
         </is>
       </c>
       <c r="H279" s="20" t="n">
-        <v>-0.1274247897950702</v>
-      </c>
-      <c r="I279" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.015</v>
+      </c>
+      <c r="I279" s="20" t="n">
+        <v>40.57895</v>
       </c>
       <c r="J279" s="20" t="n">
-        <v>0.931433673535665</v>
+        <v>1.0158103</v>
       </c>
       <c r="K279" s="20" t="n">
-        <v>55.25461700488056</v>
+        <v>0.5023761</v>
       </c>
       <c r="L279" s="22" t="n">
-        <v>-9.578523399676241</v>
+        <v>12.68861683768958</v>
       </c>
       <c r="M279" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N279" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N279" s="22" t="n">
+        <v>0.001811725487354156</v>
       </c>
       <c r="O279" s="22" t="n">
-        <v>-2419.753403544824</v>
-      </c>
-      <c r="P279" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.7374628339717</v>
+      </c>
+      <c r="P279" s="20" t="n">
+        <v>-10.25924812030075</v>
       </c>
       <c r="Q279" s="22" t="n">
-        <v>-12.67606035817856</v>
+        <v>-16.09871122854541</v>
       </c>
       <c r="R279" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S279" s="20" t="n">
-        <v>1</v>
+        <v>0.7127125270080983</v>
       </c>
       <c r="T279" s="15" t="inlineStr">
         <is>
-          <t>Oncology (100%)</t>
+          <t>IT Staffing Services (83%)</t>
         </is>
       </c>
       <c r="U279" s="17" t="inlineStr">
         <is>
-          <t>Oncology 100%</t>
+          <t>IT Staffing Services 83%; Data And Analytics Services 17%</t>
         </is>
       </c>
       <c r="V279" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W279" s="17" t="n"/>
-      <c r="X279" s="15" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W279" s="17" t="inlineStr">
+        <is>
+          <t>US 99%; India And Other 1%; CA 0%</t>
+        </is>
+      </c>
+      <c r="X279" s="15" t="inlineStr">
+        <is>
+          <t>IT Staffing Services -3%</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="16" customHeight="1">
       <c r="A280" s="13" t="n">
@@ -24790,12 +24792,12 @@
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>MHH</t>
+          <t>UBOH</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
         <is>
-          <t>Mastech Digital, Inc.</t>
+          <t>United Bancshares, Inc.</t>
         </is>
       </c>
       <c r="D280" s="16" t="inlineStr">
@@ -24805,78 +24807,70 @@
       </c>
       <c r="E280" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F280" s="18" t="n">
-        <v>92506016</v>
+        <v>109671704</v>
       </c>
       <c r="G280" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H280" s="20" t="n">
-        <v>10.015</v>
+      <c r="H280" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I280" s="20" t="n">
-        <v>40.57895</v>
+        <v>8.494279000000001</v>
       </c>
       <c r="J280" s="20" t="n">
-        <v>1.0158103</v>
+        <v>1.033575888944387</v>
       </c>
       <c r="K280" s="20" t="n">
-        <v>0.5023761</v>
+        <v>2.323060876932853</v>
       </c>
       <c r="L280" s="22" t="n">
-        <v>12.68861683768958</v>
+        <v>12.72069229452293</v>
       </c>
       <c r="M280" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N280" s="22" t="n">
-        <v>0.001811725487354156</v>
+      <c r="N280" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O280" s="22" t="n">
-        <v>1.7374628339717</v>
-      </c>
-      <c r="P280" s="20" t="n">
-        <v>-10.25924812030075</v>
+        <v>26.577</v>
+      </c>
+      <c r="P280" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q280" s="22" t="n">
-        <v>-16.09871122854541</v>
+        <v>43.15061893304754</v>
       </c>
       <c r="R280" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S280" s="20" t="n">
-        <v>0.7127125270080983</v>
-      </c>
-      <c r="T280" s="15" t="inlineStr">
-        <is>
-          <t>IT Staffing Services (83%)</t>
-        </is>
-      </c>
-      <c r="U280" s="17" t="inlineStr">
-        <is>
-          <t>IT Staffing Services 83%; Data And Analytics Services 17%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S280" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T280" s="15" t="n"/>
+      <c r="U280" s="17" t="n"/>
       <c r="V280" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W280" s="17" t="inlineStr">
-        <is>
-          <t>US 99%; India And Other 1%; CA 0%</t>
-        </is>
-      </c>
-      <c r="X280" s="15" t="inlineStr">
-        <is>
-          <t>IT Staffing Services -3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W280" s="17" t="n"/>
+      <c r="X280" s="15" t="n"/>
     </row>
     <row r="281" ht="16" customHeight="1">
       <c r="A281" s="13" t="n">
@@ -24884,12 +24878,12 @@
       </c>
       <c r="B281" s="14" t="inlineStr">
         <is>
-          <t>UBOH</t>
+          <t>INMD</t>
         </is>
       </c>
       <c r="C281" s="15" t="inlineStr">
         <is>
-          <t>United Bancshares, Inc.</t>
+          <t>Inmode Ltd.</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
@@ -24899,54 +24893,48 @@
       </c>
       <c r="E281" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F281" s="18" t="n">
-        <v>109671704</v>
+        <v>840943680</v>
       </c>
       <c r="G281" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H281" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H281" s="20" t="n">
+        <v>4.908</v>
       </c>
       <c r="I281" s="20" t="n">
-        <v>8.494279000000001</v>
+        <v>10.837037</v>
       </c>
       <c r="J281" s="20" t="n">
-        <v>1.033575888944387</v>
+        <v>1.3567653</v>
       </c>
       <c r="K281" s="20" t="n">
-        <v>2.323060876932853</v>
+        <v>2.2446833</v>
       </c>
       <c r="L281" s="22" t="n">
-        <v>12.72069229452293</v>
+        <v>10.02266881891543</v>
       </c>
       <c r="M281" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N281" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N281" s="22" t="n">
+        <v>22.43159816631858</v>
       </c>
       <c r="O281" s="22" t="n">
-        <v>26.577</v>
-      </c>
-      <c r="P281" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>23.23432165076451</v>
+      </c>
+      <c r="P281" s="20" t="n">
+        <v>-7.106875581312155</v>
       </c>
       <c r="Q281" s="22" t="n">
-        <v>43.15061893304754</v>
+        <v>3.10077904911207</v>
       </c>
       <c r="R281" s="18" t="n">
         <v>0</v>
@@ -24959,9 +24947,13 @@
       <c r="T281" s="15" t="n"/>
       <c r="U281" s="17" t="n"/>
       <c r="V281" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W281" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W281" s="17" t="inlineStr">
+        <is>
+          <t>US 54%; Europe 21%; Asia 13%</t>
+        </is>
+      </c>
       <c r="X281" s="15" t="n"/>
     </row>
     <row r="282" ht="16" customHeight="1">
@@ -24970,12 +24962,12 @@
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>INMD</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C282" s="15" t="inlineStr">
         <is>
-          <t>Inmode Ltd.</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D282" s="16" t="inlineStr">
@@ -24985,11 +24977,11 @@
       </c>
       <c r="E282" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F282" s="18" t="n">
-        <v>840943680</v>
+        <v>108295240</v>
       </c>
       <c r="G282" s="19" t="inlineStr">
         <is>
@@ -24997,19 +24989,19 @@
         </is>
       </c>
       <c r="H282" s="20" t="n">
-        <v>4.908</v>
+        <v>11.138</v>
       </c>
       <c r="I282" s="20" t="n">
-        <v>10.837037</v>
+        <v>21.333334</v>
       </c>
       <c r="J282" s="20" t="n">
-        <v>1.3567653</v>
+        <v>1.7627617</v>
       </c>
       <c r="K282" s="20" t="n">
-        <v>2.2446833</v>
+        <v>3.8745956</v>
       </c>
       <c r="L282" s="22" t="n">
-        <v>10.02266881891543</v>
+        <v>1.84264170445135</v>
       </c>
       <c r="M282" s="21" t="inlineStr">
         <is>
@@ -25017,36 +25009,46 @@
         </is>
       </c>
       <c r="N282" s="22" t="n">
-        <v>22.43159816631858</v>
+        <v>16.80549850408138</v>
       </c>
       <c r="O282" s="22" t="n">
-        <v>23.23432165076451</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="P282" s="20" t="n">
-        <v>-7.106875581312155</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q282" s="22" t="n">
-        <v>3.10077904911207</v>
+        <v>63.28571864536831</v>
       </c>
       <c r="R282" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S282" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T282" s="15" t="n"/>
-      <c r="U282" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="S282" s="20" t="n">
+        <v>0.3385873824755823</v>
+      </c>
+      <c r="T282" s="15" t="inlineStr">
+        <is>
+          <t>Defense Engineering Se (45%)</t>
+        </is>
+      </c>
+      <c r="U282" s="17" t="inlineStr">
+        <is>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+        </is>
+      </c>
       <c r="V282" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W282" s="17" t="inlineStr">
         <is>
-          <t>US 54%; Europe 21%; Asia 13%</t>
-        </is>
-      </c>
-      <c r="X282" s="15" t="n"/>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
+        </is>
+      </c>
+      <c r="X282" s="15" t="inlineStr">
+        <is>
+          <t>Marine Technology Bu +185%</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="16" customHeight="1">
       <c r="A283" s="13" t="n">
@@ -25054,12 +25056,12 @@
       </c>
       <c r="B283" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>PEGA</t>
         </is>
       </c>
       <c r="C283" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>Pegasystems Inc.</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
@@ -25069,11 +25071,11 @@
       </c>
       <c r="E283" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F283" s="18" t="n">
-        <v>108295240</v>
+        <v>5143832064</v>
       </c>
       <c r="G283" s="19" t="inlineStr">
         <is>
@@ -25081,64 +25083,62 @@
         </is>
       </c>
       <c r="H283" s="20" t="n">
-        <v>11.138</v>
+        <v>22.891</v>
       </c>
       <c r="I283" s="20" t="n">
-        <v>21.333334</v>
+        <v>16.637838</v>
       </c>
       <c r="J283" s="20" t="n">
-        <v>1.7627617</v>
+        <v>7.358355</v>
       </c>
       <c r="K283" s="20" t="n">
-        <v>3.8745956</v>
+        <v>3.025513</v>
       </c>
       <c r="L283" s="22" t="n">
-        <v>1.84264170445135</v>
-      </c>
-      <c r="M283" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.23669009802985</v>
+      </c>
+      <c r="M283" s="22" t="n">
+        <v>0.22092398679639</v>
       </c>
       <c r="N283" s="22" t="n">
-        <v>16.80549850408138</v>
+        <v>44.9328253275009</v>
       </c>
       <c r="O283" s="22" t="n">
-        <v>24.49495025980879</v>
+        <v>12.97742790056418</v>
       </c>
       <c r="P283" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>-1.821221378197574</v>
       </c>
       <c r="Q283" s="22" t="n">
-        <v>63.28571864536831</v>
+        <v>-30.73425955897104</v>
       </c>
       <c r="R283" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S283" s="20" t="n">
-        <v>0.3385873824755823</v>
+        <v>1</v>
       </c>
       <c r="T283" s="15" t="inlineStr">
         <is>
-          <t>Defense Engineering Se (45%)</t>
+          <t>Reportable (100%)</t>
         </is>
       </c>
       <c r="U283" s="17" t="inlineStr">
         <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+          <t>Reportable 100%</t>
         </is>
       </c>
       <c r="V283" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W283" s="17" t="inlineStr">
         <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
+          <t>US 55%; EMEA 16%; Asia Pacific 12%</t>
         </is>
       </c>
       <c r="X283" s="15" t="inlineStr">
         <is>
-          <t>Marine Technology Bu +185%</t>
+          <t>Reportable +17%</t>
         </is>
       </c>
     </row>
@@ -25148,12 +25148,12 @@
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>PEGA</t>
+          <t>SCNX</t>
         </is>
       </c>
       <c r="C284" s="15" t="inlineStr">
         <is>
-          <t>Pegasystems Inc.</t>
+          <t>Scienture Holdings Inc. Common</t>
         </is>
       </c>
       <c r="D284" s="16" t="inlineStr">
@@ -25163,11 +25163,11 @@
       </c>
       <c r="E284" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F284" s="18" t="n">
-        <v>5143832064</v>
+        <v>16374219</v>
       </c>
       <c r="G284" s="19" t="inlineStr">
         <is>
@@ -25175,64 +25175,56 @@
         </is>
       </c>
       <c r="H284" s="20" t="n">
-        <v>22.891</v>
-      </c>
-      <c r="I284" s="20" t="n">
-        <v>16.637838</v>
+        <v>-0.2500849747464531</v>
+      </c>
+      <c r="I284" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J284" s="20" t="n">
-        <v>7.358355</v>
+        <v>0.2335158204495856</v>
       </c>
       <c r="K284" s="20" t="n">
-        <v>3.025513</v>
+        <v>37.93762178267831</v>
       </c>
       <c r="L284" s="22" t="n">
-        <v>11.23669009802985</v>
-      </c>
-      <c r="M284" s="22" t="n">
-        <v>0.22092398679639</v>
+        <v>-81.71188500654596</v>
+      </c>
+      <c r="M284" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N284" s="22" t="n">
-        <v>44.9328253275009</v>
+        <v>-62.10204060447323</v>
       </c>
       <c r="O284" s="22" t="n">
-        <v>12.97742790056418</v>
-      </c>
-      <c r="P284" s="20" t="n">
-        <v>-1.821221378197574</v>
+        <v>-9020.237066418911</v>
+      </c>
+      <c r="P284" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q284" s="22" t="n">
-        <v>-30.73425955897104</v>
+        <v>-55.22222135390762</v>
       </c>
       <c r="R284" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S284" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T284" s="15" t="inlineStr">
-        <is>
-          <t>Reportable (100%)</t>
-        </is>
-      </c>
-      <c r="U284" s="17" t="inlineStr">
-        <is>
-          <t>Reportable 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S284" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T284" s="15" t="n"/>
+      <c r="U284" s="17" t="n"/>
       <c r="V284" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W284" s="17" t="inlineStr">
-        <is>
-          <t>US 55%; EMEA 16%; Asia Pacific 12%</t>
-        </is>
-      </c>
-      <c r="X284" s="15" t="inlineStr">
-        <is>
-          <t>Reportable +17%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W284" s="17" t="n"/>
+      <c r="X284" s="15" t="n"/>
     </row>
     <row r="285" ht="16" customHeight="1">
       <c r="A285" s="13" t="n">
@@ -25240,12 +25232,12 @@
       </c>
       <c r="B285" s="14" t="inlineStr">
         <is>
-          <t>SCNX</t>
+          <t>LNC</t>
         </is>
       </c>
       <c r="C285" s="15" t="inlineStr">
         <is>
-          <t>Scienture Holdings Inc. Common</t>
+          <t>Lincoln National Corporation</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
@@ -25255,44 +25247,42 @@
       </c>
       <c r="E285" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F285" s="18" t="n">
-        <v>16374219</v>
+        <v>7021348864</v>
       </c>
       <c r="G285" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H285" s="20" t="n">
-        <v>-0.2500849747464531</v>
-      </c>
-      <c r="I285" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H285" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I285" s="20" t="n">
+        <v>4.0175056</v>
       </c>
       <c r="J285" s="20" t="n">
-        <v>0.2335158204495856</v>
+        <v>0.76102054</v>
       </c>
       <c r="K285" s="20" t="n">
-        <v>37.93762178267831</v>
+        <v>0.37288097</v>
       </c>
       <c r="L285" s="22" t="n">
-        <v>-81.71188500654596</v>
-      </c>
-      <c r="M285" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.52715173185971</v>
+      </c>
+      <c r="M285" s="22" t="n">
+        <v>4.9000002</v>
       </c>
       <c r="N285" s="22" t="n">
-        <v>-62.10204060447323</v>
+        <v>-8.60173683631966</v>
       </c>
       <c r="O285" s="22" t="n">
-        <v>-9020.237066418911</v>
+        <v>0</v>
       </c>
       <c r="P285" s="21" t="inlineStr">
         <is>
@@ -25300,23 +25290,33 @@
         </is>
       </c>
       <c r="Q285" s="22" t="n">
-        <v>-55.22222135390762</v>
+        <v>15.68577893399005</v>
       </c>
       <c r="R285" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S285" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T285" s="15" t="n"/>
-      <c r="U285" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="S285" s="20" t="n">
+        <v>0.2943665648071563</v>
+      </c>
+      <c r="T285" s="15" t="inlineStr">
+        <is>
+          <t>Group Protection (34%)</t>
+        </is>
+      </c>
+      <c r="U285" s="17" t="inlineStr">
+        <is>
+          <t>Group Protection 34%; Life 32%; Annuities 27%</t>
+        </is>
+      </c>
       <c r="V285" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W285" s="17" t="n"/>
-      <c r="X285" s="15" t="n"/>
+      <c r="X285" s="15" t="inlineStr">
+        <is>
+          <t>Annuities +102%</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="16" customHeight="1">
       <c r="A286" s="13" t="n">
@@ -25324,12 +25324,12 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>CRCT</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
         <is>
-          <t>Lincoln National Corporation</t>
+          <t>Cricut, Inc.</t>
         </is>
       </c>
       <c r="D286" s="16" t="inlineStr">
@@ -25339,74 +25339,74 @@
       </c>
       <c r="E286" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F286" s="18" t="n">
-        <v>7021348864</v>
+        <v>971830720</v>
       </c>
       <c r="G286" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H286" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H286" s="20" t="n">
+        <v>7.711</v>
       </c>
       <c r="I286" s="20" t="n">
-        <v>4.0175056</v>
+        <v>13.617647</v>
       </c>
       <c r="J286" s="20" t="n">
-        <v>0.76102054</v>
+        <v>2.7187319</v>
       </c>
       <c r="K286" s="20" t="n">
-        <v>0.37288097</v>
+        <v>1.3772779</v>
       </c>
       <c r="L286" s="22" t="n">
-        <v>3.52715173185971</v>
+        <v>21.31320627082333</v>
       </c>
       <c r="M286" s="22" t="n">
-        <v>4.9000002</v>
+        <v>4.32</v>
       </c>
       <c r="N286" s="22" t="n">
-        <v>-8.60173683631966</v>
+        <v>136.3676368894197</v>
       </c>
       <c r="O286" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P286" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>18.75038799063179</v>
+      </c>
+      <c r="P286" s="20" t="n">
+        <v>-1.986666566339852</v>
       </c>
       <c r="Q286" s="22" t="n">
-        <v>15.68577893399005</v>
+        <v>-27.59702330899697</v>
       </c>
       <c r="R286" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S286" s="20" t="n">
-        <v>0.2943665648071563</v>
+        <v>0.5029003141229101</v>
       </c>
       <c r="T286" s="15" t="inlineStr">
         <is>
-          <t>Group Protection (34%)</t>
+          <t>Accessories And Materi (54%)</t>
         </is>
       </c>
       <c r="U286" s="17" t="inlineStr">
         <is>
-          <t>Group Protection 34%; Life 32%; Annuities 27%</t>
+          <t>Accessories And Materials 54%; Subscriptions 46%</t>
         </is>
       </c>
       <c r="V286" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W286" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W286" s="17" t="inlineStr">
+        <is>
+          <t>North America 76%; International 24%</t>
+        </is>
+      </c>
       <c r="X286" s="15" t="inlineStr">
         <is>
-          <t>Annuities +102%</t>
+          <t>Subscriptions +5%</t>
         </is>
       </c>
     </row>
@@ -25416,12 +25416,12 @@
       </c>
       <c r="B287" s="14" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>OMCC</t>
         </is>
       </c>
       <c r="C287" s="15" t="inlineStr">
         <is>
-          <t>Cricut, Inc.</t>
+          <t>Old Market Capital Corporation</t>
         </is>
       </c>
       <c r="D287" s="16" t="inlineStr">
@@ -25431,11 +25431,11 @@
       </c>
       <c r="E287" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F287" s="18" t="n">
-        <v>971830720</v>
+        <v>28974532</v>
       </c>
       <c r="G287" s="19" t="inlineStr">
         <is>
@@ -25443,64 +25443,56 @@
         </is>
       </c>
       <c r="H287" s="20" t="n">
-        <v>7.711</v>
-      </c>
-      <c r="I287" s="20" t="n">
-        <v>13.617647</v>
+        <v>-19.26914102564102</v>
+      </c>
+      <c r="I287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J287" s="20" t="n">
-        <v>2.7187319</v>
+        <v>0.5290676</v>
       </c>
       <c r="K287" s="20" t="n">
-        <v>1.3772779</v>
+        <v>2.294044</v>
       </c>
       <c r="L287" s="22" t="n">
-        <v>21.31320627082333</v>
-      </c>
-      <c r="M287" s="22" t="n">
-        <v>4.32</v>
+        <v>-10.14684206115908</v>
+      </c>
+      <c r="M287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N287" s="22" t="n">
-        <v>136.3676368894197</v>
+        <v>-9.60052219321148</v>
       </c>
       <c r="O287" s="22" t="n">
-        <v>18.75038799063179</v>
-      </c>
-      <c r="P287" s="20" t="n">
-        <v>-1.986666566339852</v>
+        <v>-10.8424787523723</v>
+      </c>
+      <c r="P287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q287" s="22" t="n">
-        <v>-27.59702330899697</v>
+        <v>-15.69767377388159</v>
       </c>
       <c r="R287" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S287" s="20" t="n">
-        <v>0.5029003141229101</v>
-      </c>
-      <c r="T287" s="15" t="inlineStr">
-        <is>
-          <t>Accessories And Materi (54%)</t>
-        </is>
-      </c>
-      <c r="U287" s="17" t="inlineStr">
-        <is>
-          <t>Accessories And Materials 54%; Subscriptions 46%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S287" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T287" s="15" t="n"/>
+      <c r="U287" s="17" t="n"/>
       <c r="V287" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W287" s="17" t="inlineStr">
-        <is>
-          <t>North America 76%; International 24%</t>
-        </is>
-      </c>
-      <c r="X287" s="15" t="inlineStr">
-        <is>
-          <t>Subscriptions +5%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W287" s="17" t="n"/>
+      <c r="X287" s="15" t="n"/>
     </row>
     <row r="288" ht="16" customHeight="1">
       <c r="A288" s="13" t="n">
@@ -25508,12 +25500,12 @@
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>OMCC</t>
+          <t>CSBR</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
         <is>
-          <t>Old Market Capital Corporation</t>
+          <t>Champions Oncology, Inc.</t>
         </is>
       </c>
       <c r="D288" s="16" t="inlineStr">
@@ -25523,11 +25515,11 @@
       </c>
       <c r="E288" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F288" s="18" t="n">
-        <v>28974532</v>
+        <v>80821328</v>
       </c>
       <c r="G288" s="19" t="inlineStr">
         <is>
@@ -25535,7 +25527,7 @@
         </is>
       </c>
       <c r="H288" s="20" t="n">
-        <v>-19.26914102564102</v>
+        <v>-101.9253919793014</v>
       </c>
       <c r="I288" s="21" t="inlineStr">
         <is>
@@ -25543,13 +25535,13 @@
         </is>
       </c>
       <c r="J288" s="20" t="n">
-        <v>0.5290676</v>
+        <v>18.87026103198692</v>
       </c>
       <c r="K288" s="20" t="n">
-        <v>2.294044</v>
+        <v>1.394817893138202</v>
       </c>
       <c r="L288" s="22" t="n">
-        <v>-10.14684206115908</v>
+        <v>4.72152598135977</v>
       </c>
       <c r="M288" s="21" t="inlineStr">
         <is>
@@ -25557,18 +25549,16 @@
         </is>
       </c>
       <c r="N288" s="22" t="n">
-        <v>-9.60052219321148</v>
+        <v>-28.77898854428611</v>
       </c>
       <c r="O288" s="22" t="n">
-        <v>-10.8424787523723</v>
-      </c>
-      <c r="P288" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.51855400140512</v>
+      </c>
+      <c r="P288" s="20" t="n">
+        <v>2.888745148771022</v>
       </c>
       <c r="Q288" s="22" t="n">
-        <v>-15.69767377388159</v>
+        <v>-33.93870721388012</v>
       </c>
       <c r="R288" s="18" t="n">
         <v>0</v>
@@ -25592,12 +25582,12 @@
       </c>
       <c r="B289" s="14" t="inlineStr">
         <is>
-          <t>CSBR</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C289" s="15" t="inlineStr">
         <is>
-          <t>Champions Oncology, Inc.</t>
+          <t>Azenta Inc.</t>
         </is>
       </c>
       <c r="D289" s="16" t="inlineStr">
@@ -25611,7 +25601,7 @@
         </is>
       </c>
       <c r="F289" s="18" t="n">
-        <v>80821328</v>
+        <v>1175366528</v>
       </c>
       <c r="G289" s="19" t="inlineStr">
         <is>
@@ -25619,7 +25609,7 @@
         </is>
       </c>
       <c r="H289" s="20" t="n">
-        <v>-101.9253919793014</v>
+        <v>23.166</v>
       </c>
       <c r="I289" s="21" t="inlineStr">
         <is>
@@ -25627,46 +25617,60 @@
         </is>
       </c>
       <c r="J289" s="20" t="n">
-        <v>18.87026103198692</v>
+        <v>0.75600356</v>
       </c>
       <c r="K289" s="20" t="n">
-        <v>1.394817893138202</v>
+        <v>1.9704914</v>
       </c>
       <c r="L289" s="22" t="n">
-        <v>4.72152598135977</v>
-      </c>
-      <c r="M289" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>9.92176777589456</v>
+      </c>
+      <c r="M289" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="N289" s="22" t="n">
-        <v>-28.77898854428611</v>
+        <v>-13.85304502611689</v>
       </c>
       <c r="O289" s="22" t="n">
-        <v>8.51855400140512</v>
-      </c>
-      <c r="P289" s="20" t="n">
-        <v>2.888745148771022</v>
+        <v>6.65789859233674</v>
+      </c>
+      <c r="P289" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q289" s="22" t="n">
-        <v>-33.93870721388012</v>
+        <v>-40.02245972716416</v>
       </c>
       <c r="R289" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S289" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T289" s="15" t="n"/>
-      <c r="U289" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="S289" s="20" t="n">
+        <v>0.276261370165999</v>
+      </c>
+      <c r="T289" s="15" t="inlineStr">
+        <is>
+          <t>Sample Management Solu (35%)</t>
+        </is>
+      </c>
+      <c r="U289" s="17" t="inlineStr">
+        <is>
+          <t>Sample Management Solutions 35%; Multiomics 29%; Core Products 22%</t>
+        </is>
+      </c>
       <c r="V289" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W289" s="17" t="n"/>
-      <c r="X289" s="15" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="W289" s="17" t="inlineStr">
+        <is>
+          <t>US 61%; Europe 18%; CN 10%</t>
+        </is>
+      </c>
+      <c r="X289" s="15" t="inlineStr">
+        <is>
+          <t>Sample Repository So +27%</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="16" customHeight="1">
       <c r="A290" s="13" t="n">
@@ -25674,12 +25678,12 @@
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>TRDA</t>
         </is>
       </c>
       <c r="C290" s="15" t="inlineStr">
         <is>
-          <t>Azenta Inc.</t>
+          <t>Entrada Therapeutics Inc. Comm</t>
         </is>
       </c>
       <c r="D290" s="16" t="inlineStr">
@@ -25693,7 +25697,7 @@
         </is>
       </c>
       <c r="F290" s="18" t="n">
-        <v>1175366528</v>
+        <v>247675536</v>
       </c>
       <c r="G290" s="19" t="inlineStr">
         <is>
@@ -25701,7 +25705,7 @@
         </is>
       </c>
       <c r="H290" s="20" t="n">
-        <v>23.166</v>
+        <v>-0.1611489837583386</v>
       </c>
       <c r="I290" s="21" t="inlineStr">
         <is>
@@ -25709,58 +25713,58 @@
         </is>
       </c>
       <c r="J290" s="20" t="n">
-        <v>0.75600356</v>
+        <v>0.8090455324973133</v>
       </c>
       <c r="K290" s="20" t="n">
-        <v>1.9704914</v>
+        <v>9.7429501593171</v>
       </c>
       <c r="L290" s="22" t="n">
-        <v>9.92176777589456</v>
-      </c>
-      <c r="M290" s="22" t="n">
+        <v>-52.30754804947711</v>
+      </c>
+      <c r="M290" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N290" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="O290" s="22" t="n">
+        <v>-605.0194720900043</v>
+      </c>
+      <c r="P290" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q290" s="22" t="n">
+        <v>-21.42856891183762</v>
+      </c>
+      <c r="R290" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S290" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T290" s="15" t="inlineStr">
+        <is>
+          <t>Reportable (100%)</t>
+        </is>
+      </c>
+      <c r="U290" s="17" t="inlineStr">
+        <is>
+          <t>Reportable 100%</t>
+        </is>
+      </c>
+      <c r="V290" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N290" s="22" t="n">
-        <v>-13.85304502611689</v>
-      </c>
-      <c r="O290" s="22" t="n">
-        <v>6.65789859233674</v>
-      </c>
-      <c r="P290" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q290" s="22" t="n">
-        <v>-40.02245972716416</v>
-      </c>
-      <c r="R290" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="S290" s="20" t="n">
-        <v>0.276261370165999</v>
-      </c>
-      <c r="T290" s="15" t="inlineStr">
-        <is>
-          <t>Sample Management Solu (35%)</t>
-        </is>
-      </c>
-      <c r="U290" s="17" t="inlineStr">
-        <is>
-          <t>Sample Management Solutions 35%; Multiomics 29%; Core Products 22%</t>
-        </is>
-      </c>
-      <c r="V290" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W290" s="17" t="inlineStr">
-        <is>
-          <t>US 61%; Europe 18%; CN 10%</t>
-        </is>
-      </c>
+      <c r="W290" s="17" t="n"/>
       <c r="X290" s="15" t="inlineStr">
         <is>
-          <t>Sample Repository So +27%</t>
+          <t>Reportable -54%</t>
         </is>
       </c>
     </row>
@@ -25770,12 +25774,12 @@
       </c>
       <c r="B291" s="14" t="inlineStr">
         <is>
-          <t>TRDA</t>
+          <t>DSWL</t>
         </is>
       </c>
       <c r="C291" s="15" t="inlineStr">
         <is>
-          <t>Entrada Therapeutics Inc. Comm</t>
+          <t>Deswell Industries, Inc.</t>
         </is>
       </c>
       <c r="D291" s="16" t="inlineStr">
@@ -25785,11 +25789,11 @@
       </c>
       <c r="E291" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F291" s="18" t="n">
-        <v>247675536</v>
+        <v>59887352</v>
       </c>
       <c r="G291" s="19" t="inlineStr">
         <is>
@@ -25797,34 +25801,28 @@
         </is>
       </c>
       <c r="H291" s="20" t="n">
-        <v>-0.1611489837583386</v>
-      </c>
-      <c r="I291" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-4.644454376163873</v>
+      </c>
+      <c r="I291" s="20" t="n">
+        <v>5.6268654</v>
       </c>
       <c r="J291" s="20" t="n">
-        <v>0.8090455324973133</v>
+        <v>0.5474876</v>
       </c>
       <c r="K291" s="20" t="n">
-        <v>9.7429501593171</v>
+        <v>0.97644544</v>
       </c>
       <c r="L291" s="22" t="n">
-        <v>-52.30754804947711</v>
-      </c>
-      <c r="M291" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N291" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.04472156324427</v>
+      </c>
+      <c r="M291" s="22" t="n">
+        <v>5.3200003</v>
+      </c>
+      <c r="N291" s="22" t="n">
+        <v>4.47916525876167</v>
       </c>
       <c r="O291" s="22" t="n">
-        <v>-605.0194720900043</v>
+        <v>7.148350835675189</v>
       </c>
       <c r="P291" s="21" t="inlineStr">
         <is>
@@ -25832,31 +25830,35 @@
         </is>
       </c>
       <c r="Q291" s="22" t="n">
-        <v>-21.42856891183762</v>
+        <v>59.61997472641421</v>
       </c>
       <c r="R291" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S291" s="20" t="n">
-        <v>1</v>
+        <v>0.7508045391738183</v>
       </c>
       <c r="T291" s="15" t="inlineStr">
         <is>
-          <t>Reportable (100%)</t>
+          <t>Electronic Product (85%)</t>
         </is>
       </c>
       <c r="U291" s="17" t="inlineStr">
         <is>
-          <t>Reportable 100%</t>
+          <t>Electronic Product 85%; Injection Molded Plastic Part 15%</t>
         </is>
       </c>
       <c r="V291" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W291" s="17" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="W291" s="17" t="inlineStr">
+        <is>
+          <t>CN 21%; GB 20%; Europe 18%</t>
+        </is>
+      </c>
       <c r="X291" s="15" t="inlineStr">
         <is>
-          <t>Reportable -54%</t>
+          <t>Electronic Product -7%</t>
         </is>
       </c>
     </row>
@@ -25866,12 +25868,12 @@
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>DSWL</t>
+          <t>VRCA</t>
         </is>
       </c>
       <c r="C292" s="15" t="inlineStr">
         <is>
-          <t>Deswell Industries, Inc.</t>
+          <t>Verrica Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="D292" s="16" t="inlineStr">
@@ -25881,11 +25883,11 @@
       </c>
       <c r="E292" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F292" s="18" t="n">
-        <v>59887352</v>
+        <v>117502912</v>
       </c>
       <c r="G292" s="19" t="inlineStr">
         <is>
@@ -25893,28 +25895,34 @@
         </is>
       </c>
       <c r="H292" s="20" t="n">
-        <v>-4.644454376163873</v>
-      </c>
-      <c r="I292" s="20" t="n">
-        <v>5.6268654</v>
+        <v>-2.777811366021892</v>
+      </c>
+      <c r="I292" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J292" s="20" t="n">
-        <v>0.5474876</v>
+        <v>7.3155084</v>
       </c>
       <c r="K292" s="20" t="n">
-        <v>0.97644544</v>
+        <v>3.1619954</v>
       </c>
       <c r="L292" s="22" t="n">
-        <v>22.04472156324427</v>
-      </c>
-      <c r="M292" s="22" t="n">
-        <v>5.3200003</v>
-      </c>
-      <c r="N292" s="22" t="n">
-        <v>4.47916525876167</v>
+        <v>-39.4688090793869</v>
+      </c>
+      <c r="M292" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N292" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O292" s="22" t="n">
-        <v>7.148350835675189</v>
+        <v>-41.03918271938718</v>
       </c>
       <c r="P292" s="21" t="inlineStr">
         <is>
@@ -25922,35 +25930,31 @@
         </is>
       </c>
       <c r="Q292" s="22" t="n">
-        <v>59.61997472641421</v>
+        <v>3.99999618530273</v>
       </c>
       <c r="R292" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S292" s="20" t="n">
-        <v>0.7508045391738183</v>
+        <v>1</v>
       </c>
       <c r="T292" s="15" t="inlineStr">
         <is>
-          <t>Electronic Product (85%)</t>
+          <t>Operating (100%)</t>
         </is>
       </c>
       <c r="U292" s="17" t="inlineStr">
         <is>
-          <t>Electronic Product 85%; Injection Molded Plastic Part 15%</t>
+          <t>Operating 100%</t>
         </is>
       </c>
       <c r="V292" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W292" s="17" t="inlineStr">
-        <is>
-          <t>CN 21%; GB 20%; Europe 18%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W292" s="17" t="n"/>
       <c r="X292" s="15" t="inlineStr">
         <is>
-          <t>Electronic Product -7%</t>
+          <t>Operating +370%</t>
         </is>
       </c>
     </row>
@@ -25960,12 +25964,12 @@
       </c>
       <c r="B293" s="14" t="inlineStr">
         <is>
-          <t>VRCA</t>
+          <t>BRLT</t>
         </is>
       </c>
       <c r="C293" s="15" t="inlineStr">
         <is>
-          <t>Verrica Pharmaceuticals Inc.</t>
+          <t>Brilliant Earth Group Inc. Cla</t>
         </is>
       </c>
       <c r="D293" s="16" t="inlineStr">
@@ -25975,11 +25979,11 @@
       </c>
       <c r="E293" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F293" s="18" t="n">
-        <v>117502912</v>
+        <v>104237232</v>
       </c>
       <c r="G293" s="19" t="inlineStr">
         <is>
@@ -25987,7 +25991,7 @@
         </is>
       </c>
       <c r="H293" s="20" t="n">
-        <v>-2.777811366021892</v>
+        <v>5.124643397524071</v>
       </c>
       <c r="I293" s="21" t="inlineStr">
         <is>
@@ -25995,60 +25999,48 @@
         </is>
       </c>
       <c r="J293" s="20" t="n">
-        <v>7.3155084</v>
+        <v>1.4589236</v>
       </c>
       <c r="K293" s="20" t="n">
-        <v>3.1619954</v>
+        <v>0.2352438</v>
       </c>
       <c r="L293" s="22" t="n">
-        <v>-39.4688090793869</v>
-      </c>
-      <c r="M293" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N293" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69729494608955</v>
+      </c>
+      <c r="M293" s="22" t="n">
+        <v>22.729999</v>
+      </c>
+      <c r="N293" s="22" t="n">
+        <v>-19.22447700929374</v>
       </c>
       <c r="O293" s="22" t="n">
-        <v>-41.03918271938718</v>
-      </c>
-      <c r="P293" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.6588461723084</v>
+      </c>
+      <c r="P293" s="20" t="n">
+        <v>-3.527338376891334</v>
       </c>
       <c r="Q293" s="22" t="n">
-        <v>3.99999618530273</v>
+        <v>-10.49357992488675</v>
       </c>
       <c r="R293" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S293" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T293" s="15" t="inlineStr">
-        <is>
-          <t>Operating (100%)</t>
-        </is>
-      </c>
-      <c r="U293" s="17" t="inlineStr">
-        <is>
-          <t>Operating 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S293" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T293" s="15" t="n"/>
+      <c r="U293" s="17" t="n"/>
       <c r="V293" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W293" s="17" t="n"/>
-      <c r="X293" s="15" t="inlineStr">
-        <is>
-          <t>Operating +370%</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W293" s="17" t="inlineStr">
+        <is>
+          <t>US 96%; Non Us 4%</t>
+        </is>
+      </c>
+      <c r="X293" s="15" t="n"/>
     </row>
     <row r="294" ht="16" customHeight="1">
       <c r="A294" s="13" t="n">
@@ -26056,12 +26048,12 @@
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>BRLT</t>
+          <t>LGCY</t>
         </is>
       </c>
       <c r="C294" s="15" t="inlineStr">
         <is>
-          <t>Brilliant Earth Group Inc. Cla</t>
+          <t>Legacy Education Inc.</t>
         </is>
       </c>
       <c r="D294" s="16" t="inlineStr">
@@ -26075,7 +26067,7 @@
         </is>
       </c>
       <c r="F294" s="18" t="n">
-        <v>104237232</v>
+        <v>144233232</v>
       </c>
       <c r="G294" s="19" t="inlineStr">
         <is>
@@ -26083,36 +26075,36 @@
         </is>
       </c>
       <c r="H294" s="20" t="n">
-        <v>5.124643397524071</v>
-      </c>
-      <c r="I294" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.741</v>
+      </c>
+      <c r="I294" s="20" t="n">
+        <v>18.999998</v>
       </c>
       <c r="J294" s="20" t="n">
-        <v>1.4589236</v>
+        <v>2.9089053</v>
       </c>
       <c r="K294" s="20" t="n">
-        <v>0.2352438</v>
+        <v>1.8514082</v>
       </c>
       <c r="L294" s="22" t="n">
-        <v>4.69729494608955</v>
-      </c>
-      <c r="M294" s="22" t="n">
-        <v>22.729999</v>
+        <v>5.53478271914478</v>
+      </c>
+      <c r="M294" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N294" s="22" t="n">
-        <v>-19.22447700929374</v>
+        <v>45.16348160383653</v>
       </c>
       <c r="O294" s="22" t="n">
-        <v>2.6588461723084</v>
+        <v>17.18455257254128</v>
       </c>
       <c r="P294" s="20" t="n">
-        <v>-3.527338376891334</v>
+        <v>-1.558726694400639</v>
       </c>
       <c r="Q294" s="22" t="n">
-        <v>-10.49357992488675</v>
+        <v>-2.48075254288006</v>
       </c>
       <c r="R294" s="18" t="n">
         <v>0</v>
@@ -26125,13 +26117,9 @@
       <c r="T294" s="15" t="n"/>
       <c r="U294" s="17" t="n"/>
       <c r="V294" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W294" s="17" t="inlineStr">
-        <is>
-          <t>US 96%; Non Us 4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W294" s="17" t="n"/>
       <c r="X294" s="15" t="n"/>
     </row>
     <row r="295" ht="16" customHeight="1">
@@ -26140,12 +26128,12 @@
       </c>
       <c r="B295" s="14" t="inlineStr">
         <is>
-          <t>LGCY</t>
+          <t>WSFS</t>
         </is>
       </c>
       <c r="C295" s="15" t="inlineStr">
         <is>
-          <t>Legacy Education Inc.</t>
+          <t>WSFS Financial Corporation</t>
         </is>
       </c>
       <c r="D295" s="16" t="inlineStr">
@@ -26155,64 +26143,78 @@
       </c>
       <c r="E295" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F295" s="18" t="n">
-        <v>144233232</v>
+        <v>4026127616</v>
       </c>
       <c r="G295" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H295" s="20" t="n">
-        <v>11.741</v>
+      <c r="H295" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I295" s="20" t="n">
-        <v>18.999998</v>
+        <v>13.789661</v>
       </c>
       <c r="J295" s="20" t="n">
-        <v>2.9089053</v>
+        <v>1.508757</v>
       </c>
       <c r="K295" s="20" t="n">
-        <v>1.8514082</v>
+        <v>3.8152764</v>
       </c>
       <c r="L295" s="22" t="n">
-        <v>5.53478271914478</v>
-      </c>
-      <c r="M295" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N295" s="22" t="n">
-        <v>45.16348160383653</v>
+        <v>6.158366732153779</v>
+      </c>
+      <c r="M295" s="22" t="n">
+        <v>0.96865806418899</v>
+      </c>
+      <c r="N295" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O295" s="22" t="n">
-        <v>17.18455257254128</v>
-      </c>
-      <c r="P295" s="20" t="n">
-        <v>-1.558726694400639</v>
+        <v>0</v>
+      </c>
+      <c r="P295" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q295" s="22" t="n">
-        <v>-2.48075254288006</v>
+        <v>37.01048893948796</v>
       </c>
       <c r="R295" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S295" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T295" s="15" t="n"/>
-      <c r="U295" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="S295" s="20" t="n">
+        <v>0.5282319551986966</v>
+      </c>
+      <c r="T295" s="15" t="inlineStr">
+        <is>
+          <t>Wsfs Bank (68%)</t>
+        </is>
+      </c>
+      <c r="U295" s="17" t="inlineStr">
+        <is>
+          <t>Wsfs Bank 68%; Wealth Management 24%; Cash Connect 8%</t>
+        </is>
+      </c>
       <c r="V295" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W295" s="17" t="n"/>
-      <c r="X295" s="15" t="n"/>
+      <c r="X295" s="15" t="inlineStr">
+        <is>
+          <t>Wealth Management +15%</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="16" customHeight="1">
       <c r="A296" s="13" t="n">
@@ -26220,12 +26222,12 @@
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>WSFS</t>
+          <t>LIDR</t>
         </is>
       </c>
       <c r="C296" s="15" t="inlineStr">
         <is>
-          <t>WSFS Financial Corporation</t>
+          <t>AEye Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D296" s="16" t="inlineStr">
@@ -26235,78 +26237,72 @@
       </c>
       <c r="E296" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F296" s="18" t="n">
-        <v>4026127616</v>
+        <v>62061860</v>
       </c>
       <c r="G296" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H296" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I296" s="20" t="n">
-        <v>13.789661</v>
+      <c r="H296" s="20" t="n">
+        <v>0.4025600520648444</v>
+      </c>
+      <c r="I296" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J296" s="20" t="n">
-        <v>1.508757</v>
+        <v>0.8362328877870001</v>
       </c>
       <c r="K296" s="20" t="n">
-        <v>3.8152764</v>
+        <v>229.8587407407408</v>
       </c>
       <c r="L296" s="22" t="n">
-        <v>6.158366732153779</v>
-      </c>
-      <c r="M296" s="22" t="n">
-        <v>0.96865806418899</v>
-      </c>
-      <c r="N296" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-46.4359269928423</v>
+      </c>
+      <c r="M296" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N296" s="22" t="n">
+        <v>-85.9514449638759</v>
       </c>
       <c r="O296" s="22" t="n">
+        <v>-13469.62025316456</v>
+      </c>
+      <c r="P296" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Q296" s="22" t="n">
+        <v>17.54386405205137</v>
+      </c>
+      <c r="R296" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P296" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Q296" s="22" t="n">
-        <v>37.01048893948796</v>
-      </c>
-      <c r="R296" s="18" t="n">
+      <c r="S296" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T296" s="15" t="n"/>
+      <c r="U296" s="17" t="n"/>
+      <c r="V296" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="S296" s="20" t="n">
-        <v>0.5282319551986966</v>
-      </c>
-      <c r="T296" s="15" t="inlineStr">
-        <is>
-          <t>Wsfs Bank (68%)</t>
-        </is>
-      </c>
-      <c r="U296" s="17" t="inlineStr">
-        <is>
-          <t>Wsfs Bank 68%; Wealth Management 24%; Cash Connect 8%</t>
-        </is>
-      </c>
-      <c r="V296" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W296" s="17" t="n"/>
-      <c r="X296" s="15" t="inlineStr">
-        <is>
-          <t>Wealth Management +15%</t>
-        </is>
-      </c>
+      <c r="W296" s="17" t="inlineStr">
+        <is>
+          <t>US 50%; Europe 40%; Asia 10%</t>
+        </is>
+      </c>
+      <c r="X296" s="15" t="n"/>
     </row>
     <row r="297" ht="16" customHeight="1">
       <c r="A297" s="13" t="n">
@@ -26314,12 +26310,12 @@
       </c>
       <c r="B297" s="14" t="inlineStr">
         <is>
-          <t>LIDR</t>
+          <t>MDRR</t>
         </is>
       </c>
       <c r="C297" s="15" t="inlineStr">
         <is>
-          <t>AEye Inc. Class A Common Stock</t>
+          <t>Medalist Diversified REIT, Inc</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
@@ -26329,11 +26325,11 @@
       </c>
       <c r="E297" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F297" s="18" t="n">
-        <v>62061860</v>
+        <v>18760158</v>
       </c>
       <c r="G297" s="19" t="inlineStr">
         <is>
@@ -26341,21 +26337,19 @@
         </is>
       </c>
       <c r="H297" s="20" t="n">
-        <v>0.4025600520648444</v>
-      </c>
-      <c r="I297" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.780036825807078</v>
+      </c>
+      <c r="I297" s="20" t="n">
+        <v>3.1219242</v>
       </c>
       <c r="J297" s="20" t="n">
-        <v>0.8362328877870001</v>
+        <v>0.8411720476936947</v>
       </c>
       <c r="K297" s="20" t="n">
-        <v>229.8587407407408</v>
+        <v>1.83307724860549</v>
       </c>
       <c r="L297" s="22" t="n">
-        <v>-46.4359269928423</v>
+        <v>-7.52920631052254</v>
       </c>
       <c r="M297" s="21" t="inlineStr">
         <is>
@@ -26363,38 +26357,42 @@
         </is>
       </c>
       <c r="N297" s="22" t="n">
-        <v>-85.9514449638759</v>
+        <v>30.01538674616187</v>
       </c>
       <c r="O297" s="22" t="n">
-        <v>-13469.62025316456</v>
-      </c>
-      <c r="P297" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>154.4775402450331</v>
+      </c>
+      <c r="P297" s="20" t="n">
+        <v>1.270310578241797</v>
       </c>
       <c r="Q297" s="22" t="n">
-        <v>17.54386405205137</v>
+        <v>1.73967414151658</v>
       </c>
       <c r="R297" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S297" s="20" t="n">
+        <v>0.4570947911909182</v>
+      </c>
+      <c r="T297" s="15" t="inlineStr">
+        <is>
+          <t>Retail Center Properti (61%)</t>
+        </is>
+      </c>
+      <c r="U297" s="17" t="inlineStr">
+        <is>
+          <t>Retail Center Properties 61%; Propertyrevenues 27%; Single Tenant Net Lease 12%</t>
+        </is>
+      </c>
+      <c r="V297" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S297" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T297" s="15" t="n"/>
-      <c r="U297" s="17" t="n"/>
-      <c r="V297" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W297" s="17" t="inlineStr">
-        <is>
-          <t>US 50%; Europe 40%; Asia 10%</t>
-        </is>
-      </c>
-      <c r="X297" s="15" t="n"/>
+      <c r="W297" s="17" t="n"/>
+      <c r="X297" s="15" t="inlineStr">
+        <is>
+          <t>Single Tenant Net Le +251%</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="16" customHeight="1">
       <c r="A298" s="13" t="n">
@@ -26402,12 +26400,12 @@
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>MDRR</t>
+          <t>DUO</t>
         </is>
       </c>
       <c r="C298" s="15" t="inlineStr">
         <is>
-          <t>Medalist Diversified REIT, Inc</t>
+          <t>Fangdd Network Group Ltd.</t>
         </is>
       </c>
       <c r="D298" s="16" t="inlineStr">
@@ -26417,11 +26415,11 @@
       </c>
       <c r="E298" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F298" s="18" t="n">
-        <v>18760158</v>
+        <v>25684806</v>
       </c>
       <c r="G298" s="19" t="inlineStr">
         <is>
@@ -26429,19 +26427,21 @@
         </is>
       </c>
       <c r="H298" s="20" t="n">
-        <v>2.780036825807078</v>
-      </c>
-      <c r="I298" s="20" t="n">
-        <v>3.1219242</v>
+        <v>1.023</v>
+      </c>
+      <c r="I298" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J298" s="20" t="n">
-        <v>0.8411720476936947</v>
+        <v>0.30155513</v>
       </c>
       <c r="K298" s="20" t="n">
-        <v>1.83307724860549</v>
+        <v>0.07238766000000001</v>
       </c>
       <c r="L298" s="22" t="n">
-        <v>-7.52920631052254</v>
+        <v>-23.31605752734946</v>
       </c>
       <c r="M298" s="21" t="inlineStr">
         <is>
@@ -26449,42 +26449,34 @@
         </is>
       </c>
       <c r="N298" s="22" t="n">
-        <v>30.01538674616187</v>
+        <v>-15.75163614728631</v>
       </c>
       <c r="O298" s="22" t="n">
-        <v>154.4775402450331</v>
-      </c>
-      <c r="P298" s="20" t="n">
-        <v>1.270310578241797</v>
+        <v>-34.64199136758706</v>
+      </c>
+      <c r="P298" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q298" s="22" t="n">
-        <v>1.73967414151658</v>
+        <v>-66.20934943652108</v>
       </c>
       <c r="R298" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="S298" s="20" t="n">
-        <v>0.4570947911909182</v>
-      </c>
-      <c r="T298" s="15" t="inlineStr">
-        <is>
-          <t>Retail Center Properti (61%)</t>
-        </is>
-      </c>
-      <c r="U298" s="17" t="inlineStr">
-        <is>
-          <t>Retail Center Properties 61%; Propertyrevenues 27%; Single Tenant Net Lease 12%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S298" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T298" s="15" t="n"/>
+      <c r="U298" s="17" t="n"/>
       <c r="V298" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W298" s="17" t="n"/>
-      <c r="X298" s="15" t="inlineStr">
-        <is>
-          <t>Single Tenant Net Le +251%</t>
-        </is>
-      </c>
+      <c r="X298" s="15" t="n"/>
     </row>
     <row r="299" ht="16" customHeight="1">
       <c r="A299" s="13" t="n">
@@ -26492,12 +26484,12 @@
       </c>
       <c r="B299" s="14" t="inlineStr">
         <is>
-          <t>DUO</t>
+          <t>CCS</t>
         </is>
       </c>
       <c r="C299" s="15" t="inlineStr">
         <is>
-          <t>Fangdd Network Group Ltd.</t>
+          <t>Century Communities, Inc.</t>
         </is>
       </c>
       <c r="D299" s="16" t="inlineStr">
@@ -26507,11 +26499,11 @@
       </c>
       <c r="E299" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F299" s="18" t="n">
-        <v>25684806</v>
+        <v>2066786816</v>
       </c>
       <c r="G299" s="19" t="inlineStr">
         <is>
@@ -26519,56 +26511,60 @@
         </is>
       </c>
       <c r="H299" s="20" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="I299" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>14.787</v>
+      </c>
+      <c r="I299" s="20" t="n">
+        <v>16.18018</v>
       </c>
       <c r="J299" s="20" t="n">
-        <v>0.30155513</v>
+        <v>0.809483</v>
       </c>
       <c r="K299" s="20" t="n">
-        <v>0.07238766000000001</v>
+        <v>0.5161474</v>
       </c>
       <c r="L299" s="22" t="n">
-        <v>-23.31605752734946</v>
-      </c>
-      <c r="M299" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.548742417841001</v>
+      </c>
+      <c r="M299" s="22" t="n">
+        <v>2.43149737225959</v>
       </c>
       <c r="N299" s="22" t="n">
-        <v>-15.75163614728631</v>
+        <v>2.58578602001868</v>
       </c>
       <c r="O299" s="22" t="n">
-        <v>-34.64199136758706</v>
-      </c>
-      <c r="P299" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.23343032178004</v>
+      </c>
+      <c r="P299" s="20" t="n">
+        <v>6.916582363046383</v>
       </c>
       <c r="Q299" s="22" t="n">
-        <v>-66.20934943652108</v>
+        <v>-11.45115502443391</v>
       </c>
       <c r="R299" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S299" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T299" s="15" t="n"/>
-      <c r="U299" s="17" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="S299" s="20" t="n">
+        <v>0.1890488694217202</v>
+      </c>
+      <c r="T299" s="15" t="inlineStr">
+        <is>
+          <t>Century Complete (23%)</t>
+        </is>
+      </c>
+      <c r="U299" s="17" t="inlineStr">
+        <is>
+          <t>Century Complete 23%; Mountain 21%; West 20%</t>
+        </is>
+      </c>
       <c r="V299" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W299" s="17" t="n"/>
-      <c r="X299" s="15" t="n"/>
+      <c r="X299" s="15" t="inlineStr">
+        <is>
+          <t>Texas +6%</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="16" customHeight="1">
       <c r="A300" s="13" t="n">
@@ -26576,12 +26572,12 @@
       </c>
       <c r="B300" s="14" t="inlineStr">
         <is>
-          <t>CCS</t>
+          <t>AMRN</t>
         </is>
       </c>
       <c r="C300" s="15" t="inlineStr">
         <is>
-          <t>Century Communities, Inc.</t>
+          <t>Amarin Corp Plc\Uk</t>
         </is>
       </c>
       <c r="D300" s="16" t="inlineStr">
@@ -26591,11 +26587,11 @@
       </c>
       <c r="E300" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F300" s="18" t="n">
-        <v>2066786816</v>
+        <v>333618496</v>
       </c>
       <c r="G300" s="19" t="inlineStr">
         <is>
@@ -26603,60 +26599,60 @@
         </is>
       </c>
       <c r="H300" s="20" t="n">
-        <v>14.787</v>
-      </c>
-      <c r="I300" s="20" t="n">
-        <v>16.18018</v>
+        <v>0.3312424123162403</v>
+      </c>
+      <c r="I300" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J300" s="20" t="n">
-        <v>0.809483</v>
+        <v>0.7427291</v>
       </c>
       <c r="K300" s="20" t="n">
-        <v>0.5161474</v>
+        <v>1.5391077</v>
       </c>
       <c r="L300" s="22" t="n">
-        <v>7.548742417841001</v>
-      </c>
-      <c r="M300" s="22" t="n">
-        <v>2.43149737225959</v>
+        <v>-7.772950334264441</v>
+      </c>
+      <c r="M300" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N300" s="22" t="n">
-        <v>2.58578602001868</v>
+        <v>-16.83575549907395</v>
       </c>
       <c r="O300" s="22" t="n">
-        <v>5.23343032178004</v>
-      </c>
-      <c r="P300" s="20" t="n">
-        <v>6.916582363046383</v>
+        <v>-26.28221034548578</v>
+      </c>
+      <c r="P300" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q300" s="22" t="n">
-        <v>-11.45115502443391</v>
+        <v>2.0074048478698</v>
       </c>
       <c r="R300" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="S300" s="20" t="n">
-        <v>0.1890488694217202</v>
-      </c>
-      <c r="T300" s="15" t="inlineStr">
-        <is>
-          <t>Century Complete (23%)</t>
-        </is>
-      </c>
-      <c r="U300" s="17" t="inlineStr">
-        <is>
-          <t>Century Complete 23%; Mountain 21%; West 20%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S300" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T300" s="15" t="n"/>
+      <c r="U300" s="17" t="n"/>
       <c r="V300" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W300" s="17" t="n"/>
-      <c r="X300" s="15" t="inlineStr">
-        <is>
-          <t>Texas +6%</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="W300" s="17" t="inlineStr">
+        <is>
+          <t>US 84%; Europe 10%; Rest Of The World Except US And Europe 6</t>
+        </is>
+      </c>
+      <c r="X300" s="15" t="n"/>
     </row>
     <row r="301" ht="16" customHeight="1">
       <c r="A301" s="13" t="n">
@@ -26664,12 +26660,12 @@
       </c>
       <c r="B301" s="14" t="inlineStr">
         <is>
-          <t>AMRN</t>
+          <t>ANIP</t>
         </is>
       </c>
       <c r="C301" s="15" t="inlineStr">
         <is>
-          <t>Amarin Corp Plc\Uk</t>
+          <t>Ani Pharmaceuticals, Inc</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
@@ -26683,7 +26679,7 @@
         </is>
       </c>
       <c r="F301" s="18" t="n">
-        <v>333618496</v>
+        <v>1921075200</v>
       </c>
       <c r="G301" s="19" t="inlineStr">
         <is>
@@ -26691,21 +26687,19 @@
         </is>
       </c>
       <c r="H301" s="20" t="n">
-        <v>0.3312424123162403</v>
-      </c>
-      <c r="I301" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.619</v>
+      </c>
+      <c r="I301" s="20" t="n">
+        <v>21.611252</v>
       </c>
       <c r="J301" s="20" t="n">
-        <v>0.7427291</v>
+        <v>3.2079268</v>
       </c>
       <c r="K301" s="20" t="n">
-        <v>1.5391077</v>
+        <v>2.0797474</v>
       </c>
       <c r="L301" s="22" t="n">
-        <v>-7.772950334264441</v>
+        <v>6.120582890248119</v>
       </c>
       <c r="M301" s="21" t="inlineStr">
         <is>
@@ -26713,38 +26707,46 @@
         </is>
       </c>
       <c r="N301" s="22" t="n">
-        <v>-16.83575549907395</v>
+        <v>20.70637542279365</v>
       </c>
       <c r="O301" s="22" t="n">
-        <v>-26.28221034548578</v>
-      </c>
-      <c r="P301" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>23.45439521703701</v>
+      </c>
+      <c r="P301" s="20" t="n">
+        <v>-0.0287015033888463</v>
       </c>
       <c r="Q301" s="22" t="n">
-        <v>2.0074048478698</v>
+        <v>26.41480058470028</v>
       </c>
       <c r="R301" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S301" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T301" s="15" t="n"/>
-      <c r="U301" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S301" s="20" t="n">
+        <v>0.5045751155060259</v>
+      </c>
+      <c r="T301" s="15" t="inlineStr">
+        <is>
+          <t>Rare Disease And Brand (55%)</t>
+        </is>
+      </c>
+      <c r="U301" s="17" t="inlineStr">
+        <is>
+          <t>Rare Disease And Brands 55%; Generics And Other 45%</t>
+        </is>
+      </c>
       <c r="V301" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W301" s="17" t="inlineStr">
         <is>
-          <t>US 84%; Europe 10%; Rest Of The World Except US And Europe 6</t>
-        </is>
-      </c>
-      <c r="X301" s="15" t="n"/>
+          <t>US 96%; Non Us 4%</t>
+        </is>
+      </c>
+      <c r="X301" s="15" t="inlineStr">
+        <is>
+          <t>Rare Disease And Bra +64%</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="13" t="n">
@@ -26752,12 +26754,12 @@
       </c>
       <c r="B302" s="14" t="inlineStr">
         <is>
-          <t>ANIP</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="C302" s="15" t="inlineStr">
         <is>
-          <t>Ani Pharmaceuticals, Inc</t>
+          <t>Teekay Corporation Ltd.</t>
         </is>
       </c>
       <c r="D302" s="16" t="inlineStr">
@@ -26767,11 +26769,11 @@
       </c>
       <c r="E302" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F302" s="18" t="n">
-        <v>1921075200</v>
+        <v>935377088</v>
       </c>
       <c r="G302" s="19" t="inlineStr">
         <is>
@@ -26779,19 +26781,19 @@
         </is>
       </c>
       <c r="H302" s="20" t="n">
-        <v>10.619</v>
+        <v>4.024</v>
       </c>
       <c r="I302" s="20" t="n">
-        <v>21.611252</v>
+        <v>9.513273999999999</v>
       </c>
       <c r="J302" s="20" t="n">
-        <v>3.2079268</v>
+        <v>1.2768738</v>
       </c>
       <c r="K302" s="20" t="n">
-        <v>2.0797474</v>
+        <v>0.9316737</v>
       </c>
       <c r="L302" s="22" t="n">
-        <v>6.120582890248119</v>
+        <v>11.92118146045501</v>
       </c>
       <c r="M302" s="21" t="inlineStr">
         <is>
@@ -26799,44 +26801,40 @@
         </is>
       </c>
       <c r="N302" s="22" t="n">
-        <v>20.70637542279365</v>
+        <v>24.78287343641048</v>
       </c>
       <c r="O302" s="22" t="n">
-        <v>23.45439521703701</v>
+        <v>41.01482854494903</v>
       </c>
       <c r="P302" s="20" t="n">
-        <v>-0.0287015033888463</v>
+        <v>-2.120166526673792</v>
       </c>
       <c r="Q302" s="22" t="n">
-        <v>26.41480058470028</v>
+        <v>56.60500796835277</v>
       </c>
       <c r="R302" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S302" s="20" t="n">
-        <v>0.5045751155060259</v>
+        <v>0.7705855121065255</v>
       </c>
       <c r="T302" s="15" t="inlineStr">
         <is>
-          <t>Rare Disease And Brand (55%)</t>
+          <t>Tankers (87%)</t>
         </is>
       </c>
       <c r="U302" s="17" t="inlineStr">
         <is>
-          <t>Rare Disease And Brands 55%; Generics And Other 45%</t>
+          <t>Tankers 87%; Marine Services And Other 13%</t>
         </is>
       </c>
       <c r="V302" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W302" s="17" t="inlineStr">
-        <is>
-          <t>US 96%; Non Us 4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W302" s="17" t="n"/>
       <c r="X302" s="15" t="inlineStr">
         <is>
-          <t>Rare Disease And Bra +64%</t>
+          <t>Marine Services And  +10%</t>
         </is>
       </c>
     </row>
@@ -26846,12 +26844,12 @@
       </c>
       <c r="B303" s="14" t="inlineStr">
         <is>
-          <t>TK</t>
+          <t>AWRE</t>
         </is>
       </c>
       <c r="C303" s="15" t="inlineStr">
         <is>
-          <t>Teekay Corporation Ltd.</t>
+          <t>Aware, Inc.</t>
         </is>
       </c>
       <c r="D303" s="16" t="inlineStr">
@@ -26861,11 +26859,11 @@
       </c>
       <c r="E303" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F303" s="18" t="n">
-        <v>935377088</v>
+        <v>28139898</v>
       </c>
       <c r="G303" s="19" t="inlineStr">
         <is>
@@ -26873,19 +26871,21 @@
         </is>
       </c>
       <c r="H303" s="20" t="n">
-        <v>4.024</v>
-      </c>
-      <c r="I303" s="20" t="n">
-        <v>9.513273999999999</v>
+        <v>-1.513124630984469</v>
+      </c>
+      <c r="I303" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J303" s="20" t="n">
-        <v>1.2768738</v>
+        <v>1.2275732</v>
       </c>
       <c r="K303" s="20" t="n">
-        <v>0.9316737</v>
+        <v>1.6484036</v>
       </c>
       <c r="L303" s="22" t="n">
-        <v>11.92118146045501</v>
+        <v>-19.12873855815686</v>
       </c>
       <c r="M303" s="21" t="inlineStr">
         <is>
@@ -26893,42 +26893,34 @@
         </is>
       </c>
       <c r="N303" s="22" t="n">
-        <v>24.78287343641048</v>
+        <v>-91.03151464667501</v>
       </c>
       <c r="O303" s="22" t="n">
-        <v>41.01482854494903</v>
-      </c>
-      <c r="P303" s="20" t="n">
-        <v>-2.120166526673792</v>
+        <v>-45.63612933458294</v>
+      </c>
+      <c r="P303" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q303" s="22" t="n">
-        <v>56.60500796835277</v>
+        <v>-23.49397551426781</v>
       </c>
       <c r="R303" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S303" s="20" t="n">
-        <v>0.7705855121065255</v>
-      </c>
-      <c r="T303" s="15" t="inlineStr">
-        <is>
-          <t>Tankers (87%)</t>
-        </is>
-      </c>
-      <c r="U303" s="17" t="inlineStr">
-        <is>
-          <t>Tankers 87%; Marine Services And Other 13%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S303" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T303" s="15" t="n"/>
+      <c r="U303" s="17" t="n"/>
       <c r="V303" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W303" s="17" t="n"/>
-      <c r="X303" s="15" t="inlineStr">
-        <is>
-          <t>Marine Services And  +10%</t>
-        </is>
-      </c>
+      <c r="X303" s="15" t="n"/>
     </row>
     <row r="304" ht="16" customHeight="1">
       <c r="A304" s="13" t="n">
@@ -26936,12 +26928,12 @@
       </c>
       <c r="B304" s="14" t="inlineStr">
         <is>
-          <t>AWRE</t>
+          <t>LTCH</t>
         </is>
       </c>
       <c r="C304" s="15" t="inlineStr">
         <is>
-          <t>Aware, Inc.</t>
+          <t>Latch Inc. Common Stock</t>
         </is>
       </c>
       <c r="D304" s="16" t="inlineStr">
@@ -26955,7 +26947,7 @@
         </is>
       </c>
       <c r="F304" s="18" t="n">
-        <v>28139898</v>
+        <v>32851562</v>
       </c>
       <c r="G304" s="19" t="inlineStr">
         <is>
@@ -26963,7 +26955,7 @@
         </is>
       </c>
       <c r="H304" s="20" t="n">
-        <v>-1.513124630984469</v>
+        <v>-0.0075030035299217</v>
       </c>
       <c r="I304" s="21" t="inlineStr">
         <is>
@@ -26971,24 +26963,28 @@
         </is>
       </c>
       <c r="J304" s="20" t="n">
-        <v>1.2275732</v>
+        <v>0.0870110976914682</v>
       </c>
       <c r="K304" s="20" t="n">
-        <v>1.6484036</v>
-      </c>
-      <c r="L304" s="22" t="n">
-        <v>-19.12873855815686</v>
+        <v>0.794283413926499</v>
+      </c>
+      <c r="L304" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="M304" s="21" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N304" s="22" t="n">
-        <v>-91.03151464667501</v>
+      <c r="N304" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O304" s="22" t="n">
-        <v>-45.63612933458294</v>
+        <v>-351.3757253384913</v>
       </c>
       <c r="P304" s="21" t="inlineStr">
         <is>
@@ -26996,7 +26992,7 @@
         </is>
       </c>
       <c r="Q304" s="22" t="n">
-        <v>-23.49397551426781</v>
+        <v>71.42858359278503</v>
       </c>
       <c r="R304" s="18" t="n">
         <v>0</v>
@@ -27009,9 +27005,13 @@
       <c r="T304" s="15" t="n"/>
       <c r="U304" s="17" t="n"/>
       <c r="V304" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W304" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="W304" s="17" t="inlineStr">
+        <is>
+          <t>Non Us 100%</t>
+        </is>
+      </c>
       <c r="X304" s="15" t="n"/>
     </row>
     <row r="305" ht="16" customHeight="1">
@@ -33237,12 +33237,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>CMCT</t>
+          <t>SNDR</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>CIM Commercial Trust Corporati</t>
+          <t>Schneider National, Inc.</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -33252,11 +33252,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>10022646</v>
+        <v>6355260928</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -33264,53 +33264,49 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>21.25711007962565</v>
+        <v>11.262</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>0.016938176</v>
+        <v>64.80356999999999</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>0.0391425514049715</v>
+        <v>2.104134</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>0.08807942631666819</v>
-      </c>
-      <c r="L69" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M69" s="21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.1206596</v>
+      </c>
+      <c r="L69" s="22" t="n">
+        <v>0.6860457893696701</v>
+      </c>
+      <c r="M69" s="22" t="n">
+        <v>1.1</v>
       </c>
       <c r="N69" s="22" t="n">
-        <v>46.79635412727057</v>
+        <v>5.202221455241441</v>
       </c>
       <c r="O69" s="22" t="n">
-        <v>502.2000508218427</v>
+        <v>10.84925615173094</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>1.289717709720373</v>
+        <v>0.2708367181153533</v>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>-99.5848595732152</v>
+        <v>50.42707445283197</v>
       </c>
       <c r="R69" s="18" t="n">
         <v>4</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.3370207613496181</v>
+        <v>0.34731905609149</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Office Properties (43%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Office Properties 43%; Hotel Properties 36%; Multifamily Properties 14%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Truckload 26%; Logist</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
@@ -33319,7 +33315,7 @@
       <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Hotel Properties +10%</t>
+          <t>Truckload +12%</t>
         </is>
       </c>
     </row>
@@ -33329,12 +33325,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>SNDR</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Schneider National, Inc.</t>
+          <t>Cnh Industrial N.V.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -33348,7 +33344,7 @@
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>6355260928</v>
+        <v>13676654592</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -33356,58 +33352,62 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>11.262</v>
+        <v>35.749</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>64.80356999999999</v>
+        <v>34.46875</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>2.104134</v>
+        <v>1.7597319</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>1.1206596</v>
+        <v>0.7559086</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>0.6860457893696701</v>
+        <v>-23.15624759473343</v>
       </c>
       <c r="M70" s="22" t="n">
-        <v>1.1</v>
+        <v>0.91</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>5.202221455241441</v>
+        <v>26.69022000963545</v>
       </c>
       <c r="O70" s="22" t="n">
-        <v>10.84925615173094</v>
+        <v>12.77737298801086</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>0.2708367181153533</v>
+        <v>-0.8216692586832556</v>
       </c>
       <c r="Q70" s="22" t="n">
-        <v>50.42707445283197</v>
+        <v>-14.53210106408921</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.34731905609149</v>
+        <v>0.2973036954946031</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Agricultural Equipment (37%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Truckload 26%; Logist</t>
+          <t>Agricultural Equipment 37%; Agriculture 37%; Construction Equipment 9%</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="17" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="W70" s="17" t="inlineStr">
+        <is>
+          <t>Rest Of World And Other 49%; US 16%; Others Countries 9%</t>
+        </is>
+      </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Truckload +12%</t>
+          <t>Construction Equipme +12%</t>
         </is>
       </c>
     </row>
@@ -33417,12 +33417,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>CMCT</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Cnh Industrial N.V.</t>
+          <t>CIM Commercial Trust Corporati</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -33432,11 +33432,11 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>13676654592</v>
+        <v>10022646</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -33444,62 +33444,62 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>35.749</v>
+        <v>21.25711007962565</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>34.46875</v>
+        <v>0.016938176</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>1.7597319</v>
+        <v>0.0391425514049715</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>0.7559086</v>
-      </c>
-      <c r="L71" s="22" t="n">
-        <v>-23.15624759473343</v>
-      </c>
-      <c r="M71" s="22" t="n">
-        <v>0.91</v>
+        <v>0.08807942631666819</v>
+      </c>
+      <c r="L71" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M71" s="21" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N71" s="22" t="n">
-        <v>26.69022000963545</v>
+        <v>46.79635412727057</v>
       </c>
       <c r="O71" s="22" t="n">
-        <v>12.77737298801086</v>
+        <v>502.2000508218427</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>-0.8216692586832556</v>
+        <v>1.289717709720373</v>
       </c>
       <c r="Q71" s="22" t="n">
-        <v>-14.53210106408921</v>
+        <v>-99.5848595732152</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.2973036954946031</v>
+        <v>0.3370207613496181</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>Agricultural Equipment (37%)</t>
+          <t>Office Properties (43%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>Agricultural Equipment 37%; Agriculture 37%; Construction Equipment 9%</t>
+          <t>Office Properties 43%; Hotel Properties 36%; Multifamily Properties 14%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="W71" s="17" t="inlineStr">
-        <is>
-          <t>Rest Of World And Other 49%; US 16%; Others Countries 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W71" s="17" t="n"/>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Construction Equipme +12%</t>
+          <t>Hotel Properties +10%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -536,6 +536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF1B2430"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -816,6 +817,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF4A5568"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -27521,6 +27523,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF3949AB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -33372,6 +33375,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF3949AB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -39241,6 +39245,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF3949AB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -45020,6 +45025,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FF3949AB"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -50810,103 +50810,89 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>VFS</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>VinFast Auto Ltd. Ordinary Sha</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F67" s="18" t="n">
-        <v>7042003968</v>
+        <v>103645716480</v>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H67" s="20" t="n">
+        <v>12.173</v>
+      </c>
+      <c r="I67" s="20" t="n">
+        <v>14.882556</v>
+      </c>
+      <c r="J67" s="20" t="n">
+        <v>3.2740192</v>
+      </c>
+      <c r="K67" s="20" t="n">
+        <v>0.68113136</v>
+      </c>
+      <c r="L67" s="21" t="n">
+        <v>0.1163535310794</v>
+      </c>
+      <c r="M67" s="21" t="n">
+        <v>2.96</v>
       </c>
       <c r="N67" s="21" t="n">
-        <v>78.31448357763071</v>
+        <v>12.24307948200071</v>
       </c>
       <c r="O67" s="21" t="n">
-        <v>-83.1176333196485</v>
-      </c>
-      <c r="P67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.84160433056228</v>
+      </c>
+      <c r="P67" s="20" t="n">
+        <v>1.675361394631018</v>
       </c>
       <c r="Q67" s="21" t="n">
-        <v>-3.75</v>
+        <v>92.92</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S67" s="20" t="n">
-        <v>0.460552269511968</v>
+        <v>0.3806408342658987</v>
       </c>
       <c r="T67" s="15" t="inlineStr">
         <is>
-          <t>Car (48%)</t>
+          <t>Marketing Speciality (46%)</t>
         </is>
       </c>
       <c r="U67" s="17" t="inlineStr">
         <is>
-          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
+          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
         </is>
       </c>
       <c r="V67" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W67" s="17" t="inlineStr">
         <is>
-          <t>VN 89%; Asia Pacific 8%; US 2%</t>
+          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
         </is>
       </c>
       <c r="X67" s="15" t="inlineStr">
         <is>
-          <t>E Scooter +230%</t>
+          <t>Refining +92%</t>
         </is>
       </c>
     </row>
@@ -50916,12 +50902,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Amphenol Corp /De/</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -50931,11 +50917,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>103645716480</v>
+        <v>197893832704</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -50943,62 +50929,62 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>12.173</v>
+        <v>29.62302222645686</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>14.882556</v>
+        <v>40.73604</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>3.2740192</v>
+        <v>12.770529</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.68113136</v>
+        <v>6.821197</v>
       </c>
       <c r="L68" s="21" t="n">
-        <v>0.1163535310794</v>
+        <v>2.30913485895705</v>
       </c>
       <c r="M68" s="21" t="n">
-        <v>2.96</v>
+        <v>0.55827491517045</v>
       </c>
       <c r="N68" s="21" t="n">
-        <v>12.24307948200071</v>
+        <v>45.67278672993024</v>
       </c>
       <c r="O68" s="21" t="n">
-        <v>6.84160433056228</v>
+        <v>29.39923710032213</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>1.675361394631018</v>
+        <v>2.057377830710813</v>
       </c>
       <c r="Q68" s="21" t="n">
-        <v>92.92</v>
+        <v>19.46</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68" s="20" t="n">
-        <v>0.3806408342658987</v>
+        <v>0.4256894967493531</v>
       </c>
       <c r="T68" s="15" t="inlineStr">
         <is>
-          <t>Marketing Speciality (46%)</t>
+          <t>Communications Solutio (58%)</t>
         </is>
       </c>
       <c r="U68" s="17" t="inlineStr">
         <is>
-          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
+          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
         </is>
       </c>
       <c r="V68" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W68" s="17" t="inlineStr">
         <is>
-          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
+          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
         </is>
       </c>
       <c r="X68" s="15" t="inlineStr">
         <is>
-          <t>Refining +92%</t>
+          <t>Communications Solut +143%</t>
         </is>
       </c>
     </row>
@@ -51008,12 +50994,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Amphenol Corp /De/</t>
+          <t>Enterprise Products Partners L</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -51023,11 +51009,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>197893832704</v>
+        <v>84932247552</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -51035,62 +51021,58 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>29.62302222645686</v>
+        <v>11.619</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>40.73604</v>
+        <v>13.608996</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>12.770529</v>
+        <v>2.8078818</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>6.821197</v>
+        <v>1.4525534</v>
       </c>
       <c r="L69" s="21" t="n">
-        <v>2.30913485895705</v>
+        <v>4.43809968934908</v>
       </c>
       <c r="M69" s="21" t="n">
-        <v>0.55827491517045</v>
+        <v>0.13529237831726</v>
       </c>
       <c r="N69" s="21" t="n">
-        <v>45.67278672993024</v>
+        <v>21.16359754470242</v>
       </c>
       <c r="O69" s="21" t="n">
-        <v>29.39923710032213</v>
+        <v>19.03228934354698</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>2.057377830710813</v>
+        <v>3.436213572447524</v>
       </c>
       <c r="Q69" s="21" t="n">
-        <v>19.46</v>
+        <v>32.34</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.4256894967493531</v>
+        <v>0.3092139839729619</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Communications Solutio (58%)</t>
+          <t>Onshore Crude Oil Pipe (39%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
+          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Communications Solut +143%</t>
+          <t>Petrochemical And Re +92%</t>
         </is>
       </c>
     </row>
@@ -51100,12 +51082,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -51115,11 +51097,11 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>84932247552</v>
+        <v>57875783680</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -51127,58 +51109,62 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>11.619</v>
+        <v>38.313</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>13.608996</v>
+        <v>52.658604</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>2.8078818</v>
+        <v>18.433002</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>1.4525534</v>
+        <v>17.07662815293724</v>
       </c>
       <c r="L70" s="21" t="n">
-        <v>4.43809968934908</v>
+        <v>1.43309891391495</v>
       </c>
       <c r="M70" s="21" t="n">
-        <v>0.13529237831726</v>
+        <v>0.11999999</v>
       </c>
       <c r="N70" s="21" t="n">
-        <v>21.16359754470242</v>
+        <v>28.59709180832235</v>
       </c>
       <c r="O70" s="21" t="n">
-        <v>19.03228934354698</v>
+        <v>44.40287939770699</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>3.436213572447524</v>
+        <v>-0.1708346552178611</v>
       </c>
       <c r="Q70" s="21" t="n">
-        <v>32.34</v>
+        <v>96.81</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.3092139839729619</v>
+        <v>0.6478300772075185</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipe (39%)</t>
+          <t>Semiconductor Test (79%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
+          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="17" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="W70" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
+        </is>
+      </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Petrochemical And Re +92%</t>
+          <t>Semiconductor Test +128%</t>
         </is>
       </c>
     </row>
@@ -51188,12 +51174,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Te Connectivity Plc</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -51207,7 +51193,7 @@
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>57875783680</v>
+        <v>59243089920</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -51215,62 +51201,62 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>38.313</v>
+        <v>12.92</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>52.658604</v>
+        <v>20.042116</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>18.433002</v>
+        <v>4.479151</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>17.07662815293724</v>
+        <v>3.066095</v>
       </c>
       <c r="L71" s="21" t="n">
-        <v>1.43309891391495</v>
+        <v>5.99434499439441</v>
       </c>
       <c r="M71" s="21" t="n">
-        <v>0.11999999</v>
+        <v>1.50999995</v>
       </c>
       <c r="N71" s="21" t="n">
-        <v>28.59709180832235</v>
+        <v>19.58952110795928</v>
       </c>
       <c r="O71" s="21" t="n">
-        <v>44.40287939770699</v>
+        <v>23.88059701492537</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>-0.1708346552178611</v>
+        <v>1.09837962962963</v>
       </c>
       <c r="Q71" s="21" t="n">
-        <v>96.81</v>
+        <v>-14.61</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.6478300772075185</v>
+        <v>0.5038462678974261</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test (79%)</t>
+          <t>Transportation Solutio (54%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
+          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W71" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
+          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
         </is>
       </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test +128%</t>
+          <t>Industrial Solutions +344%</t>
         </is>
       </c>
     </row>
@@ -51280,12 +51266,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>DWSN</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Te Connectivity Plc</t>
+          <t>Dawson Geophysical Company</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -51295,11 +51281,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>59243089920</v>
+        <v>104812712</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -51307,62 +51293,58 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>12.92</v>
+        <v>9.484</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>20.042116</v>
+        <v>28.125</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>4.479151</v>
+        <v>4.494008</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>3.066095</v>
+        <v>0.7845967601880408</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>5.99434499439441</v>
+        <v>-3.92755347083511</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>1.50999995</v>
+        <v>8.120800080331669</v>
       </c>
       <c r="N72" s="21" t="n">
-        <v>19.58952110795928</v>
+        <v>25.64674804153762</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>23.88059701492537</v>
+        <v>8.550169176872171</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>1.09837962962963</v>
+        <v>1.218788303274383</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>-14.61</v>
+        <v>85.28</v>
       </c>
       <c r="R72" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S72" s="20" t="n">
-        <v>0.5038462678974261</v>
+        <v>0.6695871789304009</v>
       </c>
       <c r="T72" s="15" t="inlineStr">
         <is>
-          <t>Transportation Solutio (54%)</t>
+          <t>United States Operatio (79%)</t>
         </is>
       </c>
       <c r="U72" s="17" t="inlineStr">
         <is>
-          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
+          <t>United States Operations 79%; Canada Operations 21%</t>
         </is>
       </c>
       <c r="V72" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W72" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W72" s="17" t="n"/>
       <c r="X72" s="15" t="inlineStr">
         <is>
-          <t>Industrial Solutions +344%</t>
+          <t>Canada Operations +152%</t>
         </is>
       </c>
     </row>
@@ -51372,12 +51354,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>DWSN</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Dawson Geophysical Company</t>
+          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -51387,11 +51369,11 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F73" s="18" t="n">
-        <v>104812712</v>
+        <v>4341746688</v>
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
@@ -51399,58 +51381,62 @@
         </is>
       </c>
       <c r="H73" s="20" t="n">
-        <v>9.484</v>
+        <v>20.13</v>
       </c>
       <c r="I73" s="20" t="n">
-        <v>28.125</v>
+        <v>38.05963</v>
       </c>
       <c r="J73" s="20" t="n">
-        <v>4.494008</v>
+        <v>4.7612762</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>0.7845967601880408</v>
+        <v>5.768651473138067</v>
       </c>
       <c r="L73" s="21" t="n">
-        <v>-3.92755347083511</v>
+        <v>0.9359515835039199</v>
       </c>
       <c r="M73" s="21" t="n">
-        <v>8.120800080331669</v>
+        <v>0.64999997</v>
       </c>
       <c r="N73" s="21" t="n">
-        <v>25.64674804153762</v>
+        <v>-5.462297040904851</v>
       </c>
       <c r="O73" s="21" t="n">
-        <v>8.550169176872171</v>
+        <v>25.49940543018288</v>
       </c>
       <c r="P73" s="20" t="n">
-        <v>1.218788303274383</v>
+        <v>-2.120367819924969</v>
       </c>
       <c r="Q73" s="21" t="n">
-        <v>85.28</v>
+        <v>106.32</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S73" s="20" t="n">
-        <v>0.6695871789304009</v>
+        <v>0.2775979208843406</v>
       </c>
       <c r="T73" s="15" t="inlineStr">
         <is>
-          <t>United States Operatio (79%)</t>
+          <t>Ball Bonding Equipment (43%)</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
         <is>
-          <t>United States Operations 79%; Canada Operations 21%</t>
+          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
         </is>
       </c>
       <c r="V73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W73" s="17" t="inlineStr">
+        <is>
+          <t>CN 56%; US 10%; All Other Segments 9%</t>
+        </is>
+      </c>
       <c r="X73" s="15" t="inlineStr">
         <is>
-          <t>Canada Operations +152%</t>
+          <t>Ball Bonding Equipme +198%</t>
         </is>
       </c>
     </row>
@@ -51460,12 +51446,12 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
+          <t>Emergent Biosolutions Inc.</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -51475,11 +51461,11 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F74" s="18" t="n">
-        <v>4341746688</v>
+        <v>300974464</v>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
@@ -51487,62 +51473,66 @@
         </is>
       </c>
       <c r="H74" s="20" t="n">
-        <v>20.13</v>
-      </c>
-      <c r="I74" s="20" t="n">
-        <v>38.05963</v>
+        <v>26.38994704225352</v>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J74" s="20" t="n">
-        <v>4.7612762</v>
+        <v>0.88204354</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>5.768651473138067</v>
+        <v>0.39077443</v>
       </c>
       <c r="L74" s="21" t="n">
-        <v>0.9359515835039199</v>
-      </c>
-      <c r="M74" s="21" t="n">
-        <v>0.64999997</v>
+        <v>26.97801418097588</v>
+      </c>
+      <c r="M74" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N74" s="21" t="n">
-        <v>-5.462297040904851</v>
+        <v>14.79068774028193</v>
       </c>
       <c r="O74" s="21" t="n">
-        <v>25.49940543018288</v>
+        <v>3.78515260562441</v>
       </c>
       <c r="P74" s="20" t="n">
-        <v>-2.120367819924969</v>
+        <v>14.55281690140845</v>
       </c>
       <c r="Q74" s="21" t="n">
-        <v>106.32</v>
+        <v>-50.23999999999999</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S74" s="20" t="n">
-        <v>0.2775979208843406</v>
+        <v>0.557029765440831</v>
       </c>
       <c r="T74" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment (43%)</t>
+          <t>MCM Products (67%)</t>
         </is>
       </c>
       <c r="U74" s="17" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
+          <t>MCM Products 67%; Commercial Products 33%</t>
         </is>
       </c>
       <c r="V74" s="18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W74" s="17" t="inlineStr">
         <is>
-          <t>CN 56%; US 10%; All Other Segments 9%</t>
+          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
         </is>
       </c>
       <c r="X74" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipme +198%</t>
+          <t>MCM Products +188%</t>
         </is>
       </c>
     </row>
@@ -51552,12 +51542,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Emergent Biosolutions Inc.</t>
+          <t>Porch Group Inc.</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -51567,11 +51557,11 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F75" s="18" t="n">
-        <v>300974464</v>
+        <v>1849238272</v>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
@@ -51579,66 +51569,62 @@
         </is>
       </c>
       <c r="H75" s="20" t="n">
-        <v>26.38994704225352</v>
+        <v>37.42943855774974</v>
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J75" s="20" t="n">
-        <v>0.88204354</v>
+      <c r="J75" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K75" s="20" t="n">
-        <v>0.39077443</v>
+        <v>3.6005628</v>
       </c>
       <c r="L75" s="21" t="n">
-        <v>26.97801418097588</v>
-      </c>
-      <c r="M75" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69353492369449</v>
+      </c>
+      <c r="M75" s="21" t="n">
+        <v>2.78673595725851</v>
       </c>
       <c r="N75" s="21" t="n">
-        <v>14.79068774028193</v>
+        <v>10.31950957042169</v>
       </c>
       <c r="O75" s="21" t="n">
-        <v>3.78515260562441</v>
+        <v>10.50153492306376</v>
       </c>
       <c r="P75" s="20" t="n">
-        <v>14.55281690140845</v>
+        <v>3.279218781110286</v>
       </c>
       <c r="Q75" s="21" t="n">
-        <v>-50.23999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75" s="20" t="n">
-        <v>0.557029765440831</v>
+        <v>0.5817970747345014</v>
       </c>
       <c r="T75" s="15" t="inlineStr">
         <is>
-          <t>MCM Products (67%)</t>
+          <t>Insurance Services (72%)</t>
         </is>
       </c>
       <c r="U75" s="17" t="inlineStr">
         <is>
-          <t>MCM Products 67%; Commercial Products 33%</t>
+          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
         </is>
       </c>
       <c r="V75" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W75" s="17" t="inlineStr">
-        <is>
-          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W75" s="17" t="n"/>
       <c r="X75" s="15" t="inlineStr">
         <is>
-          <t>MCM Products +188%</t>
+          <t>Software Data +333%</t>
         </is>
       </c>
     </row>
@@ -51648,12 +51634,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NGL</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Porch Group Inc.</t>
+          <t>NGL Energy Partners LP</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -51663,11 +51649,11 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1849238272</v>
+        <v>1989539712</v>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
@@ -51675,7 +51661,7 @@
         </is>
       </c>
       <c r="H76" s="20" t="n">
-        <v>37.42943855774974</v>
+        <v>15.20590954803408</v>
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
@@ -51688,49 +51674,55 @@
         </is>
       </c>
       <c r="K76" s="20" t="n">
-        <v>3.6005628</v>
+        <v>0.6303674</v>
       </c>
       <c r="L76" s="21" t="n">
-        <v>4.69353492369449</v>
-      </c>
-      <c r="M76" s="21" t="n">
-        <v>2.78673595725851</v>
+        <v>5.12068190373472</v>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N76" s="21" t="n">
-        <v>10.31950957042169</v>
+        <v>12.90137422847655</v>
       </c>
       <c r="O76" s="21" t="n">
-        <v>10.50153492306376</v>
+        <v>11.58580003385248</v>
       </c>
       <c r="P76" s="20" t="n">
-        <v>3.279218781110286</v>
+        <v>7.901573173509551</v>
       </c>
       <c r="Q76" s="21" t="n">
-        <v>19.2</v>
+        <v>174.77</v>
       </c>
       <c r="R76" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S76" s="20" t="n">
-        <v>0.5817970747345014</v>
+        <v>0.3423299785064143</v>
       </c>
       <c r="T76" s="15" t="inlineStr">
         <is>
-          <t>Insurance Services (72%)</t>
+          <t>Liquids Logistics (40%)</t>
         </is>
       </c>
       <c r="U76" s="17" t="inlineStr">
         <is>
-          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
+          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
         </is>
       </c>
       <c r="V76" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="W76" s="17" t="inlineStr">
+        <is>
+          <t>Non Us 100%</t>
+        </is>
+      </c>
       <c r="X76" s="15" t="inlineStr">
         <is>
-          <t>Software Data +333%</t>
+          <t>Crude Oil Logistics +162%</t>
         </is>
       </c>
     </row>
@@ -51740,12 +51732,12 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>NGL</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>NGL Energy Partners LP</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -51755,11 +51747,11 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F77" s="18" t="n">
-        <v>1989539712</v>
+        <v>322115436544</v>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
@@ -51767,12 +51759,10 @@
         </is>
       </c>
       <c r="H77" s="20" t="n">
-        <v>15.20590954803408</v>
-      </c>
-      <c r="I77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>19.51</v>
+      </c>
+      <c r="I77" s="20" t="n">
+        <v>29.506115</v>
       </c>
       <c r="J77" s="22" t="inlineStr">
         <is>
@@ -51780,55 +51770,53 @@
         </is>
       </c>
       <c r="K77" s="20" t="n">
-        <v>0.6303674</v>
+        <v>2.1304352</v>
       </c>
       <c r="L77" s="21" t="n">
-        <v>5.12068190373472</v>
-      </c>
-      <c r="M77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.02823359941622</v>
+      </c>
+      <c r="M77" s="21" t="n">
+        <v>0.76768205413026</v>
       </c>
       <c r="N77" s="21" t="n">
-        <v>12.90137422847655</v>
+        <v>81.97384514065294</v>
       </c>
       <c r="O77" s="21" t="n">
-        <v>11.58580003385248</v>
+        <v>13.94585527536068</v>
       </c>
       <c r="P77" s="20" t="n">
-        <v>7.901573173509551</v>
+        <v>1.01819258757827</v>
       </c>
       <c r="Q77" s="21" t="n">
-        <v>174.77</v>
+        <v>226.48</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77" s="20" t="n">
-        <v>0.3423299785064143</v>
+        <v>0.5038741410704293</v>
       </c>
       <c r="T77" s="15" t="inlineStr">
         <is>
-          <t>Liquids Logistics (40%)</t>
+          <t>Infrastructure Solutio (54%)</t>
         </is>
       </c>
       <c r="U77" s="17" t="inlineStr">
         <is>
-          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
+          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
         </is>
       </c>
       <c r="V77" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W77" s="17" t="inlineStr">
         <is>
-          <t>Non Us 100%</t>
+          <t>US 56%; Non Us 44%</t>
         </is>
       </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
-          <t>Crude Oil Logistics +162%</t>
+          <t>Infrastructure Solut +181%</t>
         </is>
       </c>
     </row>
@@ -51838,12 +51826,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -51857,7 +51845,7 @@
         </is>
       </c>
       <c r="F78" s="18" t="n">
-        <v>322115436544</v>
+        <v>83932291072</v>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
@@ -51865,64 +51853,64 @@
         </is>
       </c>
       <c r="H78" s="20" t="n">
-        <v>19.51</v>
+        <v>103.491</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>29.506115</v>
-      </c>
-      <c r="J78" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>142.82867</v>
+      </c>
+      <c r="J78" s="20" t="n">
+        <v>17.8521</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>2.1304352</v>
+        <v>27.847475</v>
       </c>
       <c r="L78" s="21" t="n">
-        <v>2.02823359941622</v>
-      </c>
-      <c r="M78" s="21" t="n">
-        <v>0.76768205413026</v>
+        <v>0.37963999713611</v>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N78" s="21" t="n">
-        <v>81.97384514065294</v>
+        <v>5.712871831528011</v>
       </c>
       <c r="O78" s="21" t="n">
-        <v>13.94585527536068</v>
+        <v>32.17730397042276</v>
       </c>
       <c r="P78" s="20" t="n">
-        <v>1.01819258757827</v>
+        <v>-1.18221551413651</v>
       </c>
       <c r="Q78" s="21" t="n">
-        <v>226.48</v>
+        <v>337.22</v>
       </c>
       <c r="R78" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S78" s="20" t="n">
-        <v>0.5038741410704293</v>
+        <v>0.554732848124369</v>
       </c>
       <c r="T78" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solutio (54%)</t>
+          <t>Systems (67%)</t>
         </is>
       </c>
       <c r="U78" s="17" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
+          <t>Systems 67%; Components 33%</t>
         </is>
       </c>
       <c r="V78" s="18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W78" s="17" t="inlineStr">
         <is>
-          <t>US 56%; Non Us 44%</t>
+          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
         </is>
       </c>
       <c r="X78" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solut +181%</t>
+          <t>Systems +279%</t>
         </is>
       </c>
     </row>
@@ -51932,12 +51920,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>PROG Holdings, Inc.</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -51947,11 +51935,11 @@
       </c>
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F79" s="18" t="n">
-        <v>83932291072</v>
+        <v>1479745152</v>
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
@@ -51959,64 +51947,58 @@
         </is>
       </c>
       <c r="H79" s="20" t="n">
-        <v>103.491</v>
+        <v>8.850440627472885</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>142.82867</v>
+        <v>12.061689</v>
       </c>
       <c r="J79" s="20" t="n">
-        <v>17.8521</v>
+        <v>1.8373808</v>
       </c>
       <c r="K79" s="20" t="n">
-        <v>27.847475</v>
+        <v>0.5659371600000001</v>
       </c>
       <c r="L79" s="21" t="n">
-        <v>0.37963999713611</v>
-      </c>
-      <c r="M79" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.7154094641091</v>
+      </c>
+      <c r="M79" s="21" t="n">
+        <v>1.20889722398801</v>
       </c>
       <c r="N79" s="21" t="n">
-        <v>5.712871831528011</v>
+        <v>14.37354784103989</v>
       </c>
       <c r="O79" s="21" t="n">
-        <v>32.17730397042276</v>
+        <v>10.44635139915609</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>-1.18221551413651</v>
+        <v>3.362100265326072</v>
       </c>
       <c r="Q79" s="21" t="n">
-        <v>337.22</v>
+        <v>38.15</v>
       </c>
       <c r="R79" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S79" s="20" t="n">
-        <v>0.554732848124369</v>
+        <v>0.9403673440059026</v>
       </c>
       <c r="T79" s="15" t="inlineStr">
         <is>
-          <t>Systems (67%)</t>
+          <t>Progressive Leasing (97%)</t>
         </is>
       </c>
       <c r="U79" s="17" t="inlineStr">
         <is>
-          <t>Systems 67%; Components 33%</t>
+          <t>Progressive Leasing 97%; Four 3%</t>
         </is>
       </c>
       <c r="V79" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W79" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W79" s="17" t="n"/>
       <c r="X79" s="15" t="inlineStr">
         <is>
-          <t>Systems +279%</t>
+          <t>Four +170%</t>
         </is>
       </c>
     </row>
@@ -52026,12 +52008,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>PROG Holdings, Inc.</t>
+          <t>Ies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -52045,7 +52027,7 @@
         </is>
       </c>
       <c r="F80" s="18" t="n">
-        <v>1479745152</v>
+        <v>12732460032</v>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
@@ -52053,49 +52035,51 @@
         </is>
       </c>
       <c r="H80" s="20" t="n">
-        <v>8.850440627472885</v>
+        <v>22.535</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>12.061689</v>
+        <v>28.401777</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>1.8373808</v>
+        <v>10.357883</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>0.5659371600000001</v>
+        <v>3.1945016</v>
       </c>
       <c r="L80" s="21" t="n">
-        <v>20.7154094641091</v>
-      </c>
-      <c r="M80" s="21" t="n">
-        <v>1.20889722398801</v>
+        <v>2.01426811681025</v>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N80" s="21" t="n">
-        <v>14.37354784103989</v>
+        <v>39.14787497533104</v>
       </c>
       <c r="O80" s="21" t="n">
-        <v>10.44635139915609</v>
+        <v>13.0825133917565</v>
       </c>
       <c r="P80" s="20" t="n">
-        <v>3.362100265326072</v>
+        <v>-0.6658293394323307</v>
       </c>
       <c r="Q80" s="21" t="n">
-        <v>38.15</v>
+        <v>64.63</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S80" s="20" t="n">
-        <v>0.9403673440059026</v>
+        <v>0.302118628032772</v>
       </c>
       <c r="T80" s="15" t="inlineStr">
         <is>
-          <t>Progressive Leasing (97%)</t>
+          <t>Residential (39%)</t>
         </is>
       </c>
       <c r="U80" s="17" t="inlineStr">
         <is>
-          <t>Progressive Leasing 97%; Four 3%</t>
+          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
         </is>
       </c>
       <c r="V80" s="18" t="n">
@@ -52104,7 +52088,7 @@
       <c r="W80" s="17" t="n"/>
       <c r="X80" s="15" t="inlineStr">
         <is>
-          <t>Four +170%</t>
+          <t>Commercialand Indust +109%</t>
         </is>
       </c>
     </row>
@@ -52114,12 +52098,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Ies Holdings, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
@@ -52129,11 +52113,11 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F81" s="18" t="n">
-        <v>12732460032</v>
+        <v>5272738725888</v>
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
@@ -52141,60 +52125,62 @@
         </is>
       </c>
       <c r="H81" s="20" t="n">
-        <v>22.535</v>
+        <v>26.03</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>28.401777</v>
+        <v>27.640507</v>
       </c>
       <c r="J81" s="20" t="n">
-        <v>10.357883</v>
+        <v>23.026468</v>
       </c>
       <c r="K81" s="20" t="n">
-        <v>3.1945016</v>
+        <v>195.9106311171881</v>
       </c>
       <c r="L81" s="21" t="n">
-        <v>2.01426811681025</v>
-      </c>
-      <c r="M81" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.66135648441059</v>
+      </c>
+      <c r="M81" s="21" t="n">
+        <v>0.01871342168819</v>
       </c>
       <c r="N81" s="21" t="n">
-        <v>39.14787497533104</v>
+        <v>73.21388307718124</v>
       </c>
       <c r="O81" s="21" t="n">
-        <v>13.0825133917565</v>
+        <v>79.39769221313577</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>-0.6658293394323307</v>
+        <v>-0.3535471835000259</v>
       </c>
       <c r="Q81" s="21" t="n">
-        <v>64.63</v>
+        <v>13.91</v>
       </c>
       <c r="R81" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" s="20" t="n">
+        <v>0.8136213783744384</v>
+      </c>
+      <c r="T81" s="15" t="inlineStr">
+        <is>
+          <t>Compute And Networking (90%)</t>
+        </is>
+      </c>
+      <c r="U81" s="17" t="inlineStr">
+        <is>
+          <t>Compute And Networking 90%; Graphics 10%</t>
+        </is>
+      </c>
+      <c r="V81" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S81" s="20" t="n">
-        <v>0.302118628032772</v>
-      </c>
-      <c r="T81" s="15" t="inlineStr">
-        <is>
-          <t>Residential (39%)</t>
-        </is>
-      </c>
-      <c r="U81" s="17" t="inlineStr">
-        <is>
-          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
-        </is>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" s="17" t="n"/>
+      <c r="W81" s="17" t="inlineStr">
+        <is>
+          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
+        </is>
+      </c>
       <c r="X81" s="15" t="inlineStr">
         <is>
-          <t>Commercialand Indust +109%</t>
+          <t>Compute And Networki +114%</t>
         </is>
       </c>
     </row>
@@ -52204,12 +52190,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -52219,11 +52205,11 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F82" s="18" t="n">
-        <v>5272738725888</v>
+        <v>10380166144</v>
       </c>
       <c r="G82" s="19" t="inlineStr">
         <is>
@@ -52231,62 +52217,64 @@
         </is>
       </c>
       <c r="H82" s="20" t="n">
-        <v>26.03</v>
+        <v>347.3889692037075</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>27.640507</v>
+        <v>67.52282</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>23.026468</v>
+        <v>6.511023</v>
       </c>
       <c r="K82" s="20" t="n">
-        <v>195.9106311171881</v>
+        <v>4.737009435990017</v>
       </c>
       <c r="L82" s="21" t="n">
-        <v>1.66135648441059</v>
-      </c>
-      <c r="M82" s="21" t="n">
-        <v>0.01871342168819</v>
+        <v>-8.42592261675078</v>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N82" s="21" t="n">
-        <v>73.21388307718124</v>
+        <v>-0.11123836175898</v>
       </c>
       <c r="O82" s="21" t="n">
-        <v>79.39769221313577</v>
+        <v>1.17675041790433</v>
       </c>
       <c r="P82" s="20" t="n">
-        <v>-0.3535471835000259</v>
+        <v>-59.63858781496614</v>
       </c>
       <c r="Q82" s="21" t="n">
-        <v>13.91</v>
+        <v>7.08</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S82" s="20" t="n">
-        <v>0.8136213783744384</v>
+        <v>0.3007342710765748</v>
       </c>
       <c r="T82" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networking (90%)</t>
+          <t>Brokerage (38%)</t>
         </is>
       </c>
       <c r="U82" s="17" t="inlineStr">
         <is>
-          <t>Compute And Networking 90%; Graphics 10%</t>
+          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
         </is>
       </c>
       <c r="V82" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W82" s="17" t="inlineStr">
         <is>
-          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
+          <t>KZ 84%; AM 8%; CY 7%</t>
         </is>
       </c>
       <c r="X82" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networki +114%</t>
+          <t>Other +100%</t>
         </is>
       </c>
     </row>
@@ -52296,12 +52284,12 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp.</t>
+          <t>FutureFuel Corp.</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
@@ -52311,76 +52299,80 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F83" s="18" t="n">
-        <v>10380166144</v>
+        <v>234668752</v>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H83" s="20" t="n">
-        <v>347.3889692037075</v>
-      </c>
-      <c r="I83" s="20" t="n">
-        <v>67.52282</v>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J83" s="20" t="n">
-        <v>6.511023</v>
+        <v>1.5329512</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>4.737009435990017</v>
+        <v>1.5316905</v>
       </c>
       <c r="L83" s="21" t="n">
-        <v>-8.42592261675078</v>
-      </c>
-      <c r="M83" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-19.02773752715573</v>
+      </c>
+      <c r="M83" s="21" t="n">
+        <v>5.946712029429071</v>
       </c>
       <c r="N83" s="21" t="n">
-        <v>-0.11123836175898</v>
+        <v>-51.30812980930077</v>
       </c>
       <c r="O83" s="21" t="n">
-        <v>1.17675041790433</v>
-      </c>
-      <c r="P83" s="20" t="n">
-        <v>-59.63858781496614</v>
+        <v>-11.30220868498371</v>
+      </c>
+      <c r="P83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q83" s="21" t="n">
-        <v>7.08</v>
+        <v>38.74</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S83" s="20" t="n">
-        <v>0.3007342710765748</v>
+        <v>0.5298367272208879</v>
       </c>
       <c r="T83" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (38%)</t>
+          <t>Chemicals (62%)</t>
         </is>
       </c>
       <c r="U83" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
+          <t>Chemicals 62%; Biofuels 38%</t>
         </is>
       </c>
       <c r="V83" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W83" s="17" t="inlineStr">
         <is>
-          <t>KZ 84%; AM 8%; CY 7%</t>
+          <t>US 99%; Non Us 1%</t>
         </is>
       </c>
       <c r="X83" s="15" t="inlineStr">
         <is>
-          <t>Other +100%</t>
+          <t>Biofuels +178%</t>
         </is>
       </c>
     </row>
@@ -52390,12 +52382,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>SLNH</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>FutureFuel Corp.</t>
+          <t>Soluna Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -52405,11 +52397,11 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F84" s="18" t="n">
-        <v>234668752</v>
+        <v>283725056</v>
       </c>
       <c r="G84" s="19" t="inlineStr">
         <is>
@@ -52427,22 +52419,24 @@
         </is>
       </c>
       <c r="J84" s="20" t="n">
-        <v>1.5329512</v>
+        <v>1.6666666</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>1.5316905</v>
+        <v>6.742996</v>
       </c>
       <c r="L84" s="21" t="n">
-        <v>-19.02773752715573</v>
+        <v>-15.20023065482923</v>
       </c>
       <c r="M84" s="21" t="n">
-        <v>5.946712029429071</v>
-      </c>
-      <c r="N84" s="21" t="n">
-        <v>-51.30812980930077</v>
+        <v>0.20077091953947</v>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>-11.30220868498371</v>
+        <v>-104.2041970672814</v>
       </c>
       <c r="P84" s="22" t="inlineStr">
         <is>
@@ -52450,35 +52444,31 @@
         </is>
       </c>
       <c r="Q84" s="21" t="n">
-        <v>38.74</v>
+        <v>-65.62</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S84" s="20" t="n">
-        <v>0.5298367272208879</v>
+        <v>0.5183581202661786</v>
       </c>
       <c r="T84" s="15" t="inlineStr">
         <is>
-          <t>Chemicals (62%)</t>
+          <t>Data Center Hosting (60%)</t>
         </is>
       </c>
       <c r="U84" s="17" t="inlineStr">
         <is>
-          <t>Chemicals 62%; Biofuels 38%</t>
+          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
         </is>
       </c>
       <c r="V84" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W84" s="17" t="inlineStr">
-        <is>
-          <t>US 99%; Non Us 1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W84" s="17" t="n"/>
       <c r="X84" s="15" t="inlineStr">
         <is>
-          <t>Biofuels +178%</t>
+          <t>Data Center Hosting +303%</t>
         </is>
       </c>
     </row>
@@ -52488,12 +52478,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>SLNH</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Soluna Holdings Inc. Common St</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
@@ -52503,78 +52493,74 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F85" s="18" t="n">
-        <v>283725056</v>
+        <v>95527116800</v>
       </c>
       <c r="G85" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H85" s="20" t="n">
+        <v>48.51287624683352</v>
+      </c>
+      <c r="I85" s="20" t="n">
+        <v>59.503597</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>1.6666666</v>
+        <v>20.076868</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>6.742996</v>
+        <v>8.321467</v>
       </c>
       <c r="L85" s="21" t="n">
-        <v>-15.20023065482923</v>
+        <v>2.71275941299938</v>
       </c>
       <c r="M85" s="21" t="n">
-        <v>0.20077091953947</v>
-      </c>
-      <c r="N85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.03768476778678</v>
+      </c>
+      <c r="N85" s="21" t="n">
+        <v>33.68683344961626</v>
       </c>
       <c r="O85" s="21" t="n">
-        <v>-104.2041970672814</v>
-      </c>
-      <c r="P85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.35492557684859</v>
+      </c>
+      <c r="P85" s="20" t="n">
+        <v>0.3332181723959233</v>
       </c>
       <c r="Q85" s="21" t="n">
-        <v>-65.62</v>
+        <v>45.58</v>
       </c>
       <c r="R85" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S85" s="20" t="n">
-        <v>0.5183581202661786</v>
+        <v>0.5218491323594365</v>
       </c>
       <c r="T85" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting (60%)</t>
+          <t>EMEA (66%)</t>
         </is>
       </c>
       <c r="U85" s="17" t="inlineStr">
         <is>
-          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
+          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
         </is>
       </c>
       <c r="V85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W85" s="17" t="inlineStr">
+        <is>
+          <t>US 59%; Asia 20%; Europe 14%</t>
+        </is>
+      </c>
       <c r="X85" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting +303%</t>
+          <t>Asia Pacific +290%</t>
         </is>
       </c>
     </row>
@@ -52584,12 +52570,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -52599,11 +52585,11 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F86" s="18" t="n">
-        <v>95527116800</v>
+        <v>3637856000</v>
       </c>
       <c r="G86" s="19" t="inlineStr">
         <is>
@@ -52611,62 +52597,58 @@
         </is>
       </c>
       <c r="H86" s="20" t="n">
-        <v>48.51287624683352</v>
+        <v>19.297</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>59.503597</v>
+        <v>30</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>20.076868</v>
+        <v>4.76368</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>8.321467</v>
+        <v>6.6403623</v>
       </c>
       <c r="L86" s="21" t="n">
-        <v>2.71275941299938</v>
+        <v>5.56871008366637</v>
       </c>
       <c r="M86" s="21" t="n">
-        <v>0.03768476778678</v>
+        <v>0.97</v>
       </c>
       <c r="N86" s="21" t="n">
-        <v>33.68683344961626</v>
+        <v>12.37235274898268</v>
       </c>
       <c r="O86" s="21" t="n">
-        <v>21.35492557684859</v>
+        <v>35.60723129340358</v>
       </c>
       <c r="P86" s="20" t="n">
-        <v>0.3332181723959233</v>
+        <v>1.359732752360203</v>
       </c>
       <c r="Q86" s="21" t="n">
-        <v>45.58</v>
+        <v>17.58</v>
       </c>
       <c r="R86" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S86" s="20" t="n">
-        <v>0.5218491323594365</v>
+        <v>0.4262861010394083</v>
       </c>
       <c r="T86" s="15" t="inlineStr">
         <is>
-          <t>EMEA (66%)</t>
+          <t>Hospitality (52%)</t>
         </is>
       </c>
       <c r="U86" s="17" t="inlineStr">
         <is>
-          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
+          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
         </is>
       </c>
       <c r="V86" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W86" s="17" t="inlineStr">
-        <is>
-          <t>US 59%; Asia 20%; Europe 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W86" s="17" t="n"/>
       <c r="X86" s="15" t="inlineStr">
         <is>
-          <t>Asia Pacific +290%</t>
+          <t>Hospitality +157%</t>
         </is>
       </c>
     </row>
@@ -52676,12 +52658,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>HTLM</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Homestolife Ltd</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
@@ -52691,11 +52673,11 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F87" s="18" t="n">
-        <v>3637856000</v>
+        <v>159643760</v>
       </c>
       <c r="G87" s="19" t="inlineStr">
         <is>
@@ -52703,58 +52685,66 @@
         </is>
       </c>
       <c r="H87" s="20" t="n">
-        <v>19.297</v>
+        <v>5.632</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>30</v>
+        <v>9.368421</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>4.76368</v>
+        <v>5.189504</v>
       </c>
       <c r="K87" s="20" t="n">
-        <v>6.6403623</v>
+        <v>0.4083795</v>
       </c>
       <c r="L87" s="21" t="n">
-        <v>5.56871008366637</v>
-      </c>
-      <c r="M87" s="21" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N87" s="21" t="n">
-        <v>12.37235274898268</v>
+        <v>7.56174932272778</v>
+      </c>
+      <c r="M87" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>35.60723129340358</v>
+        <v>5.26038476371263</v>
       </c>
       <c r="P87" s="20" t="n">
-        <v>1.359732752360203</v>
+        <v>-0.8495431924900106</v>
       </c>
       <c r="Q87" s="21" t="n">
-        <v>17.58</v>
+        <v>-46.17305967367813</v>
       </c>
       <c r="R87" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S87" s="20" t="n">
-        <v>0.4262861010394083</v>
+        <v>0.8590900293205138</v>
       </c>
       <c r="T87" s="15" t="inlineStr">
         <is>
-          <t>Hospitality (52%)</t>
+          <t>Export Sales (93%)</t>
         </is>
       </c>
       <c r="U87" s="17" t="inlineStr">
         <is>
-          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
+          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
         </is>
       </c>
       <c r="V87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W87" s="17" t="inlineStr">
+        <is>
+          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
+        </is>
+      </c>
       <c r="X87" s="15" t="inlineStr">
         <is>
-          <t>Hospitality +157%</t>
+          <t>Retail Sales +100%</t>
         </is>
       </c>
     </row>
@@ -52764,12 +52754,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Homestolife Ltd</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -52779,11 +52769,11 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F88" s="18" t="n">
-        <v>159643760</v>
+        <v>110777000</v>
       </c>
       <c r="G88" s="19" t="inlineStr">
         <is>
@@ -52791,66 +52781,64 @@
         </is>
       </c>
       <c r="H88" s="20" t="n">
-        <v>5.632</v>
+        <v>11.493</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>9.368421</v>
+        <v>22.837208</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>5.189504</v>
+        <v>1.8031582</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>0.4083795</v>
+        <v>3.9633882</v>
       </c>
       <c r="L88" s="21" t="n">
-        <v>7.56174932272778</v>
+        <v>5.20947381148941</v>
       </c>
       <c r="M88" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N88" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N88" s="21" t="n">
+        <v>16.80549850408138</v>
       </c>
       <c r="O88" s="21" t="n">
-        <v>5.26038476371263</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="P88" s="20" t="n">
-        <v>-0.8495431924900106</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q88" s="21" t="n">
-        <v>-46.17305967367813</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S88" s="20" t="n">
-        <v>0.8590900293205138</v>
+        <v>0.3385873824755823</v>
       </c>
       <c r="T88" s="15" t="inlineStr">
         <is>
-          <t>Export Sales (93%)</t>
+          <t>Defense Engineering Se (45%)</t>
         </is>
       </c>
       <c r="U88" s="17" t="inlineStr">
         <is>
-          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
         </is>
       </c>
       <c r="V88" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W88" s="17" t="inlineStr">
         <is>
-          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
         </is>
       </c>
       <c r="X88" s="15" t="inlineStr">
         <is>
-          <t>Retail Sales +100%</t>
+          <t>Marine Technology Bu +185%</t>
         </is>
       </c>
     </row>
@@ -52860,46 +52848,48 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>Phoenix New Media Limited</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F89" s="18" t="n">
-        <v>110777000</v>
+        <v>17775948</v>
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H89" s="20" t="n">
-        <v>11.493</v>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I89" s="20" t="n">
-        <v>22.837208</v>
+        <v>3.986052175133725</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>1.8031582</v>
+        <v>21.9582250317025</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>3.9633882</v>
+        <v>0.145113940095489</v>
       </c>
       <c r="L89" s="21" t="n">
-        <v>5.20947381148941</v>
+        <v>-0.32072677140719</v>
       </c>
       <c r="M89" s="22" t="inlineStr">
         <is>
@@ -52907,44 +52897,42 @@
         </is>
       </c>
       <c r="N89" s="21" t="n">
-        <v>16.80549850408138</v>
+        <v>-8.02638700256313</v>
       </c>
       <c r="O89" s="21" t="n">
-        <v>24.49495025980879</v>
-      </c>
-      <c r="P89" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>-1.79463043292417</v>
+      </c>
+      <c r="P89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q89" s="21" t="n">
-        <v>-0.7799999999999999</v>
+        <v>-36.75</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S89" s="20" t="n">
-        <v>0.3385873824755823</v>
+        <v>0.682948135046668</v>
       </c>
       <c r="T89" s="15" t="inlineStr">
         <is>
-          <t>Defense Engineering Se (45%)</t>
+          <t>Net Advertising Servic (80%)</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+          <t>Net Advertising Services 80%; Paid Services 20%</t>
         </is>
       </c>
       <c r="V89" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W89" s="17" t="inlineStr">
-        <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W89" s="17" t="n"/>
       <c r="X89" s="15" t="inlineStr">
         <is>
-          <t>Marine Technology Bu +185%</t>
+          <t>Paid Services +107%</t>
         </is>
       </c>
     </row>
@@ -52954,26 +52942,26 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>FENG</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Phoenix New Media Limited</t>
+          <t>Schrodinger, Inc.</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F90" s="18" t="n">
-        <v>17775948</v>
+        <v>1406345856</v>
       </c>
       <c r="G90" s="19" t="inlineStr">
         <is>
@@ -52985,28 +52973,32 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I90" s="20" t="n">
-        <v>3.986052175133725</v>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J90" s="20" t="n">
-        <v>21.9582250317025</v>
+        <v>4.1648207</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>0.145113940095489</v>
+        <v>5.429173</v>
       </c>
       <c r="L90" s="21" t="n">
-        <v>-0.32072677140719</v>
+        <v>-8.66829141064739</v>
       </c>
       <c r="M90" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N90" s="21" t="n">
-        <v>-8.02638700256313</v>
+      <c r="N90" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>-1.79463043292417</v>
+        <v>-84.61893927057798</v>
       </c>
       <c r="P90" s="22" t="inlineStr">
         <is>
@@ -53014,31 +53006,35 @@
         </is>
       </c>
       <c r="Q90" s="21" t="n">
-        <v>-36.75</v>
+        <v>-4.52</v>
       </c>
       <c r="R90" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="20" t="n">
-        <v>0.682948135046668</v>
+        <v>0.6564595481920475</v>
       </c>
       <c r="T90" s="15" t="inlineStr">
         <is>
-          <t>Net Advertising Servic (80%)</t>
+          <t>Software (78%)</t>
         </is>
       </c>
       <c r="U90" s="17" t="inlineStr">
         <is>
-          <t>Net Advertising Services 80%; Paid Services 20%</t>
+          <t>Software 78%; Drug Discovery 22%</t>
         </is>
       </c>
       <c r="V90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W90" s="17" t="inlineStr">
+        <is>
+          <t>US 60%; EMEA 29%; APAC 10%</t>
+        </is>
+      </c>
       <c r="X90" s="15" t="inlineStr">
         <is>
-          <t>Paid Services +107%</t>
+          <t>Drug Discovery +107%</t>
         </is>
       </c>
     </row>
@@ -53048,12 +53044,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Schrodinger, Inc.</t>
+          <t>Jefferies Financial Group Inc.</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
@@ -53063,84 +53059,74 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F91" s="18" t="n">
-        <v>1406345856</v>
+        <v>10968930304</v>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H91" s="20" t="n">
+        <v>-37.43331715008421</v>
+      </c>
+      <c r="I91" s="20" t="n">
+        <v>28.20940192498952</v>
       </c>
       <c r="J91" s="20" t="n">
-        <v>4.1648207</v>
+        <v>1.0380536</v>
       </c>
       <c r="K91" s="20" t="n">
-        <v>5.429173</v>
+        <v>2.030307</v>
       </c>
       <c r="L91" s="21" t="n">
-        <v>-8.66829141064739</v>
-      </c>
-      <c r="M91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-76.8279991042285</v>
+      </c>
+      <c r="M91" s="21" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N91" s="21" t="n">
+        <v>-0.21791453369172</v>
       </c>
       <c r="O91" s="21" t="n">
-        <v>-84.61893927057798</v>
-      </c>
-      <c r="P91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.51745776158655</v>
+      </c>
+      <c r="P91" s="20" t="n">
+        <v>-80.28756909079929</v>
       </c>
       <c r="Q91" s="21" t="n">
-        <v>-4.52</v>
+        <v>7.7</v>
       </c>
       <c r="R91" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>0.6564595481920475</v>
+        <v>0.8308945641579533</v>
       </c>
       <c r="T91" s="15" t="inlineStr">
         <is>
-          <t>Software (78%)</t>
+          <t>Investment Banking And (91%)</t>
         </is>
       </c>
       <c r="U91" s="17" t="inlineStr">
         <is>
-          <t>Software 78%; Drug Discovery 22%</t>
+          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
         </is>
       </c>
       <c r="V91" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W91" s="17" t="inlineStr">
         <is>
-          <t>US 60%; EMEA 29%; APAC 10%</t>
+          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
         </is>
       </c>
       <c r="X91" s="15" t="inlineStr">
         <is>
-          <t>Drug Discovery +107%</t>
+          <t>Investment Banking A +123%</t>
         </is>
       </c>
     </row>
@@ -53150,12 +53136,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>ANNA</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc.</t>
+          <t>AleAnna Inc. Class A Common St</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -53165,74 +53151,72 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>10968930304</v>
-      </c>
-      <c r="G92" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>142061808</v>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>-37.43331715008421</v>
+        <v>8.568</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>28.20940192498952</v>
+        <v>17.35</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>1.0380536</v>
+        <v>3.5121458</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>2.030307</v>
+        <v>3.5587192</v>
       </c>
       <c r="L92" s="21" t="n">
-        <v>-76.8279991042285</v>
-      </c>
-      <c r="M92" s="21" t="n">
-        <v>3.26</v>
+        <v>13.02901563263312</v>
+      </c>
+      <c r="M92" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N92" s="21" t="n">
-        <v>-0.21791453369172</v>
+        <v>1.46144795620644</v>
       </c>
       <c r="O92" s="21" t="n">
-        <v>5.51745776158655</v>
+        <v>39.48335699937504</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>-80.28756909079929</v>
+        <v>-1.974742069364569</v>
       </c>
       <c r="Q92" s="21" t="n">
-        <v>7.7</v>
+        <v>-7.69</v>
       </c>
       <c r="R92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S92" s="20" t="n">
-        <v>0.8308945641579533</v>
+        <v>0.8097190789385638</v>
       </c>
       <c r="T92" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking And (91%)</t>
+          <t>Conventional (89%)</t>
         </is>
       </c>
       <c r="U92" s="17" t="inlineStr">
         <is>
-          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
+          <t>Conventional 89%; Renewable 11%</t>
         </is>
       </c>
       <c r="V92" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W92" s="17" t="inlineStr">
-        <is>
-          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W92" s="17" t="n"/>
       <c r="X92" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking A +123%</t>
+          <t>Conventional +186%</t>
         </is>
       </c>
     </row>
@@ -53242,12 +53226,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>ANNA</t>
+          <t>LVWR</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>AleAnna Inc. Class A Common St</t>
+          <t>LiveWire Group Inc. Common Sto</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -53257,72 +53241,84 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>142061808</v>
-      </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="n">
-        <v>8.568</v>
-      </c>
-      <c r="I93" s="20" t="n">
-        <v>17.35</v>
+        <v>232116080</v>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J93" s="20" t="n">
-        <v>3.5121458</v>
+        <v>19.48276</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>3.5587192</v>
+        <v>7.4191675</v>
       </c>
       <c r="L93" s="21" t="n">
-        <v>13.02901563263312</v>
+        <v>-21.59336790483196</v>
       </c>
       <c r="M93" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N93" s="21" t="n">
-        <v>1.46144795620644</v>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>39.48335699937504</v>
-      </c>
-      <c r="P93" s="20" t="n">
-        <v>-1.974742069364569</v>
+        <v>-207.6711628204309</v>
+      </c>
+      <c r="P93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q93" s="21" t="n">
-        <v>-7.69</v>
+        <v>-76.64</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>0.8097190789385638</v>
+        <v>0.4547555777310531</v>
       </c>
       <c r="T93" s="15" t="inlineStr">
         <is>
-          <t>Conventional (89%)</t>
+          <t>STACYC (62%)</t>
         </is>
       </c>
       <c r="U93" s="17" t="inlineStr">
         <is>
-          <t>Conventional 89%; Renewable 11%</t>
+          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
         </is>
       </c>
       <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W93" s="17" t="inlineStr">
+        <is>
+          <t>US 74%; Non Us 24%; AT 2%</t>
+        </is>
+      </c>
       <c r="X93" s="15" t="inlineStr">
         <is>
-          <t>Conventional +186%</t>
+          <t>Electric Motorcycle +333%</t>
         </is>
       </c>
     </row>
@@ -53332,12 +53328,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>LVWR</t>
+          <t>KTB</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>LiveWire Group Inc. Common Sto</t>
+          <t>Kontoor Brands, Inc.</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -53351,80 +53347,70 @@
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>232116080</v>
+        <v>3615883776</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H94" s="20" t="n">
+        <v>11.55529127502649</v>
+      </c>
+      <c r="I94" s="20" t="n">
+        <v>13.5852165</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>19.48276</v>
+        <v>5.8455563</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>7.4191675</v>
+        <v>1.0528328</v>
       </c>
       <c r="L94" s="21" t="n">
-        <v>-21.59336790483196</v>
-      </c>
-      <c r="M94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.52193541631924</v>
+      </c>
+      <c r="M94" s="21" t="n">
+        <v>2.91957418972506</v>
+      </c>
+      <c r="N94" s="21" t="n">
+        <v>17.92240674479327</v>
       </c>
       <c r="O94" s="21" t="n">
-        <v>-207.6711628204309</v>
-      </c>
-      <c r="P94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>13.30013869457824</v>
+      </c>
+      <c r="P94" s="20" t="n">
+        <v>2.601238735236491</v>
       </c>
       <c r="Q94" s="21" t="n">
-        <v>-76.64</v>
+        <v>-7.049999999999999</v>
       </c>
       <c r="R94" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>0.4547555777310531</v>
+        <v>0.4547588013008751</v>
       </c>
       <c r="T94" s="15" t="inlineStr">
         <is>
-          <t>STACYC (62%)</t>
+          <t>Wrangler (61%)</t>
         </is>
       </c>
       <c r="U94" s="17" t="inlineStr">
         <is>
-          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
+          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
         </is>
       </c>
       <c r="V94" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W94" s="17" t="inlineStr">
         <is>
-          <t>US 74%; Non Us 24%; AT 2%</t>
+          <t>US 73%; Non Us 27%</t>
         </is>
       </c>
       <c r="X94" s="15" t="inlineStr">
         <is>
-          <t>Electric Motorcycle +333%</t>
+          <t>Helly Hansen +300%</t>
         </is>
       </c>
     </row>
@@ -53434,12 +53420,12 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>KTB</t>
+          <t>PED</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Kontoor Brands, Inc.</t>
+          <t>PEDEVCO Corp.</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
@@ -53449,11 +53435,11 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>3615883776</v>
+        <v>192468336</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
@@ -53461,62 +53447,62 @@
         </is>
       </c>
       <c r="H95" s="20" t="n">
-        <v>11.55529127502649</v>
-      </c>
-      <c r="I95" s="20" t="n">
-        <v>13.5852165</v>
+        <v>4.59</v>
+      </c>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J95" s="20" t="n">
-        <v>5.8455563</v>
+        <v>0.96199834</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>1.0528328</v>
+        <v>1.6538206</v>
       </c>
       <c r="L95" s="21" t="n">
-        <v>10.52193541631924</v>
-      </c>
-      <c r="M95" s="21" t="n">
-        <v>2.91957418972506</v>
+        <v>16.30471233572627</v>
+      </c>
+      <c r="M95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N95" s="21" t="n">
-        <v>17.92240674479327</v>
+        <v>2.16353455637511</v>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.30013869457824</v>
+        <v>49.94500678822457</v>
       </c>
       <c r="P95" s="20" t="n">
-        <v>2.601238735236491</v>
+        <v>1.332008602150538</v>
       </c>
       <c r="Q95" s="21" t="n">
-        <v>-7.049999999999999</v>
+        <v>18.91</v>
       </c>
       <c r="R95" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S95" s="20" t="n">
-        <v>0.4547588013008751</v>
+        <v>0.7805028355388554</v>
       </c>
       <c r="T95" s="15" t="inlineStr">
         <is>
-          <t>Wrangler (61%)</t>
+          <t>Oil Sales (88%)</t>
         </is>
       </c>
       <c r="U95" s="17" t="inlineStr">
         <is>
-          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
         </is>
       </c>
       <c r="V95" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W95" s="17" t="inlineStr">
-        <is>
-          <t>US 73%; Non Us 27%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W95" s="17" t="n"/>
       <c r="X95" s="15" t="inlineStr">
         <is>
-          <t>Helly Hansen +300%</t>
+          <t>Natural Gas Liquids  +465%</t>
         </is>
       </c>
     </row>
@@ -53526,12 +53512,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>PED</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>PEDEVCO Corp.</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -53541,11 +53527,11 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F96" s="18" t="n">
-        <v>192468336</v>
+        <v>1103880126464</v>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
@@ -53553,62 +53539,62 @@
         </is>
       </c>
       <c r="H96" s="20" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I96" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>15.893</v>
+      </c>
+      <c r="I96" s="20" t="n">
+        <v>23.255056</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.96199834</v>
+        <v>10.955669</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1.6538206</v>
+        <v>12.228107</v>
       </c>
       <c r="L96" s="21" t="n">
-        <v>16.30471233572627</v>
-      </c>
-      <c r="M96" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.27953325914988</v>
+      </c>
+      <c r="M96" s="21" t="n">
+        <v>0.05</v>
       </c>
       <c r="N96" s="21" t="n">
-        <v>2.16353455637511</v>
+        <v>38.68963277836816</v>
       </c>
       <c r="O96" s="21" t="n">
-        <v>49.94500678822457</v>
+        <v>63.47412363053029</v>
       </c>
       <c r="P96" s="20" t="n">
-        <v>1.332008602150538</v>
+        <v>-0.1351809304997128</v>
       </c>
       <c r="Q96" s="21" t="n">
-        <v>18.91</v>
+        <v>354.75</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S96" s="20" t="n">
-        <v>0.7805028355388554</v>
+        <v>0.2853460159862896</v>
       </c>
       <c r="T96" s="15" t="inlineStr">
         <is>
-          <t>Oil Sales (88%)</t>
+          <t>CMBU (36%)</t>
         </is>
       </c>
       <c r="U96" s="17" t="inlineStr">
         <is>
-          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
+          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
         </is>
       </c>
       <c r="V96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="W96" s="17" t="inlineStr">
+        <is>
+          <t>US 65%; TW 15%; CN 7%</t>
+        </is>
+      </c>
       <c r="X96" s="15" t="inlineStr">
         <is>
-          <t>Natural Gas Liquids  +465%</t>
+          <t>AEBU +311%</t>
         </is>
       </c>
     </row>
@@ -53618,12 +53604,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>EVC</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Entravision Communications Cor</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
@@ -53633,11 +53619,11 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F97" s="18" t="n">
-        <v>1103880126464</v>
+        <v>800139584</v>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
@@ -53645,62 +53631,62 @@
         </is>
       </c>
       <c r="H97" s="20" t="n">
-        <v>15.893</v>
+        <v>27.70027633395354</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>23.255056</v>
+        <v>191.3631685765692</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>10.955669</v>
+        <v>9.569535999999999</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>12.228107</v>
+        <v>1.568326092197567</v>
       </c>
       <c r="L97" s="21" t="n">
-        <v>2.27953325914988</v>
+        <v>8.44176513325125</v>
       </c>
       <c r="M97" s="21" t="n">
-        <v>0.05</v>
+        <v>2.57525386044693</v>
       </c>
       <c r="N97" s="21" t="n">
-        <v>38.68963277836816</v>
+        <v>-26.42668897457025</v>
       </c>
       <c r="O97" s="21" t="n">
-        <v>63.47412363053029</v>
+        <v>6.53133066895079</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>-0.1351809304997128</v>
+        <v>2.821679370986135</v>
       </c>
       <c r="Q97" s="21" t="n">
-        <v>354.75</v>
+        <v>322.51</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S97" s="20" t="n">
-        <v>0.2853460159862896</v>
+        <v>0.5221821576458947</v>
       </c>
       <c r="T97" s="15" t="inlineStr">
         <is>
-          <t>CMBU (36%)</t>
+          <t>Advertising Technology (61%)</t>
         </is>
       </c>
       <c r="U97" s="17" t="inlineStr">
         <is>
-          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
+          <t>Advertising Technology And Services 61%; Media 39%</t>
         </is>
       </c>
       <c r="V97" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W97" s="17" t="inlineStr">
         <is>
-          <t>US 65%; TW 15%; CN 7%</t>
+          <t>US 58%; Non Us 42%</t>
         </is>
       </c>
       <c r="X97" s="15" t="inlineStr">
         <is>
-          <t>AEBU +311%</t>
+          <t>Advertising Technolo +230%</t>
         </is>
       </c>
     </row>
@@ -53710,12 +53696,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>EVC</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Entravision Communications Cor</t>
+          <t>Compass, Inc.</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -53725,11 +53711,11 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F98" s="18" t="n">
-        <v>800139584</v>
+        <v>7776240128</v>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
@@ -53737,62 +53723,62 @@
         </is>
       </c>
       <c r="H98" s="20" t="n">
-        <v>27.70027633395354</v>
+        <v>117.5497871186441</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>191.3631685765692</v>
+        <v>115.2035574518518</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>9.569535999999999</v>
+        <v>2.5613148</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>1.568326092197567</v>
+        <v>0.9762032850435612</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>8.44176513325125</v>
-      </c>
-      <c r="M98" s="21" t="n">
-        <v>2.57525386044693</v>
+        <v>1.5004325303195</v>
+      </c>
+      <c r="M98" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-26.42668897457025</v>
+        <v>-6.802410518626729</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>6.53133066895079</v>
-      </c>
-      <c r="P98" s="20" t="n">
-        <v>2.821679370986135</v>
+        <v>1.1850661578247</v>
+      </c>
+      <c r="P98" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q98" s="21" t="n">
-        <v>322.51</v>
+        <v>44.23</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S98" s="20" t="n">
-        <v>0.5221821576458947</v>
+        <v>0.8491346718272323</v>
       </c>
       <c r="T98" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technology (61%)</t>
+          <t>Brokerage (92%)</t>
         </is>
       </c>
       <c r="U98" s="17" t="inlineStr">
         <is>
-          <t>Advertising Technology And Services 61%; Media 39%</t>
+          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
         </is>
       </c>
       <c r="V98" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W98" s="17" t="inlineStr">
-        <is>
-          <t>US 58%; Non Us 42%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W98" s="17" t="n"/>
       <c r="X98" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technolo +230%</t>
+          <t>Brokerage +97%</t>
         </is>
       </c>
     </row>
@@ -53802,12 +53788,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Compass, Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
@@ -53817,11 +53803,11 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F99" s="18" t="n">
-        <v>7776240128</v>
+        <v>417350713344</v>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
@@ -53829,53 +53815,49 @@
         </is>
       </c>
       <c r="H99" s="20" t="n">
-        <v>117.5497871186441</v>
+        <v>8.913</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>115.2035574518518</v>
+        <v>20.5764</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>2.5613148</v>
+        <v>2.1979337</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>0.9762032850435612</v>
+        <v>1.9932312</v>
       </c>
       <c r="L99" s="21" t="n">
-        <v>1.5004325303195</v>
-      </c>
-      <c r="M99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.60132683312082</v>
+      </c>
+      <c r="M99" s="21" t="n">
+        <v>4.16</v>
       </c>
       <c r="N99" s="21" t="n">
-        <v>-6.802410518626729</v>
+        <v>8.69285484505129</v>
       </c>
       <c r="O99" s="21" t="n">
-        <v>1.1850661578247</v>
-      </c>
-      <c r="P99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.36304851872374</v>
+      </c>
+      <c r="P99" s="20" t="n">
+        <v>0.9647582391147462</v>
       </c>
       <c r="Q99" s="21" t="n">
-        <v>44.23</v>
+        <v>37.47</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S99" s="20" t="n">
-        <v>0.8491346718272323</v>
+        <v>0.9067367242961308</v>
       </c>
       <c r="T99" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (92%)</t>
+          <t>Upstream (95%)</t>
         </is>
       </c>
       <c r="U99" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
+          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
         </is>
       </c>
       <c r="V99" s="18" t="n">
@@ -53884,7 +53866,7 @@
       <c r="W99" s="17" t="n"/>
       <c r="X99" s="15" t="inlineStr">
         <is>
-          <t>Brokerage +97%</t>
+          <t>Upstream +298%</t>
         </is>
       </c>
     </row>
@@ -53894,12 +53876,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Northrop Grumman Corp.</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -53909,11 +53891,11 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F100" s="18" t="n">
-        <v>417350713344</v>
+        <v>73723609088</v>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
@@ -53921,58 +53903,62 @@
         </is>
       </c>
       <c r="H100" s="20" t="n">
-        <v>8.913</v>
+        <v>15.61118953096877</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>20.5764</v>
+        <v>16.391346</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>2.1979337</v>
+        <v>4.122315</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1.9932312</v>
+        <v>1.7188195</v>
       </c>
       <c r="L100" s="21" t="n">
-        <v>6.60132683312082</v>
+        <v>4.9836238568399</v>
       </c>
       <c r="M100" s="21" t="n">
-        <v>4.16</v>
+        <v>1.505494379293</v>
       </c>
       <c r="N100" s="21" t="n">
-        <v>8.69285484505129</v>
+        <v>14.00609392594555</v>
       </c>
       <c r="O100" s="21" t="n">
-        <v>22.36304851872374</v>
+        <v>13.37597658555007</v>
       </c>
       <c r="P100" s="20" t="n">
-        <v>0.9647582391147462</v>
+        <v>2.307923063349215</v>
       </c>
       <c r="Q100" s="21" t="n">
-        <v>37.47</v>
+        <v>-10.3</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S100" s="20" t="n">
-        <v>0.9067367242961308</v>
+        <v>0.4182092579820682</v>
       </c>
       <c r="T100" s="15" t="inlineStr">
         <is>
-          <t>Upstream (95%)</t>
+          <t>Mission Systems (58%)</t>
         </is>
       </c>
       <c r="U100" s="17" t="inlineStr">
         <is>
-          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
+          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
         </is>
       </c>
       <c r="V100" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W100" s="17" t="inlineStr">
+        <is>
+          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
+        </is>
+      </c>
       <c r="X100" s="15" t="inlineStr">
         <is>
-          <t>Upstream +298%</t>
+          <t>Aeronautics Systems +130%</t>
         </is>
       </c>
     </row>
@@ -53982,12 +53968,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>JBI</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp.</t>
+          <t>Janus International Group, Inc</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
@@ -54001,7 +53987,7 @@
         </is>
       </c>
       <c r="F101" s="18" t="n">
-        <v>73723609088</v>
+        <v>623511616</v>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
@@ -54009,62 +53995,64 @@
         </is>
       </c>
       <c r="H101" s="20" t="n">
-        <v>15.61118953096877</v>
+        <v>7.664</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>16.391346</v>
+        <v>19.041668</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>4.122315</v>
+        <v>1.0901718</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>1.7188195</v>
+        <v>0.69140786</v>
       </c>
       <c r="L101" s="21" t="n">
-        <v>4.9836238568399</v>
-      </c>
-      <c r="M101" s="21" t="n">
-        <v>1.505494379293</v>
+        <v>11.5960907053962</v>
+      </c>
+      <c r="M101" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N101" s="21" t="n">
-        <v>14.00609392594555</v>
+        <v>10.43425814234016</v>
       </c>
       <c r="O101" s="21" t="n">
-        <v>13.37597658555007</v>
+        <v>16.54553713377242</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>2.307923063349215</v>
+        <v>2.983527796842828</v>
       </c>
       <c r="Q101" s="21" t="n">
-        <v>-10.3</v>
+        <v>-46.98</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S101" s="20" t="n">
-        <v>0.4182092579820682</v>
+        <v>0.6354742392804635</v>
       </c>
       <c r="T101" s="15" t="inlineStr">
         <is>
-          <t>Mission Systems (58%)</t>
+          <t>Janus North America (76%)</t>
         </is>
       </c>
       <c r="U101" s="17" t="inlineStr">
         <is>
-          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
+          <t>Janus North America 76%; Janus International 24%</t>
         </is>
       </c>
       <c r="V101" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W101" s="17" t="inlineStr">
         <is>
-          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
+          <t>US 88%; Non Us 12%</t>
         </is>
       </c>
       <c r="X101" s="15" t="inlineStr">
         <is>
-          <t>Aeronautics Systems +130%</t>
+          <t>Janus International +300%</t>
         </is>
       </c>
     </row>
@@ -54074,12 +54062,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>JBI</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Janus International Group, Inc</t>
+          <t>Flotek Industries, Inc.</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -54089,11 +54077,11 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F102" s="18" t="n">
-        <v>623511616</v>
+        <v>993164160</v>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
@@ -54101,19 +54089,19 @@
         </is>
       </c>
       <c r="H102" s="20" t="n">
-        <v>7.664</v>
+        <v>25.626</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>19.041668</v>
+        <v>27.69697</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>1.0901718</v>
+        <v>7.6763716</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.69140786</v>
+        <v>3.390009</v>
       </c>
       <c r="L102" s="21" t="n">
-        <v>11.5960907053962</v>
+        <v>-0.34082822017504</v>
       </c>
       <c r="M102" s="22" t="inlineStr">
         <is>
@@ -54121,44 +54109,44 @@
         </is>
       </c>
       <c r="N102" s="21" t="n">
-        <v>10.43425814234016</v>
+        <v>16.13992919089226</v>
       </c>
       <c r="O102" s="21" t="n">
-        <v>16.54553713377242</v>
+        <v>17.18227107585707</v>
       </c>
       <c r="P102" s="20" t="n">
-        <v>2.983527796842828</v>
+        <v>0.8771800721171535</v>
       </c>
       <c r="Q102" s="21" t="n">
-        <v>-46.98</v>
+        <v>35.99</v>
       </c>
       <c r="R102" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S102" s="20" t="n">
-        <v>0.6354742392804635</v>
+        <v>0.7993939775957156</v>
       </c>
       <c r="T102" s="15" t="inlineStr">
         <is>
-          <t>Janus North America (76%)</t>
+          <t>Chemistry Technologies (89%)</t>
         </is>
       </c>
       <c r="U102" s="17" t="inlineStr">
         <is>
-          <t>Janus North America 76%; Janus International 24%</t>
+          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
         </is>
       </c>
       <c r="V102" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W102" s="17" t="inlineStr">
         <is>
-          <t>US 88%; Non Us 12%</t>
+          <t>US 95%; AE 4%; Non Us 1%</t>
         </is>
       </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
-          <t>Janus International +300%</t>
+          <t>Data Analytics +115%</t>
         </is>
       </c>
     </row>
@@ -54168,12 +54156,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Flotek Industries, Inc.</t>
+          <t>Royal Gold, Inc.</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
@@ -54183,11 +54171,11 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F103" s="18" t="n">
-        <v>993164160</v>
+        <v>21519179776</v>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
@@ -54195,64 +54183,62 @@
         </is>
       </c>
       <c r="H103" s="20" t="n">
-        <v>25.626</v>
+        <v>17.093</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>27.69697</v>
+        <v>29.059496</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>7.6763716</v>
+        <v>2.8344717</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>3.390009</v>
+        <v>14.012775</v>
       </c>
       <c r="L103" s="21" t="n">
-        <v>-0.34082822017504</v>
-      </c>
-      <c r="M103" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-1.30764681062022</v>
+      </c>
+      <c r="M103" s="21" t="n">
+        <v>0.91</v>
       </c>
       <c r="N103" s="21" t="n">
-        <v>16.13992919089226</v>
+        <v>10.262897771322</v>
       </c>
       <c r="O103" s="21" t="n">
-        <v>17.18227107585707</v>
+        <v>79.09251477040698</v>
       </c>
       <c r="P103" s="20" t="n">
-        <v>0.8771800721171535</v>
+        <v>0.3499720252373015</v>
       </c>
       <c r="Q103" s="21" t="n">
-        <v>35.99</v>
+        <v>50.91</v>
       </c>
       <c r="R103" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S103" s="20" t="n">
-        <v>0.7993939775957156</v>
+        <v>0.5688010724435794</v>
       </c>
       <c r="T103" s="15" t="inlineStr">
         <is>
-          <t>Chemistry Technologies (89%)</t>
+          <t>Royalty Interest (69%)</t>
         </is>
       </c>
       <c r="U103" s="17" t="inlineStr">
         <is>
-          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
+          <t>Royalty Interest 69%; Stream Interest 31%</t>
         </is>
       </c>
       <c r="V103" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W103" s="17" t="inlineStr">
         <is>
-          <t>US 95%; AE 4%; Non Us 1%</t>
+          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
         </is>
       </c>
       <c r="X103" s="15" t="inlineStr">
         <is>
-          <t>Data Analytics +115%</t>
+          <t>Stream Interest +133%</t>
         </is>
       </c>
     </row>
@@ -54262,12 +54248,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Royal Gold, Inc.</t>
+          <t>Riot Blockchain, Inc.</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -54277,74 +54263,76 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F104" s="18" t="n">
-        <v>21519179776</v>
+        <v>7861675008</v>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H104" s="20" t="n">
-        <v>17.093</v>
-      </c>
-      <c r="I104" s="20" t="n">
-        <v>29.059496</v>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J104" s="20" t="n">
-        <v>2.8344717</v>
+        <v>3.612069</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>14.012775</v>
+        <v>11.655318</v>
       </c>
       <c r="L104" s="21" t="n">
-        <v>-1.30764681062022</v>
+        <v>-6.33617127278794</v>
       </c>
       <c r="M104" s="21" t="n">
-        <v>0.91</v>
+        <v>0.10325461151742</v>
       </c>
       <c r="N104" s="21" t="n">
-        <v>10.262897771322</v>
+        <v>-14.43474531538664</v>
       </c>
       <c r="O104" s="21" t="n">
-        <v>79.09251477040698</v>
-      </c>
-      <c r="P104" s="20" t="n">
-        <v>0.3499720252373015</v>
+        <v>-137.6062161413327</v>
+      </c>
+      <c r="P104" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q104" s="21" t="n">
-        <v>50.91</v>
+        <v>10.21</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S104" s="20" t="n">
-        <v>0.5688010724435794</v>
+        <v>0.4395096928547909</v>
       </c>
       <c r="T104" s="15" t="inlineStr">
         <is>
-          <t>Royalty Interest (69%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
         <is>
-          <t>Royalty Interest 69%; Stream Interest 31%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
         </is>
       </c>
       <c r="V104" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W104" s="17" t="inlineStr">
-        <is>
-          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W104" s="17" t="n"/>
       <c r="X104" s="15" t="inlineStr">
         <is>
-          <t>Stream Interest +133%</t>
+          <t>Engineering +196%</t>
         </is>
       </c>
     </row>
@@ -54354,12 +54342,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Riot Blockchain, Inc.</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
@@ -54373,72 +54361,70 @@
         </is>
       </c>
       <c r="F105" s="18" t="n">
-        <v>7861675008</v>
+        <v>76769263616</v>
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H105" s="20" t="n">
+        <v>29.95255477105907</v>
+      </c>
+      <c r="I105" s="20" t="n">
+        <v>36.240623</v>
       </c>
       <c r="J105" s="20" t="n">
-        <v>3.612069</v>
+        <v>28.732115</v>
       </c>
       <c r="K105" s="20" t="n">
-        <v>11.655318</v>
+        <v>6.2735367</v>
       </c>
       <c r="L105" s="21" t="n">
-        <v>-6.33617127278794</v>
+        <v>3.45600557054743</v>
       </c>
       <c r="M105" s="21" t="n">
-        <v>0.10325461151742</v>
+        <v>1.11367051765181</v>
       </c>
       <c r="N105" s="21" t="n">
-        <v>-14.43474531538664</v>
+        <v>24.18337569424833</v>
       </c>
       <c r="O105" s="21" t="n">
-        <v>-137.6062161413327</v>
-      </c>
-      <c r="P105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.10684192787327</v>
+      </c>
+      <c r="P105" s="20" t="n">
+        <v>2.823837818944425</v>
       </c>
       <c r="Q105" s="21" t="n">
-        <v>10.21</v>
+        <v>16.12</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S105" s="20" t="n">
-        <v>0.4395096928547909</v>
+        <v>0.5307180948206589</v>
       </c>
       <c r="T105" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Product And Systems In (62%)</t>
         </is>
       </c>
       <c r="U105" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
+          <t>Product And Systems Integration 62%; Services And Software 38%</t>
         </is>
       </c>
       <c r="V105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="17" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="W105" s="17" t="inlineStr">
+        <is>
+          <t>North America 36%; US 34%; International 14%</t>
+        </is>
+      </c>
       <c r="X105" s="15" t="inlineStr">
         <is>
-          <t>Engineering +196%</t>
+          <t>Product And Systems  +176%</t>
         </is>
       </c>
     </row>
@@ -54448,12 +54434,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Firy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
@@ -54467,70 +54453,80 @@
         </is>
       </c>
       <c r="F106" s="18" t="n">
-        <v>76769263616</v>
+        <v>156948000</v>
       </c>
       <c r="G106" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H106" s="20" t="n">
-        <v>29.95255477105907</v>
-      </c>
-      <c r="I106" s="20" t="n">
-        <v>36.240623</v>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J106" s="20" t="n">
-        <v>28.732115</v>
+        <v>1.858076431311266</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>6.2735367</v>
+        <v>1.3359323</v>
       </c>
       <c r="L106" s="21" t="n">
-        <v>3.45600557054743</v>
-      </c>
-      <c r="M106" s="21" t="n">
-        <v>1.11367051765181</v>
-      </c>
-      <c r="N106" s="21" t="n">
-        <v>24.18337569424833</v>
+        <v>-42.19957624057978</v>
+      </c>
+      <c r="M106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O106" s="21" t="n">
-        <v>24.10684192787327</v>
-      </c>
-      <c r="P106" s="20" t="n">
-        <v>2.823837818944425</v>
+        <v>-60.47052925589057</v>
+      </c>
+      <c r="P106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q106" s="21" t="n">
-        <v>16.12</v>
+        <v>51.65</v>
       </c>
       <c r="R106" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S106" s="20" t="n">
-        <v>0.5307180948206589</v>
+        <v>0.619776729861528</v>
       </c>
       <c r="T106" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems In (62%)</t>
+          <t>Skillz (74%)</t>
         </is>
       </c>
       <c r="U106" s="17" t="inlineStr">
         <is>
-          <t>Product And Systems Integration 62%; Services And Software 38%</t>
+          <t>Skillz 74%; RZR 26%</t>
         </is>
       </c>
       <c r="V106" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W106" s="17" t="inlineStr">
         <is>
-          <t>North America 36%; US 34%; International 14%</t>
+          <t>US 76%; Non Us 6%; CY 4%</t>
         </is>
       </c>
       <c r="X106" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems  +176%</t>
+          <t>RZR +146%</t>
         </is>
       </c>
     </row>
@@ -54540,12 +54536,12 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Firy Inc. Class A Common Stock</t>
+          <t>Energy Transfer Lp</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
@@ -54555,84 +54551,70 @@
       </c>
       <c r="E107" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F107" s="18" t="n">
-        <v>156948000</v>
+        <v>74822901760</v>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H107" s="20" t="n">
+        <v>9.494999999999999</v>
+      </c>
+      <c r="I107" s="20" t="n">
+        <v>14.883561</v>
       </c>
       <c r="J107" s="20" t="n">
-        <v>1.858076431311266</v>
+        <v>1.504371026800973</v>
       </c>
       <c r="K107" s="20" t="n">
-        <v>1.3359323</v>
+        <v>0.6968113</v>
       </c>
       <c r="L107" s="21" t="n">
-        <v>-42.19957624057978</v>
-      </c>
-      <c r="M107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.04975512768092</v>
+      </c>
+      <c r="M107" s="21" t="n">
+        <v>6.959999999999999</v>
+      </c>
+      <c r="N107" s="21" t="n">
+        <v>8.4099490357427</v>
       </c>
       <c r="O107" s="21" t="n">
-        <v>-60.47052925589057</v>
-      </c>
-      <c r="P107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>17.85263732142248</v>
+      </c>
+      <c r="P107" s="20" t="n">
+        <v>4.353514132925898</v>
       </c>
       <c r="Q107" s="21" t="n">
-        <v>51.65</v>
+        <v>37.32</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S107" s="20" t="n">
-        <v>0.619776729861528</v>
+        <v>0.2291888064107961</v>
       </c>
       <c r="T107" s="15" t="inlineStr">
         <is>
-          <t>Skillz (74%)</t>
+          <t>Crudeoiltransportation (27%)</t>
         </is>
       </c>
       <c r="U107" s="17" t="inlineStr">
         <is>
-          <t>Skillz 74%; RZR 26%</t>
+          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
         </is>
       </c>
       <c r="V107" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W107" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; Non Us 6%; CY 4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W107" s="17" t="n"/>
       <c r="X107" s="15" t="inlineStr">
         <is>
-          <t>RZR +146%</t>
+          <t>Investment In Sunoco +165%</t>
         </is>
       </c>
     </row>
@@ -54642,12 +54624,12 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Energy Transfer Lp</t>
+          <t>BWX Technologies, Inc.</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
@@ -54657,11 +54639,11 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F108" s="18" t="n">
-        <v>74822901760</v>
+        <v>13971436544</v>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
@@ -54669,58 +54651,62 @@
         </is>
       </c>
       <c r="H108" s="20" t="n">
-        <v>9.494999999999999</v>
+        <v>32.283</v>
       </c>
       <c r="I108" s="20" t="n">
-        <v>14.883561</v>
+        <v>39.505184</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>1.504371026800973</v>
+        <v>10.46962</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>0.6968113</v>
+        <v>3.9759693</v>
       </c>
       <c r="L108" s="21" t="n">
-        <v>7.04975512768092</v>
+        <v>2.19383891609831</v>
       </c>
       <c r="M108" s="21" t="n">
-        <v>6.959999999999999</v>
+        <v>0.5030143835716</v>
       </c>
       <c r="N108" s="21" t="n">
-        <v>8.4099490357427</v>
+        <v>15.04279234978169</v>
       </c>
       <c r="O108" s="21" t="n">
-        <v>17.85263732142248</v>
+        <v>16.8479651603609</v>
       </c>
       <c r="P108" s="20" t="n">
-        <v>4.353514132925898</v>
+        <v>2.646714786974468</v>
       </c>
       <c r="Q108" s="21" t="n">
-        <v>37.32</v>
+        <v>-25.8</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S108" s="20" t="n">
-        <v>0.2291888064107961</v>
+        <v>0.6174267863088643</v>
       </c>
       <c r="T108" s="15" t="inlineStr">
         <is>
-          <t>Crudeoiltransportation (27%)</t>
+          <t>Commercial Operations (74%)</t>
         </is>
       </c>
       <c r="U108" s="17" t="inlineStr">
         <is>
-          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
+          <t>Commercial Operations 74%; Government Operations 26%</t>
         </is>
       </c>
       <c r="V108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W108" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
+        </is>
+      </c>
       <c r="X108" s="15" t="inlineStr">
         <is>
-          <t>Investment In Sunoco +165%</t>
+          <t>Commercial Operation +143%</t>
         </is>
       </c>
     </row>
@@ -54730,12 +54716,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>LGN</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>BWX Technologies, Inc.</t>
+          <t>Legence Corp.</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
@@ -54743,13 +54729,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E109" s="17" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+      <c r="E109" s="17" t="n"/>
       <c r="F109" s="18" t="n">
-        <v>13971436544</v>
+        <v>8797458432</v>
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
@@ -54757,62 +54739,62 @@
         </is>
       </c>
       <c r="H109" s="20" t="n">
-        <v>32.283</v>
-      </c>
-      <c r="I109" s="20" t="n">
-        <v>39.505184</v>
+        <v>35.22426766420546</v>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J109" s="20" t="n">
-        <v>10.46962</v>
+        <v>14.65112493525829</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>3.9759693</v>
+        <v>3.127811730975989</v>
       </c>
       <c r="L109" s="21" t="n">
-        <v>2.19383891609831</v>
-      </c>
-      <c r="M109" s="21" t="n">
-        <v>0.5030143835716</v>
+        <v>3.41438849489116</v>
+      </c>
+      <c r="M109" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N109" s="21" t="n">
-        <v>15.04279234978169</v>
+        <v>3.69186301129894</v>
       </c>
       <c r="O109" s="21" t="n">
-        <v>16.8479651603609</v>
+        <v>5.44599126235131</v>
       </c>
       <c r="P109" s="20" t="n">
-        <v>2.646714786974468</v>
+        <v>6.20894155127728</v>
       </c>
       <c r="Q109" s="21" t="n">
-        <v>-25.8</v>
+        <v>167.4754158395236</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S109" s="20" t="n">
-        <v>0.6174267863088643</v>
+        <v>0.2963256950273106</v>
       </c>
       <c r="T109" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operations (74%)</t>
+          <t>Installation Maintenan (36%)</t>
         </is>
       </c>
       <c r="U109" s="17" t="inlineStr">
         <is>
-          <t>Commercial Operations 74%; Government Operations 26%</t>
+          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
         </is>
       </c>
       <c r="V109" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W109" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W109" s="17" t="n"/>
       <c r="X109" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operation +143%</t>
+          <t>Installation And Mai +162%</t>
         </is>
       </c>
     </row>
@@ -54822,12 +54804,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>LGN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Legence Corp.</t>
+          <t>Gen Digital Inc. Common Stock</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
@@ -54835,9 +54817,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E110" s="17" t="n"/>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>Information Te</t>
+        </is>
+      </c>
       <c r="F110" s="18" t="n">
-        <v>8797458432</v>
+        <v>17936660480</v>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
@@ -54845,62 +54831,62 @@
         </is>
       </c>
       <c r="H110" s="20" t="n">
-        <v>35.22426766420546</v>
-      </c>
-      <c r="I110" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.614</v>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>17.42151</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>14.65112493525829</v>
+        <v>6.758006</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>3.127811730975989</v>
+        <v>3.5315337</v>
       </c>
       <c r="L110" s="21" t="n">
-        <v>3.41438849489116</v>
-      </c>
-      <c r="M110" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.13133216482446</v>
+      </c>
+      <c r="M110" s="21" t="n">
+        <v>2.07549286633304</v>
       </c>
       <c r="N110" s="21" t="n">
-        <v>3.69186301129894</v>
+        <v>20.39245863793767</v>
       </c>
       <c r="O110" s="21" t="n">
-        <v>5.44599126235131</v>
+        <v>51.45999999999999</v>
       </c>
       <c r="P110" s="20" t="n">
-        <v>6.20894155127728</v>
+        <v>3.02914885347843</v>
       </c>
       <c r="Q110" s="21" t="n">
-        <v>167.4754158395236</v>
+        <v>18.59</v>
       </c>
       <c r="R110" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" s="20" t="n">
+        <v>0.5563136799999999</v>
+      </c>
+      <c r="T110" s="15" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform (67%)</t>
+        </is>
+      </c>
+      <c r="U110" s="17" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+        </is>
+      </c>
+      <c r="V110" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S110" s="20" t="n">
-        <v>0.2963256950273106</v>
-      </c>
-      <c r="T110" s="15" t="inlineStr">
-        <is>
-          <t>Installation Maintenan (36%)</t>
-        </is>
-      </c>
-      <c r="U110" s="17" t="inlineStr">
-        <is>
-          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
-        </is>
-      </c>
-      <c r="V110" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" s="17" t="n"/>
+      <c r="W110" s="17" t="inlineStr">
+        <is>
+          <t>Americas 43%; US 40%; EMEA 13%</t>
+        </is>
+      </c>
       <c r="X110" s="15" t="inlineStr">
         <is>
-          <t>Installation And Mai +162%</t>
+          <t>Trust Based Solution +119%</t>
         </is>
       </c>
     </row>
@@ -54910,12 +54896,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Gen Digital Inc. Common Stock</t>
+          <t>L3Harris Technologies, Inc.</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
@@ -54925,11 +54911,11 @@
       </c>
       <c r="E111" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F111" s="18" t="n">
-        <v>17936660480</v>
+        <v>46250123264</v>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
@@ -54937,62 +54923,62 @@
         </is>
       </c>
       <c r="H111" s="20" t="n">
-        <v>10.614</v>
+        <v>17.65892492763533</v>
       </c>
       <c r="I111" s="20" t="n">
-        <v>17.42151</v>
+        <v>25.062563</v>
       </c>
       <c r="J111" s="20" t="n">
-        <v>6.758006</v>
+        <v>2.4164972</v>
       </c>
       <c r="K111" s="20" t="n">
-        <v>3.5315337</v>
+        <v>1.181387091981915</v>
       </c>
       <c r="L111" s="21" t="n">
-        <v>10.13133216482446</v>
+        <v>5.88004410889457</v>
       </c>
       <c r="M111" s="21" t="n">
-        <v>2.07549286633304</v>
+        <v>1.56571804266048</v>
       </c>
       <c r="N111" s="21" t="n">
-        <v>20.39245863793767</v>
+        <v>8.274248192518591</v>
       </c>
       <c r="O111" s="21" t="n">
-        <v>51.45999999999999</v>
+        <v>8.96574625150067</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>3.02914885347843</v>
+        <v>2.55014245014245</v>
       </c>
       <c r="Q111" s="21" t="n">
-        <v>18.59</v>
+        <v>-9.82</v>
       </c>
       <c r="R111" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="S111" s="20" t="n">
+        <v>0.3315167177024359</v>
+      </c>
+      <c r="T111" s="15" t="inlineStr">
+        <is>
+          <t>Communication Systems (42%)</t>
+        </is>
+      </c>
+      <c r="U111" s="17" t="inlineStr">
+        <is>
+          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
+        </is>
+      </c>
+      <c r="V111" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S111" s="20" t="n">
-        <v>0.5563136799999999</v>
-      </c>
-      <c r="T111" s="15" t="inlineStr">
-        <is>
-          <t>Cyber Safety Platform (67%)</t>
-        </is>
-      </c>
-      <c r="U111" s="17" t="inlineStr">
-        <is>
-          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
-        </is>
-      </c>
-      <c r="V111" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="W111" s="17" t="inlineStr">
         <is>
-          <t>Americas 43%; US 40%; EMEA 13%</t>
+          <t>US 90%; Non Us 10%</t>
         </is>
       </c>
       <c r="X111" s="15" t="inlineStr">
         <is>
-          <t>Trust Based Solution +119%</t>
+          <t>Aerojet Rocketdyne +467%</t>
         </is>
       </c>
     </row>
@@ -55002,12 +54988,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>L3Harris Technologies, Inc.</t>
+          <t>Assured Guaranty Ltd</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
@@ -55017,74 +55003,80 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F112" s="18" t="n">
-        <v>46250123264</v>
+        <v>3213560832</v>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H112" s="20" t="n">
-        <v>17.65892492763533</v>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I112" s="20" t="n">
-        <v>25.062563</v>
+        <v>9.601839</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>2.4164972</v>
+        <v>0.57877684</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>1.181387091981915</v>
+        <v>2.937441345521024</v>
       </c>
       <c r="L112" s="21" t="n">
-        <v>5.88004410889457</v>
+        <v>5.55007068714223</v>
       </c>
       <c r="M112" s="21" t="n">
-        <v>1.56571804266048</v>
-      </c>
-      <c r="N112" s="21" t="n">
-        <v>8.274248192518591</v>
+        <v>1.91</v>
+      </c>
+      <c r="N112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O112" s="21" t="n">
-        <v>8.96574625150067</v>
-      </c>
-      <c r="P112" s="20" t="n">
-        <v>2.55014245014245</v>
+        <v>0</v>
+      </c>
+      <c r="P112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q112" s="21" t="n">
-        <v>-9.82</v>
+        <v>-4.7</v>
       </c>
       <c r="R112" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" s="20" t="n">
+        <v>0.9375650364203956</v>
+      </c>
+      <c r="T112" s="15" t="inlineStr">
+        <is>
+          <t>Insurance (97%)</t>
+        </is>
+      </c>
+      <c r="U112" s="17" t="inlineStr">
+        <is>
+          <t>Insurance 97%; Asset Management 3%</t>
+        </is>
+      </c>
+      <c r="V112" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S112" s="20" t="n">
-        <v>0.3315167177024359</v>
-      </c>
-      <c r="T112" s="15" t="inlineStr">
-        <is>
-          <t>Communication Systems (42%)</t>
-        </is>
-      </c>
-      <c r="U112" s="17" t="inlineStr">
-        <is>
-          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
-        </is>
-      </c>
-      <c r="V112" s="18" t="n">
-        <v>2</v>
-      </c>
       <c r="W112" s="17" t="inlineStr">
         <is>
-          <t>US 90%; Non Us 10%</t>
+          <t>US 77%; BM 18%; GB 5%</t>
         </is>
       </c>
       <c r="X112" s="15" t="inlineStr">
         <is>
-          <t>Aerojet Rocketdyne +467%</t>
+          <t>Asset Management +190%</t>
         </is>
       </c>
     </row>
@@ -55094,12 +55086,12 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd</t>
+          <t>Brighthouse Financial, Inc.</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
@@ -55113,7 +55105,7 @@
         </is>
       </c>
       <c r="F113" s="18" t="n">
-        <v>3213560832</v>
+        <v>2923887872</v>
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
@@ -55126,24 +55118,24 @@
         </is>
       </c>
       <c r="I113" s="20" t="n">
-        <v>9.601839</v>
+        <v>4.031721</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>0.57877684</v>
+        <v>0.4463682</v>
       </c>
       <c r="K113" s="20" t="n">
-        <v>2.937441345521024</v>
+        <v>0.42765653</v>
       </c>
       <c r="L113" s="21" t="n">
-        <v>5.55007068714223</v>
-      </c>
-      <c r="M113" s="21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="N113" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-3.50482109690038</v>
+      </c>
+      <c r="M113" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N113" s="21" t="n">
+        <v>0.007627959012433573</v>
       </c>
       <c r="O113" s="21" t="n">
         <v>0</v>
@@ -55154,35 +55146,31 @@
         </is>
       </c>
       <c r="Q113" s="21" t="n">
-        <v>-4.7</v>
+        <v>-6.12</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S113" s="20" t="n">
-        <v>0.9375650364203956</v>
+        <v>0.4403975356846814</v>
       </c>
       <c r="T113" s="15" t="inlineStr">
         <is>
-          <t>Insurance (97%)</t>
+          <t>Annuities (60%)</t>
         </is>
       </c>
       <c r="U113" s="17" t="inlineStr">
         <is>
-          <t>Insurance 97%; Asset Management 3%</t>
+          <t>Annuities 60%; Runoff 21%; Life 19%</t>
         </is>
       </c>
       <c r="V113" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W113" s="17" t="inlineStr">
-        <is>
-          <t>US 77%; BM 18%; GB 5%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W113" s="17" t="n"/>
       <c r="X113" s="15" t="inlineStr">
         <is>
-          <t>Asset Management +190%</t>
+          <t>Annuities +322%</t>
         </is>
       </c>
     </row>
@@ -55192,12 +55180,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc.</t>
+          <t>ONEOK, Inc.</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
@@ -55205,69 +55193,59 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E114" s="17" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="E114" s="17" t="n"/>
       <c r="F114" s="18" t="n">
-        <v>2923887872</v>
+        <v>60338987008</v>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H114" s="20" t="n">
+        <v>12.17</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>4.031721</v>
+        <v>16.560553</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.4463682</v>
+        <v>2.6306098</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.42765653</v>
+        <v>1.5327691</v>
       </c>
       <c r="L114" s="21" t="n">
-        <v>-3.50482109690038</v>
-      </c>
-      <c r="M114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.830758993916</v>
+      </c>
+      <c r="M114" s="21" t="n">
+        <v>4.39066236170035</v>
       </c>
       <c r="N114" s="21" t="n">
-        <v>0.007627959012433573</v>
+        <v>10.40228824506366</v>
       </c>
       <c r="O114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.48324054084763</v>
+      </c>
+      <c r="P114" s="20" t="n">
+        <v>4.229943145925458</v>
       </c>
       <c r="Q114" s="21" t="n">
-        <v>-6.12</v>
+        <v>50.16</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S114" s="20" t="n">
-        <v>0.4403975356846814</v>
+        <v>0.4959061195541746</v>
       </c>
       <c r="T114" s="15" t="inlineStr">
         <is>
-          <t>Annuities (60%)</t>
+          <t>Refined Products And C (66%)</t>
         </is>
       </c>
       <c r="U114" s="17" t="inlineStr">
         <is>
-          <t>Annuities 60%; Runoff 21%; Life 19%</t>
+          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
         </is>
       </c>
       <c r="V114" s="18" t="n">
@@ -55276,7 +55254,7 @@
       <c r="W114" s="17" t="n"/>
       <c r="X114" s="15" t="inlineStr">
         <is>
-          <t>Annuities +322%</t>
+          <t>Refined Products And +192%</t>
         </is>
       </c>
     </row>
@@ -55286,12 +55264,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>HAPN</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>ONEOK, Inc.</t>
+          <t>Happen Inc. Common Stock</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -55299,9 +55277,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E115" s="17" t="n"/>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="F115" s="18" t="n">
-        <v>60338987008</v>
+        <v>1927304704</v>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
@@ -55309,49 +55291,57 @@
         </is>
       </c>
       <c r="H115" s="20" t="n">
-        <v>12.17</v>
+        <v>3.25</v>
       </c>
       <c r="I115" s="20" t="n">
-        <v>16.560553</v>
+        <v>13.28940372062646</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>2.6306098</v>
+        <v>1.2295686</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>1.5327691</v>
-      </c>
-      <c r="L115" s="21" t="n">
-        <v>4.830758993916</v>
-      </c>
-      <c r="M115" s="21" t="n">
-        <v>4.39066236170035</v>
-      </c>
-      <c r="N115" s="21" t="n">
-        <v>10.40228824506366</v>
+        <v>3.18966609624748</v>
+      </c>
+      <c r="L115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>22.48324054084763</v>
-      </c>
-      <c r="P115" s="20" t="n">
-        <v>4.229943145925458</v>
+        <v>52.58608552315825</v>
+      </c>
+      <c r="P115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q115" s="21" t="n">
-        <v>50.16</v>
+        <v>2.07</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S115" s="20" t="n">
-        <v>0.4959061195541746</v>
+        <v>0.5010363171603962</v>
       </c>
       <c r="T115" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And C (66%)</t>
+          <t>Happen Bank (52%)</t>
         </is>
       </c>
       <c r="U115" s="17" t="inlineStr">
         <is>
-          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
+          <t>Happen Bank 52%; Happen Inc. 48%</t>
         </is>
       </c>
       <c r="V115" s="18" t="n">
@@ -55360,7 +55350,7 @@
       <c r="W115" s="17" t="n"/>
       <c r="X115" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And +192%</t>
+          <t>Happen Bank +124%</t>
         </is>
       </c>
     </row>
@@ -55370,43 +55360,51 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>HAPN</t>
+          <t>VFS</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Happen Inc. Common Stock</t>
+          <t>VinFast Auto Ltd. Ordinary Sha</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F116" s="18" t="n">
-        <v>1927304704</v>
+        <v>7042003968</v>
       </c>
       <c r="G116" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H116" s="20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I116" s="20" t="n">
-        <v>13.28940372062646</v>
-      </c>
-      <c r="J116" s="20" t="n">
-        <v>1.2295686</v>
-      </c>
-      <c r="K116" s="20" t="n">
-        <v>3.18966609624748</v>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L116" s="22" t="inlineStr">
         <is>
@@ -55418,13 +55416,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="N116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N116" s="21" t="n">
+        <v>78.31448357763071</v>
       </c>
       <c r="O116" s="21" t="n">
-        <v>52.58608552315825</v>
+        <v>-83.1176333196485</v>
       </c>
       <c r="P116" s="22" t="inlineStr">
         <is>
@@ -55432,31 +55428,35 @@
         </is>
       </c>
       <c r="Q116" s="21" t="n">
-        <v>2.07</v>
+        <v>-3.75</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S116" s="20" t="n">
-        <v>0.5010363171603962</v>
+        <v>0.460552269511968</v>
       </c>
       <c r="T116" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank (52%)</t>
+          <t>Car (48%)</t>
         </is>
       </c>
       <c r="U116" s="17" t="inlineStr">
         <is>
-          <t>Happen Bank 52%; Happen Inc. 48%</t>
+          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
         </is>
       </c>
       <c r="V116" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W116" s="17" t="inlineStr">
+        <is>
+          <t>VN 89%; Asia Pacific 8%; US 2%</t>
+        </is>
+      </c>
       <c r="X116" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank +124%</t>
+          <t>E Scooter +230%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F18" s="18" t="n">
-        <v>12457237</v>
+        <v>63345280</v>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="H18" s="20" t="n">
-        <v>-11.99</v>
+        <v>5.332</v>
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
@@ -1641,52 +1641,58 @@
         </is>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.58659774</v>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.65628195</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>0.031039892</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>51.35543081206073</v>
-      </c>
-      <c r="M18" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>64.10263948586179</v>
+      </c>
+      <c r="M18" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="N18" s="21" t="n">
-        <v>-19.53360636030006</v>
+        <v>-9.731226124022729</v>
       </c>
       <c r="O18" s="21" t="n">
-        <v>0.27102238816465</v>
+        <v>7.89126355897411</v>
       </c>
       <c r="P18" s="20" t="n">
-        <v>-20.75086540754323</v>
+        <v>5.187935432355073</v>
       </c>
       <c r="Q18" s="21" t="n">
-        <v>44.57</v>
+        <v>-60.46</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T18" s="15" t="n"/>
-      <c r="U18" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S18" s="20" t="n">
+        <v>0.6572808745010525</v>
+      </c>
+      <c r="T18" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Engage (78%)</t>
+        </is>
+      </c>
+      <c r="U18" s="17" t="inlineStr">
+        <is>
+          <t>Ttec Engage 78%; Ttec Digital 22%</t>
+        </is>
+      </c>
       <c r="V18" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W18" s="17" t="inlineStr">
         <is>
-          <t>CN 70%; HK 26%; MY 2%</t>
-        </is>
-      </c>
-      <c r="X18" s="15" t="n"/>
+          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
+        </is>
+      </c>
+      <c r="X18" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Digital +2%</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="13" t="n">
@@ -1694,12 +1700,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
@@ -1709,11 +1715,11 @@
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F19" s="18" t="n">
-        <v>63345280</v>
+        <v>12457237</v>
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
@@ -1721,7 +1727,7 @@
         </is>
       </c>
       <c r="H19" s="20" t="n">
-        <v>5.332</v>
+        <v>-11.99</v>
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
@@ -1729,58 +1735,52 @@
         </is>
       </c>
       <c r="J19" s="20" t="n">
-        <v>0.65628195</v>
-      </c>
-      <c r="K19" s="20" t="n">
-        <v>0.031039892</v>
+        <v>0.58659774</v>
+      </c>
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L19" s="21" t="n">
-        <v>64.10263948586179</v>
-      </c>
-      <c r="M19" s="21" t="n">
+        <v>51.35543081206073</v>
+      </c>
+      <c r="M19" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>-19.53360636030006</v>
+      </c>
+      <c r="O19" s="21" t="n">
+        <v>0.27102238816465</v>
+      </c>
+      <c r="P19" s="20" t="n">
+        <v>-20.75086540754323</v>
+      </c>
+      <c r="Q19" s="21" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="R19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="21" t="n">
-        <v>-9.731226124022729</v>
-      </c>
-      <c r="O19" s="21" t="n">
-        <v>7.89126355897411</v>
-      </c>
-      <c r="P19" s="20" t="n">
-        <v>5.187935432355073</v>
-      </c>
-      <c r="Q19" s="21" t="n">
-        <v>-60.46</v>
-      </c>
-      <c r="R19" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" s="20" t="n">
-        <v>0.6572808745010525</v>
-      </c>
-      <c r="T19" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Engage (78%)</t>
-        </is>
-      </c>
-      <c r="U19" s="17" t="inlineStr">
-        <is>
-          <t>Ttec Engage 78%; Ttec Digital 22%</t>
-        </is>
-      </c>
+      <c r="S19" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T19" s="15" t="n"/>
+      <c r="U19" s="17" t="n"/>
       <c r="V19" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W19" s="17" t="inlineStr">
         <is>
-          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
-        </is>
-      </c>
-      <c r="X19" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Digital +2%</t>
-        </is>
-      </c>
+          <t>CN 70%; HK 26%; MY 2%</t>
+        </is>
+      </c>
+      <c r="X19" s="15" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n">
@@ -39972,12 +39972,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -39987,11 +39987,11 @@
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F13" s="18" t="n">
-        <v>12457237</v>
+        <v>63345280</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         </is>
       </c>
       <c r="H13" s="20" t="n">
-        <v>-11.99</v>
+        <v>5.332</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
@@ -40007,52 +40007,58 @@
         </is>
       </c>
       <c r="J13" s="20" t="n">
-        <v>0.58659774</v>
-      </c>
-      <c r="K13" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.65628195</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.031039892</v>
       </c>
       <c r="L13" s="21" t="n">
-        <v>51.35543081206073</v>
-      </c>
-      <c r="M13" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>64.10263948586179</v>
+      </c>
+      <c r="M13" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="N13" s="21" t="n">
-        <v>-19.53360636030006</v>
+        <v>-9.731226124022729</v>
       </c>
       <c r="O13" s="21" t="n">
-        <v>0.27102238816465</v>
+        <v>7.89126355897411</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>-20.75086540754323</v>
+        <v>5.187935432355073</v>
       </c>
       <c r="Q13" s="21" t="n">
-        <v>44.57</v>
+        <v>-60.46</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T13" s="15" t="n"/>
-      <c r="U13" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S13" s="20" t="n">
+        <v>0.6572808745010525</v>
+      </c>
+      <c r="T13" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Engage (78%)</t>
+        </is>
+      </c>
+      <c r="U13" s="17" t="inlineStr">
+        <is>
+          <t>Ttec Engage 78%; Ttec Digital 22%</t>
+        </is>
+      </c>
       <c r="V13" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W13" s="17" t="inlineStr">
         <is>
-          <t>CN 70%; HK 26%; MY 2%</t>
-        </is>
-      </c>
-      <c r="X13" s="15" t="n"/>
+          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
+        </is>
+      </c>
+      <c r="X13" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Digital +2%</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -40060,12 +40066,12 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -40075,11 +40081,11 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="18" t="n">
-        <v>63345280</v>
+        <v>12457237</v>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
@@ -40087,7 +40093,7 @@
         </is>
       </c>
       <c r="H14" s="20" t="n">
-        <v>5.332</v>
+        <v>-11.99</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
@@ -40095,58 +40101,52 @@
         </is>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.65628195</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>0.031039892</v>
+        <v>0.58659774</v>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L14" s="21" t="n">
-        <v>64.10263948586179</v>
-      </c>
-      <c r="M14" s="21" t="n">
+        <v>51.35543081206073</v>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>-19.53360636030006</v>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>0.27102238816465</v>
+      </c>
+      <c r="P14" s="20" t="n">
+        <v>-20.75086540754323</v>
+      </c>
+      <c r="Q14" s="21" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="R14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N14" s="21" t="n">
-        <v>-9.731226124022729</v>
-      </c>
-      <c r="O14" s="21" t="n">
-        <v>7.89126355897411</v>
-      </c>
-      <c r="P14" s="20" t="n">
-        <v>5.187935432355073</v>
-      </c>
-      <c r="Q14" s="21" t="n">
-        <v>-60.46</v>
-      </c>
-      <c r="R14" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" s="20" t="n">
-        <v>0.6572808745010525</v>
-      </c>
-      <c r="T14" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Engage (78%)</t>
-        </is>
-      </c>
-      <c r="U14" s="17" t="inlineStr">
-        <is>
-          <t>Ttec Engage 78%; Ttec Digital 22%</t>
-        </is>
-      </c>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T14" s="15" t="n"/>
+      <c r="U14" s="17" t="n"/>
       <c r="V14" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W14" s="17" t="inlineStr">
         <is>
-          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
-        </is>
-      </c>
-      <c r="X14" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Digital +2%</t>
-        </is>
-      </c>
+          <t>CN 70%; HK 26%; MY 2%</t>
+        </is>
+      </c>
+      <c r="X14" s="15" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="13" t="n">
@@ -50820,103 +50820,89 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>VFS</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>VinFast Auto Ltd. Ordinary Sha</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F67" s="18" t="n">
-        <v>7509911040</v>
+        <v>104030609408</v>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H67" s="20" t="n">
+        <v>12.211</v>
+      </c>
+      <c r="I67" s="20" t="n">
+        <v>14.801482</v>
+      </c>
+      <c r="J67" s="20" t="n">
+        <v>3.2861774</v>
+      </c>
+      <c r="K67" s="20" t="n">
+        <v>0.68366075</v>
+      </c>
+      <c r="L67" s="21" t="n">
+        <v>6.14626794593043</v>
+      </c>
+      <c r="M67" s="21" t="n">
+        <v>2.96</v>
       </c>
       <c r="N67" s="21" t="n">
-        <v>78.31448357763071</v>
+        <v>12.24307948200071</v>
       </c>
       <c r="O67" s="21" t="n">
-        <v>-83.1176333196485</v>
-      </c>
-      <c r="P67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.84160433056228</v>
+      </c>
+      <c r="P67" s="20" t="n">
+        <v>1.675361394631018</v>
       </c>
       <c r="Q67" s="21" t="n">
-        <v>-3.75</v>
+        <v>92.92</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S67" s="20" t="n">
-        <v>0.460552269511968</v>
+        <v>0.3806408342658987</v>
       </c>
       <c r="T67" s="15" t="inlineStr">
         <is>
-          <t>Car (48%)</t>
+          <t>Marketing Speciality (46%)</t>
         </is>
       </c>
       <c r="U67" s="17" t="inlineStr">
         <is>
-          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
+          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
         </is>
       </c>
       <c r="V67" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W67" s="17" t="inlineStr">
         <is>
-          <t>VN 89%; Asia Pacific 8%; US 2%</t>
+          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
         </is>
       </c>
       <c r="X67" s="15" t="inlineStr">
         <is>
-          <t>E Scooter +230%</t>
+          <t>Refining +92%</t>
         </is>
       </c>
     </row>
@@ -50926,12 +50912,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Amphenol Corp /De/</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -50941,11 +50927,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>104030609408</v>
+        <v>206943928320</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -50953,62 +50939,62 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>12.211</v>
+        <v>29.62302222645686</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>14.801482</v>
+        <v>41.96</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>3.2861774</v>
+        <v>13.354551</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>0.68366075</v>
+        <v>7.1331444</v>
       </c>
       <c r="L68" s="21" t="n">
-        <v>6.14626794593043</v>
+        <v>2.30913485895705</v>
       </c>
       <c r="M68" s="21" t="n">
-        <v>2.96</v>
+        <v>0.55827491517045</v>
       </c>
       <c r="N68" s="21" t="n">
-        <v>12.24307948200071</v>
+        <v>45.67278672993024</v>
       </c>
       <c r="O68" s="21" t="n">
-        <v>6.84160433056228</v>
+        <v>29.39923710032213</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>1.675361394631018</v>
+        <v>2.057377830710813</v>
       </c>
       <c r="Q68" s="21" t="n">
-        <v>92.92</v>
+        <v>19.46</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68" s="20" t="n">
-        <v>0.3806408342658987</v>
+        <v>0.4256894967493531</v>
       </c>
       <c r="T68" s="15" t="inlineStr">
         <is>
-          <t>Marketing Speciality (46%)</t>
+          <t>Communications Solutio (58%)</t>
         </is>
       </c>
       <c r="U68" s="17" t="inlineStr">
         <is>
-          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
+          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
         </is>
       </c>
       <c r="V68" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W68" s="17" t="inlineStr">
         <is>
-          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
+          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
         </is>
       </c>
       <c r="X68" s="15" t="inlineStr">
         <is>
-          <t>Refining +92%</t>
+          <t>Communications Solut +143%</t>
         </is>
       </c>
     </row>
@@ -51018,12 +51004,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Amphenol Corp /De/</t>
+          <t>Enterprise Products Partners L</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -51033,11 +51019,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>206943928320</v>
+        <v>84003667968</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -51045,62 +51031,58 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>29.62302222645686</v>
+        <v>11.619</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>41.96</v>
+        <v>13.460208</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>13.354551</v>
+        <v>2.777183</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>7.1331444</v>
+        <v>1.4366723</v>
       </c>
       <c r="L69" s="21" t="n">
-        <v>2.30913485895705</v>
+        <v>4.43809968934908</v>
       </c>
       <c r="M69" s="21" t="n">
-        <v>0.55827491517045</v>
+        <v>0.13529237831726</v>
       </c>
       <c r="N69" s="21" t="n">
-        <v>45.67278672993024</v>
+        <v>21.16359754470242</v>
       </c>
       <c r="O69" s="21" t="n">
-        <v>29.39923710032213</v>
+        <v>19.03228934354698</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>2.057377830710813</v>
+        <v>3.436213572447524</v>
       </c>
       <c r="Q69" s="21" t="n">
-        <v>19.46</v>
+        <v>32.34</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.4256894967493531</v>
+        <v>0.3092139839729619</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Communications Solutio (58%)</t>
+          <t>Onshore Crude Oil Pipe (39%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
+          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Communications Solut +143%</t>
+          <t>Petrochemical And Re +92%</t>
         </is>
       </c>
     </row>
@@ -51110,12 +51092,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -51125,11 +51107,11 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>84003667968</v>
+        <v>59365711872</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -51137,58 +51119,62 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>11.619</v>
+        <v>38.313</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>13.460208</v>
+        <v>52.08779</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>2.777183</v>
+        <v>18.907534</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>1.4366723</v>
+        <v>17.51624120163544</v>
       </c>
       <c r="L70" s="21" t="n">
-        <v>4.43809968934908</v>
+        <v>1.43309891391495</v>
       </c>
       <c r="M70" s="21" t="n">
-        <v>0.13529237831726</v>
+        <v>0.11999999</v>
       </c>
       <c r="N70" s="21" t="n">
-        <v>21.16359754470242</v>
+        <v>28.59709180832235</v>
       </c>
       <c r="O70" s="21" t="n">
-        <v>19.03228934354698</v>
+        <v>44.40287939770699</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>3.436213572447524</v>
+        <v>-0.1708346552178611</v>
       </c>
       <c r="Q70" s="21" t="n">
-        <v>32.34</v>
+        <v>96.81</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.3092139839729619</v>
+        <v>0.6478300772075185</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipe (39%)</t>
+          <t>Semiconductor Test (79%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
+          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" s="17" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="W70" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
+        </is>
+      </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Petrochemical And Re +92%</t>
+          <t>Semiconductor Test +128%</t>
         </is>
       </c>
     </row>
@@ -51198,12 +51184,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Te Connectivity Plc</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -51217,7 +51203,7 @@
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>59365711872</v>
+        <v>61365223424</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -51225,62 +51211,62 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>38.313</v>
+        <v>12.92</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>52.08779</v>
+        <v>20.76004</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>18.907534</v>
+        <v>4.6395974</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>17.51624120163544</v>
+        <v>3.175925</v>
       </c>
       <c r="L71" s="21" t="n">
-        <v>1.43309891391495</v>
+        <v>5.99434499439441</v>
       </c>
       <c r="M71" s="21" t="n">
-        <v>0.11999999</v>
+        <v>1.50999995</v>
       </c>
       <c r="N71" s="21" t="n">
-        <v>28.59709180832235</v>
+        <v>19.58952110795928</v>
       </c>
       <c r="O71" s="21" t="n">
-        <v>44.40287939770699</v>
+        <v>23.88059701492537</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>-0.1708346552178611</v>
+        <v>1.09837962962963</v>
       </c>
       <c r="Q71" s="21" t="n">
-        <v>96.81</v>
+        <v>-14.61</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.6478300772075185</v>
+        <v>0.5038462678974261</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test (79%)</t>
+          <t>Transportation Solutio (54%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
+          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W71" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
+          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
         </is>
       </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test +128%</t>
+          <t>Industrial Solutions +344%</t>
         </is>
       </c>
     </row>
@@ -51290,12 +51276,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>DWSN</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Te Connectivity Plc</t>
+          <t>Dawson Geophysical Company</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -51305,11 +51291,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>61365223424</v>
+        <v>104346872</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -51317,62 +51303,58 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>12.92</v>
+        <v>9.484</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>20.76004</v>
+        <v>28</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>4.6395974</v>
+        <v>5.2093024</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>3.175925</v>
+        <v>0.781109620624607</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>5.99434499439441</v>
+        <v>-3.92755347083511</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>1.50999995</v>
+        <v>8.120800080331669</v>
       </c>
       <c r="N72" s="21" t="n">
-        <v>19.58952110795928</v>
+        <v>25.64674804153762</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>23.88059701492537</v>
+        <v>8.550169176872171</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>1.09837962962963</v>
+        <v>1.218788303274383</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>-14.61</v>
+        <v>85.28</v>
       </c>
       <c r="R72" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S72" s="20" t="n">
-        <v>0.5038462678974261</v>
+        <v>0.6695871789304009</v>
       </c>
       <c r="T72" s="15" t="inlineStr">
         <is>
-          <t>Transportation Solutio (54%)</t>
+          <t>United States Operatio (79%)</t>
         </is>
       </c>
       <c r="U72" s="17" t="inlineStr">
         <is>
-          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
+          <t>United States Operations 79%; Canada Operations 21%</t>
         </is>
       </c>
       <c r="V72" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W72" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W72" s="17" t="n"/>
       <c r="X72" s="15" t="inlineStr">
         <is>
-          <t>Industrial Solutions +344%</t>
+          <t>Canada Operations +152%</t>
         </is>
       </c>
     </row>
@@ -51382,12 +51364,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>DWSN</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Dawson Geophysical Company</t>
+          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -51397,11 +51379,11 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F73" s="18" t="n">
-        <v>104346872</v>
+        <v>4507106816</v>
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
@@ -51409,58 +51391,62 @@
         </is>
       </c>
       <c r="H73" s="20" t="n">
-        <v>9.484</v>
+        <v>20.979</v>
       </c>
       <c r="I73" s="20" t="n">
-        <v>28</v>
+        <v>39.50917</v>
       </c>
       <c r="J73" s="20" t="n">
-        <v>5.2093024</v>
+        <v>4.942614</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>0.781109620624607</v>
+        <v>5.988356816294535</v>
       </c>
       <c r="L73" s="21" t="n">
-        <v>-3.92755347083511</v>
+        <v>0.9359515835039199</v>
       </c>
       <c r="M73" s="21" t="n">
-        <v>8.120800080331669</v>
+        <v>0.64999997</v>
       </c>
       <c r="N73" s="21" t="n">
-        <v>25.64674804153762</v>
+        <v>-5.462297040904851</v>
       </c>
       <c r="O73" s="21" t="n">
-        <v>8.550169176872171</v>
+        <v>25.49940543018288</v>
       </c>
       <c r="P73" s="20" t="n">
-        <v>1.218788303274383</v>
+        <v>-2.120367819924969</v>
       </c>
       <c r="Q73" s="21" t="n">
-        <v>85.28</v>
+        <v>106.32</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S73" s="20" t="n">
-        <v>0.6695871789304009</v>
+        <v>0.2775979208843406</v>
       </c>
       <c r="T73" s="15" t="inlineStr">
         <is>
-          <t>United States Operatio (79%)</t>
+          <t>Ball Bonding Equipment (43%)</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
         <is>
-          <t>United States Operations 79%; Canada Operations 21%</t>
+          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
         </is>
       </c>
       <c r="V73" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W73" s="17" t="inlineStr">
+        <is>
+          <t>CN 56%; US 10%; All Other Segments 9%</t>
+        </is>
+      </c>
       <c r="X73" s="15" t="inlineStr">
         <is>
-          <t>Canada Operations +152%</t>
+          <t>Ball Bonding Equipme +198%</t>
         </is>
       </c>
     </row>
@@ -51470,12 +51456,12 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
+          <t>Emergent Biosolutions Inc.</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -51485,11 +51471,11 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F74" s="18" t="n">
-        <v>4507106816</v>
+        <v>319432896</v>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
@@ -51497,62 +51483,66 @@
         </is>
       </c>
       <c r="H74" s="20" t="n">
-        <v>20.979</v>
-      </c>
-      <c r="I74" s="20" t="n">
-        <v>39.50917</v>
+        <v>26.38994704225352</v>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J74" s="20" t="n">
-        <v>4.942614</v>
+        <v>0.9361382</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>5.988356816294535</v>
+        <v>0.4147402</v>
       </c>
       <c r="L74" s="21" t="n">
-        <v>0.9359515835039199</v>
-      </c>
-      <c r="M74" s="21" t="n">
-        <v>0.64999997</v>
+        <v>26.97801418097588</v>
+      </c>
+      <c r="M74" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N74" s="21" t="n">
-        <v>-5.462297040904851</v>
+        <v>14.79068774028193</v>
       </c>
       <c r="O74" s="21" t="n">
-        <v>25.49940543018288</v>
+        <v>3.78515260562441</v>
       </c>
       <c r="P74" s="20" t="n">
-        <v>-2.120367819924969</v>
+        <v>14.55281690140845</v>
       </c>
       <c r="Q74" s="21" t="n">
-        <v>106.32</v>
+        <v>-50.23999999999999</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S74" s="20" t="n">
-        <v>0.2775979208843406</v>
+        <v>0.557029765440831</v>
       </c>
       <c r="T74" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment (43%)</t>
+          <t>MCM Products (67%)</t>
         </is>
       </c>
       <c r="U74" s="17" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
+          <t>MCM Products 67%; Commercial Products 33%</t>
         </is>
       </c>
       <c r="V74" s="18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W74" s="17" t="inlineStr">
         <is>
-          <t>CN 56%; US 10%; All Other Segments 9%</t>
+          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
         </is>
       </c>
       <c r="X74" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipme +198%</t>
+          <t>MCM Products +188%</t>
         </is>
       </c>
     </row>
@@ -51562,12 +51552,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Emergent Biosolutions Inc.</t>
+          <t>Porch Group Inc.</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -51577,11 +51567,11 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F75" s="18" t="n">
-        <v>319432896</v>
+        <v>1867401472</v>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
@@ -51589,66 +51579,62 @@
         </is>
       </c>
       <c r="H75" s="20" t="n">
-        <v>26.38994704225352</v>
+        <v>37.42943855774974</v>
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J75" s="20" t="n">
-        <v>0.9361382</v>
+      <c r="J75" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K75" s="20" t="n">
-        <v>0.4147402</v>
+        <v>3.6359277</v>
       </c>
       <c r="L75" s="21" t="n">
-        <v>26.97801418097588</v>
-      </c>
-      <c r="M75" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69353492369449</v>
+      </c>
+      <c r="M75" s="21" t="n">
+        <v>2.78673595725851</v>
       </c>
       <c r="N75" s="21" t="n">
-        <v>14.79068774028193</v>
+        <v>10.31950957042169</v>
       </c>
       <c r="O75" s="21" t="n">
-        <v>3.78515260562441</v>
+        <v>10.50153492306376</v>
       </c>
       <c r="P75" s="20" t="n">
-        <v>14.55281690140845</v>
+        <v>3.279218781110286</v>
       </c>
       <c r="Q75" s="21" t="n">
-        <v>-50.23999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S75" s="20" t="n">
-        <v>0.557029765440831</v>
+        <v>0.5817970747345014</v>
       </c>
       <c r="T75" s="15" t="inlineStr">
         <is>
-          <t>MCM Products (67%)</t>
+          <t>Insurance Services (72%)</t>
         </is>
       </c>
       <c r="U75" s="17" t="inlineStr">
         <is>
-          <t>MCM Products 67%; Commercial Products 33%</t>
+          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
         </is>
       </c>
       <c r="V75" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W75" s="17" t="inlineStr">
-        <is>
-          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W75" s="17" t="n"/>
       <c r="X75" s="15" t="inlineStr">
         <is>
-          <t>MCM Products +188%</t>
+          <t>Software Data +333%</t>
         </is>
       </c>
     </row>
@@ -51658,12 +51644,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NGL</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Porch Group Inc.</t>
+          <t>NGL Energy Partners LP</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -51673,11 +51659,11 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1867401472</v>
+        <v>1989539712</v>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
@@ -51685,7 +51671,7 @@
         </is>
       </c>
       <c r="H76" s="20" t="n">
-        <v>37.42943855774974</v>
+        <v>15.17839608310902</v>
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
@@ -51698,49 +51684,55 @@
         </is>
       </c>
       <c r="K76" s="20" t="n">
-        <v>3.6359277</v>
+        <v>0.6303674</v>
       </c>
       <c r="L76" s="21" t="n">
-        <v>4.69353492369449</v>
-      </c>
-      <c r="M76" s="21" t="n">
-        <v>2.78673595725851</v>
+        <v>5.12068190373472</v>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N76" s="21" t="n">
-        <v>10.31950957042169</v>
+        <v>12.90137422847655</v>
       </c>
       <c r="O76" s="21" t="n">
-        <v>10.50153492306376</v>
+        <v>11.58580003385248</v>
       </c>
       <c r="P76" s="20" t="n">
-        <v>3.279218781110286</v>
+        <v>7.901573173509551</v>
       </c>
       <c r="Q76" s="21" t="n">
-        <v>19.2</v>
+        <v>174.77</v>
       </c>
       <c r="R76" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S76" s="20" t="n">
-        <v>0.5817970747345014</v>
+        <v>0.3423299785064143</v>
       </c>
       <c r="T76" s="15" t="inlineStr">
         <is>
-          <t>Insurance Services (72%)</t>
+          <t>Liquids Logistics (40%)</t>
         </is>
       </c>
       <c r="U76" s="17" t="inlineStr">
         <is>
-          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
+          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
         </is>
       </c>
       <c r="V76" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="W76" s="17" t="inlineStr">
+        <is>
+          <t>Non Us 100%</t>
+        </is>
+      </c>
       <c r="X76" s="15" t="inlineStr">
         <is>
-          <t>Software Data +333%</t>
+          <t>Crude Oil Logistics +162%</t>
         </is>
       </c>
     </row>
@@ -51750,12 +51742,12 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>NGL</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>NGL Energy Partners LP</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -51765,11 +51757,11 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F77" s="18" t="n">
-        <v>1989539712</v>
+        <v>360690188288</v>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
@@ -51777,12 +51769,10 @@
         </is>
       </c>
       <c r="H77" s="20" t="n">
-        <v>15.17839608310902</v>
-      </c>
-      <c r="I77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>19.51</v>
+      </c>
+      <c r="I77" s="20" t="n">
+        <v>33.039604</v>
       </c>
       <c r="J77" s="22" t="inlineStr">
         <is>
@@ -51790,55 +51780,53 @@
         </is>
       </c>
       <c r="K77" s="20" t="n">
-        <v>0.6303674</v>
+        <v>2.3855643</v>
       </c>
       <c r="L77" s="21" t="n">
-        <v>5.12068190373472</v>
-      </c>
-      <c r="M77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.02823359941622</v>
+      </c>
+      <c r="M77" s="21" t="n">
+        <v>0.76768205413026</v>
       </c>
       <c r="N77" s="21" t="n">
-        <v>12.90137422847655</v>
+        <v>81.97384514065294</v>
       </c>
       <c r="O77" s="21" t="n">
-        <v>11.58580003385248</v>
+        <v>13.94585527536068</v>
       </c>
       <c r="P77" s="20" t="n">
-        <v>7.901573173509551</v>
+        <v>1.01819258757827</v>
       </c>
       <c r="Q77" s="21" t="n">
-        <v>174.77</v>
+        <v>226.48</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77" s="20" t="n">
-        <v>0.3423299785064143</v>
+        <v>0.5038741410704293</v>
       </c>
       <c r="T77" s="15" t="inlineStr">
         <is>
-          <t>Liquids Logistics (40%)</t>
+          <t>Infrastructure Solutio (54%)</t>
         </is>
       </c>
       <c r="U77" s="17" t="inlineStr">
         <is>
-          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
+          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
         </is>
       </c>
       <c r="V77" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W77" s="17" t="inlineStr">
         <is>
-          <t>Non Us 100%</t>
+          <t>US 56%; Non Us 44%</t>
         </is>
       </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
-          <t>Crude Oil Logistics +162%</t>
+          <t>Infrastructure Solut +181%</t>
         </is>
       </c>
     </row>
@@ -51848,12 +51836,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -51867,7 +51855,7 @@
         </is>
       </c>
       <c r="F78" s="18" t="n">
-        <v>360690188288</v>
+        <v>83154591744</v>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
@@ -51875,64 +51863,64 @@
         </is>
       </c>
       <c r="H78" s="20" t="n">
-        <v>19.51</v>
+        <v>102.474</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>33.039604</v>
-      </c>
-      <c r="J78" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>142.82867</v>
+      </c>
+      <c r="J78" s="20" t="n">
+        <v>17.686687</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>2.3855643</v>
+        <v>27.589445</v>
       </c>
       <c r="L78" s="21" t="n">
-        <v>2.02823359941622</v>
-      </c>
-      <c r="M78" s="21" t="n">
-        <v>0.76768205413026</v>
+        <v>0.37963999713611</v>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N78" s="21" t="n">
-        <v>81.97384514065294</v>
+        <v>5.712871831528011</v>
       </c>
       <c r="O78" s="21" t="n">
-        <v>13.94585527536068</v>
+        <v>32.17730397042276</v>
       </c>
       <c r="P78" s="20" t="n">
-        <v>1.01819258757827</v>
+        <v>-1.18221551413651</v>
       </c>
       <c r="Q78" s="21" t="n">
-        <v>226.48</v>
+        <v>337.22</v>
       </c>
       <c r="R78" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S78" s="20" t="n">
-        <v>0.5038741410704293</v>
+        <v>0.554732848124369</v>
       </c>
       <c r="T78" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solutio (54%)</t>
+          <t>Systems (67%)</t>
         </is>
       </c>
       <c r="U78" s="17" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
+          <t>Systems 67%; Components 33%</t>
         </is>
       </c>
       <c r="V78" s="18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W78" s="17" t="inlineStr">
         <is>
-          <t>US 56%; Non Us 44%</t>
+          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
         </is>
       </c>
       <c r="X78" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solut +181%</t>
+          <t>Systems +279%</t>
         </is>
       </c>
     </row>
@@ -51942,12 +51930,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>PROG Holdings, Inc.</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -51957,11 +51945,11 @@
       </c>
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F79" s="18" t="n">
-        <v>83154591744</v>
+        <v>1472177024</v>
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
@@ -51969,64 +51957,58 @@
         </is>
       </c>
       <c r="H79" s="20" t="n">
-        <v>102.474</v>
+        <v>8.850440627472885</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>142.82867</v>
+        <v>11.922581</v>
       </c>
       <c r="J79" s="20" t="n">
-        <v>17.686687</v>
+        <v>1.8279835</v>
       </c>
       <c r="K79" s="20" t="n">
-        <v>27.589445</v>
+        <v>0.5630427</v>
       </c>
       <c r="L79" s="21" t="n">
-        <v>0.37963999713611</v>
-      </c>
-      <c r="M79" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.7154094641091</v>
+      </c>
+      <c r="M79" s="21" t="n">
+        <v>1.20889722398801</v>
       </c>
       <c r="N79" s="21" t="n">
-        <v>5.712871831528011</v>
+        <v>14.37354784103989</v>
       </c>
       <c r="O79" s="21" t="n">
-        <v>32.17730397042276</v>
+        <v>10.44635139915609</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>-1.18221551413651</v>
+        <v>3.362100265326072</v>
       </c>
       <c r="Q79" s="21" t="n">
-        <v>337.22</v>
+        <v>38.15</v>
       </c>
       <c r="R79" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S79" s="20" t="n">
-        <v>0.554732848124369</v>
+        <v>0.9403673440059026</v>
       </c>
       <c r="T79" s="15" t="inlineStr">
         <is>
-          <t>Systems (67%)</t>
+          <t>Progressive Leasing (97%)</t>
         </is>
       </c>
       <c r="U79" s="17" t="inlineStr">
         <is>
-          <t>Systems 67%; Components 33%</t>
+          <t>Progressive Leasing 97%; Four 3%</t>
         </is>
       </c>
       <c r="V79" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W79" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W79" s="17" t="n"/>
       <c r="X79" s="15" t="inlineStr">
         <is>
-          <t>Systems +279%</t>
+          <t>Four +170%</t>
         </is>
       </c>
     </row>
@@ -52036,12 +52018,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>PROG Holdings, Inc.</t>
+          <t>Ies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -52055,7 +52037,7 @@
         </is>
       </c>
       <c r="F80" s="18" t="n">
-        <v>1472177024</v>
+        <v>13776098304</v>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
@@ -52063,49 +52045,51 @@
         </is>
       </c>
       <c r="H80" s="20" t="n">
-        <v>8.850440627472885</v>
+        <v>22.535</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>11.922581</v>
+        <v>30.729776</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>1.8279835</v>
+        <v>11.206885</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>0.5630427</v>
+        <v>3.4563446</v>
       </c>
       <c r="L80" s="21" t="n">
-        <v>20.7154094641091</v>
-      </c>
-      <c r="M80" s="21" t="n">
-        <v>1.20889722398801</v>
+        <v>2.01426811681025</v>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N80" s="21" t="n">
-        <v>14.37354784103989</v>
+        <v>39.14787497533104</v>
       </c>
       <c r="O80" s="21" t="n">
-        <v>10.44635139915609</v>
+        <v>13.0825133917565</v>
       </c>
       <c r="P80" s="20" t="n">
-        <v>3.362100265326072</v>
+        <v>-0.6658293394323307</v>
       </c>
       <c r="Q80" s="21" t="n">
-        <v>38.15</v>
+        <v>64.63</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S80" s="20" t="n">
-        <v>0.9403673440059026</v>
+        <v>0.302118628032772</v>
       </c>
       <c r="T80" s="15" t="inlineStr">
         <is>
-          <t>Progressive Leasing (97%)</t>
+          <t>Residential (39%)</t>
         </is>
       </c>
       <c r="U80" s="17" t="inlineStr">
         <is>
-          <t>Progressive Leasing 97%; Four 3%</t>
+          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
         </is>
       </c>
       <c r="V80" s="18" t="n">
@@ -52114,7 +52098,7 @@
       <c r="W80" s="17" t="n"/>
       <c r="X80" s="15" t="inlineStr">
         <is>
-          <t>Four +170%</t>
+          <t>Commercialand Indust +109%</t>
         </is>
       </c>
     </row>
@@ -52124,12 +52108,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Ies Holdings, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
@@ -52139,11 +52123,11 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F81" s="18" t="n">
-        <v>13776098304</v>
+        <v>5271048421376</v>
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
@@ -52151,60 +52135,62 @@
         </is>
       </c>
       <c r="H81" s="20" t="n">
-        <v>22.535</v>
+        <v>26.03</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>30.729776</v>
+        <v>27.631645</v>
       </c>
       <c r="J81" s="20" t="n">
-        <v>11.206885</v>
+        <v>23.019087</v>
       </c>
       <c r="K81" s="20" t="n">
-        <v>3.4563446</v>
+        <v>195.8478272042803</v>
       </c>
       <c r="L81" s="21" t="n">
-        <v>2.01426811681025</v>
-      </c>
-      <c r="M81" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.66135648441059</v>
+      </c>
+      <c r="M81" s="21" t="n">
+        <v>0.01871342168819</v>
       </c>
       <c r="N81" s="21" t="n">
-        <v>39.14787497533104</v>
+        <v>73.21388307718124</v>
       </c>
       <c r="O81" s="21" t="n">
-        <v>13.0825133917565</v>
+        <v>79.39769221313577</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>-0.6658293394323307</v>
+        <v>-0.3535471835000259</v>
       </c>
       <c r="Q81" s="21" t="n">
-        <v>64.63</v>
+        <v>13.91</v>
       </c>
       <c r="R81" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" s="20" t="n">
+        <v>0.8136213783744384</v>
+      </c>
+      <c r="T81" s="15" t="inlineStr">
+        <is>
+          <t>Compute And Networking (90%)</t>
+        </is>
+      </c>
+      <c r="U81" s="17" t="inlineStr">
+        <is>
+          <t>Compute And Networking 90%; Graphics 10%</t>
+        </is>
+      </c>
+      <c r="V81" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S81" s="20" t="n">
-        <v>0.302118628032772</v>
-      </c>
-      <c r="T81" s="15" t="inlineStr">
-        <is>
-          <t>Residential (39%)</t>
-        </is>
-      </c>
-      <c r="U81" s="17" t="inlineStr">
-        <is>
-          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
-        </is>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" s="17" t="n"/>
+      <c r="W81" s="17" t="inlineStr">
+        <is>
+          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
+        </is>
+      </c>
       <c r="X81" s="15" t="inlineStr">
         <is>
-          <t>Commercialand Indust +109%</t>
+          <t>Compute And Networki +114%</t>
         </is>
       </c>
     </row>
@@ -52214,12 +52200,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -52229,11 +52215,11 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F82" s="18" t="n">
-        <v>5271048421376</v>
+        <v>10556858368</v>
       </c>
       <c r="G82" s="19" t="inlineStr">
         <is>
@@ -52241,62 +52227,64 @@
         </is>
       </c>
       <c r="H82" s="20" t="n">
-        <v>26.03</v>
+        <v>347.3889692037075</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>27.631645</v>
+        <v>68.672195</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>23.019087</v>
+        <v>6.6218543</v>
       </c>
       <c r="K82" s="20" t="n">
-        <v>195.8478272042803</v>
+        <v>4.817643283343015</v>
       </c>
       <c r="L82" s="21" t="n">
-        <v>1.66135648441059</v>
-      </c>
-      <c r="M82" s="21" t="n">
-        <v>0.01871342168819</v>
+        <v>-8.42592261675078</v>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N82" s="21" t="n">
-        <v>73.21388307718124</v>
+        <v>-0.11123836175898</v>
       </c>
       <c r="O82" s="21" t="n">
-        <v>79.39769221313577</v>
+        <v>1.17675041790433</v>
       </c>
       <c r="P82" s="20" t="n">
-        <v>-0.3535471835000259</v>
+        <v>-59.63858781496614</v>
       </c>
       <c r="Q82" s="21" t="n">
-        <v>13.91</v>
+        <v>7.08</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S82" s="20" t="n">
-        <v>0.8136213783744384</v>
+        <v>0.3007342710765748</v>
       </c>
       <c r="T82" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networking (90%)</t>
+          <t>Brokerage (38%)</t>
         </is>
       </c>
       <c r="U82" s="17" t="inlineStr">
         <is>
-          <t>Compute And Networking 90%; Graphics 10%</t>
+          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
         </is>
       </c>
       <c r="V82" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W82" s="17" t="inlineStr">
         <is>
-          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
+          <t>KZ 84%; AM 8%; CY 7%</t>
         </is>
       </c>
       <c r="X82" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networki +114%</t>
+          <t>Other +100%</t>
         </is>
       </c>
     </row>
@@ -52306,12 +52294,12 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp.</t>
+          <t>FutureFuel Corp.</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
@@ -52321,76 +52309,80 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F83" s="18" t="n">
-        <v>10556858368</v>
+        <v>239932352</v>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H83" s="20" t="n">
-        <v>347.3889692037075</v>
-      </c>
-      <c r="I83" s="20" t="n">
-        <v>68.672195</v>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J83" s="20" t="n">
-        <v>6.6218543</v>
+        <v>1.5673351</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>4.817643283343015</v>
+        <v>1.5660461</v>
       </c>
       <c r="L83" s="21" t="n">
-        <v>-8.42592261675078</v>
-      </c>
-      <c r="M83" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-19.02773752715573</v>
+      </c>
+      <c r="M83" s="21" t="n">
+        <v>5.946712029429071</v>
       </c>
       <c r="N83" s="21" t="n">
-        <v>-0.11123836175898</v>
+        <v>-51.30812980930077</v>
       </c>
       <c r="O83" s="21" t="n">
-        <v>1.17675041790433</v>
-      </c>
-      <c r="P83" s="20" t="n">
-        <v>-59.63858781496614</v>
+        <v>-11.30220868498371</v>
+      </c>
+      <c r="P83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q83" s="21" t="n">
-        <v>7.08</v>
+        <v>38.74</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S83" s="20" t="n">
-        <v>0.3007342710765748</v>
+        <v>0.5298367272208879</v>
       </c>
       <c r="T83" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (38%)</t>
+          <t>Chemicals (62%)</t>
         </is>
       </c>
       <c r="U83" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
+          <t>Chemicals 62%; Biofuels 38%</t>
         </is>
       </c>
       <c r="V83" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W83" s="17" t="inlineStr">
         <is>
-          <t>KZ 84%; AM 8%; CY 7%</t>
+          <t>US 99%; Non Us 1%</t>
         </is>
       </c>
       <c r="X83" s="15" t="inlineStr">
         <is>
-          <t>Other +100%</t>
+          <t>Biofuels +178%</t>
         </is>
       </c>
     </row>
@@ -52400,12 +52392,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>SLNH</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>FutureFuel Corp.</t>
+          <t>Soluna Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -52415,11 +52407,11 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F84" s="18" t="n">
-        <v>239932352</v>
+        <v>291062784</v>
       </c>
       <c r="G84" s="19" t="inlineStr">
         <is>
@@ -52437,22 +52429,24 @@
         </is>
       </c>
       <c r="J84" s="20" t="n">
-        <v>1.5673351</v>
+        <v>1.7097702</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>1.5660461</v>
+        <v>6.9173846</v>
       </c>
       <c r="L84" s="21" t="n">
-        <v>-19.02773752715573</v>
+        <v>-15.20023065482923</v>
       </c>
       <c r="M84" s="21" t="n">
-        <v>5.946712029429071</v>
-      </c>
-      <c r="N84" s="21" t="n">
-        <v>-51.30812980930077</v>
+        <v>0.20077091953947</v>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>-11.30220868498371</v>
+        <v>-104.2041970672814</v>
       </c>
       <c r="P84" s="22" t="inlineStr">
         <is>
@@ -52460,35 +52454,31 @@
         </is>
       </c>
       <c r="Q84" s="21" t="n">
-        <v>38.74</v>
+        <v>-65.62</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S84" s="20" t="n">
-        <v>0.5298367272208879</v>
+        <v>0.5183581202661786</v>
       </c>
       <c r="T84" s="15" t="inlineStr">
         <is>
-          <t>Chemicals (62%)</t>
+          <t>Data Center Hosting (60%)</t>
         </is>
       </c>
       <c r="U84" s="17" t="inlineStr">
         <is>
-          <t>Chemicals 62%; Biofuels 38%</t>
+          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
         </is>
       </c>
       <c r="V84" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W84" s="17" t="inlineStr">
-        <is>
-          <t>US 99%; Non Us 1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W84" s="17" t="n"/>
       <c r="X84" s="15" t="inlineStr">
         <is>
-          <t>Biofuels +178%</t>
+          <t>Data Center Hosting +303%</t>
         </is>
       </c>
     </row>
@@ -52498,12 +52488,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>SLNH</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Soluna Holdings Inc. Common St</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
@@ -52513,78 +52503,74 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F85" s="18" t="n">
-        <v>291062784</v>
+        <v>98965053440</v>
       </c>
       <c r="G85" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H85" s="20" t="n">
+        <v>48.51287624683352</v>
+      </c>
+      <c r="I85" s="20" t="n">
+        <v>58.15837</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>1.7097702</v>
+        <v>20.799417</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>6.9173846</v>
+        <v>8.620950000000001</v>
       </c>
       <c r="L85" s="21" t="n">
-        <v>-15.20023065482923</v>
+        <v>2.71275941299938</v>
       </c>
       <c r="M85" s="21" t="n">
-        <v>0.20077091953947</v>
-      </c>
-      <c r="N85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.03768476778678</v>
+      </c>
+      <c r="N85" s="21" t="n">
+        <v>33.68683344961626</v>
       </c>
       <c r="O85" s="21" t="n">
-        <v>-104.2041970672814</v>
-      </c>
-      <c r="P85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.35492557684859</v>
+      </c>
+      <c r="P85" s="20" t="n">
+        <v>0.3332181723959233</v>
       </c>
       <c r="Q85" s="21" t="n">
-        <v>-65.62</v>
+        <v>45.58</v>
       </c>
       <c r="R85" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S85" s="20" t="n">
-        <v>0.5183581202661786</v>
+        <v>0.5218491323594365</v>
       </c>
       <c r="T85" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting (60%)</t>
+          <t>EMEA (66%)</t>
         </is>
       </c>
       <c r="U85" s="17" t="inlineStr">
         <is>
-          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
+          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
         </is>
       </c>
       <c r="V85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W85" s="17" t="inlineStr">
+        <is>
+          <t>US 59%; Asia 20%; Europe 14%</t>
+        </is>
+      </c>
       <c r="X85" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting +303%</t>
+          <t>Asia Pacific +290%</t>
         </is>
       </c>
     </row>
@@ -52594,12 +52580,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -52609,11 +52595,11 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F86" s="18" t="n">
-        <v>98965053440</v>
+        <v>3749439488</v>
       </c>
       <c r="G86" s="19" t="inlineStr">
         <is>
@@ -52621,62 +52607,58 @@
         </is>
       </c>
       <c r="H86" s="20" t="n">
-        <v>48.51287624683352</v>
+        <v>19.297</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>58.15837</v>
+        <v>30.920187</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>20.799417</v>
+        <v>4.9097958</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>8.620950000000001</v>
+        <v>6.8440413</v>
       </c>
       <c r="L86" s="21" t="n">
-        <v>2.71275941299938</v>
+        <v>5.56871008366637</v>
       </c>
       <c r="M86" s="21" t="n">
-        <v>0.03768476778678</v>
+        <v>0.97</v>
       </c>
       <c r="N86" s="21" t="n">
-        <v>33.68683344961626</v>
+        <v>12.37235274898268</v>
       </c>
       <c r="O86" s="21" t="n">
-        <v>21.35492557684859</v>
+        <v>35.60723129340358</v>
       </c>
       <c r="P86" s="20" t="n">
-        <v>0.3332181723959233</v>
+        <v>1.359732752360203</v>
       </c>
       <c r="Q86" s="21" t="n">
-        <v>45.58</v>
+        <v>17.58</v>
       </c>
       <c r="R86" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S86" s="20" t="n">
-        <v>0.5218491323594365</v>
+        <v>0.4262861010394083</v>
       </c>
       <c r="T86" s="15" t="inlineStr">
         <is>
-          <t>EMEA (66%)</t>
+          <t>Hospitality (52%)</t>
         </is>
       </c>
       <c r="U86" s="17" t="inlineStr">
         <is>
-          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
+          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
         </is>
       </c>
       <c r="V86" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W86" s="17" t="inlineStr">
-        <is>
-          <t>US 59%; Asia 20%; Europe 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W86" s="17" t="n"/>
       <c r="X86" s="15" t="inlineStr">
         <is>
-          <t>Asia Pacific +290%</t>
+          <t>Hospitality +157%</t>
         </is>
       </c>
     </row>
@@ -52686,12 +52668,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>HTLM</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Homestolife Ltd</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
@@ -52701,11 +52683,11 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F87" s="18" t="n">
-        <v>3749439488</v>
+        <v>159643760</v>
       </c>
       <c r="G87" s="19" t="inlineStr">
         <is>
@@ -52713,58 +52695,66 @@
         </is>
       </c>
       <c r="H87" s="20" t="n">
-        <v>19.297</v>
+        <v>5.632</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>30.920187</v>
+        <v>9.368421</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>4.9097958</v>
+        <v>5.189504</v>
       </c>
       <c r="K87" s="20" t="n">
-        <v>6.8440413</v>
+        <v>0.4083795</v>
       </c>
       <c r="L87" s="21" t="n">
-        <v>5.56871008366637</v>
-      </c>
-      <c r="M87" s="21" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N87" s="21" t="n">
-        <v>12.37235274898268</v>
+        <v>7.56174932272778</v>
+      </c>
+      <c r="M87" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>35.60723129340358</v>
+        <v>5.26038476371263</v>
       </c>
       <c r="P87" s="20" t="n">
-        <v>1.359732752360203</v>
+        <v>-0.8495431924900106</v>
       </c>
       <c r="Q87" s="21" t="n">
-        <v>17.58</v>
+        <v>-46.17305967367813</v>
       </c>
       <c r="R87" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S87" s="20" t="n">
-        <v>0.4262861010394083</v>
+        <v>0.8590900293205138</v>
       </c>
       <c r="T87" s="15" t="inlineStr">
         <is>
-          <t>Hospitality (52%)</t>
+          <t>Export Sales (93%)</t>
         </is>
       </c>
       <c r="U87" s="17" t="inlineStr">
         <is>
-          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
+          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
         </is>
       </c>
       <c r="V87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W87" s="17" t="inlineStr">
+        <is>
+          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
+        </is>
+      </c>
       <c r="X87" s="15" t="inlineStr">
         <is>
-          <t>Hospitality +157%</t>
+          <t>Retail Sales +100%</t>
         </is>
       </c>
     </row>
@@ -52774,12 +52764,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Homestolife Ltd</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -52789,11 +52779,11 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F88" s="18" t="n">
-        <v>159643760</v>
+        <v>113033160</v>
       </c>
       <c r="G88" s="19" t="inlineStr">
         <is>
@@ -52801,66 +52791,64 @@
         </is>
       </c>
       <c r="H88" s="20" t="n">
-        <v>5.632</v>
+        <v>11.493</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>9.368421</v>
+        <v>22.772728</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>5.189504</v>
+        <v>1.8398825</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>0.4083795</v>
+        <v>4.0441093</v>
       </c>
       <c r="L88" s="21" t="n">
-        <v>7.56174932272778</v>
+        <v>5.20947381148941</v>
       </c>
       <c r="M88" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N88" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N88" s="21" t="n">
+        <v>16.80549850408138</v>
       </c>
       <c r="O88" s="21" t="n">
-        <v>5.26038476371263</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="P88" s="20" t="n">
-        <v>-0.8495431924900106</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q88" s="21" t="n">
-        <v>-46.17305967367813</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S88" s="20" t="n">
-        <v>0.8590900293205138</v>
+        <v>0.3385873824755823</v>
       </c>
       <c r="T88" s="15" t="inlineStr">
         <is>
-          <t>Export Sales (93%)</t>
+          <t>Defense Engineering Se (45%)</t>
         </is>
       </c>
       <c r="U88" s="17" t="inlineStr">
         <is>
-          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
         </is>
       </c>
       <c r="V88" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W88" s="17" t="inlineStr">
         <is>
-          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
         </is>
       </c>
       <c r="X88" s="15" t="inlineStr">
         <is>
-          <t>Retail Sales +100%</t>
+          <t>Marine Technology Bu +185%</t>
         </is>
       </c>
     </row>
@@ -52870,46 +52858,48 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>Phoenix New Media Limited</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F89" s="18" t="n">
-        <v>113033160</v>
+        <v>17896056</v>
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H89" s="20" t="n">
-        <v>11.493</v>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I89" s="20" t="n">
-        <v>22.772728</v>
+        <v>4.012985014645349</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>1.8398825</v>
+        <v>22.1065917175247</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>4.0441093</v>
+        <v>0.1460944416764449</v>
       </c>
       <c r="L89" s="21" t="n">
-        <v>5.20947381148941</v>
+        <v>-0.32072677140719</v>
       </c>
       <c r="M89" s="22" t="inlineStr">
         <is>
@@ -52917,44 +52907,42 @@
         </is>
       </c>
       <c r="N89" s="21" t="n">
-        <v>16.80549850408138</v>
+        <v>-8.02638700256313</v>
       </c>
       <c r="O89" s="21" t="n">
-        <v>24.49495025980879</v>
-      </c>
-      <c r="P89" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>-1.79463043292417</v>
+      </c>
+      <c r="P89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q89" s="21" t="n">
-        <v>-0.7799999999999999</v>
+        <v>-36.75</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S89" s="20" t="n">
-        <v>0.3385873824755823</v>
+        <v>0.682948135046668</v>
       </c>
       <c r="T89" s="15" t="inlineStr">
         <is>
-          <t>Defense Engineering Se (45%)</t>
+          <t>Net Advertising Servic (80%)</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+          <t>Net Advertising Services 80%; Paid Services 20%</t>
         </is>
       </c>
       <c r="V89" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W89" s="17" t="inlineStr">
-        <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W89" s="17" t="n"/>
       <c r="X89" s="15" t="inlineStr">
         <is>
-          <t>Marine Technology Bu +185%</t>
+          <t>Paid Services +107%</t>
         </is>
       </c>
     </row>
@@ -52964,26 +52952,26 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>FENG</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Phoenix New Media Limited</t>
+          <t>Schrodinger, Inc.</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F90" s="18" t="n">
-        <v>17896056</v>
+        <v>1422803200</v>
       </c>
       <c r="G90" s="19" t="inlineStr">
         <is>
@@ -52995,28 +52983,32 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I90" s="20" t="n">
-        <v>4.012985014645349</v>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J90" s="20" t="n">
-        <v>22.1065917175247</v>
+        <v>4.213558</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>0.1460944416764449</v>
+        <v>5.4927063</v>
       </c>
       <c r="L90" s="21" t="n">
-        <v>-0.32072677140719</v>
+        <v>-8.66829141064739</v>
       </c>
       <c r="M90" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N90" s="21" t="n">
-        <v>-8.02638700256313</v>
+      <c r="N90" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>-1.79463043292417</v>
+        <v>-84.61893927057798</v>
       </c>
       <c r="P90" s="22" t="inlineStr">
         <is>
@@ -53024,31 +53016,35 @@
         </is>
       </c>
       <c r="Q90" s="21" t="n">
-        <v>-36.75</v>
+        <v>-4.52</v>
       </c>
       <c r="R90" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="20" t="n">
-        <v>0.682948135046668</v>
+        <v>0.6564595481920475</v>
       </c>
       <c r="T90" s="15" t="inlineStr">
         <is>
-          <t>Net Advertising Servic (80%)</t>
+          <t>Software (78%)</t>
         </is>
       </c>
       <c r="U90" s="17" t="inlineStr">
         <is>
-          <t>Net Advertising Services 80%; Paid Services 20%</t>
+          <t>Software 78%; Drug Discovery 22%</t>
         </is>
       </c>
       <c r="V90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W90" s="17" t="inlineStr">
+        <is>
+          <t>US 60%; EMEA 29%; APAC 10%</t>
+        </is>
+      </c>
       <c r="X90" s="15" t="inlineStr">
         <is>
-          <t>Paid Services +107%</t>
+          <t>Drug Discovery +107%</t>
         </is>
       </c>
     </row>
@@ -53058,12 +53054,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Schrodinger, Inc.</t>
+          <t>Jefferies Financial Group Inc.</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
@@ -53073,84 +53069,74 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F91" s="18" t="n">
-        <v>1422803200</v>
+        <v>10568248320</v>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H91" s="20" t="n">
+        <v>-37.43331715008421</v>
+      </c>
+      <c r="I91" s="20" t="n">
+        <v>27.1789460083687</v>
       </c>
       <c r="J91" s="20" t="n">
-        <v>4.213558</v>
+        <v>1.0001347</v>
       </c>
       <c r="K91" s="20" t="n">
-        <v>5.4927063</v>
+        <v>1.9561423</v>
       </c>
       <c r="L91" s="21" t="n">
-        <v>-8.66829141064739</v>
-      </c>
-      <c r="M91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.83374525401008</v>
+      </c>
+      <c r="M91" s="21" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N91" s="21" t="n">
+        <v>-0.21791453369172</v>
       </c>
       <c r="O91" s="21" t="n">
-        <v>-84.61893927057798</v>
-      </c>
-      <c r="P91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.51745776158655</v>
+      </c>
+      <c r="P91" s="20" t="n">
+        <v>-80.28756909079929</v>
       </c>
       <c r="Q91" s="21" t="n">
-        <v>-4.52</v>
+        <v>7.7</v>
       </c>
       <c r="R91" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>0.6564595481920475</v>
+        <v>0.8308945641579533</v>
       </c>
       <c r="T91" s="15" t="inlineStr">
         <is>
-          <t>Software (78%)</t>
+          <t>Investment Banking And (91%)</t>
         </is>
       </c>
       <c r="U91" s="17" t="inlineStr">
         <is>
-          <t>Software 78%; Drug Discovery 22%</t>
+          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
         </is>
       </c>
       <c r="V91" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W91" s="17" t="inlineStr">
         <is>
-          <t>US 60%; EMEA 29%; APAC 10%</t>
+          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
         </is>
       </c>
       <c r="X91" s="15" t="inlineStr">
         <is>
-          <t>Drug Discovery +107%</t>
+          <t>Investment Banking A +123%</t>
         </is>
       </c>
     </row>
@@ -53160,12 +53146,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>ANNA</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc.</t>
+          <t>AleAnna Inc. Class A Common St</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -53175,74 +53161,72 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>10568248320</v>
-      </c>
-      <c r="G92" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>143290000</v>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>-37.43331715008421</v>
+        <v>8.568</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>27.1789460083687</v>
+        <v>18.421053</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>1.0001347</v>
+        <v>3.5425103</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>1.9561423</v>
+        <v>3.5894861</v>
       </c>
       <c r="L92" s="21" t="n">
-        <v>16.83374525401008</v>
-      </c>
-      <c r="M92" s="21" t="n">
-        <v>3.26</v>
+        <v>7.167953799986041</v>
+      </c>
+      <c r="M92" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N92" s="21" t="n">
-        <v>-0.21791453369172</v>
+        <v>1.46144795620644</v>
       </c>
       <c r="O92" s="21" t="n">
-        <v>5.51745776158655</v>
+        <v>39.48335699937504</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>-80.28756909079929</v>
+        <v>-1.974742069364569</v>
       </c>
       <c r="Q92" s="21" t="n">
-        <v>7.7</v>
+        <v>-7.69</v>
       </c>
       <c r="R92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S92" s="20" t="n">
-        <v>0.8308945641579533</v>
+        <v>0.8097190789385638</v>
       </c>
       <c r="T92" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking And (91%)</t>
+          <t>Conventional (89%)</t>
         </is>
       </c>
       <c r="U92" s="17" t="inlineStr">
         <is>
-          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
+          <t>Conventional 89%; Renewable 11%</t>
         </is>
       </c>
       <c r="V92" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W92" s="17" t="inlineStr">
-        <is>
-          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W92" s="17" t="n"/>
       <c r="X92" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking A +123%</t>
+          <t>Conventional +186%</t>
         </is>
       </c>
     </row>
@@ -53252,12 +53236,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>ANNA</t>
+          <t>LVWR</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>AleAnna Inc. Class A Common St</t>
+          <t>LiveWire Group Inc. Common Sto</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -53267,72 +53251,84 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>143290000</v>
-      </c>
-      <c r="G93" s="23" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="n">
-        <v>8.568</v>
-      </c>
-      <c r="I93" s="20" t="n">
-        <v>18.421053</v>
+        <v>234170208</v>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J93" s="20" t="n">
-        <v>3.5425103</v>
+        <v>19.655172</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>3.5894861</v>
+        <v>7.484824</v>
       </c>
       <c r="L93" s="21" t="n">
-        <v>7.167953799986041</v>
+        <v>-21.59336790483196</v>
       </c>
       <c r="M93" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N93" s="21" t="n">
-        <v>1.46144795620644</v>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>39.48335699937504</v>
-      </c>
-      <c r="P93" s="20" t="n">
-        <v>-1.974742069364569</v>
+        <v>-207.6711628204309</v>
+      </c>
+      <c r="P93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q93" s="21" t="n">
-        <v>-7.69</v>
+        <v>-76.64</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>0.8097190789385638</v>
+        <v>0.4547555777310531</v>
       </c>
       <c r="T93" s="15" t="inlineStr">
         <is>
-          <t>Conventional (89%)</t>
+          <t>STACYC (62%)</t>
         </is>
       </c>
       <c r="U93" s="17" t="inlineStr">
         <is>
-          <t>Conventional 89%; Renewable 11%</t>
+          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
         </is>
       </c>
       <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W93" s="17" t="inlineStr">
+        <is>
+          <t>US 74%; Non Us 24%; AT 2%</t>
+        </is>
+      </c>
       <c r="X93" s="15" t="inlineStr">
         <is>
-          <t>Conventional +186%</t>
+          <t>Electric Motorcycle +333%</t>
         </is>
       </c>
     </row>
@@ -53342,12 +53338,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>LVWR</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>LiveWire Group Inc. Common Sto</t>
+          <t>Assured Guaranty Ltd</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -53357,11 +53353,11 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>234170208</v>
+        <v>3207403776</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
@@ -53373,24 +53369,20 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I94" s="20" t="n">
+        <v>9.698138</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>19.655172</v>
+        <v>0.57766795</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>7.484824</v>
+        <v>2.931813323583181</v>
       </c>
       <c r="L94" s="21" t="n">
-        <v>-21.59336790483196</v>
-      </c>
-      <c r="M94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.10162806517815</v>
+      </c>
+      <c r="M94" s="21" t="n">
+        <v>1.91</v>
       </c>
       <c r="N94" s="22" t="inlineStr">
         <is>
@@ -53398,7 +53390,7 @@
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>-207.6711628204309</v>
+        <v>0</v>
       </c>
       <c r="P94" s="22" t="inlineStr">
         <is>
@@ -53406,35 +53398,35 @@
         </is>
       </c>
       <c r="Q94" s="21" t="n">
-        <v>-76.64</v>
+        <v>-4.7</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>0.4547555777310531</v>
+        <v>0.9375650364203956</v>
       </c>
       <c r="T94" s="15" t="inlineStr">
         <is>
-          <t>STACYC (62%)</t>
+          <t>Insurance (97%)</t>
         </is>
       </c>
       <c r="U94" s="17" t="inlineStr">
         <is>
-          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
+          <t>Insurance 97%; Asset Management 3%</t>
         </is>
       </c>
       <c r="V94" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W94" s="17" t="inlineStr">
         <is>
-          <t>US 74%; Non Us 24%; AT 2%</t>
+          <t>US 77%; BM 18%; GB 5%</t>
         </is>
       </c>
       <c r="X94" s="15" t="inlineStr">
         <is>
-          <t>Electric Motorcycle +333%</t>
+          <t>Asset Management +190%</t>
         </is>
       </c>
     </row>
@@ -53444,12 +53436,12 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>KTB</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd</t>
+          <t>Kontoor Brands, Inc.</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
@@ -53459,80 +53451,74 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>3207403776</v>
+        <v>3641024256</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H95" s="20" t="n">
+        <v>11.55529127502649</v>
       </c>
       <c r="I95" s="20" t="n">
-        <v>9.698138</v>
+        <v>13.48583</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>0.57766795</v>
+        <v>5.8861995</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>2.931813323583181</v>
+        <v>1.0601529</v>
       </c>
       <c r="L95" s="21" t="n">
-        <v>10.10162806517815</v>
+        <v>10.52193541631924</v>
       </c>
       <c r="M95" s="21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="N95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.91957418972506</v>
+      </c>
+      <c r="N95" s="21" t="n">
+        <v>17.92240674479327</v>
       </c>
       <c r="O95" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>13.30013869457824</v>
+      </c>
+      <c r="P95" s="20" t="n">
+        <v>2.601238735236491</v>
       </c>
       <c r="Q95" s="21" t="n">
-        <v>-4.7</v>
+        <v>-7.049999999999999</v>
       </c>
       <c r="R95" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S95" s="20" t="n">
+        <v>0.4547588013008751</v>
+      </c>
+      <c r="T95" s="15" t="inlineStr">
+        <is>
+          <t>Wrangler (61%)</t>
+        </is>
+      </c>
+      <c r="U95" s="17" t="inlineStr">
+        <is>
+          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+        </is>
+      </c>
+      <c r="V95" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S95" s="20" t="n">
-        <v>0.9375650364203956</v>
-      </c>
-      <c r="T95" s="15" t="inlineStr">
-        <is>
-          <t>Insurance (97%)</t>
-        </is>
-      </c>
-      <c r="U95" s="17" t="inlineStr">
-        <is>
-          <t>Insurance 97%; Asset Management 3%</t>
-        </is>
-      </c>
-      <c r="V95" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="W95" s="17" t="inlineStr">
         <is>
-          <t>US 77%; BM 18%; GB 5%</t>
+          <t>US 73%; Non Us 27%</t>
         </is>
       </c>
       <c r="X95" s="15" t="inlineStr">
         <is>
-          <t>Asset Management +190%</t>
+          <t>Helly Hansen +300%</t>
         </is>
       </c>
     </row>
@@ -53542,12 +53528,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>KTB</t>
+          <t>PED</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Kontoor Brands, Inc.</t>
+          <t>PEDEVCO Corp.</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -53557,11 +53543,11 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F96" s="18" t="n">
-        <v>3641024256</v>
+        <v>197253472</v>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
@@ -53569,62 +53555,62 @@
         </is>
       </c>
       <c r="H96" s="20" t="n">
-        <v>11.55529127502649</v>
-      </c>
-      <c r="I96" s="20" t="n">
-        <v>13.48583</v>
+        <v>4.59</v>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J96" s="20" t="n">
-        <v>5.8861995</v>
+        <v>0.9859154999999999</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1.0601529</v>
+        <v>1.6949378</v>
       </c>
       <c r="L96" s="21" t="n">
-        <v>10.52193541631924</v>
-      </c>
-      <c r="M96" s="21" t="n">
-        <v>2.91957418972506</v>
+        <v>16.30471233572627</v>
+      </c>
+      <c r="M96" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N96" s="21" t="n">
-        <v>17.92240674479327</v>
+        <v>2.16353455637511</v>
       </c>
       <c r="O96" s="21" t="n">
-        <v>13.30013869457824</v>
+        <v>49.94500678822457</v>
       </c>
       <c r="P96" s="20" t="n">
-        <v>2.601238735236491</v>
+        <v>1.332008602150538</v>
       </c>
       <c r="Q96" s="21" t="n">
-        <v>-7.049999999999999</v>
+        <v>18.91</v>
       </c>
       <c r="R96" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S96" s="20" t="n">
-        <v>0.4547588013008751</v>
+        <v>0.7805028355388554</v>
       </c>
       <c r="T96" s="15" t="inlineStr">
         <is>
-          <t>Wrangler (61%)</t>
+          <t>Oil Sales (88%)</t>
         </is>
       </c>
       <c r="U96" s="17" t="inlineStr">
         <is>
-          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
         </is>
       </c>
       <c r="V96" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W96" s="17" t="inlineStr">
-        <is>
-          <t>US 73%; Non Us 27%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W96" s="17" t="n"/>
       <c r="X96" s="15" t="inlineStr">
         <is>
-          <t>Helly Hansen +300%</t>
+          <t>Natural Gas Liquids  +465%</t>
         </is>
       </c>
     </row>
@@ -53634,12 +53620,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>PED</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>PEDEVCO Corp.</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
@@ -53649,11 +53635,11 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F97" s="18" t="n">
-        <v>197253472</v>
+        <v>1101452017664</v>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
@@ -53661,62 +53647,62 @@
         </is>
       </c>
       <c r="H97" s="20" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I97" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>15.852</v>
+      </c>
+      <c r="I97" s="20" t="n">
+        <v>22.024843</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>0.9859154999999999</v>
+        <v>10.93157</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>1.6949378</v>
+        <v>12.20121</v>
       </c>
       <c r="L97" s="21" t="n">
-        <v>16.30471233572627</v>
-      </c>
-      <c r="M97" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.27953325914988</v>
+      </c>
+      <c r="M97" s="21" t="n">
+        <v>0.05</v>
       </c>
       <c r="N97" s="21" t="n">
-        <v>2.16353455637511</v>
+        <v>38.68963277836816</v>
       </c>
       <c r="O97" s="21" t="n">
-        <v>49.94500678822457</v>
+        <v>63.47412363053029</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.332008602150538</v>
+        <v>-0.1351809304997128</v>
       </c>
       <c r="Q97" s="21" t="n">
-        <v>18.91</v>
+        <v>354.75</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S97" s="20" t="n">
-        <v>0.7805028355388554</v>
+        <v>0.2853460159862896</v>
       </c>
       <c r="T97" s="15" t="inlineStr">
         <is>
-          <t>Oil Sales (88%)</t>
+          <t>CMBU (36%)</t>
         </is>
       </c>
       <c r="U97" s="17" t="inlineStr">
         <is>
-          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
+          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
         </is>
       </c>
       <c r="V97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="W97" s="17" t="inlineStr">
+        <is>
+          <t>US 65%; TW 15%; CN 7%</t>
+        </is>
+      </c>
       <c r="X97" s="15" t="inlineStr">
         <is>
-          <t>Natural Gas Liquids  +465%</t>
+          <t>AEBU +311%</t>
         </is>
       </c>
     </row>
@@ -53726,12 +53712,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>EVC</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Entravision Communications Cor</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -53741,11 +53727,11 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F98" s="18" t="n">
-        <v>1101452017664</v>
+        <v>794602240</v>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
@@ -53753,62 +53739,62 @@
         </is>
       </c>
       <c r="H98" s="20" t="n">
-        <v>15.852</v>
+        <v>27.53410143448773</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>22.024843</v>
+        <v>190.0388450278689</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>10.93157</v>
+        <v>9.503311</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>12.20121</v>
+        <v>1.557472534580458</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>2.27953325914988</v>
+        <v>8.44176513325125</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>0.05</v>
+        <v>2.57525386044693</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>38.68963277836816</v>
+        <v>-26.42668897457025</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>63.47412363053029</v>
+        <v>6.53133066895079</v>
       </c>
       <c r="P98" s="20" t="n">
-        <v>-0.1351809304997128</v>
+        <v>2.821679370986135</v>
       </c>
       <c r="Q98" s="21" t="n">
-        <v>354.75</v>
+        <v>322.51</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S98" s="20" t="n">
-        <v>0.2853460159862896</v>
+        <v>0.5221821576458947</v>
       </c>
       <c r="T98" s="15" t="inlineStr">
         <is>
-          <t>CMBU (36%)</t>
+          <t>Advertising Technology (61%)</t>
         </is>
       </c>
       <c r="U98" s="17" t="inlineStr">
         <is>
-          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
+          <t>Advertising Technology And Services 61%; Media 39%</t>
         </is>
       </c>
       <c r="V98" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W98" s="17" t="inlineStr">
         <is>
-          <t>US 65%; TW 15%; CN 7%</t>
+          <t>US 58%; Non Us 42%</t>
         </is>
       </c>
       <c r="X98" s="15" t="inlineStr">
         <is>
-          <t>AEBU +311%</t>
+          <t>Advertising Technolo +230%</t>
         </is>
       </c>
     </row>
@@ -53818,12 +53804,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>EVC</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Entravision Communications Cor</t>
+          <t>Compass, Inc.</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
@@ -53833,11 +53819,11 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F99" s="18" t="n">
-        <v>794602240</v>
+        <v>8067944960</v>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
@@ -53845,62 +53831,62 @@
         </is>
       </c>
       <c r="H99" s="20" t="n">
-        <v>27.53410143448773</v>
+        <v>120.5991376271186</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>190.0388450278689</v>
+        <v>119.5251105185185</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>9.503311</v>
+        <v>2.6573958</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>1.557472534580458</v>
+        <v>1.012822938060207</v>
       </c>
       <c r="L99" s="21" t="n">
-        <v>8.44176513325125</v>
-      </c>
-      <c r="M99" s="21" t="n">
-        <v>2.57525386044693</v>
+        <v>1.5004325303195</v>
+      </c>
+      <c r="M99" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N99" s="21" t="n">
-        <v>-26.42668897457025</v>
+        <v>-6.802410518626729</v>
       </c>
       <c r="O99" s="21" t="n">
-        <v>6.53133066895079</v>
-      </c>
-      <c r="P99" s="20" t="n">
-        <v>2.821679370986135</v>
+        <v>1.1850661578247</v>
+      </c>
+      <c r="P99" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q99" s="21" t="n">
-        <v>322.51</v>
+        <v>44.23</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S99" s="20" t="n">
-        <v>0.5221821576458947</v>
+        <v>0.8491346718272323</v>
       </c>
       <c r="T99" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technology (61%)</t>
+          <t>Brokerage (92%)</t>
         </is>
       </c>
       <c r="U99" s="17" t="inlineStr">
         <is>
-          <t>Advertising Technology And Services 61%; Media 39%</t>
+          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
         </is>
       </c>
       <c r="V99" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W99" s="17" t="inlineStr">
-        <is>
-          <t>US 58%; Non Us 42%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W99" s="17" t="n"/>
       <c r="X99" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technolo +230%</t>
+          <t>Brokerage +97%</t>
         </is>
       </c>
     </row>
@@ -53910,12 +53896,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Compass, Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -53925,11 +53911,11 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F100" s="18" t="n">
-        <v>8067944960</v>
+        <v>419900817408</v>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
@@ -53937,53 +53923,49 @@
         </is>
       </c>
       <c r="H100" s="20" t="n">
-        <v>120.5991376271186</v>
+        <v>8.913</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>119.5251105185185</v>
+        <v>20.62235</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>2.6573958</v>
+        <v>2.2113636</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1.012822938060207</v>
+        <v>2.0054102</v>
       </c>
       <c r="L100" s="21" t="n">
-        <v>1.5004325303195</v>
-      </c>
-      <c r="M100" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.60132683312082</v>
+      </c>
+      <c r="M100" s="21" t="n">
+        <v>4.16</v>
       </c>
       <c r="N100" s="21" t="n">
-        <v>-6.802410518626729</v>
+        <v>8.69285484505129</v>
       </c>
       <c r="O100" s="21" t="n">
-        <v>1.1850661578247</v>
-      </c>
-      <c r="P100" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.36304851872374</v>
+      </c>
+      <c r="P100" s="20" t="n">
+        <v>0.9647582391147462</v>
       </c>
       <c r="Q100" s="21" t="n">
-        <v>44.23</v>
+        <v>37.47</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S100" s="20" t="n">
-        <v>0.8491346718272323</v>
+        <v>0.9067367242961308</v>
       </c>
       <c r="T100" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (92%)</t>
+          <t>Upstream (95%)</t>
         </is>
       </c>
       <c r="U100" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
+          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
         </is>
       </c>
       <c r="V100" s="18" t="n">
@@ -53992,7 +53974,7 @@
       <c r="W100" s="17" t="n"/>
       <c r="X100" s="15" t="inlineStr">
         <is>
-          <t>Brokerage +97%</t>
+          <t>Upstream +298%</t>
         </is>
       </c>
     </row>
@@ -54002,12 +53984,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Northrop Grumman Corp.</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
@@ -54017,11 +53999,11 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F101" s="18" t="n">
-        <v>419900817408</v>
+        <v>73726443520</v>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
@@ -54029,58 +54011,62 @@
         </is>
       </c>
       <c r="H101" s="20" t="n">
-        <v>8.913</v>
+        <v>15.61168969542968</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>20.62235</v>
+        <v>16.501429</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>2.2113636</v>
+        <v>4.1224737</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>2.0054102</v>
+        <v>1.7188857</v>
       </c>
       <c r="L101" s="21" t="n">
-        <v>6.60132683312082</v>
+        <v>4.9836238568399</v>
       </c>
       <c r="M101" s="21" t="n">
-        <v>4.16</v>
+        <v>1.505494379293</v>
       </c>
       <c r="N101" s="21" t="n">
-        <v>8.69285484505129</v>
+        <v>14.00609392594555</v>
       </c>
       <c r="O101" s="21" t="n">
-        <v>22.36304851872374</v>
+        <v>13.37597658555007</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>0.9647582391147462</v>
+        <v>2.307923063349215</v>
       </c>
       <c r="Q101" s="21" t="n">
-        <v>37.47</v>
+        <v>-10.3</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S101" s="20" t="n">
-        <v>0.9067367242961308</v>
+        <v>0.4182092579820682</v>
       </c>
       <c r="T101" s="15" t="inlineStr">
         <is>
-          <t>Upstream (95%)</t>
+          <t>Mission Systems (58%)</t>
         </is>
       </c>
       <c r="U101" s="17" t="inlineStr">
         <is>
-          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
+          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
         </is>
       </c>
       <c r="V101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W101" s="17" t="inlineStr">
+        <is>
+          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
+        </is>
+      </c>
       <c r="X101" s="15" t="inlineStr">
         <is>
-          <t>Upstream +298%</t>
+          <t>Aeronautics Systems +130%</t>
         </is>
       </c>
     </row>
@@ -54090,12 +54076,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>JBI</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp.</t>
+          <t>Janus International Group, Inc</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -54109,7 +54095,7 @@
         </is>
       </c>
       <c r="F102" s="18" t="n">
-        <v>73726443520</v>
+        <v>626240320</v>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
@@ -54117,62 +54103,64 @@
         </is>
       </c>
       <c r="H102" s="20" t="n">
-        <v>15.61168969542968</v>
+        <v>7.682</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>16.501429</v>
+        <v>19.125002</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>4.1224737</v>
+        <v>1.0949428</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>1.7188857</v>
+        <v>0.6944337</v>
       </c>
       <c r="L102" s="21" t="n">
-        <v>4.9836238568399</v>
-      </c>
-      <c r="M102" s="21" t="n">
-        <v>1.505494379293</v>
+        <v>11.5960907053962</v>
+      </c>
+      <c r="M102" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N102" s="21" t="n">
-        <v>14.00609392594555</v>
+        <v>10.43425814234016</v>
       </c>
       <c r="O102" s="21" t="n">
-        <v>13.37597658555007</v>
+        <v>16.54553713377242</v>
       </c>
       <c r="P102" s="20" t="n">
-        <v>2.307923063349215</v>
+        <v>2.983527796842828</v>
       </c>
       <c r="Q102" s="21" t="n">
-        <v>-10.3</v>
+        <v>-46.98</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S102" s="20" t="n">
-        <v>0.4182092579820682</v>
+        <v>0.6354742392804635</v>
       </c>
       <c r="T102" s="15" t="inlineStr">
         <is>
-          <t>Mission Systems (58%)</t>
+          <t>Janus North America (76%)</t>
         </is>
       </c>
       <c r="U102" s="17" t="inlineStr">
         <is>
-          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
+          <t>Janus North America 76%; Janus International 24%</t>
         </is>
       </c>
       <c r="V102" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W102" s="17" t="inlineStr">
         <is>
-          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
+          <t>US 88%; Non Us 12%</t>
         </is>
       </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
-          <t>Aeronautics Systems +130%</t>
+          <t>Janus International +300%</t>
         </is>
       </c>
     </row>
@@ -54182,12 +54170,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>JBI</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Janus International Group, Inc</t>
+          <t>Flotek Industries, Inc.</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
@@ -54197,11 +54185,11 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F103" s="18" t="n">
-        <v>626240320</v>
+        <v>989904320</v>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
@@ -54209,19 +54197,19 @@
         </is>
       </c>
       <c r="H103" s="20" t="n">
-        <v>7.682</v>
+        <v>25.626</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>19.125002</v>
+        <v>27.059406</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>1.0949428</v>
+        <v>7.6511755</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>0.6944337</v>
+        <v>3.3788822</v>
       </c>
       <c r="L103" s="21" t="n">
-        <v>11.5960907053962</v>
+        <v>-0.34082822017504</v>
       </c>
       <c r="M103" s="22" t="inlineStr">
         <is>
@@ -54229,44 +54217,44 @@
         </is>
       </c>
       <c r="N103" s="21" t="n">
-        <v>10.43425814234016</v>
+        <v>16.13992919089226</v>
       </c>
       <c r="O103" s="21" t="n">
-        <v>16.54553713377242</v>
+        <v>17.18227107585707</v>
       </c>
       <c r="P103" s="20" t="n">
-        <v>2.983527796842828</v>
+        <v>0.8771800721171535</v>
       </c>
       <c r="Q103" s="21" t="n">
-        <v>-46.98</v>
+        <v>35.99</v>
       </c>
       <c r="R103" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S103" s="20" t="n">
-        <v>0.6354742392804635</v>
+        <v>0.7993939775957156</v>
       </c>
       <c r="T103" s="15" t="inlineStr">
         <is>
-          <t>Janus North America (76%)</t>
+          <t>Chemistry Technologies (89%)</t>
         </is>
       </c>
       <c r="U103" s="17" t="inlineStr">
         <is>
-          <t>Janus North America 76%; Janus International 24%</t>
+          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
         </is>
       </c>
       <c r="V103" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W103" s="17" t="inlineStr">
         <is>
-          <t>US 88%; Non Us 12%</t>
+          <t>US 95%; AE 4%; Non Us 1%</t>
         </is>
       </c>
       <c r="X103" s="15" t="inlineStr">
         <is>
-          <t>Janus International +300%</t>
+          <t>Data Analytics +115%</t>
         </is>
       </c>
     </row>
@@ -54276,12 +54264,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Flotek Industries, Inc.</t>
+          <t>Royal Gold, Inc.</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -54291,11 +54279,11 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F104" s="18" t="n">
-        <v>989904320</v>
+        <v>21375143936</v>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
@@ -54303,64 +54291,62 @@
         </is>
       </c>
       <c r="H104" s="20" t="n">
-        <v>25.626</v>
+        <v>17.093</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>27.059406</v>
+        <v>27.90708</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>7.6511755</v>
+        <v>2.8154993</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>3.3788822</v>
+        <v>13.9189825</v>
       </c>
       <c r="L104" s="21" t="n">
-        <v>-0.34082822017504</v>
-      </c>
-      <c r="M104" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.00273682367590865</v>
+      </c>
+      <c r="M104" s="21" t="n">
+        <v>0.91</v>
       </c>
       <c r="N104" s="21" t="n">
-        <v>16.13992919089226</v>
+        <v>10.262897771322</v>
       </c>
       <c r="O104" s="21" t="n">
-        <v>17.18227107585707</v>
+        <v>79.09251477040698</v>
       </c>
       <c r="P104" s="20" t="n">
-        <v>0.8771800721171535</v>
+        <v>0.3499720252373015</v>
       </c>
       <c r="Q104" s="21" t="n">
-        <v>35.99</v>
+        <v>50.91</v>
       </c>
       <c r="R104" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S104" s="20" t="n">
-        <v>0.7993939775957156</v>
+        <v>0.5688010724435794</v>
       </c>
       <c r="T104" s="15" t="inlineStr">
         <is>
-          <t>Chemistry Technologies (89%)</t>
+          <t>Royalty Interest (69%)</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
         <is>
-          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
+          <t>Royalty Interest 69%; Stream Interest 31%</t>
         </is>
       </c>
       <c r="V104" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W104" s="17" t="inlineStr">
         <is>
-          <t>US 95%; AE 4%; Non Us 1%</t>
+          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
         </is>
       </c>
       <c r="X104" s="15" t="inlineStr">
         <is>
-          <t>Data Analytics +115%</t>
+          <t>Stream Interest +133%</t>
         </is>
       </c>
     </row>
@@ -54370,12 +54356,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Royal Gold, Inc.</t>
+          <t>Riot Blockchain, Inc.</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
@@ -54385,74 +54371,76 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F105" s="18" t="n">
-        <v>21375143936</v>
+        <v>8056809472</v>
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H105" s="20" t="n">
-        <v>17.093</v>
-      </c>
-      <c r="I105" s="20" t="n">
-        <v>27.90708</v>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J105" s="20" t="n">
-        <v>2.8154993</v>
+        <v>3.7017238</v>
       </c>
       <c r="K105" s="20" t="n">
-        <v>13.9189825</v>
+        <v>11.944614</v>
       </c>
       <c r="L105" s="21" t="n">
-        <v>0.00273682367590865</v>
+        <v>-6.33617127278794</v>
       </c>
       <c r="M105" s="21" t="n">
-        <v>0.91</v>
+        <v>0.10325461151742</v>
       </c>
       <c r="N105" s="21" t="n">
-        <v>10.262897771322</v>
+        <v>-14.43474531538664</v>
       </c>
       <c r="O105" s="21" t="n">
-        <v>79.09251477040698</v>
-      </c>
-      <c r="P105" s="20" t="n">
-        <v>0.3499720252373015</v>
+        <v>-137.6062161413327</v>
+      </c>
+      <c r="P105" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q105" s="21" t="n">
-        <v>50.91</v>
+        <v>10.21</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S105" s="20" t="n">
-        <v>0.5688010724435794</v>
+        <v>0.4395096928547909</v>
       </c>
       <c r="T105" s="15" t="inlineStr">
         <is>
-          <t>Royalty Interest (69%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U105" s="17" t="inlineStr">
         <is>
-          <t>Royalty Interest 69%; Stream Interest 31%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
         </is>
       </c>
       <c r="V105" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W105" s="17" t="inlineStr">
-        <is>
-          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W105" s="17" t="n"/>
       <c r="X105" s="15" t="inlineStr">
         <is>
-          <t>Stream Interest +133%</t>
+          <t>Engineering +196%</t>
         </is>
       </c>
     </row>
@@ -54462,12 +54450,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Riot Blockchain, Inc.</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
@@ -54481,72 +54469,70 @@
         </is>
       </c>
       <c r="F106" s="18" t="n">
-        <v>8056809472</v>
+        <v>77146587136</v>
       </c>
       <c r="G106" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H106" s="20" t="n">
+        <v>29.95255477105907</v>
+      </c>
+      <c r="I106" s="20" t="n">
+        <v>36.676632</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>3.7017238</v>
+        <v>28.873335</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>11.944614</v>
+        <v>6.304371</v>
       </c>
       <c r="L106" s="21" t="n">
-        <v>-6.33617127278794</v>
+        <v>3.45600557054743</v>
       </c>
       <c r="M106" s="21" t="n">
-        <v>0.10325461151742</v>
+        <v>1.11367051765181</v>
       </c>
       <c r="N106" s="21" t="n">
-        <v>-14.43474531538664</v>
+        <v>24.18337569424833</v>
       </c>
       <c r="O106" s="21" t="n">
-        <v>-137.6062161413327</v>
-      </c>
-      <c r="P106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.10684192787327</v>
+      </c>
+      <c r="P106" s="20" t="n">
+        <v>2.823837818944425</v>
       </c>
       <c r="Q106" s="21" t="n">
-        <v>10.21</v>
+        <v>16.12</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S106" s="20" t="n">
-        <v>0.4395096928547909</v>
+        <v>0.5307180948206589</v>
       </c>
       <c r="T106" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Product And Systems In (62%)</t>
         </is>
       </c>
       <c r="U106" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
+          <t>Product And Systems Integration 62%; Services And Software 38%</t>
         </is>
       </c>
       <c r="V106" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" s="17" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="W106" s="17" t="inlineStr">
+        <is>
+          <t>North America 36%; US 34%; International 14%</t>
+        </is>
+      </c>
       <c r="X106" s="15" t="inlineStr">
         <is>
-          <t>Engineering +196%</t>
+          <t>Product And Systems  +176%</t>
         </is>
       </c>
     </row>
@@ -54556,12 +54542,12 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Firy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
@@ -54575,70 +54561,80 @@
         </is>
       </c>
       <c r="F107" s="18" t="n">
-        <v>77146587136</v>
+        <v>163180000</v>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H107" s="20" t="n">
-        <v>29.95255477105907</v>
-      </c>
-      <c r="I107" s="20" t="n">
-        <v>36.676632</v>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J107" s="20" t="n">
-        <v>28.873335</v>
+        <v>1.931855850736373</v>
       </c>
       <c r="K107" s="20" t="n">
-        <v>6.304371</v>
+        <v>1.3889787</v>
       </c>
       <c r="L107" s="21" t="n">
-        <v>3.45600557054743</v>
-      </c>
-      <c r="M107" s="21" t="n">
-        <v>1.11367051765181</v>
-      </c>
-      <c r="N107" s="21" t="n">
-        <v>24.18337569424833</v>
+        <v>-42.19957624057978</v>
+      </c>
+      <c r="M107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>24.10684192787327</v>
-      </c>
-      <c r="P107" s="20" t="n">
-        <v>2.823837818944425</v>
+        <v>-60.47052925589057</v>
+      </c>
+      <c r="P107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q107" s="21" t="n">
-        <v>16.12</v>
+        <v>51.65</v>
       </c>
       <c r="R107" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S107" s="20" t="n">
-        <v>0.5307180948206589</v>
+        <v>0.619776729861528</v>
       </c>
       <c r="T107" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems In (62%)</t>
+          <t>Skillz (74%)</t>
         </is>
       </c>
       <c r="U107" s="17" t="inlineStr">
         <is>
-          <t>Product And Systems Integration 62%; Services And Software 38%</t>
+          <t>Skillz 74%; RZR 26%</t>
         </is>
       </c>
       <c r="V107" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W107" s="17" t="inlineStr">
         <is>
-          <t>North America 36%; US 34%; International 14%</t>
+          <t>US 76%; Non Us 6%; CY 4%</t>
         </is>
       </c>
       <c r="X107" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems  +176%</t>
+          <t>RZR +146%</t>
         </is>
       </c>
     </row>
@@ -54648,12 +54644,12 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Firy Inc. Class A Common Stock</t>
+          <t>Energy Transfer Lp</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
@@ -54663,84 +54659,70 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F108" s="18" t="n">
-        <v>163180000</v>
+        <v>74203103232</v>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H108" s="20" t="n">
+        <v>9.459</v>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>14.760273</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>1.931855850736373</v>
+        <v>1.491909508655528</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>1.3889787</v>
+        <v>0.69103926</v>
       </c>
       <c r="L108" s="21" t="n">
-        <v>-42.19957624057978</v>
-      </c>
-      <c r="M108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.04975512768092</v>
+      </c>
+      <c r="M108" s="21" t="n">
+        <v>6.959999999999999</v>
+      </c>
+      <c r="N108" s="21" t="n">
+        <v>8.4099490357427</v>
       </c>
       <c r="O108" s="21" t="n">
-        <v>-60.47052925589057</v>
-      </c>
-      <c r="P108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>17.85263732142248</v>
+      </c>
+      <c r="P108" s="20" t="n">
+        <v>4.353514132925898</v>
       </c>
       <c r="Q108" s="21" t="n">
-        <v>51.65</v>
+        <v>37.32</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S108" s="20" t="n">
-        <v>0.619776729861528</v>
+        <v>0.2291888064107961</v>
       </c>
       <c r="T108" s="15" t="inlineStr">
         <is>
-          <t>Skillz (74%)</t>
+          <t>Crudeoiltransportation (27%)</t>
         </is>
       </c>
       <c r="U108" s="17" t="inlineStr">
         <is>
-          <t>Skillz 74%; RZR 26%</t>
+          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
         </is>
       </c>
       <c r="V108" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W108" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; Non Us 6%; CY 4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W108" s="17" t="n"/>
       <c r="X108" s="15" t="inlineStr">
         <is>
-          <t>RZR +146%</t>
+          <t>Investment In Sunoco +165%</t>
         </is>
       </c>
     </row>
@@ -54750,12 +54732,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Energy Transfer Lp</t>
+          <t>BWX Technologies, Inc.</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
@@ -54765,11 +54747,11 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F109" s="18" t="n">
-        <v>74203103232</v>
+        <v>13754292224</v>
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
@@ -54777,58 +54759,62 @@
         </is>
       </c>
       <c r="H109" s="20" t="n">
-        <v>9.459</v>
+        <v>31.828</v>
       </c>
       <c r="I109" s="20" t="n">
-        <v>14.760273</v>
+        <v>38.891193</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>1.491909508655528</v>
+        <v>10.3069</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>0.69103926</v>
+        <v>3.9141748</v>
       </c>
       <c r="L109" s="21" t="n">
-        <v>7.04975512768092</v>
+        <v>2.19383891609831</v>
       </c>
       <c r="M109" s="21" t="n">
-        <v>6.959999999999999</v>
+        <v>0.5030143835716</v>
       </c>
       <c r="N109" s="21" t="n">
-        <v>8.4099490357427</v>
+        <v>15.04279234978169</v>
       </c>
       <c r="O109" s="21" t="n">
-        <v>17.85263732142248</v>
+        <v>16.8479651603609</v>
       </c>
       <c r="P109" s="20" t="n">
-        <v>4.353514132925898</v>
+        <v>2.646714786974468</v>
       </c>
       <c r="Q109" s="21" t="n">
-        <v>37.32</v>
+        <v>-25.8</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S109" s="20" t="n">
-        <v>0.2291888064107961</v>
+        <v>0.6174267863088643</v>
       </c>
       <c r="T109" s="15" t="inlineStr">
         <is>
-          <t>Crudeoiltransportation (27%)</t>
+          <t>Commercial Operations (74%)</t>
         </is>
       </c>
       <c r="U109" s="17" t="inlineStr">
         <is>
-          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
+          <t>Commercial Operations 74%; Government Operations 26%</t>
         </is>
       </c>
       <c r="V109" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W109" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
+        </is>
+      </c>
       <c r="X109" s="15" t="inlineStr">
         <is>
-          <t>Investment In Sunoco +165%</t>
+          <t>Commercial Operation +143%</t>
         </is>
       </c>
     </row>
@@ -54838,12 +54824,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>LGN</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>BWX Technologies, Inc.</t>
+          <t>Legence Corp.</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
@@ -54851,13 +54837,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E110" s="17" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+      <c r="E110" s="17" t="n"/>
       <c r="F110" s="18" t="n">
-        <v>13754292224</v>
+        <v>9306742784</v>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
@@ -54865,62 +54847,62 @@
         </is>
       </c>
       <c r="H110" s="20" t="n">
-        <v>31.828</v>
-      </c>
-      <c r="I110" s="20" t="n">
-        <v>38.891193</v>
+        <v>35.22426766420546</v>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J110" s="20" t="n">
-        <v>10.3069</v>
+        <v>15.49927769737686</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>3.9141748</v>
+        <v>3.30888056840225</v>
       </c>
       <c r="L110" s="21" t="n">
-        <v>2.19383891609831</v>
-      </c>
-      <c r="M110" s="21" t="n">
-        <v>0.5030143835716</v>
+        <v>3.41438849489116</v>
+      </c>
+      <c r="M110" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N110" s="21" t="n">
-        <v>15.04279234978169</v>
+        <v>3.69186301129894</v>
       </c>
       <c r="O110" s="21" t="n">
-        <v>16.8479651603609</v>
+        <v>5.44599126235131</v>
       </c>
       <c r="P110" s="20" t="n">
-        <v>2.646714786974468</v>
+        <v>6.20894155127728</v>
       </c>
       <c r="Q110" s="21" t="n">
-        <v>-25.8</v>
+        <v>167.4754158395236</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S110" s="20" t="n">
-        <v>0.6174267863088643</v>
+        <v>0.2963256950273106</v>
       </c>
       <c r="T110" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operations (74%)</t>
+          <t>Installation Maintenan (36%)</t>
         </is>
       </c>
       <c r="U110" s="17" t="inlineStr">
         <is>
-          <t>Commercial Operations 74%; Government Operations 26%</t>
+          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
         </is>
       </c>
       <c r="V110" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W110" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W110" s="17" t="n"/>
       <c r="X110" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operation +143%</t>
+          <t>Installation And Mai +162%</t>
         </is>
       </c>
     </row>
@@ -54930,12 +54912,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>LGN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Legence Corp.</t>
+          <t>Gen Digital Inc. Common Stock</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
@@ -54943,9 +54925,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E111" s="17" t="n"/>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Information Te</t>
+        </is>
+      </c>
       <c r="F111" s="18" t="n">
-        <v>9306742784</v>
+        <v>18113243136</v>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
@@ -54953,62 +54939,62 @@
         </is>
       </c>
       <c r="H111" s="20" t="n">
-        <v>35.22426766420546</v>
-      </c>
-      <c r="I111" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.614</v>
+      </c>
+      <c r="I111" s="20" t="n">
+        <v>17.695906</v>
       </c>
       <c r="J111" s="20" t="n">
-        <v>15.49927769737686</v>
+        <v>6.8245378</v>
       </c>
       <c r="K111" s="20" t="n">
-        <v>3.30888056840225</v>
+        <v>3.566301</v>
       </c>
       <c r="L111" s="21" t="n">
-        <v>3.41438849489116</v>
-      </c>
-      <c r="M111" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.13133216482446</v>
+      </c>
+      <c r="M111" s="21" t="n">
+        <v>2.07549286633304</v>
       </c>
       <c r="N111" s="21" t="n">
-        <v>3.69186301129894</v>
+        <v>20.39245863793767</v>
       </c>
       <c r="O111" s="21" t="n">
-        <v>5.44599126235131</v>
+        <v>51.45999999999999</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>6.20894155127728</v>
+        <v>3.02914885347843</v>
       </c>
       <c r="Q111" s="21" t="n">
-        <v>167.4754158395236</v>
+        <v>18.59</v>
       </c>
       <c r="R111" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S111" s="20" t="n">
+        <v>0.5563136799999999</v>
+      </c>
+      <c r="T111" s="15" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform (67%)</t>
+        </is>
+      </c>
+      <c r="U111" s="17" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+        </is>
+      </c>
+      <c r="V111" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S111" s="20" t="n">
-        <v>0.2963256950273106</v>
-      </c>
-      <c r="T111" s="15" t="inlineStr">
-        <is>
-          <t>Installation Maintenan (36%)</t>
-        </is>
-      </c>
-      <c r="U111" s="17" t="inlineStr">
-        <is>
-          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
-        </is>
-      </c>
-      <c r="V111" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="17" t="n"/>
+      <c r="W111" s="17" t="inlineStr">
+        <is>
+          <t>Americas 43%; US 40%; EMEA 13%</t>
+        </is>
+      </c>
       <c r="X111" s="15" t="inlineStr">
         <is>
-          <t>Installation And Mai +162%</t>
+          <t>Trust Based Solution +119%</t>
         </is>
       </c>
     </row>
@@ -55018,12 +55004,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Gen Digital Inc. Common Stock</t>
+          <t>L3Harris Technologies, Inc.</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
@@ -55033,11 +55019,11 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F112" s="18" t="n">
-        <v>18113243136</v>
+        <v>45723136000</v>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
@@ -55045,62 +55031,62 @@
         </is>
       </c>
       <c r="H112" s="20" t="n">
-        <v>10.614</v>
+        <v>17.48068824615385</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>17.695906</v>
+        <v>24.776993</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>6.8245378</v>
+        <v>2.388963</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>3.566301</v>
+        <v>1.167926026207566</v>
       </c>
       <c r="L112" s="21" t="n">
-        <v>10.13133216482446</v>
+        <v>5.88004410889457</v>
       </c>
       <c r="M112" s="21" t="n">
-        <v>2.07549286633304</v>
+        <v>1.56571804266048</v>
       </c>
       <c r="N112" s="21" t="n">
-        <v>20.39245863793767</v>
+        <v>8.274248192518591</v>
       </c>
       <c r="O112" s="21" t="n">
-        <v>51.45999999999999</v>
+        <v>8.96574625150067</v>
       </c>
       <c r="P112" s="20" t="n">
-        <v>3.02914885347843</v>
+        <v>2.55014245014245</v>
       </c>
       <c r="Q112" s="21" t="n">
-        <v>18.59</v>
+        <v>-9.82</v>
       </c>
       <c r="R112" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="S112" s="20" t="n">
+        <v>0.3315167177024359</v>
+      </c>
+      <c r="T112" s="15" t="inlineStr">
+        <is>
+          <t>Communication Systems (42%)</t>
+        </is>
+      </c>
+      <c r="U112" s="17" t="inlineStr">
+        <is>
+          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
+        </is>
+      </c>
+      <c r="V112" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S112" s="20" t="n">
-        <v>0.5563136799999999</v>
-      </c>
-      <c r="T112" s="15" t="inlineStr">
-        <is>
-          <t>Cyber Safety Platform (67%)</t>
-        </is>
-      </c>
-      <c r="U112" s="17" t="inlineStr">
-        <is>
-          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
-        </is>
-      </c>
-      <c r="V112" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="W112" s="17" t="inlineStr">
         <is>
-          <t>Americas 43%; US 40%; EMEA 13%</t>
+          <t>US 90%; Non Us 10%</t>
         </is>
       </c>
       <c r="X112" s="15" t="inlineStr">
         <is>
-          <t>Trust Based Solution +119%</t>
+          <t>Aerojet Rocketdyne +467%</t>
         </is>
       </c>
     </row>
@@ -55110,12 +55096,12 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>L3Harris Technologies, Inc.</t>
+          <t>Brighthouse Financial, Inc.</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
@@ -55125,74 +55111,76 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F113" s="18" t="n">
-        <v>45723136000</v>
+        <v>2881904384</v>
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H113" s="20" t="n">
-        <v>17.48068824615385</v>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I113" s="20" t="n">
-        <v>24.776993</v>
+        <v>3.9738305</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>2.388963</v>
+        <v>0.4399589</v>
       </c>
       <c r="K113" s="20" t="n">
-        <v>1.167926026207566</v>
+        <v>0.4215159</v>
       </c>
       <c r="L113" s="21" t="n">
-        <v>5.88004410889457</v>
-      </c>
-      <c r="M113" s="21" t="n">
-        <v>1.56571804266048</v>
+        <v>-18.66821130454271</v>
+      </c>
+      <c r="M113" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N113" s="21" t="n">
-        <v>8.274248192518591</v>
+        <v>0.007627959012433573</v>
       </c>
       <c r="O113" s="21" t="n">
-        <v>8.96574625150067</v>
-      </c>
-      <c r="P113" s="20" t="n">
-        <v>2.55014245014245</v>
+        <v>0</v>
+      </c>
+      <c r="P113" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q113" s="21" t="n">
-        <v>-9.82</v>
+        <v>-6.12</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S113" s="20" t="n">
-        <v>0.3315167177024359</v>
+        <v>0.4403975356846814</v>
       </c>
       <c r="T113" s="15" t="inlineStr">
         <is>
-          <t>Communication Systems (42%)</t>
+          <t>Annuities (60%)</t>
         </is>
       </c>
       <c r="U113" s="17" t="inlineStr">
         <is>
-          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
+          <t>Annuities 60%; Runoff 21%; Life 19%</t>
         </is>
       </c>
       <c r="V113" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W113" s="17" t="inlineStr">
-        <is>
-          <t>US 90%; Non Us 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W113" s="17" t="n"/>
       <c r="X113" s="15" t="inlineStr">
         <is>
-          <t>Aerojet Rocketdyne +467%</t>
+          <t>Annuities +322%</t>
         </is>
       </c>
     </row>
@@ -55202,12 +55190,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc.</t>
+          <t>ONEOK, Inc.</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
@@ -55215,69 +55203,59 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E114" s="17" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="E114" s="17" t="n"/>
       <c r="F114" s="18" t="n">
-        <v>2881904384</v>
+        <v>60906319872</v>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H114" s="20" t="n">
+        <v>12.17</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>3.9738305</v>
+        <v>16.687393</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.4399589</v>
+        <v>2.655344</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.4215159</v>
+        <v>1.5471808</v>
       </c>
       <c r="L114" s="21" t="n">
-        <v>-18.66821130454271</v>
-      </c>
-      <c r="M114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.830758993916</v>
+      </c>
+      <c r="M114" s="21" t="n">
+        <v>4.39066236170035</v>
       </c>
       <c r="N114" s="21" t="n">
-        <v>0.007627959012433573</v>
+        <v>10.40228824506366</v>
       </c>
       <c r="O114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.48324054084763</v>
+      </c>
+      <c r="P114" s="20" t="n">
+        <v>4.229943145925458</v>
       </c>
       <c r="Q114" s="21" t="n">
-        <v>-6.12</v>
+        <v>50.16</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S114" s="20" t="n">
-        <v>0.4403975356846814</v>
+        <v>0.4959061195541746</v>
       </c>
       <c r="T114" s="15" t="inlineStr">
         <is>
-          <t>Annuities (60%)</t>
+          <t>Refined Products And C (66%)</t>
         </is>
       </c>
       <c r="U114" s="17" t="inlineStr">
         <is>
-          <t>Annuities 60%; Runoff 21%; Life 19%</t>
+          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
         </is>
       </c>
       <c r="V114" s="18" t="n">
@@ -55286,7 +55264,7 @@
       <c r="W114" s="17" t="n"/>
       <c r="X114" s="15" t="inlineStr">
         <is>
-          <t>Annuities +322%</t>
+          <t>Refined Products And +192%</t>
         </is>
       </c>
     </row>
@@ -55296,12 +55274,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>HAPN</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>ONEOK, Inc.</t>
+          <t>Happen Inc. Common Stock</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -55309,9 +55287,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E115" s="17" t="n"/>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="F115" s="18" t="n">
-        <v>60906319872</v>
+        <v>1938845312</v>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
@@ -55319,49 +55301,57 @@
         </is>
       </c>
       <c r="H115" s="20" t="n">
-        <v>12.17</v>
+        <v>3.25</v>
       </c>
       <c r="I115" s="20" t="n">
-        <v>16.687393</v>
+        <v>13.36898003182167</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>2.655344</v>
+        <v>1.2369312</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>1.5471808</v>
-      </c>
-      <c r="L115" s="21" t="n">
-        <v>4.830758993916</v>
-      </c>
-      <c r="M115" s="21" t="n">
-        <v>4.39066236170035</v>
-      </c>
-      <c r="N115" s="21" t="n">
-        <v>10.40228824506366</v>
+        <v>3.208765663633625</v>
+      </c>
+      <c r="L115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O115" s="21" t="n">
-        <v>22.48324054084763</v>
-      </c>
-      <c r="P115" s="20" t="n">
-        <v>4.229943145925458</v>
+        <v>52.58608552315825</v>
+      </c>
+      <c r="P115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q115" s="21" t="n">
-        <v>50.16</v>
+        <v>2.07</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S115" s="20" t="n">
-        <v>0.4959061195541746</v>
+        <v>0.5010363171603962</v>
       </c>
       <c r="T115" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And C (66%)</t>
+          <t>Happen Bank (52%)</t>
         </is>
       </c>
       <c r="U115" s="17" t="inlineStr">
         <is>
-          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
+          <t>Happen Bank 52%; Happen Inc. 48%</t>
         </is>
       </c>
       <c r="V115" s="18" t="n">
@@ -55370,7 +55360,7 @@
       <c r="W115" s="17" t="n"/>
       <c r="X115" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And +192%</t>
+          <t>Happen Bank +124%</t>
         </is>
       </c>
     </row>
@@ -55380,43 +55370,51 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>HAPN</t>
+          <t>VFS</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Happen Inc. Common Stock</t>
+          <t>VinFast Auto Ltd. Ordinary Sha</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F116" s="18" t="n">
-        <v>1938845312</v>
+        <v>7509911040</v>
       </c>
       <c r="G116" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H116" s="20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I116" s="20" t="n">
-        <v>13.36898003182167</v>
-      </c>
-      <c r="J116" s="20" t="n">
-        <v>1.2369312</v>
-      </c>
-      <c r="K116" s="20" t="n">
-        <v>3.208765663633625</v>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L116" s="22" t="inlineStr">
         <is>
@@ -55428,13 +55426,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="N116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N116" s="21" t="n">
+        <v>78.31448357763071</v>
       </c>
       <c r="O116" s="21" t="n">
-        <v>52.58608552315825</v>
+        <v>-83.1176333196485</v>
       </c>
       <c r="P116" s="22" t="inlineStr">
         <is>
@@ -55442,31 +55438,35 @@
         </is>
       </c>
       <c r="Q116" s="21" t="n">
-        <v>2.07</v>
+        <v>-3.75</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S116" s="20" t="n">
-        <v>0.5010363171603962</v>
+        <v>0.460552269511968</v>
       </c>
       <c r="T116" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank (52%)</t>
+          <t>Car (48%)</t>
         </is>
       </c>
       <c r="U116" s="17" t="inlineStr">
         <is>
-          <t>Happen Bank 52%; Happen Inc. 48%</t>
+          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
         </is>
       </c>
       <c r="V116" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W116" s="17" t="inlineStr">
+        <is>
+          <t>VN 89%; Asia Pacific 8%; US 2%</t>
+        </is>
+      </c>
       <c r="X116" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank +124%</t>
+          <t>E Scooter +230%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="18" t="n">
-        <v>63345280</v>
+        <v>12457237</v>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="H18" s="20" t="n">
-        <v>5.332</v>
+        <v>-11.99</v>
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
@@ -1641,58 +1641,52 @@
         </is>
       </c>
       <c r="J18" s="20" t="n">
-        <v>0.65628195</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>0.031039892</v>
+        <v>0.58659774</v>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L18" s="21" t="n">
-        <v>64.10263948586179</v>
-      </c>
-      <c r="M18" s="21" t="n">
+        <v>51.35543081206073</v>
+      </c>
+      <c r="M18" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>-19.53360636030006</v>
+      </c>
+      <c r="O18" s="21" t="n">
+        <v>0.27102238816465</v>
+      </c>
+      <c r="P18" s="20" t="n">
+        <v>-20.75086540754323</v>
+      </c>
+      <c r="Q18" s="21" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="R18" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="21" t="n">
-        <v>-9.731226124022729</v>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>7.89126355897411</v>
-      </c>
-      <c r="P18" s="20" t="n">
-        <v>5.187935432355073</v>
-      </c>
-      <c r="Q18" s="21" t="n">
-        <v>-60.46</v>
-      </c>
-      <c r="R18" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S18" s="20" t="n">
-        <v>0.6572808745010525</v>
-      </c>
-      <c r="T18" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Engage (78%)</t>
-        </is>
-      </c>
-      <c r="U18" s="17" t="inlineStr">
-        <is>
-          <t>Ttec Engage 78%; Ttec Digital 22%</t>
-        </is>
-      </c>
+      <c r="S18" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="17" t="n"/>
       <c r="V18" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W18" s="17" t="inlineStr">
         <is>
-          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
-        </is>
-      </c>
-      <c r="X18" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Digital +2%</t>
-        </is>
-      </c>
+          <t>CN 70%; HK 26%; MY 2%</t>
+        </is>
+      </c>
+      <c r="X18" s="15" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="13" t="n">
@@ -1700,12 +1694,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
@@ -1715,11 +1709,11 @@
       </c>
       <c r="E19" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F19" s="18" t="n">
-        <v>12457237</v>
+        <v>63345280</v>
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
@@ -1727,7 +1721,7 @@
         </is>
       </c>
       <c r="H19" s="20" t="n">
-        <v>-11.99</v>
+        <v>5.332</v>
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
@@ -1735,52 +1729,58 @@
         </is>
       </c>
       <c r="J19" s="20" t="n">
-        <v>0.58659774</v>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.65628195</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>0.031039892</v>
       </c>
       <c r="L19" s="21" t="n">
-        <v>51.35543081206073</v>
-      </c>
-      <c r="M19" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>64.10263948586179</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="N19" s="21" t="n">
-        <v>-19.53360636030006</v>
+        <v>-9.731226124022729</v>
       </c>
       <c r="O19" s="21" t="n">
-        <v>0.27102238816465</v>
+        <v>7.89126355897411</v>
       </c>
       <c r="P19" s="20" t="n">
-        <v>-20.75086540754323</v>
+        <v>5.187935432355073</v>
       </c>
       <c r="Q19" s="21" t="n">
-        <v>44.57</v>
+        <v>-60.46</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T19" s="15" t="n"/>
-      <c r="U19" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S19" s="20" t="n">
+        <v>0.6572808745010525</v>
+      </c>
+      <c r="T19" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Engage (78%)</t>
+        </is>
+      </c>
+      <c r="U19" s="17" t="inlineStr">
+        <is>
+          <t>Ttec Engage 78%; Ttec Digital 22%</t>
+        </is>
+      </c>
       <c r="V19" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W19" s="17" t="inlineStr">
         <is>
-          <t>CN 70%; HK 26%; MY 2%</t>
-        </is>
-      </c>
-      <c r="X19" s="15" t="n"/>
+          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
+        </is>
+      </c>
+      <c r="X19" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Digital +2%</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n">
@@ -39972,12 +39972,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>TTEC</t>
+          <t>BANL</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Ttec Holdings, Inc.</t>
+          <t>Cbl International Limited</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
@@ -39987,11 +39987,11 @@
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F13" s="18" t="n">
-        <v>63345280</v>
+        <v>12457237</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         </is>
       </c>
       <c r="H13" s="20" t="n">
-        <v>5.332</v>
+        <v>-11.99</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
@@ -40007,58 +40007,52 @@
         </is>
       </c>
       <c r="J13" s="20" t="n">
-        <v>0.65628195</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.031039892</v>
+        <v>0.58659774</v>
+      </c>
+      <c r="K13" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L13" s="21" t="n">
-        <v>64.10263948586179</v>
-      </c>
-      <c r="M13" s="21" t="n">
+        <v>51.35543081206073</v>
+      </c>
+      <c r="M13" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>-19.53360636030006</v>
+      </c>
+      <c r="O13" s="21" t="n">
+        <v>0.27102238816465</v>
+      </c>
+      <c r="P13" s="20" t="n">
+        <v>-20.75086540754323</v>
+      </c>
+      <c r="Q13" s="21" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="R13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="21" t="n">
-        <v>-9.731226124022729</v>
-      </c>
-      <c r="O13" s="21" t="n">
-        <v>7.89126355897411</v>
-      </c>
-      <c r="P13" s="20" t="n">
-        <v>5.187935432355073</v>
-      </c>
-      <c r="Q13" s="21" t="n">
-        <v>-60.46</v>
-      </c>
-      <c r="R13" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" s="20" t="n">
-        <v>0.6572808745010525</v>
-      </c>
-      <c r="T13" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Engage (78%)</t>
-        </is>
-      </c>
-      <c r="U13" s="17" t="inlineStr">
-        <is>
-          <t>Ttec Engage 78%; Ttec Digital 22%</t>
-        </is>
-      </c>
+      <c r="S13" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T13" s="15" t="n"/>
+      <c r="U13" s="17" t="n"/>
       <c r="V13" s="18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W13" s="17" t="inlineStr">
         <is>
-          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
-        </is>
-      </c>
-      <c r="X13" s="15" t="inlineStr">
-        <is>
-          <t>Ttec Digital +2%</t>
-        </is>
-      </c>
+          <t>CN 70%; HK 26%; MY 2%</t>
+        </is>
+      </c>
+      <c r="X13" s="15" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="13" t="n">
@@ -40066,12 +40060,12 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>TTEC</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Cbl International Limited</t>
+          <t>Ttec Holdings, Inc.</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -40081,11 +40075,11 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F14" s="18" t="n">
-        <v>12457237</v>
+        <v>63345280</v>
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
@@ -40093,7 +40087,7 @@
         </is>
       </c>
       <c r="H14" s="20" t="n">
-        <v>-11.99</v>
+        <v>5.332</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
@@ -40101,52 +40095,58 @@
         </is>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0.58659774</v>
-      </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.65628195</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>0.031039892</v>
       </c>
       <c r="L14" s="21" t="n">
-        <v>51.35543081206073</v>
-      </c>
-      <c r="M14" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>64.10263948586179</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="N14" s="21" t="n">
-        <v>-19.53360636030006</v>
+        <v>-9.731226124022729</v>
       </c>
       <c r="O14" s="21" t="n">
-        <v>0.27102238816465</v>
+        <v>7.89126355897411</v>
       </c>
       <c r="P14" s="20" t="n">
-        <v>-20.75086540754323</v>
+        <v>5.187935432355073</v>
       </c>
       <c r="Q14" s="21" t="n">
-        <v>44.57</v>
+        <v>-60.46</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S14" s="20" t="n">
+        <v>0.6572808745010525</v>
+      </c>
+      <c r="T14" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Engage (78%)</t>
+        </is>
+      </c>
+      <c r="U14" s="17" t="inlineStr">
+        <is>
+          <t>Ttec Engage 78%; Ttec Digital 22%</t>
+        </is>
+      </c>
       <c r="V14" s="18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W14" s="17" t="inlineStr">
         <is>
-          <t>CN 70%; HK 26%; MY 2%</t>
-        </is>
-      </c>
-      <c r="X14" s="15" t="n"/>
+          <t>United States Canada 68%; Philippines Asia Pacific India 18%</t>
+        </is>
+      </c>
+      <c r="X14" s="15" t="inlineStr">
+        <is>
+          <t>Ttec Digital +2%</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="13" t="n">
@@ -50820,89 +50820,103 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VFS</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>VinFast Auto Ltd. Ordinary Sha</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F67" s="18" t="n">
-        <v>104030609408</v>
+        <v>7509911040</v>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H67" s="20" t="n">
-        <v>12.211</v>
-      </c>
-      <c r="I67" s="20" t="n">
-        <v>14.801482</v>
-      </c>
-      <c r="J67" s="20" t="n">
-        <v>3.2861774</v>
-      </c>
-      <c r="K67" s="20" t="n">
-        <v>0.68366075</v>
-      </c>
-      <c r="L67" s="21" t="n">
-        <v>6.14626794593043</v>
-      </c>
-      <c r="M67" s="21" t="n">
-        <v>2.96</v>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N67" s="21" t="n">
-        <v>12.24307948200071</v>
+        <v>78.31448357763071</v>
       </c>
       <c r="O67" s="21" t="n">
-        <v>6.84160433056228</v>
-      </c>
-      <c r="P67" s="20" t="n">
-        <v>1.675361394631018</v>
+        <v>-83.1176333196485</v>
+      </c>
+      <c r="P67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q67" s="21" t="n">
-        <v>92.92</v>
+        <v>-3.75</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S67" s="20" t="n">
-        <v>0.3806408342658987</v>
+        <v>0.460552269511968</v>
       </c>
       <c r="T67" s="15" t="inlineStr">
         <is>
-          <t>Marketing Speciality (46%)</t>
+          <t>Car (48%)</t>
         </is>
       </c>
       <c r="U67" s="17" t="inlineStr">
         <is>
-          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
+          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
         </is>
       </c>
       <c r="V67" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W67" s="17" t="inlineStr">
         <is>
-          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
+          <t>VN 89%; Asia Pacific 8%; US 2%</t>
         </is>
       </c>
       <c r="X67" s="15" t="inlineStr">
         <is>
-          <t>Refining +92%</t>
+          <t>E Scooter +230%</t>
         </is>
       </c>
     </row>
@@ -50912,12 +50926,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Amphenol Corp /De/</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -50927,11 +50941,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>206943928320</v>
+        <v>104030609408</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -50939,62 +50953,62 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>29.62302222645686</v>
+        <v>12.211</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>41.96</v>
+        <v>14.801482</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>13.354551</v>
+        <v>3.2861774</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>7.1331444</v>
+        <v>0.68366075</v>
       </c>
       <c r="L68" s="21" t="n">
-        <v>2.30913485895705</v>
+        <v>6.14626794593043</v>
       </c>
       <c r="M68" s="21" t="n">
-        <v>0.55827491517045</v>
+        <v>2.96</v>
       </c>
       <c r="N68" s="21" t="n">
-        <v>45.67278672993024</v>
+        <v>12.24307948200071</v>
       </c>
       <c r="O68" s="21" t="n">
-        <v>29.39923710032213</v>
+        <v>6.84160433056228</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>2.057377830710813</v>
+        <v>1.675361394631018</v>
       </c>
       <c r="Q68" s="21" t="n">
-        <v>19.46</v>
+        <v>92.92</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68" s="20" t="n">
-        <v>0.4256894967493531</v>
+        <v>0.3806408342658987</v>
       </c>
       <c r="T68" s="15" t="inlineStr">
         <is>
-          <t>Communications Solutio (58%)</t>
+          <t>Marketing Speciality (46%)</t>
         </is>
       </c>
       <c r="U68" s="17" t="inlineStr">
         <is>
-          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
+          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
         </is>
       </c>
       <c r="V68" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W68" s="17" t="inlineStr">
         <is>
-          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
+          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
         </is>
       </c>
       <c r="X68" s="15" t="inlineStr">
         <is>
-          <t>Communications Solut +143%</t>
+          <t>Refining +92%</t>
         </is>
       </c>
     </row>
@@ -51004,12 +51018,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L</t>
+          <t>Amphenol Corp /De/</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -51019,11 +51033,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>84003667968</v>
+        <v>206943928320</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -51031,58 +51045,62 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>11.619</v>
+        <v>29.62302222645686</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>13.460208</v>
+        <v>41.96</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>2.777183</v>
+        <v>13.354551</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>1.4366723</v>
+        <v>7.1331444</v>
       </c>
       <c r="L69" s="21" t="n">
-        <v>4.43809968934908</v>
+        <v>2.30913485895705</v>
       </c>
       <c r="M69" s="21" t="n">
-        <v>0.13529237831726</v>
+        <v>0.55827491517045</v>
       </c>
       <c r="N69" s="21" t="n">
-        <v>21.16359754470242</v>
+        <v>45.67278672993024</v>
       </c>
       <c r="O69" s="21" t="n">
-        <v>19.03228934354698</v>
+        <v>29.39923710032213</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>3.436213572447524</v>
+        <v>2.057377830710813</v>
       </c>
       <c r="Q69" s="21" t="n">
-        <v>32.34</v>
+        <v>19.46</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.3092139839729619</v>
+        <v>0.4256894967493531</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipe (39%)</t>
+          <t>Communications Solutio (58%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
+          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W69" s="17" t="inlineStr">
+        <is>
+          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
+        </is>
+      </c>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Petrochemical And Re +92%</t>
+          <t>Communications Solut +143%</t>
         </is>
       </c>
     </row>
@@ -51092,12 +51110,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Enterprise Products Partners L</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -51107,11 +51125,11 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>59365711872</v>
+        <v>84003667968</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -51119,62 +51137,58 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>38.313</v>
+        <v>11.619</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>52.08779</v>
+        <v>13.460208</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>18.907534</v>
+        <v>2.777183</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>17.51624120163544</v>
+        <v>1.4366723</v>
       </c>
       <c r="L70" s="21" t="n">
-        <v>1.43309891391495</v>
+        <v>4.43809968934908</v>
       </c>
       <c r="M70" s="21" t="n">
-        <v>0.11999999</v>
+        <v>0.13529237831726</v>
       </c>
       <c r="N70" s="21" t="n">
-        <v>28.59709180832235</v>
+        <v>21.16359754470242</v>
       </c>
       <c r="O70" s="21" t="n">
-        <v>44.40287939770699</v>
+        <v>19.03228934354698</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>-0.1708346552178611</v>
+        <v>3.436213572447524</v>
       </c>
       <c r="Q70" s="21" t="n">
-        <v>96.81</v>
+        <v>32.34</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.6478300772075185</v>
+        <v>0.3092139839729619</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test (79%)</t>
+          <t>Onshore Crude Oil Pipe (39%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
+          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="W70" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W70" s="17" t="n"/>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test +128%</t>
+          <t>Petrochemical And Re +92%</t>
         </is>
       </c>
     </row>
@@ -51184,12 +51198,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Te Connectivity Plc</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -51203,7 +51217,7 @@
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>61365223424</v>
+        <v>59365711872</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -51211,62 +51225,62 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>12.92</v>
+        <v>38.313</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>20.76004</v>
+        <v>52.08779</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>4.6395974</v>
+        <v>18.907534</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>3.175925</v>
+        <v>17.51624120163544</v>
       </c>
       <c r="L71" s="21" t="n">
-        <v>5.99434499439441</v>
+        <v>1.43309891391495</v>
       </c>
       <c r="M71" s="21" t="n">
-        <v>1.50999995</v>
+        <v>0.11999999</v>
       </c>
       <c r="N71" s="21" t="n">
-        <v>19.58952110795928</v>
+        <v>28.59709180832235</v>
       </c>
       <c r="O71" s="21" t="n">
-        <v>23.88059701492537</v>
+        <v>44.40287939770699</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>1.09837962962963</v>
+        <v>-0.1708346552178611</v>
       </c>
       <c r="Q71" s="21" t="n">
-        <v>-14.61</v>
+        <v>96.81</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.5038462678974261</v>
+        <v>0.6478300772075185</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>Transportation Solutio (54%)</t>
+          <t>Semiconductor Test (79%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
+          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W71" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
+          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
         </is>
       </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Industrial Solutions +344%</t>
+          <t>Semiconductor Test +128%</t>
         </is>
       </c>
     </row>
@@ -51276,12 +51290,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>DWSN</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Dawson Geophysical Company</t>
+          <t>Te Connectivity Plc</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -51291,11 +51305,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>104346872</v>
+        <v>61365223424</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -51303,58 +51317,62 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>9.484</v>
+        <v>12.92</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>28</v>
+        <v>20.76004</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>5.2093024</v>
+        <v>4.6395974</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.781109620624607</v>
+        <v>3.175925</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>-3.92755347083511</v>
+        <v>5.99434499439441</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>8.120800080331669</v>
+        <v>1.50999995</v>
       </c>
       <c r="N72" s="21" t="n">
-        <v>25.64674804153762</v>
+        <v>19.58952110795928</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>8.550169176872171</v>
+        <v>23.88059701492537</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>1.218788303274383</v>
+        <v>1.09837962962963</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>85.28</v>
+        <v>-14.61</v>
       </c>
       <c r="R72" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S72" s="20" t="n">
-        <v>0.6695871789304009</v>
+        <v>0.5038462678974261</v>
       </c>
       <c r="T72" s="15" t="inlineStr">
         <is>
-          <t>United States Operatio (79%)</t>
+          <t>Transportation Solutio (54%)</t>
         </is>
       </c>
       <c r="U72" s="17" t="inlineStr">
         <is>
-          <t>United States Operations 79%; Canada Operations 21%</t>
+          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
         </is>
       </c>
       <c r="V72" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="17" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="W72" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
+        </is>
+      </c>
       <c r="X72" s="15" t="inlineStr">
         <is>
-          <t>Canada Operations +152%</t>
+          <t>Industrial Solutions +344%</t>
         </is>
       </c>
     </row>
@@ -51364,12 +51382,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>DWSN</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
+          <t>Dawson Geophysical Company</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -51379,11 +51397,11 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F73" s="18" t="n">
-        <v>4507106816</v>
+        <v>104346872</v>
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
@@ -51391,62 +51409,58 @@
         </is>
       </c>
       <c r="H73" s="20" t="n">
-        <v>20.979</v>
+        <v>9.484</v>
       </c>
       <c r="I73" s="20" t="n">
-        <v>39.50917</v>
+        <v>28</v>
       </c>
       <c r="J73" s="20" t="n">
-        <v>4.942614</v>
+        <v>5.2093024</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>5.988356816294535</v>
+        <v>0.781109620624607</v>
       </c>
       <c r="L73" s="21" t="n">
-        <v>0.9359515835039199</v>
+        <v>-3.92755347083511</v>
       </c>
       <c r="M73" s="21" t="n">
-        <v>0.64999997</v>
+        <v>8.120800080331669</v>
       </c>
       <c r="N73" s="21" t="n">
-        <v>-5.462297040904851</v>
+        <v>25.64674804153762</v>
       </c>
       <c r="O73" s="21" t="n">
-        <v>25.49940543018288</v>
+        <v>8.550169176872171</v>
       </c>
       <c r="P73" s="20" t="n">
-        <v>-2.120367819924969</v>
+        <v>1.218788303274383</v>
       </c>
       <c r="Q73" s="21" t="n">
-        <v>106.32</v>
+        <v>85.28</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S73" s="20" t="n">
-        <v>0.2775979208843406</v>
+        <v>0.6695871789304009</v>
       </c>
       <c r="T73" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment (43%)</t>
+          <t>United States Operatio (79%)</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
+          <t>United States Operations 79%; Canada Operations 21%</t>
         </is>
       </c>
       <c r="V73" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W73" s="17" t="inlineStr">
-        <is>
-          <t>CN 56%; US 10%; All Other Segments 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W73" s="17" t="n"/>
       <c r="X73" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipme +198%</t>
+          <t>Canada Operations +152%</t>
         </is>
       </c>
     </row>
@@ -51456,12 +51470,12 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Emergent Biosolutions Inc.</t>
+          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -51471,11 +51485,11 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F74" s="18" t="n">
-        <v>319432896</v>
+        <v>4507106816</v>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
@@ -51483,66 +51497,62 @@
         </is>
       </c>
       <c r="H74" s="20" t="n">
-        <v>26.38994704225352</v>
-      </c>
-      <c r="I74" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.979</v>
+      </c>
+      <c r="I74" s="20" t="n">
+        <v>39.50917</v>
       </c>
       <c r="J74" s="20" t="n">
-        <v>0.9361382</v>
+        <v>4.942614</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.4147402</v>
+        <v>5.988356816294535</v>
       </c>
       <c r="L74" s="21" t="n">
-        <v>26.97801418097588</v>
-      </c>
-      <c r="M74" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9359515835039199</v>
+      </c>
+      <c r="M74" s="21" t="n">
+        <v>0.64999997</v>
       </c>
       <c r="N74" s="21" t="n">
-        <v>14.79068774028193</v>
+        <v>-5.462297040904851</v>
       </c>
       <c r="O74" s="21" t="n">
-        <v>3.78515260562441</v>
+        <v>25.49940543018288</v>
       </c>
       <c r="P74" s="20" t="n">
-        <v>14.55281690140845</v>
+        <v>-2.120367819924969</v>
       </c>
       <c r="Q74" s="21" t="n">
-        <v>-50.23999999999999</v>
+        <v>106.32</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S74" s="20" t="n">
-        <v>0.557029765440831</v>
+        <v>0.2775979208843406</v>
       </c>
       <c r="T74" s="15" t="inlineStr">
         <is>
-          <t>MCM Products (67%)</t>
+          <t>Ball Bonding Equipment (43%)</t>
         </is>
       </c>
       <c r="U74" s="17" t="inlineStr">
         <is>
-          <t>MCM Products 67%; Commercial Products 33%</t>
+          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
         </is>
       </c>
       <c r="V74" s="18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W74" s="17" t="inlineStr">
         <is>
-          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
+          <t>CN 56%; US 10%; All Other Segments 9%</t>
         </is>
       </c>
       <c r="X74" s="15" t="inlineStr">
         <is>
-          <t>MCM Products +188%</t>
+          <t>Ball Bonding Equipme +198%</t>
         </is>
       </c>
     </row>
@@ -51552,12 +51562,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Porch Group Inc.</t>
+          <t>Emergent Biosolutions Inc.</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -51567,11 +51577,11 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F75" s="18" t="n">
-        <v>1867401472</v>
+        <v>319432896</v>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
@@ -51579,62 +51589,66 @@
         </is>
       </c>
       <c r="H75" s="20" t="n">
-        <v>37.42943855774974</v>
+        <v>26.38994704225352</v>
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J75" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="J75" s="20" t="n">
+        <v>0.9361382</v>
       </c>
       <c r="K75" s="20" t="n">
-        <v>3.6359277</v>
+        <v>0.4147402</v>
       </c>
       <c r="L75" s="21" t="n">
-        <v>4.69353492369449</v>
-      </c>
-      <c r="M75" s="21" t="n">
-        <v>2.78673595725851</v>
+        <v>26.97801418097588</v>
+      </c>
+      <c r="M75" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N75" s="21" t="n">
-        <v>10.31950957042169</v>
+        <v>14.79068774028193</v>
       </c>
       <c r="O75" s="21" t="n">
-        <v>10.50153492306376</v>
+        <v>3.78515260562441</v>
       </c>
       <c r="P75" s="20" t="n">
-        <v>3.279218781110286</v>
+        <v>14.55281690140845</v>
       </c>
       <c r="Q75" s="21" t="n">
-        <v>19.2</v>
+        <v>-50.23999999999999</v>
       </c>
       <c r="R75" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S75" s="20" t="n">
+        <v>0.557029765440831</v>
+      </c>
+      <c r="T75" s="15" t="inlineStr">
+        <is>
+          <t>MCM Products (67%)</t>
+        </is>
+      </c>
+      <c r="U75" s="17" t="inlineStr">
+        <is>
+          <t>MCM Products 67%; Commercial Products 33%</t>
+        </is>
+      </c>
+      <c r="V75" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="S75" s="20" t="n">
-        <v>0.5817970747345014</v>
-      </c>
-      <c r="T75" s="15" t="inlineStr">
-        <is>
-          <t>Insurance Services (72%)</t>
-        </is>
-      </c>
-      <c r="U75" s="17" t="inlineStr">
-        <is>
-          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
-        </is>
-      </c>
-      <c r="V75" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" s="17" t="n"/>
+      <c r="W75" s="17" t="inlineStr">
+        <is>
+          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
+        </is>
+      </c>
       <c r="X75" s="15" t="inlineStr">
         <is>
-          <t>Software Data +333%</t>
+          <t>MCM Products +188%</t>
         </is>
       </c>
     </row>
@@ -51644,12 +51658,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>NGL</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>NGL Energy Partners LP</t>
+          <t>Porch Group Inc.</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -51659,11 +51673,11 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1989539712</v>
+        <v>1867401472</v>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
@@ -51671,7 +51685,7 @@
         </is>
       </c>
       <c r="H76" s="20" t="n">
-        <v>15.17839608310902</v>
+        <v>37.42943855774974</v>
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
@@ -51684,55 +51698,49 @@
         </is>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.6303674</v>
+        <v>3.6359277</v>
       </c>
       <c r="L76" s="21" t="n">
-        <v>5.12068190373472</v>
-      </c>
-      <c r="M76" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69353492369449</v>
+      </c>
+      <c r="M76" s="21" t="n">
+        <v>2.78673595725851</v>
       </c>
       <c r="N76" s="21" t="n">
-        <v>12.90137422847655</v>
+        <v>10.31950957042169</v>
       </c>
       <c r="O76" s="21" t="n">
-        <v>11.58580003385248</v>
+        <v>10.50153492306376</v>
       </c>
       <c r="P76" s="20" t="n">
-        <v>7.901573173509551</v>
+        <v>3.279218781110286</v>
       </c>
       <c r="Q76" s="21" t="n">
-        <v>174.77</v>
+        <v>19.2</v>
       </c>
       <c r="R76" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S76" s="20" t="n">
-        <v>0.3423299785064143</v>
+        <v>0.5817970747345014</v>
       </c>
       <c r="T76" s="15" t="inlineStr">
         <is>
-          <t>Liquids Logistics (40%)</t>
+          <t>Insurance Services (72%)</t>
         </is>
       </c>
       <c r="U76" s="17" t="inlineStr">
         <is>
-          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
+          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
         </is>
       </c>
       <c r="V76" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W76" s="17" t="inlineStr">
-        <is>
-          <t>Non Us 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W76" s="17" t="n"/>
       <c r="X76" s="15" t="inlineStr">
         <is>
-          <t>Crude Oil Logistics +162%</t>
+          <t>Software Data +333%</t>
         </is>
       </c>
     </row>
@@ -51742,12 +51750,12 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NGL</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NGL Energy Partners LP</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -51757,11 +51765,11 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F77" s="18" t="n">
-        <v>360690188288</v>
+        <v>1989539712</v>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
@@ -51769,10 +51777,12 @@
         </is>
       </c>
       <c r="H77" s="20" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="I77" s="20" t="n">
-        <v>33.039604</v>
+        <v>15.17839608310902</v>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J77" s="22" t="inlineStr">
         <is>
@@ -51780,53 +51790,55 @@
         </is>
       </c>
       <c r="K77" s="20" t="n">
-        <v>2.3855643</v>
+        <v>0.6303674</v>
       </c>
       <c r="L77" s="21" t="n">
-        <v>2.02823359941622</v>
-      </c>
-      <c r="M77" s="21" t="n">
-        <v>0.76768205413026</v>
+        <v>5.12068190373472</v>
+      </c>
+      <c r="M77" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N77" s="21" t="n">
-        <v>81.97384514065294</v>
+        <v>12.90137422847655</v>
       </c>
       <c r="O77" s="21" t="n">
-        <v>13.94585527536068</v>
+        <v>11.58580003385248</v>
       </c>
       <c r="P77" s="20" t="n">
-        <v>1.01819258757827</v>
+        <v>7.901573173509551</v>
       </c>
       <c r="Q77" s="21" t="n">
-        <v>226.48</v>
+        <v>174.77</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S77" s="20" t="n">
-        <v>0.5038741410704293</v>
+        <v>0.3423299785064143</v>
       </c>
       <c r="T77" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solutio (54%)</t>
+          <t>Liquids Logistics (40%)</t>
         </is>
       </c>
       <c r="U77" s="17" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
+          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
         </is>
       </c>
       <c r="V77" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W77" s="17" t="inlineStr">
         <is>
-          <t>US 56%; Non Us 44%</t>
+          <t>Non Us 100%</t>
         </is>
       </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solut +181%</t>
+          <t>Crude Oil Logistics +162%</t>
         </is>
       </c>
     </row>
@@ -51836,12 +51848,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -51855,7 +51867,7 @@
         </is>
       </c>
       <c r="F78" s="18" t="n">
-        <v>83154591744</v>
+        <v>360690188288</v>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
@@ -51863,64 +51875,64 @@
         </is>
       </c>
       <c r="H78" s="20" t="n">
-        <v>102.474</v>
+        <v>19.51</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>142.82867</v>
-      </c>
-      <c r="J78" s="20" t="n">
-        <v>17.686687</v>
+        <v>33.039604</v>
+      </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K78" s="20" t="n">
-        <v>27.589445</v>
+        <v>2.3855643</v>
       </c>
       <c r="L78" s="21" t="n">
-        <v>0.37963999713611</v>
-      </c>
-      <c r="M78" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.02823359941622</v>
+      </c>
+      <c r="M78" s="21" t="n">
+        <v>0.76768205413026</v>
       </c>
       <c r="N78" s="21" t="n">
-        <v>5.712871831528011</v>
+        <v>81.97384514065294</v>
       </c>
       <c r="O78" s="21" t="n">
-        <v>32.17730397042276</v>
+        <v>13.94585527536068</v>
       </c>
       <c r="P78" s="20" t="n">
-        <v>-1.18221551413651</v>
+        <v>1.01819258757827</v>
       </c>
       <c r="Q78" s="21" t="n">
-        <v>337.22</v>
+        <v>226.48</v>
       </c>
       <c r="R78" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S78" s="20" t="n">
-        <v>0.554732848124369</v>
+        <v>0.5038741410704293</v>
       </c>
       <c r="T78" s="15" t="inlineStr">
         <is>
-          <t>Systems (67%)</t>
+          <t>Infrastructure Solutio (54%)</t>
         </is>
       </c>
       <c r="U78" s="17" t="inlineStr">
         <is>
-          <t>Systems 67%; Components 33%</t>
+          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
         </is>
       </c>
       <c r="V78" s="18" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="W78" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
+          <t>US 56%; Non Us 44%</t>
         </is>
       </c>
       <c r="X78" s="15" t="inlineStr">
         <is>
-          <t>Systems +279%</t>
+          <t>Infrastructure Solut +181%</t>
         </is>
       </c>
     </row>
@@ -51930,12 +51942,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>PROG Holdings, Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -51945,11 +51957,11 @@
       </c>
       <c r="E79" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F79" s="18" t="n">
-        <v>1472177024</v>
+        <v>83154591744</v>
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
@@ -51957,58 +51969,64 @@
         </is>
       </c>
       <c r="H79" s="20" t="n">
-        <v>8.850440627472885</v>
+        <v>102.474</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>11.922581</v>
+        <v>142.82867</v>
       </c>
       <c r="J79" s="20" t="n">
-        <v>1.8279835</v>
+        <v>17.686687</v>
       </c>
       <c r="K79" s="20" t="n">
-        <v>0.5630427</v>
+        <v>27.589445</v>
       </c>
       <c r="L79" s="21" t="n">
-        <v>20.7154094641091</v>
-      </c>
-      <c r="M79" s="21" t="n">
-        <v>1.20889722398801</v>
+        <v>0.37963999713611</v>
+      </c>
+      <c r="M79" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N79" s="21" t="n">
-        <v>14.37354784103989</v>
+        <v>5.712871831528011</v>
       </c>
       <c r="O79" s="21" t="n">
-        <v>10.44635139915609</v>
+        <v>32.17730397042276</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>3.362100265326072</v>
+        <v>-1.18221551413651</v>
       </c>
       <c r="Q79" s="21" t="n">
-        <v>38.15</v>
+        <v>337.22</v>
       </c>
       <c r="R79" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S79" s="20" t="n">
-        <v>0.9403673440059026</v>
+        <v>0.554732848124369</v>
       </c>
       <c r="T79" s="15" t="inlineStr">
         <is>
-          <t>Progressive Leasing (97%)</t>
+          <t>Systems (67%)</t>
         </is>
       </c>
       <c r="U79" s="17" t="inlineStr">
         <is>
-          <t>Progressive Leasing 97%; Four 3%</t>
+          <t>Systems 67%; Components 33%</t>
         </is>
       </c>
       <c r="V79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" s="17" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="W79" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
+        </is>
+      </c>
       <c r="X79" s="15" t="inlineStr">
         <is>
-          <t>Four +170%</t>
+          <t>Systems +279%</t>
         </is>
       </c>
     </row>
@@ -52018,12 +52036,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Ies Holdings, Inc.</t>
+          <t>PROG Holdings, Inc.</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -52037,7 +52055,7 @@
         </is>
       </c>
       <c r="F80" s="18" t="n">
-        <v>13776098304</v>
+        <v>1472177024</v>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
@@ -52045,51 +52063,49 @@
         </is>
       </c>
       <c r="H80" s="20" t="n">
-        <v>22.535</v>
+        <v>8.850440627472885</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>30.729776</v>
+        <v>11.922581</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>11.206885</v>
+        <v>1.8279835</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>3.4563446</v>
+        <v>0.5630427</v>
       </c>
       <c r="L80" s="21" t="n">
-        <v>2.01426811681025</v>
-      </c>
-      <c r="M80" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.7154094641091</v>
+      </c>
+      <c r="M80" s="21" t="n">
+        <v>1.20889722398801</v>
       </c>
       <c r="N80" s="21" t="n">
-        <v>39.14787497533104</v>
+        <v>14.37354784103989</v>
       </c>
       <c r="O80" s="21" t="n">
-        <v>13.0825133917565</v>
+        <v>10.44635139915609</v>
       </c>
       <c r="P80" s="20" t="n">
-        <v>-0.6658293394323307</v>
+        <v>3.362100265326072</v>
       </c>
       <c r="Q80" s="21" t="n">
-        <v>64.63</v>
+        <v>38.15</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S80" s="20" t="n">
-        <v>0.302118628032772</v>
+        <v>0.9403673440059026</v>
       </c>
       <c r="T80" s="15" t="inlineStr">
         <is>
-          <t>Residential (39%)</t>
+          <t>Progressive Leasing (97%)</t>
         </is>
       </c>
       <c r="U80" s="17" t="inlineStr">
         <is>
-          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
+          <t>Progressive Leasing 97%; Four 3%</t>
         </is>
       </c>
       <c r="V80" s="18" t="n">
@@ -52098,7 +52114,7 @@
       <c r="W80" s="17" t="n"/>
       <c r="X80" s="15" t="inlineStr">
         <is>
-          <t>Commercialand Indust +109%</t>
+          <t>Four +170%</t>
         </is>
       </c>
     </row>
@@ -52108,12 +52124,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Ies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
@@ -52123,11 +52139,11 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F81" s="18" t="n">
-        <v>5271048421376</v>
+        <v>13776098304</v>
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
@@ -52135,62 +52151,60 @@
         </is>
       </c>
       <c r="H81" s="20" t="n">
-        <v>26.03</v>
+        <v>22.535</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>27.631645</v>
+        <v>30.729776</v>
       </c>
       <c r="J81" s="20" t="n">
-        <v>23.019087</v>
+        <v>11.206885</v>
       </c>
       <c r="K81" s="20" t="n">
-        <v>195.8478272042803</v>
+        <v>3.4563446</v>
       </c>
       <c r="L81" s="21" t="n">
-        <v>1.66135648441059</v>
-      </c>
-      <c r="M81" s="21" t="n">
-        <v>0.01871342168819</v>
+        <v>2.01426811681025</v>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N81" s="21" t="n">
-        <v>73.21388307718124</v>
+        <v>39.14787497533104</v>
       </c>
       <c r="O81" s="21" t="n">
-        <v>79.39769221313577</v>
+        <v>13.0825133917565</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>-0.3535471835000259</v>
+        <v>-0.6658293394323307</v>
       </c>
       <c r="Q81" s="21" t="n">
-        <v>13.91</v>
+        <v>64.63</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S81" s="20" t="n">
-        <v>0.8136213783744384</v>
+        <v>0.302118628032772</v>
       </c>
       <c r="T81" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networking (90%)</t>
+          <t>Residential (39%)</t>
         </is>
       </c>
       <c r="U81" s="17" t="inlineStr">
         <is>
-          <t>Compute And Networking 90%; Graphics 10%</t>
+          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
         </is>
       </c>
       <c r="V81" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W81" s="17" t="inlineStr">
-        <is>
-          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W81" s="17" t="n"/>
       <c r="X81" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networki +114%</t>
+          <t>Commercialand Indust +109%</t>
         </is>
       </c>
     </row>
@@ -52200,12 +52214,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -52215,11 +52229,11 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F82" s="18" t="n">
-        <v>10556858368</v>
+        <v>5271048421376</v>
       </c>
       <c r="G82" s="19" t="inlineStr">
         <is>
@@ -52227,64 +52241,62 @@
         </is>
       </c>
       <c r="H82" s="20" t="n">
-        <v>347.3889692037075</v>
+        <v>26.03</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>68.672195</v>
+        <v>27.631645</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>6.6218543</v>
+        <v>23.019087</v>
       </c>
       <c r="K82" s="20" t="n">
-        <v>4.817643283343015</v>
+        <v>195.8478272042803</v>
       </c>
       <c r="L82" s="21" t="n">
-        <v>-8.42592261675078</v>
-      </c>
-      <c r="M82" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.66135648441059</v>
+      </c>
+      <c r="M82" s="21" t="n">
+        <v>0.01871342168819</v>
       </c>
       <c r="N82" s="21" t="n">
-        <v>-0.11123836175898</v>
+        <v>73.21388307718124</v>
       </c>
       <c r="O82" s="21" t="n">
-        <v>1.17675041790433</v>
+        <v>79.39769221313577</v>
       </c>
       <c r="P82" s="20" t="n">
-        <v>-59.63858781496614</v>
+        <v>-0.3535471835000259</v>
       </c>
       <c r="Q82" s="21" t="n">
-        <v>7.08</v>
+        <v>13.91</v>
       </c>
       <c r="R82" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" s="20" t="n">
+        <v>0.8136213783744384</v>
+      </c>
+      <c r="T82" s="15" t="inlineStr">
+        <is>
+          <t>Compute And Networking (90%)</t>
+        </is>
+      </c>
+      <c r="U82" s="17" t="inlineStr">
+        <is>
+          <t>Compute And Networking 90%; Graphics 10%</t>
+        </is>
+      </c>
+      <c r="V82" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S82" s="20" t="n">
-        <v>0.3007342710765748</v>
-      </c>
-      <c r="T82" s="15" t="inlineStr">
-        <is>
-          <t>Brokerage (38%)</t>
-        </is>
-      </c>
-      <c r="U82" s="17" t="inlineStr">
-        <is>
-          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
-        </is>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>5</v>
-      </c>
       <c r="W82" s="17" t="inlineStr">
         <is>
-          <t>KZ 84%; AM 8%; CY 7%</t>
+          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
         </is>
       </c>
       <c r="X82" s="15" t="inlineStr">
         <is>
-          <t>Other +100%</t>
+          <t>Compute And Networki +114%</t>
         </is>
       </c>
     </row>
@@ -52294,12 +52306,12 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>FutureFuel Corp.</t>
+          <t>Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
@@ -52309,80 +52321,76 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F83" s="18" t="n">
-        <v>239932352</v>
+        <v>10556858368</v>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H83" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I83" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H83" s="20" t="n">
+        <v>347.3889692037075</v>
+      </c>
+      <c r="I83" s="20" t="n">
+        <v>68.672195</v>
       </c>
       <c r="J83" s="20" t="n">
-        <v>1.5673351</v>
+        <v>6.6218543</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>1.5660461</v>
+        <v>4.817643283343015</v>
       </c>
       <c r="L83" s="21" t="n">
-        <v>-19.02773752715573</v>
-      </c>
-      <c r="M83" s="21" t="n">
-        <v>5.946712029429071</v>
+        <v>-8.42592261675078</v>
+      </c>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N83" s="21" t="n">
-        <v>-51.30812980930077</v>
+        <v>-0.11123836175898</v>
       </c>
       <c r="O83" s="21" t="n">
-        <v>-11.30220868498371</v>
-      </c>
-      <c r="P83" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.17675041790433</v>
+      </c>
+      <c r="P83" s="20" t="n">
+        <v>-59.63858781496614</v>
       </c>
       <c r="Q83" s="21" t="n">
-        <v>38.74</v>
+        <v>7.08</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S83" s="20" t="n">
-        <v>0.5298367272208879</v>
+        <v>0.3007342710765748</v>
       </c>
       <c r="T83" s="15" t="inlineStr">
         <is>
-          <t>Chemicals (62%)</t>
+          <t>Brokerage (38%)</t>
         </is>
       </c>
       <c r="U83" s="17" t="inlineStr">
         <is>
-          <t>Chemicals 62%; Biofuels 38%</t>
+          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
         </is>
       </c>
       <c r="V83" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W83" s="17" t="inlineStr">
         <is>
-          <t>US 99%; Non Us 1%</t>
+          <t>KZ 84%; AM 8%; CY 7%</t>
         </is>
       </c>
       <c r="X83" s="15" t="inlineStr">
         <is>
-          <t>Biofuels +178%</t>
+          <t>Other +100%</t>
         </is>
       </c>
     </row>
@@ -52392,12 +52400,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>SLNH</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Soluna Holdings Inc. Common St</t>
+          <t>FutureFuel Corp.</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -52407,11 +52415,11 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F84" s="18" t="n">
-        <v>291062784</v>
+        <v>239932352</v>
       </c>
       <c r="G84" s="19" t="inlineStr">
         <is>
@@ -52429,24 +52437,22 @@
         </is>
       </c>
       <c r="J84" s="20" t="n">
-        <v>1.7097702</v>
+        <v>1.5673351</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>6.9173846</v>
+        <v>1.5660461</v>
       </c>
       <c r="L84" s="21" t="n">
-        <v>-15.20023065482923</v>
+        <v>-19.02773752715573</v>
       </c>
       <c r="M84" s="21" t="n">
-        <v>0.20077091953947</v>
-      </c>
-      <c r="N84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.946712029429071</v>
+      </c>
+      <c r="N84" s="21" t="n">
+        <v>-51.30812980930077</v>
       </c>
       <c r="O84" s="21" t="n">
-        <v>-104.2041970672814</v>
+        <v>-11.30220868498371</v>
       </c>
       <c r="P84" s="22" t="inlineStr">
         <is>
@@ -52454,31 +52460,35 @@
         </is>
       </c>
       <c r="Q84" s="21" t="n">
-        <v>-65.62</v>
+        <v>38.74</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S84" s="20" t="n">
-        <v>0.5183581202661786</v>
+        <v>0.5298367272208879</v>
       </c>
       <c r="T84" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting (60%)</t>
+          <t>Chemicals (62%)</t>
         </is>
       </c>
       <c r="U84" s="17" t="inlineStr">
         <is>
-          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
+          <t>Chemicals 62%; Biofuels 38%</t>
         </is>
       </c>
       <c r="V84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W84" s="17" t="inlineStr">
+        <is>
+          <t>US 99%; Non Us 1%</t>
+        </is>
+      </c>
       <c r="X84" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting +303%</t>
+          <t>Biofuels +178%</t>
         </is>
       </c>
     </row>
@@ -52488,12 +52498,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>SLNH</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Soluna Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
@@ -52503,74 +52513,78 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F85" s="18" t="n">
-        <v>98965053440</v>
+        <v>291062784</v>
       </c>
       <c r="G85" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H85" s="20" t="n">
-        <v>48.51287624683352</v>
-      </c>
-      <c r="I85" s="20" t="n">
-        <v>58.15837</v>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J85" s="20" t="n">
-        <v>20.799417</v>
+        <v>1.7097702</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>8.620950000000001</v>
+        <v>6.9173846</v>
       </c>
       <c r="L85" s="21" t="n">
-        <v>2.71275941299938</v>
+        <v>-15.20023065482923</v>
       </c>
       <c r="M85" s="21" t="n">
-        <v>0.03768476778678</v>
-      </c>
-      <c r="N85" s="21" t="n">
-        <v>33.68683344961626</v>
+        <v>0.20077091953947</v>
+      </c>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O85" s="21" t="n">
-        <v>21.35492557684859</v>
-      </c>
-      <c r="P85" s="20" t="n">
-        <v>0.3332181723959233</v>
+        <v>-104.2041970672814</v>
+      </c>
+      <c r="P85" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q85" s="21" t="n">
-        <v>45.58</v>
+        <v>-65.62</v>
       </c>
       <c r="R85" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S85" s="20" t="n">
-        <v>0.5218491323594365</v>
+        <v>0.5183581202661786</v>
       </c>
       <c r="T85" s="15" t="inlineStr">
         <is>
-          <t>EMEA (66%)</t>
+          <t>Data Center Hosting (60%)</t>
         </is>
       </c>
       <c r="U85" s="17" t="inlineStr">
         <is>
-          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
+          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
         </is>
       </c>
       <c r="V85" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W85" s="17" t="inlineStr">
-        <is>
-          <t>US 59%; Asia 20%; Europe 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W85" s="17" t="n"/>
       <c r="X85" s="15" t="inlineStr">
         <is>
-          <t>Asia Pacific +290%</t>
+          <t>Data Center Hosting +303%</t>
         </is>
       </c>
     </row>
@@ -52580,12 +52594,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -52595,11 +52609,11 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F86" s="18" t="n">
-        <v>3749439488</v>
+        <v>98965053440</v>
       </c>
       <c r="G86" s="19" t="inlineStr">
         <is>
@@ -52607,58 +52621,62 @@
         </is>
       </c>
       <c r="H86" s="20" t="n">
-        <v>19.297</v>
+        <v>48.51287624683352</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>30.920187</v>
+        <v>58.15837</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>4.9097958</v>
+        <v>20.799417</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>6.8440413</v>
+        <v>8.620950000000001</v>
       </c>
       <c r="L86" s="21" t="n">
-        <v>5.56871008366637</v>
+        <v>2.71275941299938</v>
       </c>
       <c r="M86" s="21" t="n">
-        <v>0.97</v>
+        <v>0.03768476778678</v>
       </c>
       <c r="N86" s="21" t="n">
-        <v>12.37235274898268</v>
+        <v>33.68683344961626</v>
       </c>
       <c r="O86" s="21" t="n">
-        <v>35.60723129340358</v>
+        <v>21.35492557684859</v>
       </c>
       <c r="P86" s="20" t="n">
-        <v>1.359732752360203</v>
+        <v>0.3332181723959233</v>
       </c>
       <c r="Q86" s="21" t="n">
-        <v>17.58</v>
+        <v>45.58</v>
       </c>
       <c r="R86" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S86" s="20" t="n">
-        <v>0.4262861010394083</v>
+        <v>0.5218491323594365</v>
       </c>
       <c r="T86" s="15" t="inlineStr">
         <is>
-          <t>Hospitality (52%)</t>
+          <t>EMEA (66%)</t>
         </is>
       </c>
       <c r="U86" s="17" t="inlineStr">
         <is>
-          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
+          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
         </is>
       </c>
       <c r="V86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W86" s="17" t="inlineStr">
+        <is>
+          <t>US 59%; Asia 20%; Europe 14%</t>
+        </is>
+      </c>
       <c r="X86" s="15" t="inlineStr">
         <is>
-          <t>Hospitality +157%</t>
+          <t>Asia Pacific +290%</t>
         </is>
       </c>
     </row>
@@ -52668,12 +52686,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Homestolife Ltd</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
@@ -52683,11 +52701,11 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F87" s="18" t="n">
-        <v>159643760</v>
+        <v>3749439488</v>
       </c>
       <c r="G87" s="19" t="inlineStr">
         <is>
@@ -52695,66 +52713,58 @@
         </is>
       </c>
       <c r="H87" s="20" t="n">
-        <v>5.632</v>
+        <v>19.297</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>9.368421</v>
+        <v>30.920187</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>5.189504</v>
+        <v>4.9097958</v>
       </c>
       <c r="K87" s="20" t="n">
-        <v>0.4083795</v>
+        <v>6.8440413</v>
       </c>
       <c r="L87" s="21" t="n">
-        <v>7.56174932272778</v>
-      </c>
-      <c r="M87" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N87" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.56871008366637</v>
+      </c>
+      <c r="M87" s="21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N87" s="21" t="n">
+        <v>12.37235274898268</v>
       </c>
       <c r="O87" s="21" t="n">
-        <v>5.26038476371263</v>
+        <v>35.60723129340358</v>
       </c>
       <c r="P87" s="20" t="n">
-        <v>-0.8495431924900106</v>
+        <v>1.359732752360203</v>
       </c>
       <c r="Q87" s="21" t="n">
-        <v>-46.17305967367813</v>
+        <v>17.58</v>
       </c>
       <c r="R87" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S87" s="20" t="n">
-        <v>0.8590900293205138</v>
+        <v>0.4262861010394083</v>
       </c>
       <c r="T87" s="15" t="inlineStr">
         <is>
-          <t>Export Sales (93%)</t>
+          <t>Hospitality (52%)</t>
         </is>
       </c>
       <c r="U87" s="17" t="inlineStr">
         <is>
-          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
+          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
         </is>
       </c>
       <c r="V87" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W87" s="17" t="inlineStr">
-        <is>
-          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W87" s="17" t="n"/>
       <c r="X87" s="15" t="inlineStr">
         <is>
-          <t>Retail Sales +100%</t>
+          <t>Hospitality +157%</t>
         </is>
       </c>
     </row>
@@ -52764,12 +52774,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>HTLM</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>Homestolife Ltd</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -52779,11 +52789,11 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F88" s="18" t="n">
-        <v>113033160</v>
+        <v>159643760</v>
       </c>
       <c r="G88" s="19" t="inlineStr">
         <is>
@@ -52791,64 +52801,66 @@
         </is>
       </c>
       <c r="H88" s="20" t="n">
-        <v>11.493</v>
+        <v>5.632</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>22.772728</v>
+        <v>9.368421</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>1.8398825</v>
+        <v>5.189504</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>4.0441093</v>
+        <v>0.4083795</v>
       </c>
       <c r="L88" s="21" t="n">
-        <v>5.20947381148941</v>
+        <v>7.56174932272778</v>
       </c>
       <c r="M88" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N88" s="21" t="n">
-        <v>16.80549850408138</v>
+      <c r="N88" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O88" s="21" t="n">
-        <v>24.49495025980879</v>
+        <v>5.26038476371263</v>
       </c>
       <c r="P88" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>-0.8495431924900106</v>
       </c>
       <c r="Q88" s="21" t="n">
-        <v>-0.7799999999999999</v>
+        <v>-46.17305967367813</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S88" s="20" t="n">
-        <v>0.3385873824755823</v>
+        <v>0.8590900293205138</v>
       </c>
       <c r="T88" s="15" t="inlineStr">
         <is>
-          <t>Defense Engineering Se (45%)</t>
+          <t>Export Sales (93%)</t>
         </is>
       </c>
       <c r="U88" s="17" t="inlineStr">
         <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
         </is>
       </c>
       <c r="V88" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W88" s="17" t="inlineStr">
         <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
+          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
         </is>
       </c>
       <c r="X88" s="15" t="inlineStr">
         <is>
-          <t>Marine Technology Bu +185%</t>
+          <t>Retail Sales +100%</t>
         </is>
       </c>
     </row>
@@ -52858,48 +52870,46 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>FENG</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Phoenix New Media Limited</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F89" s="18" t="n">
-        <v>17896056</v>
+        <v>113033160</v>
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H89" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H89" s="20" t="n">
+        <v>11.493</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>4.012985014645349</v>
+        <v>22.772728</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>22.1065917175247</v>
+        <v>1.8398825</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>0.1460944416764449</v>
+        <v>4.0441093</v>
       </c>
       <c r="L89" s="21" t="n">
-        <v>-0.32072677140719</v>
+        <v>5.20947381148941</v>
       </c>
       <c r="M89" s="22" t="inlineStr">
         <is>
@@ -52907,42 +52917,44 @@
         </is>
       </c>
       <c r="N89" s="21" t="n">
-        <v>-8.02638700256313</v>
+        <v>16.80549850408138</v>
       </c>
       <c r="O89" s="21" t="n">
-        <v>-1.79463043292417</v>
-      </c>
-      <c r="P89" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.49495025980879</v>
+      </c>
+      <c r="P89" s="20" t="n">
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q89" s="21" t="n">
-        <v>-36.75</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S89" s="20" t="n">
-        <v>0.682948135046668</v>
+        <v>0.3385873824755823</v>
       </c>
       <c r="T89" s="15" t="inlineStr">
         <is>
-          <t>Net Advertising Servic (80%)</t>
+          <t>Defense Engineering Se (45%)</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
-          <t>Net Advertising Services 80%; Paid Services 20%</t>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
         </is>
       </c>
       <c r="V89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W89" s="17" t="inlineStr">
+        <is>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
+        </is>
+      </c>
       <c r="X89" s="15" t="inlineStr">
         <is>
-          <t>Paid Services +107%</t>
+          <t>Marine Technology Bu +185%</t>
         </is>
       </c>
     </row>
@@ -52952,26 +52964,26 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Schrodinger, Inc.</t>
+          <t>Phoenix New Media Limited</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F90" s="18" t="n">
-        <v>1422803200</v>
+        <v>17896056</v>
       </c>
       <c r="G90" s="19" t="inlineStr">
         <is>
@@ -52983,32 +52995,28 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I90" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I90" s="20" t="n">
+        <v>4.012985014645349</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>4.213558</v>
+        <v>22.1065917175247</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>5.4927063</v>
+        <v>0.1460944416764449</v>
       </c>
       <c r="L90" s="21" t="n">
-        <v>-8.66829141064739</v>
+        <v>-0.32072677140719</v>
       </c>
       <c r="M90" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N90" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N90" s="21" t="n">
+        <v>-8.02638700256313</v>
       </c>
       <c r="O90" s="21" t="n">
-        <v>-84.61893927057798</v>
+        <v>-1.79463043292417</v>
       </c>
       <c r="P90" s="22" t="inlineStr">
         <is>
@@ -53016,35 +53024,31 @@
         </is>
       </c>
       <c r="Q90" s="21" t="n">
-        <v>-4.52</v>
+        <v>-36.75</v>
       </c>
       <c r="R90" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="20" t="n">
-        <v>0.6564595481920475</v>
+        <v>0.682948135046668</v>
       </c>
       <c r="T90" s="15" t="inlineStr">
         <is>
-          <t>Software (78%)</t>
+          <t>Net Advertising Servic (80%)</t>
         </is>
       </c>
       <c r="U90" s="17" t="inlineStr">
         <is>
-          <t>Software 78%; Drug Discovery 22%</t>
+          <t>Net Advertising Services 80%; Paid Services 20%</t>
         </is>
       </c>
       <c r="V90" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W90" s="17" t="inlineStr">
-        <is>
-          <t>US 60%; EMEA 29%; APAC 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W90" s="17" t="n"/>
       <c r="X90" s="15" t="inlineStr">
         <is>
-          <t>Drug Discovery +107%</t>
+          <t>Paid Services +107%</t>
         </is>
       </c>
     </row>
@@ -53054,12 +53058,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc.</t>
+          <t>Schrodinger, Inc.</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
@@ -53069,74 +53073,84 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F91" s="18" t="n">
-        <v>10568248320</v>
+        <v>1422803200</v>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H91" s="20" t="n">
-        <v>-37.43331715008421</v>
-      </c>
-      <c r="I91" s="20" t="n">
-        <v>27.1789460083687</v>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J91" s="20" t="n">
-        <v>1.0001347</v>
+        <v>4.213558</v>
       </c>
       <c r="K91" s="20" t="n">
-        <v>1.9561423</v>
+        <v>5.4927063</v>
       </c>
       <c r="L91" s="21" t="n">
-        <v>16.83374525401008</v>
-      </c>
-      <c r="M91" s="21" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N91" s="21" t="n">
-        <v>-0.21791453369172</v>
+        <v>-8.66829141064739</v>
+      </c>
+      <c r="M91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>5.51745776158655</v>
-      </c>
-      <c r="P91" s="20" t="n">
-        <v>-80.28756909079929</v>
+        <v>-84.61893927057798</v>
+      </c>
+      <c r="P91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q91" s="21" t="n">
-        <v>7.7</v>
+        <v>-4.52</v>
       </c>
       <c r="R91" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>0.8308945641579533</v>
+        <v>0.6564595481920475</v>
       </c>
       <c r="T91" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking And (91%)</t>
+          <t>Software (78%)</t>
         </is>
       </c>
       <c r="U91" s="17" t="inlineStr">
         <is>
-          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
+          <t>Software 78%; Drug Discovery 22%</t>
         </is>
       </c>
       <c r="V91" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W91" s="17" t="inlineStr">
         <is>
-          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
+          <t>US 60%; EMEA 29%; APAC 10%</t>
         </is>
       </c>
       <c r="X91" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking A +123%</t>
+          <t>Drug Discovery +107%</t>
         </is>
       </c>
     </row>
@@ -53146,12 +53160,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>ANNA</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>AleAnna Inc. Class A Common St</t>
+          <t>Jefferies Financial Group Inc.</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -53161,72 +53175,74 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>143290000</v>
-      </c>
-      <c r="G92" s="23" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>10568248320</v>
+      </c>
+      <c r="G92" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>8.568</v>
+        <v>-37.43331715008421</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>18.421053</v>
+        <v>27.1789460083687</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>3.5425103</v>
+        <v>1.0001347</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>3.5894861</v>
+        <v>1.9561423</v>
       </c>
       <c r="L92" s="21" t="n">
-        <v>7.167953799986041</v>
-      </c>
-      <c r="M92" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.83374525401008</v>
+      </c>
+      <c r="M92" s="21" t="n">
+        <v>3.26</v>
       </c>
       <c r="N92" s="21" t="n">
-        <v>1.46144795620644</v>
+        <v>-0.21791453369172</v>
       </c>
       <c r="O92" s="21" t="n">
-        <v>39.48335699937504</v>
+        <v>5.51745776158655</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>-1.974742069364569</v>
+        <v>-80.28756909079929</v>
       </c>
       <c r="Q92" s="21" t="n">
-        <v>-7.69</v>
+        <v>7.7</v>
       </c>
       <c r="R92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S92" s="20" t="n">
-        <v>0.8097190789385638</v>
+        <v>0.8308945641579533</v>
       </c>
       <c r="T92" s="15" t="inlineStr">
         <is>
-          <t>Conventional (89%)</t>
+          <t>Investment Banking And (91%)</t>
         </is>
       </c>
       <c r="U92" s="17" t="inlineStr">
         <is>
-          <t>Conventional 89%; Renewable 11%</t>
+          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
         </is>
       </c>
       <c r="V92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W92" s="17" t="inlineStr">
+        <is>
+          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
+        </is>
+      </c>
       <c r="X92" s="15" t="inlineStr">
         <is>
-          <t>Conventional +186%</t>
+          <t>Investment Banking A +123%</t>
         </is>
       </c>
     </row>
@@ -53236,12 +53252,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>LVWR</t>
+          <t>ANNA</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>LiveWire Group Inc. Common Sto</t>
+          <t>AleAnna Inc. Class A Common St</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -53251,84 +53267,72 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>234170208</v>
-      </c>
-      <c r="G93" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="H93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>143290000</v>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>8.568</v>
+      </c>
+      <c r="I93" s="20" t="n">
+        <v>18.421053</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>19.655172</v>
+        <v>3.5425103</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>7.484824</v>
+        <v>3.5894861</v>
       </c>
       <c r="L93" s="21" t="n">
-        <v>-21.59336790483196</v>
+        <v>7.167953799986041</v>
       </c>
       <c r="M93" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N93" s="21" t="n">
+        <v>1.46144795620644</v>
       </c>
       <c r="O93" s="21" t="n">
-        <v>-207.6711628204309</v>
-      </c>
-      <c r="P93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>39.48335699937504</v>
+      </c>
+      <c r="P93" s="20" t="n">
+        <v>-1.974742069364569</v>
       </c>
       <c r="Q93" s="21" t="n">
-        <v>-76.64</v>
+        <v>-7.69</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>0.4547555777310531</v>
+        <v>0.8097190789385638</v>
       </c>
       <c r="T93" s="15" t="inlineStr">
         <is>
-          <t>STACYC (62%)</t>
+          <t>Conventional (89%)</t>
         </is>
       </c>
       <c r="U93" s="17" t="inlineStr">
         <is>
-          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
+          <t>Conventional 89%; Renewable 11%</t>
         </is>
       </c>
       <c r="V93" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W93" s="17" t="inlineStr">
-        <is>
-          <t>US 74%; Non Us 24%; AT 2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W93" s="17" t="n"/>
       <c r="X93" s="15" t="inlineStr">
         <is>
-          <t>Electric Motorcycle +333%</t>
+          <t>Conventional +186%</t>
         </is>
       </c>
     </row>
@@ -53338,12 +53342,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>LVWR</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd</t>
+          <t>LiveWire Group Inc. Common Sto</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -53353,11 +53357,11 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>3207403776</v>
+        <v>234170208</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
@@ -53369,20 +53373,24 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I94" s="20" t="n">
-        <v>9.698138</v>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.57766795</v>
+        <v>19.655172</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>2.931813323583181</v>
+        <v>7.484824</v>
       </c>
       <c r="L94" s="21" t="n">
-        <v>10.10162806517815</v>
-      </c>
-      <c r="M94" s="21" t="n">
-        <v>1.91</v>
+        <v>-21.59336790483196</v>
+      </c>
+      <c r="M94" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N94" s="22" t="inlineStr">
         <is>
@@ -53390,7 +53398,7 @@
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>0</v>
+        <v>-207.6711628204309</v>
       </c>
       <c r="P94" s="22" t="inlineStr">
         <is>
@@ -53398,35 +53406,35 @@
         </is>
       </c>
       <c r="Q94" s="21" t="n">
-        <v>-4.7</v>
+        <v>-76.64</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>0.9375650364203956</v>
+        <v>0.4547555777310531</v>
       </c>
       <c r="T94" s="15" t="inlineStr">
         <is>
-          <t>Insurance (97%)</t>
+          <t>STACYC (62%)</t>
         </is>
       </c>
       <c r="U94" s="17" t="inlineStr">
         <is>
-          <t>Insurance 97%; Asset Management 3%</t>
+          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
         </is>
       </c>
       <c r="V94" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W94" s="17" t="inlineStr">
         <is>
-          <t>US 77%; BM 18%; GB 5%</t>
+          <t>US 74%; Non Us 24%; AT 2%</t>
         </is>
       </c>
       <c r="X94" s="15" t="inlineStr">
         <is>
-          <t>Asset Management +190%</t>
+          <t>Electric Motorcycle +333%</t>
         </is>
       </c>
     </row>
@@ -53436,12 +53444,12 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>KTB</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Kontoor Brands, Inc.</t>
+          <t>Assured Guaranty Ltd</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
@@ -53451,74 +53459,80 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>3641024256</v>
+        <v>3207403776</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H95" s="20" t="n">
-        <v>11.55529127502649</v>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I95" s="20" t="n">
-        <v>13.48583</v>
+        <v>9.698138</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>5.8861995</v>
+        <v>0.57766795</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>1.0601529</v>
+        <v>2.931813323583181</v>
       </c>
       <c r="L95" s="21" t="n">
-        <v>10.52193541631924</v>
+        <v>10.10162806517815</v>
       </c>
       <c r="M95" s="21" t="n">
-        <v>2.91957418972506</v>
-      </c>
-      <c r="N95" s="21" t="n">
-        <v>17.92240674479327</v>
+        <v>1.91</v>
+      </c>
+      <c r="N95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.30013869457824</v>
-      </c>
-      <c r="P95" s="20" t="n">
-        <v>2.601238735236491</v>
+        <v>0</v>
+      </c>
+      <c r="P95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q95" s="21" t="n">
-        <v>-7.049999999999999</v>
+        <v>-4.7</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S95" s="20" t="n">
-        <v>0.4547588013008751</v>
+        <v>0.9375650364203956</v>
       </c>
       <c r="T95" s="15" t="inlineStr">
         <is>
-          <t>Wrangler (61%)</t>
+          <t>Insurance (97%)</t>
         </is>
       </c>
       <c r="U95" s="17" t="inlineStr">
         <is>
-          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+          <t>Insurance 97%; Asset Management 3%</t>
         </is>
       </c>
       <c r="V95" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W95" s="17" t="inlineStr">
         <is>
-          <t>US 73%; Non Us 27%</t>
+          <t>US 77%; BM 18%; GB 5%</t>
         </is>
       </c>
       <c r="X95" s="15" t="inlineStr">
         <is>
-          <t>Helly Hansen +300%</t>
+          <t>Asset Management +190%</t>
         </is>
       </c>
     </row>
@@ -53528,12 +53542,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>PED</t>
+          <t>KTB</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>PEDEVCO Corp.</t>
+          <t>Kontoor Brands, Inc.</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -53543,11 +53557,11 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F96" s="18" t="n">
-        <v>197253472</v>
+        <v>3641024256</v>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
@@ -53555,62 +53569,62 @@
         </is>
       </c>
       <c r="H96" s="20" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I96" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.55529127502649</v>
+      </c>
+      <c r="I96" s="20" t="n">
+        <v>13.48583</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.9859154999999999</v>
+        <v>5.8861995</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1.6949378</v>
+        <v>1.0601529</v>
       </c>
       <c r="L96" s="21" t="n">
-        <v>16.30471233572627</v>
-      </c>
-      <c r="M96" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.52193541631924</v>
+      </c>
+      <c r="M96" s="21" t="n">
+        <v>2.91957418972506</v>
       </c>
       <c r="N96" s="21" t="n">
-        <v>2.16353455637511</v>
+        <v>17.92240674479327</v>
       </c>
       <c r="O96" s="21" t="n">
-        <v>49.94500678822457</v>
+        <v>13.30013869457824</v>
       </c>
       <c r="P96" s="20" t="n">
-        <v>1.332008602150538</v>
+        <v>2.601238735236491</v>
       </c>
       <c r="Q96" s="21" t="n">
-        <v>18.91</v>
+        <v>-7.049999999999999</v>
       </c>
       <c r="R96" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S96" s="20" t="n">
-        <v>0.7805028355388554</v>
+        <v>0.4547588013008751</v>
       </c>
       <c r="T96" s="15" t="inlineStr">
         <is>
-          <t>Oil Sales (88%)</t>
+          <t>Wrangler (61%)</t>
         </is>
       </c>
       <c r="U96" s="17" t="inlineStr">
         <is>
-          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
+          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
         </is>
       </c>
       <c r="V96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W96" s="17" t="inlineStr">
+        <is>
+          <t>US 73%; Non Us 27%</t>
+        </is>
+      </c>
       <c r="X96" s="15" t="inlineStr">
         <is>
-          <t>Natural Gas Liquids  +465%</t>
+          <t>Helly Hansen +300%</t>
         </is>
       </c>
     </row>
@@ -53620,12 +53634,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>PED</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>PEDEVCO Corp.</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
@@ -53635,11 +53649,11 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F97" s="18" t="n">
-        <v>1101452017664</v>
+        <v>197253472</v>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
@@ -53647,62 +53661,62 @@
         </is>
       </c>
       <c r="H97" s="20" t="n">
-        <v>15.852</v>
-      </c>
-      <c r="I97" s="20" t="n">
-        <v>22.024843</v>
+        <v>4.59</v>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J97" s="20" t="n">
-        <v>10.93157</v>
+        <v>0.9859154999999999</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>12.20121</v>
+        <v>1.6949378</v>
       </c>
       <c r="L97" s="21" t="n">
-        <v>2.27953325914988</v>
-      </c>
-      <c r="M97" s="21" t="n">
-        <v>0.05</v>
+        <v>16.30471233572627</v>
+      </c>
+      <c r="M97" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N97" s="21" t="n">
-        <v>38.68963277836816</v>
+        <v>2.16353455637511</v>
       </c>
       <c r="O97" s="21" t="n">
-        <v>63.47412363053029</v>
+        <v>49.94500678822457</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>-0.1351809304997128</v>
+        <v>1.332008602150538</v>
       </c>
       <c r="Q97" s="21" t="n">
-        <v>354.75</v>
+        <v>18.91</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S97" s="20" t="n">
-        <v>0.2853460159862896</v>
+        <v>0.7805028355388554</v>
       </c>
       <c r="T97" s="15" t="inlineStr">
         <is>
-          <t>CMBU (36%)</t>
+          <t>Oil Sales (88%)</t>
         </is>
       </c>
       <c r="U97" s="17" t="inlineStr">
         <is>
-          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
+          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
         </is>
       </c>
       <c r="V97" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="W97" s="17" t="inlineStr">
-        <is>
-          <t>US 65%; TW 15%; CN 7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W97" s="17" t="n"/>
       <c r="X97" s="15" t="inlineStr">
         <is>
-          <t>AEBU +311%</t>
+          <t>Natural Gas Liquids  +465%</t>
         </is>
       </c>
     </row>
@@ -53712,12 +53726,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>EVC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Entravision Communications Cor</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -53727,11 +53741,11 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F98" s="18" t="n">
-        <v>794602240</v>
+        <v>1101452017664</v>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
@@ -53739,62 +53753,62 @@
         </is>
       </c>
       <c r="H98" s="20" t="n">
-        <v>27.53410143448773</v>
+        <v>15.852</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>190.0388450278689</v>
+        <v>22.024843</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>9.503311</v>
+        <v>10.93157</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>1.557472534580458</v>
+        <v>12.20121</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>8.44176513325125</v>
+        <v>2.27953325914988</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>2.57525386044693</v>
+        <v>0.05</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-26.42668897457025</v>
+        <v>38.68963277836816</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>6.53133066895079</v>
+        <v>63.47412363053029</v>
       </c>
       <c r="P98" s="20" t="n">
-        <v>2.821679370986135</v>
+        <v>-0.1351809304997128</v>
       </c>
       <c r="Q98" s="21" t="n">
-        <v>322.51</v>
+        <v>354.75</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S98" s="20" t="n">
-        <v>0.5221821576458947</v>
+        <v>0.2853460159862896</v>
       </c>
       <c r="T98" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technology (61%)</t>
+          <t>CMBU (36%)</t>
         </is>
       </c>
       <c r="U98" s="17" t="inlineStr">
         <is>
-          <t>Advertising Technology And Services 61%; Media 39%</t>
+          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
         </is>
       </c>
       <c r="V98" s="18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W98" s="17" t="inlineStr">
         <is>
-          <t>US 58%; Non Us 42%</t>
+          <t>US 65%; TW 15%; CN 7%</t>
         </is>
       </c>
       <c r="X98" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technolo +230%</t>
+          <t>AEBU +311%</t>
         </is>
       </c>
     </row>
@@ -53804,12 +53818,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>EVC</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Compass, Inc.</t>
+          <t>Entravision Communications Cor</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
@@ -53819,11 +53833,11 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F99" s="18" t="n">
-        <v>8067944960</v>
+        <v>794602240</v>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
@@ -53831,62 +53845,62 @@
         </is>
       </c>
       <c r="H99" s="20" t="n">
-        <v>120.5991376271186</v>
+        <v>27.53410143448773</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>119.5251105185185</v>
+        <v>190.0388450278689</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>2.6573958</v>
+        <v>9.503311</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>1.012822938060207</v>
+        <v>1.557472534580458</v>
       </c>
       <c r="L99" s="21" t="n">
-        <v>1.5004325303195</v>
-      </c>
-      <c r="M99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.44176513325125</v>
+      </c>
+      <c r="M99" s="21" t="n">
+        <v>2.57525386044693</v>
       </c>
       <c r="N99" s="21" t="n">
-        <v>-6.802410518626729</v>
+        <v>-26.42668897457025</v>
       </c>
       <c r="O99" s="21" t="n">
-        <v>1.1850661578247</v>
-      </c>
-      <c r="P99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.53133066895079</v>
+      </c>
+      <c r="P99" s="20" t="n">
+        <v>2.821679370986135</v>
       </c>
       <c r="Q99" s="21" t="n">
-        <v>44.23</v>
+        <v>322.51</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S99" s="20" t="n">
-        <v>0.8491346718272323</v>
+        <v>0.5221821576458947</v>
       </c>
       <c r="T99" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (92%)</t>
+          <t>Advertising Technology (61%)</t>
         </is>
       </c>
       <c r="U99" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
+          <t>Advertising Technology And Services 61%; Media 39%</t>
         </is>
       </c>
       <c r="V99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W99" s="17" t="inlineStr">
+        <is>
+          <t>US 58%; Non Us 42%</t>
+        </is>
+      </c>
       <c r="X99" s="15" t="inlineStr">
         <is>
-          <t>Brokerage +97%</t>
+          <t>Advertising Technolo +230%</t>
         </is>
       </c>
     </row>
@@ -53896,12 +53910,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Compass, Inc.</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -53911,11 +53925,11 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F100" s="18" t="n">
-        <v>419900817408</v>
+        <v>8067944960</v>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
@@ -53923,49 +53937,53 @@
         </is>
       </c>
       <c r="H100" s="20" t="n">
-        <v>8.913</v>
+        <v>120.5991376271186</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>20.62235</v>
+        <v>119.5251105185185</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>2.2113636</v>
+        <v>2.6573958</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>2.0054102</v>
+        <v>1.012822938060207</v>
       </c>
       <c r="L100" s="21" t="n">
-        <v>6.60132683312082</v>
-      </c>
-      <c r="M100" s="21" t="n">
-        <v>4.16</v>
+        <v>1.5004325303195</v>
+      </c>
+      <c r="M100" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N100" s="21" t="n">
-        <v>8.69285484505129</v>
+        <v>-6.802410518626729</v>
       </c>
       <c r="O100" s="21" t="n">
-        <v>22.36304851872374</v>
-      </c>
-      <c r="P100" s="20" t="n">
-        <v>0.9647582391147462</v>
+        <v>1.1850661578247</v>
+      </c>
+      <c r="P100" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q100" s="21" t="n">
-        <v>37.47</v>
+        <v>44.23</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S100" s="20" t="n">
-        <v>0.9067367242961308</v>
+        <v>0.8491346718272323</v>
       </c>
       <c r="T100" s="15" t="inlineStr">
         <is>
-          <t>Upstream (95%)</t>
+          <t>Brokerage (92%)</t>
         </is>
       </c>
       <c r="U100" s="17" t="inlineStr">
         <is>
-          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
+          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
         </is>
       </c>
       <c r="V100" s="18" t="n">
@@ -53974,7 +53992,7 @@
       <c r="W100" s="17" t="n"/>
       <c r="X100" s="15" t="inlineStr">
         <is>
-          <t>Upstream +298%</t>
+          <t>Brokerage +97%</t>
         </is>
       </c>
     </row>
@@ -53984,12 +54002,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
@@ -53999,11 +54017,11 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F101" s="18" t="n">
-        <v>73726443520</v>
+        <v>419900817408</v>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
@@ -54011,62 +54029,58 @@
         </is>
       </c>
       <c r="H101" s="20" t="n">
-        <v>15.61168969542968</v>
+        <v>8.913</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>16.501429</v>
+        <v>20.62235</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>4.1224737</v>
+        <v>2.2113636</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>1.7188857</v>
+        <v>2.0054102</v>
       </c>
       <c r="L101" s="21" t="n">
-        <v>4.9836238568399</v>
+        <v>6.60132683312082</v>
       </c>
       <c r="M101" s="21" t="n">
-        <v>1.505494379293</v>
+        <v>4.16</v>
       </c>
       <c r="N101" s="21" t="n">
-        <v>14.00609392594555</v>
+        <v>8.69285484505129</v>
       </c>
       <c r="O101" s="21" t="n">
-        <v>13.37597658555007</v>
+        <v>22.36304851872374</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>2.307923063349215</v>
+        <v>0.9647582391147462</v>
       </c>
       <c r="Q101" s="21" t="n">
-        <v>-10.3</v>
+        <v>37.47</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S101" s="20" t="n">
-        <v>0.4182092579820682</v>
+        <v>0.9067367242961308</v>
       </c>
       <c r="T101" s="15" t="inlineStr">
         <is>
-          <t>Mission Systems (58%)</t>
+          <t>Upstream (95%)</t>
         </is>
       </c>
       <c r="U101" s="17" t="inlineStr">
         <is>
-          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
+          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
         </is>
       </c>
       <c r="V101" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W101" s="17" t="inlineStr">
-        <is>
-          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W101" s="17" t="n"/>
       <c r="X101" s="15" t="inlineStr">
         <is>
-          <t>Aeronautics Systems +130%</t>
+          <t>Upstream +298%</t>
         </is>
       </c>
     </row>
@@ -54076,12 +54090,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>JBI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Janus International Group, Inc</t>
+          <t>Northrop Grumman Corp.</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -54095,7 +54109,7 @@
         </is>
       </c>
       <c r="F102" s="18" t="n">
-        <v>626240320</v>
+        <v>73726443520</v>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
@@ -54103,64 +54117,62 @@
         </is>
       </c>
       <c r="H102" s="20" t="n">
-        <v>7.682</v>
+        <v>15.61168969542968</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>19.125002</v>
+        <v>16.501429</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>1.0949428</v>
+        <v>4.1224737</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.6944337</v>
+        <v>1.7188857</v>
       </c>
       <c r="L102" s="21" t="n">
-        <v>11.5960907053962</v>
-      </c>
-      <c r="M102" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.9836238568399</v>
+      </c>
+      <c r="M102" s="21" t="n">
+        <v>1.505494379293</v>
       </c>
       <c r="N102" s="21" t="n">
-        <v>10.43425814234016</v>
+        <v>14.00609392594555</v>
       </c>
       <c r="O102" s="21" t="n">
-        <v>16.54553713377242</v>
+        <v>13.37597658555007</v>
       </c>
       <c r="P102" s="20" t="n">
-        <v>2.983527796842828</v>
+        <v>2.307923063349215</v>
       </c>
       <c r="Q102" s="21" t="n">
-        <v>-46.98</v>
+        <v>-10.3</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S102" s="20" t="n">
-        <v>0.6354742392804635</v>
+        <v>0.4182092579820682</v>
       </c>
       <c r="T102" s="15" t="inlineStr">
         <is>
-          <t>Janus North America (76%)</t>
+          <t>Mission Systems (58%)</t>
         </is>
       </c>
       <c r="U102" s="17" t="inlineStr">
         <is>
-          <t>Janus North America 76%; Janus International 24%</t>
+          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
         </is>
       </c>
       <c r="V102" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W102" s="17" t="inlineStr">
         <is>
-          <t>US 88%; Non Us 12%</t>
+          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
         </is>
       </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
-          <t>Janus International +300%</t>
+          <t>Aeronautics Systems +130%</t>
         </is>
       </c>
     </row>
@@ -54170,12 +54182,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>JBI</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Flotek Industries, Inc.</t>
+          <t>Janus International Group, Inc</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
@@ -54185,11 +54197,11 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F103" s="18" t="n">
-        <v>989904320</v>
+        <v>626240320</v>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
@@ -54197,19 +54209,19 @@
         </is>
       </c>
       <c r="H103" s="20" t="n">
-        <v>25.626</v>
+        <v>7.682</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>27.059406</v>
+        <v>19.125002</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>7.6511755</v>
+        <v>1.0949428</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>3.3788822</v>
+        <v>0.6944337</v>
       </c>
       <c r="L103" s="21" t="n">
-        <v>-0.34082822017504</v>
+        <v>11.5960907053962</v>
       </c>
       <c r="M103" s="22" t="inlineStr">
         <is>
@@ -54217,44 +54229,44 @@
         </is>
       </c>
       <c r="N103" s="21" t="n">
-        <v>16.13992919089226</v>
+        <v>10.43425814234016</v>
       </c>
       <c r="O103" s="21" t="n">
-        <v>17.18227107585707</v>
+        <v>16.54553713377242</v>
       </c>
       <c r="P103" s="20" t="n">
-        <v>0.8771800721171535</v>
+        <v>2.983527796842828</v>
       </c>
       <c r="Q103" s="21" t="n">
-        <v>35.99</v>
+        <v>-46.98</v>
       </c>
       <c r="R103" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S103" s="20" t="n">
-        <v>0.7993939775957156</v>
+        <v>0.6354742392804635</v>
       </c>
       <c r="T103" s="15" t="inlineStr">
         <is>
-          <t>Chemistry Technologies (89%)</t>
+          <t>Janus North America (76%)</t>
         </is>
       </c>
       <c r="U103" s="17" t="inlineStr">
         <is>
-          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
+          <t>Janus North America 76%; Janus International 24%</t>
         </is>
       </c>
       <c r="V103" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W103" s="17" t="inlineStr">
         <is>
-          <t>US 95%; AE 4%; Non Us 1%</t>
+          <t>US 88%; Non Us 12%</t>
         </is>
       </c>
       <c r="X103" s="15" t="inlineStr">
         <is>
-          <t>Data Analytics +115%</t>
+          <t>Janus International +300%</t>
         </is>
       </c>
     </row>
@@ -54264,12 +54276,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Royal Gold, Inc.</t>
+          <t>Flotek Industries, Inc.</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -54279,11 +54291,11 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F104" s="18" t="n">
-        <v>21375143936</v>
+        <v>989904320</v>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
@@ -54291,62 +54303,64 @@
         </is>
       </c>
       <c r="H104" s="20" t="n">
-        <v>17.093</v>
+        <v>25.626</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>27.90708</v>
+        <v>27.059406</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>2.8154993</v>
+        <v>7.6511755</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>13.9189825</v>
+        <v>3.3788822</v>
       </c>
       <c r="L104" s="21" t="n">
-        <v>0.00273682367590865</v>
-      </c>
-      <c r="M104" s="21" t="n">
-        <v>0.91</v>
+        <v>-0.34082822017504</v>
+      </c>
+      <c r="M104" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N104" s="21" t="n">
-        <v>10.262897771322</v>
+        <v>16.13992919089226</v>
       </c>
       <c r="O104" s="21" t="n">
-        <v>79.09251477040698</v>
+        <v>17.18227107585707</v>
       </c>
       <c r="P104" s="20" t="n">
-        <v>0.3499720252373015</v>
+        <v>0.8771800721171535</v>
       </c>
       <c r="Q104" s="21" t="n">
-        <v>50.91</v>
+        <v>35.99</v>
       </c>
       <c r="R104" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S104" s="20" t="n">
-        <v>0.5688010724435794</v>
+        <v>0.7993939775957156</v>
       </c>
       <c r="T104" s="15" t="inlineStr">
         <is>
-          <t>Royalty Interest (69%)</t>
+          <t>Chemistry Technologies (89%)</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
         <is>
-          <t>Royalty Interest 69%; Stream Interest 31%</t>
+          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
         </is>
       </c>
       <c r="V104" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W104" s="17" t="inlineStr">
         <is>
-          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
+          <t>US 95%; AE 4%; Non Us 1%</t>
         </is>
       </c>
       <c r="X104" s="15" t="inlineStr">
         <is>
-          <t>Stream Interest +133%</t>
+          <t>Data Analytics +115%</t>
         </is>
       </c>
     </row>
@@ -54356,12 +54370,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Riot Blockchain, Inc.</t>
+          <t>Royal Gold, Inc.</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
@@ -54371,76 +54385,74 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F105" s="18" t="n">
-        <v>8056809472</v>
+        <v>21375143936</v>
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H105" s="20" t="n">
+        <v>17.093</v>
+      </c>
+      <c r="I105" s="20" t="n">
+        <v>27.90708</v>
       </c>
       <c r="J105" s="20" t="n">
-        <v>3.7017238</v>
+        <v>2.8154993</v>
       </c>
       <c r="K105" s="20" t="n">
-        <v>11.944614</v>
+        <v>13.9189825</v>
       </c>
       <c r="L105" s="21" t="n">
-        <v>-6.33617127278794</v>
+        <v>0.00273682367590865</v>
       </c>
       <c r="M105" s="21" t="n">
-        <v>0.10325461151742</v>
+        <v>0.91</v>
       </c>
       <c r="N105" s="21" t="n">
-        <v>-14.43474531538664</v>
+        <v>10.262897771322</v>
       </c>
       <c r="O105" s="21" t="n">
-        <v>-137.6062161413327</v>
-      </c>
-      <c r="P105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>79.09251477040698</v>
+      </c>
+      <c r="P105" s="20" t="n">
+        <v>0.3499720252373015</v>
       </c>
       <c r="Q105" s="21" t="n">
-        <v>10.21</v>
+        <v>50.91</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S105" s="20" t="n">
-        <v>0.4395096928547909</v>
+        <v>0.5688010724435794</v>
       </c>
       <c r="T105" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Royalty Interest (69%)</t>
         </is>
       </c>
       <c r="U105" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
+          <t>Royalty Interest 69%; Stream Interest 31%</t>
         </is>
       </c>
       <c r="V105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W105" s="17" t="inlineStr">
+        <is>
+          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
+        </is>
+      </c>
       <c r="X105" s="15" t="inlineStr">
         <is>
-          <t>Engineering +196%</t>
+          <t>Stream Interest +133%</t>
         </is>
       </c>
     </row>
@@ -54450,12 +54462,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Riot Blockchain, Inc.</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
@@ -54469,70 +54481,72 @@
         </is>
       </c>
       <c r="F106" s="18" t="n">
-        <v>77146587136</v>
+        <v>8056809472</v>
       </c>
       <c r="G106" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H106" s="20" t="n">
-        <v>29.95255477105907</v>
-      </c>
-      <c r="I106" s="20" t="n">
-        <v>36.676632</v>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J106" s="20" t="n">
-        <v>28.873335</v>
+        <v>3.7017238</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>6.304371</v>
+        <v>11.944614</v>
       </c>
       <c r="L106" s="21" t="n">
-        <v>3.45600557054743</v>
+        <v>-6.33617127278794</v>
       </c>
       <c r="M106" s="21" t="n">
-        <v>1.11367051765181</v>
+        <v>0.10325461151742</v>
       </c>
       <c r="N106" s="21" t="n">
-        <v>24.18337569424833</v>
+        <v>-14.43474531538664</v>
       </c>
       <c r="O106" s="21" t="n">
-        <v>24.10684192787327</v>
-      </c>
-      <c r="P106" s="20" t="n">
-        <v>2.823837818944425</v>
+        <v>-137.6062161413327</v>
+      </c>
+      <c r="P106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q106" s="21" t="n">
-        <v>16.12</v>
+        <v>10.21</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S106" s="20" t="n">
-        <v>0.5307180948206589</v>
+        <v>0.4395096928547909</v>
       </c>
       <c r="T106" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems In (62%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U106" s="17" t="inlineStr">
         <is>
-          <t>Product And Systems Integration 62%; Services And Software 38%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
         </is>
       </c>
       <c r="V106" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W106" s="17" t="inlineStr">
-        <is>
-          <t>North America 36%; US 34%; International 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W106" s="17" t="n"/>
       <c r="X106" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems  +176%</t>
+          <t>Engineering +196%</t>
         </is>
       </c>
     </row>
@@ -54542,12 +54556,12 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Firy Inc. Class A Common Stock</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
@@ -54561,80 +54575,70 @@
         </is>
       </c>
       <c r="F107" s="18" t="n">
-        <v>163180000</v>
+        <v>77146587136</v>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H107" s="20" t="n">
+        <v>29.95255477105907</v>
+      </c>
+      <c r="I107" s="20" t="n">
+        <v>36.676632</v>
       </c>
       <c r="J107" s="20" t="n">
-        <v>1.931855850736373</v>
+        <v>28.873335</v>
       </c>
       <c r="K107" s="20" t="n">
-        <v>1.3889787</v>
+        <v>6.304371</v>
       </c>
       <c r="L107" s="21" t="n">
-        <v>-42.19957624057978</v>
-      </c>
-      <c r="M107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.45600557054743</v>
+      </c>
+      <c r="M107" s="21" t="n">
+        <v>1.11367051765181</v>
+      </c>
+      <c r="N107" s="21" t="n">
+        <v>24.18337569424833</v>
       </c>
       <c r="O107" s="21" t="n">
-        <v>-60.47052925589057</v>
-      </c>
-      <c r="P107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.10684192787327</v>
+      </c>
+      <c r="P107" s="20" t="n">
+        <v>2.823837818944425</v>
       </c>
       <c r="Q107" s="21" t="n">
-        <v>51.65</v>
+        <v>16.12</v>
       </c>
       <c r="R107" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S107" s="20" t="n">
-        <v>0.619776729861528</v>
+        <v>0.5307180948206589</v>
       </c>
       <c r="T107" s="15" t="inlineStr">
         <is>
-          <t>Skillz (74%)</t>
+          <t>Product And Systems In (62%)</t>
         </is>
       </c>
       <c r="U107" s="17" t="inlineStr">
         <is>
-          <t>Skillz 74%; RZR 26%</t>
+          <t>Product And Systems Integration 62%; Services And Software 38%</t>
         </is>
       </c>
       <c r="V107" s="18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W107" s="17" t="inlineStr">
         <is>
-          <t>US 76%; Non Us 6%; CY 4%</t>
+          <t>North America 36%; US 34%; International 14%</t>
         </is>
       </c>
       <c r="X107" s="15" t="inlineStr">
         <is>
-          <t>RZR +146%</t>
+          <t>Product And Systems  +176%</t>
         </is>
       </c>
     </row>
@@ -54644,12 +54648,12 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Energy Transfer Lp</t>
+          <t>Firy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
@@ -54659,70 +54663,84 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F108" s="18" t="n">
-        <v>74203103232</v>
+        <v>163180000</v>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H108" s="20" t="n">
-        <v>9.459</v>
-      </c>
-      <c r="I108" s="20" t="n">
-        <v>14.760273</v>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J108" s="20" t="n">
-        <v>1.491909508655528</v>
+        <v>1.931855850736373</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>0.69103926</v>
+        <v>1.3889787</v>
       </c>
       <c r="L108" s="21" t="n">
-        <v>7.04975512768092</v>
-      </c>
-      <c r="M108" s="21" t="n">
-        <v>6.959999999999999</v>
-      </c>
-      <c r="N108" s="21" t="n">
-        <v>8.4099490357427</v>
+        <v>-42.19957624057978</v>
+      </c>
+      <c r="M108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>17.85263732142248</v>
-      </c>
-      <c r="P108" s="20" t="n">
-        <v>4.353514132925898</v>
+        <v>-60.47052925589057</v>
+      </c>
+      <c r="P108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q108" s="21" t="n">
-        <v>37.32</v>
+        <v>51.65</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S108" s="20" t="n">
-        <v>0.2291888064107961</v>
+        <v>0.619776729861528</v>
       </c>
       <c r="T108" s="15" t="inlineStr">
         <is>
-          <t>Crudeoiltransportation (27%)</t>
+          <t>Skillz (74%)</t>
         </is>
       </c>
       <c r="U108" s="17" t="inlineStr">
         <is>
-          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
+          <t>Skillz 74%; RZR 26%</t>
         </is>
       </c>
       <c r="V108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W108" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; Non Us 6%; CY 4%</t>
+        </is>
+      </c>
       <c r="X108" s="15" t="inlineStr">
         <is>
-          <t>Investment In Sunoco +165%</t>
+          <t>RZR +146%</t>
         </is>
       </c>
     </row>
@@ -54732,12 +54750,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>BWX Technologies, Inc.</t>
+          <t>Energy Transfer Lp</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
@@ -54747,11 +54765,11 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F109" s="18" t="n">
-        <v>13754292224</v>
+        <v>74203103232</v>
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
@@ -54759,62 +54777,58 @@
         </is>
       </c>
       <c r="H109" s="20" t="n">
-        <v>31.828</v>
+        <v>9.459</v>
       </c>
       <c r="I109" s="20" t="n">
-        <v>38.891193</v>
+        <v>14.760273</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>10.3069</v>
+        <v>1.491909508655528</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>3.9141748</v>
+        <v>0.69103926</v>
       </c>
       <c r="L109" s="21" t="n">
-        <v>2.19383891609831</v>
+        <v>7.04975512768092</v>
       </c>
       <c r="M109" s="21" t="n">
-        <v>0.5030143835716</v>
+        <v>6.959999999999999</v>
       </c>
       <c r="N109" s="21" t="n">
-        <v>15.04279234978169</v>
+        <v>8.4099490357427</v>
       </c>
       <c r="O109" s="21" t="n">
-        <v>16.8479651603609</v>
+        <v>17.85263732142248</v>
       </c>
       <c r="P109" s="20" t="n">
-        <v>2.646714786974468</v>
+        <v>4.353514132925898</v>
       </c>
       <c r="Q109" s="21" t="n">
-        <v>-25.8</v>
+        <v>37.32</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S109" s="20" t="n">
-        <v>0.6174267863088643</v>
+        <v>0.2291888064107961</v>
       </c>
       <c r="T109" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operations (74%)</t>
+          <t>Crudeoiltransportation (27%)</t>
         </is>
       </c>
       <c r="U109" s="17" t="inlineStr">
         <is>
-          <t>Commercial Operations 74%; Government Operations 26%</t>
+          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
         </is>
       </c>
       <c r="V109" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W109" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W109" s="17" t="n"/>
       <c r="X109" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operation +143%</t>
+          <t>Investment In Sunoco +165%</t>
         </is>
       </c>
     </row>
@@ -54824,12 +54838,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>LGN</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Legence Corp.</t>
+          <t>BWX Technologies, Inc.</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
@@ -54837,9 +54851,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E110" s="17" t="n"/>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="F110" s="18" t="n">
-        <v>9306742784</v>
+        <v>13754292224</v>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
@@ -54847,62 +54865,62 @@
         </is>
       </c>
       <c r="H110" s="20" t="n">
-        <v>35.22426766420546</v>
-      </c>
-      <c r="I110" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>31.828</v>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>38.891193</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>15.49927769737686</v>
+        <v>10.3069</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>3.30888056840225</v>
+        <v>3.9141748</v>
       </c>
       <c r="L110" s="21" t="n">
-        <v>3.41438849489116</v>
-      </c>
-      <c r="M110" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.19383891609831</v>
+      </c>
+      <c r="M110" s="21" t="n">
+        <v>0.5030143835716</v>
       </c>
       <c r="N110" s="21" t="n">
-        <v>3.69186301129894</v>
+        <v>15.04279234978169</v>
       </c>
       <c r="O110" s="21" t="n">
-        <v>5.44599126235131</v>
+        <v>16.8479651603609</v>
       </c>
       <c r="P110" s="20" t="n">
-        <v>6.20894155127728</v>
+        <v>2.646714786974468</v>
       </c>
       <c r="Q110" s="21" t="n">
-        <v>167.4754158395236</v>
+        <v>-25.8</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S110" s="20" t="n">
-        <v>0.2963256950273106</v>
+        <v>0.6174267863088643</v>
       </c>
       <c r="T110" s="15" t="inlineStr">
         <is>
-          <t>Installation Maintenan (36%)</t>
+          <t>Commercial Operations (74%)</t>
         </is>
       </c>
       <c r="U110" s="17" t="inlineStr">
         <is>
-          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
+          <t>Commercial Operations 74%; Government Operations 26%</t>
         </is>
       </c>
       <c r="V110" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W110" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
+        </is>
+      </c>
       <c r="X110" s="15" t="inlineStr">
         <is>
-          <t>Installation And Mai +162%</t>
+          <t>Commercial Operation +143%</t>
         </is>
       </c>
     </row>
@@ -54912,12 +54930,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>LGN</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Gen Digital Inc. Common Stock</t>
+          <t>Legence Corp.</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
@@ -54925,13 +54943,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E111" s="17" t="inlineStr">
-        <is>
-          <t>Information Te</t>
-        </is>
-      </c>
+      <c r="E111" s="17" t="n"/>
       <c r="F111" s="18" t="n">
-        <v>18113243136</v>
+        <v>9306742784</v>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
@@ -54939,62 +54953,62 @@
         </is>
       </c>
       <c r="H111" s="20" t="n">
-        <v>10.614</v>
-      </c>
-      <c r="I111" s="20" t="n">
-        <v>17.695906</v>
+        <v>35.22426766420546</v>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J111" s="20" t="n">
-        <v>6.8245378</v>
+        <v>15.49927769737686</v>
       </c>
       <c r="K111" s="20" t="n">
-        <v>3.566301</v>
+        <v>3.30888056840225</v>
       </c>
       <c r="L111" s="21" t="n">
-        <v>10.13133216482446</v>
-      </c>
-      <c r="M111" s="21" t="n">
-        <v>2.07549286633304</v>
+        <v>3.41438849489116</v>
+      </c>
+      <c r="M111" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N111" s="21" t="n">
-        <v>20.39245863793767</v>
+        <v>3.69186301129894</v>
       </c>
       <c r="O111" s="21" t="n">
-        <v>51.45999999999999</v>
+        <v>5.44599126235131</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>3.02914885347843</v>
+        <v>6.20894155127728</v>
       </c>
       <c r="Q111" s="21" t="n">
-        <v>18.59</v>
+        <v>167.4754158395236</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S111" s="20" t="n">
-        <v>0.5563136799999999</v>
+        <v>0.2963256950273106</v>
       </c>
       <c r="T111" s="15" t="inlineStr">
         <is>
-          <t>Cyber Safety Platform (67%)</t>
+          <t>Installation Maintenan (36%)</t>
         </is>
       </c>
       <c r="U111" s="17" t="inlineStr">
         <is>
-          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
         </is>
       </c>
       <c r="V111" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W111" s="17" t="inlineStr">
-        <is>
-          <t>Americas 43%; US 40%; EMEA 13%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W111" s="17" t="n"/>
       <c r="X111" s="15" t="inlineStr">
         <is>
-          <t>Trust Based Solution +119%</t>
+          <t>Installation And Mai +162%</t>
         </is>
       </c>
     </row>
@@ -55004,12 +55018,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>L3Harris Technologies, Inc.</t>
+          <t>Gen Digital Inc. Common Stock</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
@@ -55019,11 +55033,11 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F112" s="18" t="n">
-        <v>45723136000</v>
+        <v>18113243136</v>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
@@ -55031,62 +55045,62 @@
         </is>
       </c>
       <c r="H112" s="20" t="n">
-        <v>17.48068824615385</v>
+        <v>10.614</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>24.776993</v>
+        <v>17.695906</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>2.388963</v>
+        <v>6.8245378</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>1.167926026207566</v>
+        <v>3.566301</v>
       </c>
       <c r="L112" s="21" t="n">
-        <v>5.88004410889457</v>
+        <v>10.13133216482446</v>
       </c>
       <c r="M112" s="21" t="n">
-        <v>1.56571804266048</v>
+        <v>2.07549286633304</v>
       </c>
       <c r="N112" s="21" t="n">
-        <v>8.274248192518591</v>
+        <v>20.39245863793767</v>
       </c>
       <c r="O112" s="21" t="n">
-        <v>8.96574625150067</v>
+        <v>51.45999999999999</v>
       </c>
       <c r="P112" s="20" t="n">
-        <v>2.55014245014245</v>
+        <v>3.02914885347843</v>
       </c>
       <c r="Q112" s="21" t="n">
-        <v>-9.82</v>
+        <v>18.59</v>
       </c>
       <c r="R112" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" s="20" t="n">
+        <v>0.5563136799999999</v>
+      </c>
+      <c r="T112" s="15" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform (67%)</t>
+        </is>
+      </c>
+      <c r="U112" s="17" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+        </is>
+      </c>
+      <c r="V112" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S112" s="20" t="n">
-        <v>0.3315167177024359</v>
-      </c>
-      <c r="T112" s="15" t="inlineStr">
-        <is>
-          <t>Communication Systems (42%)</t>
-        </is>
-      </c>
-      <c r="U112" s="17" t="inlineStr">
-        <is>
-          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
-        </is>
-      </c>
-      <c r="V112" s="18" t="n">
-        <v>2</v>
-      </c>
       <c r="W112" s="17" t="inlineStr">
         <is>
-          <t>US 90%; Non Us 10%</t>
+          <t>Americas 43%; US 40%; EMEA 13%</t>
         </is>
       </c>
       <c r="X112" s="15" t="inlineStr">
         <is>
-          <t>Aerojet Rocketdyne +467%</t>
+          <t>Trust Based Solution +119%</t>
         </is>
       </c>
     </row>
@@ -55096,12 +55110,12 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc.</t>
+          <t>L3Harris Technologies, Inc.</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
@@ -55111,76 +55125,74 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F113" s="18" t="n">
-        <v>2881904384</v>
+        <v>45723136000</v>
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H113" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H113" s="20" t="n">
+        <v>17.48068824615385</v>
       </c>
       <c r="I113" s="20" t="n">
-        <v>3.9738305</v>
+        <v>24.776993</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>0.4399589</v>
+        <v>2.388963</v>
       </c>
       <c r="K113" s="20" t="n">
-        <v>0.4215159</v>
+        <v>1.167926026207566</v>
       </c>
       <c r="L113" s="21" t="n">
-        <v>-18.66821130454271</v>
-      </c>
-      <c r="M113" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.88004410889457</v>
+      </c>
+      <c r="M113" s="21" t="n">
+        <v>1.56571804266048</v>
       </c>
       <c r="N113" s="21" t="n">
-        <v>0.007627959012433573</v>
+        <v>8.274248192518591</v>
       </c>
       <c r="O113" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.96574625150067</v>
+      </c>
+      <c r="P113" s="20" t="n">
+        <v>2.55014245014245</v>
       </c>
       <c r="Q113" s="21" t="n">
-        <v>-6.12</v>
+        <v>-9.82</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S113" s="20" t="n">
-        <v>0.4403975356846814</v>
+        <v>0.3315167177024359</v>
       </c>
       <c r="T113" s="15" t="inlineStr">
         <is>
-          <t>Annuities (60%)</t>
+          <t>Communication Systems (42%)</t>
         </is>
       </c>
       <c r="U113" s="17" t="inlineStr">
         <is>
-          <t>Annuities 60%; Runoff 21%; Life 19%</t>
+          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
         </is>
       </c>
       <c r="V113" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W113" s="17" t="inlineStr">
+        <is>
+          <t>US 90%; Non Us 10%</t>
+        </is>
+      </c>
       <c r="X113" s="15" t="inlineStr">
         <is>
-          <t>Annuities +322%</t>
+          <t>Aerojet Rocketdyne +467%</t>
         </is>
       </c>
     </row>
@@ -55190,12 +55202,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>ONEOK, Inc.</t>
+          <t>Brighthouse Financial, Inc.</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
@@ -55203,59 +55215,69 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E114" s="17" t="n"/>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="F114" s="18" t="n">
-        <v>60906319872</v>
+        <v>2881904384</v>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H114" s="20" t="n">
-        <v>12.17</v>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I114" s="20" t="n">
-        <v>16.687393</v>
+        <v>3.9738305</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>2.655344</v>
+        <v>0.4399589</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>1.5471808</v>
+        <v>0.4215159</v>
       </c>
       <c r="L114" s="21" t="n">
-        <v>4.830758993916</v>
-      </c>
-      <c r="M114" s="21" t="n">
-        <v>4.39066236170035</v>
+        <v>-18.66821130454271</v>
+      </c>
+      <c r="M114" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N114" s="21" t="n">
-        <v>10.40228824506366</v>
+        <v>0.007627959012433573</v>
       </c>
       <c r="O114" s="21" t="n">
-        <v>22.48324054084763</v>
-      </c>
-      <c r="P114" s="20" t="n">
-        <v>4.229943145925458</v>
+        <v>0</v>
+      </c>
+      <c r="P114" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q114" s="21" t="n">
-        <v>50.16</v>
+        <v>-6.12</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S114" s="20" t="n">
-        <v>0.4959061195541746</v>
+        <v>0.4403975356846814</v>
       </c>
       <c r="T114" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And C (66%)</t>
+          <t>Annuities (60%)</t>
         </is>
       </c>
       <c r="U114" s="17" t="inlineStr">
         <is>
-          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
+          <t>Annuities 60%; Runoff 21%; Life 19%</t>
         </is>
       </c>
       <c r="V114" s="18" t="n">
@@ -55264,7 +55286,7 @@
       <c r="W114" s="17" t="n"/>
       <c r="X114" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And +192%</t>
+          <t>Annuities +322%</t>
         </is>
       </c>
     </row>
@@ -55274,12 +55296,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>HAPN</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>Happen Inc. Common Stock</t>
+          <t>ONEOK, Inc.</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -55287,13 +55309,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E115" s="17" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="E115" s="17" t="n"/>
       <c r="F115" s="18" t="n">
-        <v>1938845312</v>
+        <v>60906319872</v>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
@@ -55301,57 +55319,49 @@
         </is>
       </c>
       <c r="H115" s="20" t="n">
-        <v>3.25</v>
+        <v>12.17</v>
       </c>
       <c r="I115" s="20" t="n">
-        <v>13.36898003182167</v>
+        <v>16.687393</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>1.2369312</v>
+        <v>2.655344</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>3.208765663633625</v>
-      </c>
-      <c r="L115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.5471808</v>
+      </c>
+      <c r="L115" s="21" t="n">
+        <v>4.830758993916</v>
+      </c>
+      <c r="M115" s="21" t="n">
+        <v>4.39066236170035</v>
+      </c>
+      <c r="N115" s="21" t="n">
+        <v>10.40228824506366</v>
       </c>
       <c r="O115" s="21" t="n">
-        <v>52.58608552315825</v>
-      </c>
-      <c r="P115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.48324054084763</v>
+      </c>
+      <c r="P115" s="20" t="n">
+        <v>4.229943145925458</v>
       </c>
       <c r="Q115" s="21" t="n">
-        <v>2.07</v>
+        <v>50.16</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S115" s="20" t="n">
-        <v>0.5010363171603962</v>
+        <v>0.4959061195541746</v>
       </c>
       <c r="T115" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank (52%)</t>
+          <t>Refined Products And C (66%)</t>
         </is>
       </c>
       <c r="U115" s="17" t="inlineStr">
         <is>
-          <t>Happen Bank 52%; Happen Inc. 48%</t>
+          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
         </is>
       </c>
       <c r="V115" s="18" t="n">
@@ -55360,7 +55370,7 @@
       <c r="W115" s="17" t="n"/>
       <c r="X115" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank +124%</t>
+          <t>Refined Products And +192%</t>
         </is>
       </c>
     </row>
@@ -55370,51 +55380,43 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>VFS</t>
+          <t>HAPN</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>VinFast Auto Ltd. Ordinary Sha</t>
+          <t>Happen Inc. Common Stock</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F116" s="18" t="n">
-        <v>7509911040</v>
+        <v>1938845312</v>
       </c>
       <c r="G116" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H116" s="20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I116" s="20" t="n">
+        <v>13.36898003182167</v>
+      </c>
+      <c r="J116" s="20" t="n">
+        <v>1.2369312</v>
+      </c>
+      <c r="K116" s="20" t="n">
+        <v>3.208765663633625</v>
       </c>
       <c r="L116" s="22" t="inlineStr">
         <is>
@@ -55426,11 +55428,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="N116" s="21" t="n">
-        <v>78.31448357763071</v>
+      <c r="N116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>-83.1176333196485</v>
+        <v>52.58608552315825</v>
       </c>
       <c r="P116" s="22" t="inlineStr">
         <is>
@@ -55438,35 +55442,31 @@
         </is>
       </c>
       <c r="Q116" s="21" t="n">
-        <v>-3.75</v>
+        <v>2.07</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S116" s="20" t="n">
-        <v>0.460552269511968</v>
+        <v>0.5010363171603962</v>
       </c>
       <c r="T116" s="15" t="inlineStr">
         <is>
-          <t>Car (48%)</t>
+          <t>Happen Bank (52%)</t>
         </is>
       </c>
       <c r="U116" s="17" t="inlineStr">
         <is>
-          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
+          <t>Happen Bank 52%; Happen Inc. 48%</t>
         </is>
       </c>
       <c r="V116" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W116" s="17" t="inlineStr">
-        <is>
-          <t>VN 89%; Asia Pacific 8%; US 2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W116" s="17" t="n"/>
       <c r="X116" s="15" t="inlineStr">
         <is>
-          <t>E Scooter +230%</t>
+          <t>Happen Bank +124%</t>
         </is>
       </c>
     </row>

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -30415,12 +30415,12 @@
       </c>
       <c r="B306" s="14" t="inlineStr">
         <is>
-          <t>POWW</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="C306" s="15" t="inlineStr">
         <is>
-          <t>Outdoor Holding Company</t>
+          <t>CNX Resources Corporation</t>
         </is>
       </c>
       <c r="D306" s="16" t="inlineStr">
@@ -30430,78 +30430,72 @@
       </c>
       <c r="E306" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F306" s="18" t="n">
-        <v>247209792</v>
+        <v>5312655872</v>
       </c>
       <c r="G306" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H306" s="20" t="n">
+        <v>4.263</v>
+      </c>
+      <c r="I306" s="20" t="n">
+        <v>5.820097</v>
+      </c>
+      <c r="J306" s="20" t="n">
+        <v>1.104889</v>
+      </c>
+      <c r="K306" s="20" t="n">
+        <v>2.4826064</v>
+      </c>
+      <c r="L306" s="21" t="n">
+        <v>9.483220548820769</v>
+      </c>
+      <c r="M306" s="21" t="n">
+        <v>0.91466961578586</v>
       </c>
       <c r="N306" s="21" t="n">
-        <v>-3.36760903464687</v>
-      </c>
-      <c r="O306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="P306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>15.73999400545232</v>
+      </c>
+      <c r="O306" s="21" t="n">
+        <v>71.88341690652736</v>
+      </c>
+      <c r="P306" s="20" t="n">
+        <v>1.047819320167076</v>
       </c>
       <c r="Q306" s="21" t="n">
-        <v>35.63</v>
+        <v>11.38</v>
       </c>
       <c r="R306" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S306" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T306" s="15" t="n"/>
-      <c r="U306" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="S306" s="20" t="n">
+        <v>0.8596950469074589</v>
+      </c>
+      <c r="T306" s="15" t="inlineStr">
+        <is>
+          <t>Shale (92%)</t>
+        </is>
+      </c>
+      <c r="U306" s="17" t="inlineStr">
+        <is>
+          <t>Shale 92%; Coalbed Methane 8%</t>
+        </is>
+      </c>
       <c r="V306" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W306" s="17" t="n"/>
-      <c r="X306" s="15" t="n"/>
+      <c r="X306" s="15" t="inlineStr">
+        <is>
+          <t>Shale +18%</t>
+        </is>
+      </c>
       <c r="Y306" s="22" t="inlineStr">
         <is>
           <t>–</t>
@@ -30520,12 +30514,12 @@
       </c>
       <c r="B307" s="14" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>EVER</t>
         </is>
       </c>
       <c r="C307" s="15" t="inlineStr">
         <is>
-          <t>CNX Resources Corporation</t>
+          <t>Everquote, Inc.</t>
         </is>
       </c>
       <c r="D307" s="16" t="inlineStr">
@@ -30535,11 +30529,11 @@
       </c>
       <c r="E307" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F307" s="18" t="n">
-        <v>5312655872</v>
+        <v>845049216</v>
       </c>
       <c r="G307" s="19" t="inlineStr">
         <is>
@@ -30547,60 +30541,52 @@
         </is>
       </c>
       <c r="H307" s="20" t="n">
-        <v>4.263</v>
+        <v>7.624</v>
       </c>
       <c r="I307" s="20" t="n">
-        <v>5.820097</v>
+        <v>7.8110747</v>
       </c>
       <c r="J307" s="20" t="n">
-        <v>1.104889</v>
+        <v>3.2907917</v>
       </c>
       <c r="K307" s="20" t="n">
-        <v>2.4826064</v>
+        <v>1.118977</v>
       </c>
       <c r="L307" s="21" t="n">
-        <v>9.483220548820769</v>
-      </c>
-      <c r="M307" s="21" t="n">
-        <v>0.91466961578586</v>
+        <v>10.96520447110857</v>
+      </c>
+      <c r="M307" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N307" s="21" t="n">
-        <v>15.73999400545232</v>
+        <v>90.53629570131528</v>
       </c>
       <c r="O307" s="21" t="n">
-        <v>71.88341690652736</v>
+        <v>9.85345605643751</v>
       </c>
       <c r="P307" s="20" t="n">
-        <v>1.047819320167076</v>
+        <v>-2.524418484593713</v>
       </c>
       <c r="Q307" s="21" t="n">
-        <v>11.38</v>
+        <v>15.65</v>
       </c>
       <c r="R307" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="S307" s="20" t="n">
-        <v>0.8596950469074589</v>
-      </c>
-      <c r="T307" s="15" t="inlineStr">
-        <is>
-          <t>Shale (92%)</t>
-        </is>
-      </c>
-      <c r="U307" s="17" t="inlineStr">
-        <is>
-          <t>Shale 92%; Coalbed Methane 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S307" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T307" s="15" t="n"/>
+      <c r="U307" s="17" t="n"/>
       <c r="V307" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W307" s="17" t="n"/>
-      <c r="X307" s="15" t="inlineStr">
-        <is>
-          <t>Shale +18%</t>
-        </is>
-      </c>
+      <c r="X307" s="15" t="n"/>
       <c r="Y307" s="22" t="inlineStr">
         <is>
           <t>–</t>
@@ -30619,12 +30605,12 @@
       </c>
       <c r="B308" s="14" t="inlineStr">
         <is>
-          <t>EVER</t>
+          <t>FSP</t>
         </is>
       </c>
       <c r="C308" s="15" t="inlineStr">
         <is>
-          <t>Everquote, Inc.</t>
+          <t>Franklin Street Properties Cor</t>
         </is>
       </c>
       <c r="D308" s="16" t="inlineStr">
@@ -30634,11 +30620,11 @@
       </c>
       <c r="E308" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F308" s="18" t="n">
-        <v>845049216</v>
+        <v>35977652</v>
       </c>
       <c r="G308" s="19" t="inlineStr">
         <is>
@@ -30646,61 +30632,67 @@
         </is>
       </c>
       <c r="H308" s="20" t="n">
-        <v>7.624</v>
-      </c>
-      <c r="I308" s="20" t="n">
-        <v>7.8110747</v>
+        <v>7.49</v>
+      </c>
+      <c r="I308" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J308" s="20" t="n">
-        <v>3.2907917</v>
+        <v>0.062033713</v>
       </c>
       <c r="K308" s="20" t="n">
-        <v>1.118977</v>
+        <v>0.33966815</v>
       </c>
       <c r="L308" s="21" t="n">
-        <v>10.96520447110857</v>
-      </c>
-      <c r="M308" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-13.47641016402107</v>
+      </c>
+      <c r="M308" s="21" t="n">
+        <v>5.56</v>
       </c>
       <c r="N308" s="21" t="n">
-        <v>90.53629570131528</v>
+        <v>-1.92347990081374</v>
       </c>
       <c r="O308" s="21" t="n">
-        <v>9.85345605643751</v>
+        <v>30.12753034551501</v>
       </c>
       <c r="P308" s="20" t="n">
-        <v>-2.524418484593713</v>
+        <v>7.121177700132958</v>
       </c>
       <c r="Q308" s="21" t="n">
-        <v>15.65</v>
+        <v>-65.93000000000001</v>
       </c>
       <c r="R308" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S308" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="T308" s="15" t="n"/>
-      <c r="U308" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="S308" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T308" s="15" t="inlineStr">
+        <is>
+          <t>Real Estate Operations (100%)</t>
+        </is>
+      </c>
+      <c r="U308" s="17" t="inlineStr">
+        <is>
+          <t>Real Estate Operations 100%</t>
+        </is>
+      </c>
       <c r="V308" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W308" s="17" t="n"/>
-      <c r="X308" s="15" t="n"/>
-      <c r="Y308" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z308" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="X308" s="15" t="inlineStr">
+        <is>
+          <t>Real Estate Operatio -1%</t>
+        </is>
+      </c>
+      <c r="Y308" s="21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z308" s="20" t="n">
+        <v>0.0042</v>
       </c>
       <c r="AA308" s="24" t="inlineStr"/>
     </row>
@@ -30710,12 +30702,12 @@
       </c>
       <c r="B309" s="14" t="inlineStr">
         <is>
-          <t>FSP</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C309" s="15" t="inlineStr">
         <is>
-          <t>Franklin Street Properties Cor</t>
+          <t>Amphenol Corp /De/</t>
         </is>
       </c>
       <c r="D309" s="16" t="inlineStr">
@@ -30725,11 +30717,11 @@
       </c>
       <c r="E309" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F309" s="18" t="n">
-        <v>35977652</v>
+        <v>206943928320</v>
       </c>
       <c r="G309" s="19" t="inlineStr">
         <is>
@@ -30737,67 +30729,69 @@
         </is>
       </c>
       <c r="H309" s="20" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="I309" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>29.62302222645686</v>
+      </c>
+      <c r="I309" s="20" t="n">
+        <v>41.96</v>
       </c>
       <c r="J309" s="20" t="n">
-        <v>0.062033713</v>
+        <v>13.354551</v>
       </c>
       <c r="K309" s="20" t="n">
-        <v>0.33966815</v>
+        <v>7.1331444</v>
       </c>
       <c r="L309" s="21" t="n">
-        <v>-13.47641016402107</v>
+        <v>2.30913485895705</v>
       </c>
       <c r="M309" s="21" t="n">
-        <v>5.56</v>
+        <v>0.55827491517045</v>
       </c>
       <c r="N309" s="21" t="n">
-        <v>-1.92347990081374</v>
+        <v>45.67278672993024</v>
       </c>
       <c r="O309" s="21" t="n">
-        <v>30.12753034551501</v>
+        <v>29.39923710032213</v>
       </c>
       <c r="P309" s="20" t="n">
-        <v>7.121177700132958</v>
+        <v>2.057377830710813</v>
       </c>
       <c r="Q309" s="21" t="n">
-        <v>-65.93000000000001</v>
+        <v>19.46</v>
       </c>
       <c r="R309" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S309" s="20" t="n">
-        <v>1</v>
+        <v>0.4256894967493531</v>
       </c>
       <c r="T309" s="15" t="inlineStr">
         <is>
-          <t>Real Estate Operations (100%)</t>
+          <t>Communications Solutio (58%)</t>
         </is>
       </c>
       <c r="U309" s="17" t="inlineStr">
         <is>
-          <t>Real Estate Operations 100%</t>
+          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
         </is>
       </c>
       <c r="V309" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W309" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W309" s="17" t="inlineStr">
+        <is>
+          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
+        </is>
+      </c>
       <c r="X309" s="15" t="inlineStr">
         <is>
-          <t>Real Estate Operatio -1%</t>
+          <t>Communications Solut +143%</t>
         </is>
       </c>
       <c r="Y309" s="21" t="n">
-        <v>0.2</v>
+        <v>-1.03</v>
       </c>
       <c r="Z309" s="20" t="n">
-        <v>0.0042</v>
+        <v>-0.0436</v>
       </c>
       <c r="AA309" s="24" t="inlineStr"/>
     </row>
@@ -30807,96 +30801,108 @@
       </c>
       <c r="B310" s="14" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>BCYC</t>
         </is>
       </c>
       <c r="C310" s="15" t="inlineStr">
         <is>
-          <t>Amphenol Corp /De/</t>
+          <t>Bicycle Therapeutics plc</t>
         </is>
       </c>
       <c r="D310" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="E310" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F310" s="18" t="n">
-        <v>206943928320</v>
+        <v>270172480</v>
       </c>
       <c r="G310" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H310" s="20" t="n">
-        <v>29.62302222645686</v>
-      </c>
-      <c r="I310" s="20" t="n">
-        <v>41.96</v>
+      <c r="H310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J310" s="20" t="n">
-        <v>13.354551</v>
+        <v>0.528116</v>
       </c>
       <c r="K310" s="20" t="n">
-        <v>7.1331444</v>
-      </c>
-      <c r="L310" s="21" t="n">
-        <v>2.30913485895705</v>
-      </c>
-      <c r="M310" s="21" t="n">
-        <v>0.55827491517045</v>
-      </c>
-      <c r="N310" s="21" t="n">
-        <v>45.67278672993024</v>
+        <v>4.4142222</v>
+      </c>
+      <c r="L310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O310" s="21" t="n">
-        <v>29.39923710032213</v>
-      </c>
-      <c r="P310" s="20" t="n">
-        <v>2.057377830710813</v>
+        <v>-328.0973776652235</v>
+      </c>
+      <c r="P310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q310" s="21" t="n">
-        <v>19.46</v>
+        <v>-46.72</v>
       </c>
       <c r="R310" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S310" s="20" t="n">
-        <v>0.4256894967493531</v>
+        <v>1</v>
       </c>
       <c r="T310" s="15" t="inlineStr">
         <is>
-          <t>Communications Solutio (58%)</t>
+          <t>Single Reportable (100%)</t>
         </is>
       </c>
       <c r="U310" s="17" t="inlineStr">
         <is>
-          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
+          <t>Single Reportable 100%</t>
         </is>
       </c>
       <c r="V310" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W310" s="17" t="inlineStr">
-        <is>
-          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W310" s="17" t="n"/>
       <c r="X310" s="15" t="inlineStr">
         <is>
-          <t>Communications Solut +143%</t>
-        </is>
-      </c>
-      <c r="Y310" s="21" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="Z310" s="20" t="n">
-        <v>-0.0436</v>
+          <t>Single Reportable +106%</t>
+        </is>
+      </c>
+      <c r="Y310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z310" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA310" s="24" t="inlineStr"/>
     </row>
@@ -30906,36 +30912,34 @@
       </c>
       <c r="B311" s="14" t="inlineStr">
         <is>
-          <t>BCYC</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="C311" s="15" t="inlineStr">
         <is>
-          <t>Bicycle Therapeutics plc</t>
+          <t>Bill Holdings, Inc.</t>
         </is>
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E311" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F311" s="18" t="n">
-        <v>270172480</v>
+        <v>4029328128</v>
       </c>
       <c r="G311" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H311" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H311" s="20" t="n">
+        <v>40.175</v>
       </c>
       <c r="I311" s="22" t="inlineStr">
         <is>
@@ -30943,62 +30947,46 @@
         </is>
       </c>
       <c r="J311" s="20" t="n">
-        <v>0.528116</v>
+        <v>1.2320731</v>
       </c>
       <c r="K311" s="20" t="n">
-        <v>4.4142222</v>
-      </c>
-      <c r="L311" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.4373493</v>
+      </c>
+      <c r="L311" s="21" t="n">
+        <v>9.84534017926566</v>
       </c>
       <c r="M311" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N311" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N311" s="21" t="n">
+        <v>-1.46761184832724</v>
       </c>
       <c r="O311" s="21" t="n">
-        <v>-328.0973776652235</v>
-      </c>
-      <c r="P311" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.355034814803521</v>
+      </c>
+      <c r="P311" s="20" t="n">
+        <v>-1.025483417246064</v>
       </c>
       <c r="Q311" s="21" t="n">
-        <v>-46.72</v>
+        <v>-1.01</v>
       </c>
       <c r="R311" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S311" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T311" s="15" t="inlineStr">
-        <is>
-          <t>Single Reportable (100%)</t>
-        </is>
-      </c>
-      <c r="U311" s="17" t="inlineStr">
-        <is>
-          <t>Single Reportable 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S311" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="T311" s="15" t="n"/>
+      <c r="U311" s="17" t="n"/>
       <c r="V311" s="18" t="n">
         <v>0</v>
       </c>
       <c r="W311" s="17" t="n"/>
-      <c r="X311" s="15" t="inlineStr">
-        <is>
-          <t>Single Reportable +106%</t>
-        </is>
-      </c>
+      <c r="X311" s="15" t="n"/>
       <c r="Y311" s="22" t="inlineStr">
         <is>
           <t>–</t>
@@ -31017,12 +31005,12 @@
       </c>
       <c r="B312" s="14" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>NPB</t>
         </is>
       </c>
       <c r="C312" s="15" t="inlineStr">
         <is>
-          <t>Bill Holdings, Inc.</t>
+          <t>Northpointe Bancshares, Inc.</t>
         </is>
       </c>
       <c r="D312" s="16" t="inlineStr">
@@ -31032,50 +31020,52 @@
       </c>
       <c r="E312" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F312" s="18" t="n">
-        <v>4029328128</v>
+        <v>595499264</v>
       </c>
       <c r="G312" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H312" s="20" t="n">
-        <v>40.175</v>
-      </c>
-      <c r="I312" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H312" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I312" s="20" t="n">
+        <v>7.422414</v>
       </c>
       <c r="J312" s="20" t="n">
-        <v>1.2320731</v>
+        <v>0.9735964</v>
       </c>
       <c r="K312" s="20" t="n">
-        <v>2.4373493</v>
+        <v>2.314884</v>
       </c>
       <c r="L312" s="21" t="n">
-        <v>9.84534017926566</v>
-      </c>
-      <c r="M312" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N312" s="21" t="n">
-        <v>-1.46761184832724</v>
+        <v>16.61132603634727</v>
+      </c>
+      <c r="M312" s="21" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N312" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O312" s="21" t="n">
-        <v>6.355034814803521</v>
-      </c>
-      <c r="P312" s="20" t="n">
-        <v>-1.025483417246064</v>
+        <v>0</v>
+      </c>
+      <c r="P312" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q312" s="21" t="n">
-        <v>-1.01</v>
+        <v>34.13127005687629</v>
       </c>
       <c r="R312" s="18" t="n">
         <v>0</v>
@@ -56509,89 +56499,103 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>VFS</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>VinFast Auto Ltd. Ordinary Sha</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F66" s="18" t="n">
-        <v>104030609408</v>
+        <v>7509911040</v>
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H66" s="20" t="n">
-        <v>12.211</v>
-      </c>
-      <c r="I66" s="20" t="n">
-        <v>14.801482</v>
-      </c>
-      <c r="J66" s="20" t="n">
-        <v>3.2861774</v>
-      </c>
-      <c r="K66" s="20" t="n">
-        <v>0.68366075</v>
-      </c>
-      <c r="L66" s="21" t="n">
-        <v>6.14626794593043</v>
-      </c>
-      <c r="M66" s="21" t="n">
-        <v>2.96</v>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N66" s="21" t="n">
-        <v>12.24307948200071</v>
+        <v>78.31448357763071</v>
       </c>
       <c r="O66" s="21" t="n">
-        <v>6.84160433056228</v>
-      </c>
-      <c r="P66" s="20" t="n">
-        <v>1.675361394631018</v>
+        <v>-83.1176333196485</v>
+      </c>
+      <c r="P66" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q66" s="21" t="n">
-        <v>92.92</v>
+        <v>-3.75</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S66" s="20" t="n">
-        <v>0.3806408342658987</v>
+        <v>0.460552269511968</v>
       </c>
       <c r="T66" s="15" t="inlineStr">
         <is>
-          <t>Marketing Speciality (46%)</t>
+          <t>Car (48%)</t>
         </is>
       </c>
       <c r="U66" s="17" t="inlineStr">
         <is>
-          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
+          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
         </is>
       </c>
       <c r="V66" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W66" s="17" t="inlineStr">
         <is>
-          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
+          <t>VN 89%; Asia Pacific 8%; US 2%</t>
         </is>
       </c>
       <c r="X66" s="15" t="inlineStr">
         <is>
-          <t>Refining +92%</t>
+          <t>E Scooter +230%</t>
         </is>
       </c>
       <c r="Y66" s="22" t="inlineStr">
@@ -56612,12 +56616,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Amphenol Corp /De/</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -56627,11 +56631,11 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F67" s="18" t="n">
-        <v>206943928320</v>
+        <v>104030609408</v>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
@@ -56639,69 +56643,73 @@
         </is>
       </c>
       <c r="H67" s="20" t="n">
-        <v>29.62302222645686</v>
+        <v>12.211</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>41.96</v>
+        <v>14.801482</v>
       </c>
       <c r="J67" s="20" t="n">
-        <v>13.354551</v>
+        <v>3.2861774</v>
       </c>
       <c r="K67" s="20" t="n">
-        <v>7.1331444</v>
+        <v>0.68366075</v>
       </c>
       <c r="L67" s="21" t="n">
-        <v>2.30913485895705</v>
+        <v>6.14626794593043</v>
       </c>
       <c r="M67" s="21" t="n">
-        <v>0.55827491517045</v>
+        <v>2.96</v>
       </c>
       <c r="N67" s="21" t="n">
-        <v>45.67278672993024</v>
+        <v>12.24307948200071</v>
       </c>
       <c r="O67" s="21" t="n">
-        <v>29.39923710032213</v>
+        <v>6.84160433056228</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>2.057377830710813</v>
+        <v>1.675361394631018</v>
       </c>
       <c r="Q67" s="21" t="n">
-        <v>19.46</v>
+        <v>92.92</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S67" s="20" t="n">
-        <v>0.4256894967493531</v>
+        <v>0.3806408342658987</v>
       </c>
       <c r="T67" s="15" t="inlineStr">
         <is>
-          <t>Communications Solutio (58%)</t>
+          <t>Marketing Speciality (46%)</t>
         </is>
       </c>
       <c r="U67" s="17" t="inlineStr">
         <is>
-          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
+          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
         </is>
       </c>
       <c r="V67" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W67" s="17" t="inlineStr">
         <is>
-          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
+          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
         </is>
       </c>
       <c r="X67" s="15" t="inlineStr">
         <is>
-          <t>Communications Solut +143%</t>
-        </is>
-      </c>
-      <c r="Y67" s="21" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="Z67" s="20" t="n">
-        <v>-0.0436</v>
+          <t>Refining +92%</t>
+        </is>
+      </c>
+      <c r="Y67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z67" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA67" s="24" t="inlineStr"/>
     </row>
@@ -56711,12 +56719,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L</t>
+          <t>Amphenol Corp /De/</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -56726,11 +56734,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>84003667968</v>
+        <v>206943928320</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -56738,69 +56746,69 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>11.619</v>
+        <v>29.62302222645686</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>13.460208</v>
+        <v>41.96</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>2.777183</v>
+        <v>13.354551</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>1.4366723</v>
+        <v>7.1331444</v>
       </c>
       <c r="L68" s="21" t="n">
-        <v>4.43809968934908</v>
+        <v>2.30913485895705</v>
       </c>
       <c r="M68" s="21" t="n">
-        <v>0.13529237831726</v>
+        <v>0.55827491517045</v>
       </c>
       <c r="N68" s="21" t="n">
-        <v>21.16359754470242</v>
+        <v>45.67278672993024</v>
       </c>
       <c r="O68" s="21" t="n">
-        <v>19.03228934354698</v>
+        <v>29.39923710032213</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>3.436213572447524</v>
+        <v>2.057377830710813</v>
       </c>
       <c r="Q68" s="21" t="n">
-        <v>32.34</v>
+        <v>19.46</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S68" s="20" t="n">
-        <v>0.3092139839729619</v>
+        <v>0.4256894967493531</v>
       </c>
       <c r="T68" s="15" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipe (39%)</t>
+          <t>Communications Solutio (58%)</t>
         </is>
       </c>
       <c r="U68" s="17" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
+          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
         </is>
       </c>
       <c r="V68" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W68" s="17" t="inlineStr">
+        <is>
+          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
+        </is>
+      </c>
       <c r="X68" s="15" t="inlineStr">
         <is>
-          <t>Petrochemical And Re +92%</t>
-        </is>
-      </c>
-      <c r="Y68" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z68" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Communications Solut +143%</t>
+        </is>
+      </c>
+      <c r="Y68" s="21" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="Z68" s="20" t="n">
+        <v>-0.0436</v>
       </c>
       <c r="AA68" s="24" t="inlineStr"/>
     </row>
@@ -56810,12 +56818,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Enterprise Products Partners L</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -56825,11 +56833,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>59365711872</v>
+        <v>84003667968</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -56837,62 +56845,58 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>38.313</v>
+        <v>11.619</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>52.08779</v>
+        <v>13.460208</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>18.907534</v>
+        <v>2.777183</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>17.51624120163544</v>
+        <v>1.4366723</v>
       </c>
       <c r="L69" s="21" t="n">
-        <v>1.43309891391495</v>
+        <v>4.43809968934908</v>
       </c>
       <c r="M69" s="21" t="n">
-        <v>0.11999999</v>
+        <v>0.13529237831726</v>
       </c>
       <c r="N69" s="21" t="n">
-        <v>28.59709180832235</v>
+        <v>21.16359754470242</v>
       </c>
       <c r="O69" s="21" t="n">
-        <v>44.40287939770699</v>
+        <v>19.03228934354698</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>-0.1708346552178611</v>
+        <v>3.436213572447524</v>
       </c>
       <c r="Q69" s="21" t="n">
-        <v>96.81</v>
+        <v>32.34</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.6478300772075185</v>
+        <v>0.3092139839729619</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test (79%)</t>
+          <t>Onshore Crude Oil Pipe (39%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
+          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="W69" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W69" s="17" t="n"/>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test +128%</t>
+          <t>Petrochemical And Re +92%</t>
         </is>
       </c>
       <c r="Y69" s="22" t="inlineStr">
@@ -56913,12 +56917,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Te Connectivity Plc</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -56932,7 +56936,7 @@
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>61365223424</v>
+        <v>59365711872</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -56940,69 +56944,73 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>12.92</v>
+        <v>38.313</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>20.76004</v>
+        <v>52.08779</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>4.6395974</v>
+        <v>18.907534</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>3.175925</v>
+        <v>17.51624120163544</v>
       </c>
       <c r="L70" s="21" t="n">
-        <v>5.99434499439441</v>
+        <v>1.43309891391495</v>
       </c>
       <c r="M70" s="21" t="n">
-        <v>1.50999995</v>
+        <v>0.11999999</v>
       </c>
       <c r="N70" s="21" t="n">
-        <v>19.58952110795928</v>
+        <v>28.59709180832235</v>
       </c>
       <c r="O70" s="21" t="n">
-        <v>23.88059701492537</v>
+        <v>44.40287939770699</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>1.09837962962963</v>
+        <v>-0.1708346552178611</v>
       </c>
       <c r="Q70" s="21" t="n">
-        <v>-14.61</v>
+        <v>96.81</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.5038462678974261</v>
+        <v>0.6478300772075185</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Transportation Solutio (54%)</t>
+          <t>Semiconductor Test (79%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
+          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W70" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
+          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
         </is>
       </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Industrial Solutions +344%</t>
-        </is>
-      </c>
-      <c r="Y70" s="21" t="n">
-        <v>-15.49</v>
-      </c>
-      <c r="Z70" s="20" t="n">
-        <v>-2.0745</v>
+          <t>Semiconductor Test +128%</t>
+        </is>
+      </c>
+      <c r="Y70" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z70" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA70" s="24" t="inlineStr"/>
     </row>
@@ -57012,12 +57020,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>DWSN</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Dawson Geophysical Company</t>
+          <t>Te Connectivity Plc</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -57027,11 +57035,11 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>104346872</v>
+        <v>61365223424</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -57039,71 +57047,71 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>9.484</v>
+        <v>12.92</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>28</v>
+        <v>20.76004</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>5.2093024</v>
+        <v>4.6395974</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>0.781109620624607</v>
+        <v>3.175925</v>
       </c>
       <c r="L71" s="21" t="n">
-        <v>-3.92755347083511</v>
+        <v>5.99434499439441</v>
       </c>
       <c r="M71" s="21" t="n">
-        <v>8.120800080331669</v>
+        <v>1.50999995</v>
       </c>
       <c r="N71" s="21" t="n">
-        <v>25.64674804153762</v>
+        <v>19.58952110795928</v>
       </c>
       <c r="O71" s="21" t="n">
-        <v>8.550169176872171</v>
+        <v>23.88059701492537</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>1.218788303274383</v>
+        <v>1.09837962962963</v>
       </c>
       <c r="Q71" s="21" t="n">
-        <v>85.28</v>
+        <v>-14.61</v>
       </c>
       <c r="R71" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.6695871789304009</v>
+        <v>0.5038462678974261</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>United States Operatio (79%)</t>
+          <t>Transportation Solutio (54%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>United States Operations 79%; Canada Operations 21%</t>
+          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" s="17" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="W71" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
+        </is>
+      </c>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Canada Operations +152%</t>
+          <t>Industrial Solutions +344%</t>
         </is>
       </c>
       <c r="Y71" s="21" t="n">
-        <v>7.52</v>
+        <v>-15.49</v>
       </c>
       <c r="Z71" s="20" t="n">
-        <v>1.4961</v>
-      </c>
-      <c r="AA71" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-2.0745</v>
+      </c>
+      <c r="AA71" s="24" t="inlineStr"/>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="13" t="n">
@@ -57111,12 +57119,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>DWSN</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
+          <t>Dawson Geophysical Company</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -57126,11 +57134,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>4507106816</v>
+        <v>104346872</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -57138,71 +57146,71 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>20.979</v>
+        <v>9.484</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>39.50917</v>
+        <v>28</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>4.942614</v>
+        <v>5.2093024</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>5.988356816294535</v>
+        <v>0.781109620624607</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>0.9359515835039199</v>
+        <v>-3.92755347083511</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>0.64999997</v>
+        <v>8.120800080331669</v>
       </c>
       <c r="N72" s="21" t="n">
-        <v>-5.462297040904851</v>
+        <v>25.64674804153762</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>25.49940543018288</v>
+        <v>8.550169176872171</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>-2.120367819924969</v>
+        <v>1.218788303274383</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>106.32</v>
+        <v>85.28</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S72" s="20" t="n">
-        <v>0.2775979208843406</v>
+        <v>0.6695871789304009</v>
       </c>
       <c r="T72" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment (43%)</t>
+          <t>United States Operatio (79%)</t>
         </is>
       </c>
       <c r="U72" s="17" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
+          <t>United States Operations 79%; Canada Operations 21%</t>
         </is>
       </c>
       <c r="V72" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W72" s="17" t="inlineStr">
-        <is>
-          <t>CN 56%; US 10%; All Other Segments 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W72" s="17" t="n"/>
       <c r="X72" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipme +198%</t>
+          <t>Canada Operations +152%</t>
         </is>
       </c>
       <c r="Y72" s="21" t="n">
-        <v>-2.76</v>
+        <v>7.52</v>
       </c>
       <c r="Z72" s="20" t="n">
-        <v>-0.07149999999999999</v>
-      </c>
-      <c r="AA72" s="24" t="inlineStr"/>
+        <v>1.4961</v>
+      </c>
+      <c r="AA72" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="13" t="n">
@@ -57210,12 +57218,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>Emergent Biosolutions Inc.</t>
+          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -57225,11 +57233,11 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F73" s="18" t="n">
-        <v>319432896</v>
+        <v>4507106816</v>
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
@@ -57237,77 +57245,69 @@
         </is>
       </c>
       <c r="H73" s="20" t="n">
-        <v>26.38994704225352</v>
-      </c>
-      <c r="I73" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.979</v>
+      </c>
+      <c r="I73" s="20" t="n">
+        <v>39.50917</v>
       </c>
       <c r="J73" s="20" t="n">
-        <v>0.9361382</v>
+        <v>4.942614</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>0.4147402</v>
+        <v>5.988356816294535</v>
       </c>
       <c r="L73" s="21" t="n">
-        <v>26.97801418097588</v>
-      </c>
-      <c r="M73" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.9359515835039199</v>
+      </c>
+      <c r="M73" s="21" t="n">
+        <v>0.64999997</v>
       </c>
       <c r="N73" s="21" t="n">
-        <v>14.79068774028193</v>
+        <v>-5.462297040904851</v>
       </c>
       <c r="O73" s="21" t="n">
-        <v>3.78515260562441</v>
+        <v>25.49940543018288</v>
       </c>
       <c r="P73" s="20" t="n">
-        <v>14.55281690140845</v>
+        <v>-2.120367819924969</v>
       </c>
       <c r="Q73" s="21" t="n">
-        <v>-50.23999999999999</v>
+        <v>106.32</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S73" s="20" t="n">
-        <v>0.557029765440831</v>
+        <v>0.2775979208843406</v>
       </c>
       <c r="T73" s="15" t="inlineStr">
         <is>
-          <t>MCM Products (67%)</t>
+          <t>Ball Bonding Equipment (43%)</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
         <is>
-          <t>MCM Products 67%; Commercial Products 33%</t>
+          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
         </is>
       </c>
       <c r="V73" s="18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W73" s="17" t="inlineStr">
         <is>
-          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
+          <t>CN 56%; US 10%; All Other Segments 9%</t>
         </is>
       </c>
       <c r="X73" s="15" t="inlineStr">
         <is>
-          <t>MCM Products +188%</t>
-        </is>
-      </c>
-      <c r="Y73" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z73" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Ball Bonding Equipme +198%</t>
+        </is>
+      </c>
+      <c r="Y73" s="21" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="Z73" s="20" t="n">
+        <v>-0.07149999999999999</v>
       </c>
       <c r="AA73" s="24" t="inlineStr"/>
     </row>
@@ -57317,12 +57317,12 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Porch Group Inc.</t>
+          <t>Emergent Biosolutions Inc.</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -57332,11 +57332,11 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F74" s="18" t="n">
-        <v>1867401472</v>
+        <v>319432896</v>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
@@ -57344,62 +57344,66 @@
         </is>
       </c>
       <c r="H74" s="20" t="n">
-        <v>37.42943855774974</v>
+        <v>26.38994704225352</v>
       </c>
       <c r="I74" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J74" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="J74" s="20" t="n">
+        <v>0.9361382</v>
       </c>
       <c r="K74" s="20" t="n">
-        <v>3.6359277</v>
+        <v>0.4147402</v>
       </c>
       <c r="L74" s="21" t="n">
-        <v>4.69353492369449</v>
-      </c>
-      <c r="M74" s="21" t="n">
-        <v>2.78673595725851</v>
+        <v>26.97801418097588</v>
+      </c>
+      <c r="M74" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N74" s="21" t="n">
-        <v>10.31950957042169</v>
+        <v>14.79068774028193</v>
       </c>
       <c r="O74" s="21" t="n">
-        <v>10.50153492306376</v>
+        <v>3.78515260562441</v>
       </c>
       <c r="P74" s="20" t="n">
-        <v>3.279218781110286</v>
+        <v>14.55281690140845</v>
       </c>
       <c r="Q74" s="21" t="n">
-        <v>19.2</v>
+        <v>-50.23999999999999</v>
       </c>
       <c r="R74" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" s="20" t="n">
+        <v>0.557029765440831</v>
+      </c>
+      <c r="T74" s="15" t="inlineStr">
+        <is>
+          <t>MCM Products (67%)</t>
+        </is>
+      </c>
+      <c r="U74" s="17" t="inlineStr">
+        <is>
+          <t>MCM Products 67%; Commercial Products 33%</t>
+        </is>
+      </c>
+      <c r="V74" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="S74" s="20" t="n">
-        <v>0.5817970747345014</v>
-      </c>
-      <c r="T74" s="15" t="inlineStr">
-        <is>
-          <t>Insurance Services (72%)</t>
-        </is>
-      </c>
-      <c r="U74" s="17" t="inlineStr">
-        <is>
-          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
-        </is>
-      </c>
-      <c r="V74" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="17" t="n"/>
+      <c r="W74" s="17" t="inlineStr">
+        <is>
+          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
+        </is>
+      </c>
       <c r="X74" s="15" t="inlineStr">
         <is>
-          <t>Software Data +333%</t>
+          <t>MCM Products +188%</t>
         </is>
       </c>
       <c r="Y74" s="22" t="inlineStr">
@@ -57420,12 +57424,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>NGL</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>NGL Energy Partners LP</t>
+          <t>Porch Group Inc.</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -57435,11 +57439,11 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F75" s="18" t="n">
-        <v>1989539712</v>
+        <v>1867401472</v>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
@@ -57447,7 +57451,7 @@
         </is>
       </c>
       <c r="H75" s="20" t="n">
-        <v>15.17839608310902</v>
+        <v>37.42943855774974</v>
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
@@ -57460,55 +57464,49 @@
         </is>
       </c>
       <c r="K75" s="20" t="n">
-        <v>0.6303674</v>
+        <v>3.6359277</v>
       </c>
       <c r="L75" s="21" t="n">
-        <v>5.12068190373472</v>
-      </c>
-      <c r="M75" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69353492369449</v>
+      </c>
+      <c r="M75" s="21" t="n">
+        <v>2.78673595725851</v>
       </c>
       <c r="N75" s="21" t="n">
-        <v>12.90137422847655</v>
+        <v>10.31950957042169</v>
       </c>
       <c r="O75" s="21" t="n">
-        <v>11.58580003385248</v>
+        <v>10.50153492306376</v>
       </c>
       <c r="P75" s="20" t="n">
-        <v>7.901573173509551</v>
+        <v>3.279218781110286</v>
       </c>
       <c r="Q75" s="21" t="n">
-        <v>174.77</v>
+        <v>19.2</v>
       </c>
       <c r="R75" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S75" s="20" t="n">
-        <v>0.3423299785064143</v>
+        <v>0.5817970747345014</v>
       </c>
       <c r="T75" s="15" t="inlineStr">
         <is>
-          <t>Liquids Logistics (40%)</t>
+          <t>Insurance Services (72%)</t>
         </is>
       </c>
       <c r="U75" s="17" t="inlineStr">
         <is>
-          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
+          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
         </is>
       </c>
       <c r="V75" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="W75" s="17" t="inlineStr">
-        <is>
-          <t>Non Us 100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W75" s="17" t="n"/>
       <c r="X75" s="15" t="inlineStr">
         <is>
-          <t>Crude Oil Logistics +162%</t>
+          <t>Software Data +333%</t>
         </is>
       </c>
       <c r="Y75" s="22" t="inlineStr">
@@ -57529,12 +57527,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NGL</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NGL Energy Partners LP</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -57544,11 +57542,11 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F76" s="18" t="n">
-        <v>360690188288</v>
+        <v>1989539712</v>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
@@ -57556,10 +57554,12 @@
         </is>
       </c>
       <c r="H76" s="20" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="I76" s="20" t="n">
-        <v>33.039604</v>
+        <v>15.17839608310902</v>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J76" s="22" t="inlineStr">
         <is>
@@ -57567,60 +57567,66 @@
         </is>
       </c>
       <c r="K76" s="20" t="n">
-        <v>2.3855643</v>
+        <v>0.6303674</v>
       </c>
       <c r="L76" s="21" t="n">
-        <v>2.02823359941622</v>
-      </c>
-      <c r="M76" s="21" t="n">
-        <v>0.76768205413026</v>
+        <v>5.12068190373472</v>
+      </c>
+      <c r="M76" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N76" s="21" t="n">
-        <v>81.97384514065294</v>
+        <v>12.90137422847655</v>
       </c>
       <c r="O76" s="21" t="n">
-        <v>13.94585527536068</v>
+        <v>11.58580003385248</v>
       </c>
       <c r="P76" s="20" t="n">
-        <v>1.01819258757827</v>
+        <v>7.901573173509551</v>
       </c>
       <c r="Q76" s="21" t="n">
-        <v>226.48</v>
+        <v>174.77</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76" s="20" t="n">
-        <v>0.5038741410704293</v>
+        <v>0.3423299785064143</v>
       </c>
       <c r="T76" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solutio (54%)</t>
+          <t>Liquids Logistics (40%)</t>
         </is>
       </c>
       <c r="U76" s="17" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
+          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
         </is>
       </c>
       <c r="V76" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W76" s="17" t="inlineStr">
         <is>
-          <t>US 56%; Non Us 44%</t>
+          <t>Non Us 100%</t>
         </is>
       </c>
       <c r="X76" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solut +181%</t>
-        </is>
-      </c>
-      <c r="Y76" s="21" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="Z76" s="20" t="n">
-        <v>-0.1207</v>
+          <t>Crude Oil Logistics +162%</t>
+        </is>
+      </c>
+      <c r="Y76" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z76" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA76" s="24" t="inlineStr"/>
     </row>
@@ -57630,12 +57636,12 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -57649,7 +57655,7 @@
         </is>
       </c>
       <c r="F77" s="18" t="n">
-        <v>83154591744</v>
+        <v>360690188288</v>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
@@ -57657,75 +57663,71 @@
         </is>
       </c>
       <c r="H77" s="20" t="n">
-        <v>102.474</v>
+        <v>19.51</v>
       </c>
       <c r="I77" s="20" t="n">
-        <v>142.82867</v>
-      </c>
-      <c r="J77" s="20" t="n">
-        <v>17.686687</v>
+        <v>33.039604</v>
+      </c>
+      <c r="J77" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K77" s="20" t="n">
-        <v>27.589445</v>
+        <v>2.3855643</v>
       </c>
       <c r="L77" s="21" t="n">
-        <v>0.37963999713611</v>
-      </c>
-      <c r="M77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.02823359941622</v>
+      </c>
+      <c r="M77" s="21" t="n">
+        <v>0.76768205413026</v>
       </c>
       <c r="N77" s="21" t="n">
-        <v>5.712871831528011</v>
+        <v>81.97384514065294</v>
       </c>
       <c r="O77" s="21" t="n">
-        <v>32.17730397042276</v>
+        <v>13.94585527536068</v>
       </c>
       <c r="P77" s="20" t="n">
-        <v>-1.18221551413651</v>
+        <v>1.01819258757827</v>
       </c>
       <c r="Q77" s="21" t="n">
-        <v>337.22</v>
+        <v>226.48</v>
       </c>
       <c r="R77" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S77" s="20" t="n">
-        <v>0.554732848124369</v>
+        <v>0.5038741410704293</v>
       </c>
       <c r="T77" s="15" t="inlineStr">
         <is>
-          <t>Systems (67%)</t>
+          <t>Infrastructure Solutio (54%)</t>
         </is>
       </c>
       <c r="U77" s="17" t="inlineStr">
         <is>
-          <t>Systems 67%; Components 33%</t>
+          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
         </is>
       </c>
       <c r="V77" s="18" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="W77" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
+          <t>US 56%; Non Us 44%</t>
         </is>
       </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
-          <t>Systems +279%</t>
-        </is>
-      </c>
-      <c r="Y77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Infrastructure Solut +181%</t>
+        </is>
+      </c>
+      <c r="Y77" s="21" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="Z77" s="20" t="n">
+        <v>-0.1207</v>
       </c>
       <c r="AA77" s="24" t="inlineStr"/>
     </row>
@@ -57735,12 +57737,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>PROG Holdings, Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -57750,11 +57752,11 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F78" s="18" t="n">
-        <v>1472177024</v>
+        <v>83154591744</v>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
@@ -57762,58 +57764,64 @@
         </is>
       </c>
       <c r="H78" s="20" t="n">
-        <v>8.850440627472885</v>
+        <v>102.474</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>11.922581</v>
+        <v>142.82867</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>1.8279835</v>
+        <v>17.686687</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>0.5630427</v>
+        <v>27.589445</v>
       </c>
       <c r="L78" s="21" t="n">
-        <v>20.7154094641091</v>
-      </c>
-      <c r="M78" s="21" t="n">
-        <v>1.20889722398801</v>
+        <v>0.37963999713611</v>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N78" s="21" t="n">
-        <v>14.37354784103989</v>
+        <v>5.712871831528011</v>
       </c>
       <c r="O78" s="21" t="n">
-        <v>10.44635139915609</v>
+        <v>32.17730397042276</v>
       </c>
       <c r="P78" s="20" t="n">
-        <v>3.362100265326072</v>
+        <v>-1.18221551413651</v>
       </c>
       <c r="Q78" s="21" t="n">
-        <v>38.15</v>
+        <v>337.22</v>
       </c>
       <c r="R78" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S78" s="20" t="n">
-        <v>0.9403673440059026</v>
+        <v>0.554732848124369</v>
       </c>
       <c r="T78" s="15" t="inlineStr">
         <is>
-          <t>Progressive Leasing (97%)</t>
+          <t>Systems (67%)</t>
         </is>
       </c>
       <c r="U78" s="17" t="inlineStr">
         <is>
-          <t>Progressive Leasing 97%; Four 3%</t>
+          <t>Systems 67%; Components 33%</t>
         </is>
       </c>
       <c r="V78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="17" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="W78" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
+        </is>
+      </c>
       <c r="X78" s="15" t="inlineStr">
         <is>
-          <t>Four +170%</t>
+          <t>Systems +279%</t>
         </is>
       </c>
       <c r="Y78" s="22" t="inlineStr">
@@ -57834,12 +57842,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Ies Holdings, Inc.</t>
+          <t>PROG Holdings, Inc.</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -57853,7 +57861,7 @@
         </is>
       </c>
       <c r="F79" s="18" t="n">
-        <v>13776098304</v>
+        <v>1472177024</v>
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
@@ -57861,51 +57869,49 @@
         </is>
       </c>
       <c r="H79" s="20" t="n">
-        <v>22.535</v>
+        <v>8.850440627472885</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>30.729776</v>
+        <v>11.922581</v>
       </c>
       <c r="J79" s="20" t="n">
-        <v>11.206885</v>
+        <v>1.8279835</v>
       </c>
       <c r="K79" s="20" t="n">
-        <v>3.4563446</v>
+        <v>0.5630427</v>
       </c>
       <c r="L79" s="21" t="n">
-        <v>2.01426811681025</v>
-      </c>
-      <c r="M79" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.7154094641091</v>
+      </c>
+      <c r="M79" s="21" t="n">
+        <v>1.20889722398801</v>
       </c>
       <c r="N79" s="21" t="n">
-        <v>39.14787497533104</v>
+        <v>14.37354784103989</v>
       </c>
       <c r="O79" s="21" t="n">
-        <v>13.0825133917565</v>
+        <v>10.44635139915609</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>-0.6658293394323307</v>
+        <v>3.362100265326072</v>
       </c>
       <c r="Q79" s="21" t="n">
-        <v>64.63</v>
+        <v>38.15</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S79" s="20" t="n">
-        <v>0.302118628032772</v>
+        <v>0.9403673440059026</v>
       </c>
       <c r="T79" s="15" t="inlineStr">
         <is>
-          <t>Residential (39%)</t>
+          <t>Progressive Leasing (97%)</t>
         </is>
       </c>
       <c r="U79" s="17" t="inlineStr">
         <is>
-          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
+          <t>Progressive Leasing 97%; Four 3%</t>
         </is>
       </c>
       <c r="V79" s="18" t="n">
@@ -57914,14 +57920,18 @@
       <c r="W79" s="17" t="n"/>
       <c r="X79" s="15" t="inlineStr">
         <is>
-          <t>Commercialand Indust +109%</t>
-        </is>
-      </c>
-      <c r="Y79" s="21" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Z79" s="20" t="n">
-        <v>-0.0209</v>
+          <t>Four +170%</t>
+        </is>
+      </c>
+      <c r="Y79" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z79" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA79" s="24" t="inlineStr"/>
     </row>
@@ -57931,12 +57941,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Ies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -57946,11 +57956,11 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F80" s="18" t="n">
-        <v>5271048421376</v>
+        <v>13776098304</v>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
@@ -57958,69 +57968,67 @@
         </is>
       </c>
       <c r="H80" s="20" t="n">
-        <v>26.03</v>
+        <v>22.535</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>27.631645</v>
+        <v>30.729776</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>23.019087</v>
+        <v>11.206885</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>195.8478272042803</v>
+        <v>3.4563446</v>
       </c>
       <c r="L80" s="21" t="n">
-        <v>1.66135648441059</v>
-      </c>
-      <c r="M80" s="21" t="n">
-        <v>0.01871342168819</v>
+        <v>2.01426811681025</v>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N80" s="21" t="n">
-        <v>73.21388307718124</v>
+        <v>39.14787497533104</v>
       </c>
       <c r="O80" s="21" t="n">
-        <v>79.39769221313577</v>
+        <v>13.0825133917565</v>
       </c>
       <c r="P80" s="20" t="n">
-        <v>-0.3535471835000259</v>
+        <v>-0.6658293394323307</v>
       </c>
       <c r="Q80" s="21" t="n">
-        <v>13.91</v>
+        <v>64.63</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S80" s="20" t="n">
-        <v>0.8136213783744384</v>
+        <v>0.302118628032772</v>
       </c>
       <c r="T80" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networking (90%)</t>
+          <t>Residential (39%)</t>
         </is>
       </c>
       <c r="U80" s="17" t="inlineStr">
         <is>
-          <t>Compute And Networking 90%; Graphics 10%</t>
+          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
         </is>
       </c>
       <c r="V80" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W80" s="17" t="inlineStr">
-        <is>
-          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W80" s="17" t="n"/>
       <c r="X80" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networki +114%</t>
+          <t>Commercialand Indust +109%</t>
         </is>
       </c>
       <c r="Y80" s="21" t="n">
-        <v>-4.06</v>
+        <v>-0.2</v>
       </c>
       <c r="Z80" s="20" t="n">
-        <v>-0.0948</v>
+        <v>-0.0209</v>
       </c>
       <c r="AA80" s="24" t="inlineStr"/>
     </row>
@@ -58030,12 +58038,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
@@ -58045,11 +58053,11 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F81" s="18" t="n">
-        <v>10556858368</v>
+        <v>5271048421376</v>
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
@@ -58057,75 +58065,69 @@
         </is>
       </c>
       <c r="H81" s="20" t="n">
-        <v>347.3889692037075</v>
+        <v>26.03</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>68.672195</v>
+        <v>27.631645</v>
       </c>
       <c r="J81" s="20" t="n">
-        <v>6.6218543</v>
+        <v>23.019087</v>
       </c>
       <c r="K81" s="20" t="n">
-        <v>4.817643283343015</v>
+        <v>195.8478272042803</v>
       </c>
       <c r="L81" s="21" t="n">
-        <v>-8.42592261675078</v>
-      </c>
-      <c r="M81" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.66135648441059</v>
+      </c>
+      <c r="M81" s="21" t="n">
+        <v>0.01871342168819</v>
       </c>
       <c r="N81" s="21" t="n">
-        <v>-0.11123836175898</v>
+        <v>73.21388307718124</v>
       </c>
       <c r="O81" s="21" t="n">
-        <v>1.17675041790433</v>
+        <v>79.39769221313577</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>-59.63858781496614</v>
+        <v>-0.3535471835000259</v>
       </c>
       <c r="Q81" s="21" t="n">
-        <v>7.08</v>
+        <v>13.91</v>
       </c>
       <c r="R81" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" s="20" t="n">
+        <v>0.8136213783744384</v>
+      </c>
+      <c r="T81" s="15" t="inlineStr">
+        <is>
+          <t>Compute And Networking (90%)</t>
+        </is>
+      </c>
+      <c r="U81" s="17" t="inlineStr">
+        <is>
+          <t>Compute And Networking 90%; Graphics 10%</t>
+        </is>
+      </c>
+      <c r="V81" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S81" s="20" t="n">
-        <v>0.3007342710765748</v>
-      </c>
-      <c r="T81" s="15" t="inlineStr">
-        <is>
-          <t>Brokerage (38%)</t>
-        </is>
-      </c>
-      <c r="U81" s="17" t="inlineStr">
-        <is>
-          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
-        </is>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>5</v>
-      </c>
       <c r="W81" s="17" t="inlineStr">
         <is>
-          <t>KZ 84%; AM 8%; CY 7%</t>
+          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
         </is>
       </c>
       <c r="X81" s="15" t="inlineStr">
         <is>
-          <t>Other +100%</t>
-        </is>
-      </c>
-      <c r="Y81" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z81" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Compute And Networki +114%</t>
+        </is>
+      </c>
+      <c r="Y81" s="21" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="Z81" s="20" t="n">
+        <v>-0.0948</v>
       </c>
       <c r="AA81" s="24" t="inlineStr"/>
     </row>
@@ -58135,12 +58137,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>FutureFuel Corp.</t>
+          <t>Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -58150,80 +58152,76 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F82" s="18" t="n">
-        <v>239932352</v>
+        <v>10556858368</v>
       </c>
       <c r="G82" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H82" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I82" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H82" s="20" t="n">
+        <v>347.3889692037075</v>
+      </c>
+      <c r="I82" s="20" t="n">
+        <v>68.672195</v>
       </c>
       <c r="J82" s="20" t="n">
-        <v>1.5673351</v>
+        <v>6.6218543</v>
       </c>
       <c r="K82" s="20" t="n">
-        <v>1.5660461</v>
+        <v>4.817643283343015</v>
       </c>
       <c r="L82" s="21" t="n">
-        <v>-19.02773752715573</v>
-      </c>
-      <c r="M82" s="21" t="n">
-        <v>5.946712029429071</v>
+        <v>-8.42592261675078</v>
+      </c>
+      <c r="M82" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N82" s="21" t="n">
-        <v>-51.30812980930077</v>
+        <v>-0.11123836175898</v>
       </c>
       <c r="O82" s="21" t="n">
-        <v>-11.30220868498371</v>
-      </c>
-      <c r="P82" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.17675041790433</v>
+      </c>
+      <c r="P82" s="20" t="n">
+        <v>-59.63858781496614</v>
       </c>
       <c r="Q82" s="21" t="n">
-        <v>38.74</v>
+        <v>7.08</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S82" s="20" t="n">
-        <v>0.5298367272208879</v>
+        <v>0.3007342710765748</v>
       </c>
       <c r="T82" s="15" t="inlineStr">
         <is>
-          <t>Chemicals (62%)</t>
+          <t>Brokerage (38%)</t>
         </is>
       </c>
       <c r="U82" s="17" t="inlineStr">
         <is>
-          <t>Chemicals 62%; Biofuels 38%</t>
+          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
         </is>
       </c>
       <c r="V82" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W82" s="17" t="inlineStr">
         <is>
-          <t>US 99%; Non Us 1%</t>
+          <t>KZ 84%; AM 8%; CY 7%</t>
         </is>
       </c>
       <c r="X82" s="15" t="inlineStr">
         <is>
-          <t>Biofuels +178%</t>
+          <t>Other +100%</t>
         </is>
       </c>
       <c r="Y82" s="22" t="inlineStr">
@@ -58244,12 +58242,12 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>SLNH</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Soluna Holdings Inc. Common St</t>
+          <t>FutureFuel Corp.</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
@@ -58259,11 +58257,11 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F83" s="18" t="n">
-        <v>291062784</v>
+        <v>239932352</v>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
@@ -58281,24 +58279,22 @@
         </is>
       </c>
       <c r="J83" s="20" t="n">
-        <v>1.7097702</v>
+        <v>1.5673351</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>6.9173846</v>
+        <v>1.5660461</v>
       </c>
       <c r="L83" s="21" t="n">
-        <v>-15.20023065482923</v>
+        <v>-19.02773752715573</v>
       </c>
       <c r="M83" s="21" t="n">
-        <v>0.20077091953947</v>
-      </c>
-      <c r="N83" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.946712029429071</v>
+      </c>
+      <c r="N83" s="21" t="n">
+        <v>-51.30812980930077</v>
       </c>
       <c r="O83" s="21" t="n">
-        <v>-104.2041970672814</v>
+        <v>-11.30220868498371</v>
       </c>
       <c r="P83" s="22" t="inlineStr">
         <is>
@@ -58306,31 +58302,35 @@
         </is>
       </c>
       <c r="Q83" s="21" t="n">
-        <v>-65.62</v>
+        <v>38.74</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S83" s="20" t="n">
-        <v>0.5183581202661786</v>
+        <v>0.5298367272208879</v>
       </c>
       <c r="T83" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting (60%)</t>
+          <t>Chemicals (62%)</t>
         </is>
       </c>
       <c r="U83" s="17" t="inlineStr">
         <is>
-          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
+          <t>Chemicals 62%; Biofuels 38%</t>
         </is>
       </c>
       <c r="V83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W83" s="17" t="inlineStr">
+        <is>
+          <t>US 99%; Non Us 1%</t>
+        </is>
+      </c>
       <c r="X83" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting +303%</t>
+          <t>Biofuels +178%</t>
         </is>
       </c>
       <c r="Y83" s="22" t="inlineStr">
@@ -58351,12 +58351,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>SLNH</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Soluna Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -58366,81 +58366,89 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F84" s="18" t="n">
-        <v>98965053440</v>
+        <v>291062784</v>
       </c>
       <c r="G84" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H84" s="20" t="n">
-        <v>48.51287624683352</v>
-      </c>
-      <c r="I84" s="20" t="n">
-        <v>58.15837</v>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J84" s="20" t="n">
-        <v>20.799417</v>
+        <v>1.7097702</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>8.620950000000001</v>
+        <v>6.9173846</v>
       </c>
       <c r="L84" s="21" t="n">
-        <v>2.71275941299938</v>
+        <v>-15.20023065482923</v>
       </c>
       <c r="M84" s="21" t="n">
-        <v>0.03768476778678</v>
-      </c>
-      <c r="N84" s="21" t="n">
-        <v>33.68683344961626</v>
+        <v>0.20077091953947</v>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O84" s="21" t="n">
-        <v>21.35492557684859</v>
-      </c>
-      <c r="P84" s="20" t="n">
-        <v>0.3332181723959233</v>
+        <v>-104.2041970672814</v>
+      </c>
+      <c r="P84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q84" s="21" t="n">
-        <v>45.58</v>
+        <v>-65.62</v>
       </c>
       <c r="R84" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S84" s="20" t="n">
-        <v>0.5218491323594365</v>
+        <v>0.5183581202661786</v>
       </c>
       <c r="T84" s="15" t="inlineStr">
         <is>
-          <t>EMEA (66%)</t>
+          <t>Data Center Hosting (60%)</t>
         </is>
       </c>
       <c r="U84" s="17" t="inlineStr">
         <is>
-          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
+          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
         </is>
       </c>
       <c r="V84" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W84" s="17" t="inlineStr">
-        <is>
-          <t>US 59%; Asia 20%; Europe 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W84" s="17" t="n"/>
       <c r="X84" s="15" t="inlineStr">
         <is>
-          <t>Asia Pacific +290%</t>
-        </is>
-      </c>
-      <c r="Y84" s="21" t="n">
-        <v>-22.44</v>
-      </c>
-      <c r="Z84" s="20" t="n">
-        <v>-0.3272</v>
+          <t>Data Center Hosting +303%</t>
+        </is>
+      </c>
+      <c r="Y84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z84" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA84" s="24" t="inlineStr"/>
     </row>
@@ -58450,12 +58458,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
@@ -58465,11 +58473,11 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F85" s="18" t="n">
-        <v>3749439488</v>
+        <v>98965053440</v>
       </c>
       <c r="G85" s="19" t="inlineStr">
         <is>
@@ -58477,69 +58485,69 @@
         </is>
       </c>
       <c r="H85" s="20" t="n">
-        <v>19.297</v>
+        <v>48.51287624683352</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>30.920187</v>
+        <v>58.15837</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>4.9097958</v>
+        <v>20.799417</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>6.8440413</v>
+        <v>8.620950000000001</v>
       </c>
       <c r="L85" s="21" t="n">
-        <v>5.56871008366637</v>
+        <v>2.71275941299938</v>
       </c>
       <c r="M85" s="21" t="n">
-        <v>0.97</v>
+        <v>0.03768476778678</v>
       </c>
       <c r="N85" s="21" t="n">
-        <v>12.37235274898268</v>
+        <v>33.68683344961626</v>
       </c>
       <c r="O85" s="21" t="n">
-        <v>35.60723129340358</v>
+        <v>21.35492557684859</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>1.359732752360203</v>
+        <v>0.3332181723959233</v>
       </c>
       <c r="Q85" s="21" t="n">
-        <v>17.58</v>
+        <v>45.58</v>
       </c>
       <c r="R85" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S85" s="20" t="n">
-        <v>0.4262861010394083</v>
+        <v>0.5218491323594365</v>
       </c>
       <c r="T85" s="15" t="inlineStr">
         <is>
-          <t>Hospitality (52%)</t>
+          <t>EMEA (66%)</t>
         </is>
       </c>
       <c r="U85" s="17" t="inlineStr">
         <is>
-          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
+          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
         </is>
       </c>
       <c r="V85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W85" s="17" t="inlineStr">
+        <is>
+          <t>US 59%; Asia 20%; Europe 14%</t>
+        </is>
+      </c>
       <c r="X85" s="15" t="inlineStr">
         <is>
-          <t>Hospitality +157%</t>
-        </is>
-      </c>
-      <c r="Y85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z85" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Asia Pacific +290%</t>
+        </is>
+      </c>
+      <c r="Y85" s="21" t="n">
+        <v>-22.44</v>
+      </c>
+      <c r="Z85" s="20" t="n">
+        <v>-0.3272</v>
       </c>
       <c r="AA85" s="24" t="inlineStr"/>
     </row>
@@ -58549,12 +58557,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Homestolife Ltd</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -58564,11 +58572,11 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F86" s="18" t="n">
-        <v>159643760</v>
+        <v>3749439488</v>
       </c>
       <c r="G86" s="19" t="inlineStr">
         <is>
@@ -58576,81 +58584,71 @@
         </is>
       </c>
       <c r="H86" s="20" t="n">
-        <v>5.632</v>
+        <v>19.297</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>9.368421</v>
+        <v>30.920187</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>5.189504</v>
+        <v>4.9097958</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>0.4083795</v>
+        <v>6.8440413</v>
       </c>
       <c r="L86" s="21" t="n">
-        <v>7.56174932272778</v>
-      </c>
-      <c r="M86" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N86" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.56871008366637</v>
+      </c>
+      <c r="M86" s="21" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N86" s="21" t="n">
+        <v>12.37235274898268</v>
       </c>
       <c r="O86" s="21" t="n">
-        <v>5.26038476371263</v>
+        <v>35.60723129340358</v>
       </c>
       <c r="P86" s="20" t="n">
-        <v>-0.8495431924900106</v>
+        <v>1.359732752360203</v>
       </c>
       <c r="Q86" s="21" t="n">
-        <v>-46.17305967367813</v>
+        <v>17.58</v>
       </c>
       <c r="R86" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S86" s="20" t="n">
-        <v>0.8590900293205138</v>
+        <v>0.4262861010394083</v>
       </c>
       <c r="T86" s="15" t="inlineStr">
         <is>
-          <t>Export Sales (93%)</t>
+          <t>Hospitality (52%)</t>
         </is>
       </c>
       <c r="U86" s="17" t="inlineStr">
         <is>
-          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
+          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
         </is>
       </c>
       <c r="V86" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W86" s="17" t="inlineStr">
-        <is>
-          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W86" s="17" t="n"/>
       <c r="X86" s="15" t="inlineStr">
         <is>
-          <t>Retail Sales +100%</t>
-        </is>
-      </c>
-      <c r="Y86" s="21" t="n">
-        <v>38.69</v>
+          <t>Hospitality +157%</t>
+        </is>
+      </c>
+      <c r="Y86" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Z86" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="AA86" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA86" s="24" t="inlineStr"/>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="13" t="n">
@@ -58658,12 +58656,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>HTLM</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>Homestolife Ltd</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
@@ -58673,11 +58671,11 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F87" s="18" t="n">
-        <v>113033160</v>
+        <v>159643760</v>
       </c>
       <c r="G87" s="19" t="inlineStr">
         <is>
@@ -58685,71 +58683,75 @@
         </is>
       </c>
       <c r="H87" s="20" t="n">
-        <v>11.493</v>
+        <v>5.632</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>22.772728</v>
+        <v>9.368421</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>1.8398825</v>
+        <v>5.189504</v>
       </c>
       <c r="K87" s="20" t="n">
-        <v>4.0441093</v>
+        <v>0.4083795</v>
       </c>
       <c r="L87" s="21" t="n">
-        <v>5.20947381148941</v>
+        <v>7.56174932272778</v>
       </c>
       <c r="M87" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N87" s="21" t="n">
-        <v>16.80549850408138</v>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O87" s="21" t="n">
-        <v>24.49495025980879</v>
+        <v>5.26038476371263</v>
       </c>
       <c r="P87" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>-0.8495431924900106</v>
       </c>
       <c r="Q87" s="21" t="n">
-        <v>-0.7799999999999999</v>
+        <v>-46.17305967367813</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S87" s="20" t="n">
-        <v>0.3385873824755823</v>
+        <v>0.8590900293205138</v>
       </c>
       <c r="T87" s="15" t="inlineStr">
         <is>
-          <t>Defense Engineering Se (45%)</t>
+          <t>Export Sales (93%)</t>
         </is>
       </c>
       <c r="U87" s="17" t="inlineStr">
         <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
         </is>
       </c>
       <c r="V87" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W87" s="17" t="inlineStr">
         <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
+          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
         </is>
       </c>
       <c r="X87" s="15" t="inlineStr">
         <is>
-          <t>Marine Technology Bu +185%</t>
+          <t>Retail Sales +100%</t>
         </is>
       </c>
       <c r="Y87" s="21" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="Z87" s="20" t="n">
-        <v>0.2903</v>
+        <v>38.69</v>
+      </c>
+      <c r="Z87" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA87" s="24" t="inlineStr">
         <is>
@@ -58763,12 +58765,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>International Seaways, Inc.</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -58782,7 +58784,7 @@
         </is>
       </c>
       <c r="F88" s="18" t="n">
-        <v>5133920768</v>
+        <v>113033160</v>
       </c>
       <c r="G88" s="19" t="inlineStr">
         <is>
@@ -58790,71 +58792,77 @@
         </is>
       </c>
       <c r="H88" s="20" t="n">
-        <v>6.541</v>
+        <v>11.493</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>6.627238</v>
+        <v>22.772728</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>2.2658215</v>
+        <v>1.8398825</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>4.070105</v>
+        <v>4.0441093</v>
       </c>
       <c r="L88" s="21" t="n">
-        <v>5.245834756131551</v>
-      </c>
-      <c r="M88" s="21" t="n">
-        <v>4.9099997</v>
+        <v>5.20947381148941</v>
+      </c>
+      <c r="M88" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N88" s="21" t="n">
-        <v>18.67715244511617</v>
+        <v>16.80549850408138</v>
       </c>
       <c r="O88" s="21" t="n">
-        <v>76.86433409911049</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="P88" s="20" t="n">
-        <v>0.1987435438854886</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q88" s="21" t="n">
-        <v>126.34</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S88" s="20" t="n">
-        <v>0.5009071443494075</v>
+        <v>0.3385873824755823</v>
       </c>
       <c r="T88" s="15" t="inlineStr">
         <is>
-          <t>International Crude Ta (52%)</t>
+          <t>Defense Engineering Se (45%)</t>
         </is>
       </c>
       <c r="U88" s="17" t="inlineStr">
         <is>
-          <t>International Crude Tankers 52%; International Product Carriers 48%</t>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
         </is>
       </c>
       <c r="V88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W88" s="17" t="inlineStr">
+        <is>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
+        </is>
+      </c>
       <c r="X88" s="15" t="inlineStr">
         <is>
-          <t>International Crude  +175%</t>
-        </is>
-      </c>
-      <c r="Y88" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z88" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA88" s="24" t="inlineStr"/>
+          <t>Marine Technology Bu +185%</t>
+        </is>
+      </c>
+      <c r="Y88" s="21" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="Z88" s="20" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AA88" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -58862,82 +58870,76 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>FENG</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Phoenix New Media Limited</t>
+          <t>International Seaways, Inc.</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F89" s="18" t="n">
-        <v>17896056</v>
+        <v>5133920768</v>
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H89" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H89" s="20" t="n">
+        <v>6.541</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>4.012985014645349</v>
+        <v>6.627238</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>22.1065917175247</v>
+        <v>2.2658215</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>0.1460944416764449</v>
+        <v>4.070105</v>
       </c>
       <c r="L89" s="21" t="n">
-        <v>-0.32072677140719</v>
-      </c>
-      <c r="M89" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.245834756131551</v>
+      </c>
+      <c r="M89" s="21" t="n">
+        <v>4.9099997</v>
       </c>
       <c r="N89" s="21" t="n">
-        <v>-8.02638700256313</v>
+        <v>18.67715244511617</v>
       </c>
       <c r="O89" s="21" t="n">
-        <v>-1.79463043292417</v>
-      </c>
-      <c r="P89" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>76.86433409911049</v>
+      </c>
+      <c r="P89" s="20" t="n">
+        <v>0.1987435438854886</v>
       </c>
       <c r="Q89" s="21" t="n">
-        <v>-36.75</v>
+        <v>126.34</v>
       </c>
       <c r="R89" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S89" s="20" t="n">
-        <v>0.682948135046668</v>
+        <v>0.5009071443494075</v>
       </c>
       <c r="T89" s="15" t="inlineStr">
         <is>
-          <t>Net Advertising Servic (80%)</t>
+          <t>International Crude Ta (52%)</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
-          <t>Net Advertising Services 80%; Paid Services 20%</t>
+          <t>International Crude Tankers 52%; International Product Carriers 48%</t>
         </is>
       </c>
       <c r="V89" s="18" t="n">
@@ -58946,7 +58948,7 @@
       <c r="W89" s="17" t="n"/>
       <c r="X89" s="15" t="inlineStr">
         <is>
-          <t>Paid Services +107%</t>
+          <t>International Crude  +175%</t>
         </is>
       </c>
       <c r="Y89" s="22" t="inlineStr">
@@ -58959,11 +58961,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="AA89" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA89" s="24" t="inlineStr"/>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="13" t="n">
@@ -58971,26 +58969,26 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Schrodinger, Inc.</t>
+          <t>Phoenix New Media Limited</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F90" s="18" t="n">
-        <v>1422803200</v>
+        <v>17896056</v>
       </c>
       <c r="G90" s="19" t="inlineStr">
         <is>
@@ -59002,32 +59000,28 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I90" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I90" s="20" t="n">
+        <v>4.012985014645349</v>
       </c>
       <c r="J90" s="20" t="n">
-        <v>4.213558</v>
+        <v>22.1065917175247</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>5.4927063</v>
+        <v>0.1460944416764449</v>
       </c>
       <c r="L90" s="21" t="n">
-        <v>-8.66829141064739</v>
+        <v>-0.32072677140719</v>
       </c>
       <c r="M90" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N90" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N90" s="21" t="n">
+        <v>-8.02638700256313</v>
       </c>
       <c r="O90" s="21" t="n">
-        <v>-84.61893927057798</v>
+        <v>-1.79463043292417</v>
       </c>
       <c r="P90" s="22" t="inlineStr">
         <is>
@@ -59035,35 +59029,31 @@
         </is>
       </c>
       <c r="Q90" s="21" t="n">
-        <v>-4.52</v>
+        <v>-36.75</v>
       </c>
       <c r="R90" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="20" t="n">
-        <v>0.6564595481920475</v>
+        <v>0.682948135046668</v>
       </c>
       <c r="T90" s="15" t="inlineStr">
         <is>
-          <t>Software (78%)</t>
+          <t>Net Advertising Servic (80%)</t>
         </is>
       </c>
       <c r="U90" s="17" t="inlineStr">
         <is>
-          <t>Software 78%; Drug Discovery 22%</t>
+          <t>Net Advertising Services 80%; Paid Services 20%</t>
         </is>
       </c>
       <c r="V90" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W90" s="17" t="inlineStr">
-        <is>
-          <t>US 60%; EMEA 29%; APAC 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W90" s="17" t="n"/>
       <c r="X90" s="15" t="inlineStr">
         <is>
-          <t>Drug Discovery +107%</t>
+          <t>Paid Services +107%</t>
         </is>
       </c>
       <c r="Y90" s="22" t="inlineStr">
@@ -59088,12 +59078,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc.</t>
+          <t>Schrodinger, Inc.</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
@@ -59103,74 +59093,84 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F91" s="18" t="n">
-        <v>10568248320</v>
+        <v>1422803200</v>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H91" s="20" t="n">
-        <v>-37.43331715008421</v>
-      </c>
-      <c r="I91" s="20" t="n">
-        <v>27.1789460083687</v>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J91" s="20" t="n">
-        <v>1.0001347</v>
+        <v>4.213558</v>
       </c>
       <c r="K91" s="20" t="n">
-        <v>1.9561423</v>
+        <v>5.4927063</v>
       </c>
       <c r="L91" s="21" t="n">
-        <v>16.83374525401008</v>
-      </c>
-      <c r="M91" s="21" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="N91" s="21" t="n">
-        <v>-0.21791453369172</v>
+        <v>-8.66829141064739</v>
+      </c>
+      <c r="M91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O91" s="21" t="n">
-        <v>5.51745776158655</v>
-      </c>
-      <c r="P91" s="20" t="n">
-        <v>-80.28756909079929</v>
+        <v>-84.61893927057798</v>
+      </c>
+      <c r="P91" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q91" s="21" t="n">
-        <v>7.7</v>
+        <v>-4.52</v>
       </c>
       <c r="R91" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>0.8308945641579533</v>
+        <v>0.6564595481920475</v>
       </c>
       <c r="T91" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking And (91%)</t>
+          <t>Software (78%)</t>
         </is>
       </c>
       <c r="U91" s="17" t="inlineStr">
         <is>
-          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
+          <t>Software 78%; Drug Discovery 22%</t>
         </is>
       </c>
       <c r="V91" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W91" s="17" t="inlineStr">
         <is>
-          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
+          <t>US 60%; EMEA 29%; APAC 10%</t>
         </is>
       </c>
       <c r="X91" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking A +123%</t>
+          <t>Drug Discovery +107%</t>
         </is>
       </c>
       <c r="Y91" s="22" t="inlineStr">
@@ -59183,7 +59183,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="AA91" s="24" t="inlineStr"/>
+      <c r="AA91" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -59191,12 +59195,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>ANNA</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>AleAnna Inc. Class A Common St</t>
+          <t>Jefferies Financial Group Inc.</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -59206,72 +59210,74 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>143290000</v>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>10568248320</v>
+      </c>
+      <c r="G92" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>8.568</v>
+        <v>-37.43331715008421</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>18.421053</v>
+        <v>27.1789460083687</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>3.5425103</v>
+        <v>1.0001347</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>3.5894861</v>
+        <v>1.9561423</v>
       </c>
       <c r="L92" s="21" t="n">
-        <v>7.167953799986041</v>
-      </c>
-      <c r="M92" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.83374525401008</v>
+      </c>
+      <c r="M92" s="21" t="n">
+        <v>3.26</v>
       </c>
       <c r="N92" s="21" t="n">
-        <v>1.46144795620644</v>
+        <v>-0.21791453369172</v>
       </c>
       <c r="O92" s="21" t="n">
-        <v>39.48335699937504</v>
+        <v>5.51745776158655</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>-1.974742069364569</v>
+        <v>-80.28756909079929</v>
       </c>
       <c r="Q92" s="21" t="n">
-        <v>-7.69</v>
+        <v>7.7</v>
       </c>
       <c r="R92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S92" s="20" t="n">
-        <v>0.8097190789385638</v>
+        <v>0.8308945641579533</v>
       </c>
       <c r="T92" s="15" t="inlineStr">
         <is>
-          <t>Conventional (89%)</t>
+          <t>Investment Banking And (91%)</t>
         </is>
       </c>
       <c r="U92" s="17" t="inlineStr">
         <is>
-          <t>Conventional 89%; Renewable 11%</t>
+          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
         </is>
       </c>
       <c r="V92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W92" s="17" t="inlineStr">
+        <is>
+          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
+        </is>
+      </c>
       <c r="X92" s="15" t="inlineStr">
         <is>
-          <t>Conventional +186%</t>
+          <t>Investment Banking A +123%</t>
         </is>
       </c>
       <c r="Y92" s="22" t="inlineStr">
@@ -59292,12 +59298,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>LVWR</t>
+          <t>ANNA</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>LiveWire Group Inc. Common Sto</t>
+          <t>AleAnna Inc. Class A Common St</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -59307,84 +59313,72 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>234170208</v>
-      </c>
-      <c r="G93" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="H93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>143290000</v>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>8.568</v>
+      </c>
+      <c r="I93" s="20" t="n">
+        <v>18.421053</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>19.655172</v>
+        <v>3.5425103</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>7.484824</v>
+        <v>3.5894861</v>
       </c>
       <c r="L93" s="21" t="n">
-        <v>-21.59336790483196</v>
+        <v>7.167953799986041</v>
       </c>
       <c r="M93" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N93" s="21" t="n">
+        <v>1.46144795620644</v>
       </c>
       <c r="O93" s="21" t="n">
-        <v>-207.6711628204309</v>
-      </c>
-      <c r="P93" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>39.48335699937504</v>
+      </c>
+      <c r="P93" s="20" t="n">
+        <v>-1.974742069364569</v>
       </c>
       <c r="Q93" s="21" t="n">
-        <v>-76.64</v>
+        <v>-7.69</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>0.4547555777310531</v>
+        <v>0.8097190789385638</v>
       </c>
       <c r="T93" s="15" t="inlineStr">
         <is>
-          <t>STACYC (62%)</t>
+          <t>Conventional (89%)</t>
         </is>
       </c>
       <c r="U93" s="17" t="inlineStr">
         <is>
-          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
+          <t>Conventional 89%; Renewable 11%</t>
         </is>
       </c>
       <c r="V93" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W93" s="17" t="inlineStr">
-        <is>
-          <t>US 74%; Non Us 24%; AT 2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W93" s="17" t="n"/>
       <c r="X93" s="15" t="inlineStr">
         <is>
-          <t>Electric Motorcycle +333%</t>
+          <t>Conventional +186%</t>
         </is>
       </c>
       <c r="Y93" s="22" t="inlineStr">
@@ -59405,12 +59399,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>LVWR</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd</t>
+          <t>LiveWire Group Inc. Common Sto</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -59420,11 +59414,11 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>3207403776</v>
+        <v>234170208</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
@@ -59436,20 +59430,24 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I94" s="20" t="n">
-        <v>9.698138</v>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0.57766795</v>
+        <v>19.655172</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>2.931813323583181</v>
+        <v>7.484824</v>
       </c>
       <c r="L94" s="21" t="n">
-        <v>10.10162806517815</v>
-      </c>
-      <c r="M94" s="21" t="n">
-        <v>1.91</v>
+        <v>-21.59336790483196</v>
+      </c>
+      <c r="M94" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N94" s="22" t="inlineStr">
         <is>
@@ -59457,7 +59455,7 @@
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>0</v>
+        <v>-207.6711628204309</v>
       </c>
       <c r="P94" s="22" t="inlineStr">
         <is>
@@ -59465,48 +59463,48 @@
         </is>
       </c>
       <c r="Q94" s="21" t="n">
-        <v>-4.7</v>
+        <v>-76.64</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>0.9375650364203956</v>
+        <v>0.4547555777310531</v>
       </c>
       <c r="T94" s="15" t="inlineStr">
         <is>
-          <t>Insurance (97%)</t>
+          <t>STACYC (62%)</t>
         </is>
       </c>
       <c r="U94" s="17" t="inlineStr">
         <is>
-          <t>Insurance 97%; Asset Management 3%</t>
+          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
         </is>
       </c>
       <c r="V94" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W94" s="17" t="inlineStr">
         <is>
-          <t>US 77%; BM 18%; GB 5%</t>
+          <t>US 74%; Non Us 24%; AT 2%</t>
         </is>
       </c>
       <c r="X94" s="15" t="inlineStr">
         <is>
-          <t>Asset Management +190%</t>
-        </is>
-      </c>
-      <c r="Y94" s="21" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="Z94" s="20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA94" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Electric Motorcycle +333%</t>
+        </is>
+      </c>
+      <c r="Y94" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z94" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA94" s="24" t="inlineStr"/>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="13" t="n">
@@ -59514,12 +59512,12 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>KTB</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Kontoor Brands, Inc.</t>
+          <t>Assured Guaranty Ltd</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
@@ -59529,87 +59527,93 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>3641024256</v>
+        <v>3207403776</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H95" s="20" t="n">
-        <v>11.55529127502649</v>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I95" s="20" t="n">
-        <v>13.48583</v>
+        <v>9.698138</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>5.8861995</v>
+        <v>0.57766795</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>1.0601529</v>
+        <v>2.931813323583181</v>
       </c>
       <c r="L95" s="21" t="n">
-        <v>10.52193541631924</v>
+        <v>10.10162806517815</v>
       </c>
       <c r="M95" s="21" t="n">
-        <v>2.91957418972506</v>
-      </c>
-      <c r="N95" s="21" t="n">
-        <v>17.92240674479327</v>
+        <v>1.91</v>
+      </c>
+      <c r="N95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O95" s="21" t="n">
-        <v>13.30013869457824</v>
-      </c>
-      <c r="P95" s="20" t="n">
-        <v>2.601238735236491</v>
+        <v>0</v>
+      </c>
+      <c r="P95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q95" s="21" t="n">
-        <v>-7.049999999999999</v>
+        <v>-4.7</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S95" s="20" t="n">
-        <v>0.4547588013008751</v>
+        <v>0.9375650364203956</v>
       </c>
       <c r="T95" s="15" t="inlineStr">
         <is>
-          <t>Wrangler (61%)</t>
+          <t>Insurance (97%)</t>
         </is>
       </c>
       <c r="U95" s="17" t="inlineStr">
         <is>
-          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+          <t>Insurance 97%; Asset Management 3%</t>
         </is>
       </c>
       <c r="V95" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W95" s="17" t="inlineStr">
         <is>
-          <t>US 73%; Non Us 27%</t>
+          <t>US 77%; BM 18%; GB 5%</t>
         </is>
       </c>
       <c r="X95" s="15" t="inlineStr">
         <is>
-          <t>Helly Hansen +300%</t>
-        </is>
-      </c>
-      <c r="Y95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA95" s="24" t="inlineStr"/>
+          <t>Asset Management +190%</t>
+        </is>
+      </c>
+      <c r="Y95" s="21" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="Z95" s="20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA95" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -59617,12 +59621,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>PED</t>
+          <t>KTB</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>PEDEVCO Corp.</t>
+          <t>Kontoor Brands, Inc.</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -59632,11 +59636,11 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F96" s="18" t="n">
-        <v>197253472</v>
+        <v>3641024256</v>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
@@ -59644,62 +59648,62 @@
         </is>
       </c>
       <c r="H96" s="20" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I96" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>11.55529127502649</v>
+      </c>
+      <c r="I96" s="20" t="n">
+        <v>13.48583</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0.9859154999999999</v>
+        <v>5.8861995</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1.6949378</v>
+        <v>1.0601529</v>
       </c>
       <c r="L96" s="21" t="n">
-        <v>16.30471233572627</v>
-      </c>
-      <c r="M96" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.52193541631924</v>
+      </c>
+      <c r="M96" s="21" t="n">
+        <v>2.91957418972506</v>
       </c>
       <c r="N96" s="21" t="n">
-        <v>2.16353455637511</v>
+        <v>17.92240674479327</v>
       </c>
       <c r="O96" s="21" t="n">
-        <v>49.94500678822457</v>
+        <v>13.30013869457824</v>
       </c>
       <c r="P96" s="20" t="n">
-        <v>1.332008602150538</v>
+        <v>2.601238735236491</v>
       </c>
       <c r="Q96" s="21" t="n">
-        <v>18.91</v>
+        <v>-7.049999999999999</v>
       </c>
       <c r="R96" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S96" s="20" t="n">
-        <v>0.7805028355388554</v>
+        <v>0.4547588013008751</v>
       </c>
       <c r="T96" s="15" t="inlineStr">
         <is>
-          <t>Oil Sales (88%)</t>
+          <t>Wrangler (61%)</t>
         </is>
       </c>
       <c r="U96" s="17" t="inlineStr">
         <is>
-          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
+          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
         </is>
       </c>
       <c r="V96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W96" s="17" t="inlineStr">
+        <is>
+          <t>US 73%; Non Us 27%</t>
+        </is>
+      </c>
       <c r="X96" s="15" t="inlineStr">
         <is>
-          <t>Natural Gas Liquids  +465%</t>
+          <t>Helly Hansen +300%</t>
         </is>
       </c>
       <c r="Y96" s="22" t="inlineStr">
@@ -59720,12 +59724,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>PED</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>PEDEVCO Corp.</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
@@ -59735,11 +59739,11 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F97" s="18" t="n">
-        <v>1101452017664</v>
+        <v>197253472</v>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
@@ -59747,75 +59751,75 @@
         </is>
       </c>
       <c r="H97" s="20" t="n">
-        <v>15.852</v>
-      </c>
-      <c r="I97" s="20" t="n">
-        <v>22.024843</v>
+        <v>4.59</v>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J97" s="20" t="n">
-        <v>10.93157</v>
+        <v>0.9859154999999999</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>12.20121</v>
+        <v>1.6949378</v>
       </c>
       <c r="L97" s="21" t="n">
-        <v>2.27953325914988</v>
-      </c>
-      <c r="M97" s="21" t="n">
-        <v>0.05</v>
+        <v>16.30471233572627</v>
+      </c>
+      <c r="M97" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N97" s="21" t="n">
-        <v>38.68963277836816</v>
+        <v>2.16353455637511</v>
       </c>
       <c r="O97" s="21" t="n">
-        <v>63.47412363053029</v>
+        <v>49.94500678822457</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>-0.1351809304997128</v>
+        <v>1.332008602150538</v>
       </c>
       <c r="Q97" s="21" t="n">
-        <v>354.75</v>
+        <v>18.91</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S97" s="20" t="n">
-        <v>0.2853460159862896</v>
+        <v>0.7805028355388554</v>
       </c>
       <c r="T97" s="15" t="inlineStr">
         <is>
-          <t>CMBU (36%)</t>
+          <t>Oil Sales (88%)</t>
         </is>
       </c>
       <c r="U97" s="17" t="inlineStr">
         <is>
-          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
+          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
         </is>
       </c>
       <c r="V97" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="W97" s="17" t="inlineStr">
-        <is>
-          <t>US 65%; TW 15%; CN 7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W97" s="17" t="n"/>
       <c r="X97" s="15" t="inlineStr">
         <is>
-          <t>AEBU +311%</t>
-        </is>
-      </c>
-      <c r="Y97" s="21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z97" s="20" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="AA97" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Natural Gas Liquids  +465%</t>
+        </is>
+      </c>
+      <c r="Y97" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z97" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA97" s="24" t="inlineStr"/>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="13" t="n">
@@ -59823,12 +59827,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>EVC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Entravision Communications Cor</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -59838,11 +59842,11 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F98" s="18" t="n">
-        <v>794602240</v>
+        <v>1101452017664</v>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
@@ -59850,69 +59854,69 @@
         </is>
       </c>
       <c r="H98" s="20" t="n">
-        <v>27.53410143448773</v>
+        <v>15.852</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>190.0388450278689</v>
+        <v>22.024843</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>9.503311</v>
+        <v>10.93157</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>1.557472534580458</v>
+        <v>12.20121</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>8.44176513325125</v>
+        <v>2.27953325914988</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>2.57525386044693</v>
+        <v>0.05</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-26.42668897457025</v>
+        <v>38.68963277836816</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>6.53133066895079</v>
+        <v>63.47412363053029</v>
       </c>
       <c r="P98" s="20" t="n">
-        <v>2.821679370986135</v>
+        <v>-0.1351809304997128</v>
       </c>
       <c r="Q98" s="21" t="n">
-        <v>322.51</v>
+        <v>354.75</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S98" s="20" t="n">
-        <v>0.5221821576458947</v>
+        <v>0.2853460159862896</v>
       </c>
       <c r="T98" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technology (61%)</t>
+          <t>CMBU (36%)</t>
         </is>
       </c>
       <c r="U98" s="17" t="inlineStr">
         <is>
-          <t>Advertising Technology And Services 61%; Media 39%</t>
+          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
         </is>
       </c>
       <c r="V98" s="18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W98" s="17" t="inlineStr">
         <is>
-          <t>US 58%; Non Us 42%</t>
+          <t>US 65%; TW 15%; CN 7%</t>
         </is>
       </c>
       <c r="X98" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technolo +230%</t>
+          <t>AEBU +311%</t>
         </is>
       </c>
       <c r="Y98" s="21" t="n">
-        <v>6.79</v>
+        <v>2.39</v>
       </c>
       <c r="Z98" s="20" t="n">
-        <v>2.2707</v>
+        <v>0.263</v>
       </c>
       <c r="AA98" s="24" t="inlineStr">
         <is>
@@ -59926,12 +59930,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>EVC</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Compass, Inc.</t>
+          <t>Entravision Communications Cor</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
@@ -59941,11 +59945,11 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F99" s="18" t="n">
-        <v>8067944960</v>
+        <v>794602240</v>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
@@ -59953,75 +59957,75 @@
         </is>
       </c>
       <c r="H99" s="20" t="n">
-        <v>120.5991376271186</v>
+        <v>27.53410143448773</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>119.5251105185185</v>
+        <v>190.0388450278689</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>2.6573958</v>
+        <v>9.503311</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>1.012822938060207</v>
+        <v>1.557472534580458</v>
       </c>
       <c r="L99" s="21" t="n">
-        <v>1.5004325303195</v>
-      </c>
-      <c r="M99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.44176513325125</v>
+      </c>
+      <c r="M99" s="21" t="n">
+        <v>2.57525386044693</v>
       </c>
       <c r="N99" s="21" t="n">
-        <v>-6.802410518626729</v>
+        <v>-26.42668897457025</v>
       </c>
       <c r="O99" s="21" t="n">
-        <v>1.1850661578247</v>
-      </c>
-      <c r="P99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.53133066895079</v>
+      </c>
+      <c r="P99" s="20" t="n">
+        <v>2.821679370986135</v>
       </c>
       <c r="Q99" s="21" t="n">
-        <v>44.23</v>
+        <v>322.51</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S99" s="20" t="n">
-        <v>0.8491346718272323</v>
+        <v>0.5221821576458947</v>
       </c>
       <c r="T99" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (92%)</t>
+          <t>Advertising Technology (61%)</t>
         </is>
       </c>
       <c r="U99" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
+          <t>Advertising Technology And Services 61%; Media 39%</t>
         </is>
       </c>
       <c r="V99" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W99" s="17" t="inlineStr">
+        <is>
+          <t>US 58%; Non Us 42%</t>
+        </is>
+      </c>
       <c r="X99" s="15" t="inlineStr">
         <is>
-          <t>Brokerage +97%</t>
-        </is>
-      </c>
-      <c r="Y99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z99" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA99" s="24" t="inlineStr"/>
+          <t>Advertising Technolo +230%</t>
+        </is>
+      </c>
+      <c r="Y99" s="21" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="Z99" s="20" t="n">
+        <v>2.2707</v>
+      </c>
+      <c r="AA99" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="13" t="n">
@@ -60029,12 +60033,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Compass, Inc.</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -60044,11 +60048,11 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F100" s="18" t="n">
-        <v>419900817408</v>
+        <v>8067944960</v>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
@@ -60056,49 +60060,53 @@
         </is>
       </c>
       <c r="H100" s="20" t="n">
-        <v>8.913</v>
+        <v>120.5991376271186</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>20.62235</v>
+        <v>119.5251105185185</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>2.2113636</v>
+        <v>2.6573958</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>2.0054102</v>
+        <v>1.012822938060207</v>
       </c>
       <c r="L100" s="21" t="n">
-        <v>6.60132683312082</v>
-      </c>
-      <c r="M100" s="21" t="n">
-        <v>4.16</v>
+        <v>1.5004325303195</v>
+      </c>
+      <c r="M100" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N100" s="21" t="n">
-        <v>8.69285484505129</v>
+        <v>-6.802410518626729</v>
       </c>
       <c r="O100" s="21" t="n">
-        <v>22.36304851872374</v>
-      </c>
-      <c r="P100" s="20" t="n">
-        <v>0.9647582391147462</v>
+        <v>1.1850661578247</v>
+      </c>
+      <c r="P100" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q100" s="21" t="n">
-        <v>37.47</v>
+        <v>44.23</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S100" s="20" t="n">
-        <v>0.9067367242961308</v>
+        <v>0.8491346718272323</v>
       </c>
       <c r="T100" s="15" t="inlineStr">
         <is>
-          <t>Upstream (95%)</t>
+          <t>Brokerage (92%)</t>
         </is>
       </c>
       <c r="U100" s="17" t="inlineStr">
         <is>
-          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
+          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
         </is>
       </c>
       <c r="V100" s="18" t="n">
@@ -60107,7 +60115,7 @@
       <c r="W100" s="17" t="n"/>
       <c r="X100" s="15" t="inlineStr">
         <is>
-          <t>Upstream +298%</t>
+          <t>Brokerage +97%</t>
         </is>
       </c>
       <c r="Y100" s="22" t="inlineStr">
@@ -60128,12 +60136,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
@@ -60143,11 +60151,11 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F101" s="18" t="n">
-        <v>73726443520</v>
+        <v>419900817408</v>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
@@ -60155,69 +60163,69 @@
         </is>
       </c>
       <c r="H101" s="20" t="n">
-        <v>15.61168969542968</v>
+        <v>8.913</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>16.501429</v>
+        <v>20.62235</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>4.1224737</v>
+        <v>2.2113636</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>1.7188857</v>
+        <v>2.0054102</v>
       </c>
       <c r="L101" s="21" t="n">
-        <v>4.9836238568399</v>
+        <v>6.60132683312082</v>
       </c>
       <c r="M101" s="21" t="n">
-        <v>1.505494379293</v>
+        <v>4.16</v>
       </c>
       <c r="N101" s="21" t="n">
-        <v>14.00609392594555</v>
+        <v>8.69285484505129</v>
       </c>
       <c r="O101" s="21" t="n">
-        <v>13.37597658555007</v>
+        <v>22.36304851872374</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>2.307923063349215</v>
+        <v>0.9647582391147462</v>
       </c>
       <c r="Q101" s="21" t="n">
-        <v>-10.3</v>
+        <v>37.47</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S101" s="20" t="n">
-        <v>0.4182092579820682</v>
+        <v>0.9067367242961308</v>
       </c>
       <c r="T101" s="15" t="inlineStr">
         <is>
-          <t>Mission Systems (58%)</t>
+          <t>Upstream (95%)</t>
         </is>
       </c>
       <c r="U101" s="17" t="inlineStr">
         <is>
-          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
+          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
         </is>
       </c>
       <c r="V101" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W101" s="17" t="inlineStr">
-        <is>
-          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W101" s="17" t="n"/>
       <c r="X101" s="15" t="inlineStr">
         <is>
-          <t>Aeronautics Systems +130%</t>
-        </is>
-      </c>
-      <c r="Y101" s="21" t="n">
-        <v>-17.49</v>
-      </c>
-      <c r="Z101" s="20" t="n">
-        <v>-1.1435</v>
+          <t>Upstream +298%</t>
+        </is>
+      </c>
+      <c r="Y101" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z101" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA101" s="24" t="inlineStr"/>
     </row>
@@ -60227,12 +60235,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>JBI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Janus International Group, Inc</t>
+          <t>Northrop Grumman Corp.</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -60246,7 +60254,7 @@
         </is>
       </c>
       <c r="F102" s="18" t="n">
-        <v>626240320</v>
+        <v>73726443520</v>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
@@ -60254,75 +60262,69 @@
         </is>
       </c>
       <c r="H102" s="20" t="n">
-        <v>7.682</v>
+        <v>15.61168969542968</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>19.125002</v>
+        <v>16.501429</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>1.0949428</v>
+        <v>4.1224737</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>0.6944337</v>
+        <v>1.7188857</v>
       </c>
       <c r="L102" s="21" t="n">
-        <v>11.5960907053962</v>
-      </c>
-      <c r="M102" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.9836238568399</v>
+      </c>
+      <c r="M102" s="21" t="n">
+        <v>1.505494379293</v>
       </c>
       <c r="N102" s="21" t="n">
-        <v>10.43425814234016</v>
+        <v>14.00609392594555</v>
       </c>
       <c r="O102" s="21" t="n">
-        <v>16.54553713377242</v>
+        <v>13.37597658555007</v>
       </c>
       <c r="P102" s="20" t="n">
-        <v>2.983527796842828</v>
+        <v>2.307923063349215</v>
       </c>
       <c r="Q102" s="21" t="n">
-        <v>-46.98</v>
+        <v>-10.3</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S102" s="20" t="n">
-        <v>0.6354742392804635</v>
+        <v>0.4182092579820682</v>
       </c>
       <c r="T102" s="15" t="inlineStr">
         <is>
-          <t>Janus North America (76%)</t>
+          <t>Mission Systems (58%)</t>
         </is>
       </c>
       <c r="U102" s="17" t="inlineStr">
         <is>
-          <t>Janus North America 76%; Janus International 24%</t>
+          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
         </is>
       </c>
       <c r="V102" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W102" s="17" t="inlineStr">
         <is>
-          <t>US 88%; Non Us 12%</t>
+          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
         </is>
       </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
-          <t>Janus International +300%</t>
-        </is>
-      </c>
-      <c r="Y102" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z102" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Aeronautics Systems +130%</t>
+        </is>
+      </c>
+      <c r="Y102" s="21" t="n">
+        <v>-17.49</v>
+      </c>
+      <c r="Z102" s="20" t="n">
+        <v>-1.1435</v>
       </c>
       <c r="AA102" s="24" t="inlineStr"/>
     </row>
@@ -60332,12 +60334,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>JBI</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Flotek Industries, Inc.</t>
+          <t>Janus International Group, Inc</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
@@ -60347,11 +60349,11 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F103" s="18" t="n">
-        <v>989904320</v>
+        <v>626240320</v>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
@@ -60359,19 +60361,19 @@
         </is>
       </c>
       <c r="H103" s="20" t="n">
-        <v>25.626</v>
+        <v>7.682</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>27.059406</v>
+        <v>19.125002</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>7.6511755</v>
+        <v>1.0949428</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>3.3788822</v>
+        <v>0.6944337</v>
       </c>
       <c r="L103" s="21" t="n">
-        <v>-0.34082822017504</v>
+        <v>11.5960907053962</v>
       </c>
       <c r="M103" s="22" t="inlineStr">
         <is>
@@ -60379,59 +60381,57 @@
         </is>
       </c>
       <c r="N103" s="21" t="n">
-        <v>16.13992919089226</v>
+        <v>10.43425814234016</v>
       </c>
       <c r="O103" s="21" t="n">
-        <v>17.18227107585707</v>
+        <v>16.54553713377242</v>
       </c>
       <c r="P103" s="20" t="n">
-        <v>0.8771800721171535</v>
+        <v>2.983527796842828</v>
       </c>
       <c r="Q103" s="21" t="n">
-        <v>35.99</v>
+        <v>-46.98</v>
       </c>
       <c r="R103" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S103" s="20" t="n">
-        <v>0.7993939775957156</v>
+        <v>0.6354742392804635</v>
       </c>
       <c r="T103" s="15" t="inlineStr">
         <is>
-          <t>Chemistry Technologies (89%)</t>
+          <t>Janus North America (76%)</t>
         </is>
       </c>
       <c r="U103" s="17" t="inlineStr">
         <is>
-          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
+          <t>Janus North America 76%; Janus International 24%</t>
         </is>
       </c>
       <c r="V103" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W103" s="17" t="inlineStr">
         <is>
-          <t>US 95%; AE 4%; Non Us 1%</t>
+          <t>US 88%; Non Us 12%</t>
         </is>
       </c>
       <c r="X103" s="15" t="inlineStr">
         <is>
-          <t>Data Analytics +115%</t>
-        </is>
-      </c>
-      <c r="Y103" s="21" t="n">
-        <v>162.68</v>
+          <t>Janus International +300%</t>
+        </is>
+      </c>
+      <c r="Y103" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Z103" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="AA103" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA103" s="24" t="inlineStr"/>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="13" t="n">
@@ -60439,12 +60439,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Royal Gold, Inc.</t>
+          <t>Flotek Industries, Inc.</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -60454,11 +60454,11 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F104" s="18" t="n">
-        <v>21375143936</v>
+        <v>989904320</v>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
@@ -60466,75 +60466,79 @@
         </is>
       </c>
       <c r="H104" s="20" t="n">
-        <v>17.093</v>
+        <v>25.626</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>27.90708</v>
+        <v>27.059406</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>2.8154993</v>
+        <v>7.6511755</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>13.9189825</v>
+        <v>3.3788822</v>
       </c>
       <c r="L104" s="21" t="n">
-        <v>0.00273682367590865</v>
-      </c>
-      <c r="M104" s="21" t="n">
-        <v>0.91</v>
+        <v>-0.34082822017504</v>
+      </c>
+      <c r="M104" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N104" s="21" t="n">
-        <v>10.262897771322</v>
+        <v>16.13992919089226</v>
       </c>
       <c r="O104" s="21" t="n">
-        <v>79.09251477040698</v>
+        <v>17.18227107585707</v>
       </c>
       <c r="P104" s="20" t="n">
-        <v>0.3499720252373015</v>
+        <v>0.8771800721171535</v>
       </c>
       <c r="Q104" s="21" t="n">
-        <v>50.91</v>
+        <v>35.99</v>
       </c>
       <c r="R104" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S104" s="20" t="n">
-        <v>0.5688010724435794</v>
+        <v>0.7993939775957156</v>
       </c>
       <c r="T104" s="15" t="inlineStr">
         <is>
-          <t>Royalty Interest (69%)</t>
+          <t>Chemistry Technologies (89%)</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
         <is>
-          <t>Royalty Interest 69%; Stream Interest 31%</t>
+          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
         </is>
       </c>
       <c r="V104" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W104" s="17" t="inlineStr">
         <is>
-          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
+          <t>US 95%; AE 4%; Non Us 1%</t>
         </is>
       </c>
       <c r="X104" s="15" t="inlineStr">
         <is>
-          <t>Stream Interest +133%</t>
-        </is>
-      </c>
-      <c r="Y104" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Data Analytics +115%</t>
+        </is>
+      </c>
+      <c r="Y104" s="21" t="n">
+        <v>162.68</v>
       </c>
       <c r="Z104" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="AA104" s="24" t="inlineStr"/>
+      <c r="AA104" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="13" t="n">
@@ -60542,12 +60546,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Riot Blockchain, Inc.</t>
+          <t>Royal Gold, Inc.</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
@@ -60557,76 +60561,74 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F105" s="18" t="n">
-        <v>8056809472</v>
+        <v>21375143936</v>
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H105" s="20" t="n">
+        <v>17.093</v>
+      </c>
+      <c r="I105" s="20" t="n">
+        <v>27.90708</v>
       </c>
       <c r="J105" s="20" t="n">
-        <v>3.7017238</v>
+        <v>2.8154993</v>
       </c>
       <c r="K105" s="20" t="n">
-        <v>11.944614</v>
+        <v>13.9189825</v>
       </c>
       <c r="L105" s="21" t="n">
-        <v>-6.33617127278794</v>
+        <v>0.00273682367590865</v>
       </c>
       <c r="M105" s="21" t="n">
-        <v>0.10325461151742</v>
+        <v>0.91</v>
       </c>
       <c r="N105" s="21" t="n">
-        <v>-14.43474531538664</v>
+        <v>10.262897771322</v>
       </c>
       <c r="O105" s="21" t="n">
-        <v>-137.6062161413327</v>
-      </c>
-      <c r="P105" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>79.09251477040698</v>
+      </c>
+      <c r="P105" s="20" t="n">
+        <v>0.3499720252373015</v>
       </c>
       <c r="Q105" s="21" t="n">
-        <v>10.21</v>
+        <v>50.91</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S105" s="20" t="n">
-        <v>0.4395096928547909</v>
+        <v>0.5688010724435794</v>
       </c>
       <c r="T105" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Royalty Interest (69%)</t>
         </is>
       </c>
       <c r="U105" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
+          <t>Royalty Interest 69%; Stream Interest 31%</t>
         </is>
       </c>
       <c r="V105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W105" s="17" t="inlineStr">
+        <is>
+          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
+        </is>
+      </c>
       <c r="X105" s="15" t="inlineStr">
         <is>
-          <t>Engineering +196%</t>
+          <t>Stream Interest +133%</t>
         </is>
       </c>
       <c r="Y105" s="22" t="inlineStr">
@@ -60639,11 +60641,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="AA105" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA105" s="24" t="inlineStr"/>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="13" t="n">
@@ -60651,12 +60649,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Riot Blockchain, Inc.</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
@@ -60670,79 +60668,89 @@
         </is>
       </c>
       <c r="F106" s="18" t="n">
-        <v>77146587136</v>
+        <v>8056809472</v>
       </c>
       <c r="G106" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H106" s="20" t="n">
-        <v>29.95255477105907</v>
-      </c>
-      <c r="I106" s="20" t="n">
-        <v>36.676632</v>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J106" s="20" t="n">
-        <v>28.873335</v>
+        <v>3.7017238</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>6.304371</v>
+        <v>11.944614</v>
       </c>
       <c r="L106" s="21" t="n">
-        <v>3.45600557054743</v>
+        <v>-6.33617127278794</v>
       </c>
       <c r="M106" s="21" t="n">
-        <v>1.11367051765181</v>
+        <v>0.10325461151742</v>
       </c>
       <c r="N106" s="21" t="n">
-        <v>24.18337569424833</v>
+        <v>-14.43474531538664</v>
       </c>
       <c r="O106" s="21" t="n">
-        <v>24.10684192787327</v>
-      </c>
-      <c r="P106" s="20" t="n">
-        <v>2.823837818944425</v>
+        <v>-137.6062161413327</v>
+      </c>
+      <c r="P106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q106" s="21" t="n">
-        <v>16.12</v>
+        <v>10.21</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S106" s="20" t="n">
-        <v>0.5307180948206589</v>
+        <v>0.4395096928547909</v>
       </c>
       <c r="T106" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems In (62%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U106" s="17" t="inlineStr">
         <is>
-          <t>Product And Systems Integration 62%; Services And Software 38%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
         </is>
       </c>
       <c r="V106" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="W106" s="17" t="inlineStr">
-        <is>
-          <t>North America 36%; US 34%; International 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W106" s="17" t="n"/>
       <c r="X106" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems  +176%</t>
-        </is>
-      </c>
-      <c r="Y106" s="21" t="n">
-        <v>-39.24</v>
-      </c>
-      <c r="Z106" s="20" t="n">
-        <v>-1.7092</v>
-      </c>
-      <c r="AA106" s="24" t="inlineStr"/>
+          <t>Engineering +196%</t>
+        </is>
+      </c>
+      <c r="Y106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z106" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA106" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="13" t="n">
@@ -60750,12 +60758,12 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Firy Inc. Class A Common Stock</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
@@ -60769,91 +60777,77 @@
         </is>
       </c>
       <c r="F107" s="18" t="n">
-        <v>163180000</v>
+        <v>77146587136</v>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H107" s="20" t="n">
+        <v>29.95255477105907</v>
+      </c>
+      <c r="I107" s="20" t="n">
+        <v>36.676632</v>
       </c>
       <c r="J107" s="20" t="n">
-        <v>1.931855850736373</v>
+        <v>28.873335</v>
       </c>
       <c r="K107" s="20" t="n">
-        <v>1.3889787</v>
+        <v>6.304371</v>
       </c>
       <c r="L107" s="21" t="n">
-        <v>-42.19957624057978</v>
-      </c>
-      <c r="M107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>3.45600557054743</v>
+      </c>
+      <c r="M107" s="21" t="n">
+        <v>1.11367051765181</v>
+      </c>
+      <c r="N107" s="21" t="n">
+        <v>24.18337569424833</v>
       </c>
       <c r="O107" s="21" t="n">
-        <v>-60.47052925589057</v>
-      </c>
-      <c r="P107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.10684192787327</v>
+      </c>
+      <c r="P107" s="20" t="n">
+        <v>2.823837818944425</v>
       </c>
       <c r="Q107" s="21" t="n">
-        <v>51.65</v>
+        <v>16.12</v>
       </c>
       <c r="R107" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S107" s="20" t="n">
-        <v>0.619776729861528</v>
+        <v>0.5307180948206589</v>
       </c>
       <c r="T107" s="15" t="inlineStr">
         <is>
-          <t>Skillz (74%)</t>
+          <t>Product And Systems In (62%)</t>
         </is>
       </c>
       <c r="U107" s="17" t="inlineStr">
         <is>
-          <t>Skillz 74%; RZR 26%</t>
+          <t>Product And Systems Integration 62%; Services And Software 38%</t>
         </is>
       </c>
       <c r="V107" s="18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W107" s="17" t="inlineStr">
         <is>
-          <t>US 76%; Non Us 6%; CY 4%</t>
+          <t>North America 36%; US 34%; International 14%</t>
         </is>
       </c>
       <c r="X107" s="15" t="inlineStr">
         <is>
-          <t>RZR +146%</t>
-        </is>
-      </c>
-      <c r="Y107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z107" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Product And Systems  +176%</t>
+        </is>
+      </c>
+      <c r="Y107" s="21" t="n">
+        <v>-39.24</v>
+      </c>
+      <c r="Z107" s="20" t="n">
+        <v>-1.7092</v>
       </c>
       <c r="AA107" s="24" t="inlineStr"/>
     </row>
@@ -60863,12 +60857,12 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Energy Transfer Lp</t>
+          <t>Firy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
@@ -60878,70 +60872,84 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F108" s="18" t="n">
-        <v>74203103232</v>
+        <v>163180000</v>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H108" s="20" t="n">
-        <v>9.459</v>
-      </c>
-      <c r="I108" s="20" t="n">
-        <v>14.760273</v>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J108" s="20" t="n">
-        <v>1.491909508655528</v>
+        <v>1.931855850736373</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>0.69103926</v>
+        <v>1.3889787</v>
       </c>
       <c r="L108" s="21" t="n">
-        <v>7.04975512768092</v>
-      </c>
-      <c r="M108" s="21" t="n">
-        <v>6.959999999999999</v>
-      </c>
-      <c r="N108" s="21" t="n">
-        <v>8.4099490357427</v>
+        <v>-42.19957624057978</v>
+      </c>
+      <c r="M108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O108" s="21" t="n">
-        <v>17.85263732142248</v>
-      </c>
-      <c r="P108" s="20" t="n">
-        <v>4.353514132925898</v>
+        <v>-60.47052925589057</v>
+      </c>
+      <c r="P108" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q108" s="21" t="n">
-        <v>37.32</v>
+        <v>51.65</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S108" s="20" t="n">
-        <v>0.2291888064107961</v>
+        <v>0.619776729861528</v>
       </c>
       <c r="T108" s="15" t="inlineStr">
         <is>
-          <t>Crudeoiltransportation (27%)</t>
+          <t>Skillz (74%)</t>
         </is>
       </c>
       <c r="U108" s="17" t="inlineStr">
         <is>
-          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
+          <t>Skillz 74%; RZR 26%</t>
         </is>
       </c>
       <c r="V108" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W108" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; Non Us 6%; CY 4%</t>
+        </is>
+      </c>
       <c r="X108" s="15" t="inlineStr">
         <is>
-          <t>Investment In Sunoco +165%</t>
+          <t>RZR +146%</t>
         </is>
       </c>
       <c r="Y108" s="22" t="inlineStr">
@@ -60962,12 +60970,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Jd.Com, Inc.</t>
+          <t>Energy Transfer Lp</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
@@ -60977,11 +60985,11 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F109" s="18" t="n">
-        <v>36544528384</v>
+        <v>74203103232</v>
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
@@ -60989,49 +60997,49 @@
         </is>
       </c>
       <c r="H109" s="20" t="n">
-        <v>11.09408477609406</v>
+        <v>9.459</v>
       </c>
       <c r="I109" s="20" t="n">
-        <v>16.7176140061608</v>
+        <v>14.760273</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>7.683095555258829</v>
+        <v>1.491909508655528</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>0.1882403337093706</v>
+        <v>0.69103926</v>
       </c>
       <c r="L109" s="21" t="n">
-        <v>14.93799506720002</v>
+        <v>7.04975512768092</v>
       </c>
       <c r="M109" s="21" t="n">
-        <v>3.94</v>
+        <v>6.959999999999999</v>
       </c>
       <c r="N109" s="21" t="n">
-        <v>2.81257184190512</v>
+        <v>8.4099490357427</v>
       </c>
       <c r="O109" s="21" t="n">
-        <v>0.95674610170034</v>
+        <v>17.85263732142248</v>
       </c>
       <c r="P109" s="20" t="n">
-        <v>-9.862180948218128</v>
+        <v>4.353514132925898</v>
       </c>
       <c r="Q109" s="21" t="n">
-        <v>-11.42</v>
+        <v>37.32</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S109" s="20" t="n">
-        <v>0.8099111106081265</v>
+        <v>0.2291888064107961</v>
       </c>
       <c r="T109" s="15" t="inlineStr">
         <is>
-          <t>Jd Retail (90%)</t>
+          <t>Crudeoiltransportation (27%)</t>
         </is>
       </c>
       <c r="U109" s="17" t="inlineStr">
         <is>
-          <t>Jd Retail 90%; Jd Logistics 6%; New Business 4%</t>
+          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
         </is>
       </c>
       <c r="V109" s="18" t="n">
@@ -61040,11 +61048,13 @@
       <c r="W109" s="17" t="n"/>
       <c r="X109" s="15" t="inlineStr">
         <is>
-          <t>New Business +157%</t>
-        </is>
-      </c>
-      <c r="Y109" s="21" t="n">
-        <v>-79.69000000000001</v>
+          <t>Investment In Sunoco +165%</t>
+        </is>
+      </c>
+      <c r="Y109" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Z109" s="22" t="inlineStr">
         <is>
@@ -61059,12 +61069,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>BWX Technologies, Inc.</t>
+          <t>Jd.Com, Inc.</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
@@ -61074,11 +61084,11 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F110" s="18" t="n">
-        <v>13754292224</v>
+        <v>36544528384</v>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
@@ -61086,75 +61096,69 @@
         </is>
       </c>
       <c r="H110" s="20" t="n">
-        <v>31.828</v>
+        <v>11.09408477609406</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>38.891193</v>
+        <v>16.7176140061608</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>10.3069</v>
+        <v>7.683095555258829</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>3.9141748</v>
+        <v>0.1882403337093706</v>
       </c>
       <c r="L110" s="21" t="n">
-        <v>2.19383891609831</v>
+        <v>14.93799506720002</v>
       </c>
       <c r="M110" s="21" t="n">
-        <v>0.5030143835716</v>
+        <v>3.94</v>
       </c>
       <c r="N110" s="21" t="n">
-        <v>15.04279234978169</v>
+        <v>2.81257184190512</v>
       </c>
       <c r="O110" s="21" t="n">
-        <v>16.8479651603609</v>
+        <v>0.95674610170034</v>
       </c>
       <c r="P110" s="20" t="n">
-        <v>2.646714786974468</v>
+        <v>-9.862180948218128</v>
       </c>
       <c r="Q110" s="21" t="n">
-        <v>-25.8</v>
+        <v>-11.42</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S110" s="20" t="n">
-        <v>0.6174267863088643</v>
+        <v>0.8099111106081265</v>
       </c>
       <c r="T110" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operations (74%)</t>
+          <t>Jd Retail (90%)</t>
         </is>
       </c>
       <c r="U110" s="17" t="inlineStr">
         <is>
-          <t>Commercial Operations 74%; Government Operations 26%</t>
+          <t>Jd Retail 90%; Jd Logistics 6%; New Business 4%</t>
         </is>
       </c>
       <c r="V110" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W110" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W110" s="17" t="n"/>
       <c r="X110" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operation +143%</t>
+          <t>New Business +157%</t>
         </is>
       </c>
       <c r="Y110" s="21" t="n">
-        <v>4.399999999999999</v>
-      </c>
-      <c r="Z110" s="20" t="n">
-        <v>1.1084</v>
-      </c>
-      <c r="AA110" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-79.69000000000001</v>
+      </c>
+      <c r="Z110" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA110" s="24" t="inlineStr"/>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="13" t="n">
@@ -61162,12 +61166,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>LGN</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Legence Corp.</t>
+          <t>BWX Technologies, Inc.</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
@@ -61175,9 +61179,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E111" s="17" t="n"/>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="F111" s="18" t="n">
-        <v>9306742784</v>
+        <v>13754292224</v>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
@@ -61185,75 +61193,75 @@
         </is>
       </c>
       <c r="H111" s="20" t="n">
-        <v>35.22426766420546</v>
-      </c>
-      <c r="I111" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>31.828</v>
+      </c>
+      <c r="I111" s="20" t="n">
+        <v>38.891193</v>
       </c>
       <c r="J111" s="20" t="n">
-        <v>15.49927769737686</v>
+        <v>10.3069</v>
       </c>
       <c r="K111" s="20" t="n">
-        <v>3.30888056840225</v>
+        <v>3.9141748</v>
       </c>
       <c r="L111" s="21" t="n">
-        <v>3.41438849489116</v>
-      </c>
-      <c r="M111" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.19383891609831</v>
+      </c>
+      <c r="M111" s="21" t="n">
+        <v>0.5030143835716</v>
       </c>
       <c r="N111" s="21" t="n">
-        <v>3.69186301129894</v>
+        <v>15.04279234978169</v>
       </c>
       <c r="O111" s="21" t="n">
-        <v>5.44599126235131</v>
+        <v>16.8479651603609</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>6.20894155127728</v>
+        <v>2.646714786974468</v>
       </c>
       <c r="Q111" s="21" t="n">
-        <v>167.4754158395236</v>
+        <v>-25.8</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S111" s="20" t="n">
-        <v>0.2963256950273106</v>
+        <v>0.6174267863088643</v>
       </c>
       <c r="T111" s="15" t="inlineStr">
         <is>
-          <t>Installation Maintenan (36%)</t>
+          <t>Commercial Operations (74%)</t>
         </is>
       </c>
       <c r="U111" s="17" t="inlineStr">
         <is>
-          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
+          <t>Commercial Operations 74%; Government Operations 26%</t>
         </is>
       </c>
       <c r="V111" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W111" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
+        </is>
+      </c>
       <c r="X111" s="15" t="inlineStr">
         <is>
-          <t>Installation And Mai +162%</t>
-        </is>
-      </c>
-      <c r="Y111" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z111" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA111" s="24" t="inlineStr"/>
+          <t>Commercial Operation +143%</t>
+        </is>
+      </c>
+      <c r="Y111" s="21" t="n">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="Z111" s="20" t="n">
+        <v>1.1084</v>
+      </c>
+      <c r="AA111" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="13" t="n">
@@ -61261,12 +61269,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>LGN</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Gen Digital Inc. Common Stock</t>
+          <t>Legence Corp.</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
@@ -61274,13 +61282,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E112" s="17" t="inlineStr">
-        <is>
-          <t>Information Te</t>
-        </is>
-      </c>
+      <c r="E112" s="17" t="n"/>
       <c r="F112" s="18" t="n">
-        <v>18113243136</v>
+        <v>9306742784</v>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
@@ -61288,69 +61292,73 @@
         </is>
       </c>
       <c r="H112" s="20" t="n">
-        <v>10.614</v>
-      </c>
-      <c r="I112" s="20" t="n">
-        <v>17.695906</v>
+        <v>35.22426766420546</v>
+      </c>
+      <c r="I112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J112" s="20" t="n">
-        <v>6.8245378</v>
+        <v>15.49927769737686</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>3.566301</v>
+        <v>3.30888056840225</v>
       </c>
       <c r="L112" s="21" t="n">
-        <v>10.13133216482446</v>
-      </c>
-      <c r="M112" s="21" t="n">
-        <v>2.07549286633304</v>
+        <v>3.41438849489116</v>
+      </c>
+      <c r="M112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N112" s="21" t="n">
-        <v>20.39245863793767</v>
+        <v>3.69186301129894</v>
       </c>
       <c r="O112" s="21" t="n">
-        <v>51.45999999999999</v>
+        <v>5.44599126235131</v>
       </c>
       <c r="P112" s="20" t="n">
-        <v>3.02914885347843</v>
+        <v>6.20894155127728</v>
       </c>
       <c r="Q112" s="21" t="n">
-        <v>18.59</v>
+        <v>167.4754158395236</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S112" s="20" t="n">
-        <v>0.5563136799999999</v>
+        <v>0.2963256950273106</v>
       </c>
       <c r="T112" s="15" t="inlineStr">
         <is>
-          <t>Cyber Safety Platform (67%)</t>
+          <t>Installation Maintenan (36%)</t>
         </is>
       </c>
       <c r="U112" s="17" t="inlineStr">
         <is>
-          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
         </is>
       </c>
       <c r="V112" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W112" s="17" t="inlineStr">
-        <is>
-          <t>Americas 43%; US 40%; EMEA 13%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W112" s="17" t="n"/>
       <c r="X112" s="15" t="inlineStr">
         <is>
-          <t>Trust Based Solution +119%</t>
-        </is>
-      </c>
-      <c r="Y112" s="21" t="n">
-        <v>-20.77</v>
-      </c>
-      <c r="Z112" s="20" t="n">
-        <v>-0.8912</v>
+          <t>Installation And Mai +162%</t>
+        </is>
+      </c>
+      <c r="Y112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z112" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA112" s="24" t="inlineStr"/>
     </row>
@@ -61360,12 +61368,12 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>L3Harris Technologies, Inc.</t>
+          <t>Gen Digital Inc. Common Stock</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
@@ -61375,11 +61383,11 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F113" s="18" t="n">
-        <v>45723136000</v>
+        <v>18113243136</v>
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
@@ -61387,75 +61395,71 @@
         </is>
       </c>
       <c r="H113" s="20" t="n">
-        <v>17.48068824615385</v>
+        <v>10.614</v>
       </c>
       <c r="I113" s="20" t="n">
-        <v>24.776993</v>
+        <v>17.695906</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>2.388963</v>
+        <v>6.8245378</v>
       </c>
       <c r="K113" s="20" t="n">
-        <v>1.167926026207566</v>
+        <v>3.566301</v>
       </c>
       <c r="L113" s="21" t="n">
-        <v>5.88004410889457</v>
+        <v>10.13133216482446</v>
       </c>
       <c r="M113" s="21" t="n">
-        <v>1.56571804266048</v>
+        <v>2.07549286633304</v>
       </c>
       <c r="N113" s="21" t="n">
-        <v>8.274248192518591</v>
+        <v>20.39245863793767</v>
       </c>
       <c r="O113" s="21" t="n">
-        <v>8.96574625150067</v>
+        <v>51.45999999999999</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>2.55014245014245</v>
+        <v>3.02914885347843</v>
       </c>
       <c r="Q113" s="21" t="n">
-        <v>-9.82</v>
+        <v>18.59</v>
       </c>
       <c r="R113" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S113" s="20" t="n">
+        <v>0.5563136799999999</v>
+      </c>
+      <c r="T113" s="15" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform (67%)</t>
+        </is>
+      </c>
+      <c r="U113" s="17" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+        </is>
+      </c>
+      <c r="V113" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S113" s="20" t="n">
-        <v>0.3315167177024359</v>
-      </c>
-      <c r="T113" s="15" t="inlineStr">
-        <is>
-          <t>Communication Systems (42%)</t>
-        </is>
-      </c>
-      <c r="U113" s="17" t="inlineStr">
-        <is>
-          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
-        </is>
-      </c>
-      <c r="V113" s="18" t="n">
-        <v>2</v>
-      </c>
       <c r="W113" s="17" t="inlineStr">
         <is>
-          <t>US 90%; Non Us 10%</t>
+          <t>Americas 43%; US 40%; EMEA 13%</t>
         </is>
       </c>
       <c r="X113" s="15" t="inlineStr">
         <is>
-          <t>Aerojet Rocketdyne +467%</t>
+          <t>Trust Based Solution +119%</t>
         </is>
       </c>
       <c r="Y113" s="21" t="n">
-        <v>258.65</v>
+        <v>-20.77</v>
       </c>
       <c r="Z113" s="20" t="n">
-        <v>0.8997000000000001</v>
-      </c>
-      <c r="AA113" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-0.8912</v>
+      </c>
+      <c r="AA113" s="24" t="inlineStr"/>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="13" t="n">
@@ -61463,12 +61467,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc.</t>
+          <t>L3Harris Technologies, Inc.</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
@@ -61478,85 +61482,87 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F114" s="18" t="n">
-        <v>2881904384</v>
+        <v>45723136000</v>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H114" s="20" t="n">
+        <v>17.48068824615385</v>
       </c>
       <c r="I114" s="20" t="n">
-        <v>3.9738305</v>
+        <v>24.776993</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>0.4399589</v>
+        <v>2.388963</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>0.4215159</v>
+        <v>1.167926026207566</v>
       </c>
       <c r="L114" s="21" t="n">
-        <v>-18.66821130454271</v>
-      </c>
-      <c r="M114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.88004410889457</v>
+      </c>
+      <c r="M114" s="21" t="n">
+        <v>1.56571804266048</v>
       </c>
       <c r="N114" s="21" t="n">
-        <v>0.007627959012433573</v>
+        <v>8.274248192518591</v>
       </c>
       <c r="O114" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>8.96574625150067</v>
+      </c>
+      <c r="P114" s="20" t="n">
+        <v>2.55014245014245</v>
       </c>
       <c r="Q114" s="21" t="n">
-        <v>-6.12</v>
+        <v>-9.82</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S114" s="20" t="n">
-        <v>0.4403975356846814</v>
+        <v>0.3315167177024359</v>
       </c>
       <c r="T114" s="15" t="inlineStr">
         <is>
-          <t>Annuities (60%)</t>
+          <t>Communication Systems (42%)</t>
         </is>
       </c>
       <c r="U114" s="17" t="inlineStr">
         <is>
-          <t>Annuities 60%; Runoff 21%; Life 19%</t>
+          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
         </is>
       </c>
       <c r="V114" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" s="17" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="W114" s="17" t="inlineStr">
+        <is>
+          <t>US 90%; Non Us 10%</t>
+        </is>
+      </c>
       <c r="X114" s="15" t="inlineStr">
         <is>
-          <t>Annuities +322%</t>
+          <t>Aerojet Rocketdyne +467%</t>
         </is>
       </c>
       <c r="Y114" s="21" t="n">
-        <v>-30.28</v>
+        <v>258.65</v>
       </c>
       <c r="Z114" s="20" t="n">
-        <v>-0.8806</v>
-      </c>
-      <c r="AA114" s="24" t="inlineStr"/>
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="AA114" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n">
@@ -61564,12 +61570,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>ONEOK, Inc.</t>
+          <t>Brighthouse Financial, Inc.</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -61577,59 +61583,69 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E115" s="17" t="n"/>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="F115" s="18" t="n">
-        <v>60906319872</v>
+        <v>2881904384</v>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H115" s="20" t="n">
-        <v>12.17</v>
+      <c r="H115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I115" s="20" t="n">
-        <v>16.687393</v>
+        <v>3.9738305</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>2.655344</v>
+        <v>0.4399589</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>1.5471808</v>
+        <v>0.4215159</v>
       </c>
       <c r="L115" s="21" t="n">
-        <v>4.830758993916</v>
-      </c>
-      <c r="M115" s="21" t="n">
-        <v>4.39066236170035</v>
+        <v>-18.66821130454271</v>
+      </c>
+      <c r="M115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N115" s="21" t="n">
-        <v>10.40228824506366</v>
+        <v>0.007627959012433573</v>
       </c>
       <c r="O115" s="21" t="n">
-        <v>22.48324054084763</v>
-      </c>
-      <c r="P115" s="20" t="n">
-        <v>4.229943145925458</v>
+        <v>0</v>
+      </c>
+      <c r="P115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q115" s="21" t="n">
-        <v>50.16</v>
+        <v>-6.12</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S115" s="20" t="n">
-        <v>0.4959061195541746</v>
+        <v>0.4403975356846814</v>
       </c>
       <c r="T115" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And C (66%)</t>
+          <t>Annuities (60%)</t>
         </is>
       </c>
       <c r="U115" s="17" t="inlineStr">
         <is>
-          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
+          <t>Annuities 60%; Runoff 21%; Life 19%</t>
         </is>
       </c>
       <c r="V115" s="18" t="n">
@@ -61638,18 +61654,14 @@
       <c r="W115" s="17" t="n"/>
       <c r="X115" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And +192%</t>
-        </is>
-      </c>
-      <c r="Y115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Annuities +322%</t>
+        </is>
+      </c>
+      <c r="Y115" s="21" t="n">
+        <v>-30.28</v>
+      </c>
+      <c r="Z115" s="20" t="n">
+        <v>-0.8806</v>
       </c>
       <c r="AA115" s="24" t="inlineStr"/>
     </row>
@@ -61659,12 +61671,12 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>HAPN</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Happen Inc. Common Stock</t>
+          <t>ONEOK, Inc.</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
@@ -61672,13 +61684,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E116" s="17" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="E116" s="17" t="n"/>
       <c r="F116" s="18" t="n">
-        <v>1938845312</v>
+        <v>60906319872</v>
       </c>
       <c r="G116" s="19" t="inlineStr">
         <is>
@@ -61686,57 +61694,49 @@
         </is>
       </c>
       <c r="H116" s="20" t="n">
-        <v>3.25</v>
+        <v>12.17</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>13.36898003182167</v>
+        <v>16.687393</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>1.2369312</v>
+        <v>2.655344</v>
       </c>
       <c r="K116" s="20" t="n">
-        <v>3.208765663633625</v>
-      </c>
-      <c r="L116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.5471808</v>
+      </c>
+      <c r="L116" s="21" t="n">
+        <v>4.830758993916</v>
+      </c>
+      <c r="M116" s="21" t="n">
+        <v>4.39066236170035</v>
+      </c>
+      <c r="N116" s="21" t="n">
+        <v>10.40228824506366</v>
       </c>
       <c r="O116" s="21" t="n">
-        <v>52.58608552315825</v>
-      </c>
-      <c r="P116" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.48324054084763</v>
+      </c>
+      <c r="P116" s="20" t="n">
+        <v>4.229943145925458</v>
       </c>
       <c r="Q116" s="21" t="n">
-        <v>2.07</v>
+        <v>50.16</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S116" s="20" t="n">
-        <v>0.5010363171603962</v>
+        <v>0.4959061195541746</v>
       </c>
       <c r="T116" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank (52%)</t>
+          <t>Refined Products And C (66%)</t>
         </is>
       </c>
       <c r="U116" s="17" t="inlineStr">
         <is>
-          <t>Happen Bank 52%; Happen Inc. 48%</t>
+          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
         </is>
       </c>
       <c r="V116" s="18" t="n">
@@ -61745,7 +61745,7 @@
       <c r="W116" s="17" t="n"/>
       <c r="X116" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank +124%</t>
+          <t>Refined Products And +192%</t>
         </is>
       </c>
       <c r="Y116" s="22" t="inlineStr">
@@ -61766,51 +61766,43 @@
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>VFS</t>
+          <t>HAPN</t>
         </is>
       </c>
       <c r="C117" s="15" t="inlineStr">
         <is>
-          <t>VinFast Auto Ltd. Ordinary Sha</t>
+          <t>Happen Inc. Common Stock</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F117" s="18" t="n">
-        <v>7509911040</v>
+        <v>1938845312</v>
       </c>
       <c r="G117" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H117" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I117" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J117" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K117" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H117" s="20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I117" s="20" t="n">
+        <v>13.36898003182167</v>
+      </c>
+      <c r="J117" s="20" t="n">
+        <v>1.2369312</v>
+      </c>
+      <c r="K117" s="20" t="n">
+        <v>3.208765663633625</v>
       </c>
       <c r="L117" s="22" t="inlineStr">
         <is>
@@ -61822,11 +61814,13 @@
           <t>–</t>
         </is>
       </c>
-      <c r="N117" s="21" t="n">
-        <v>78.31448357763071</v>
+      <c r="N117" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O117" s="21" t="n">
-        <v>-83.1176333196485</v>
+        <v>52.58608552315825</v>
       </c>
       <c r="P117" s="22" t="inlineStr">
         <is>
@@ -61834,35 +61828,31 @@
         </is>
       </c>
       <c r="Q117" s="21" t="n">
-        <v>-3.75</v>
+        <v>2.07</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S117" s="20" t="n">
-        <v>0.460552269511968</v>
+        <v>0.5010363171603962</v>
       </c>
       <c r="T117" s="15" t="inlineStr">
         <is>
-          <t>Car (48%)</t>
+          <t>Happen Bank (52%)</t>
         </is>
       </c>
       <c r="U117" s="17" t="inlineStr">
         <is>
-          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
+          <t>Happen Bank 52%; Happen Inc. 48%</t>
         </is>
       </c>
       <c r="V117" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W117" s="17" t="inlineStr">
-        <is>
-          <t>VN 89%; Asia Pacific 8%; US 2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W117" s="17" t="n"/>
       <c r="X117" s="15" t="inlineStr">
         <is>
-          <t>E Scooter +230%</t>
+          <t>Happen Bank +124%</t>
         </is>
       </c>
       <c r="Y117" s="22" t="inlineStr">

--- a/segment_detail_book.xlsx
+++ b/segment_detail_book.xlsx
@@ -56499,103 +56499,89 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>VFS</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>VinFast Auto Ltd. Ordinary Sha</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F66" s="18" t="n">
-        <v>7509911040</v>
+        <v>104030609408</v>
       </c>
       <c r="G66" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H66" s="20" t="n">
+        <v>12.211</v>
+      </c>
+      <c r="I66" s="20" t="n">
+        <v>14.801482</v>
+      </c>
+      <c r="J66" s="20" t="n">
+        <v>3.2861774</v>
+      </c>
+      <c r="K66" s="20" t="n">
+        <v>0.68366075</v>
+      </c>
+      <c r="L66" s="21" t="n">
+        <v>6.14626794593043</v>
+      </c>
+      <c r="M66" s="21" t="n">
+        <v>2.96</v>
       </c>
       <c r="N66" s="21" t="n">
-        <v>78.31448357763071</v>
+        <v>12.24307948200071</v>
       </c>
       <c r="O66" s="21" t="n">
-        <v>-83.1176333196485</v>
-      </c>
-      <c r="P66" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.84160433056228</v>
+      </c>
+      <c r="P66" s="20" t="n">
+        <v>1.675361394631018</v>
       </c>
       <c r="Q66" s="21" t="n">
-        <v>-3.75</v>
+        <v>92.92</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S66" s="20" t="n">
-        <v>0.460552269511968</v>
+        <v>0.3806408342658987</v>
       </c>
       <c r="T66" s="15" t="inlineStr">
         <is>
-          <t>Car (48%)</t>
+          <t>Marketing Speciality (46%)</t>
         </is>
       </c>
       <c r="U66" s="17" t="inlineStr">
         <is>
-          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
+          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
         </is>
       </c>
       <c r="V66" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W66" s="17" t="inlineStr">
         <is>
-          <t>VN 89%; Asia Pacific 8%; US 2%</t>
+          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
         </is>
       </c>
       <c r="X66" s="15" t="inlineStr">
         <is>
-          <t>E Scooter +230%</t>
+          <t>Refining +92%</t>
         </is>
       </c>
       <c r="Y66" s="22" t="inlineStr">
@@ -56616,12 +56602,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Amphenol Corp /De/</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -56631,11 +56617,11 @@
       </c>
       <c r="E67" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F67" s="18" t="n">
-        <v>104030609408</v>
+        <v>206943928320</v>
       </c>
       <c r="G67" s="19" t="inlineStr">
         <is>
@@ -56643,73 +56629,69 @@
         </is>
       </c>
       <c r="H67" s="20" t="n">
-        <v>12.211</v>
+        <v>29.62302222645686</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>14.801482</v>
+        <v>41.96</v>
       </c>
       <c r="J67" s="20" t="n">
-        <v>3.2861774</v>
+        <v>13.354551</v>
       </c>
       <c r="K67" s="20" t="n">
-        <v>0.68366075</v>
+        <v>7.1331444</v>
       </c>
       <c r="L67" s="21" t="n">
-        <v>6.14626794593043</v>
+        <v>2.30913485895705</v>
       </c>
       <c r="M67" s="21" t="n">
-        <v>2.96</v>
+        <v>0.55827491517045</v>
       </c>
       <c r="N67" s="21" t="n">
-        <v>12.24307948200071</v>
+        <v>45.67278672993024</v>
       </c>
       <c r="O67" s="21" t="n">
-        <v>6.84160433056228</v>
+        <v>29.39923710032213</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>1.675361394631018</v>
+        <v>2.057377830710813</v>
       </c>
       <c r="Q67" s="21" t="n">
-        <v>92.92</v>
+        <v>19.46</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67" s="20" t="n">
-        <v>0.3806408342658987</v>
+        <v>0.4256894967493531</v>
       </c>
       <c r="T67" s="15" t="inlineStr">
         <is>
-          <t>Marketing Speciality (46%)</t>
+          <t>Communications Solutio (58%)</t>
         </is>
       </c>
       <c r="U67" s="17" t="inlineStr">
         <is>
-          <t>Marketing Speciality 46%; Refining 40%; Midstream 11%</t>
+          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
         </is>
       </c>
       <c r="V67" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W67" s="17" t="inlineStr">
         <is>
-          <t>US 79%; GB 10%; Other Geographical Areas 7%</t>
+          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
         </is>
       </c>
       <c r="X67" s="15" t="inlineStr">
         <is>
-          <t>Refining +92%</t>
-        </is>
-      </c>
-      <c r="Y67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z67" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Communications Solut +143%</t>
+        </is>
+      </c>
+      <c r="Y67" s="21" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="Z67" s="20" t="n">
+        <v>-0.0436</v>
       </c>
       <c r="AA67" s="24" t="inlineStr"/>
     </row>
@@ -56719,12 +56701,12 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Amphenol Corp /De/</t>
+          <t>Enterprise Products Partners L</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -56734,11 +56716,11 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F68" s="18" t="n">
-        <v>206943928320</v>
+        <v>84003667968</v>
       </c>
       <c r="G68" s="19" t="inlineStr">
         <is>
@@ -56746,69 +56728,69 @@
         </is>
       </c>
       <c r="H68" s="20" t="n">
-        <v>29.62302222645686</v>
+        <v>11.619</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>41.96</v>
+        <v>13.460208</v>
       </c>
       <c r="J68" s="20" t="n">
-        <v>13.354551</v>
+        <v>2.777183</v>
       </c>
       <c r="K68" s="20" t="n">
-        <v>7.1331444</v>
+        <v>1.4366723</v>
       </c>
       <c r="L68" s="21" t="n">
-        <v>2.30913485895705</v>
+        <v>4.43809968934908</v>
       </c>
       <c r="M68" s="21" t="n">
-        <v>0.55827491517045</v>
+        <v>0.13529237831726</v>
       </c>
       <c r="N68" s="21" t="n">
-        <v>45.67278672993024</v>
+        <v>21.16359754470242</v>
       </c>
       <c r="O68" s="21" t="n">
-        <v>29.39923710032213</v>
+        <v>19.03228934354698</v>
       </c>
       <c r="P68" s="20" t="n">
-        <v>2.057377830710813</v>
+        <v>3.436213572447524</v>
       </c>
       <c r="Q68" s="21" t="n">
-        <v>19.46</v>
+        <v>32.34</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68" s="20" t="n">
-        <v>0.4256894967493531</v>
+        <v>0.3092139839729619</v>
       </c>
       <c r="T68" s="15" t="inlineStr">
         <is>
-          <t>Communications Solutio (58%)</t>
+          <t>Onshore Crude Oil Pipe (39%)</t>
         </is>
       </c>
       <c r="U68" s="17" t="inlineStr">
         <is>
-          <t>Communications Solutions 58%; Interconnect And Sensor Systems 23%; Harsh Environ</t>
+          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
         </is>
       </c>
       <c r="V68" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W68" s="17" t="inlineStr">
-        <is>
-          <t>Other Foreign Locations 50%; US 35%; CN 16%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W68" s="17" t="n"/>
       <c r="X68" s="15" t="inlineStr">
         <is>
-          <t>Communications Solut +143%</t>
-        </is>
-      </c>
-      <c r="Y68" s="21" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="Z68" s="20" t="n">
-        <v>-0.0436</v>
+          <t>Petrochemical And Re +92%</t>
+        </is>
+      </c>
+      <c r="Y68" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z68" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA68" s="24" t="inlineStr"/>
     </row>
@@ -56818,12 +56800,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners L</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -56833,11 +56815,11 @@
       </c>
       <c r="E69" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F69" s="18" t="n">
-        <v>84003667968</v>
+        <v>59365711872</v>
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
@@ -56845,58 +56827,62 @@
         </is>
       </c>
       <c r="H69" s="20" t="n">
-        <v>11.619</v>
+        <v>38.313</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>13.460208</v>
+        <v>52.08779</v>
       </c>
       <c r="J69" s="20" t="n">
-        <v>2.777183</v>
+        <v>18.907534</v>
       </c>
       <c r="K69" s="20" t="n">
-        <v>1.4366723</v>
+        <v>17.51624120163544</v>
       </c>
       <c r="L69" s="21" t="n">
-        <v>4.43809968934908</v>
+        <v>1.43309891391495</v>
       </c>
       <c r="M69" s="21" t="n">
-        <v>0.13529237831726</v>
+        <v>0.11999999</v>
       </c>
       <c r="N69" s="21" t="n">
-        <v>21.16359754470242</v>
+        <v>28.59709180832235</v>
       </c>
       <c r="O69" s="21" t="n">
-        <v>19.03228934354698</v>
+        <v>44.40287939770699</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>3.436213572447524</v>
+        <v>-0.1708346552178611</v>
       </c>
       <c r="Q69" s="21" t="n">
-        <v>32.34</v>
+        <v>96.81</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S69" s="20" t="n">
-        <v>0.3092139839729619</v>
+        <v>0.6478300772075185</v>
       </c>
       <c r="T69" s="15" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipe (39%)</t>
+          <t>Semiconductor Test (79%)</t>
         </is>
       </c>
       <c r="U69" s="17" t="inlineStr">
         <is>
-          <t>Onshore Crude Oil Pipelines And Services 39%; Ngl Pipelines And Services 33%; Pe</t>
+          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
         </is>
       </c>
       <c r="V69" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" s="17" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="W69" s="17" t="inlineStr">
+        <is>
+          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
+        </is>
+      </c>
       <c r="X69" s="15" t="inlineStr">
         <is>
-          <t>Petrochemical And Re +92%</t>
+          <t>Semiconductor Test +128%</t>
         </is>
       </c>
       <c r="Y69" s="22" t="inlineStr">
@@ -56917,12 +56903,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Te Connectivity Plc</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -56936,7 +56922,7 @@
         </is>
       </c>
       <c r="F70" s="18" t="n">
-        <v>59365711872</v>
+        <v>61365223424</v>
       </c>
       <c r="G70" s="19" t="inlineStr">
         <is>
@@ -56944,73 +56930,69 @@
         </is>
       </c>
       <c r="H70" s="20" t="n">
-        <v>38.313</v>
+        <v>12.92</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>52.08779</v>
+        <v>20.76004</v>
       </c>
       <c r="J70" s="20" t="n">
-        <v>18.907534</v>
+        <v>4.6395974</v>
       </c>
       <c r="K70" s="20" t="n">
-        <v>17.51624120163544</v>
+        <v>3.175925</v>
       </c>
       <c r="L70" s="21" t="n">
-        <v>1.43309891391495</v>
+        <v>5.99434499439441</v>
       </c>
       <c r="M70" s="21" t="n">
-        <v>0.11999999</v>
+        <v>1.50999995</v>
       </c>
       <c r="N70" s="21" t="n">
-        <v>28.59709180832235</v>
+        <v>19.58952110795928</v>
       </c>
       <c r="O70" s="21" t="n">
-        <v>44.40287939770699</v>
+        <v>23.88059701492537</v>
       </c>
       <c r="P70" s="20" t="n">
-        <v>-0.1708346552178611</v>
+        <v>1.09837962962963</v>
       </c>
       <c r="Q70" s="21" t="n">
-        <v>96.81</v>
+        <v>-14.61</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S70" s="20" t="n">
-        <v>0.6478300772075185</v>
+        <v>0.5038462678974261</v>
       </c>
       <c r="T70" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test (79%)</t>
+          <t>Transportation Solutio (54%)</t>
         </is>
       </c>
       <c r="U70" s="17" t="inlineStr">
         <is>
-          <t>Semiconductor Test 79%; Product Test 11%; Robotics 10%</t>
+          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
         </is>
       </c>
       <c r="V70" s="18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W70" s="17" t="inlineStr">
         <is>
-          <t>Asia Pacific 40%; TW 18%; CN 7%</t>
+          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
         </is>
       </c>
       <c r="X70" s="15" t="inlineStr">
         <is>
-          <t>Semiconductor Test +128%</t>
-        </is>
-      </c>
-      <c r="Y70" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z70" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Industrial Solutions +344%</t>
+        </is>
+      </c>
+      <c r="Y70" s="21" t="n">
+        <v>-15.49</v>
+      </c>
+      <c r="Z70" s="20" t="n">
+        <v>-2.0745</v>
       </c>
       <c r="AA70" s="24" t="inlineStr"/>
     </row>
@@ -57020,12 +57002,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>DWSN</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>Te Connectivity Plc</t>
+          <t>Dawson Geophysical Company</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -57035,11 +57017,11 @@
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F71" s="18" t="n">
-        <v>61365223424</v>
+        <v>104346872</v>
       </c>
       <c r="G71" s="19" t="inlineStr">
         <is>
@@ -57047,71 +57029,71 @@
         </is>
       </c>
       <c r="H71" s="20" t="n">
-        <v>12.92</v>
+        <v>9.484</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>20.76004</v>
+        <v>28</v>
       </c>
       <c r="J71" s="20" t="n">
-        <v>4.6395974</v>
+        <v>5.2093024</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>3.175925</v>
+        <v>0.781109620624607</v>
       </c>
       <c r="L71" s="21" t="n">
-        <v>5.99434499439441</v>
+        <v>-3.92755347083511</v>
       </c>
       <c r="M71" s="21" t="n">
-        <v>1.50999995</v>
+        <v>8.120800080331669</v>
       </c>
       <c r="N71" s="21" t="n">
-        <v>19.58952110795928</v>
+        <v>25.64674804153762</v>
       </c>
       <c r="O71" s="21" t="n">
-        <v>23.88059701492537</v>
+        <v>8.550169176872171</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>1.09837962962963</v>
+        <v>1.218788303274383</v>
       </c>
       <c r="Q71" s="21" t="n">
-        <v>-14.61</v>
+        <v>85.28</v>
       </c>
       <c r="R71" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S71" s="20" t="n">
-        <v>0.5038462678974261</v>
+        <v>0.6695871789304009</v>
       </c>
       <c r="T71" s="15" t="inlineStr">
         <is>
-          <t>Transportation Solutio (54%)</t>
+          <t>United States Operatio (79%)</t>
         </is>
       </c>
       <c r="U71" s="17" t="inlineStr">
         <is>
-          <t>Transportation Solutions 54%; Industrial Solutions 46%</t>
+          <t>United States Operations 79%; Canada Operations 21%</t>
         </is>
       </c>
       <c r="V71" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W71" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 19%; EMEA 17%; Americas 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W71" s="17" t="n"/>
       <c r="X71" s="15" t="inlineStr">
         <is>
-          <t>Industrial Solutions +344%</t>
+          <t>Canada Operations +152%</t>
         </is>
       </c>
       <c r="Y71" s="21" t="n">
-        <v>-15.49</v>
+        <v>7.52</v>
       </c>
       <c r="Z71" s="20" t="n">
-        <v>-2.0745</v>
-      </c>
-      <c r="AA71" s="24" t="inlineStr"/>
+        <v>1.4961</v>
+      </c>
+      <c r="AA71" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="13" t="n">
@@ -57119,12 +57101,12 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>DWSN</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Dawson Geophysical Company</t>
+          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -57134,11 +57116,11 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F72" s="18" t="n">
-        <v>104346872</v>
+        <v>4507106816</v>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
@@ -57146,71 +57128,71 @@
         </is>
       </c>
       <c r="H72" s="20" t="n">
-        <v>9.484</v>
+        <v>20.979</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>28</v>
+        <v>39.50917</v>
       </c>
       <c r="J72" s="20" t="n">
-        <v>5.2093024</v>
+        <v>4.942614</v>
       </c>
       <c r="K72" s="20" t="n">
-        <v>0.781109620624607</v>
+        <v>5.988356816294535</v>
       </c>
       <c r="L72" s="21" t="n">
-        <v>-3.92755347083511</v>
+        <v>0.9359515835039199</v>
       </c>
       <c r="M72" s="21" t="n">
-        <v>8.120800080331669</v>
+        <v>0.64999997</v>
       </c>
       <c r="N72" s="21" t="n">
-        <v>25.64674804153762</v>
+        <v>-5.462297040904851</v>
       </c>
       <c r="O72" s="21" t="n">
-        <v>8.550169176872171</v>
+        <v>25.49940543018288</v>
       </c>
       <c r="P72" s="20" t="n">
-        <v>1.218788303274383</v>
+        <v>-2.120367819924969</v>
       </c>
       <c r="Q72" s="21" t="n">
-        <v>85.28</v>
+        <v>106.32</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S72" s="20" t="n">
-        <v>0.6695871789304009</v>
+        <v>0.2775979208843406</v>
       </c>
       <c r="T72" s="15" t="inlineStr">
         <is>
-          <t>United States Operatio (79%)</t>
+          <t>Ball Bonding Equipment (43%)</t>
         </is>
       </c>
       <c r="U72" s="17" t="inlineStr">
         <is>
-          <t>United States Operations 79%; Canada Operations 21%</t>
+          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
         </is>
       </c>
       <c r="V72" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" s="17" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="W72" s="17" t="inlineStr">
+        <is>
+          <t>CN 56%; US 10%; All Other Segments 9%</t>
+        </is>
+      </c>
       <c r="X72" s="15" t="inlineStr">
         <is>
-          <t>Canada Operations +152%</t>
+          <t>Ball Bonding Equipme +198%</t>
         </is>
       </c>
       <c r="Y72" s="21" t="n">
-        <v>7.52</v>
+        <v>-2.76</v>
       </c>
       <c r="Z72" s="20" t="n">
-        <v>1.4961</v>
-      </c>
-      <c r="AA72" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-0.07149999999999999</v>
+      </c>
+      <c r="AA72" s="24" t="inlineStr"/>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="13" t="n">
@@ -57218,12 +57200,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>KLIC</t>
+          <t>EBS</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulicke And Soffa Industries, </t>
+          <t>Emergent Biosolutions Inc.</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -57233,11 +57215,11 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F73" s="18" t="n">
-        <v>4507106816</v>
+        <v>319432896</v>
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
@@ -57245,69 +57227,77 @@
         </is>
       </c>
       <c r="H73" s="20" t="n">
-        <v>20.979</v>
-      </c>
-      <c r="I73" s="20" t="n">
-        <v>39.50917</v>
+        <v>26.38994704225352</v>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J73" s="20" t="n">
-        <v>4.942614</v>
+        <v>0.9361382</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>5.988356816294535</v>
+        <v>0.4147402</v>
       </c>
       <c r="L73" s="21" t="n">
-        <v>0.9359515835039199</v>
-      </c>
-      <c r="M73" s="21" t="n">
-        <v>0.64999997</v>
+        <v>26.97801418097588</v>
+      </c>
+      <c r="M73" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N73" s="21" t="n">
-        <v>-5.462297040904851</v>
+        <v>14.79068774028193</v>
       </c>
       <c r="O73" s="21" t="n">
-        <v>25.49940543018288</v>
+        <v>3.78515260562441</v>
       </c>
       <c r="P73" s="20" t="n">
-        <v>-2.120367819924969</v>
+        <v>14.55281690140845</v>
       </c>
       <c r="Q73" s="21" t="n">
-        <v>106.32</v>
+        <v>-50.23999999999999</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S73" s="20" t="n">
-        <v>0.2775979208843406</v>
+        <v>0.557029765440831</v>
       </c>
       <c r="T73" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment (43%)</t>
+          <t>MCM Products (67%)</t>
         </is>
       </c>
       <c r="U73" s="17" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipment 43%; Aftermarket Productsand Services APS 23%; Wedge Bond</t>
+          <t>MCM Products 67%; Commercial Products 33%</t>
         </is>
       </c>
       <c r="V73" s="18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W73" s="17" t="inlineStr">
         <is>
-          <t>CN 56%; US 10%; All Other Segments 9%</t>
+          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
         </is>
       </c>
       <c r="X73" s="15" t="inlineStr">
         <is>
-          <t>Ball Bonding Equipme +198%</t>
-        </is>
-      </c>
-      <c r="Y73" s="21" t="n">
-        <v>-2.76</v>
-      </c>
-      <c r="Z73" s="20" t="n">
-        <v>-0.07149999999999999</v>
+          <t>MCM Products +188%</t>
+        </is>
+      </c>
+      <c r="Y73" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z73" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA73" s="24" t="inlineStr"/>
     </row>
@@ -57317,12 +57307,12 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>EBS</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Emergent Biosolutions Inc.</t>
+          <t>Porch Group Inc.</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -57332,11 +57322,11 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F74" s="18" t="n">
-        <v>319432896</v>
+        <v>1867401472</v>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
@@ -57344,66 +57334,62 @@
         </is>
       </c>
       <c r="H74" s="20" t="n">
-        <v>26.38994704225352</v>
+        <v>37.42943855774974</v>
       </c>
       <c r="I74" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J74" s="20" t="n">
-        <v>0.9361382</v>
+      <c r="J74" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K74" s="20" t="n">
-        <v>0.4147402</v>
+        <v>3.6359277</v>
       </c>
       <c r="L74" s="21" t="n">
-        <v>26.97801418097588</v>
-      </c>
-      <c r="M74" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.69353492369449</v>
+      </c>
+      <c r="M74" s="21" t="n">
+        <v>2.78673595725851</v>
       </c>
       <c r="N74" s="21" t="n">
-        <v>14.79068774028193</v>
+        <v>10.31950957042169</v>
       </c>
       <c r="O74" s="21" t="n">
-        <v>3.78515260562441</v>
+        <v>10.50153492306376</v>
       </c>
       <c r="P74" s="20" t="n">
-        <v>14.55281690140845</v>
+        <v>3.279218781110286</v>
       </c>
       <c r="Q74" s="21" t="n">
-        <v>-50.23999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S74" s="20" t="n">
-        <v>0.557029765440831</v>
+        <v>0.5817970747345014</v>
       </c>
       <c r="T74" s="15" t="inlineStr">
         <is>
-          <t>MCM Products (67%)</t>
+          <t>Insurance Services (72%)</t>
         </is>
       </c>
       <c r="U74" s="17" t="inlineStr">
         <is>
-          <t>MCM Products 67%; Commercial Products 33%</t>
+          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
         </is>
       </c>
       <c r="V74" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W74" s="17" t="inlineStr">
-        <is>
-          <t>US 71%; Other Geographical Area 18%; CA 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W74" s="17" t="n"/>
       <c r="X74" s="15" t="inlineStr">
         <is>
-          <t>MCM Products +188%</t>
+          <t>Software Data +333%</t>
         </is>
       </c>
       <c r="Y74" s="22" t="inlineStr">
@@ -57424,12 +57410,12 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>NGL</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Porch Group Inc.</t>
+          <t>NGL Energy Partners LP</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -57439,11 +57425,11 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F75" s="18" t="n">
-        <v>1867401472</v>
+        <v>1989539712</v>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
@@ -57451,7 +57437,7 @@
         </is>
       </c>
       <c r="H75" s="20" t="n">
-        <v>37.42943855774974</v>
+        <v>15.17839608310902</v>
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
@@ -57464,49 +57450,55 @@
         </is>
       </c>
       <c r="K75" s="20" t="n">
-        <v>3.6359277</v>
+        <v>0.6303674</v>
       </c>
       <c r="L75" s="21" t="n">
-        <v>4.69353492369449</v>
-      </c>
-      <c r="M75" s="21" t="n">
-        <v>2.78673595725851</v>
+        <v>5.12068190373472</v>
+      </c>
+      <c r="M75" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N75" s="21" t="n">
-        <v>10.31950957042169</v>
+        <v>12.90137422847655</v>
       </c>
       <c r="O75" s="21" t="n">
-        <v>10.50153492306376</v>
+        <v>11.58580003385248</v>
       </c>
       <c r="P75" s="20" t="n">
-        <v>3.279218781110286</v>
+        <v>7.901573173509551</v>
       </c>
       <c r="Q75" s="21" t="n">
-        <v>19.2</v>
+        <v>174.77</v>
       </c>
       <c r="R75" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S75" s="20" t="n">
-        <v>0.5817970747345014</v>
+        <v>0.3423299785064143</v>
       </c>
       <c r="T75" s="15" t="inlineStr">
         <is>
-          <t>Insurance Services (72%)</t>
+          <t>Liquids Logistics (40%)</t>
         </is>
       </c>
       <c r="U75" s="17" t="inlineStr">
         <is>
-          <t>Insurance Services 72%; Consumer Services 25%; Software Data 3%</t>
+          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
         </is>
       </c>
       <c r="V75" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W75" s="17" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="W75" s="17" t="inlineStr">
+        <is>
+          <t>Non Us 100%</t>
+        </is>
+      </c>
       <c r="X75" s="15" t="inlineStr">
         <is>
-          <t>Software Data +333%</t>
+          <t>Crude Oil Logistics +162%</t>
         </is>
       </c>
       <c r="Y75" s="22" t="inlineStr">
@@ -57527,12 +57519,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>NGL</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>NGL Energy Partners LP</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -57542,11 +57534,11 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1989539712</v>
+        <v>360690188288</v>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
@@ -57554,12 +57546,10 @@
         </is>
       </c>
       <c r="H76" s="20" t="n">
-        <v>15.17839608310902</v>
-      </c>
-      <c r="I76" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>19.51</v>
+      </c>
+      <c r="I76" s="20" t="n">
+        <v>33.039604</v>
       </c>
       <c r="J76" s="22" t="inlineStr">
         <is>
@@ -57567,66 +57557,60 @@
         </is>
       </c>
       <c r="K76" s="20" t="n">
-        <v>0.6303674</v>
+        <v>2.3855643</v>
       </c>
       <c r="L76" s="21" t="n">
-        <v>5.12068190373472</v>
-      </c>
-      <c r="M76" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.02823359941622</v>
+      </c>
+      <c r="M76" s="21" t="n">
+        <v>0.76768205413026</v>
       </c>
       <c r="N76" s="21" t="n">
-        <v>12.90137422847655</v>
+        <v>81.97384514065294</v>
       </c>
       <c r="O76" s="21" t="n">
-        <v>11.58580003385248</v>
+        <v>13.94585527536068</v>
       </c>
       <c r="P76" s="20" t="n">
-        <v>7.901573173509551</v>
+        <v>1.01819258757827</v>
       </c>
       <c r="Q76" s="21" t="n">
-        <v>174.77</v>
+        <v>226.48</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76" s="20" t="n">
-        <v>0.3423299785064143</v>
+        <v>0.5038741410704293</v>
       </c>
       <c r="T76" s="15" t="inlineStr">
         <is>
-          <t>Liquids Logistics (40%)</t>
+          <t>Infrastructure Solutio (54%)</t>
         </is>
       </c>
       <c r="U76" s="17" t="inlineStr">
         <is>
-          <t>Liquids Logistics 40%; Crude Oil Logistics 33%; Water Solutions 27%</t>
+          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
         </is>
       </c>
       <c r="V76" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="17" t="inlineStr">
         <is>
-          <t>Non Us 100%</t>
+          <t>US 56%; Non Us 44%</t>
         </is>
       </c>
       <c r="X76" s="15" t="inlineStr">
         <is>
-          <t>Crude Oil Logistics +162%</t>
-        </is>
-      </c>
-      <c r="Y76" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z76" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Infrastructure Solut +181%</t>
+        </is>
+      </c>
+      <c r="Y76" s="21" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="Z76" s="20" t="n">
+        <v>-0.1207</v>
       </c>
       <c r="AA76" s="24" t="inlineStr"/>
     </row>
@@ -57636,12 +57620,12 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -57655,7 +57639,7 @@
         </is>
       </c>
       <c r="F77" s="18" t="n">
-        <v>360690188288</v>
+        <v>83154591744</v>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
@@ -57663,71 +57647,75 @@
         </is>
       </c>
       <c r="H77" s="20" t="n">
-        <v>19.51</v>
+        <v>102.474</v>
       </c>
       <c r="I77" s="20" t="n">
-        <v>33.039604</v>
-      </c>
-      <c r="J77" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>142.82867</v>
+      </c>
+      <c r="J77" s="20" t="n">
+        <v>17.686687</v>
       </c>
       <c r="K77" s="20" t="n">
-        <v>2.3855643</v>
+        <v>27.589445</v>
       </c>
       <c r="L77" s="21" t="n">
-        <v>2.02823359941622</v>
-      </c>
-      <c r="M77" s="21" t="n">
-        <v>0.76768205413026</v>
+        <v>0.37963999713611</v>
+      </c>
+      <c r="M77" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N77" s="21" t="n">
-        <v>81.97384514065294</v>
+        <v>5.712871831528011</v>
       </c>
       <c r="O77" s="21" t="n">
-        <v>13.94585527536068</v>
+        <v>32.17730397042276</v>
       </c>
       <c r="P77" s="20" t="n">
-        <v>1.01819258757827</v>
+        <v>-1.18221551413651</v>
       </c>
       <c r="Q77" s="21" t="n">
-        <v>226.48</v>
+        <v>337.22</v>
       </c>
       <c r="R77" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S77" s="20" t="n">
-        <v>0.5038741410704293</v>
+        <v>0.554732848124369</v>
       </c>
       <c r="T77" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solutio (54%)</t>
+          <t>Systems (67%)</t>
         </is>
       </c>
       <c r="U77" s="17" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Group 54%; Client Solutions 46%</t>
+          <t>Systems 67%; Components 33%</t>
         </is>
       </c>
       <c r="V77" s="18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="W77" s="17" t="inlineStr">
         <is>
-          <t>US 56%; Non Us 44%</t>
+          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
         </is>
       </c>
       <c r="X77" s="15" t="inlineStr">
         <is>
-          <t>Infrastructure Solut +181%</t>
-        </is>
-      </c>
-      <c r="Y77" s="21" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="Z77" s="20" t="n">
-        <v>-0.1207</v>
+          <t>Systems +279%</t>
+        </is>
+      </c>
+      <c r="Y77" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z77" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA77" s="24" t="inlineStr"/>
     </row>
@@ -57737,12 +57725,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>PROG Holdings, Inc.</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -57752,11 +57740,11 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F78" s="18" t="n">
-        <v>83154591744</v>
+        <v>1472177024</v>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
@@ -57764,64 +57752,58 @@
         </is>
       </c>
       <c r="H78" s="20" t="n">
-        <v>102.474</v>
+        <v>8.850440627472885</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>142.82867</v>
+        <v>11.922581</v>
       </c>
       <c r="J78" s="20" t="n">
-        <v>17.686687</v>
+        <v>1.8279835</v>
       </c>
       <c r="K78" s="20" t="n">
-        <v>27.589445</v>
+        <v>0.5630427</v>
       </c>
       <c r="L78" s="21" t="n">
-        <v>0.37963999713611</v>
-      </c>
-      <c r="M78" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>20.7154094641091</v>
+      </c>
+      <c r="M78" s="21" t="n">
+        <v>1.20889722398801</v>
       </c>
       <c r="N78" s="21" t="n">
-        <v>5.712871831528011</v>
+        <v>14.37354784103989</v>
       </c>
       <c r="O78" s="21" t="n">
-        <v>32.17730397042276</v>
+        <v>10.44635139915609</v>
       </c>
       <c r="P78" s="20" t="n">
-        <v>-1.18221551413651</v>
+        <v>3.362100265326072</v>
       </c>
       <c r="Q78" s="21" t="n">
-        <v>337.22</v>
+        <v>38.15</v>
       </c>
       <c r="R78" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S78" s="20" t="n">
-        <v>0.554732848124369</v>
+        <v>0.9403673440059026</v>
       </c>
       <c r="T78" s="15" t="inlineStr">
         <is>
-          <t>Systems (67%)</t>
+          <t>Progressive Leasing (97%)</t>
         </is>
       </c>
       <c r="U78" s="17" t="inlineStr">
         <is>
-          <t>Systems 67%; Components 33%</t>
+          <t>Progressive Leasing 97%; Four 3%</t>
         </is>
       </c>
       <c r="V78" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="W78" s="17" t="inlineStr">
-        <is>
-          <t>Asia Pacific 30%; Americas 19%; US 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W78" s="17" t="n"/>
       <c r="X78" s="15" t="inlineStr">
         <is>
-          <t>Systems +279%</t>
+          <t>Four +170%</t>
         </is>
       </c>
       <c r="Y78" s="22" t="inlineStr">
@@ -57842,12 +57824,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>PROG Holdings, Inc.</t>
+          <t>Ies Holdings, Inc.</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -57861,7 +57843,7 @@
         </is>
       </c>
       <c r="F79" s="18" t="n">
-        <v>1472177024</v>
+        <v>13776098304</v>
       </c>
       <c r="G79" s="19" t="inlineStr">
         <is>
@@ -57869,49 +57851,51 @@
         </is>
       </c>
       <c r="H79" s="20" t="n">
-        <v>8.850440627472885</v>
+        <v>22.535</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>11.922581</v>
+        <v>30.729776</v>
       </c>
       <c r="J79" s="20" t="n">
-        <v>1.8279835</v>
+        <v>11.206885</v>
       </c>
       <c r="K79" s="20" t="n">
-        <v>0.5630427</v>
+        <v>3.4563446</v>
       </c>
       <c r="L79" s="21" t="n">
-        <v>20.7154094641091</v>
-      </c>
-      <c r="M79" s="21" t="n">
-        <v>1.20889722398801</v>
+        <v>2.01426811681025</v>
+      </c>
+      <c r="M79" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N79" s="21" t="n">
-        <v>14.37354784103989</v>
+        <v>39.14787497533104</v>
       </c>
       <c r="O79" s="21" t="n">
-        <v>10.44635139915609</v>
+        <v>13.0825133917565</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>3.362100265326072</v>
+        <v>-0.6658293394323307</v>
       </c>
       <c r="Q79" s="21" t="n">
-        <v>38.15</v>
+        <v>64.63</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S79" s="20" t="n">
-        <v>0.9403673440059026</v>
+        <v>0.302118628032772</v>
       </c>
       <c r="T79" s="15" t="inlineStr">
         <is>
-          <t>Progressive Leasing (97%)</t>
+          <t>Residential (39%)</t>
         </is>
       </c>
       <c r="U79" s="17" t="inlineStr">
         <is>
-          <t>Progressive Leasing 97%; Four 3%</t>
+          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
         </is>
       </c>
       <c r="V79" s="18" t="n">
@@ -57920,18 +57904,14 @@
       <c r="W79" s="17" t="n"/>
       <c r="X79" s="15" t="inlineStr">
         <is>
-          <t>Four +170%</t>
-        </is>
-      </c>
-      <c r="Y79" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z79" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Commercialand Indust +109%</t>
+        </is>
+      </c>
+      <c r="Y79" s="21" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Z79" s="20" t="n">
+        <v>-0.0209</v>
       </c>
       <c r="AA79" s="24" t="inlineStr"/>
     </row>
@@ -57941,12 +57921,12 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>IESC</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Ies Holdings, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -57956,11 +57936,11 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F80" s="18" t="n">
-        <v>13776098304</v>
+        <v>5271048421376</v>
       </c>
       <c r="G80" s="19" t="inlineStr">
         <is>
@@ -57968,67 +57948,69 @@
         </is>
       </c>
       <c r="H80" s="20" t="n">
-        <v>22.535</v>
+        <v>26.03</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>30.729776</v>
+        <v>27.631645</v>
       </c>
       <c r="J80" s="20" t="n">
-        <v>11.206885</v>
+        <v>23.019087</v>
       </c>
       <c r="K80" s="20" t="n">
-        <v>3.4563446</v>
+        <v>195.8478272042803</v>
       </c>
       <c r="L80" s="21" t="n">
-        <v>2.01426811681025</v>
-      </c>
-      <c r="M80" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.66135648441059</v>
+      </c>
+      <c r="M80" s="21" t="n">
+        <v>0.01871342168819</v>
       </c>
       <c r="N80" s="21" t="n">
-        <v>39.14787497533104</v>
+        <v>73.21388307718124</v>
       </c>
       <c r="O80" s="21" t="n">
-        <v>13.0825133917565</v>
+        <v>79.39769221313577</v>
       </c>
       <c r="P80" s="20" t="n">
-        <v>-0.6658293394323307</v>
+        <v>-0.3535471835000259</v>
       </c>
       <c r="Q80" s="21" t="n">
-        <v>64.63</v>
+        <v>13.91</v>
       </c>
       <c r="R80" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S80" s="20" t="n">
+        <v>0.8136213783744384</v>
+      </c>
+      <c r="T80" s="15" t="inlineStr">
+        <is>
+          <t>Compute And Networking (90%)</t>
+        </is>
+      </c>
+      <c r="U80" s="17" t="inlineStr">
+        <is>
+          <t>Compute And Networking 90%; Graphics 10%</t>
+        </is>
+      </c>
+      <c r="V80" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S80" s="20" t="n">
-        <v>0.302118628032772</v>
-      </c>
-      <c r="T80" s="15" t="inlineStr">
-        <is>
-          <t>Residential (39%)</t>
-        </is>
-      </c>
-      <c r="U80" s="17" t="inlineStr">
-        <is>
-          <t>Residential 39%; Communications 34%; Infrastructure Solutions 15%</t>
-        </is>
-      </c>
-      <c r="V80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" s="17" t="n"/>
+      <c r="W80" s="17" t="inlineStr">
+        <is>
+          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
+        </is>
+      </c>
       <c r="X80" s="15" t="inlineStr">
         <is>
-          <t>Commercialand Indust +109%</t>
+          <t>Compute And Networki +114%</t>
         </is>
       </c>
       <c r="Y80" s="21" t="n">
-        <v>-0.2</v>
+        <v>-4.06</v>
       </c>
       <c r="Z80" s="20" t="n">
-        <v>-0.0209</v>
+        <v>-0.0948</v>
       </c>
       <c r="AA80" s="24" t="inlineStr"/>
     </row>
@@ -58038,12 +58020,12 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Freedom Holding Corp.</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
@@ -58053,11 +58035,11 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F81" s="18" t="n">
-        <v>5271048421376</v>
+        <v>10556858368</v>
       </c>
       <c r="G81" s="19" t="inlineStr">
         <is>
@@ -58065,69 +58047,75 @@
         </is>
       </c>
       <c r="H81" s="20" t="n">
-        <v>26.03</v>
+        <v>347.3889692037075</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>27.631645</v>
+        <v>68.672195</v>
       </c>
       <c r="J81" s="20" t="n">
-        <v>23.019087</v>
+        <v>6.6218543</v>
       </c>
       <c r="K81" s="20" t="n">
-        <v>195.8478272042803</v>
+        <v>4.817643283343015</v>
       </c>
       <c r="L81" s="21" t="n">
-        <v>1.66135648441059</v>
-      </c>
-      <c r="M81" s="21" t="n">
-        <v>0.01871342168819</v>
+        <v>-8.42592261675078</v>
+      </c>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N81" s="21" t="n">
-        <v>73.21388307718124</v>
+        <v>-0.11123836175898</v>
       </c>
       <c r="O81" s="21" t="n">
-        <v>79.39769221313577</v>
+        <v>1.17675041790433</v>
       </c>
       <c r="P81" s="20" t="n">
-        <v>-0.3535471835000259</v>
+        <v>-59.63858781496614</v>
       </c>
       <c r="Q81" s="21" t="n">
-        <v>13.91</v>
+        <v>7.08</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S81" s="20" t="n">
-        <v>0.8136213783744384</v>
+        <v>0.3007342710765748</v>
       </c>
       <c r="T81" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networking (90%)</t>
+          <t>Brokerage (38%)</t>
         </is>
       </c>
       <c r="U81" s="17" t="inlineStr">
         <is>
-          <t>Compute And Networking 90%; Graphics 10%</t>
+          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
         </is>
       </c>
       <c r="V81" s="18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W81" s="17" t="inlineStr">
         <is>
-          <t>US 69%; TW 20%; China Including Hong Kong 9%</t>
+          <t>KZ 84%; AM 8%; CY 7%</t>
         </is>
       </c>
       <c r="X81" s="15" t="inlineStr">
         <is>
-          <t>Compute And Networki +114%</t>
-        </is>
-      </c>
-      <c r="Y81" s="21" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="Z81" s="20" t="n">
-        <v>-0.0948</v>
+          <t>Other +100%</t>
+        </is>
+      </c>
+      <c r="Y81" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z81" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA81" s="24" t="inlineStr"/>
     </row>
@@ -58137,12 +58125,12 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Freedom Holding Corp.</t>
+          <t>FutureFuel Corp.</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
@@ -58152,76 +58140,80 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F82" s="18" t="n">
-        <v>10556858368</v>
+        <v>239932352</v>
       </c>
       <c r="G82" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H82" s="20" t="n">
-        <v>347.3889692037075</v>
-      </c>
-      <c r="I82" s="20" t="n">
-        <v>68.672195</v>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J82" s="20" t="n">
-        <v>6.6218543</v>
+        <v>1.5673351</v>
       </c>
       <c r="K82" s="20" t="n">
-        <v>4.817643283343015</v>
+        <v>1.5660461</v>
       </c>
       <c r="L82" s="21" t="n">
-        <v>-8.42592261675078</v>
-      </c>
-      <c r="M82" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>-19.02773752715573</v>
+      </c>
+      <c r="M82" s="21" t="n">
+        <v>5.946712029429071</v>
       </c>
       <c r="N82" s="21" t="n">
-        <v>-0.11123836175898</v>
+        <v>-51.30812980930077</v>
       </c>
       <c r="O82" s="21" t="n">
-        <v>1.17675041790433</v>
-      </c>
-      <c r="P82" s="20" t="n">
-        <v>-59.63858781496614</v>
+        <v>-11.30220868498371</v>
+      </c>
+      <c r="P82" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q82" s="21" t="n">
-        <v>7.08</v>
+        <v>38.74</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S82" s="20" t="n">
-        <v>0.3007342710765748</v>
+        <v>0.5298367272208879</v>
       </c>
       <c r="T82" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (38%)</t>
+          <t>Chemicals (62%)</t>
         </is>
       </c>
       <c r="U82" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 38%; Banking 31%; Insurance 23%</t>
+          <t>Chemicals 62%; Biofuels 38%</t>
         </is>
       </c>
       <c r="V82" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W82" s="17" t="inlineStr">
         <is>
-          <t>KZ 84%; AM 8%; CY 7%</t>
+          <t>US 99%; Non Us 1%</t>
         </is>
       </c>
       <c r="X82" s="15" t="inlineStr">
         <is>
-          <t>Other +100%</t>
+          <t>Biofuels +178%</t>
         </is>
       </c>
       <c r="Y82" s="22" t="inlineStr">
@@ -58242,12 +58234,12 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>SLNH</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>FutureFuel Corp.</t>
+          <t>Soluna Holdings Inc. Common St</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
@@ -58257,11 +58249,11 @@
       </c>
       <c r="E83" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F83" s="18" t="n">
-        <v>239932352</v>
+        <v>291062784</v>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
@@ -58279,22 +58271,24 @@
         </is>
       </c>
       <c r="J83" s="20" t="n">
-        <v>1.5673351</v>
+        <v>1.7097702</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>1.5660461</v>
+        <v>6.9173846</v>
       </c>
       <c r="L83" s="21" t="n">
-        <v>-19.02773752715573</v>
+        <v>-15.20023065482923</v>
       </c>
       <c r="M83" s="21" t="n">
-        <v>5.946712029429071</v>
-      </c>
-      <c r="N83" s="21" t="n">
-        <v>-51.30812980930077</v>
+        <v>0.20077091953947</v>
+      </c>
+      <c r="N83" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O83" s="21" t="n">
-        <v>-11.30220868498371</v>
+        <v>-104.2041970672814</v>
       </c>
       <c r="P83" s="22" t="inlineStr">
         <is>
@@ -58302,35 +58296,31 @@
         </is>
       </c>
       <c r="Q83" s="21" t="n">
-        <v>38.74</v>
+        <v>-65.62</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S83" s="20" t="n">
-        <v>0.5298367272208879</v>
+        <v>0.5183581202661786</v>
       </c>
       <c r="T83" s="15" t="inlineStr">
         <is>
-          <t>Chemicals (62%)</t>
+          <t>Data Center Hosting (60%)</t>
         </is>
       </c>
       <c r="U83" s="17" t="inlineStr">
         <is>
-          <t>Chemicals 62%; Biofuels 38%</t>
+          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
         </is>
       </c>
       <c r="V83" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W83" s="17" t="inlineStr">
-        <is>
-          <t>US 99%; Non Us 1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W83" s="17" t="n"/>
       <c r="X83" s="15" t="inlineStr">
         <is>
-          <t>Biofuels +178%</t>
+          <t>Data Center Hosting +303%</t>
         </is>
       </c>
       <c r="Y83" s="22" t="inlineStr">
@@ -58351,12 +58341,12 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>SLNH</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Soluna Holdings Inc. Common St</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
@@ -58366,89 +58356,81 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F84" s="18" t="n">
-        <v>291062784</v>
+        <v>98965053440</v>
       </c>
       <c r="G84" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H84" s="20" t="n">
+        <v>48.51287624683352</v>
+      </c>
+      <c r="I84" s="20" t="n">
+        <v>58.15837</v>
       </c>
       <c r="J84" s="20" t="n">
-        <v>1.7097702</v>
+        <v>20.799417</v>
       </c>
       <c r="K84" s="20" t="n">
-        <v>6.9173846</v>
+        <v>8.620950000000001</v>
       </c>
       <c r="L84" s="21" t="n">
-        <v>-15.20023065482923</v>
+        <v>2.71275941299938</v>
       </c>
       <c r="M84" s="21" t="n">
-        <v>0.20077091953947</v>
-      </c>
-      <c r="N84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.03768476778678</v>
+      </c>
+      <c r="N84" s="21" t="n">
+        <v>33.68683344961626</v>
       </c>
       <c r="O84" s="21" t="n">
-        <v>-104.2041970672814</v>
-      </c>
-      <c r="P84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>21.35492557684859</v>
+      </c>
+      <c r="P84" s="20" t="n">
+        <v>0.3332181723959233</v>
       </c>
       <c r="Q84" s="21" t="n">
-        <v>-65.62</v>
+        <v>45.58</v>
       </c>
       <c r="R84" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S84" s="20" t="n">
-        <v>0.5183581202661786</v>
+        <v>0.5218491323594365</v>
       </c>
       <c r="T84" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting (60%)</t>
+          <t>EMEA (66%)</t>
         </is>
       </c>
       <c r="U84" s="17" t="inlineStr">
         <is>
-          <t>Data Center Hosting 60%; Cryptocurrency Mining 40%; High Performance Computing S</t>
+          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
         </is>
       </c>
       <c r="V84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W84" s="17" t="inlineStr">
+        <is>
+          <t>US 59%; Asia 20%; Europe 14%</t>
+        </is>
+      </c>
       <c r="X84" s="15" t="inlineStr">
         <is>
-          <t>Data Center Hosting +303%</t>
-        </is>
-      </c>
-      <c r="Y84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z84" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Asia Pacific +290%</t>
+        </is>
+      </c>
+      <c r="Y84" s="21" t="n">
+        <v>-22.44</v>
+      </c>
+      <c r="Z84" s="20" t="n">
+        <v>-0.3272</v>
       </c>
       <c r="AA84" s="24" t="inlineStr"/>
     </row>
@@ -58458,12 +58440,12 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
@@ -58473,11 +58455,11 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F85" s="18" t="n">
-        <v>98965053440</v>
+        <v>3749439488</v>
       </c>
       <c r="G85" s="19" t="inlineStr">
         <is>
@@ -58485,69 +58467,69 @@
         </is>
       </c>
       <c r="H85" s="20" t="n">
-        <v>48.51287624683352</v>
+        <v>19.297</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>58.15837</v>
+        <v>30.920187</v>
       </c>
       <c r="J85" s="20" t="n">
-        <v>20.799417</v>
+        <v>4.9097958</v>
       </c>
       <c r="K85" s="20" t="n">
-        <v>8.620950000000001</v>
+        <v>6.8440413</v>
       </c>
       <c r="L85" s="21" t="n">
-        <v>2.71275941299938</v>
+        <v>5.56871008366637</v>
       </c>
       <c r="M85" s="21" t="n">
-        <v>0.03768476778678</v>
+        <v>0.97</v>
       </c>
       <c r="N85" s="21" t="n">
-        <v>33.68683344961626</v>
+        <v>12.37235274898268</v>
       </c>
       <c r="O85" s="21" t="n">
-        <v>21.35492557684859</v>
+        <v>35.60723129340358</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>0.3332181723959233</v>
+        <v>1.359732752360203</v>
       </c>
       <c r="Q85" s="21" t="n">
-        <v>45.58</v>
+        <v>17.58</v>
       </c>
       <c r="R85" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S85" s="20" t="n">
-        <v>0.5218491323594365</v>
+        <v>0.4262861010394083</v>
       </c>
       <c r="T85" s="15" t="inlineStr">
         <is>
-          <t>EMEA (66%)</t>
+          <t>Hospitality (52%)</t>
         </is>
       </c>
       <c r="U85" s="17" t="inlineStr">
         <is>
-          <t>EMEA 66%; Asia Pacific 30%; Americas 4%</t>
+          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
         </is>
       </c>
       <c r="V85" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W85" s="17" t="inlineStr">
-        <is>
-          <t>US 59%; Asia 20%; Europe 14%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W85" s="17" t="n"/>
       <c r="X85" s="15" t="inlineStr">
         <is>
-          <t>Asia Pacific +290%</t>
-        </is>
-      </c>
-      <c r="Y85" s="21" t="n">
-        <v>-22.44</v>
-      </c>
-      <c r="Z85" s="20" t="n">
-        <v>-0.3272</v>
+          <t>Hospitality +157%</t>
+        </is>
+      </c>
+      <c r="Y85" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z85" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA85" s="24" t="inlineStr"/>
     </row>
@@ -58557,12 +58539,12 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>HTLM</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Homestolife Ltd</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
@@ -58572,11 +58554,11 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F86" s="18" t="n">
-        <v>3749439488</v>
+        <v>159643760</v>
       </c>
       <c r="G86" s="19" t="inlineStr">
         <is>
@@ -58584,71 +58566,81 @@
         </is>
       </c>
       <c r="H86" s="20" t="n">
-        <v>19.297</v>
+        <v>5.632</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>30.920187</v>
+        <v>9.368421</v>
       </c>
       <c r="J86" s="20" t="n">
-        <v>4.9097958</v>
+        <v>5.189504</v>
       </c>
       <c r="K86" s="20" t="n">
-        <v>6.8440413</v>
+        <v>0.4083795</v>
       </c>
       <c r="L86" s="21" t="n">
-        <v>5.56871008366637</v>
-      </c>
-      <c r="M86" s="21" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N86" s="21" t="n">
-        <v>12.37235274898268</v>
+        <v>7.56174932272778</v>
+      </c>
+      <c r="M86" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N86" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O86" s="21" t="n">
-        <v>35.60723129340358</v>
+        <v>5.26038476371263</v>
       </c>
       <c r="P86" s="20" t="n">
-        <v>1.359732752360203</v>
+        <v>-0.8495431924900106</v>
       </c>
       <c r="Q86" s="21" t="n">
-        <v>17.58</v>
+        <v>-46.17305967367813</v>
       </c>
       <c r="R86" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S86" s="20" t="n">
-        <v>0.4262861010394083</v>
+        <v>0.8590900293205138</v>
       </c>
       <c r="T86" s="15" t="inlineStr">
         <is>
-          <t>Hospitality (52%)</t>
+          <t>Export Sales (93%)</t>
         </is>
       </c>
       <c r="U86" s="17" t="inlineStr">
         <is>
-          <t>Hospitality 52%; Residential Real Estate 39%; Commercial 10%</t>
+          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
         </is>
       </c>
       <c r="V86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W86" s="17" t="inlineStr">
+        <is>
+          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
+        </is>
+      </c>
       <c r="X86" s="15" t="inlineStr">
         <is>
-          <t>Hospitality +157%</t>
-        </is>
-      </c>
-      <c r="Y86" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Retail Sales +100%</t>
+        </is>
+      </c>
+      <c r="Y86" s="21" t="n">
+        <v>38.69</v>
       </c>
       <c r="Z86" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="AA86" s="24" t="inlineStr"/>
+      <c r="AA86" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="13" t="n">
@@ -58656,12 +58648,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>HTLM</t>
+          <t>CODA</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Homestolife Ltd</t>
+          <t>Coda Octopus Group, Inc.</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
@@ -58671,11 +58663,11 @@
       </c>
       <c r="E87" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F87" s="18" t="n">
-        <v>159643760</v>
+        <v>113033160</v>
       </c>
       <c r="G87" s="19" t="inlineStr">
         <is>
@@ -58683,75 +58675,71 @@
         </is>
       </c>
       <c r="H87" s="20" t="n">
-        <v>5.632</v>
+        <v>11.493</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>9.368421</v>
+        <v>22.772728</v>
       </c>
       <c r="J87" s="20" t="n">
-        <v>5.189504</v>
+        <v>1.8398825</v>
       </c>
       <c r="K87" s="20" t="n">
-        <v>0.4083795</v>
+        <v>4.0441093</v>
       </c>
       <c r="L87" s="21" t="n">
-        <v>7.56174932272778</v>
+        <v>5.20947381148941</v>
       </c>
       <c r="M87" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N87" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N87" s="21" t="n">
+        <v>16.80549850408138</v>
       </c>
       <c r="O87" s="21" t="n">
-        <v>5.26038476371263</v>
+        <v>24.49495025980879</v>
       </c>
       <c r="P87" s="20" t="n">
-        <v>-0.8495431924900106</v>
+        <v>-4.37058436058821</v>
       </c>
       <c r="Q87" s="21" t="n">
-        <v>-46.17305967367813</v>
+        <v>-0.7799999999999999</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S87" s="20" t="n">
-        <v>0.8590900293205138</v>
+        <v>0.3385873824755823</v>
       </c>
       <c r="T87" s="15" t="inlineStr">
         <is>
-          <t>Export Sales (93%)</t>
+          <t>Defense Engineering Se (45%)</t>
         </is>
       </c>
       <c r="U87" s="17" t="inlineStr">
         <is>
-          <t>Export Sales 93%; Leather Trading 5%; Retail Sales 2%</t>
+          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
         </is>
       </c>
       <c r="V87" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W87" s="17" t="inlineStr">
         <is>
-          <t>Europe 60%; Asia Pacific 27%; North America 13%</t>
+          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
         </is>
       </c>
       <c r="X87" s="15" t="inlineStr">
         <is>
-          <t>Retail Sales +100%</t>
+          <t>Marine Technology Bu +185%</t>
         </is>
       </c>
       <c r="Y87" s="21" t="n">
-        <v>38.69</v>
-      </c>
-      <c r="Z87" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>39.33</v>
+      </c>
+      <c r="Z87" s="20" t="n">
+        <v>0.2903</v>
       </c>
       <c r="AA87" s="24" t="inlineStr">
         <is>
@@ -58765,12 +58753,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Coda Octopus Group, Inc.</t>
+          <t>International Seaways, Inc.</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
@@ -58784,7 +58772,7 @@
         </is>
       </c>
       <c r="F88" s="18" t="n">
-        <v>113033160</v>
+        <v>5133920768</v>
       </c>
       <c r="G88" s="19" t="inlineStr">
         <is>
@@ -58792,77 +58780,71 @@
         </is>
       </c>
       <c r="H88" s="20" t="n">
-        <v>11.493</v>
+        <v>6.541</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>22.772728</v>
+        <v>6.627238</v>
       </c>
       <c r="J88" s="20" t="n">
-        <v>1.8398825</v>
+        <v>2.2658215</v>
       </c>
       <c r="K88" s="20" t="n">
-        <v>4.0441093</v>
+        <v>4.070105</v>
       </c>
       <c r="L88" s="21" t="n">
-        <v>5.20947381148941</v>
-      </c>
-      <c r="M88" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.245834756131551</v>
+      </c>
+      <c r="M88" s="21" t="n">
+        <v>4.9099997</v>
       </c>
       <c r="N88" s="21" t="n">
-        <v>16.80549850408138</v>
+        <v>18.67715244511617</v>
       </c>
       <c r="O88" s="21" t="n">
-        <v>24.49495025980879</v>
+        <v>76.86433409911049</v>
       </c>
       <c r="P88" s="20" t="n">
-        <v>-4.37058436058821</v>
+        <v>0.1987435438854886</v>
       </c>
       <c r="Q88" s="21" t="n">
-        <v>-0.7799999999999999</v>
+        <v>126.34</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S88" s="20" t="n">
-        <v>0.3385873824755823</v>
+        <v>0.5009071443494075</v>
       </c>
       <c r="T88" s="15" t="inlineStr">
         <is>
-          <t>Defense Engineering Se (45%)</t>
+          <t>International Crude Ta (52%)</t>
         </is>
       </c>
       <c r="U88" s="17" t="inlineStr">
         <is>
-          <t>Defense Engineering Services Business Services 45%; Acoustic Sensors And Materia</t>
+          <t>International Crude Tankers 52%; International Product Carriers 48%</t>
         </is>
       </c>
       <c r="V88" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W88" s="17" t="inlineStr">
-        <is>
-          <t>Americas 34%; Europe 31%; Australia And Asia 30%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W88" s="17" t="n"/>
       <c r="X88" s="15" t="inlineStr">
         <is>
-          <t>Marine Technology Bu +185%</t>
-        </is>
-      </c>
-      <c r="Y88" s="21" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="Z88" s="20" t="n">
-        <v>0.2903</v>
-      </c>
-      <c r="AA88" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>International Crude  +175%</t>
+        </is>
+      </c>
+      <c r="Y88" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z88" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA88" s="24" t="inlineStr"/>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="13" t="n">
@@ -58870,76 +58852,82 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FENG</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>International Seaways, Inc.</t>
+          <t>Phoenix New Media Limited</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F89" s="18" t="n">
-        <v>5133920768</v>
+        <v>17896056</v>
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H89" s="20" t="n">
-        <v>6.541</v>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I89" s="20" t="n">
-        <v>6.627238</v>
+        <v>4.012985014645349</v>
       </c>
       <c r="J89" s="20" t="n">
-        <v>2.2658215</v>
+        <v>22.1065917175247</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>4.070105</v>
+        <v>0.1460944416764449</v>
       </c>
       <c r="L89" s="21" t="n">
-        <v>5.245834756131551</v>
-      </c>
-      <c r="M89" s="21" t="n">
-        <v>4.9099997</v>
+        <v>-0.32072677140719</v>
+      </c>
+      <c r="M89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N89" s="21" t="n">
-        <v>18.67715244511617</v>
+        <v>-8.02638700256313</v>
       </c>
       <c r="O89" s="21" t="n">
-        <v>76.86433409911049</v>
-      </c>
-      <c r="P89" s="20" t="n">
-        <v>0.1987435438854886</v>
+        <v>-1.79463043292417</v>
+      </c>
+      <c r="P89" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q89" s="21" t="n">
-        <v>126.34</v>
+        <v>-36.75</v>
       </c>
       <c r="R89" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S89" s="20" t="n">
-        <v>0.5009071443494075</v>
+        <v>0.682948135046668</v>
       </c>
       <c r="T89" s="15" t="inlineStr">
         <is>
-          <t>International Crude Ta (52%)</t>
+          <t>Net Advertising Servic (80%)</t>
         </is>
       </c>
       <c r="U89" s="17" t="inlineStr">
         <is>
-          <t>International Crude Tankers 52%; International Product Carriers 48%</t>
+          <t>Net Advertising Services 80%; Paid Services 20%</t>
         </is>
       </c>
       <c r="V89" s="18" t="n">
@@ -58948,7 +58936,7 @@
       <c r="W89" s="17" t="n"/>
       <c r="X89" s="15" t="inlineStr">
         <is>
-          <t>International Crude  +175%</t>
+          <t>Paid Services +107%</t>
         </is>
       </c>
       <c r="Y89" s="22" t="inlineStr">
@@ -58961,7 +58949,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="AA89" s="24" t="inlineStr"/>
+      <c r="AA89" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="13" t="n">
@@ -58969,26 +58961,26 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>FENG</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Phoenix New Media Limited</t>
+          <t>Schrodinger, Inc.</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F90" s="18" t="n">
-        <v>17896056</v>
+        <v>1422803200</v>
       </c>
       <c r="G90" s="19" t="inlineStr">
         <is>
@@ -59000,28 +58992,32 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I90" s="20" t="n">
-        <v>4.012985014645349</v>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J90" s="20" t="n">
-        <v>22.1065917175247</v>
+        <v>4.213558</v>
       </c>
       <c r="K90" s="20" t="n">
-        <v>0.1460944416764449</v>
+        <v>5.4927063</v>
       </c>
       <c r="L90" s="21" t="n">
-        <v>-0.32072677140719</v>
+        <v>-8.66829141064739</v>
       </c>
       <c r="M90" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N90" s="21" t="n">
-        <v>-8.02638700256313</v>
+      <c r="N90" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O90" s="21" t="n">
-        <v>-1.79463043292417</v>
+        <v>-84.61893927057798</v>
       </c>
       <c r="P90" s="22" t="inlineStr">
         <is>
@@ -59029,31 +59025,35 @@
         </is>
       </c>
       <c r="Q90" s="21" t="n">
-        <v>-36.75</v>
+        <v>-4.52</v>
       </c>
       <c r="R90" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S90" s="20" t="n">
-        <v>0.682948135046668</v>
+        <v>0.6564595481920475</v>
       </c>
       <c r="T90" s="15" t="inlineStr">
         <is>
-          <t>Net Advertising Servic (80%)</t>
+          <t>Software (78%)</t>
         </is>
       </c>
       <c r="U90" s="17" t="inlineStr">
         <is>
-          <t>Net Advertising Services 80%; Paid Services 20%</t>
+          <t>Software 78%; Drug Discovery 22%</t>
         </is>
       </c>
       <c r="V90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W90" s="17" t="inlineStr">
+        <is>
+          <t>US 60%; EMEA 29%; APAC 10%</t>
+        </is>
+      </c>
       <c r="X90" s="15" t="inlineStr">
         <is>
-          <t>Paid Services +107%</t>
+          <t>Drug Discovery +107%</t>
         </is>
       </c>
       <c r="Y90" s="22" t="inlineStr">
@@ -59078,12 +59078,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>JEF</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Schrodinger, Inc.</t>
+          <t>Jefferies Financial Group Inc.</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
@@ -59093,84 +59093,74 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F91" s="18" t="n">
-        <v>1422803200</v>
+        <v>10568248320</v>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H91" s="20" t="n">
+        <v>-37.43331715008421</v>
+      </c>
+      <c r="I91" s="20" t="n">
+        <v>27.1789460083687</v>
       </c>
       <c r="J91" s="20" t="n">
-        <v>4.213558</v>
+        <v>1.0001347</v>
       </c>
       <c r="K91" s="20" t="n">
-        <v>5.4927063</v>
+        <v>1.9561423</v>
       </c>
       <c r="L91" s="21" t="n">
-        <v>-8.66829141064739</v>
-      </c>
-      <c r="M91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>16.83374525401008</v>
+      </c>
+      <c r="M91" s="21" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N91" s="21" t="n">
+        <v>-0.21791453369172</v>
       </c>
       <c r="O91" s="21" t="n">
-        <v>-84.61893927057798</v>
-      </c>
-      <c r="P91" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.51745776158655</v>
+      </c>
+      <c r="P91" s="20" t="n">
+        <v>-80.28756909079929</v>
       </c>
       <c r="Q91" s="21" t="n">
-        <v>-4.52</v>
+        <v>7.7</v>
       </c>
       <c r="R91" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S91" s="20" t="n">
-        <v>0.6564595481920475</v>
+        <v>0.8308945641579533</v>
       </c>
       <c r="T91" s="15" t="inlineStr">
         <is>
-          <t>Software (78%)</t>
+          <t>Investment Banking And (91%)</t>
         </is>
       </c>
       <c r="U91" s="17" t="inlineStr">
         <is>
-          <t>Software 78%; Drug Discovery 22%</t>
+          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
         </is>
       </c>
       <c r="V91" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W91" s="17" t="inlineStr">
         <is>
-          <t>US 60%; EMEA 29%; APAC 10%</t>
+          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
         </is>
       </c>
       <c r="X91" s="15" t="inlineStr">
         <is>
-          <t>Drug Discovery +107%</t>
+          <t>Investment Banking A +123%</t>
         </is>
       </c>
       <c r="Y91" s="22" t="inlineStr">
@@ -59183,11 +59173,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="AA91" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA91" s="24" t="inlineStr"/>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="13" t="n">
@@ -59195,12 +59181,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>ANNA</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc.</t>
+          <t>AleAnna Inc. Class A Common St</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
@@ -59210,74 +59196,72 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F92" s="18" t="n">
-        <v>10568248320</v>
-      </c>
-      <c r="G92" s="19" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>143290000</v>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H92" s="20" t="n">
-        <v>-37.43331715008421</v>
+        <v>8.568</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>27.1789460083687</v>
+        <v>18.421053</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>1.0001347</v>
+        <v>3.5425103</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>1.9561423</v>
+        <v>3.5894861</v>
       </c>
       <c r="L92" s="21" t="n">
-        <v>16.83374525401008</v>
-      </c>
-      <c r="M92" s="21" t="n">
-        <v>3.26</v>
+        <v>7.167953799986041</v>
+      </c>
+      <c r="M92" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N92" s="21" t="n">
-        <v>-0.21791453369172</v>
+        <v>1.46144795620644</v>
       </c>
       <c r="O92" s="21" t="n">
-        <v>5.51745776158655</v>
+        <v>39.48335699937504</v>
       </c>
       <c r="P92" s="20" t="n">
-        <v>-80.28756909079929</v>
+        <v>-1.974742069364569</v>
       </c>
       <c r="Q92" s="21" t="n">
-        <v>7.7</v>
+        <v>-7.69</v>
       </c>
       <c r="R92" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S92" s="20" t="n">
-        <v>0.8308945641579533</v>
+        <v>0.8097190789385638</v>
       </c>
       <c r="T92" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking And (91%)</t>
+          <t>Conventional (89%)</t>
         </is>
       </c>
       <c r="U92" s="17" t="inlineStr">
         <is>
-          <t>Investment Banking And Capital Markets 91%; Asset Management 9%</t>
+          <t>Conventional 89%; Renewable 11%</t>
         </is>
       </c>
       <c r="V92" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W92" s="17" t="inlineStr">
-        <is>
-          <t>Americas 71%; Europe And Middle East 22%; Asia Pacific 8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W92" s="17" t="n"/>
       <c r="X92" s="15" t="inlineStr">
         <is>
-          <t>Investment Banking A +123%</t>
+          <t>Conventional +186%</t>
         </is>
       </c>
       <c r="Y92" s="22" t="inlineStr">
@@ -59298,12 +59282,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>ANNA</t>
+          <t>LVWR</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>AleAnna Inc. Class A Common St</t>
+          <t>LiveWire Group Inc. Common Sto</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
@@ -59313,72 +59297,84 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F93" s="18" t="n">
-        <v>143290000</v>
-      </c>
-      <c r="G93" s="24" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-      <c r="H93" s="20" t="n">
-        <v>8.568</v>
-      </c>
-      <c r="I93" s="20" t="n">
-        <v>18.421053</v>
+        <v>234170208</v>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J93" s="20" t="n">
-        <v>3.5425103</v>
+        <v>19.655172</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>3.5894861</v>
+        <v>7.484824</v>
       </c>
       <c r="L93" s="21" t="n">
-        <v>7.167953799986041</v>
+        <v>-21.59336790483196</v>
       </c>
       <c r="M93" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="N93" s="21" t="n">
-        <v>1.46144795620644</v>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O93" s="21" t="n">
-        <v>39.48335699937504</v>
-      </c>
-      <c r="P93" s="20" t="n">
-        <v>-1.974742069364569</v>
+        <v>-207.6711628204309</v>
+      </c>
+      <c r="P93" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q93" s="21" t="n">
-        <v>-7.69</v>
+        <v>-76.64</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S93" s="20" t="n">
-        <v>0.8097190789385638</v>
+        <v>0.4547555777310531</v>
       </c>
       <c r="T93" s="15" t="inlineStr">
         <is>
-          <t>Conventional (89%)</t>
+          <t>STACYC (62%)</t>
         </is>
       </c>
       <c r="U93" s="17" t="inlineStr">
         <is>
-          <t>Conventional 89%; Renewable 11%</t>
+          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
         </is>
       </c>
       <c r="V93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="17" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="W93" s="17" t="inlineStr">
+        <is>
+          <t>US 74%; Non Us 24%; AT 2%</t>
+        </is>
+      </c>
       <c r="X93" s="15" t="inlineStr">
         <is>
-          <t>Conventional +186%</t>
+          <t>Electric Motorcycle +333%</t>
         </is>
       </c>
       <c r="Y93" s="22" t="inlineStr">
@@ -59399,12 +59395,12 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>LVWR</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>LiveWire Group Inc. Common Sto</t>
+          <t>Assured Guaranty Ltd</t>
         </is>
       </c>
       <c r="D94" s="16" t="inlineStr">
@@ -59414,11 +59410,11 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F94" s="18" t="n">
-        <v>234170208</v>
+        <v>3207403776</v>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
@@ -59430,24 +59426,20 @@
           <t>–</t>
         </is>
       </c>
-      <c r="I94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="I94" s="20" t="n">
+        <v>9.698138</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>19.655172</v>
+        <v>0.57766795</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>7.484824</v>
+        <v>2.931813323583181</v>
       </c>
       <c r="L94" s="21" t="n">
-        <v>-21.59336790483196</v>
-      </c>
-      <c r="M94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.10162806517815</v>
+      </c>
+      <c r="M94" s="21" t="n">
+        <v>1.91</v>
       </c>
       <c r="N94" s="22" t="inlineStr">
         <is>
@@ -59455,7 +59447,7 @@
         </is>
       </c>
       <c r="O94" s="21" t="n">
-        <v>-207.6711628204309</v>
+        <v>0</v>
       </c>
       <c r="P94" s="22" t="inlineStr">
         <is>
@@ -59463,48 +59455,48 @@
         </is>
       </c>
       <c r="Q94" s="21" t="n">
-        <v>-76.64</v>
+        <v>-4.7</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S94" s="20" t="n">
-        <v>0.4547555777310531</v>
+        <v>0.9375650364203956</v>
       </c>
       <c r="T94" s="15" t="inlineStr">
         <is>
-          <t>STACYC (62%)</t>
+          <t>Insurance (97%)</t>
         </is>
       </c>
       <c r="U94" s="17" t="inlineStr">
         <is>
-          <t>STACYC 62%; Electric Motorcycle 19%; Electronic Motor Cycle 19%</t>
+          <t>Insurance 97%; Asset Management 3%</t>
         </is>
       </c>
       <c r="V94" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W94" s="17" t="inlineStr">
         <is>
-          <t>US 74%; Non Us 24%; AT 2%</t>
+          <t>US 77%; BM 18%; GB 5%</t>
         </is>
       </c>
       <c r="X94" s="15" t="inlineStr">
         <is>
-          <t>Electric Motorcycle +333%</t>
-        </is>
-      </c>
-      <c r="Y94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z94" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA94" s="24" t="inlineStr"/>
+          <t>Asset Management +190%</t>
+        </is>
+      </c>
+      <c r="Y94" s="21" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="Z94" s="20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AA94" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="13" t="n">
@@ -59512,12 +59504,12 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>KTB</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd</t>
+          <t>Kontoor Brands, Inc.</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
@@ -59527,93 +59519,87 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F95" s="18" t="n">
-        <v>3207403776</v>
+        <v>3641024256</v>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H95" s="20" t="n">
+        <v>11.55529127502649</v>
       </c>
       <c r="I95" s="20" t="n">
-        <v>9.698138</v>
+        <v>13.48583</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>0.57766795</v>
+        <v>5.8861995</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>2.931813323583181</v>
+        <v>1.0601529</v>
       </c>
       <c r="L95" s="21" t="n">
-        <v>10.10162806517815</v>
+        <v>10.52193541631924</v>
       </c>
       <c r="M95" s="21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="N95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.91957418972506</v>
+      </c>
+      <c r="N95" s="21" t="n">
+        <v>17.92240674479327</v>
       </c>
       <c r="O95" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>13.30013869457824</v>
+      </c>
+      <c r="P95" s="20" t="n">
+        <v>2.601238735236491</v>
       </c>
       <c r="Q95" s="21" t="n">
-        <v>-4.7</v>
+        <v>-7.049999999999999</v>
       </c>
       <c r="R95" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S95" s="20" t="n">
+        <v>0.4547588013008751</v>
+      </c>
+      <c r="T95" s="15" t="inlineStr">
+        <is>
+          <t>Wrangler (61%)</t>
+        </is>
+      </c>
+      <c r="U95" s="17" t="inlineStr">
+        <is>
+          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+        </is>
+      </c>
+      <c r="V95" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S95" s="20" t="n">
-        <v>0.9375650364203956</v>
-      </c>
-      <c r="T95" s="15" t="inlineStr">
-        <is>
-          <t>Insurance (97%)</t>
-        </is>
-      </c>
-      <c r="U95" s="17" t="inlineStr">
-        <is>
-          <t>Insurance 97%; Asset Management 3%</t>
-        </is>
-      </c>
-      <c r="V95" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="W95" s="17" t="inlineStr">
         <is>
-          <t>US 77%; BM 18%; GB 5%</t>
+          <t>US 73%; Non Us 27%</t>
         </is>
       </c>
       <c r="X95" s="15" t="inlineStr">
         <is>
-          <t>Asset Management +190%</t>
-        </is>
-      </c>
-      <c r="Y95" s="21" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="Z95" s="20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AA95" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Helly Hansen +300%</t>
+        </is>
+      </c>
+      <c r="Y95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z95" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA95" s="24" t="inlineStr"/>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="13" t="n">
@@ -59621,12 +59607,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>KTB</t>
+          <t>PED</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Kontoor Brands, Inc.</t>
+          <t>PEDEVCO Corp.</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
@@ -59636,11 +59622,11 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F96" s="18" t="n">
-        <v>3641024256</v>
+        <v>197253472</v>
       </c>
       <c r="G96" s="19" t="inlineStr">
         <is>
@@ -59648,62 +59634,62 @@
         </is>
       </c>
       <c r="H96" s="20" t="n">
-        <v>11.55529127502649</v>
-      </c>
-      <c r="I96" s="20" t="n">
-        <v>13.48583</v>
+        <v>4.59</v>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J96" s="20" t="n">
-        <v>5.8861995</v>
+        <v>0.9859154999999999</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1.0601529</v>
+        <v>1.6949378</v>
       </c>
       <c r="L96" s="21" t="n">
-        <v>10.52193541631924</v>
-      </c>
-      <c r="M96" s="21" t="n">
-        <v>2.91957418972506</v>
+        <v>16.30471233572627</v>
+      </c>
+      <c r="M96" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N96" s="21" t="n">
-        <v>17.92240674479327</v>
+        <v>2.16353455637511</v>
       </c>
       <c r="O96" s="21" t="n">
-        <v>13.30013869457824</v>
+        <v>49.94500678822457</v>
       </c>
       <c r="P96" s="20" t="n">
-        <v>2.601238735236491</v>
+        <v>1.332008602150538</v>
       </c>
       <c r="Q96" s="21" t="n">
-        <v>-7.049999999999999</v>
+        <v>18.91</v>
       </c>
       <c r="R96" s="18" t="n">
         <v>3</v>
       </c>
       <c r="S96" s="20" t="n">
-        <v>0.4547588013008751</v>
+        <v>0.7805028355388554</v>
       </c>
       <c r="T96" s="15" t="inlineStr">
         <is>
-          <t>Wrangler (61%)</t>
+          <t>Oil Sales (88%)</t>
         </is>
       </c>
       <c r="U96" s="17" t="inlineStr">
         <is>
-          <t>Wrangler 61%; Lee 24%; Helly Hansen 15%</t>
+          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
         </is>
       </c>
       <c r="V96" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W96" s="17" t="inlineStr">
-        <is>
-          <t>US 73%; Non Us 27%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W96" s="17" t="n"/>
       <c r="X96" s="15" t="inlineStr">
         <is>
-          <t>Helly Hansen +300%</t>
+          <t>Natural Gas Liquids  +465%</t>
         </is>
       </c>
       <c r="Y96" s="22" t="inlineStr">
@@ -59724,12 +59710,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>PED</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>PEDEVCO Corp.</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="D97" s="16" t="inlineStr">
@@ -59739,11 +59725,11 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F97" s="18" t="n">
-        <v>197253472</v>
+        <v>1101452017664</v>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
@@ -59751,75 +59737,75 @@
         </is>
       </c>
       <c r="H97" s="20" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I97" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>15.852</v>
+      </c>
+      <c r="I97" s="20" t="n">
+        <v>22.024843</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>0.9859154999999999</v>
+        <v>10.93157</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>1.6949378</v>
+        <v>12.20121</v>
       </c>
       <c r="L97" s="21" t="n">
-        <v>16.30471233572627</v>
-      </c>
-      <c r="M97" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>2.27953325914988</v>
+      </c>
+      <c r="M97" s="21" t="n">
+        <v>0.05</v>
       </c>
       <c r="N97" s="21" t="n">
-        <v>2.16353455637511</v>
+        <v>38.68963277836816</v>
       </c>
       <c r="O97" s="21" t="n">
-        <v>49.94500678822457</v>
+        <v>63.47412363053029</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.332008602150538</v>
+        <v>-0.1351809304997128</v>
       </c>
       <c r="Q97" s="21" t="n">
-        <v>18.91</v>
+        <v>354.75</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S97" s="20" t="n">
-        <v>0.7805028355388554</v>
+        <v>0.2853460159862896</v>
       </c>
       <c r="T97" s="15" t="inlineStr">
         <is>
-          <t>Oil Sales (88%)</t>
+          <t>CMBU (36%)</t>
         </is>
       </c>
       <c r="U97" s="17" t="inlineStr">
         <is>
-          <t>Oil Sales 88%; Natural Gas Liquids Sales 6%; Natural Gas Sales 6%</t>
+          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
         </is>
       </c>
       <c r="V97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="17" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="W97" s="17" t="inlineStr">
+        <is>
+          <t>US 65%; TW 15%; CN 7%</t>
+        </is>
+      </c>
       <c r="X97" s="15" t="inlineStr">
         <is>
-          <t>Natural Gas Liquids  +465%</t>
-        </is>
-      </c>
-      <c r="Y97" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z97" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA97" s="24" t="inlineStr"/>
+          <t>AEBU +311%</t>
+        </is>
+      </c>
+      <c r="Y97" s="21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z97" s="20" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AA97" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="13" t="n">
@@ -59827,12 +59813,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>EVC</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Entravision Communications Cor</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
@@ -59842,11 +59828,11 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t xml:space="preserve">Communication </t>
         </is>
       </c>
       <c r="F98" s="18" t="n">
-        <v>1101452017664</v>
+        <v>794602240</v>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
@@ -59854,69 +59840,69 @@
         </is>
       </c>
       <c r="H98" s="20" t="n">
-        <v>15.852</v>
+        <v>27.53410143448773</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>22.024843</v>
+        <v>190.0388450278689</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>10.93157</v>
+        <v>9.503311</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>12.20121</v>
+        <v>1.557472534580458</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>2.27953325914988</v>
+        <v>8.44176513325125</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>0.05</v>
+        <v>2.57525386044693</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>38.68963277836816</v>
+        <v>-26.42668897457025</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>63.47412363053029</v>
+        <v>6.53133066895079</v>
       </c>
       <c r="P98" s="20" t="n">
-        <v>-0.1351809304997128</v>
+        <v>2.821679370986135</v>
       </c>
       <c r="Q98" s="21" t="n">
-        <v>354.75</v>
+        <v>322.51</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S98" s="20" t="n">
-        <v>0.2853460159862896</v>
+        <v>0.5221821576458947</v>
       </c>
       <c r="T98" s="15" t="inlineStr">
         <is>
-          <t>CMBU (36%)</t>
+          <t>Advertising Technology (61%)</t>
         </is>
       </c>
       <c r="U98" s="17" t="inlineStr">
         <is>
-          <t>CMBU 36%; MCBU 32%; CDBU 19%</t>
+          <t>Advertising Technology And Services 61%; Media 39%</t>
         </is>
       </c>
       <c r="V98" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W98" s="17" t="inlineStr">
         <is>
-          <t>US 65%; TW 15%; CN 7%</t>
+          <t>US 58%; Non Us 42%</t>
         </is>
       </c>
       <c r="X98" s="15" t="inlineStr">
         <is>
-          <t>AEBU +311%</t>
+          <t>Advertising Technolo +230%</t>
         </is>
       </c>
       <c r="Y98" s="21" t="n">
-        <v>2.39</v>
+        <v>6.79</v>
       </c>
       <c r="Z98" s="20" t="n">
-        <v>0.263</v>
+        <v>2.2707</v>
       </c>
       <c r="AA98" s="24" t="inlineStr">
         <is>
@@ -59930,12 +59916,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>EVC</t>
+          <t>COMP</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Entravision Communications Cor</t>
+          <t>Compass, Inc.</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
@@ -59945,11 +59931,11 @@
       </c>
       <c r="E99" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Communication </t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F99" s="18" t="n">
-        <v>794602240</v>
+        <v>8067944960</v>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
@@ -59957,75 +59943,75 @@
         </is>
       </c>
       <c r="H99" s="20" t="n">
-        <v>27.53410143448773</v>
+        <v>120.5991376271186</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>190.0388450278689</v>
+        <v>119.5251105185185</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>9.503311</v>
+        <v>2.6573958</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>1.557472534580458</v>
+        <v>1.012822938060207</v>
       </c>
       <c r="L99" s="21" t="n">
-        <v>8.44176513325125</v>
-      </c>
-      <c r="M99" s="21" t="n">
-        <v>2.57525386044693</v>
+        <v>1.5004325303195</v>
+      </c>
+      <c r="M99" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N99" s="21" t="n">
-        <v>-26.42668897457025</v>
+        <v>-6.802410518626729</v>
       </c>
       <c r="O99" s="21" t="n">
-        <v>6.53133066895079</v>
-      </c>
-      <c r="P99" s="20" t="n">
-        <v>2.821679370986135</v>
+        <v>1.1850661578247</v>
+      </c>
+      <c r="P99" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q99" s="21" t="n">
-        <v>322.51</v>
+        <v>44.23</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S99" s="20" t="n">
-        <v>0.5221821576458947</v>
+        <v>0.8491346718272323</v>
       </c>
       <c r="T99" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technology (61%)</t>
+          <t>Brokerage (92%)</t>
         </is>
       </c>
       <c r="U99" s="17" t="inlineStr">
         <is>
-          <t>Advertising Technology And Services 61%; Media 39%</t>
+          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
         </is>
       </c>
       <c r="V99" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W99" s="17" t="inlineStr">
-        <is>
-          <t>US 58%; Non Us 42%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W99" s="17" t="n"/>
       <c r="X99" s="15" t="inlineStr">
         <is>
-          <t>Advertising Technolo +230%</t>
-        </is>
-      </c>
-      <c r="Y99" s="21" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="Z99" s="20" t="n">
-        <v>2.2707</v>
-      </c>
-      <c r="AA99" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Brokerage +97%</t>
+        </is>
+      </c>
+      <c r="Y99" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z99" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA99" s="24" t="inlineStr"/>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="13" t="n">
@@ -60033,12 +60019,12 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>COMP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Compass, Inc.</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="D100" s="16" t="inlineStr">
@@ -60048,11 +60034,11 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F100" s="18" t="n">
-        <v>8067944960</v>
+        <v>419900817408</v>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
@@ -60060,53 +60046,49 @@
         </is>
       </c>
       <c r="H100" s="20" t="n">
-        <v>120.5991376271186</v>
+        <v>8.913</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>119.5251105185185</v>
+        <v>20.62235</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>2.6573958</v>
+        <v>2.2113636</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1.012822938060207</v>
+        <v>2.0054102</v>
       </c>
       <c r="L100" s="21" t="n">
-        <v>1.5004325303195</v>
-      </c>
-      <c r="M100" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.60132683312082</v>
+      </c>
+      <c r="M100" s="21" t="n">
+        <v>4.16</v>
       </c>
       <c r="N100" s="21" t="n">
-        <v>-6.802410518626729</v>
+        <v>8.69285484505129</v>
       </c>
       <c r="O100" s="21" t="n">
-        <v>1.1850661578247</v>
-      </c>
-      <c r="P100" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.36304851872374</v>
+      </c>
+      <c r="P100" s="20" t="n">
+        <v>0.9647582391147462</v>
       </c>
       <c r="Q100" s="21" t="n">
-        <v>44.23</v>
+        <v>37.47</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S100" s="20" t="n">
-        <v>0.8491346718272323</v>
+        <v>0.9067367242961308</v>
       </c>
       <c r="T100" s="15" t="inlineStr">
         <is>
-          <t>Brokerage (92%)</t>
+          <t>Upstream (95%)</t>
         </is>
       </c>
       <c r="U100" s="17" t="inlineStr">
         <is>
-          <t>Brokerage 92%; Integrated Services 5%; Franchise 3%</t>
+          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
         </is>
       </c>
       <c r="V100" s="18" t="n">
@@ -60115,7 +60097,7 @@
       <c r="W100" s="17" t="n"/>
       <c r="X100" s="15" t="inlineStr">
         <is>
-          <t>Brokerage +97%</t>
+          <t>Upstream +298%</t>
         </is>
       </c>
       <c r="Y100" s="22" t="inlineStr">
@@ -60136,12 +60118,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Northrop Grumman Corp.</t>
         </is>
       </c>
       <c r="D101" s="16" t="inlineStr">
@@ -60151,11 +60133,11 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F101" s="18" t="n">
-        <v>419900817408</v>
+        <v>73726443520</v>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
@@ -60163,69 +60145,69 @@
         </is>
       </c>
       <c r="H101" s="20" t="n">
-        <v>8.913</v>
+        <v>15.61168969542968</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>20.62235</v>
+        <v>16.501429</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>2.2113636</v>
+        <v>4.1224737</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>2.0054102</v>
+        <v>1.7188857</v>
       </c>
       <c r="L101" s="21" t="n">
-        <v>6.60132683312082</v>
+        <v>4.9836238568399</v>
       </c>
       <c r="M101" s="21" t="n">
-        <v>4.16</v>
+        <v>1.505494379293</v>
       </c>
       <c r="N101" s="21" t="n">
-        <v>8.69285484505129</v>
+        <v>14.00609392594555</v>
       </c>
       <c r="O101" s="21" t="n">
-        <v>22.36304851872374</v>
+        <v>13.37597658555007</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>0.9647582391147462</v>
+        <v>2.307923063349215</v>
       </c>
       <c r="Q101" s="21" t="n">
-        <v>37.47</v>
+        <v>-10.3</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S101" s="20" t="n">
-        <v>0.9067367242961308</v>
+        <v>0.4182092579820682</v>
       </c>
       <c r="T101" s="15" t="inlineStr">
         <is>
-          <t>Upstream (95%)</t>
+          <t>Mission Systems (58%)</t>
         </is>
       </c>
       <c r="U101" s="17" t="inlineStr">
         <is>
-          <t>Upstream 95%; Reportable Segment Aggregation Before Other Operating 5%</t>
+          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
         </is>
       </c>
       <c r="V101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="17" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="W101" s="17" t="inlineStr">
+        <is>
+          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
+        </is>
+      </c>
       <c r="X101" s="15" t="inlineStr">
         <is>
-          <t>Upstream +298%</t>
-        </is>
-      </c>
-      <c r="Y101" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z101" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Aeronautics Systems +130%</t>
+        </is>
+      </c>
+      <c r="Y101" s="21" t="n">
+        <v>-17.49</v>
+      </c>
+      <c r="Z101" s="20" t="n">
+        <v>-1.1435</v>
       </c>
       <c r="AA101" s="24" t="inlineStr"/>
     </row>
@@ -60235,12 +60217,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>JBI</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp.</t>
+          <t>Janus International Group, Inc</t>
         </is>
       </c>
       <c r="D102" s="16" t="inlineStr">
@@ -60254,7 +60236,7 @@
         </is>
       </c>
       <c r="F102" s="18" t="n">
-        <v>73726443520</v>
+        <v>626240320</v>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
@@ -60262,69 +60244,75 @@
         </is>
       </c>
       <c r="H102" s="20" t="n">
-        <v>15.61168969542968</v>
+        <v>7.682</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>16.501429</v>
+        <v>19.125002</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>4.1224737</v>
+        <v>1.0949428</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>1.7188857</v>
+        <v>0.6944337</v>
       </c>
       <c r="L102" s="21" t="n">
-        <v>4.9836238568399</v>
-      </c>
-      <c r="M102" s="21" t="n">
-        <v>1.505494379293</v>
+        <v>11.5960907053962</v>
+      </c>
+      <c r="M102" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N102" s="21" t="n">
-        <v>14.00609392594555</v>
+        <v>10.43425814234016</v>
       </c>
       <c r="O102" s="21" t="n">
-        <v>13.37597658555007</v>
+        <v>16.54553713377242</v>
       </c>
       <c r="P102" s="20" t="n">
-        <v>2.307923063349215</v>
+        <v>2.983527796842828</v>
       </c>
       <c r="Q102" s="21" t="n">
-        <v>-10.3</v>
+        <v>-46.98</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S102" s="20" t="n">
-        <v>0.4182092579820682</v>
+        <v>0.6354742392804635</v>
       </c>
       <c r="T102" s="15" t="inlineStr">
         <is>
-          <t>Mission Systems (58%)</t>
+          <t>Janus North America (76%)</t>
         </is>
       </c>
       <c r="U102" s="17" t="inlineStr">
         <is>
-          <t>Mission Systems 58%; Defense Systems 26%; Aeronautics Systems 11%</t>
+          <t>Janus North America 76%; Janus International 24%</t>
         </is>
       </c>
       <c r="V102" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W102" s="17" t="inlineStr">
         <is>
-          <t>US 86%; Europe 8%; Asia Pacific 5%</t>
+          <t>US 88%; Non Us 12%</t>
         </is>
       </c>
       <c r="X102" s="15" t="inlineStr">
         <is>
-          <t>Aeronautics Systems +130%</t>
-        </is>
-      </c>
-      <c r="Y102" s="21" t="n">
-        <v>-17.49</v>
-      </c>
-      <c r="Z102" s="20" t="n">
-        <v>-1.1435</v>
+          <t>Janus International +300%</t>
+        </is>
+      </c>
+      <c r="Y102" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z102" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA102" s="24" t="inlineStr"/>
     </row>
@@ -60334,12 +60322,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>JBI</t>
+          <t>FTK</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Janus International Group, Inc</t>
+          <t>Flotek Industries, Inc.</t>
         </is>
       </c>
       <c r="D103" s="16" t="inlineStr">
@@ -60349,11 +60337,11 @@
       </c>
       <c r="E103" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F103" s="18" t="n">
-        <v>626240320</v>
+        <v>989904320</v>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
@@ -60361,19 +60349,19 @@
         </is>
       </c>
       <c r="H103" s="20" t="n">
-        <v>7.682</v>
+        <v>25.626</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>19.125002</v>
+        <v>27.059406</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>1.0949428</v>
+        <v>7.6511755</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>0.6944337</v>
+        <v>3.3788822</v>
       </c>
       <c r="L103" s="21" t="n">
-        <v>11.5960907053962</v>
+        <v>-0.34082822017504</v>
       </c>
       <c r="M103" s="22" t="inlineStr">
         <is>
@@ -60381,57 +60369,59 @@
         </is>
       </c>
       <c r="N103" s="21" t="n">
-        <v>10.43425814234016</v>
+        <v>16.13992919089226</v>
       </c>
       <c r="O103" s="21" t="n">
-        <v>16.54553713377242</v>
+        <v>17.18227107585707</v>
       </c>
       <c r="P103" s="20" t="n">
-        <v>2.983527796842828</v>
+        <v>0.8771800721171535</v>
       </c>
       <c r="Q103" s="21" t="n">
-        <v>-46.98</v>
+        <v>35.99</v>
       </c>
       <c r="R103" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S103" s="20" t="n">
-        <v>0.6354742392804635</v>
+        <v>0.7993939775957156</v>
       </c>
       <c r="T103" s="15" t="inlineStr">
         <is>
-          <t>Janus North America (76%)</t>
+          <t>Chemistry Technologies (89%)</t>
         </is>
       </c>
       <c r="U103" s="17" t="inlineStr">
         <is>
-          <t>Janus North America 76%; Janus International 24%</t>
+          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
         </is>
       </c>
       <c r="V103" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W103" s="17" t="inlineStr">
         <is>
-          <t>US 88%; Non Us 12%</t>
+          <t>US 95%; AE 4%; Non Us 1%</t>
         </is>
       </c>
       <c r="X103" s="15" t="inlineStr">
         <is>
-          <t>Janus International +300%</t>
-        </is>
-      </c>
-      <c r="Y103" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Data Analytics +115%</t>
+        </is>
+      </c>
+      <c r="Y103" s="21" t="n">
+        <v>162.68</v>
       </c>
       <c r="Z103" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="AA103" s="24" t="inlineStr"/>
+      <c r="AA103" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="13" t="n">
@@ -60439,12 +60429,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>FTK</t>
+          <t>RGLD</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Flotek Industries, Inc.</t>
+          <t>Royal Gold, Inc.</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
@@ -60454,11 +60444,11 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F104" s="18" t="n">
-        <v>989904320</v>
+        <v>21375143936</v>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
@@ -60466,79 +60456,75 @@
         </is>
       </c>
       <c r="H104" s="20" t="n">
-        <v>25.626</v>
+        <v>17.093</v>
       </c>
       <c r="I104" s="20" t="n">
-        <v>27.059406</v>
+        <v>27.90708</v>
       </c>
       <c r="J104" s="20" t="n">
-        <v>7.6511755</v>
+        <v>2.8154993</v>
       </c>
       <c r="K104" s="20" t="n">
-        <v>3.3788822</v>
+        <v>13.9189825</v>
       </c>
       <c r="L104" s="21" t="n">
-        <v>-0.34082822017504</v>
-      </c>
-      <c r="M104" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.00273682367590865</v>
+      </c>
+      <c r="M104" s="21" t="n">
+        <v>0.91</v>
       </c>
       <c r="N104" s="21" t="n">
-        <v>16.13992919089226</v>
+        <v>10.262897771322</v>
       </c>
       <c r="O104" s="21" t="n">
-        <v>17.18227107585707</v>
+        <v>79.09251477040698</v>
       </c>
       <c r="P104" s="20" t="n">
-        <v>0.8771800721171535</v>
+        <v>0.3499720252373015</v>
       </c>
       <c r="Q104" s="21" t="n">
-        <v>35.99</v>
+        <v>50.91</v>
       </c>
       <c r="R104" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S104" s="20" t="n">
-        <v>0.7993939775957156</v>
+        <v>0.5688010724435794</v>
       </c>
       <c r="T104" s="15" t="inlineStr">
         <is>
-          <t>Chemistry Technologies (89%)</t>
+          <t>Royalty Interest (69%)</t>
         </is>
       </c>
       <c r="U104" s="17" t="inlineStr">
         <is>
-          <t>Chemistry Technologies 89%; Data Analytics 11%</t>
+          <t>Royalty Interest 69%; Stream Interest 31%</t>
         </is>
       </c>
       <c r="V104" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W104" s="17" t="inlineStr">
         <is>
-          <t>US 95%; AE 4%; Non Us 1%</t>
+          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
         </is>
       </c>
       <c r="X104" s="15" t="inlineStr">
         <is>
-          <t>Data Analytics +115%</t>
-        </is>
-      </c>
-      <c r="Y104" s="21" t="n">
-        <v>162.68</v>
+          <t>Stream Interest +133%</t>
+        </is>
+      </c>
+      <c r="Y104" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Z104" s="22" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="AA104" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA104" s="24" t="inlineStr"/>
     </row>
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="13" t="n">
@@ -60546,12 +60532,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Royal Gold, Inc.</t>
+          <t>Riot Blockchain, Inc.</t>
         </is>
       </c>
       <c r="D105" s="16" t="inlineStr">
@@ -60561,74 +60547,76 @@
       </c>
       <c r="E105" s="17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Te</t>
         </is>
       </c>
       <c r="F105" s="18" t="n">
-        <v>21375143936</v>
+        <v>8056809472</v>
       </c>
       <c r="G105" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H105" s="20" t="n">
-        <v>17.093</v>
-      </c>
-      <c r="I105" s="20" t="n">
-        <v>27.90708</v>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J105" s="20" t="n">
-        <v>2.8154993</v>
+        <v>3.7017238</v>
       </c>
       <c r="K105" s="20" t="n">
-        <v>13.9189825</v>
+        <v>11.944614</v>
       </c>
       <c r="L105" s="21" t="n">
-        <v>0.00273682367590865</v>
+        <v>-6.33617127278794</v>
       </c>
       <c r="M105" s="21" t="n">
-        <v>0.91</v>
+        <v>0.10325461151742</v>
       </c>
       <c r="N105" s="21" t="n">
-        <v>10.262897771322</v>
+        <v>-14.43474531538664</v>
       </c>
       <c r="O105" s="21" t="n">
-        <v>79.09251477040698</v>
-      </c>
-      <c r="P105" s="20" t="n">
-        <v>0.3499720252373015</v>
+        <v>-137.6062161413327</v>
+      </c>
+      <c r="P105" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q105" s="21" t="n">
-        <v>50.91</v>
+        <v>10.21</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S105" s="20" t="n">
-        <v>0.5688010724435794</v>
+        <v>0.4395096928547909</v>
       </c>
       <c r="T105" s="15" t="inlineStr">
         <is>
-          <t>Royalty Interest (69%)</t>
+          <t>Reportable Segment Agg (50%)</t>
         </is>
       </c>
       <c r="U105" s="17" t="inlineStr">
         <is>
-          <t>Royalty Interest 69%; Stream Interest 31%</t>
+          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
         </is>
       </c>
       <c r="V105" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W105" s="17" t="inlineStr">
-        <is>
-          <t>North America 77%; AU 12%; South And Central Amercia 11%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W105" s="17" t="n"/>
       <c r="X105" s="15" t="inlineStr">
         <is>
-          <t>Stream Interest +133%</t>
+          <t>Engineering +196%</t>
         </is>
       </c>
       <c r="Y105" s="22" t="inlineStr">
@@ -60641,7 +60629,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="AA105" s="24" t="inlineStr"/>
+      <c r="AA105" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="13" t="n">
@@ -60649,12 +60641,12 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Riot Blockchain, Inc.</t>
+          <t>Motorola Solutions, Inc.</t>
         </is>
       </c>
       <c r="D106" s="16" t="inlineStr">
@@ -60668,89 +60660,79 @@
         </is>
       </c>
       <c r="F106" s="18" t="n">
-        <v>8056809472</v>
+        <v>77146587136</v>
       </c>
       <c r="G106" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H106" s="20" t="n">
+        <v>29.95255477105907</v>
+      </c>
+      <c r="I106" s="20" t="n">
+        <v>36.676632</v>
       </c>
       <c r="J106" s="20" t="n">
-        <v>3.7017238</v>
+        <v>28.873335</v>
       </c>
       <c r="K106" s="20" t="n">
-        <v>11.944614</v>
+        <v>6.304371</v>
       </c>
       <c r="L106" s="21" t="n">
-        <v>-6.33617127278794</v>
+        <v>3.45600557054743</v>
       </c>
       <c r="M106" s="21" t="n">
-        <v>0.10325461151742</v>
+        <v>1.11367051765181</v>
       </c>
       <c r="N106" s="21" t="n">
-        <v>-14.43474531538664</v>
+        <v>24.18337569424833</v>
       </c>
       <c r="O106" s="21" t="n">
-        <v>-137.6062161413327</v>
-      </c>
-      <c r="P106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>24.10684192787327</v>
+      </c>
+      <c r="P106" s="20" t="n">
+        <v>2.823837818944425</v>
       </c>
       <c r="Q106" s="21" t="n">
-        <v>10.21</v>
+        <v>16.12</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S106" s="20" t="n">
-        <v>0.4395096928547909</v>
+        <v>0.5307180948206589</v>
       </c>
       <c r="T106" s="15" t="inlineStr">
         <is>
-          <t>Reportable Segment Agg (50%)</t>
+          <t>Product And Systems In (62%)</t>
         </is>
       </c>
       <c r="U106" s="17" t="inlineStr">
         <is>
-          <t>Reportable Segment Aggregation Before Other Operating 50%; Bitcoin Mining 43%; E</t>
+          <t>Product And Systems Integration 62%; Services And Software 38%</t>
         </is>
       </c>
       <c r="V106" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" s="17" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="W106" s="17" t="inlineStr">
+        <is>
+          <t>North America 36%; US 34%; International 14%</t>
+        </is>
+      </c>
       <c r="X106" s="15" t="inlineStr">
         <is>
-          <t>Engineering +196%</t>
-        </is>
-      </c>
-      <c r="Y106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z106" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA106" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Product And Systems  +176%</t>
+        </is>
+      </c>
+      <c r="Y106" s="21" t="n">
+        <v>-39.24</v>
+      </c>
+      <c r="Z106" s="20" t="n">
+        <v>-1.7092</v>
+      </c>
+      <c r="AA106" s="24" t="inlineStr"/>
     </row>
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="13" t="n">
@@ -60758,12 +60740,12 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Motorola Solutions, Inc.</t>
+          <t>Firy Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D107" s="16" t="inlineStr">
@@ -60777,77 +60759,91 @@
         </is>
       </c>
       <c r="F107" s="18" t="n">
-        <v>77146587136</v>
+        <v>163180000</v>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H107" s="20" t="n">
-        <v>29.95255477105907</v>
-      </c>
-      <c r="I107" s="20" t="n">
-        <v>36.676632</v>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J107" s="20" t="n">
-        <v>28.873335</v>
+        <v>1.931855850736373</v>
       </c>
       <c r="K107" s="20" t="n">
-        <v>6.304371</v>
+        <v>1.3889787</v>
       </c>
       <c r="L107" s="21" t="n">
-        <v>3.45600557054743</v>
-      </c>
-      <c r="M107" s="21" t="n">
-        <v>1.11367051765181</v>
-      </c>
-      <c r="N107" s="21" t="n">
-        <v>24.18337569424833</v>
+        <v>-42.19957624057978</v>
+      </c>
+      <c r="M107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O107" s="21" t="n">
-        <v>24.10684192787327</v>
-      </c>
-      <c r="P107" s="20" t="n">
-        <v>2.823837818944425</v>
+        <v>-60.47052925589057</v>
+      </c>
+      <c r="P107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q107" s="21" t="n">
-        <v>16.12</v>
+        <v>51.65</v>
       </c>
       <c r="R107" s="18" t="n">
         <v>2</v>
       </c>
       <c r="S107" s="20" t="n">
-        <v>0.5307180948206589</v>
+        <v>0.619776729861528</v>
       </c>
       <c r="T107" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems In (62%)</t>
+          <t>Skillz (74%)</t>
         </is>
       </c>
       <c r="U107" s="17" t="inlineStr">
         <is>
-          <t>Product And Systems Integration 62%; Services And Software 38%</t>
+          <t>Skillz 74%; RZR 26%</t>
         </is>
       </c>
       <c r="V107" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W107" s="17" t="inlineStr">
         <is>
-          <t>North America 36%; US 34%; International 14%</t>
+          <t>US 76%; Non Us 6%; CY 4%</t>
         </is>
       </c>
       <c r="X107" s="15" t="inlineStr">
         <is>
-          <t>Product And Systems  +176%</t>
-        </is>
-      </c>
-      <c r="Y107" s="21" t="n">
-        <v>-39.24</v>
-      </c>
-      <c r="Z107" s="20" t="n">
-        <v>-1.7092</v>
+          <t>RZR +146%</t>
+        </is>
+      </c>
+      <c r="Y107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z107" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA107" s="24" t="inlineStr"/>
     </row>
@@ -60857,12 +60853,12 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Firy Inc. Class A Common Stock</t>
+          <t>Energy Transfer Lp</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
@@ -60872,84 +60868,70 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F108" s="18" t="n">
-        <v>163180000</v>
+        <v>74203103232</v>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H108" s="20" t="n">
+        <v>9.459</v>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>14.760273</v>
       </c>
       <c r="J108" s="20" t="n">
-        <v>1.931855850736373</v>
+        <v>1.491909508655528</v>
       </c>
       <c r="K108" s="20" t="n">
-        <v>1.3889787</v>
+        <v>0.69103926</v>
       </c>
       <c r="L108" s="21" t="n">
-        <v>-42.19957624057978</v>
-      </c>
-      <c r="M108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>7.04975512768092</v>
+      </c>
+      <c r="M108" s="21" t="n">
+        <v>6.959999999999999</v>
+      </c>
+      <c r="N108" s="21" t="n">
+        <v>8.4099490357427</v>
       </c>
       <c r="O108" s="21" t="n">
-        <v>-60.47052925589057</v>
-      </c>
-      <c r="P108" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>17.85263732142248</v>
+      </c>
+      <c r="P108" s="20" t="n">
+        <v>4.353514132925898</v>
       </c>
       <c r="Q108" s="21" t="n">
-        <v>51.65</v>
+        <v>37.32</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S108" s="20" t="n">
-        <v>0.619776729861528</v>
+        <v>0.2291888064107961</v>
       </c>
       <c r="T108" s="15" t="inlineStr">
         <is>
-          <t>Skillz (74%)</t>
+          <t>Crudeoiltransportation (27%)</t>
         </is>
       </c>
       <c r="U108" s="17" t="inlineStr">
         <is>
-          <t>Skillz 74%; RZR 26%</t>
+          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
         </is>
       </c>
       <c r="V108" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W108" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; Non Us 6%; CY 4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W108" s="17" t="n"/>
       <c r="X108" s="15" t="inlineStr">
         <is>
-          <t>RZR +146%</t>
+          <t>Investment In Sunoco +165%</t>
         </is>
       </c>
       <c r="Y108" s="22" t="inlineStr">
@@ -60970,12 +60952,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Energy Transfer Lp</t>
+          <t>Jd.Com, Inc.</t>
         </is>
       </c>
       <c r="D109" s="16" t="inlineStr">
@@ -60985,11 +60967,11 @@
       </c>
       <c r="E109" s="17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F109" s="18" t="n">
-        <v>74203103232</v>
+        <v>36544528384</v>
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
@@ -60997,49 +60979,49 @@
         </is>
       </c>
       <c r="H109" s="20" t="n">
-        <v>9.459</v>
+        <v>11.09408477609406</v>
       </c>
       <c r="I109" s="20" t="n">
-        <v>14.760273</v>
+        <v>16.7176140061608</v>
       </c>
       <c r="J109" s="20" t="n">
-        <v>1.491909508655528</v>
+        <v>7.683095555258829</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>0.69103926</v>
+        <v>0.1882403337093706</v>
       </c>
       <c r="L109" s="21" t="n">
-        <v>7.04975512768092</v>
+        <v>14.93799506720002</v>
       </c>
       <c r="M109" s="21" t="n">
-        <v>6.959999999999999</v>
+        <v>3.94</v>
       </c>
       <c r="N109" s="21" t="n">
-        <v>8.4099490357427</v>
+        <v>2.81257184190512</v>
       </c>
       <c r="O109" s="21" t="n">
-        <v>17.85263732142248</v>
+        <v>0.95674610170034</v>
       </c>
       <c r="P109" s="20" t="n">
-        <v>4.353514132925898</v>
+        <v>-9.862180948218128</v>
       </c>
       <c r="Q109" s="21" t="n">
-        <v>37.32</v>
+        <v>-11.42</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S109" s="20" t="n">
-        <v>0.2291888064107961</v>
+        <v>0.8099111106081265</v>
       </c>
       <c r="T109" s="15" t="inlineStr">
         <is>
-          <t>Crudeoiltransportation (27%)</t>
+          <t>Jd Retail (90%)</t>
         </is>
       </c>
       <c r="U109" s="17" t="inlineStr">
         <is>
-          <t>Crudeoiltransportationandservices 27%; Investment In Sunoco LP 26%; NG Landrefin</t>
+          <t>Jd Retail 90%; Jd Logistics 6%; New Business 4%</t>
         </is>
       </c>
       <c r="V109" s="18" t="n">
@@ -61048,13 +61030,11 @@
       <c r="W109" s="17" t="n"/>
       <c r="X109" s="15" t="inlineStr">
         <is>
-          <t>Investment In Sunoco +165%</t>
-        </is>
-      </c>
-      <c r="Y109" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>New Business +157%</t>
+        </is>
+      </c>
+      <c r="Y109" s="21" t="n">
+        <v>-79.69000000000001</v>
       </c>
       <c r="Z109" s="22" t="inlineStr">
         <is>
@@ -61069,12 +61049,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>BWXT</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Jd.Com, Inc.</t>
+          <t>BWX Technologies, Inc.</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
@@ -61084,11 +61064,11 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>Consumer Discr</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F110" s="18" t="n">
-        <v>36544528384</v>
+        <v>13754292224</v>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
@@ -61096,69 +61076,75 @@
         </is>
       </c>
       <c r="H110" s="20" t="n">
-        <v>11.09408477609406</v>
+        <v>31.828</v>
       </c>
       <c r="I110" s="20" t="n">
-        <v>16.7176140061608</v>
+        <v>38.891193</v>
       </c>
       <c r="J110" s="20" t="n">
-        <v>7.683095555258829</v>
+        <v>10.3069</v>
       </c>
       <c r="K110" s="20" t="n">
-        <v>0.1882403337093706</v>
+        <v>3.9141748</v>
       </c>
       <c r="L110" s="21" t="n">
-        <v>14.93799506720002</v>
+        <v>2.19383891609831</v>
       </c>
       <c r="M110" s="21" t="n">
-        <v>3.94</v>
+        <v>0.5030143835716</v>
       </c>
       <c r="N110" s="21" t="n">
-        <v>2.81257184190512</v>
+        <v>15.04279234978169</v>
       </c>
       <c r="O110" s="21" t="n">
-        <v>0.95674610170034</v>
+        <v>16.8479651603609</v>
       </c>
       <c r="P110" s="20" t="n">
-        <v>-9.862180948218128</v>
+        <v>2.646714786974468</v>
       </c>
       <c r="Q110" s="21" t="n">
-        <v>-11.42</v>
+        <v>-25.8</v>
       </c>
       <c r="R110" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" s="20" t="n">
+        <v>0.6174267863088643</v>
+      </c>
+      <c r="T110" s="15" t="inlineStr">
+        <is>
+          <t>Commercial Operations (74%)</t>
+        </is>
+      </c>
+      <c r="U110" s="17" t="inlineStr">
+        <is>
+          <t>Commercial Operations 74%; Government Operations 26%</t>
+        </is>
+      </c>
+      <c r="V110" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="S110" s="20" t="n">
-        <v>0.8099111106081265</v>
-      </c>
-      <c r="T110" s="15" t="inlineStr">
-        <is>
-          <t>Jd Retail (90%)</t>
-        </is>
-      </c>
-      <c r="U110" s="17" t="inlineStr">
-        <is>
-          <t>Jd Retail 90%; Jd Logistics 6%; New Business 4%</t>
-        </is>
-      </c>
-      <c r="V110" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" s="17" t="n"/>
+      <c r="W110" s="17" t="inlineStr">
+        <is>
+          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
+        </is>
+      </c>
       <c r="X110" s="15" t="inlineStr">
         <is>
-          <t>New Business +157%</t>
+          <t>Commercial Operation +143%</t>
         </is>
       </c>
       <c r="Y110" s="21" t="n">
-        <v>-79.69000000000001</v>
-      </c>
-      <c r="Z110" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="AA110" s="24" t="inlineStr"/>
+        <v>4.399999999999999</v>
+      </c>
+      <c r="Z110" s="20" t="n">
+        <v>1.1084</v>
+      </c>
+      <c r="AA110" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="13" t="n">
@@ -61166,12 +61152,12 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>BWXT</t>
+          <t>LGN</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>BWX Technologies, Inc.</t>
+          <t>Legence Corp.</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
@@ -61179,13 +61165,9 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E111" s="17" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+      <c r="E111" s="17" t="n"/>
       <c r="F111" s="18" t="n">
-        <v>13754292224</v>
+        <v>9306742784</v>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
@@ -61193,75 +61175,75 @@
         </is>
       </c>
       <c r="H111" s="20" t="n">
-        <v>31.828</v>
-      </c>
-      <c r="I111" s="20" t="n">
-        <v>38.891193</v>
+        <v>35.22426766420546</v>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="J111" s="20" t="n">
-        <v>10.3069</v>
+        <v>15.49927769737686</v>
       </c>
       <c r="K111" s="20" t="n">
-        <v>3.9141748</v>
+        <v>3.30888056840225</v>
       </c>
       <c r="L111" s="21" t="n">
-        <v>2.19383891609831</v>
-      </c>
-      <c r="M111" s="21" t="n">
-        <v>0.5030143835716</v>
+        <v>3.41438849489116</v>
+      </c>
+      <c r="M111" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N111" s="21" t="n">
-        <v>15.04279234978169</v>
+        <v>3.69186301129894</v>
       </c>
       <c r="O111" s="21" t="n">
-        <v>16.8479651603609</v>
+        <v>5.44599126235131</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>2.646714786974468</v>
+        <v>6.20894155127728</v>
       </c>
       <c r="Q111" s="21" t="n">
-        <v>-25.8</v>
+        <v>167.4754158395236</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S111" s="20" t="n">
-        <v>0.6174267863088643</v>
+        <v>0.2963256950273106</v>
       </c>
       <c r="T111" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operations (74%)</t>
+          <t>Installation Maintenan (36%)</t>
         </is>
       </c>
       <c r="U111" s="17" t="inlineStr">
         <is>
-          <t>Commercial Operations 74%; Government Operations 26%</t>
+          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
         </is>
       </c>
       <c r="V111" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W111" s="17" t="inlineStr">
-        <is>
-          <t>US 76%; CA 21%; Other Geographic Location 3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W111" s="17" t="n"/>
       <c r="X111" s="15" t="inlineStr">
         <is>
-          <t>Commercial Operation +143%</t>
-        </is>
-      </c>
-      <c r="Y111" s="21" t="n">
-        <v>4.399999999999999</v>
-      </c>
-      <c r="Z111" s="20" t="n">
-        <v>1.1084</v>
-      </c>
-      <c r="AA111" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Installation And Mai +162%</t>
+        </is>
+      </c>
+      <c r="Y111" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z111" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="AA111" s="24" t="inlineStr"/>
     </row>
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="13" t="n">
@@ -61269,12 +61251,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>LGN</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Legence Corp.</t>
+          <t>Gen Digital Inc. Common Stock</t>
         </is>
       </c>
       <c r="D112" s="16" t="inlineStr">
@@ -61282,9 +61264,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E112" s="17" t="n"/>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>Information Te</t>
+        </is>
+      </c>
       <c r="F112" s="18" t="n">
-        <v>9306742784</v>
+        <v>18113243136</v>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
@@ -61292,73 +61278,69 @@
         </is>
       </c>
       <c r="H112" s="20" t="n">
-        <v>35.22426766420546</v>
-      </c>
-      <c r="I112" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.614</v>
+      </c>
+      <c r="I112" s="20" t="n">
+        <v>17.695906</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>15.49927769737686</v>
+        <v>6.8245378</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>3.30888056840225</v>
+        <v>3.566301</v>
       </c>
       <c r="L112" s="21" t="n">
-        <v>3.41438849489116</v>
-      </c>
-      <c r="M112" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>10.13133216482446</v>
+      </c>
+      <c r="M112" s="21" t="n">
+        <v>2.07549286633304</v>
       </c>
       <c r="N112" s="21" t="n">
-        <v>3.69186301129894</v>
+        <v>20.39245863793767</v>
       </c>
       <c r="O112" s="21" t="n">
-        <v>5.44599126235131</v>
+        <v>51.45999999999999</v>
       </c>
       <c r="P112" s="20" t="n">
-        <v>6.20894155127728</v>
+        <v>3.02914885347843</v>
       </c>
       <c r="Q112" s="21" t="n">
-        <v>167.4754158395236</v>
+        <v>18.59</v>
       </c>
       <c r="R112" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" s="20" t="n">
+        <v>0.5563136799999999</v>
+      </c>
+      <c r="T112" s="15" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform (67%)</t>
+        </is>
+      </c>
+      <c r="U112" s="17" t="inlineStr">
+        <is>
+          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
+        </is>
+      </c>
+      <c r="V112" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="S112" s="20" t="n">
-        <v>0.2963256950273106</v>
-      </c>
-      <c r="T112" s="15" t="inlineStr">
-        <is>
-          <t>Installation Maintenan (36%)</t>
-        </is>
-      </c>
-      <c r="U112" s="17" t="inlineStr">
-        <is>
-          <t>Installation Maintenance 36%; Installation And Maintenance 36%; Engineering Cons</t>
-        </is>
-      </c>
-      <c r="V112" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" s="17" t="n"/>
+      <c r="W112" s="17" t="inlineStr">
+        <is>
+          <t>Americas 43%; US 40%; EMEA 13%</t>
+        </is>
+      </c>
       <c r="X112" s="15" t="inlineStr">
         <is>
-          <t>Installation And Mai +162%</t>
-        </is>
-      </c>
-      <c r="Y112" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="Z112" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Trust Based Solution +119%</t>
+        </is>
+      </c>
+      <c r="Y112" s="21" t="n">
+        <v>-20.77</v>
+      </c>
+      <c r="Z112" s="20" t="n">
+        <v>-0.8912</v>
       </c>
       <c r="AA112" s="24" t="inlineStr"/>
     </row>
@@ -61368,12 +61350,12 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>Gen Digital Inc. Common Stock</t>
+          <t>L3Harris Technologies, Inc.</t>
         </is>
       </c>
       <c r="D113" s="16" t="inlineStr">
@@ -61383,11 +61365,11 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>Information Te</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F113" s="18" t="n">
-        <v>18113243136</v>
+        <v>45723136000</v>
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
@@ -61395,71 +61377,75 @@
         </is>
       </c>
       <c r="H113" s="20" t="n">
-        <v>10.614</v>
+        <v>17.48068824615385</v>
       </c>
       <c r="I113" s="20" t="n">
-        <v>17.695906</v>
+        <v>24.776993</v>
       </c>
       <c r="J113" s="20" t="n">
-        <v>6.8245378</v>
+        <v>2.388963</v>
       </c>
       <c r="K113" s="20" t="n">
-        <v>3.566301</v>
+        <v>1.167926026207566</v>
       </c>
       <c r="L113" s="21" t="n">
-        <v>10.13133216482446</v>
+        <v>5.88004410889457</v>
       </c>
       <c r="M113" s="21" t="n">
-        <v>2.07549286633304</v>
+        <v>1.56571804266048</v>
       </c>
       <c r="N113" s="21" t="n">
-        <v>20.39245863793767</v>
+        <v>8.274248192518591</v>
       </c>
       <c r="O113" s="21" t="n">
-        <v>51.45999999999999</v>
+        <v>8.96574625150067</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>3.02914885347843</v>
+        <v>2.55014245014245</v>
       </c>
       <c r="Q113" s="21" t="n">
-        <v>18.59</v>
+        <v>-9.82</v>
       </c>
       <c r="R113" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="S113" s="20" t="n">
+        <v>0.3315167177024359</v>
+      </c>
+      <c r="T113" s="15" t="inlineStr">
+        <is>
+          <t>Communication Systems (42%)</t>
+        </is>
+      </c>
+      <c r="U113" s="17" t="inlineStr">
+        <is>
+          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
+        </is>
+      </c>
+      <c r="V113" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S113" s="20" t="n">
-        <v>0.5563136799999999</v>
-      </c>
-      <c r="T113" s="15" t="inlineStr">
-        <is>
-          <t>Cyber Safety Platform (67%)</t>
-        </is>
-      </c>
-      <c r="U113" s="17" t="inlineStr">
-        <is>
-          <t>Cyber Safety Platform 67%; Trust Based Solutions 33%</t>
-        </is>
-      </c>
-      <c r="V113" s="18" t="n">
-        <v>4</v>
-      </c>
       <c r="W113" s="17" t="inlineStr">
         <is>
-          <t>Americas 43%; US 40%; EMEA 13%</t>
+          <t>US 90%; Non Us 10%</t>
         </is>
       </c>
       <c r="X113" s="15" t="inlineStr">
         <is>
-          <t>Trust Based Solution +119%</t>
+          <t>Aerojet Rocketdyne +467%</t>
         </is>
       </c>
       <c r="Y113" s="21" t="n">
-        <v>-20.77</v>
+        <v>258.65</v>
       </c>
       <c r="Z113" s="20" t="n">
-        <v>-0.8912</v>
-      </c>
-      <c r="AA113" s="24" t="inlineStr"/>
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="AA113" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="13" t="n">
@@ -61467,12 +61453,12 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>L3Harris Technologies, Inc.</t>
+          <t>Brighthouse Financial, Inc.</t>
         </is>
       </c>
       <c r="D114" s="16" t="inlineStr">
@@ -61482,87 +61468,85 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F114" s="18" t="n">
-        <v>45723136000</v>
+        <v>2881904384</v>
       </c>
       <c r="G114" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H114" s="20" t="n">
-        <v>17.48068824615385</v>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="I114" s="20" t="n">
-        <v>24.776993</v>
+        <v>3.9738305</v>
       </c>
       <c r="J114" s="20" t="n">
-        <v>2.388963</v>
+        <v>0.4399589</v>
       </c>
       <c r="K114" s="20" t="n">
-        <v>1.167926026207566</v>
+        <v>0.4215159</v>
       </c>
       <c r="L114" s="21" t="n">
-        <v>5.88004410889457</v>
-      </c>
-      <c r="M114" s="21" t="n">
-        <v>1.56571804266048</v>
+        <v>-18.66821130454271</v>
+      </c>
+      <c r="M114" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="N114" s="21" t="n">
-        <v>8.274248192518591</v>
+        <v>0.007627959012433573</v>
       </c>
       <c r="O114" s="21" t="n">
-        <v>8.96574625150067</v>
-      </c>
-      <c r="P114" s="20" t="n">
-        <v>2.55014245014245</v>
+        <v>0</v>
+      </c>
+      <c r="P114" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q114" s="21" t="n">
-        <v>-9.82</v>
+        <v>-6.12</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S114" s="20" t="n">
-        <v>0.3315167177024359</v>
+        <v>0.4403975356846814</v>
       </c>
       <c r="T114" s="15" t="inlineStr">
         <is>
-          <t>Communication Systems (42%)</t>
+          <t>Annuities (60%)</t>
         </is>
       </c>
       <c r="U114" s="17" t="inlineStr">
         <is>
-          <t>Communication Systems 42%; Integrated Mission Systems 35%; Space And Airborne Sy</t>
+          <t>Annuities 60%; Runoff 21%; Life 19%</t>
         </is>
       </c>
       <c r="V114" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W114" s="17" t="inlineStr">
-        <is>
-          <t>US 90%; Non Us 10%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W114" s="17" t="n"/>
       <c r="X114" s="15" t="inlineStr">
         <is>
-          <t>Aerojet Rocketdyne +467%</t>
+          <t>Annuities +322%</t>
         </is>
       </c>
       <c r="Y114" s="21" t="n">
-        <v>258.65</v>
+        <v>-30.28</v>
       </c>
       <c r="Z114" s="20" t="n">
-        <v>0.8997000000000001</v>
-      </c>
-      <c r="AA114" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+        <v>-0.8806</v>
+      </c>
+      <c r="AA114" s="24" t="inlineStr"/>
     </row>
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n">
@@ -61570,12 +61554,12 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>BHF</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="C115" s="15" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc.</t>
+          <t>ONEOK, Inc.</t>
         </is>
       </c>
       <c r="D115" s="16" t="inlineStr">
@@ -61583,69 +61567,59 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E115" s="17" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+      <c r="E115" s="17" t="n"/>
       <c r="F115" s="18" t="n">
-        <v>2881904384</v>
+        <v>60906319872</v>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="H115" s="20" t="n">
+        <v>12.17</v>
       </c>
       <c r="I115" s="20" t="n">
-        <v>3.9738305</v>
+        <v>16.687393</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>0.4399589</v>
+        <v>2.655344</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>0.4215159</v>
+        <v>1.5471808</v>
       </c>
       <c r="L115" s="21" t="n">
-        <v>-18.66821130454271</v>
-      </c>
-      <c r="M115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.830758993916</v>
+      </c>
+      <c r="M115" s="21" t="n">
+        <v>4.39066236170035</v>
       </c>
       <c r="N115" s="21" t="n">
-        <v>0.007627959012433573</v>
+        <v>10.40228824506366</v>
       </c>
       <c r="O115" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>22.48324054084763</v>
+      </c>
+      <c r="P115" s="20" t="n">
+        <v>4.229943145925458</v>
       </c>
       <c r="Q115" s="21" t="n">
-        <v>-6.12</v>
+        <v>50.16</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S115" s="20" t="n">
-        <v>0.4403975356846814</v>
+        <v>0.4959061195541746</v>
       </c>
       <c r="T115" s="15" t="inlineStr">
         <is>
-          <t>Annuities (60%)</t>
+          <t>Refined Products And C (66%)</t>
         </is>
       </c>
       <c r="U115" s="17" t="inlineStr">
         <is>
-          <t>Annuities 60%; Runoff 21%; Life 19%</t>
+          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
         </is>
       </c>
       <c r="V115" s="18" t="n">
@@ -61654,14 +61628,18 @@
       <c r="W115" s="17" t="n"/>
       <c r="X115" s="15" t="inlineStr">
         <is>
-          <t>Annuities +322%</t>
-        </is>
-      </c>
-      <c r="Y115" s="21" t="n">
-        <v>-30.28</v>
-      </c>
-      <c r="Z115" s="20" t="n">
-        <v>-0.8806</v>
+          <t>Refined Products And +192%</t>
+        </is>
+      </c>
+      <c r="Y115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="Z115" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="AA115" s="24" t="inlineStr"/>
     </row>
@@ -61671,12 +61649,12 @@
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>HAPN</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>ONEOK, Inc.</t>
+          <t>Happen Inc. Common Stock</t>
         </is>
       </c>
       <c r="D116" s="16" t="inlineStr">
@@ -61684,9 +61662,13 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E116" s="17" t="n"/>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="F116" s="18" t="n">
-        <v>60906319872</v>
+        <v>1938845312</v>
       </c>
       <c r="G116" s="19" t="inlineStr">
         <is>
@@ -61694,49 +61676,57 @@
         </is>
       </c>
       <c r="H116" s="20" t="n">
-        <v>12.17</v>
+        <v>3.25</v>
       </c>
       <c r="I116" s="20" t="n">
-        <v>16.687393</v>
+        <v>13.36898003182167</v>
       </c>
       <c r="J116" s="20" t="n">
-        <v>2.655344</v>
+        <v>1.2369312</v>
       </c>
       <c r="K116" s="20" t="n">
-        <v>1.5471808</v>
-      </c>
-      <c r="L116" s="21" t="n">
-        <v>4.830758993916</v>
-      </c>
-      <c r="M116" s="21" t="n">
-        <v>4.39066236170035</v>
-      </c>
-      <c r="N116" s="21" t="n">
-        <v>10.40228824506366</v>
+        <v>3.208765663633625</v>
+      </c>
+      <c r="L116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="O116" s="21" t="n">
-        <v>22.48324054084763</v>
-      </c>
-      <c r="P116" s="20" t="n">
-        <v>4.229943145925458</v>
+        <v>52.58608552315825</v>
+      </c>
+      <c r="P116" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="Q116" s="21" t="n">
-        <v>50.16</v>
+        <v>2.07</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S116" s="20" t="n">
-        <v>0.4959061195541746</v>
+        <v>0.5010363171603962</v>
       </c>
       <c r="T116" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And C (66%)</t>
+          <t>Happen Bank (52%)</t>
         </is>
       </c>
       <c r="U116" s="17" t="inlineStr">
         <is>
-          <t>Refined Products And Crude Oil 66%; Natural Gas Gathering And Processing 22%; Wh</t>
+          <t>Happen Bank 52%; Happen Inc. 48%</t>
         </is>
       </c>
       <c r="V116" s="18" t="n">
@@ -61745,7 +61735,7 @@
       <c r="W116" s="17" t="n"/>
       <c r="X116" s="15" t="inlineStr">
         <is>
-          <t>Refined Products And +192%</t>
+          <t>Happen Bank +124%</t>
         </is>
       </c>
       <c r="Y116" s="22" t="inlineStr">
@@ -61766,43 +61756,51 @@
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>HAPN</t>
+          <t>VFS</t>
         </is>
       </c>
       <c r="C117" s="15" t="inlineStr">
         <is>
-          <t>Happen Inc. Common Stock</t>
+          <t>VinFast Auto Ltd. Ordinary Sha</t>
         </is>
       </c>
       <c r="D117" s="16" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discr</t>
         </is>
       </c>
       <c r="F117" s="18" t="n">
-        <v>1938845312</v>
+        <v>7509911040</v>
       </c>
       <c r="G117" s="19" t="inlineStr">
         <is>
           <t>UNRESEARCHED</t>
         </is>
       </c>
-      <c r="H117" s="20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I117" s="20" t="n">
-        <v>13.36898003182167</v>
-      </c>
-      <c r="J117" s="20" t="n">
-        <v>1.2369312</v>
-      </c>
-      <c r="K117" s="20" t="n">
-        <v>3.208765663633625</v>
+      <c r="H117" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I117" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J117" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K117" s="22" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="L117" s="22" t="inlineStr">
         <is>
@@ -61814,13 +61812,11 @@
           <t>–</t>
         </is>
       </c>
-      <c r="N117" s="22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="N117" s="21" t="n">
+        <v>78.31448357763071</v>
       </c>
       <c r="O117" s="21" t="n">
-        <v>52.58608552315825</v>
+        <v>-83.1176333196485</v>
       </c>
       <c r="P117" s="22" t="inlineStr">
         <is>
@@ -61828,31 +61824,35 @@
         </is>
       </c>
       <c r="Q117" s="21" t="n">
-        <v>2.07</v>
+        <v>-3.75</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S117" s="20" t="n">
-        <v>0.5010363171603962</v>
+        <v>0.460552269511968</v>
       </c>
       <c r="T117" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank (52%)</t>
+          <t>Car (48%)</t>
         </is>
       </c>
       <c r="U117" s="17" t="inlineStr">
         <is>
-          <t>Happen Bank 52%; Happen Inc. 48%</t>
+          <t>Car 48%; Car Segments 48%; E Scooter 3%</t>
         </is>
       </c>
       <c r="V117" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" s="17" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="W117" s="17" t="inlineStr">
+        <is>
+          <t>VN 89%; Asia Pacific 8%; US 2%</t>
+        </is>
+      </c>
       <c r="X117" s="15" t="inlineStr">
         <is>
-          <t>Happen Bank +124%</t>
+          <t>E Scooter +230%</t>
         </is>
       </c>
       <c r="Y117" s="22" t="inlineStr">
